--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="337">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -205,10 +205,10 @@
     <t>Supply the real product catalogue</t>
   </si>
   <si>
-    <t>50 of 61 products are invented placeholders. Only 11 products are real, and they carry no categories, images or descriptions.</t>
-  </si>
-  <si>
-    <t>Placeholders are flagged isPlaceholder and badged in the UI; removable in one query.</t>
+    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
+  </si>
+  <si>
+    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
   </si>
   <si>
     <t>DA-03</t>
@@ -229,10 +229,22 @@
     <t>Supply the real supplier list</t>
   </si>
   <si>
-    <t>All seven supplier names are invented. Only supplier IDs 20 and 21 are evidenced by the extraction.</t>
-  </si>
-  <si>
-    <t>Names are flagged isPlaceholder in the data.</t>
+    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
+  </si>
+  <si>
+    <t>All are flagged isPlaceholder in the data.</t>
+  </si>
+  <si>
+    <t>DA-17</t>
+  </si>
+  <si>
+    <t>Replace the test supplier attribution</t>
+  </si>
+  <si>
+    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
+  </si>
+  <si>
+    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
   </si>
   <si>
     <t>FN-01</t>
@@ -934,6 +946,18 @@
     <t>Outers are asserted to beat buying their contents separately.</t>
   </si>
   <si>
+    <t>DN-14</t>
+  </si>
+  <si>
+    <t>Control characters in generated code</t>
+  </si>
+  <si>
+    <t>Shell escaping wrote literal backspace bytes into regex rules, so every packaging and variant rule silently matched nothing while looking correct in every editor.</t>
+  </si>
+  <si>
+    <t>Found via od. A data check now asserts each variant selection matches an option.</t>
+  </si>
+  <si>
     <t>DN-07</t>
   </si>
   <si>
@@ -989,6 +1013,18 @@
   </si>
   <si>
     <t>Logo, favicon and all 11 category images are the brand own.</t>
+  </si>
+  <si>
+    <t>DN-13</t>
+  </si>
+  <si>
+    <t>Catalogue seeded with real products</t>
+  </si>
+  <si>
+    <t>Sixty real items replaced invented placeholders so the storefront can be judged against products that actually exist.</t>
+  </si>
+  <si>
+    <t>Thirty from each of two public supplier catalogues, spanning 23 categories.</t>
   </si>
 </sst>
 </file>
@@ -1497,7 +1533,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1505,7 +1541,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1513,7 +1549,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1539,7 +1575,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1573,7 +1609,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1623,7 +1659,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1681,7 +1717,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1984,7 +2020,7 @@
         <v>73</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>74</v>
@@ -1992,8 +2028,8 @@
       <c r="D12" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>15</v>
+      <c r="E12" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>34</v>
@@ -2042,7 +2078,7 @@
         <v>82</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>15</v>
@@ -2054,21 +2090,21 @@
         <v>35</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>15</v>
@@ -2080,7 +2116,7 @@
         <v>35</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2140,7 +2176,7 @@
         <v>95</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>96</v>
@@ -2174,8 +2210,8 @@
       <c r="D19" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>12</v>
+      <c r="E19" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>34</v>
@@ -2192,7 +2228,7 @@
         <v>103</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>104</v>
@@ -2236,21 +2272,21 @@
         <v>35</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>12</v>
@@ -2262,7 +2298,7 @@
         <v>35</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2270,7 +2306,7 @@
         <v>114</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>115</v>
@@ -2279,36 +2315,36 @@
         <v>116</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="E24" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>121</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>117</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>35</v>
@@ -2331,10 +2367,10 @@
         <v>125</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>35</v>
@@ -2357,10 +2393,10 @@
         <v>129</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>35</v>
@@ -2374,7 +2410,7 @@
         <v>131</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>132</v>
@@ -2382,11 +2418,11 @@
       <c r="D27" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>15</v>
+      <c r="E27" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>35</v>
@@ -2412,7 +2448,7 @@
         <v>15</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>35</v>
@@ -2438,7 +2474,7 @@
         <v>15</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>35</v>
@@ -2452,7 +2488,7 @@
         <v>143</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>144</v>
@@ -2460,11 +2496,11 @@
       <c r="D30" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>12</v>
+      <c r="E30" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>35</v>
@@ -2490,7 +2526,7 @@
         <v>12</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>35</v>
@@ -2516,7 +2552,7 @@
         <v>12</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>35</v>
@@ -2538,11 +2574,11 @@
       <c r="D33" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>14</v>
+      <c r="E33" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>35</v>
@@ -2564,11 +2600,11 @@
       <c r="D34" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>12</v>
+      <c r="E34" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>35</v>
@@ -2594,7 +2630,7 @@
         <v>12</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>35</v>
@@ -2620,7 +2656,7 @@
         <v>12</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>35</v>
@@ -2646,7 +2682,7 @@
         <v>12</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>35</v>
@@ -2660,7 +2696,7 @@
         <v>175</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>176</v>
@@ -2668,11 +2704,11 @@
       <c r="D38" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>15</v>
+      <c r="E38" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>35</v>
@@ -2698,7 +2734,7 @@
         <v>15</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>35</v>
@@ -2720,11 +2756,11 @@
       <c r="D40" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>12</v>
+      <c r="E40" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>35</v>
@@ -2738,7 +2774,7 @@
         <v>187</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>188</v>
@@ -2750,7 +2786,7 @@
         <v>12</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>35</v>
@@ -2772,43 +2808,43 @@
       <c r="D42" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>15</v>
+      <c r="E42" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>2</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>12</v>
+        <v>197</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>197</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2828,39 +2864,39 @@
         <v>12</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>2</v>
+        <v>201</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>14</v>
+        <v>204</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>204</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2876,63 +2912,63 @@
       <c r="D46" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="E46" s="7" t="s">
-        <v>12</v>
+      <c r="E46" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>2</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>211</v>
+        <v>12</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>212</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C48" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="E48" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="10" t="s">
         <v>215</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>35</v>
@@ -2946,7 +2982,7 @@
         <v>217</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>218</v>
@@ -2958,7 +2994,7 @@
         <v>12</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>35</v>
@@ -2984,7 +3020,7 @@
         <v>12</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>35</v>
@@ -3010,7 +3046,7 @@
         <v>12</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>35</v>
@@ -3036,7 +3072,7 @@
         <v>12</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>35</v>
@@ -3062,7 +3098,7 @@
         <v>12</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>35</v>
@@ -3076,7 +3112,7 @@
         <v>237</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>238</v>
@@ -3084,11 +3120,11 @@
       <c r="D54" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>15</v>
+      <c r="E54" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>35</v>
@@ -3102,7 +3138,7 @@
         <v>241</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>242</v>
@@ -3110,43 +3146,43 @@
       <c r="D55" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="E55" s="7" t="s">
-        <v>12</v>
+      <c r="E55" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>2</v>
+        <v>244</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>247</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3162,11 +3198,11 @@
       <c r="D57" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>15</v>
+      <c r="E57" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>35</v>
@@ -3188,11 +3224,11 @@
       <c r="D58" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="E58" s="7" t="s">
-        <v>12</v>
+      <c r="E58" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>35</v>
@@ -3206,7 +3242,7 @@
         <v>256</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>257</v>
@@ -3218,7 +3254,7 @@
         <v>12</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>35</v>
@@ -3227,8 +3263,34 @@
         <v>259</v>
       </c>
     </row>
+    <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H59"/>
+  <autoFilter ref="A1:H60"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3279,100 +3341,100 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>6</v>
@@ -3383,28 +3445,28 @@
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -3419,7 +3481,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3459,16 +3521,16 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
@@ -3477,24 +3539,24 @@
         <v>34</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>280</v>
-      </c>
       <c r="C3" s="6" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>15</v>
@@ -3503,24 +3565,24 @@
         <v>34</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
@@ -3529,24 +3591,24 @@
         <v>34</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
@@ -3555,24 +3617,24 @@
         <v>34</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>15</v>
@@ -3581,24 +3643,24 @@
         <v>34</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>15</v>
@@ -3607,24 +3669,24 @@
         <v>34</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>15</v>
@@ -3633,144 +3695,196 @@
         <v>34</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>117</v>
+      <c r="F9" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>271</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>320</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="341">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -217,10 +217,10 @@
     <t>Supply product photography</t>
   </si>
   <si>
-    <t>There is essentially no product imagery. listImage was null or a social-media icon; pdpImages led with a scraped JavaScript fragment.</t>
-  </si>
-  <si>
-    <t>Missing images currently render as a typographic tile. Only 2 usable photos exist in the whole extraction.</t>
+    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
+  </si>
+  <si>
+    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
   </si>
   <si>
     <t>DA-06</t>
@@ -1025,6 +1025,18 @@
   </si>
   <si>
     <t>Thirty from each of two public supplier catalogues, spanning 23 categories.</t>
+  </si>
+  <si>
+    <t>DN-15</t>
+  </si>
+  <si>
+    <t>Product images added for testing</t>
+  </si>
+  <si>
+    <t>Fifty-two of 71 products now carry real photography so the layout can be judged with images rather than placeholder tiles.</t>
+  </si>
+  <si>
+    <t>Third-party supplier images in public/products/seed. A data check now asserts every referenced image file exists on disk.</t>
   </si>
 </sst>
 </file>
@@ -1533,7 +1545,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1549,7 +1561,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3481,7 +3493,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3883,8 +3895,34 @@
         <v>336</v>
       </c>
     </row>
+    <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H15"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="354">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -172,7 +172,10 @@
     <t>Express and Prisma per extraction/BACKEND_SPEC.md: roles, auth, orders, invoices, emails. Eight phases.</t>
   </si>
   <si>
-    <t>/api/v1 already defines the contract it must satisfy.</t>
+    <t>In progress</t>
+  </si>
+  <si>
+    <t>Phase 1 started. Schema designed and migrated: 30 tables, 19 unique constraints. Application code not started.</t>
   </si>
   <si>
     <t>BE-02</t>
@@ -199,6 +202,18 @@
     <t>Approval is an admin-only transition enforced in the service layer.</t>
   </si>
   <si>
+    <t>BE-07</t>
+  </si>
+  <si>
+    <t>Seed the database from the catalogue</t>
+  </si>
+  <si>
+    <t>The schema exists but is empty. Categories, products, SKUs and suppliers need loading from src/data/catalog.json so the app can run against the database.</t>
+  </si>
+  <si>
+    <t>Next step after the schema.</t>
+  </si>
+  <si>
     <t>DA-01</t>
   </si>
   <si>
@@ -457,6 +472,18 @@
     <t>Specified in the backend spec.</t>
   </si>
   <si>
+    <t>BE-08</t>
+  </si>
+  <si>
+    <t>Decide money representation before any data lands</t>
+  </si>
+  <si>
+    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
+  </si>
+  <si>
+    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
+  </si>
+  <si>
     <t>DA-02</t>
   </si>
   <si>
@@ -956,6 +983,18 @@
   </si>
   <si>
     <t>Found via od. A data check now asserts each variant selection matches an option.</t>
+  </si>
+  <si>
+    <t>DN-16</t>
+  </si>
+  <si>
+    <t>Database schema designed and migrated</t>
+  </si>
+  <si>
+    <t>Thirty tables covering catalogue, packs as SKUs, variants, attributes, documents, batches, orders, per-supplier invoices, quotes, bulk upload and audit.</t>
+  </si>
+  <si>
+    <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
   </si>
   <si>
     <t>DN-07</t>
@@ -1545,7 +1584,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1553,7 +1592,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1561,7 +1600,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1587,7 +1626,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1595,7 +1634,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1629,7 +1668,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1645,7 +1684,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1695,7 +1734,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1729,7 +1768,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1891,24 +1930,24 @@
         <v>34</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>15</v>
@@ -1920,21 +1959,21 @@
         <v>35</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>15</v>
@@ -1946,24 +1985,24 @@
         <v>35</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -1972,21 +2011,21 @@
         <v>35</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>12</v>
@@ -1998,21 +2037,21 @@
         <v>35</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>12</v>
@@ -2024,21 +2063,21 @@
         <v>35</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>12</v>
@@ -2050,24 +2089,24 @@
         <v>35</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>15</v>
+        <v>80</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -2076,21 +2115,21 @@
         <v>35</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>15</v>
@@ -2102,21 +2141,21 @@
         <v>35</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>15</v>
@@ -2128,21 +2167,21 @@
         <v>35</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>15</v>
@@ -2154,21 +2193,21 @@
         <v>35</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>15</v>
@@ -2180,21 +2219,21 @@
         <v>35</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>15</v>
@@ -2206,21 +2245,21 @@
         <v>35</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>15</v>
@@ -2232,24 +2271,24 @@
         <v>35</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>12</v>
+        <v>106</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>34</v>
@@ -2258,21 +2297,21 @@
         <v>35</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>12</v>
@@ -2284,21 +2323,21 @@
         <v>35</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>12</v>
@@ -2310,21 +2349,21 @@
         <v>35</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>12</v>
@@ -2336,27 +2375,27 @@
         <v>35</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>121</v>
+        <v>12</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>35</v>
@@ -2379,530 +2418,530 @@
         <v>125</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>15</v>
+        <v>138</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>12</v>
+        <v>150</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>14</v>
+        <v>162</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>12</v>
+        <v>170</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>15</v>
+        <v>182</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>15</v>
+        <v>186</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>12</v>
+        <v>190</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>12</v>
+        <v>194</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>15</v>
+        <v>198</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>2</v>
+        <v>199</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>12</v>
+        <v>206</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>35</v>
@@ -2913,48 +2952,48 @@
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>14</v>
+        <v>209</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>35</v>
@@ -2965,54 +3004,54 @@
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>215</v>
+      <c r="F49" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>220</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3020,7 +3059,7 @@
         <v>221</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>222</v>
@@ -3029,280 +3068,332 @@
         <v>223</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>15</v>
+        <v>244</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>2</v>
+        <v>249</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>12</v>
+        <v>252</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>15</v>
+        <v>256</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>255</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B60" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E60" s="7" t="s">
+      <c r="C62" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="E62" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F60" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>263</v>
+      <c r="F62" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H60"/>
+  <autoFilter ref="A1:H62"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3353,100 +3444,100 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>6</v>
@@ -3457,28 +3548,28 @@
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -3493,7 +3584,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3533,16 +3624,16 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
@@ -3551,24 +3642,24 @@
         <v>34</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>15</v>
@@ -3577,24 +3668,24 @@
         <v>34</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
@@ -3603,24 +3694,24 @@
         <v>34</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
@@ -3629,24 +3720,24 @@
         <v>34</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>15</v>
@@ -3655,24 +3746,24 @@
         <v>34</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>15</v>
@@ -3681,24 +3772,24 @@
         <v>34</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>15</v>
@@ -3707,24 +3798,24 @@
         <v>34</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>15</v>
@@ -3733,196 +3824,222 @@
         <v>34</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>121</v>
+      <c r="F10" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>275</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G13" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>340</v>
+        <v>349</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="358">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -202,700 +202,712 @@
     <t>Approval is an admin-only transition enforced in the service layer.</t>
   </si>
   <si>
+    <t>BE-09</t>
+  </si>
+  <si>
+    <t>Point the storefront at the database</t>
+  </si>
+  <si>
+    <t>The site still reads catalog.json. The API layer needs to read Prisma instead, which is the swap the data-access seam was built for.</t>
+  </si>
+  <si>
+    <t>Only src/lib/catalog.ts should need to change.</t>
+  </si>
+  <si>
+    <t>DA-01</t>
+  </si>
+  <si>
+    <t>Supply the real product catalogue</t>
+  </si>
+  <si>
+    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
+  </si>
+  <si>
+    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
+  </si>
+  <si>
+    <t>DA-03</t>
+  </si>
+  <si>
+    <t>Supply product photography</t>
+  </si>
+  <si>
+    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
+  </si>
+  <si>
+    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
+  </si>
+  <si>
+    <t>DA-06</t>
+  </si>
+  <si>
+    <t>Supply the real supplier list</t>
+  </si>
+  <si>
+    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
+  </si>
+  <si>
+    <t>All are flagged isPlaceholder in the data.</t>
+  </si>
+  <si>
+    <t>DA-17</t>
+  </si>
+  <si>
+    <t>Replace the test supplier attribution</t>
+  </si>
+  <si>
+    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
+  </si>
+  <si>
+    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
+  </si>
+  <si>
+    <t>FN-01</t>
+  </si>
+  <si>
+    <t>Checkout does not submit an order</t>
+  </si>
+  <si>
+    <t>The form is complete and the flow is reviewable, but nothing is created and no payment is taken. A preview reference number is generated in the browser.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend. States this on screen.</t>
+  </si>
+  <si>
+    <t>FN-02</t>
+  </si>
+  <si>
+    <t>Quote requests are not delivered</t>
+  </si>
+  <si>
+    <t>Captured in the browser only.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend and an email provider.</t>
+  </si>
+  <si>
+    <t>FN-03</t>
+  </si>
+  <si>
+    <t>Bulk buy enquiries are not delivered</t>
+  </si>
+  <si>
+    <t>FN-04</t>
+  </si>
+  <si>
+    <t>Notify Me does not register a subscription</t>
+  </si>
+  <si>
+    <t>Captured locally. The restock email flow does not exist.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend.</t>
+  </si>
+  <si>
+    <t>FN-05</t>
+  </si>
+  <si>
+    <t>Sign-in is a demo flag</t>
+  </si>
+  <si>
+    <t>A localStorage boolean opens a fabricated session. Real auth is email OTP per the backend spec.</t>
+  </si>
+  <si>
+    <t>Must be replaced wholesale rather than extended.</t>
+  </si>
+  <si>
+    <t>FN-06</t>
+  </si>
+  <si>
+    <t>Account history is fabricated</t>
+  </si>
+  <si>
+    <t>The customer, three orders and their invoices are invented so the account screens could be built and reviewed.</t>
+  </si>
+  <si>
+    <t>Every account page carries a visible notice.</t>
+  </si>
+  <si>
+    <t>IN-06</t>
+  </si>
+  <si>
+    <t>Remove noindex before launch</t>
+  </si>
+  <si>
+    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
+  </si>
+  <si>
+    <t>Must be removed deliberately at launch — and only then.</t>
+  </si>
+  <si>
+    <t>IN-07</t>
+  </si>
+  <si>
+    <t>Confirm the GitHub repository is private</t>
+  </si>
+  <si>
+    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
+  </si>
+  <si>
+    <t>https://github.com/musawi1989/aussiemed</t>
+  </si>
+  <si>
+    <t>LG-01</t>
+  </si>
+  <si>
+    <t>Supply terms and conditions</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
+  </si>
+  <si>
+    <t>Page exists and says so on screen.</t>
+  </si>
+  <si>
+    <t>LG-02</t>
+  </si>
+  <si>
+    <t>Supply the privacy policy</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
+  </si>
+  <si>
+    <t>LG-03</t>
+  </si>
+  <si>
+    <t>Confirm the contact email address</t>
+  </si>
+  <si>
+    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
+  </si>
+  <si>
+    <t>Also determines the sending domain for transactional email.</t>
+  </si>
+  <si>
+    <t>AC-05</t>
+  </si>
+  <si>
+    <t>Confirm the VAT rate and whether it must be configurable</t>
+  </si>
+  <si>
+    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Rate must be stored on the order at the time it is placed.</t>
+  </si>
+  <si>
+    <t>AC-06</t>
+  </si>
+  <si>
+    <t>Approve the reference number format</t>
+  </si>
+  <si>
+    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
+  </si>
+  <si>
+    <t>Wording is fixed as Reference number, never order number.</t>
+  </si>
+  <si>
+    <t>AC-07</t>
+  </si>
+  <si>
+    <t>Approve the supplier invoice numbering</t>
+  </si>
+  <si>
+    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
+  </si>
+  <si>
+    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
+  </si>
+  <si>
+    <t>AC-09</t>
+  </si>
+  <si>
+    <t>Decide payment terms and credit accounts</t>
+  </si>
+  <si>
+    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
+  </si>
+  <si>
+    <t>Affects the schema — decide before the backend.</t>
+  </si>
+  <si>
+    <t>BE-04</t>
+  </si>
+  <si>
+    <t>Build comma-safe .xlsx bulk upload</t>
+  </si>
+  <si>
+    <t>Parsed natively with exceljs, never by splitting on commas — that is what broke comma-containing category names.</t>
+  </si>
+  <si>
+    <t>Unknown brands must be reported per row, never skipped silently.</t>
+  </si>
+  <si>
+    <t>BE-05</t>
+  </si>
+  <si>
+    <t>Build the email flows</t>
+  </si>
+  <si>
+    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
+  </si>
+  <si>
+    <t>Needs an SMTP provider.</t>
+  </si>
+  <si>
+    <t>BE-06</t>
+  </si>
+  <si>
+    <t>Add an audit log</t>
+  </si>
+  <si>
+    <t>Every status transition and every admin or supplier write should be recorded.</t>
+  </si>
+  <si>
+    <t>Specified in the backend spec.</t>
+  </si>
+  <si>
+    <t>BE-08</t>
+  </si>
+  <si>
+    <t>Decide money representation before any data lands</t>
+  </si>
+  <si>
+    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
+  </si>
+  <si>
+    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
+  </si>
+  <si>
+    <t>DA-02</t>
+  </si>
+  <si>
+    <t>Verify the product-to-category mapping</t>
+  </si>
+  <si>
+    <t>The extraction had no product-category link at all. All 11 real products were mapped by hand from their names.</t>
+  </si>
+  <si>
+    <t>146 categories exist; the mapping is ours and unverified.</t>
+  </si>
+  <si>
+    <t>DA-05</t>
+  </si>
+  <si>
+    <t>Approve the product descriptions</t>
+  </si>
+  <si>
+    <t>The source had no descriptions. Eleven were written from the product names and need approval before launch.</t>
+  </si>
+  <si>
+    <t>Placeholder products carry generated filler text.</t>
+  </si>
+  <si>
+    <t>DA-07</t>
+  </si>
+  <si>
+    <t>Supply the hero banner image</t>
+  </si>
+  <si>
+    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured — only Brand, Category, Product and WebHtml folders were mirrored.</t>
+  </si>
+  <si>
+    <t>A genuine AussieMed CMS image stands in.</t>
+  </si>
+  <si>
+    <t>DA-08</t>
+  </si>
+  <si>
+    <t>Obtain Gilroy Regular and Medium</t>
+  </si>
+  <si>
+    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
+  </si>
+  <si>
+    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
+  </si>
+  <si>
+    <t>DA-10</t>
+  </si>
+  <si>
+    <t>Supply real pack and carton structures</t>
+  </si>
+  <si>
+    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
+  </si>
+  <si>
+    <t>Pack is the purchasable unit; getting it wrong misprices every carton.</t>
+  </si>
+  <si>
+    <t>DA-11</t>
+  </si>
+  <si>
+    <t>Supply real variant data</t>
+  </si>
+  <si>
+    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
+  </si>
+  <si>
+    <t>Variant switching is not wired until sibling SKUs exist.</t>
+  </si>
+  <si>
+    <t>DA-12</t>
+  </si>
+  <si>
+    <t>Supply real product specifications</t>
+  </si>
+  <si>
+    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
+  </si>
+  <si>
+    <t>These become search filters later.</t>
+  </si>
+  <si>
+    <t>DA-13</t>
+  </si>
+  <si>
+    <t>Supply safety data sheets and spec sheets</t>
+  </si>
+  <si>
+    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
+  </si>
+  <si>
+    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
+  </si>
+  <si>
+    <t>FN-07</t>
+  </si>
+  <si>
+    <t>Variant switching is not wired</t>
+  </si>
+  <si>
+    <t>Size and colour chips display the current value; other options are disabled because sibling SKUs do not exist yet.</t>
+  </si>
+  <si>
+    <t>Needs the variant model in the database.</t>
+  </si>
+  <si>
+    <t>FN-08</t>
+  </si>
+  <si>
+    <t>Stock is a boolean</t>
+  </si>
+  <si>
+    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
+  </si>
+  <si>
+    <t>Decide whether real stock levels are needed.</t>
+  </si>
+  <si>
+    <t>FN-09</t>
+  </si>
+  <si>
+    <t>Decide on expiry and short-dated stock</t>
+  </si>
+  <si>
+    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
+  </si>
+  <si>
+    <t>Schema-shaping — decide before the backend is built.</t>
+  </si>
+  <si>
+    <t>IN-01</t>
+  </si>
+  <si>
+    <t>Choose a hosting target</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. The site runs locally only.</t>
+  </si>
+  <si>
+    <t>Deliberately deferred until the build is approved.</t>
+  </si>
+  <si>
+    <t>IN-02</t>
+  </si>
+  <si>
+    <t>Choose the database</t>
+  </si>
+  <si>
+    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
+  </si>
+  <si>
+    <t>IN-03</t>
+  </si>
+  <si>
+    <t>Choose an SMTP provider and sending domain</t>
+  </si>
+  <si>
+    <t>Required for every transactional email.</t>
+  </si>
+  <si>
+    <t>Must not be the misspelled assuiemed.com domain.</t>
+  </si>
+  <si>
+    <t>IN-04</t>
+  </si>
+  <si>
+    <t>Decide on a payment gateway</t>
+  </si>
+  <si>
+    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
+  </si>
+  <si>
+    <t>LG-05</t>
+  </si>
+  <si>
+    <t>Transfer the theme licence</t>
+  </si>
+  <si>
+    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
+  </si>
+  <si>
+    <t>Repository must stay private because of this.</t>
+  </si>
+  <si>
+    <t>LG-06</t>
+  </si>
+  <si>
+    <t>Supply company registration details</t>
+  </si>
+  <si>
+    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
+  </si>
+  <si>
+    <t>AC-08</t>
+  </si>
+  <si>
+    <t>Confirm the rounding policy</t>
+  </si>
+  <si>
+    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Verified by test; needs sign-off that the method is acceptable.</t>
+  </si>
+  <si>
+    <t>AC-10</t>
+  </si>
+  <si>
+    <t>Confirm the default price display</t>
+  </si>
+  <si>
+    <t>Prices default to Ex. VAT with a toggle to Inc. VAT.</t>
+  </si>
+  <si>
+    <t>Preference persists per browser.</t>
+  </si>
+  <si>
+    <t>DA-04</t>
+  </si>
+  <si>
+    <t>Wrong image on the scrub top</t>
+  </si>
+  <si>
+    <t>The product's primary image was a stock photo of a pocket watch. Excluded from the build; the file is still in public/products/.</t>
+  </si>
+  <si>
+    <t>Suggests image uploads were not being checked in the old admin.</t>
+  </si>
+  <si>
+    <t>DA-09</t>
+  </si>
+  <si>
+    <t>Explain the disappearing product</t>
+  </si>
+  <si>
+    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
+  </si>
+  <si>
+    <t>Evidence of a real defect in the old platform. Worth understanding before trusting any migrated data.</t>
+  </si>
+  <si>
+    <t>DA-14</t>
+  </si>
+  <si>
+    <t>Confirm the brand list</t>
+  </si>
+  <si>
+    <t>Brands were assigned by reading product names.</t>
+  </si>
+  <si>
+    <t>Eleven real brands identified.</t>
+  </si>
+  <si>
+    <t>DA-15</t>
+  </si>
+  <si>
+    <t>Decide on duplicate categories</t>
+  </si>
+  <si>
+    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
+  </si>
+  <si>
+    <t>Affected: Respiratory Management, Oral Care, Monitoring &amp; Testing, Dispensers, Bags, Medicine.</t>
+  </si>
+  <si>
+    <t>DA-16</t>
+  </si>
+  <si>
+    <t>Confirm the missing department</t>
+  </si>
+  <si>
+    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
+  </si>
+  <si>
+    <t>Confirm this is intentional rather than lost.</t>
+  </si>
+  <si>
+    <t>FN-10</t>
+  </si>
+  <si>
+    <t>Search is client-side only</t>
+  </si>
+  <si>
+    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
+  </si>
+  <si>
+    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
+  </si>
+  <si>
+    <t>IN-05</t>
+  </si>
+  <si>
+    <t>Supply Google and Facebook OAuth keys</t>
+  </si>
+  <si>
+    <t>Social login endpoints currently return 501.</t>
+  </si>
+  <si>
+    <t>IN-08</t>
+  </si>
+  <si>
+    <t>Correct the git author name</t>
+  </si>
+  <si>
+    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
+  </si>
+  <si>
+    <t>Fixable with git config user.name and an amend.</t>
+  </si>
+  <si>
+    <t>IN-09</t>
+  </si>
+  <si>
+    <t>Set up continuous integration</t>
+  </si>
+  <si>
+    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
+  </si>
+  <si>
+    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
+  </si>
+  <si>
+    <t>IN-10</t>
+  </si>
+  <si>
+    <t>Plan backups and disaster recovery</t>
+  </si>
+  <si>
+    <t>No backup strategy exists for the database or uploaded files.</t>
+  </si>
+  <si>
+    <t>Relevant once there is a real database.</t>
+  </si>
+  <si>
+    <t>LG-04</t>
+  </si>
+  <si>
+    <t>Approve the About / Contact / Order Support copy</t>
+  </si>
+  <si>
+    <t>All placeholder text.</t>
+  </si>
+  <si>
+    <t>Pages carry a visible placeholder notice.</t>
+  </si>
+  <si>
+    <t>DF-01</t>
+  </si>
+  <si>
+    <t>Industry taxonomy</t>
+  </si>
+  <si>
+    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
+  </si>
+  <si>
+    <t>Additive; adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-02</t>
+  </si>
+  <si>
+    <t>Subscribe and Save</t>
+  </si>
+  <si>
+    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
+  </si>
+  <si>
+    <t>Needs the backend.</t>
+  </si>
+  <si>
+    <t>DF-03</t>
+  </si>
+  <si>
+    <t>Frequently bought together</t>
+  </si>
+  <si>
+    <t>Bundle suggestion with a combined total and one action to add all.</t>
+  </si>
+  <si>
+    <t>Adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-04</t>
+  </si>
+  <si>
+    <t>Quick view</t>
+  </si>
+  <si>
+    <t>View a product from the listing without a page load.</t>
+  </si>
+  <si>
+    <t>DF-05</t>
+  </si>
+  <si>
+    <t>Downloadable PDF catalogues</t>
+  </si>
+  <si>
+    <t>Still how a lot of trade buying happens.</t>
+  </si>
+  <si>
+    <t>Needs the actual catalogue files.</t>
+  </si>
+  <si>
     <t>BE-07</t>
   </si>
   <si>
     <t>Seed the database from the catalogue</t>
   </si>
   <si>
-    <t>The schema exists but is empty. Categories, products, SKUs and suppliers need loading from src/data/catalog.json so the app can run against the database.</t>
-  </si>
-  <si>
-    <t>Next step after the schema.</t>
-  </si>
-  <si>
-    <t>DA-01</t>
-  </si>
-  <si>
-    <t>Supply the real product catalogue</t>
-  </si>
-  <si>
-    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
-  </si>
-  <si>
-    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
-  </si>
-  <si>
-    <t>DA-03</t>
-  </si>
-  <si>
-    <t>Supply product photography</t>
-  </si>
-  <si>
-    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
-  </si>
-  <si>
-    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
-  </si>
-  <si>
-    <t>DA-06</t>
-  </si>
-  <si>
-    <t>Supply the real supplier list</t>
-  </si>
-  <si>
-    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
-  </si>
-  <si>
-    <t>All are flagged isPlaceholder in the data.</t>
-  </si>
-  <si>
-    <t>DA-17</t>
-  </si>
-  <si>
-    <t>Replace the test supplier attribution</t>
-  </si>
-  <si>
-    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
-  </si>
-  <si>
-    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
-  </si>
-  <si>
-    <t>FN-01</t>
-  </si>
-  <si>
-    <t>Checkout does not submit an order</t>
-  </si>
-  <si>
-    <t>The form is complete and the flow is reviewable, but nothing is created and no payment is taken. A preview reference number is generated in the browser.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend. States this on screen.</t>
-  </si>
-  <si>
-    <t>FN-02</t>
-  </si>
-  <si>
-    <t>Quote requests are not delivered</t>
-  </si>
-  <si>
-    <t>Captured in the browser only.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend and an email provider.</t>
-  </si>
-  <si>
-    <t>FN-03</t>
-  </si>
-  <si>
-    <t>Bulk buy enquiries are not delivered</t>
-  </si>
-  <si>
-    <t>FN-04</t>
-  </si>
-  <si>
-    <t>Notify Me does not register a subscription</t>
-  </si>
-  <si>
-    <t>Captured locally. The restock email flow does not exist.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend.</t>
-  </si>
-  <si>
-    <t>FN-05</t>
-  </si>
-  <si>
-    <t>Sign-in is a demo flag</t>
-  </si>
-  <si>
-    <t>A localStorage boolean opens a fabricated session. Real auth is email OTP per the backend spec.</t>
-  </si>
-  <si>
-    <t>Must be replaced wholesale rather than extended.</t>
-  </si>
-  <si>
-    <t>FN-06</t>
-  </si>
-  <si>
-    <t>Account history is fabricated</t>
-  </si>
-  <si>
-    <t>The customer, three orders and their invoices are invented so the account screens could be built and reviewed.</t>
-  </si>
-  <si>
-    <t>Every account page carries a visible notice.</t>
-  </si>
-  <si>
-    <t>IN-06</t>
-  </si>
-  <si>
-    <t>Remove noindex before launch</t>
-  </si>
-  <si>
-    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
-  </si>
-  <si>
-    <t>Must be removed deliberately at launch — and only then.</t>
-  </si>
-  <si>
-    <t>IN-07</t>
-  </si>
-  <si>
-    <t>Confirm the GitHub repository is private</t>
-  </si>
-  <si>
-    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
-  </si>
-  <si>
-    <t>https://github.com/musawi1989/aussiemed</t>
-  </si>
-  <si>
-    <t>LG-01</t>
-  </si>
-  <si>
-    <t>Supply terms and conditions</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
-  </si>
-  <si>
-    <t>Page exists and says so on screen.</t>
-  </si>
-  <si>
-    <t>LG-02</t>
-  </si>
-  <si>
-    <t>Supply the privacy policy</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
-  </si>
-  <si>
-    <t>LG-03</t>
-  </si>
-  <si>
-    <t>Confirm the contact email address</t>
-  </si>
-  <si>
-    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
-  </si>
-  <si>
-    <t>Also determines the sending domain for transactional email.</t>
-  </si>
-  <si>
-    <t>AC-05</t>
-  </si>
-  <si>
-    <t>Confirm the VAT rate and whether it must be configurable</t>
-  </si>
-  <si>
-    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>Rate must be stored on the order at the time it is placed.</t>
-  </si>
-  <si>
-    <t>AC-06</t>
-  </si>
-  <si>
-    <t>Approve the reference number format</t>
-  </si>
-  <si>
-    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
-  </si>
-  <si>
-    <t>Wording is fixed as Reference number, never order number.</t>
-  </si>
-  <si>
-    <t>AC-07</t>
-  </si>
-  <si>
-    <t>Approve the supplier invoice numbering</t>
-  </si>
-  <si>
-    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
-  </si>
-  <si>
-    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
-  </si>
-  <si>
-    <t>AC-09</t>
-  </si>
-  <si>
-    <t>Decide payment terms and credit accounts</t>
-  </si>
-  <si>
-    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
-  </si>
-  <si>
-    <t>Affects the schema — decide before the backend.</t>
-  </si>
-  <si>
-    <t>BE-04</t>
-  </si>
-  <si>
-    <t>Build comma-safe .xlsx bulk upload</t>
-  </si>
-  <si>
-    <t>Parsed natively with exceljs, never by splitting on commas — that is what broke comma-containing category names.</t>
-  </si>
-  <si>
-    <t>Unknown brands must be reported per row, never skipped silently.</t>
-  </si>
-  <si>
-    <t>BE-05</t>
-  </si>
-  <si>
-    <t>Build the email flows</t>
-  </si>
-  <si>
-    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
-  </si>
-  <si>
-    <t>Needs an SMTP provider.</t>
-  </si>
-  <si>
-    <t>BE-06</t>
-  </si>
-  <si>
-    <t>Add an audit log</t>
-  </si>
-  <si>
-    <t>Every status transition and every admin or supplier write should be recorded.</t>
-  </si>
-  <si>
-    <t>Specified in the backend spec.</t>
-  </si>
-  <si>
-    <t>BE-08</t>
-  </si>
-  <si>
-    <t>Decide money representation before any data lands</t>
-  </si>
-  <si>
-    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
-  </si>
-  <si>
-    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
-  </si>
-  <si>
-    <t>DA-02</t>
-  </si>
-  <si>
-    <t>Verify the product-to-category mapping</t>
-  </si>
-  <si>
-    <t>The extraction had no product-category link at all. All 11 real products were mapped by hand from their names.</t>
-  </si>
-  <si>
-    <t>146 categories exist; the mapping is ours and unverified.</t>
-  </si>
-  <si>
-    <t>DA-05</t>
-  </si>
-  <si>
-    <t>Approve the product descriptions</t>
-  </si>
-  <si>
-    <t>The source had no descriptions. Eleven were written from the product names and need approval before launch.</t>
-  </si>
-  <si>
-    <t>Placeholder products carry generated filler text.</t>
-  </si>
-  <si>
-    <t>DA-07</t>
-  </si>
-  <si>
-    <t>Supply the hero banner image</t>
-  </si>
-  <si>
-    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured — only Brand, Category, Product and WebHtml folders were mirrored.</t>
-  </si>
-  <si>
-    <t>A genuine AussieMed CMS image stands in.</t>
-  </si>
-  <si>
-    <t>DA-08</t>
-  </si>
-  <si>
-    <t>Obtain Gilroy Regular and Medium</t>
-  </si>
-  <si>
-    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
-  </si>
-  <si>
-    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
-  </si>
-  <si>
-    <t>DA-10</t>
-  </si>
-  <si>
-    <t>Supply real pack and carton structures</t>
-  </si>
-  <si>
-    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
-  </si>
-  <si>
-    <t>Pack is the purchasable unit; getting it wrong misprices every carton.</t>
-  </si>
-  <si>
-    <t>DA-11</t>
-  </si>
-  <si>
-    <t>Supply real variant data</t>
-  </si>
-  <si>
-    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
-  </si>
-  <si>
-    <t>Variant switching is not wired until sibling SKUs exist.</t>
-  </si>
-  <si>
-    <t>DA-12</t>
-  </si>
-  <si>
-    <t>Supply real product specifications</t>
-  </si>
-  <si>
-    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
-  </si>
-  <si>
-    <t>These become search filters later.</t>
-  </si>
-  <si>
-    <t>DA-13</t>
-  </si>
-  <si>
-    <t>Supply safety data sheets and spec sheets</t>
-  </si>
-  <si>
-    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
-  </si>
-  <si>
-    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
-  </si>
-  <si>
-    <t>FN-07</t>
-  </si>
-  <si>
-    <t>Variant switching is not wired</t>
-  </si>
-  <si>
-    <t>Size and colour chips display the current value; other options are disabled because sibling SKUs do not exist yet.</t>
-  </si>
-  <si>
-    <t>Needs the variant model in the database.</t>
-  </si>
-  <si>
-    <t>FN-08</t>
-  </si>
-  <si>
-    <t>Stock is a boolean</t>
-  </si>
-  <si>
-    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
-  </si>
-  <si>
-    <t>Decide whether real stock levels are needed.</t>
-  </si>
-  <si>
-    <t>FN-09</t>
-  </si>
-  <si>
-    <t>Decide on expiry and short-dated stock</t>
-  </si>
-  <si>
-    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
-  </si>
-  <si>
-    <t>Schema-shaping — decide before the backend is built.</t>
-  </si>
-  <si>
-    <t>IN-01</t>
-  </si>
-  <si>
-    <t>Choose a hosting target</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. The site runs locally only.</t>
-  </si>
-  <si>
-    <t>Deliberately deferred until the build is approved.</t>
-  </si>
-  <si>
-    <t>IN-02</t>
-  </si>
-  <si>
-    <t>Choose the database</t>
-  </si>
-  <si>
-    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
-  </si>
-  <si>
-    <t>IN-03</t>
-  </si>
-  <si>
-    <t>Choose an SMTP provider and sending domain</t>
-  </si>
-  <si>
-    <t>Required for every transactional email.</t>
-  </si>
-  <si>
-    <t>Must not be the misspelled assuiemed.com domain.</t>
-  </si>
-  <si>
-    <t>IN-04</t>
-  </si>
-  <si>
-    <t>Decide on a payment gateway</t>
-  </si>
-  <si>
-    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
-  </si>
-  <si>
-    <t>LG-05</t>
-  </si>
-  <si>
-    <t>Transfer the theme licence</t>
-  </si>
-  <si>
-    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
-  </si>
-  <si>
-    <t>Repository must stay private because of this.</t>
-  </si>
-  <si>
-    <t>LG-06</t>
-  </si>
-  <si>
-    <t>Supply company registration details</t>
-  </si>
-  <si>
-    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
-  </si>
-  <si>
-    <t>AC-08</t>
-  </si>
-  <si>
-    <t>Confirm the rounding policy</t>
-  </si>
-  <si>
-    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>Verified by test; needs sign-off that the method is acceptable.</t>
-  </si>
-  <si>
-    <t>AC-10</t>
-  </si>
-  <si>
-    <t>Confirm the default price display</t>
-  </si>
-  <si>
-    <t>Prices default to Ex. VAT with a toggle to Inc. VAT.</t>
-  </si>
-  <si>
-    <t>Preference persists per browser.</t>
-  </si>
-  <si>
-    <t>DA-04</t>
-  </si>
-  <si>
-    <t>Wrong image on the scrub top</t>
-  </si>
-  <si>
-    <t>The product's primary image was a stock photo of a pocket watch. Excluded from the build; the file is still in public/products/.</t>
-  </si>
-  <si>
-    <t>Suggests image uploads were not being checked in the old admin.</t>
-  </si>
-  <si>
-    <t>DA-09</t>
-  </si>
-  <si>
-    <t>Explain the disappearing product</t>
-  </si>
-  <si>
-    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
-  </si>
-  <si>
-    <t>Evidence of a real defect in the old platform. Worth understanding before trusting any migrated data.</t>
-  </si>
-  <si>
-    <t>DA-14</t>
-  </si>
-  <si>
-    <t>Confirm the brand list</t>
-  </si>
-  <si>
-    <t>Brands were assigned by reading product names.</t>
-  </si>
-  <si>
-    <t>Eleven real brands identified.</t>
-  </si>
-  <si>
-    <t>DA-15</t>
-  </si>
-  <si>
-    <t>Decide on duplicate categories</t>
-  </si>
-  <si>
-    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
-  </si>
-  <si>
-    <t>Affected: Respiratory Management, Oral Care, Monitoring &amp; Testing, Dispensers, Bags, Medicine.</t>
-  </si>
-  <si>
-    <t>DA-16</t>
-  </si>
-  <si>
-    <t>Confirm the missing department</t>
-  </si>
-  <si>
-    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
-  </si>
-  <si>
-    <t>Confirm this is intentional rather than lost.</t>
-  </si>
-  <si>
-    <t>FN-10</t>
-  </si>
-  <si>
-    <t>Search is client-side only</t>
-  </si>
-  <si>
-    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
-  </si>
-  <si>
-    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
-  </si>
-  <si>
-    <t>IN-05</t>
-  </si>
-  <si>
-    <t>Supply Google and Facebook OAuth keys</t>
-  </si>
-  <si>
-    <t>Social login endpoints currently return 501.</t>
-  </si>
-  <si>
-    <t>IN-08</t>
-  </si>
-  <si>
-    <t>Correct the git author name</t>
-  </si>
-  <si>
-    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
-  </si>
-  <si>
-    <t>Fixable with git config user.name and an amend.</t>
-  </si>
-  <si>
-    <t>IN-09</t>
-  </si>
-  <si>
-    <t>Set up continuous integration</t>
-  </si>
-  <si>
-    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
-  </si>
-  <si>
-    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
-  </si>
-  <si>
-    <t>IN-10</t>
-  </si>
-  <si>
-    <t>Plan backups and disaster recovery</t>
-  </si>
-  <si>
-    <t>No backup strategy exists for the database or uploaded files.</t>
-  </si>
-  <si>
-    <t>Relevant once there is a real database.</t>
-  </si>
-  <si>
-    <t>LG-04</t>
-  </si>
-  <si>
-    <t>Approve the About / Contact / Order Support copy</t>
-  </si>
-  <si>
-    <t>All placeholder text.</t>
-  </si>
-  <si>
-    <t>Pages carry a visible placeholder notice.</t>
-  </si>
-  <si>
-    <t>DF-01</t>
-  </si>
-  <si>
-    <t>Industry taxonomy</t>
-  </si>
-  <si>
-    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
-  </si>
-  <si>
-    <t>Additive; adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-02</t>
-  </si>
-  <si>
-    <t>Subscribe and Save</t>
-  </si>
-  <si>
-    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
-  </si>
-  <si>
-    <t>Needs the backend.</t>
-  </si>
-  <si>
-    <t>DF-03</t>
-  </si>
-  <si>
-    <t>Frequently bought together</t>
-  </si>
-  <si>
-    <t>Bundle suggestion with a combined total and one action to add all.</t>
-  </si>
-  <si>
-    <t>Adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-04</t>
-  </si>
-  <si>
-    <t>Quick view</t>
-  </si>
-  <si>
-    <t>View a product from the listing without a page load.</t>
-  </si>
-  <si>
-    <t>DF-05</t>
-  </si>
-  <si>
-    <t>Downloadable PDF catalogues</t>
-  </si>
-  <si>
-    <t>Still how a lot of trade buying happens.</t>
-  </si>
-  <si>
-    <t>Needs the actual catalogue files.</t>
+    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
   </si>
   <si>
     <t>DN-01</t>
-  </si>
-  <si>
-    <t>Done</t>
   </si>
   <si>
     <t>Currency rendering</t>
@@ -1584,7 +1596,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1600,7 +1612,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3584,7 +3596,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3627,13 +3639,13 @@
         <v>292</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>294</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>295</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
@@ -3642,7 +3654,7 @@
         <v>34</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>296</v>
@@ -3653,7 +3665,7 @@
         <v>297</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>298</v>
@@ -3668,24 +3680,24 @@
         <v>34</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
@@ -3694,24 +3706,24 @@
         <v>34</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
@@ -3720,10 +3732,10 @@
         <v>34</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3731,7 +3743,7 @@
         <v>307</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>308</v>
@@ -3746,7 +3758,7 @@
         <v>34</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>310</v>
@@ -3757,7 +3769,7 @@
         <v>311</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>312</v>
@@ -3772,7 +3784,7 @@
         <v>34</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>314</v>
@@ -3783,7 +3795,7 @@
         <v>315</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>316</v>
@@ -3798,7 +3810,7 @@
         <v>34</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>318</v>
@@ -3809,7 +3821,7 @@
         <v>319</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>320</v>
@@ -3824,7 +3836,7 @@
         <v>34</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>322</v>
@@ -3835,7 +3847,7 @@
         <v>323</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>324</v>
@@ -3850,7 +3862,7 @@
         <v>34</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>326</v>
@@ -3861,7 +3873,7 @@
         <v>327</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>328</v>
@@ -3872,11 +3884,11 @@
       <c r="E11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>126</v>
+      <c r="F11" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>330</v>
@@ -3887,7 +3899,7 @@
         <v>331</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>332</v>
@@ -3902,7 +3914,7 @@
         <v>126</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>334</v>
@@ -3913,7 +3925,7 @@
         <v>335</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>336</v>
@@ -3928,24 +3940,24 @@
         <v>126</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>284</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>15</v>
@@ -3954,10 +3966,10 @@
         <v>126</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>341</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3965,7 +3977,7 @@
         <v>342</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>343</v>
@@ -3980,7 +3992,7 @@
         <v>126</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>345</v>
@@ -3991,7 +4003,7 @@
         <v>346</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>347</v>
@@ -4006,7 +4018,7 @@
         <v>126</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>349</v>
@@ -4017,7 +4029,7 @@
         <v>350</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>351</v>
@@ -4032,14 +4044,40 @@
         <v>126</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>353</v>
       </c>
     </row>
+    <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>357</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:H18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="370">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -202,709 +202,733 @@
     <t>Approval is an admin-only transition enforced in the service layer.</t>
   </si>
   <si>
+    <t>DA-01</t>
+  </si>
+  <si>
+    <t>Supply the real product catalogue</t>
+  </si>
+  <si>
+    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
+  </si>
+  <si>
+    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
+  </si>
+  <si>
+    <t>DA-03</t>
+  </si>
+  <si>
+    <t>Supply product photography</t>
+  </si>
+  <si>
+    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
+  </si>
+  <si>
+    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
+  </si>
+  <si>
+    <t>DA-06</t>
+  </si>
+  <si>
+    <t>Supply the real supplier list</t>
+  </si>
+  <si>
+    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
+  </si>
+  <si>
+    <t>All are flagged isPlaceholder in the data.</t>
+  </si>
+  <si>
+    <t>DA-17</t>
+  </si>
+  <si>
+    <t>Replace the test supplier attribution</t>
+  </si>
+  <si>
+    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
+  </si>
+  <si>
+    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
+  </si>
+  <si>
+    <t>FN-01</t>
+  </si>
+  <si>
+    <t>Checkout does not submit an order</t>
+  </si>
+  <si>
+    <t>The form is complete and the flow is reviewable, but nothing is created and no payment is taken. A preview reference number is generated in the browser.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend. States this on screen.</t>
+  </si>
+  <si>
+    <t>FN-02</t>
+  </si>
+  <si>
+    <t>Quote requests are not delivered</t>
+  </si>
+  <si>
+    <t>Captured in the browser only.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend and an email provider.</t>
+  </si>
+  <si>
+    <t>FN-03</t>
+  </si>
+  <si>
+    <t>Bulk buy enquiries are not delivered</t>
+  </si>
+  <si>
+    <t>FN-04</t>
+  </si>
+  <si>
+    <t>Notify Me does not register a subscription</t>
+  </si>
+  <si>
+    <t>Captured locally. The restock email flow does not exist.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend.</t>
+  </si>
+  <si>
+    <t>FN-05</t>
+  </si>
+  <si>
+    <t>Sign-in is a demo flag</t>
+  </si>
+  <si>
+    <t>A localStorage boolean opens a fabricated session. Real auth is email OTP per the backend spec.</t>
+  </si>
+  <si>
+    <t>Must be replaced wholesale rather than extended.</t>
+  </si>
+  <si>
+    <t>FN-06</t>
+  </si>
+  <si>
+    <t>Account history is fabricated</t>
+  </si>
+  <si>
+    <t>The customer, three orders and their invoices are invented so the account screens could be built and reviewed.</t>
+  </si>
+  <si>
+    <t>Every account page carries a visible notice.</t>
+  </si>
+  <si>
+    <t>IN-06</t>
+  </si>
+  <si>
+    <t>Remove noindex before launch</t>
+  </si>
+  <si>
+    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
+  </si>
+  <si>
+    <t>Must be removed deliberately at launch — and only then.</t>
+  </si>
+  <si>
+    <t>IN-07</t>
+  </si>
+  <si>
+    <t>Confirm the GitHub repository is private</t>
+  </si>
+  <si>
+    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
+  </si>
+  <si>
+    <t>https://github.com/musawi1989/aussiemed</t>
+  </si>
+  <si>
+    <t>LG-01</t>
+  </si>
+  <si>
+    <t>Supply terms and conditions</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
+  </si>
+  <si>
+    <t>Page exists and says so on screen.</t>
+  </si>
+  <si>
+    <t>LG-02</t>
+  </si>
+  <si>
+    <t>Supply the privacy policy</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
+  </si>
+  <si>
+    <t>LG-03</t>
+  </si>
+  <si>
+    <t>Confirm the contact email address</t>
+  </si>
+  <si>
+    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
+  </si>
+  <si>
+    <t>Also determines the sending domain for transactional email.</t>
+  </si>
+  <si>
+    <t>AC-05</t>
+  </si>
+  <si>
+    <t>Confirm the VAT rate and whether it must be configurable</t>
+  </si>
+  <si>
+    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Rate must be stored on the order at the time it is placed.</t>
+  </si>
+  <si>
+    <t>AC-06</t>
+  </si>
+  <si>
+    <t>Approve the reference number format</t>
+  </si>
+  <si>
+    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
+  </si>
+  <si>
+    <t>Wording is fixed as Reference number, never order number.</t>
+  </si>
+  <si>
+    <t>AC-07</t>
+  </si>
+  <si>
+    <t>Approve the supplier invoice numbering</t>
+  </si>
+  <si>
+    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
+  </si>
+  <si>
+    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
+  </si>
+  <si>
+    <t>AC-09</t>
+  </si>
+  <si>
+    <t>Decide payment terms and credit accounts</t>
+  </si>
+  <si>
+    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
+  </si>
+  <si>
+    <t>Affects the schema — decide before the backend.</t>
+  </si>
+  <si>
+    <t>BE-04</t>
+  </si>
+  <si>
+    <t>Build comma-safe .xlsx bulk upload</t>
+  </si>
+  <si>
+    <t>Parsed natively with exceljs, never by splitting on commas — that is what broke comma-containing category names.</t>
+  </si>
+  <si>
+    <t>Unknown brands must be reported per row, never skipped silently.</t>
+  </si>
+  <si>
+    <t>BE-05</t>
+  </si>
+  <si>
+    <t>Build the email flows</t>
+  </si>
+  <si>
+    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
+  </si>
+  <si>
+    <t>Needs an SMTP provider.</t>
+  </si>
+  <si>
+    <t>BE-06</t>
+  </si>
+  <si>
+    <t>Add an audit log</t>
+  </si>
+  <si>
+    <t>Every status transition and every admin or supplier write should be recorded.</t>
+  </si>
+  <si>
+    <t>Specified in the backend spec.</t>
+  </si>
+  <si>
+    <t>BE-08</t>
+  </si>
+  <si>
+    <t>Decide money representation before any data lands</t>
+  </si>
+  <si>
+    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
+  </si>
+  <si>
+    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
+  </si>
+  <si>
+    <t>BE-10</t>
+  </si>
+  <si>
+    <t>Retire the catalogue snapshot endpoint</t>
+  </si>
+  <si>
+    <t>Client components fetch the whole catalogue from /api/v1/catalog/snapshot. Fine for 71 products; not for thousands. Goes away when the cart moves server-side.</t>
+  </si>
+  <si>
+    <t>Phase 3 removes the need.</t>
+  </si>
+  <si>
+    <t>DA-02</t>
+  </si>
+  <si>
+    <t>Verify the product-to-category mapping</t>
+  </si>
+  <si>
+    <t>The extraction had no product-category link at all. All 11 real products were mapped by hand from their names.</t>
+  </si>
+  <si>
+    <t>146 categories exist; the mapping is ours and unverified.</t>
+  </si>
+  <si>
+    <t>DA-05</t>
+  </si>
+  <si>
+    <t>Approve the product descriptions</t>
+  </si>
+  <si>
+    <t>The source had no descriptions. Eleven were written from the product names and need approval before launch.</t>
+  </si>
+  <si>
+    <t>Placeholder products carry generated filler text.</t>
+  </si>
+  <si>
+    <t>DA-07</t>
+  </si>
+  <si>
+    <t>Supply the hero banner image</t>
+  </si>
+  <si>
+    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured — only Brand, Category, Product and WebHtml folders were mirrored.</t>
+  </si>
+  <si>
+    <t>A genuine AussieMed CMS image stands in.</t>
+  </si>
+  <si>
+    <t>DA-08</t>
+  </si>
+  <si>
+    <t>Obtain Gilroy Regular and Medium</t>
+  </si>
+  <si>
+    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
+  </si>
+  <si>
+    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
+  </si>
+  <si>
+    <t>DA-10</t>
+  </si>
+  <si>
+    <t>Supply real pack and carton structures</t>
+  </si>
+  <si>
+    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
+  </si>
+  <si>
+    <t>Pack is the purchasable unit; getting it wrong misprices every carton.</t>
+  </si>
+  <si>
+    <t>DA-11</t>
+  </si>
+  <si>
+    <t>Supply real variant data</t>
+  </si>
+  <si>
+    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
+  </si>
+  <si>
+    <t>Variant switching is not wired until sibling SKUs exist.</t>
+  </si>
+  <si>
+    <t>DA-12</t>
+  </si>
+  <si>
+    <t>Supply real product specifications</t>
+  </si>
+  <si>
+    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
+  </si>
+  <si>
+    <t>These become search filters later.</t>
+  </si>
+  <si>
+    <t>DA-13</t>
+  </si>
+  <si>
+    <t>Supply safety data sheets and spec sheets</t>
+  </si>
+  <si>
+    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
+  </si>
+  <si>
+    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
+  </si>
+  <si>
+    <t>DA-18</t>
+  </si>
+  <si>
+    <t>Product ids are derived from slugs</t>
+  </si>
+  <si>
+    <t>Carts and wishlists are stored in the browser against a product id. Ids are now hashed from the slug so they survive a re-seed, which means CHANGING A PRODUCT SLUG ORPHANS ANY SAVED CART LINE referencing it.</t>
+  </si>
+  <si>
+    <t>Resolved properly when the cart moves server-side and references SKU rows directly.</t>
+  </si>
+  <si>
+    <t>FN-07</t>
+  </si>
+  <si>
+    <t>Variant switching is not wired</t>
+  </si>
+  <si>
+    <t>Size and colour chips display the current value; other options are disabled because sibling SKUs do not exist yet.</t>
+  </si>
+  <si>
+    <t>Needs the variant model in the database.</t>
+  </si>
+  <si>
+    <t>FN-08</t>
+  </si>
+  <si>
+    <t>Stock is a boolean</t>
+  </si>
+  <si>
+    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
+  </si>
+  <si>
+    <t>Decide whether real stock levels are needed.</t>
+  </si>
+  <si>
+    <t>FN-09</t>
+  </si>
+  <si>
+    <t>Decide on expiry and short-dated stock</t>
+  </si>
+  <si>
+    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
+  </si>
+  <si>
+    <t>Schema-shaping — decide before the backend is built.</t>
+  </si>
+  <si>
+    <t>IN-01</t>
+  </si>
+  <si>
+    <t>Choose a hosting target</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. The site runs locally only.</t>
+  </si>
+  <si>
+    <t>Deliberately deferred until the build is approved.</t>
+  </si>
+  <si>
+    <t>IN-02</t>
+  </si>
+  <si>
+    <t>Choose the database</t>
+  </si>
+  <si>
+    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
+  </si>
+  <si>
+    <t>IN-03</t>
+  </si>
+  <si>
+    <t>Choose an SMTP provider and sending domain</t>
+  </si>
+  <si>
+    <t>Required for every transactional email.</t>
+  </si>
+  <si>
+    <t>Must not be the misspelled assuiemed.com domain.</t>
+  </si>
+  <si>
+    <t>IN-04</t>
+  </si>
+  <si>
+    <t>Decide on a payment gateway</t>
+  </si>
+  <si>
+    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
+  </si>
+  <si>
+    <t>LG-05</t>
+  </si>
+  <si>
+    <t>Transfer the theme licence</t>
+  </si>
+  <si>
+    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
+  </si>
+  <si>
+    <t>Repository must stay private because of this.</t>
+  </si>
+  <si>
+    <t>LG-06</t>
+  </si>
+  <si>
+    <t>Supply company registration details</t>
+  </si>
+  <si>
+    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
+  </si>
+  <si>
+    <t>AC-08</t>
+  </si>
+  <si>
+    <t>Confirm the rounding policy</t>
+  </si>
+  <si>
+    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Verified by test; needs sign-off that the method is acceptable.</t>
+  </si>
+  <si>
+    <t>AC-10</t>
+  </si>
+  <si>
+    <t>Confirm the default price display</t>
+  </si>
+  <si>
+    <t>Prices default to Ex. VAT with a toggle to Inc. VAT.</t>
+  </si>
+  <si>
+    <t>Preference persists per browser.</t>
+  </si>
+  <si>
+    <t>DA-04</t>
+  </si>
+  <si>
+    <t>Wrong image on the scrub top</t>
+  </si>
+  <si>
+    <t>The product's primary image was a stock photo of a pocket watch. Excluded from the build; the file is still in public/products/.</t>
+  </si>
+  <si>
+    <t>Suggests image uploads were not being checked in the old admin.</t>
+  </si>
+  <si>
+    <t>DA-09</t>
+  </si>
+  <si>
+    <t>Explain the disappearing product</t>
+  </si>
+  <si>
+    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
+  </si>
+  <si>
+    <t>Evidence of a real defect in the old platform. Worth understanding before trusting any migrated data.</t>
+  </si>
+  <si>
+    <t>DA-14</t>
+  </si>
+  <si>
+    <t>Confirm the brand list</t>
+  </si>
+  <si>
+    <t>Brands were assigned by reading product names.</t>
+  </si>
+  <si>
+    <t>Eleven real brands identified.</t>
+  </si>
+  <si>
+    <t>DA-15</t>
+  </si>
+  <si>
+    <t>Decide on duplicate categories</t>
+  </si>
+  <si>
+    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
+  </si>
+  <si>
+    <t>Affected: Respiratory Management, Oral Care, Monitoring &amp; Testing, Dispensers, Bags, Medicine.</t>
+  </si>
+  <si>
+    <t>DA-16</t>
+  </si>
+  <si>
+    <t>Confirm the missing department</t>
+  </si>
+  <si>
+    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
+  </si>
+  <si>
+    <t>Confirm this is intentional rather than lost.</t>
+  </si>
+  <si>
+    <t>FN-10</t>
+  </si>
+  <si>
+    <t>Search is client-side only</t>
+  </si>
+  <si>
+    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
+  </si>
+  <si>
+    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
+  </si>
+  <si>
+    <t>IN-05</t>
+  </si>
+  <si>
+    <t>Supply Google and Facebook OAuth keys</t>
+  </si>
+  <si>
+    <t>Social login endpoints currently return 501.</t>
+  </si>
+  <si>
+    <t>IN-08</t>
+  </si>
+  <si>
+    <t>Correct the git author name</t>
+  </si>
+  <si>
+    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
+  </si>
+  <si>
+    <t>Fixable with git config user.name and an amend.</t>
+  </si>
+  <si>
+    <t>IN-09</t>
+  </si>
+  <si>
+    <t>Set up continuous integration</t>
+  </si>
+  <si>
+    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
+  </si>
+  <si>
+    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
+  </si>
+  <si>
+    <t>IN-10</t>
+  </si>
+  <si>
+    <t>Plan backups and disaster recovery</t>
+  </si>
+  <si>
+    <t>No backup strategy exists for the database or uploaded files.</t>
+  </si>
+  <si>
+    <t>Relevant once there is a real database.</t>
+  </si>
+  <si>
+    <t>LG-04</t>
+  </si>
+  <si>
+    <t>Approve the About / Contact / Order Support copy</t>
+  </si>
+  <si>
+    <t>All placeholder text.</t>
+  </si>
+  <si>
+    <t>Pages carry a visible placeholder notice.</t>
+  </si>
+  <si>
+    <t>DF-01</t>
+  </si>
+  <si>
+    <t>Industry taxonomy</t>
+  </si>
+  <si>
+    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
+  </si>
+  <si>
+    <t>Additive; adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-02</t>
+  </si>
+  <si>
+    <t>Subscribe and Save</t>
+  </si>
+  <si>
+    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
+  </si>
+  <si>
+    <t>Needs the backend.</t>
+  </si>
+  <si>
+    <t>DF-03</t>
+  </si>
+  <si>
+    <t>Frequently bought together</t>
+  </si>
+  <si>
+    <t>Bundle suggestion with a combined total and one action to add all.</t>
+  </si>
+  <si>
+    <t>Adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-04</t>
+  </si>
+  <si>
+    <t>Quick view</t>
+  </si>
+  <si>
+    <t>View a product from the listing without a page load.</t>
+  </si>
+  <si>
+    <t>DF-05</t>
+  </si>
+  <si>
+    <t>Downloadable PDF catalogues</t>
+  </si>
+  <si>
+    <t>Still how a lot of trade buying happens.</t>
+  </si>
+  <si>
+    <t>Needs the actual catalogue files.</t>
+  </si>
+  <si>
+    <t>BE-07</t>
+  </si>
+  <si>
+    <t>Seed the database from the catalogue</t>
+  </si>
+  <si>
+    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
+  </si>
+  <si>
     <t>BE-09</t>
   </si>
   <si>
     <t>Point the storefront at the database</t>
   </si>
   <si>
-    <t>The site still reads catalog.json. The API layer needs to read Prisma instead, which is the swap the data-access seam was built for.</t>
-  </si>
-  <si>
-    <t>Only src/lib/catalog.ts should need to change.</t>
-  </si>
-  <si>
-    <t>DA-01</t>
-  </si>
-  <si>
-    <t>Supply the real product catalogue</t>
-  </si>
-  <si>
-    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
-  </si>
-  <si>
-    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
-  </si>
-  <si>
-    <t>DA-03</t>
-  </si>
-  <si>
-    <t>Supply product photography</t>
-  </si>
-  <si>
-    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
-  </si>
-  <si>
-    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
-  </si>
-  <si>
-    <t>DA-06</t>
-  </si>
-  <si>
-    <t>Supply the real supplier list</t>
-  </si>
-  <si>
-    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
-  </si>
-  <si>
-    <t>All are flagged isPlaceholder in the data.</t>
-  </si>
-  <si>
-    <t>DA-17</t>
-  </si>
-  <si>
-    <t>Replace the test supplier attribution</t>
-  </si>
-  <si>
-    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
-  </si>
-  <si>
-    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
-  </si>
-  <si>
-    <t>FN-01</t>
-  </si>
-  <si>
-    <t>Checkout does not submit an order</t>
-  </si>
-  <si>
-    <t>The form is complete and the flow is reviewable, but nothing is created and no payment is taken. A preview reference number is generated in the browser.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend. States this on screen.</t>
-  </si>
-  <si>
-    <t>FN-02</t>
-  </si>
-  <si>
-    <t>Quote requests are not delivered</t>
-  </si>
-  <si>
-    <t>Captured in the browser only.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend and an email provider.</t>
-  </si>
-  <si>
-    <t>FN-03</t>
-  </si>
-  <si>
-    <t>Bulk buy enquiries are not delivered</t>
-  </si>
-  <si>
-    <t>FN-04</t>
-  </si>
-  <si>
-    <t>Notify Me does not register a subscription</t>
-  </si>
-  <si>
-    <t>Captured locally. The restock email flow does not exist.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend.</t>
-  </si>
-  <si>
-    <t>FN-05</t>
-  </si>
-  <si>
-    <t>Sign-in is a demo flag</t>
-  </si>
-  <si>
-    <t>A localStorage boolean opens a fabricated session. Real auth is email OTP per the backend spec.</t>
-  </si>
-  <si>
-    <t>Must be replaced wholesale rather than extended.</t>
-  </si>
-  <si>
-    <t>FN-06</t>
-  </si>
-  <si>
-    <t>Account history is fabricated</t>
-  </si>
-  <si>
-    <t>The customer, three orders and their invoices are invented so the account screens could be built and reviewed.</t>
-  </si>
-  <si>
-    <t>Every account page carries a visible notice.</t>
-  </si>
-  <si>
-    <t>IN-06</t>
-  </si>
-  <si>
-    <t>Remove noindex before launch</t>
-  </si>
-  <si>
-    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
-  </si>
-  <si>
-    <t>Must be removed deliberately at launch — and only then.</t>
-  </si>
-  <si>
-    <t>IN-07</t>
-  </si>
-  <si>
-    <t>Confirm the GitHub repository is private</t>
-  </si>
-  <si>
-    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
-  </si>
-  <si>
-    <t>https://github.com/musawi1989/aussiemed</t>
-  </si>
-  <si>
-    <t>LG-01</t>
-  </si>
-  <si>
-    <t>Supply terms and conditions</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
-  </si>
-  <si>
-    <t>Page exists and says so on screen.</t>
-  </si>
-  <si>
-    <t>LG-02</t>
-  </si>
-  <si>
-    <t>Supply the privacy policy</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
-  </si>
-  <si>
-    <t>LG-03</t>
-  </si>
-  <si>
-    <t>Confirm the contact email address</t>
-  </si>
-  <si>
-    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
-  </si>
-  <si>
-    <t>Also determines the sending domain for transactional email.</t>
-  </si>
-  <si>
-    <t>AC-05</t>
-  </si>
-  <si>
-    <t>Confirm the VAT rate and whether it must be configurable</t>
-  </si>
-  <si>
-    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>Rate must be stored on the order at the time it is placed.</t>
-  </si>
-  <si>
-    <t>AC-06</t>
-  </si>
-  <si>
-    <t>Approve the reference number format</t>
-  </si>
-  <si>
-    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
-  </si>
-  <si>
-    <t>Wording is fixed as Reference number, never order number.</t>
-  </si>
-  <si>
-    <t>AC-07</t>
-  </si>
-  <si>
-    <t>Approve the supplier invoice numbering</t>
-  </si>
-  <si>
-    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
-  </si>
-  <si>
-    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
-  </si>
-  <si>
-    <t>AC-09</t>
-  </si>
-  <si>
-    <t>Decide payment terms and credit accounts</t>
-  </si>
-  <si>
-    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
-  </si>
-  <si>
-    <t>Affects the schema — decide before the backend.</t>
-  </si>
-  <si>
-    <t>BE-04</t>
-  </si>
-  <si>
-    <t>Build comma-safe .xlsx bulk upload</t>
-  </si>
-  <si>
-    <t>Parsed natively with exceljs, never by splitting on commas — that is what broke comma-containing category names.</t>
-  </si>
-  <si>
-    <t>Unknown brands must be reported per row, never skipped silently.</t>
-  </si>
-  <si>
-    <t>BE-05</t>
-  </si>
-  <si>
-    <t>Build the email flows</t>
-  </si>
-  <si>
-    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
-  </si>
-  <si>
-    <t>Needs an SMTP provider.</t>
-  </si>
-  <si>
-    <t>BE-06</t>
-  </si>
-  <si>
-    <t>Add an audit log</t>
-  </si>
-  <si>
-    <t>Every status transition and every admin or supplier write should be recorded.</t>
-  </si>
-  <si>
-    <t>Specified in the backend spec.</t>
-  </si>
-  <si>
-    <t>BE-08</t>
-  </si>
-  <si>
-    <t>Decide money representation before any data lands</t>
-  </si>
-  <si>
-    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
-  </si>
-  <si>
-    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
-  </si>
-  <si>
-    <t>DA-02</t>
-  </si>
-  <si>
-    <t>Verify the product-to-category mapping</t>
-  </si>
-  <si>
-    <t>The extraction had no product-category link at all. All 11 real products were mapped by hand from their names.</t>
-  </si>
-  <si>
-    <t>146 categories exist; the mapping is ours and unverified.</t>
-  </si>
-  <si>
-    <t>DA-05</t>
-  </si>
-  <si>
-    <t>Approve the product descriptions</t>
-  </si>
-  <si>
-    <t>The source had no descriptions. Eleven were written from the product names and need approval before launch.</t>
-  </si>
-  <si>
-    <t>Placeholder products carry generated filler text.</t>
-  </si>
-  <si>
-    <t>DA-07</t>
-  </si>
-  <si>
-    <t>Supply the hero banner image</t>
-  </si>
-  <si>
-    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured — only Brand, Category, Product and WebHtml folders were mirrored.</t>
-  </si>
-  <si>
-    <t>A genuine AussieMed CMS image stands in.</t>
-  </si>
-  <si>
-    <t>DA-08</t>
-  </si>
-  <si>
-    <t>Obtain Gilroy Regular and Medium</t>
-  </si>
-  <si>
-    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
-  </si>
-  <si>
-    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
-  </si>
-  <si>
-    <t>DA-10</t>
-  </si>
-  <si>
-    <t>Supply real pack and carton structures</t>
-  </si>
-  <si>
-    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
-  </si>
-  <si>
-    <t>Pack is the purchasable unit; getting it wrong misprices every carton.</t>
-  </si>
-  <si>
-    <t>DA-11</t>
-  </si>
-  <si>
-    <t>Supply real variant data</t>
-  </si>
-  <si>
-    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
-  </si>
-  <si>
-    <t>Variant switching is not wired until sibling SKUs exist.</t>
-  </si>
-  <si>
-    <t>DA-12</t>
-  </si>
-  <si>
-    <t>Supply real product specifications</t>
-  </si>
-  <si>
-    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
-  </si>
-  <si>
-    <t>These become search filters later.</t>
-  </si>
-  <si>
-    <t>DA-13</t>
-  </si>
-  <si>
-    <t>Supply safety data sheets and spec sheets</t>
-  </si>
-  <si>
-    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
-  </si>
-  <si>
-    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
-  </si>
-  <si>
-    <t>FN-07</t>
-  </si>
-  <si>
-    <t>Variant switching is not wired</t>
-  </si>
-  <si>
-    <t>Size and colour chips display the current value; other options are disabled because sibling SKUs do not exist yet.</t>
-  </si>
-  <si>
-    <t>Needs the variant model in the database.</t>
-  </si>
-  <si>
-    <t>FN-08</t>
-  </si>
-  <si>
-    <t>Stock is a boolean</t>
-  </si>
-  <si>
-    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
-  </si>
-  <si>
-    <t>Decide whether real stock levels are needed.</t>
-  </si>
-  <si>
-    <t>FN-09</t>
-  </si>
-  <si>
-    <t>Decide on expiry and short-dated stock</t>
-  </si>
-  <si>
-    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
-  </si>
-  <si>
-    <t>Schema-shaping — decide before the backend is built.</t>
-  </si>
-  <si>
-    <t>IN-01</t>
-  </si>
-  <si>
-    <t>Choose a hosting target</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. The site runs locally only.</t>
-  </si>
-  <si>
-    <t>Deliberately deferred until the build is approved.</t>
-  </si>
-  <si>
-    <t>IN-02</t>
-  </si>
-  <si>
-    <t>Choose the database</t>
-  </si>
-  <si>
-    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
-  </si>
-  <si>
-    <t>IN-03</t>
-  </si>
-  <si>
-    <t>Choose an SMTP provider and sending domain</t>
-  </si>
-  <si>
-    <t>Required for every transactional email.</t>
-  </si>
-  <si>
-    <t>Must not be the misspelled assuiemed.com domain.</t>
-  </si>
-  <si>
-    <t>IN-04</t>
-  </si>
-  <si>
-    <t>Decide on a payment gateway</t>
-  </si>
-  <si>
-    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
-  </si>
-  <si>
-    <t>LG-05</t>
-  </si>
-  <si>
-    <t>Transfer the theme licence</t>
-  </si>
-  <si>
-    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
-  </si>
-  <si>
-    <t>Repository must stay private because of this.</t>
-  </si>
-  <si>
-    <t>LG-06</t>
-  </si>
-  <si>
-    <t>Supply company registration details</t>
-  </si>
-  <si>
-    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
-  </si>
-  <si>
-    <t>AC-08</t>
-  </si>
-  <si>
-    <t>Confirm the rounding policy</t>
-  </si>
-  <si>
-    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>Verified by test; needs sign-off that the method is acceptable.</t>
-  </si>
-  <si>
-    <t>AC-10</t>
-  </si>
-  <si>
-    <t>Confirm the default price display</t>
-  </si>
-  <si>
-    <t>Prices default to Ex. VAT with a toggle to Inc. VAT.</t>
-  </si>
-  <si>
-    <t>Preference persists per browser.</t>
-  </si>
-  <si>
-    <t>DA-04</t>
-  </si>
-  <si>
-    <t>Wrong image on the scrub top</t>
-  </si>
-  <si>
-    <t>The product's primary image was a stock photo of a pocket watch. Excluded from the build; the file is still in public/products/.</t>
-  </si>
-  <si>
-    <t>Suggests image uploads were not being checked in the old admin.</t>
-  </si>
-  <si>
-    <t>DA-09</t>
-  </si>
-  <si>
-    <t>Explain the disappearing product</t>
-  </si>
-  <si>
-    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
-  </si>
-  <si>
-    <t>Evidence of a real defect in the old platform. Worth understanding before trusting any migrated data.</t>
-  </si>
-  <si>
-    <t>DA-14</t>
-  </si>
-  <si>
-    <t>Confirm the brand list</t>
-  </si>
-  <si>
-    <t>Brands were assigned by reading product names.</t>
-  </si>
-  <si>
-    <t>Eleven real brands identified.</t>
-  </si>
-  <si>
-    <t>DA-15</t>
-  </si>
-  <si>
-    <t>Decide on duplicate categories</t>
-  </si>
-  <si>
-    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
-  </si>
-  <si>
-    <t>Affected: Respiratory Management, Oral Care, Monitoring &amp; Testing, Dispensers, Bags, Medicine.</t>
-  </si>
-  <si>
-    <t>DA-16</t>
-  </si>
-  <si>
-    <t>Confirm the missing department</t>
-  </si>
-  <si>
-    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
-  </si>
-  <si>
-    <t>Confirm this is intentional rather than lost.</t>
-  </si>
-  <si>
-    <t>FN-10</t>
-  </si>
-  <si>
-    <t>Search is client-side only</t>
-  </si>
-  <si>
-    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
-  </si>
-  <si>
-    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
-  </si>
-  <si>
-    <t>IN-05</t>
-  </si>
-  <si>
-    <t>Supply Google and Facebook OAuth keys</t>
-  </si>
-  <si>
-    <t>Social login endpoints currently return 501.</t>
-  </si>
-  <si>
-    <t>IN-08</t>
-  </si>
-  <si>
-    <t>Correct the git author name</t>
-  </si>
-  <si>
-    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
-  </si>
-  <si>
-    <t>Fixable with git config user.name and an amend.</t>
-  </si>
-  <si>
-    <t>IN-09</t>
-  </si>
-  <si>
-    <t>Set up continuous integration</t>
-  </si>
-  <si>
-    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
-  </si>
-  <si>
-    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
-  </si>
-  <si>
-    <t>IN-10</t>
-  </si>
-  <si>
-    <t>Plan backups and disaster recovery</t>
-  </si>
-  <si>
-    <t>No backup strategy exists for the database or uploaded files.</t>
-  </si>
-  <si>
-    <t>Relevant once there is a real database.</t>
-  </si>
-  <si>
-    <t>LG-04</t>
-  </si>
-  <si>
-    <t>Approve the About / Contact / Order Support copy</t>
-  </si>
-  <si>
-    <t>All placeholder text.</t>
-  </si>
-  <si>
-    <t>Pages carry a visible placeholder notice.</t>
-  </si>
-  <si>
-    <t>DF-01</t>
-  </si>
-  <si>
-    <t>Industry taxonomy</t>
-  </si>
-  <si>
-    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
-  </si>
-  <si>
-    <t>Additive; adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-02</t>
-  </si>
-  <si>
-    <t>Subscribe and Save</t>
-  </si>
-  <si>
-    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
-  </si>
-  <si>
-    <t>Needs the backend.</t>
-  </si>
-  <si>
-    <t>DF-03</t>
-  </si>
-  <si>
-    <t>Frequently bought together</t>
-  </si>
-  <si>
-    <t>Bundle suggestion with a combined total and one action to add all.</t>
-  </si>
-  <si>
-    <t>Adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-04</t>
-  </si>
-  <si>
-    <t>Quick view</t>
-  </si>
-  <si>
-    <t>View a product from the listing without a page load.</t>
-  </si>
-  <si>
-    <t>DF-05</t>
-  </si>
-  <si>
-    <t>Downloadable PDF catalogues</t>
-  </si>
-  <si>
-    <t>Still how a lot of trade buying happens.</t>
-  </si>
-  <si>
-    <t>Needs the actual catalogue files.</t>
-  </si>
-  <si>
-    <t>BE-07</t>
-  </si>
-  <si>
-    <t>Seed the database from the catalogue</t>
-  </si>
-  <si>
-    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
+    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
+  </si>
+  <si>
+    <t>query.ts was untouched — it never knew where products came from.</t>
   </si>
   <si>
     <t>DN-01</t>
@@ -1007,6 +1031,18 @@
   </si>
   <si>
     <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
+  </si>
+  <si>
+    <t>DN-17</t>
+  </si>
+  <si>
+    <t>Typecheck was silently passing on a stale cache</t>
+  </si>
+  <si>
+    <t>tsc ran with incremental caching and reported no errors while real type errors existed in the tree. Every earlier typecheck-clean claim was suspect.</t>
+  </si>
+  <si>
+    <t>npm run typecheck now runs with --incremental false. Caught seven genuine errors the moment it was disabled.</t>
   </si>
   <si>
     <t>DN-07</t>
@@ -1596,7 +1632,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1604,7 +1640,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1612,7 +1648,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1638,7 +1674,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1646,7 +1682,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1696,7 +1732,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1722,7 +1758,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1780,7 +1816,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2005,7 +2041,7 @@
         <v>62</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>63</v>
@@ -2013,8 +2049,8 @@
       <c r="D9" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>15</v>
+      <c r="E9" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -2109,7 +2145,7 @@
         <v>78</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>79</v>
@@ -2117,8 +2153,8 @@
       <c r="D13" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>12</v>
+      <c r="E13" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -2167,7 +2203,7 @@
         <v>87</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>15</v>
@@ -2179,21 +2215,21 @@
         <v>35</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>15</v>
@@ -2205,7 +2241,7 @@
         <v>35</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2265,7 +2301,7 @@
         <v>100</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>101</v>
@@ -2299,8 +2335,8 @@
       <c r="D20" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>15</v>
+      <c r="E20" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>34</v>
@@ -2317,7 +2353,7 @@
         <v>108</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>109</v>
@@ -2361,21 +2397,21 @@
         <v>35</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>12</v>
@@ -2387,7 +2423,7 @@
         <v>35</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2395,7 +2431,7 @@
         <v>119</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>120</v>
@@ -2404,36 +2440,36 @@
         <v>121</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>34</v>
+        <v>13</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>35</v>
@@ -2456,10 +2492,10 @@
         <v>130</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>35</v>
@@ -2482,10 +2518,10 @@
         <v>134</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>35</v>
@@ -2499,7 +2535,7 @@
         <v>136</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>137</v>
@@ -2507,11 +2543,11 @@
       <c r="D28" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>12</v>
+      <c r="E28" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>35</v>
@@ -2537,7 +2573,7 @@
         <v>15</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>35</v>
@@ -2563,7 +2599,7 @@
         <v>15</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>35</v>
@@ -2585,11 +2621,11 @@
       <c r="D31" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>15</v>
+      <c r="E31" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>35</v>
@@ -2611,11 +2647,11 @@
       <c r="D32" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>13</v>
+      <c r="E32" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>35</v>
@@ -2641,7 +2677,7 @@
         <v>12</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>35</v>
@@ -2667,7 +2703,7 @@
         <v>12</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>35</v>
@@ -2693,7 +2729,7 @@
         <v>12</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>35</v>
@@ -2719,7 +2755,7 @@
         <v>14</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>35</v>
@@ -2745,7 +2781,7 @@
         <v>12</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>35</v>
@@ -2771,7 +2807,7 @@
         <v>12</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>35</v>
@@ -2797,7 +2833,7 @@
         <v>12</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>35</v>
@@ -2823,7 +2859,7 @@
         <v>12</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>35</v>
@@ -2837,7 +2873,7 @@
         <v>188</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>189</v>
@@ -2849,7 +2885,7 @@
         <v>15</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>35</v>
@@ -2875,7 +2911,7 @@
         <v>15</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>35</v>
@@ -2897,11 +2933,11 @@
       <c r="D43" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="E43" s="7" t="s">
-        <v>12</v>
+      <c r="E43" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>35</v>
@@ -2915,7 +2951,7 @@
         <v>200</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>201</v>
@@ -2927,7 +2963,7 @@
         <v>12</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>35</v>
@@ -2949,43 +2985,43 @@
       <c r="D45" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>15</v>
+      <c r="E45" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>2</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>12</v>
+        <v>210</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>210</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3005,39 +3041,39 @@
         <v>12</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>2</v>
+        <v>214</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>14</v>
+        <v>217</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>217</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3053,63 +3089,63 @@
       <c r="D49" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="E49" s="7" t="s">
-        <v>12</v>
+      <c r="E49" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>2</v>
+        <v>221</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>224</v>
+        <v>12</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>225</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="E51" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="10" t="s">
         <v>228</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>35</v>
@@ -3123,7 +3159,7 @@
         <v>230</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>231</v>
@@ -3135,7 +3171,7 @@
         <v>12</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>35</v>
@@ -3161,7 +3197,7 @@
         <v>12</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>35</v>
@@ -3187,7 +3223,7 @@
         <v>12</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>35</v>
@@ -3213,7 +3249,7 @@
         <v>12</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>35</v>
@@ -3239,7 +3275,7 @@
         <v>12</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>35</v>
@@ -3253,7 +3289,7 @@
         <v>250</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>251</v>
@@ -3261,11 +3297,11 @@
       <c r="D57" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>15</v>
+      <c r="E57" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>35</v>
@@ -3279,7 +3315,7 @@
         <v>254</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>255</v>
@@ -3287,43 +3323,43 @@
       <c r="D58" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="E58" s="7" t="s">
-        <v>12</v>
+      <c r="E58" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>2</v>
+        <v>257</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>260</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3339,11 +3375,11 @@
       <c r="D60" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="E60" s="6" t="s">
-        <v>15</v>
+      <c r="E60" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>35</v>
@@ -3365,11 +3401,11 @@
       <c r="D61" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="E61" s="7" t="s">
-        <v>12</v>
+      <c r="E61" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>35</v>
@@ -3383,7 +3419,7 @@
         <v>269</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>270</v>
@@ -3395,7 +3431,7 @@
         <v>12</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>35</v>
@@ -3404,8 +3440,34 @@
         <v>272</v>
       </c>
     </row>
+    <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H62"/>
+  <autoFilter ref="A1:H63"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3456,100 +3518,100 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>6</v>
@@ -3560,28 +3622,28 @@
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -3596,7 +3658,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3636,16 +3698,16 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
@@ -3654,24 +3716,24 @@
         <v>34</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>295</v>
+        <v>21</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>15</v>
@@ -3680,24 +3742,24 @@
         <v>34</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
@@ -3706,24 +3768,24 @@
         <v>34</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
@@ -3732,24 +3794,24 @@
         <v>34</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>15</v>
@@ -3758,24 +3820,24 @@
         <v>34</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>15</v>
@@ -3784,24 +3846,24 @@
         <v>34</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>15</v>
@@ -3810,24 +3872,24 @@
         <v>34</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>15</v>
@@ -3836,24 +3898,24 @@
         <v>34</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>15</v>
@@ -3862,24 +3924,24 @@
         <v>34</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>15</v>
@@ -3888,196 +3950,248 @@
         <v>34</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>126</v>
+      <c r="F12" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>126</v>
+      <c r="F13" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>349</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>357</v>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H18"/>
+  <autoFilter ref="A1:H20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="410">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -202,6 +202,18 @@
     <t>Approval is an admin-only transition enforced in the service layer.</t>
   </si>
   <si>
+    <t>BE-11</t>
+  </si>
+  <si>
+    <t>Restrict order pages to the account that placed the order</t>
+  </si>
+  <si>
+    <t>An order at /orders/REFERENCE is readable by anyone who knows the reference. There is no sign-in yet, so there is nothing to check against.</t>
+  </si>
+  <si>
+    <t>Must be closed before launch. References are sequential and therefore guessable.</t>
+  </si>
+  <si>
     <t>DA-01</t>
   </si>
   <si>
@@ -250,799 +262,907 @@
     <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
   </si>
   <si>
+    <t>FN-02</t>
+  </si>
+  <si>
+    <t>Quote requests are not delivered</t>
+  </si>
+  <si>
+    <t>Captured in the browser only.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend and an email provider.</t>
+  </si>
+  <si>
+    <t>FN-03</t>
+  </si>
+  <si>
+    <t>Bulk buy enquiries are not delivered</t>
+  </si>
+  <si>
+    <t>FN-04</t>
+  </si>
+  <si>
+    <t>Notify Me does not register a subscription</t>
+  </si>
+  <si>
+    <t>Captured locally. The restock email flow does not exist.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend.</t>
+  </si>
+  <si>
+    <t>FN-05</t>
+  </si>
+  <si>
+    <t>Sign-in is a demo flag</t>
+  </si>
+  <si>
+    <t>A localStorage boolean opens a fabricated session. Real auth is email OTP per the backend spec.</t>
+  </si>
+  <si>
+    <t>Must be replaced wholesale rather than extended.</t>
+  </si>
+  <si>
+    <t>FN-06</t>
+  </si>
+  <si>
+    <t>Account history is fabricated</t>
+  </si>
+  <si>
+    <t>The customer, three orders and their invoices are invented so the account screens could be built and reviewed.</t>
+  </si>
+  <si>
+    <t>Every account page carries a visible notice.</t>
+  </si>
+  <si>
+    <t>IN-06</t>
+  </si>
+  <si>
+    <t>Remove noindex before launch</t>
+  </si>
+  <si>
+    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
+  </si>
+  <si>
+    <t>Must be removed deliberately at launch — and only then.</t>
+  </si>
+  <si>
+    <t>IN-07</t>
+  </si>
+  <si>
+    <t>Confirm the GitHub repository is private</t>
+  </si>
+  <si>
+    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
+  </si>
+  <si>
+    <t>https://github.com/musawi1989/aussiemed</t>
+  </si>
+  <si>
+    <t>LG-01</t>
+  </si>
+  <si>
+    <t>Supply terms and conditions</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
+  </si>
+  <si>
+    <t>Page exists and says so on screen.</t>
+  </si>
+  <si>
+    <t>LG-02</t>
+  </si>
+  <si>
+    <t>Supply the privacy policy</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
+  </si>
+  <si>
+    <t>LG-03</t>
+  </si>
+  <si>
+    <t>Confirm the contact email address</t>
+  </si>
+  <si>
+    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
+  </si>
+  <si>
+    <t>Also determines the sending domain for transactional email.</t>
+  </si>
+  <si>
+    <t>AC-05</t>
+  </si>
+  <si>
+    <t>Confirm the VAT rate and whether it must be configurable</t>
+  </si>
+  <si>
+    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Rate must be stored on the order at the time it is placed.</t>
+  </si>
+  <si>
+    <t>AC-06</t>
+  </si>
+  <si>
+    <t>Approve the reference number format</t>
+  </si>
+  <si>
+    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
+  </si>
+  <si>
+    <t>Wording is fixed as Reference number, never order number.</t>
+  </si>
+  <si>
+    <t>AC-07</t>
+  </si>
+  <si>
+    <t>Approve the supplier invoice numbering</t>
+  </si>
+  <si>
+    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
+  </si>
+  <si>
+    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
+  </si>
+  <si>
+    <t>AC-09</t>
+  </si>
+  <si>
+    <t>Decide payment terms and credit accounts</t>
+  </si>
+  <si>
+    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
+  </si>
+  <si>
+    <t>Affects the schema — decide before the backend.</t>
+  </si>
+  <si>
+    <t>AC-11</t>
+  </si>
+  <si>
+    <t>Approve the VAT rounding method on invoices</t>
+  </si>
+  <si>
+    <t>VAT is rounded per line rather than once per invoice, so the printed lines always add up to the printed total. The alternative rounds once and can leave lines that do not sum.</t>
+  </si>
+  <si>
+    <t>Verified by test: per-invoice VAT sums to the order VAT exactly.</t>
+  </si>
+  <si>
+    <t>AC-12</t>
+  </si>
+  <si>
+    <t>Confirm the reference number sequence resets each year</t>
+  </si>
+  <si>
+    <t>OUR DECISION: the sequence restarts at 000001 each calendar year, so AM-2026-000001 and AM-2027-000001 can both exist. If accounting needs a single unbroken sequence this must change before real orders.</t>
+  </si>
+  <si>
+    <t>Held in a settings row keyed orderSequence:YYYY and incremented inside the checkout transaction.</t>
+  </si>
+  <si>
+    <t>AC-13</t>
+  </si>
+  <si>
+    <t>Decide whether an order should reserve stock</t>
+  </si>
+  <si>
+    <t>OUR DECISION: checkout does not decrement or reserve anything, because there are no stock levels — only an in/out flag. Two customers can order the last unit.</t>
+  </si>
+  <si>
+    <t>Depends on FN-08. Out-of-stock is re-checked at checkout, so a line that sold out while the form was open is rejected.</t>
+  </si>
+  <si>
+    <t>BE-04</t>
+  </si>
+  <si>
+    <t>Build comma-safe .xlsx bulk upload</t>
+  </si>
+  <si>
+    <t>Parsed natively with exceljs, never by splitting on commas — that is what broke comma-containing category names.</t>
+  </si>
+  <si>
+    <t>Unknown brands must be reported per row, never skipped silently.</t>
+  </si>
+  <si>
+    <t>BE-05</t>
+  </si>
+  <si>
+    <t>Build the email flows</t>
+  </si>
+  <si>
+    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
+  </si>
+  <si>
+    <t>Needs an SMTP provider.</t>
+  </si>
+  <si>
+    <t>BE-06</t>
+  </si>
+  <si>
+    <t>Add an audit log</t>
+  </si>
+  <si>
+    <t>Every status transition and every admin or supplier write should be recorded.</t>
+  </si>
+  <si>
+    <t>Specified in the backend spec.</t>
+  </si>
+  <si>
+    <t>BE-08</t>
+  </si>
+  <si>
+    <t>Decide money representation before any data lands</t>
+  </si>
+  <si>
+    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
+  </si>
+  <si>
+    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
+  </si>
+  <si>
+    <t>BE-10</t>
+  </si>
+  <si>
+    <t>Retire the catalogue snapshot endpoint</t>
+  </si>
+  <si>
+    <t>Client components fetch the whole catalogue from /api/v1/catalog/snapshot. Fine for 71 products; not for thousands. Goes away when the cart moves server-side.</t>
+  </si>
+  <si>
+    <t>Phase 3 removes the need.</t>
+  </si>
+  <si>
+    <t>BE-12</t>
+  </si>
+  <si>
+    <t>Merge a guest cart into the user cart on sign-in</t>
+  </si>
+  <si>
+    <t>Carts are keyed by a cookie so a visitor can shop before signing in. The merge on sign-in is specified but cannot be built until auth exists.</t>
+  </si>
+  <si>
+    <t>Cart cookie: aussiemed_cart, httpOnly, 30 day lifetime — OUR INVENTED VALUES.</t>
+  </si>
+  <si>
+    <t>BE-14</t>
+  </si>
+  <si>
+    <t>Confirm the default order and invoice status</t>
+  </si>
+  <si>
+    <t>OUR DECISION: new orders are Pending and each supplier invoice is Pending. The real workflow — who moves an order to Processing, and when an invoice becomes Issued — is not defined.</t>
+  </si>
+  <si>
+    <t>Order statuses available: Pending, Processing, Dispatched, Delivered, Cancelled.</t>
+  </si>
+  <si>
+    <t>DA-02</t>
+  </si>
+  <si>
+    <t>Verify the product-to-category mapping</t>
+  </si>
+  <si>
+    <t>The extraction had no product-category link at all. All 11 real products were mapped by hand from their names.</t>
+  </si>
+  <si>
+    <t>146 categories exist; the mapping is ours and unverified.</t>
+  </si>
+  <si>
+    <t>DA-05</t>
+  </si>
+  <si>
+    <t>Approve the product descriptions</t>
+  </si>
+  <si>
+    <t>The source had no descriptions. Eleven were written from the product names and need approval before launch.</t>
+  </si>
+  <si>
+    <t>Placeholder products carry generated filler text.</t>
+  </si>
+  <si>
+    <t>DA-07</t>
+  </si>
+  <si>
+    <t>Supply the hero banner image</t>
+  </si>
+  <si>
+    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured — only Brand, Category, Product and WebHtml folders were mirrored.</t>
+  </si>
+  <si>
+    <t>A genuine AussieMed CMS image stands in.</t>
+  </si>
+  <si>
+    <t>DA-08</t>
+  </si>
+  <si>
+    <t>Obtain Gilroy Regular and Medium</t>
+  </si>
+  <si>
+    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
+  </si>
+  <si>
+    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
+  </si>
+  <si>
+    <t>DA-10</t>
+  </si>
+  <si>
+    <t>Supply real pack and carton structures</t>
+  </si>
+  <si>
+    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
+  </si>
+  <si>
+    <t>Pack is the purchasable unit; getting it wrong misprices every carton.</t>
+  </si>
+  <si>
+    <t>DA-11</t>
+  </si>
+  <si>
+    <t>Supply real variant data</t>
+  </si>
+  <si>
+    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
+  </si>
+  <si>
+    <t>Variant switching is not wired until sibling SKUs exist.</t>
+  </si>
+  <si>
+    <t>DA-12</t>
+  </si>
+  <si>
+    <t>Supply real product specifications</t>
+  </si>
+  <si>
+    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
+  </si>
+  <si>
+    <t>These become search filters later.</t>
+  </si>
+  <si>
+    <t>DA-13</t>
+  </si>
+  <si>
+    <t>Supply safety data sheets and spec sheets</t>
+  </si>
+  <si>
+    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
+  </si>
+  <si>
+    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
+  </si>
+  <si>
+    <t>DA-18</t>
+  </si>
+  <si>
+    <t>Product ids are derived from slugs</t>
+  </si>
+  <si>
+    <t>Carts and wishlists are stored in the browser against a product id. Ids are now hashed from the slug so they survive a re-seed, which means CHANGING A PRODUCT SLUG ORPHANS ANY SAVED CART LINE referencing it.</t>
+  </si>
+  <si>
+    <t>Resolved properly when the cart moves server-side and references SKU rows directly.</t>
+  </si>
+  <si>
+    <t>DA-19</t>
+  </si>
+  <si>
+    <t>Supplier email addresses are invented</t>
+  </si>
+  <si>
+    <t>The seed writes orders@&lt;supplier&gt;.example and accounts@&lt;supplier&gt;.example because secondaryEmail is mandatory. No supplier will receive anything at these addresses.</t>
+  </si>
+  <si>
+    <t>Both addresses are meant to receive order notifications once email exists.</t>
+  </si>
+  <si>
+    <t>FN-07</t>
+  </si>
+  <si>
+    <t>Variant switching is not wired</t>
+  </si>
+  <si>
+    <t>Size and colour chips display the current value; other options are disabled because sibling SKUs do not exist yet.</t>
+  </si>
+  <si>
+    <t>Needs the variant model in the database.</t>
+  </si>
+  <si>
+    <t>FN-08</t>
+  </si>
+  <si>
+    <t>Stock is a boolean</t>
+  </si>
+  <si>
+    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
+  </si>
+  <si>
+    <t>Decide whether real stock levels are needed.</t>
+  </si>
+  <si>
+    <t>FN-09</t>
+  </si>
+  <si>
+    <t>Decide on expiry and short-dated stock</t>
+  </si>
+  <si>
+    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
+  </si>
+  <si>
+    <t>Schema-shaping — decide before the backend is built.</t>
+  </si>
+  <si>
+    <t>IN-01</t>
+  </si>
+  <si>
+    <t>Choose a hosting target</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. The site runs locally only.</t>
+  </si>
+  <si>
+    <t>Deliberately deferred until the build is approved.</t>
+  </si>
+  <si>
+    <t>IN-02</t>
+  </si>
+  <si>
+    <t>Choose the database</t>
+  </si>
+  <si>
+    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
+  </si>
+  <si>
+    <t>IN-03</t>
+  </si>
+  <si>
+    <t>Choose an SMTP provider and sending domain</t>
+  </si>
+  <si>
+    <t>Required for every transactional email.</t>
+  </si>
+  <si>
+    <t>Must not be the misspelled assuiemed.com domain.</t>
+  </si>
+  <si>
+    <t>IN-04</t>
+  </si>
+  <si>
+    <t>Decide on a payment gateway</t>
+  </si>
+  <si>
+    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
+  </si>
+  <si>
+    <t>LG-05</t>
+  </si>
+  <si>
+    <t>Transfer the theme licence</t>
+  </si>
+  <si>
+    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
+  </si>
+  <si>
+    <t>Repository must stay private because of this.</t>
+  </si>
+  <si>
+    <t>LG-06</t>
+  </si>
+  <si>
+    <t>Supply company registration details</t>
+  </si>
+  <si>
+    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
+  </si>
+  <si>
+    <t>AC-08</t>
+  </si>
+  <si>
+    <t>Confirm the rounding policy</t>
+  </si>
+  <si>
+    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Verified by test; needs sign-off that the method is acceptable.</t>
+  </si>
+  <si>
+    <t>AC-10</t>
+  </si>
+  <si>
+    <t>Confirm the default price display</t>
+  </si>
+  <si>
+    <t>Prices default to Ex. VAT with a toggle to Inc. VAT.</t>
+  </si>
+  <si>
+    <t>Preference persists per browser.</t>
+  </si>
+  <si>
+    <t>BE-13</t>
+  </si>
+  <si>
+    <t>Expire abandoned guest carts</t>
+  </si>
+  <si>
+    <t>Cart rows are never cleaned up. Every visitor who adds an item creates one that lives forever.</t>
+  </si>
+  <si>
+    <t>The spec wants abandoned carts over 24h reportable under Admin &gt; Marketing, so expiry and that report should be designed together.</t>
+  </si>
+  <si>
+    <t>DA-04</t>
+  </si>
+  <si>
+    <t>Wrong image on the scrub top</t>
+  </si>
+  <si>
+    <t>The product's primary image was a stock photo of a pocket watch. Excluded from the build; the file is still in public/products/.</t>
+  </si>
+  <si>
+    <t>Suggests image uploads were not being checked in the old admin.</t>
+  </si>
+  <si>
+    <t>DA-09</t>
+  </si>
+  <si>
+    <t>Explain the disappearing product</t>
+  </si>
+  <si>
+    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
+  </si>
+  <si>
+    <t>Evidence of a real defect in the old platform. Worth understanding before trusting any migrated data.</t>
+  </si>
+  <si>
+    <t>DA-14</t>
+  </si>
+  <si>
+    <t>Confirm the brand list</t>
+  </si>
+  <si>
+    <t>Brands were assigned by reading product names.</t>
+  </si>
+  <si>
+    <t>Eleven real brands identified.</t>
+  </si>
+  <si>
+    <t>DA-15</t>
+  </si>
+  <si>
+    <t>Decide on duplicate categories</t>
+  </si>
+  <si>
+    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
+  </si>
+  <si>
+    <t>Affected: Respiratory Management, Oral Care, Monitoring &amp; Testing, Dispensers, Bags, Medicine.</t>
+  </si>
+  <si>
+    <t>DA-16</t>
+  </si>
+  <si>
+    <t>Confirm the missing department</t>
+  </si>
+  <si>
+    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
+  </si>
+  <si>
+    <t>Confirm this is intentional rather than lost.</t>
+  </si>
+  <si>
+    <t>FN-10</t>
+  </si>
+  <si>
+    <t>Search is client-side only</t>
+  </si>
+  <si>
+    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
+  </si>
+  <si>
+    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
+  </si>
+  <si>
+    <t>IN-05</t>
+  </si>
+  <si>
+    <t>Supply Google and Facebook OAuth keys</t>
+  </si>
+  <si>
+    <t>Social login endpoints currently return 501.</t>
+  </si>
+  <si>
+    <t>IN-08</t>
+  </si>
+  <si>
+    <t>Correct the git author name</t>
+  </si>
+  <si>
+    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
+  </si>
+  <si>
+    <t>Fixable with git config user.name and an amend.</t>
+  </si>
+  <si>
+    <t>IN-09</t>
+  </si>
+  <si>
+    <t>Set up continuous integration</t>
+  </si>
+  <si>
+    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
+  </si>
+  <si>
+    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
+  </si>
+  <si>
+    <t>IN-10</t>
+  </si>
+  <si>
+    <t>Plan backups and disaster recovery</t>
+  </si>
+  <si>
+    <t>No backup strategy exists for the database or uploaded files.</t>
+  </si>
+  <si>
+    <t>Relevant once there is a real database.</t>
+  </si>
+  <si>
+    <t>LG-04</t>
+  </si>
+  <si>
+    <t>Approve the About / Contact / Order Support copy</t>
+  </si>
+  <si>
+    <t>All placeholder text.</t>
+  </si>
+  <si>
+    <t>Pages carry a visible placeholder notice.</t>
+  </si>
+  <si>
+    <t>DF-01</t>
+  </si>
+  <si>
+    <t>Industry taxonomy</t>
+  </si>
+  <si>
+    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
+  </si>
+  <si>
+    <t>Additive; adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-02</t>
+  </si>
+  <si>
+    <t>Subscribe and Save</t>
+  </si>
+  <si>
+    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
+  </si>
+  <si>
+    <t>Needs the backend.</t>
+  </si>
+  <si>
+    <t>DF-03</t>
+  </si>
+  <si>
+    <t>Frequently bought together</t>
+  </si>
+  <si>
+    <t>Bundle suggestion with a combined total and one action to add all.</t>
+  </si>
+  <si>
+    <t>Adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-04</t>
+  </si>
+  <si>
+    <t>Quick view</t>
+  </si>
+  <si>
+    <t>View a product from the listing without a page load.</t>
+  </si>
+  <si>
+    <t>DF-05</t>
+  </si>
+  <si>
+    <t>Downloadable PDF catalogues</t>
+  </si>
+  <si>
+    <t>Still how a lot of trade buying happens.</t>
+  </si>
+  <si>
+    <t>Needs the actual catalogue files.</t>
+  </si>
+  <si>
+    <t>BE-07</t>
+  </si>
+  <si>
+    <t>Seed the database from the catalogue</t>
+  </si>
+  <si>
+    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
+  </si>
+  <si>
+    <t>BE-09</t>
+  </si>
+  <si>
+    <t>Point the storefront at the database</t>
+  </si>
+  <si>
+    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
+  </si>
+  <si>
+    <t>query.ts was untouched — it never knew where products came from.</t>
+  </si>
+  <si>
+    <t>DN-01</t>
+  </si>
+  <si>
+    <t>Currency rendering</t>
+  </si>
+  <si>
+    <t>Was rendering the Arabic symbol and 4 decimals. Now always the English string AED with exactly 2 decimals, enforced by test and by a grep check.</t>
+  </si>
+  <si>
+    <t>Fixed in the initial build.</t>
+  </si>
+  <si>
+    <t>DN-02</t>
+  </si>
+  <si>
+    <t>Integer quantities</t>
+  </si>
+  <si>
+    <t>Quantities were rendering as decimals such as 3.00.</t>
+  </si>
+  <si>
+    <t>DN-03</t>
+  </si>
+  <si>
+    <t>Category filtering</t>
+  </si>
+  <si>
+    <t>Every category link redirected to the full product list. Filtering now works, including rolling a department up to everything beneath it.</t>
+  </si>
+  <si>
+    <t>DN-04</t>
+  </si>
+  <si>
+    <t>Category counts matching results</t>
+  </si>
+  <si>
+    <t>Admin and storefront counts could diverge. Counts are now derived from the same query that lists the products.</t>
+  </si>
+  <si>
+    <t>Asserted in the data checks and the API contract checks.</t>
+  </si>
+  <si>
+    <t>DN-05</t>
+  </si>
+  <si>
+    <t>Category slug collisions</t>
+  </si>
+  <si>
+    <t>Six categories shared a slug with another category, so one was unreachable and the other answered to the wrong name.</t>
+  </si>
+  <si>
+    <t>Found by the API contract check. Slugs are now unique tree-wide and asserted.</t>
+  </si>
+  <si>
+    <t>DN-06</t>
+  </si>
+  <si>
+    <t>Per-supplier invoicing</t>
+  </si>
+  <si>
+    <t>An order spanning N suppliers now produces exactly N invoices under one reference number, with per-invoice VAT summing to the order VAT without drift.</t>
+  </si>
+  <si>
+    <t>Verified end to end in the browser and by test.</t>
+  </si>
+  <si>
+    <t>DN-11</t>
+  </si>
+  <si>
+    <t>Pack and unit of measure model</t>
+  </si>
+  <si>
+    <t>The same line sells by the box and by the carton at different prices. Cart lines are keyed by product and pack so they never merge.</t>
+  </si>
+  <si>
+    <t>Outers are asserted to beat buying their contents separately.</t>
+  </si>
+  <si>
+    <t>DN-14</t>
+  </si>
+  <si>
+    <t>Control characters in generated code</t>
+  </si>
+  <si>
+    <t>Shell escaping wrote literal backspace bytes into regex rules, so every packaging and variant rule silently matched nothing while looking correct in every editor.</t>
+  </si>
+  <si>
+    <t>Found via od. A data check now asserts each variant selection matches an option.</t>
+  </si>
+  <si>
+    <t>DN-16</t>
+  </si>
+  <si>
+    <t>Database schema designed and migrated</t>
+  </si>
+  <si>
+    <t>Thirty tables covering catalogue, packs as SKUs, variants, attributes, documents, batches, orders, per-supplier invoices, quotes, bulk upload and audit.</t>
+  </si>
+  <si>
+    <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
+  </si>
+  <si>
+    <t>DN-17</t>
+  </si>
+  <si>
+    <t>Typecheck was silently passing on a stale cache</t>
+  </si>
+  <si>
+    <t>tsc ran with incremental caching and reported no errors while real type errors existed in the tree. Every earlier typecheck-clean claim was suspect.</t>
+  </si>
+  <si>
+    <t>npm run typecheck now runs with --incremental false. Caught seven genuine errors the moment it was disabled.</t>
+  </si>
+  <si>
+    <t>DN-18</t>
+  </si>
+  <si>
+    <t>Cart moved to the server</t>
+  </si>
+  <si>
+    <t>The cart was localStorage, so the browser held prices. It is now database rows priced entirely on the server; the client cannot tell the server what anything costs.</t>
+  </si>
+  <si>
+    <t>Guest carts are cookie-keyed. The catalogue snapshot endpoint stays until the wishlist and quote cart follow.</t>
+  </si>
+  <si>
+    <t>DN-19</t>
+  </si>
+  <si>
+    <t>Checkout writes real orders</t>
+  </si>
+  <si>
+    <t>One transaction creates the order, one invoice per supplier and every line, or nothing at all. Reference numbers are allocated server-side inside that transaction.</t>
+  </si>
+  <si>
+    <t>Verified in a browser end to end, and by 14 order invariants in npm run db:check.</t>
+  </si>
+  <si>
     <t>FN-01</t>
   </si>
   <si>
     <t>Checkout does not submit an order</t>
   </si>
   <si>
-    <t>The form is complete and the flow is reviewable, but nothing is created and no payment is taken. A preview reference number is generated in the browser.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend. States this on screen.</t>
-  </si>
-  <si>
-    <t>FN-02</t>
-  </si>
-  <si>
-    <t>Quote requests are not delivered</t>
-  </si>
-  <si>
-    <t>Captured in the browser only.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend and an email provider.</t>
-  </si>
-  <si>
-    <t>FN-03</t>
-  </si>
-  <si>
-    <t>Bulk buy enquiries are not delivered</t>
-  </si>
-  <si>
-    <t>FN-04</t>
-  </si>
-  <si>
-    <t>Notify Me does not register a subscription</t>
-  </si>
-  <si>
-    <t>Captured locally. The restock email flow does not exist.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend.</t>
-  </si>
-  <si>
-    <t>FN-05</t>
-  </si>
-  <si>
-    <t>Sign-in is a demo flag</t>
-  </si>
-  <si>
-    <t>A localStorage boolean opens a fabricated session. Real auth is email OTP per the backend spec.</t>
-  </si>
-  <si>
-    <t>Must be replaced wholesale rather than extended.</t>
-  </si>
-  <si>
-    <t>FN-06</t>
-  </si>
-  <si>
-    <t>Account history is fabricated</t>
-  </si>
-  <si>
-    <t>The customer, three orders and their invoices are invented so the account screens could be built and reviewed.</t>
-  </si>
-  <si>
-    <t>Every account page carries a visible notice.</t>
-  </si>
-  <si>
-    <t>IN-06</t>
-  </si>
-  <si>
-    <t>Remove noindex before launch</t>
-  </si>
-  <si>
-    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
-  </si>
-  <si>
-    <t>Must be removed deliberately at launch — and only then.</t>
-  </si>
-  <si>
-    <t>IN-07</t>
-  </si>
-  <si>
-    <t>Confirm the GitHub repository is private</t>
-  </si>
-  <si>
-    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
-  </si>
-  <si>
-    <t>https://github.com/musawi1989/aussiemed</t>
-  </si>
-  <si>
-    <t>LG-01</t>
-  </si>
-  <si>
-    <t>Supply terms and conditions</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
-  </si>
-  <si>
-    <t>Page exists and says so on screen.</t>
-  </si>
-  <si>
-    <t>LG-02</t>
-  </si>
-  <si>
-    <t>Supply the privacy policy</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
-  </si>
-  <si>
-    <t>LG-03</t>
-  </si>
-  <si>
-    <t>Confirm the contact email address</t>
-  </si>
-  <si>
-    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
-  </si>
-  <si>
-    <t>Also determines the sending domain for transactional email.</t>
-  </si>
-  <si>
-    <t>AC-05</t>
-  </si>
-  <si>
-    <t>Confirm the VAT rate and whether it must be configurable</t>
-  </si>
-  <si>
-    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>Rate must be stored on the order at the time it is placed.</t>
-  </si>
-  <si>
-    <t>AC-06</t>
-  </si>
-  <si>
-    <t>Approve the reference number format</t>
-  </si>
-  <si>
-    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
-  </si>
-  <si>
-    <t>Wording is fixed as Reference number, never order number.</t>
-  </si>
-  <si>
-    <t>AC-07</t>
-  </si>
-  <si>
-    <t>Approve the supplier invoice numbering</t>
-  </si>
-  <si>
-    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
-  </si>
-  <si>
-    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
-  </si>
-  <si>
-    <t>AC-09</t>
-  </si>
-  <si>
-    <t>Decide payment terms and credit accounts</t>
-  </si>
-  <si>
-    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
-  </si>
-  <si>
-    <t>Affects the schema — decide before the backend.</t>
-  </si>
-  <si>
-    <t>BE-04</t>
-  </si>
-  <si>
-    <t>Build comma-safe .xlsx bulk upload</t>
-  </si>
-  <si>
-    <t>Parsed natively with exceljs, never by splitting on commas — that is what broke comma-containing category names.</t>
-  </si>
-  <si>
-    <t>Unknown brands must be reported per row, never skipped silently.</t>
-  </si>
-  <si>
-    <t>BE-05</t>
-  </si>
-  <si>
-    <t>Build the email flows</t>
-  </si>
-  <si>
-    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
-  </si>
-  <si>
-    <t>Needs an SMTP provider.</t>
-  </si>
-  <si>
-    <t>BE-06</t>
-  </si>
-  <si>
-    <t>Add an audit log</t>
-  </si>
-  <si>
-    <t>Every status transition and every admin or supplier write should be recorded.</t>
-  </si>
-  <si>
-    <t>Specified in the backend spec.</t>
-  </si>
-  <si>
-    <t>BE-08</t>
-  </si>
-  <si>
-    <t>Decide money representation before any data lands</t>
-  </si>
-  <si>
-    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
-  </si>
-  <si>
-    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
-  </si>
-  <si>
-    <t>BE-10</t>
-  </si>
-  <si>
-    <t>Retire the catalogue snapshot endpoint</t>
-  </si>
-  <si>
-    <t>Client components fetch the whole catalogue from /api/v1/catalog/snapshot. Fine for 71 products; not for thousands. Goes away when the cart moves server-side.</t>
-  </si>
-  <si>
-    <t>Phase 3 removes the need.</t>
-  </si>
-  <si>
-    <t>DA-02</t>
-  </si>
-  <si>
-    <t>Verify the product-to-category mapping</t>
-  </si>
-  <si>
-    <t>The extraction had no product-category link at all. All 11 real products were mapped by hand from their names.</t>
-  </si>
-  <si>
-    <t>146 categories exist; the mapping is ours and unverified.</t>
-  </si>
-  <si>
-    <t>DA-05</t>
-  </si>
-  <si>
-    <t>Approve the product descriptions</t>
-  </si>
-  <si>
-    <t>The source had no descriptions. Eleven were written from the product names and need approval before launch.</t>
-  </si>
-  <si>
-    <t>Placeholder products carry generated filler text.</t>
-  </si>
-  <si>
-    <t>DA-07</t>
-  </si>
-  <si>
-    <t>Supply the hero banner image</t>
-  </si>
-  <si>
-    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured — only Brand, Category, Product and WebHtml folders were mirrored.</t>
-  </si>
-  <si>
-    <t>A genuine AussieMed CMS image stands in.</t>
-  </si>
-  <si>
-    <t>DA-08</t>
-  </si>
-  <si>
-    <t>Obtain Gilroy Regular and Medium</t>
-  </si>
-  <si>
-    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
-  </si>
-  <si>
-    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
-  </si>
-  <si>
-    <t>DA-10</t>
-  </si>
-  <si>
-    <t>Supply real pack and carton structures</t>
-  </si>
-  <si>
-    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
-  </si>
-  <si>
-    <t>Pack is the purchasable unit; getting it wrong misprices every carton.</t>
-  </si>
-  <si>
-    <t>DA-11</t>
-  </si>
-  <si>
-    <t>Supply real variant data</t>
-  </si>
-  <si>
-    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
-  </si>
-  <si>
-    <t>Variant switching is not wired until sibling SKUs exist.</t>
-  </si>
-  <si>
-    <t>DA-12</t>
-  </si>
-  <si>
-    <t>Supply real product specifications</t>
-  </si>
-  <si>
-    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
-  </si>
-  <si>
-    <t>These become search filters later.</t>
-  </si>
-  <si>
-    <t>DA-13</t>
-  </si>
-  <si>
-    <t>Supply safety data sheets and spec sheets</t>
-  </si>
-  <si>
-    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
-  </si>
-  <si>
-    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
-  </si>
-  <si>
-    <t>DA-18</t>
-  </si>
-  <si>
-    <t>Product ids are derived from slugs</t>
-  </si>
-  <si>
-    <t>Carts and wishlists are stored in the browser against a product id. Ids are now hashed from the slug so they survive a re-seed, which means CHANGING A PRODUCT SLUG ORPHANS ANY SAVED CART LINE referencing it.</t>
-  </si>
-  <si>
-    <t>Resolved properly when the cart moves server-side and references SKU rows directly.</t>
-  </si>
-  <si>
-    <t>FN-07</t>
-  </si>
-  <si>
-    <t>Variant switching is not wired</t>
-  </si>
-  <si>
-    <t>Size and colour chips display the current value; other options are disabled because sibling SKUs do not exist yet.</t>
-  </si>
-  <si>
-    <t>Needs the variant model in the database.</t>
-  </si>
-  <si>
-    <t>FN-08</t>
-  </si>
-  <si>
-    <t>Stock is a boolean</t>
-  </si>
-  <si>
-    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
-  </si>
-  <si>
-    <t>Decide whether real stock levels are needed.</t>
-  </si>
-  <si>
-    <t>FN-09</t>
-  </si>
-  <si>
-    <t>Decide on expiry and short-dated stock</t>
-  </si>
-  <si>
-    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
-  </si>
-  <si>
-    <t>Schema-shaping — decide before the backend is built.</t>
-  </si>
-  <si>
-    <t>IN-01</t>
-  </si>
-  <si>
-    <t>Choose a hosting target</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. The site runs locally only.</t>
-  </si>
-  <si>
-    <t>Deliberately deferred until the build is approved.</t>
-  </si>
-  <si>
-    <t>IN-02</t>
-  </si>
-  <si>
-    <t>Choose the database</t>
-  </si>
-  <si>
-    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
-  </si>
-  <si>
-    <t>IN-03</t>
-  </si>
-  <si>
-    <t>Choose an SMTP provider and sending domain</t>
-  </si>
-  <si>
-    <t>Required for every transactional email.</t>
-  </si>
-  <si>
-    <t>Must not be the misspelled assuiemed.com domain.</t>
-  </si>
-  <si>
-    <t>IN-04</t>
-  </si>
-  <si>
-    <t>Decide on a payment gateway</t>
-  </si>
-  <si>
-    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
-  </si>
-  <si>
-    <t>LG-05</t>
-  </si>
-  <si>
-    <t>Transfer the theme licence</t>
-  </si>
-  <si>
-    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
-  </si>
-  <si>
-    <t>Repository must stay private because of this.</t>
-  </si>
-  <si>
-    <t>LG-06</t>
-  </si>
-  <si>
-    <t>Supply company registration details</t>
-  </si>
-  <si>
-    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
-  </si>
-  <si>
-    <t>AC-08</t>
-  </si>
-  <si>
-    <t>Confirm the rounding policy</t>
-  </si>
-  <si>
-    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>Verified by test; needs sign-off that the method is acceptable.</t>
-  </si>
-  <si>
-    <t>AC-10</t>
-  </si>
-  <si>
-    <t>Confirm the default price display</t>
-  </si>
-  <si>
-    <t>Prices default to Ex. VAT with a toggle to Inc. VAT.</t>
-  </si>
-  <si>
-    <t>Preference persists per browser.</t>
-  </si>
-  <si>
-    <t>DA-04</t>
-  </si>
-  <si>
-    <t>Wrong image on the scrub top</t>
-  </si>
-  <si>
-    <t>The product's primary image was a stock photo of a pocket watch. Excluded from the build; the file is still in public/products/.</t>
-  </si>
-  <si>
-    <t>Suggests image uploads were not being checked in the old admin.</t>
-  </si>
-  <si>
-    <t>DA-09</t>
-  </si>
-  <si>
-    <t>Explain the disappearing product</t>
-  </si>
-  <si>
-    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
-  </si>
-  <si>
-    <t>Evidence of a real defect in the old platform. Worth understanding before trusting any migrated data.</t>
-  </si>
-  <si>
-    <t>DA-14</t>
-  </si>
-  <si>
-    <t>Confirm the brand list</t>
-  </si>
-  <si>
-    <t>Brands were assigned by reading product names.</t>
-  </si>
-  <si>
-    <t>Eleven real brands identified.</t>
-  </si>
-  <si>
-    <t>DA-15</t>
-  </si>
-  <si>
-    <t>Decide on duplicate categories</t>
-  </si>
-  <si>
-    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
-  </si>
-  <si>
-    <t>Affected: Respiratory Management, Oral Care, Monitoring &amp; Testing, Dispensers, Bags, Medicine.</t>
-  </si>
-  <si>
-    <t>DA-16</t>
-  </si>
-  <si>
-    <t>Confirm the missing department</t>
-  </si>
-  <si>
-    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
-  </si>
-  <si>
-    <t>Confirm this is intentional rather than lost.</t>
-  </si>
-  <si>
-    <t>FN-10</t>
-  </si>
-  <si>
-    <t>Search is client-side only</t>
-  </si>
-  <si>
-    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
-  </si>
-  <si>
-    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
-  </si>
-  <si>
-    <t>IN-05</t>
-  </si>
-  <si>
-    <t>Supply Google and Facebook OAuth keys</t>
-  </si>
-  <si>
-    <t>Social login endpoints currently return 501.</t>
-  </si>
-  <si>
-    <t>IN-08</t>
-  </si>
-  <si>
-    <t>Correct the git author name</t>
-  </si>
-  <si>
-    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
-  </si>
-  <si>
-    <t>Fixable with git config user.name and an amend.</t>
-  </si>
-  <si>
-    <t>IN-09</t>
-  </si>
-  <si>
-    <t>Set up continuous integration</t>
-  </si>
-  <si>
-    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
-  </si>
-  <si>
-    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
-  </si>
-  <si>
-    <t>IN-10</t>
-  </si>
-  <si>
-    <t>Plan backups and disaster recovery</t>
-  </si>
-  <si>
-    <t>No backup strategy exists for the database or uploaded files.</t>
-  </si>
-  <si>
-    <t>Relevant once there is a real database.</t>
-  </si>
-  <si>
-    <t>LG-04</t>
-  </si>
-  <si>
-    <t>Approve the About / Contact / Order Support copy</t>
-  </si>
-  <si>
-    <t>All placeholder text.</t>
-  </si>
-  <si>
-    <t>Pages carry a visible placeholder notice.</t>
-  </si>
-  <si>
-    <t>DF-01</t>
-  </si>
-  <si>
-    <t>Industry taxonomy</t>
-  </si>
-  <si>
-    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
-  </si>
-  <si>
-    <t>Additive; adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-02</t>
-  </si>
-  <si>
-    <t>Subscribe and Save</t>
-  </si>
-  <si>
-    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
-  </si>
-  <si>
-    <t>Needs the backend.</t>
-  </si>
-  <si>
-    <t>DF-03</t>
-  </si>
-  <si>
-    <t>Frequently bought together</t>
-  </si>
-  <si>
-    <t>Bundle suggestion with a combined total and one action to add all.</t>
-  </si>
-  <si>
-    <t>Adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-04</t>
-  </si>
-  <si>
-    <t>Quick view</t>
-  </si>
-  <si>
-    <t>View a product from the listing without a page load.</t>
-  </si>
-  <si>
-    <t>DF-05</t>
-  </si>
-  <si>
-    <t>Downloadable PDF catalogues</t>
-  </si>
-  <si>
-    <t>Still how a lot of trade buying happens.</t>
-  </si>
-  <si>
-    <t>Needs the actual catalogue files.</t>
-  </si>
-  <si>
-    <t>BE-07</t>
-  </si>
-  <si>
-    <t>Seed the database from the catalogue</t>
-  </si>
-  <si>
-    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
-  </si>
-  <si>
-    <t>BE-09</t>
-  </si>
-  <si>
-    <t>Point the storefront at the database</t>
-  </si>
-  <si>
-    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
-  </si>
-  <si>
-    <t>query.ts was untouched — it never knew where products came from.</t>
-  </si>
-  <si>
-    <t>DN-01</t>
-  </si>
-  <si>
-    <t>Currency rendering</t>
-  </si>
-  <si>
-    <t>Was rendering the Arabic symbol and 4 decimals. Now always the English string AED with exactly 2 decimals, enforced by test and by a grep check.</t>
-  </si>
-  <si>
-    <t>Fixed in the initial build.</t>
-  </si>
-  <si>
-    <t>DN-02</t>
-  </si>
-  <si>
-    <t>Integer quantities</t>
-  </si>
-  <si>
-    <t>Quantities were rendering as decimals such as 3.00.</t>
-  </si>
-  <si>
-    <t>DN-03</t>
-  </si>
-  <si>
-    <t>Category filtering</t>
-  </si>
-  <si>
-    <t>Every category link redirected to the full product list. Filtering now works, including rolling a department up to everything beneath it.</t>
-  </si>
-  <si>
-    <t>DN-04</t>
-  </si>
-  <si>
-    <t>Category counts matching results</t>
-  </si>
-  <si>
-    <t>Admin and storefront counts could diverge. Counts are now derived from the same query that lists the products.</t>
-  </si>
-  <si>
-    <t>Asserted in the data checks and the API contract checks.</t>
-  </si>
-  <si>
-    <t>DN-05</t>
-  </si>
-  <si>
-    <t>Category slug collisions</t>
-  </si>
-  <si>
-    <t>Six categories shared a slug with another category, so one was unreachable and the other answered to the wrong name.</t>
-  </si>
-  <si>
-    <t>Found by the API contract check. Slugs are now unique tree-wide and asserted.</t>
-  </si>
-  <si>
-    <t>DN-06</t>
-  </si>
-  <si>
-    <t>Per-supplier invoicing</t>
-  </si>
-  <si>
-    <t>An order spanning N suppliers now produces exactly N invoices under one reference number, with per-invoice VAT summing to the order VAT without drift.</t>
-  </si>
-  <si>
-    <t>Verified end to end in the browser and by test.</t>
-  </si>
-  <si>
-    <t>DN-11</t>
-  </si>
-  <si>
-    <t>Pack and unit of measure model</t>
-  </si>
-  <si>
-    <t>The same line sells by the box and by the carton at different prices. Cart lines are keyed by product and pack so they never merge.</t>
-  </si>
-  <si>
-    <t>Outers are asserted to beat buying their contents separately.</t>
-  </si>
-  <si>
-    <t>DN-14</t>
-  </si>
-  <si>
-    <t>Control characters in generated code</t>
-  </si>
-  <si>
-    <t>Shell escaping wrote literal backspace bytes into regex rules, so every packaging and variant rule silently matched nothing while looking correct in every editor.</t>
-  </si>
-  <si>
-    <t>Found via od. A data check now asserts each variant selection matches an option.</t>
-  </si>
-  <si>
-    <t>DN-16</t>
-  </si>
-  <si>
-    <t>Database schema designed and migrated</t>
-  </si>
-  <si>
-    <t>Thirty tables covering catalogue, packs as SKUs, variants, attributes, documents, batches, orders, per-supplier invoices, quotes, bulk upload and audit.</t>
-  </si>
-  <si>
-    <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
-  </si>
-  <si>
-    <t>DN-17</t>
-  </si>
-  <si>
-    <t>Typecheck was silently passing on a stale cache</t>
-  </si>
-  <si>
-    <t>tsc ran with incremental caching and reported no errors while real type errors existed in the tree. Every earlier typecheck-clean claim was suspect.</t>
-  </si>
-  <si>
-    <t>npm run typecheck now runs with --incremental false. Caught seven genuine errors the moment it was disabled.</t>
+    <t>Done. Checkout writes a real order in one transaction, with one invoice per supplier and a server-allocated reference number.</t>
+  </si>
+  <si>
+    <t>Payment is still not taken and no email is sent.</t>
   </si>
   <si>
     <t>DN-07</t>
@@ -1632,7 +1752,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1640,7 +1760,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1648,7 +1768,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1682,7 +1802,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1690,7 +1810,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1708,7 +1828,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1716,7 +1836,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1732,7 +1852,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1750,7 +1870,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1758,7 +1878,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1774,7 +1894,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1782,7 +1902,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1816,7 +1936,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2041,7 +2161,7 @@
         <v>62</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>63</v>
@@ -2049,8 +2169,8 @@
       <c r="D9" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>12</v>
+      <c r="E9" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>34</v>
@@ -2145,7 +2265,7 @@
         <v>78</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>79</v>
@@ -2153,8 +2273,8 @@
       <c r="D13" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>15</v>
+      <c r="E13" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>34</v>
@@ -2535,7 +2655,7 @@
         <v>136</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>137</v>
@@ -2543,8 +2663,8 @@
       <c r="D28" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>15</v>
+      <c r="E28" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>122</v>
@@ -2561,7 +2681,7 @@
         <v>140</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>141</v>
@@ -2569,8 +2689,8 @@
       <c r="D29" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>15</v>
+      <c r="E29" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>122</v>
@@ -2587,7 +2707,7 @@
         <v>144</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>145</v>
@@ -2595,8 +2715,8 @@
       <c r="D30" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>15</v>
+      <c r="E30" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>122</v>
@@ -2621,8 +2741,8 @@
       <c r="D31" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>13</v>
+      <c r="E31" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>122</v>
@@ -2665,7 +2785,7 @@
         <v>156</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>157</v>
@@ -2673,8 +2793,8 @@
       <c r="D33" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>12</v>
+      <c r="E33" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>122</v>
@@ -2691,7 +2811,7 @@
         <v>160</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>161</v>
@@ -2700,7 +2820,7 @@
         <v>162</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>122</v>
@@ -2717,7 +2837,7 @@
         <v>164</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>165</v>
@@ -2725,8 +2845,8 @@
       <c r="D35" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>12</v>
+      <c r="E35" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>122</v>
@@ -2743,7 +2863,7 @@
         <v>168</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>169</v>
@@ -2752,7 +2872,7 @@
         <v>170</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>122</v>
@@ -2769,7 +2889,7 @@
         <v>172</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>173</v>
@@ -2882,7 +3002,7 @@
         <v>190</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>122</v>
@@ -2899,7 +3019,7 @@
         <v>192</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>193</v>
@@ -2907,8 +3027,8 @@
       <c r="D42" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>15</v>
+      <c r="E42" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>122</v>
@@ -2925,7 +3045,7 @@
         <v>196</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>197</v>
@@ -2933,8 +3053,8 @@
       <c r="D43" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>15</v>
+      <c r="E43" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>122</v>
@@ -2951,7 +3071,7 @@
         <v>200</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>201</v>
@@ -2977,7 +3097,7 @@
         <v>204</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>205</v>
@@ -3003,7 +3123,7 @@
         <v>208</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>209</v>
@@ -3021,21 +3141,21 @@
         <v>35</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>2</v>
+        <v>211</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>12</v>
@@ -3047,24 +3167,24 @@
         <v>35</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>12</v>
+        <v>218</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>122</v>
@@ -3073,24 +3193,24 @@
         <v>35</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>2</v>
+        <v>219</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>122</v>
@@ -3099,21 +3219,21 @@
         <v>35</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>12</v>
@@ -3125,111 +3245,111 @@
         <v>35</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>2</v>
+        <v>227</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>228</v>
+        <v>12</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>228</v>
+        <v>234</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>233</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>228</v>
+      <c r="F53" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F54" s="10" t="s">
-        <v>228</v>
+      <c r="F54" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>241</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3237,7 +3357,7 @@
         <v>242</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>243</v>
@@ -3245,11 +3365,11 @@
       <c r="D55" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="E55" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>228</v>
+      <c r="E55" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>35</v>
@@ -3263,7 +3383,7 @@
         <v>246</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>247</v>
@@ -3274,34 +3394,34 @@
       <c r="E56" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F56" s="10" t="s">
-        <v>228</v>
+      <c r="F56" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>249</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="B57" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C57" s="6" t="s">
+      <c r="D57" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="E57" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>35</v>
@@ -3315,7 +3435,7 @@
         <v>254</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>255</v>
@@ -3323,11 +3443,11 @@
       <c r="D58" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="E58" s="6" t="s">
-        <v>15</v>
+      <c r="E58" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>35</v>
@@ -3341,7 +3461,7 @@
         <v>258</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>259</v>
@@ -3349,125 +3469,307 @@
       <c r="D59" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="E59" s="7" t="s">
-        <v>12</v>
+      <c r="E59" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>2</v>
+        <v>261</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>15</v>
+        <v>268</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>304</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H63"/>
+  <autoFilter ref="A1:H70"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3518,100 +3820,100 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>6</v>
@@ -3622,28 +3924,28 @@
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>292</v>
+        <v>320</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -3658,7 +3960,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3698,16 +4000,16 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>296</v>
+        <v>324</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
@@ -3716,24 +4018,24 @@
         <v>34</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>301</v>
+        <v>329</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>15</v>
@@ -3742,24 +4044,24 @@
         <v>34</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>304</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>307</v>
+        <v>335</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
@@ -3768,24 +4070,24 @@
         <v>34</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
@@ -3794,24 +4096,24 @@
         <v>34</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>15</v>
@@ -3820,24 +4122,24 @@
         <v>34</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>15</v>
@@ -3846,24 +4148,24 @@
         <v>34</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>318</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>319</v>
+        <v>347</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>15</v>
@@ -3872,24 +4174,24 @@
         <v>34</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>15</v>
@@ -3898,24 +4200,24 @@
         <v>34</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>299</v>
-      </c>
       <c r="C10" s="6" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>15</v>
@@ -3924,24 +4226,24 @@
         <v>34</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>15</v>
@@ -3950,24 +4252,24 @@
         <v>34</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>334</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>15</v>
@@ -3976,24 +4278,24 @@
         <v>34</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>15</v>
@@ -4002,102 +4304,102 @@
         <v>34</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>122</v>
+      <c r="F14" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>122</v>
+      <c r="F15" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>299</v>
+        <v>20</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>122</v>
+      <c r="F16" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>288</v>
+        <v>382</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>356</v>
+        <v>385</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>15</v>
@@ -4106,24 +4408,24 @@
         <v>122</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>15</v>
@@ -4132,24 +4434,24 @@
         <v>122</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>361</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>363</v>
+        <v>392</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>364</v>
+        <v>393</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>15</v>
@@ -4158,24 +4460,24 @@
         <v>122</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>365</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>15</v>
@@ -4184,14 +4486,92 @@
         <v>122</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>369</v>
+        <v>397</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>409</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H20"/>
+  <autoFilter ref="A1:H23"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="447">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -85,6 +85,9 @@
     <t>Infrastructure</t>
   </si>
   <si>
+    <t>Security</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
@@ -202,967 +205,1075 @@
     <t>Approval is an admin-only transition enforced in the service layer.</t>
   </si>
   <si>
+    <t>DA-01</t>
+  </si>
+  <si>
+    <t>Supply the real product catalogue</t>
+  </si>
+  <si>
+    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
+  </si>
+  <si>
+    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
+  </si>
+  <si>
+    <t>DA-03</t>
+  </si>
+  <si>
+    <t>Supply product photography</t>
+  </si>
+  <si>
+    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
+  </si>
+  <si>
+    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
+  </si>
+  <si>
+    <t>DA-06</t>
+  </si>
+  <si>
+    <t>Supply the real supplier list</t>
+  </si>
+  <si>
+    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
+  </si>
+  <si>
+    <t>All are flagged isPlaceholder in the data.</t>
+  </si>
+  <si>
+    <t>DA-17</t>
+  </si>
+  <si>
+    <t>Replace the test supplier attribution</t>
+  </si>
+  <si>
+    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
+  </si>
+  <si>
+    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
+  </si>
+  <si>
+    <t>FN-02</t>
+  </si>
+  <si>
+    <t>Quote requests are not delivered</t>
+  </si>
+  <si>
+    <t>Captured in the browser only.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend and an email provider.</t>
+  </si>
+  <si>
+    <t>FN-03</t>
+  </si>
+  <si>
+    <t>Bulk buy enquiries are not delivered</t>
+  </si>
+  <si>
+    <t>FN-04</t>
+  </si>
+  <si>
+    <t>Notify Me does not register a subscription</t>
+  </si>
+  <si>
+    <t>Captured locally. The restock email flow does not exist.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend.</t>
+  </si>
+  <si>
+    <t>IN-06</t>
+  </si>
+  <si>
+    <t>Remove noindex before launch</t>
+  </si>
+  <si>
+    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
+  </si>
+  <si>
+    <t>Must be removed deliberately at launch — and only then.</t>
+  </si>
+  <si>
+    <t>IN-07</t>
+  </si>
+  <si>
+    <t>Confirm the GitHub repository is private</t>
+  </si>
+  <si>
+    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
+  </si>
+  <si>
+    <t>https://github.com/musawi1989/aussiemed</t>
+  </si>
+  <si>
+    <t>LG-01</t>
+  </si>
+  <si>
+    <t>Supply terms and conditions</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
+  </si>
+  <si>
+    <t>Page exists and says so on screen.</t>
+  </si>
+  <si>
+    <t>LG-02</t>
+  </si>
+  <si>
+    <t>Supply the privacy policy</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
+  </si>
+  <si>
+    <t>LG-03</t>
+  </si>
+  <si>
+    <t>Confirm the contact email address</t>
+  </si>
+  <si>
+    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
+  </si>
+  <si>
+    <t>Also determines the sending domain for transactional email.</t>
+  </si>
+  <si>
+    <t>SEC-01</t>
+  </si>
+  <si>
+    <t>Remove the test credentials before any deployment</t>
+  </si>
+  <si>
+    <t>Four accounts exist with the password 123456: admin, musawi1989@gmail.com, supplier1, supplier2. The sign-in page lists them on screen. This is fine on a local machine and unacceptable anywhere else.</t>
+  </si>
+  <si>
+    <t>Delete the accounts or set real passwords, and remove the credentials panel from src/app/sign-in/page.tsx.</t>
+  </si>
+  <si>
+    <t>AC-05</t>
+  </si>
+  <si>
+    <t>Confirm the VAT rate and whether it must be configurable</t>
+  </si>
+  <si>
+    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Rate must be stored on the order at the time it is placed.</t>
+  </si>
+  <si>
+    <t>AC-06</t>
+  </si>
+  <si>
+    <t>Approve the reference number format</t>
+  </si>
+  <si>
+    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
+  </si>
+  <si>
+    <t>Wording is fixed as Reference number, never order number.</t>
+  </si>
+  <si>
+    <t>AC-07</t>
+  </si>
+  <si>
+    <t>Approve the supplier invoice numbering</t>
+  </si>
+  <si>
+    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
+  </si>
+  <si>
+    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
+  </si>
+  <si>
+    <t>AC-09</t>
+  </si>
+  <si>
+    <t>Decide payment terms and credit accounts</t>
+  </si>
+  <si>
+    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
+  </si>
+  <si>
+    <t>Affects the schema — decide before the backend.</t>
+  </si>
+  <si>
+    <t>AC-11</t>
+  </si>
+  <si>
+    <t>Approve the VAT rounding method on invoices</t>
+  </si>
+  <si>
+    <t>VAT is rounded per line rather than once per invoice, so the printed lines always add up to the printed total. The alternative rounds once and can leave lines that do not sum.</t>
+  </si>
+  <si>
+    <t>Verified by test: per-invoice VAT sums to the order VAT exactly.</t>
+  </si>
+  <si>
+    <t>AC-12</t>
+  </si>
+  <si>
+    <t>Confirm the reference number sequence resets each year</t>
+  </si>
+  <si>
+    <t>OUR DECISION: the sequence restarts at 000001 each calendar year, so AM-2026-000001 and AM-2027-000001 can both exist. If accounting needs a single unbroken sequence this must change before real orders.</t>
+  </si>
+  <si>
+    <t>Held in a settings row keyed orderSequence:YYYY and incremented inside the checkout transaction.</t>
+  </si>
+  <si>
+    <t>AC-13</t>
+  </si>
+  <si>
+    <t>Decide whether an order should reserve stock</t>
+  </si>
+  <si>
+    <t>OUR DECISION: checkout does not decrement or reserve anything, because there are no stock levels — only an in/out flag. Two customers can order the last unit.</t>
+  </si>
+  <si>
+    <t>Depends on FN-08. Out-of-stock is re-checked at checkout, so a line that sold out while the form was open is rejected.</t>
+  </si>
+  <si>
+    <t>BE-04</t>
+  </si>
+  <si>
+    <t>Build comma-safe .xlsx bulk upload</t>
+  </si>
+  <si>
+    <t>Parsed natively with exceljs, never by splitting on commas — that is what broke comma-containing category names.</t>
+  </si>
+  <si>
+    <t>Unknown brands must be reported per row, never skipped silently.</t>
+  </si>
+  <si>
+    <t>BE-05</t>
+  </si>
+  <si>
+    <t>Build the email flows</t>
+  </si>
+  <si>
+    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
+  </si>
+  <si>
+    <t>Needs an SMTP provider.</t>
+  </si>
+  <si>
+    <t>BE-06</t>
+  </si>
+  <si>
+    <t>Add an audit log</t>
+  </si>
+  <si>
+    <t>Every status transition and every admin or supplier write should be recorded.</t>
+  </si>
+  <si>
+    <t>Specified in the backend spec.</t>
+  </si>
+  <si>
+    <t>BE-08</t>
+  </si>
+  <si>
+    <t>Decide money representation before any data lands</t>
+  </si>
+  <si>
+    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
+  </si>
+  <si>
+    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
+  </si>
+  <si>
+    <t>BE-10</t>
+  </si>
+  <si>
+    <t>Retire the catalogue snapshot endpoint</t>
+  </si>
+  <si>
+    <t>Client components fetch the whole catalogue from /api/v1/catalog/snapshot. Fine for 71 products; not for thousands. Goes away when the cart moves server-side.</t>
+  </si>
+  <si>
+    <t>Phase 3 removes the need.</t>
+  </si>
+  <si>
+    <t>BE-12</t>
+  </si>
+  <si>
+    <t>Merge a guest cart into the user cart on sign-in</t>
+  </si>
+  <si>
+    <t>Carts are keyed by a cookie so a visitor can shop before signing in. The merge on sign-in is specified but cannot be built until auth exists.</t>
+  </si>
+  <si>
+    <t>Cart cookie: aussiemed_cart, httpOnly, 30 day lifetime — OUR INVENTED VALUES.</t>
+  </si>
+  <si>
+    <t>BE-14</t>
+  </si>
+  <si>
+    <t>Confirm the default order and invoice status</t>
+  </si>
+  <si>
+    <t>OUR DECISION: new orders are Pending and each supplier invoice is Pending. The real workflow — who moves an order to Processing, and when an invoice becomes Issued — is not defined.</t>
+  </si>
+  <si>
+    <t>Order statuses available: Pending, Processing, Dispatched, Delivered, Cancelled.</t>
+  </si>
+  <si>
+    <t>BE-15</t>
+  </si>
+  <si>
+    <t>Passwords were built instead of the specified email OTP</t>
+  </si>
+  <si>
+    <t>BACKEND_SPEC.md specifies passwordless sign-in by emailed code. Passwords were requested instead and built. Livingstone advertises password-free login as a feature, so the spec was not arbitrary.</t>
+  </si>
+  <si>
+    <t>Both can coexist: the schema keeps otpCode and otpExpiresAt. Decide before launch.</t>
+  </si>
+  <si>
+    <t>BE-19</t>
+  </si>
+  <si>
+    <t>Guest checkout is allowed</t>
+  </si>
+  <si>
+    <t>OUR DECISION: an order can be placed without signing in, and is then tied to the cart cookie. Signing in simply attaches the order to the account.</t>
+  </si>
+  <si>
+    <t>If trade accounts should be required to order, this must change — it also affects credit terms and pricing.</t>
+  </si>
+  <si>
+    <t>DA-02</t>
+  </si>
+  <si>
+    <t>Verify the product-to-category mapping</t>
+  </si>
+  <si>
+    <t>The extraction had no product-category link at all. All 11 real products were mapped by hand from their names.</t>
+  </si>
+  <si>
+    <t>146 categories exist; the mapping is ours and unverified.</t>
+  </si>
+  <si>
+    <t>DA-05</t>
+  </si>
+  <si>
+    <t>Approve the product descriptions</t>
+  </si>
+  <si>
+    <t>The source had no descriptions. Eleven were written from the product names and need approval before launch.</t>
+  </si>
+  <si>
+    <t>Placeholder products carry generated filler text.</t>
+  </si>
+  <si>
+    <t>DA-07</t>
+  </si>
+  <si>
+    <t>Supply the hero banner image</t>
+  </si>
+  <si>
+    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured — only Brand, Category, Product and WebHtml folders were mirrored.</t>
+  </si>
+  <si>
+    <t>A genuine AussieMed CMS image stands in.</t>
+  </si>
+  <si>
+    <t>DA-08</t>
+  </si>
+  <si>
+    <t>Obtain Gilroy Regular and Medium</t>
+  </si>
+  <si>
+    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
+  </si>
+  <si>
+    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
+  </si>
+  <si>
+    <t>DA-10</t>
+  </si>
+  <si>
+    <t>Supply real pack and carton structures</t>
+  </si>
+  <si>
+    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
+  </si>
+  <si>
+    <t>Pack is the purchasable unit; getting it wrong misprices every carton.</t>
+  </si>
+  <si>
+    <t>DA-11</t>
+  </si>
+  <si>
+    <t>Supply real variant data</t>
+  </si>
+  <si>
+    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
+  </si>
+  <si>
+    <t>Variant switching is not wired until sibling SKUs exist.</t>
+  </si>
+  <si>
+    <t>DA-12</t>
+  </si>
+  <si>
+    <t>Supply real product specifications</t>
+  </si>
+  <si>
+    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
+  </si>
+  <si>
+    <t>These become search filters later.</t>
+  </si>
+  <si>
+    <t>DA-13</t>
+  </si>
+  <si>
+    <t>Supply safety data sheets and spec sheets</t>
+  </si>
+  <si>
+    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
+  </si>
+  <si>
+    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
+  </si>
+  <si>
+    <t>DA-18</t>
+  </si>
+  <si>
+    <t>Product ids are derived from slugs</t>
+  </si>
+  <si>
+    <t>Carts and wishlists are stored in the browser against a product id. Ids are now hashed from the slug so they survive a re-seed, which means CHANGING A PRODUCT SLUG ORPHANS ANY SAVED CART LINE referencing it.</t>
+  </si>
+  <si>
+    <t>Resolved properly when the cart moves server-side and references SKU rows directly.</t>
+  </si>
+  <si>
+    <t>DA-19</t>
+  </si>
+  <si>
+    <t>Supplier email addresses are invented</t>
+  </si>
+  <si>
+    <t>The seed writes orders@&lt;supplier&gt;.example and accounts@&lt;supplier&gt;.example because secondaryEmail is mandatory. No supplier will receive anything at these addresses.</t>
+  </si>
+  <si>
+    <t>Both addresses are meant to receive order notifications once email exists.</t>
+  </si>
+  <si>
+    <t>FN-07</t>
+  </si>
+  <si>
+    <t>Variant switching is not wired</t>
+  </si>
+  <si>
+    <t>Size and colour chips display the current value; other options are disabled because sibling SKUs do not exist yet.</t>
+  </si>
+  <si>
+    <t>Needs the variant model in the database.</t>
+  </si>
+  <si>
+    <t>FN-08</t>
+  </si>
+  <si>
+    <t>Stock is a boolean</t>
+  </si>
+  <si>
+    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
+  </si>
+  <si>
+    <t>Decide whether real stock levels are needed.</t>
+  </si>
+  <si>
+    <t>FN-09</t>
+  </si>
+  <si>
+    <t>Decide on expiry and short-dated stock</t>
+  </si>
+  <si>
+    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
+  </si>
+  <si>
+    <t>Schema-shaping — decide before the backend is built.</t>
+  </si>
+  <si>
+    <t>IN-01</t>
+  </si>
+  <si>
+    <t>Choose a hosting target</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. The site runs locally only.</t>
+  </si>
+  <si>
+    <t>Deliberately deferred until the build is approved.</t>
+  </si>
+  <si>
+    <t>IN-02</t>
+  </si>
+  <si>
+    <t>Choose the database</t>
+  </si>
+  <si>
+    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
+  </si>
+  <si>
+    <t>IN-03</t>
+  </si>
+  <si>
+    <t>Choose an SMTP provider and sending domain</t>
+  </si>
+  <si>
+    <t>Required for every transactional email.</t>
+  </si>
+  <si>
+    <t>Must not be the misspelled assuiemed.com domain.</t>
+  </si>
+  <si>
+    <t>IN-04</t>
+  </si>
+  <si>
+    <t>Decide on a payment gateway</t>
+  </si>
+  <si>
+    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
+  </si>
+  <si>
+    <t>LG-05</t>
+  </si>
+  <si>
+    <t>Transfer the theme licence</t>
+  </si>
+  <si>
+    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
+  </si>
+  <si>
+    <t>Repository must stay private because of this.</t>
+  </si>
+  <si>
+    <t>LG-06</t>
+  </si>
+  <si>
+    <t>Supply company registration details</t>
+  </si>
+  <si>
+    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
+  </si>
+  <si>
+    <t>SEC-02</t>
+  </si>
+  <si>
+    <t>Add rate limiting to sign-in</t>
+  </si>
+  <si>
+    <t>Nothing limits password attempts, so the sign-in endpoint can be brute forced. The spec asks for rate limiting on auth in the hardening phase.</t>
+  </si>
+  <si>
+    <t>Matters more with short passwords than with OTP.</t>
+  </si>
+  <si>
+    <t>SEC-03</t>
+  </si>
+  <si>
+    <t>Agree a password policy</t>
+  </si>
+  <si>
+    <t>No minimum length, complexity or reuse rule is enforced. 123456 was accepted because nothing rejects it.</t>
+  </si>
+  <si>
+    <t>Moot if the OTP flow in BE-15 is adopted instead.</t>
+  </si>
+  <si>
+    <t>AC-08</t>
+  </si>
+  <si>
+    <t>Confirm the rounding policy</t>
+  </si>
+  <si>
+    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Verified by test; needs sign-off that the method is acceptable.</t>
+  </si>
+  <si>
+    <t>AC-10</t>
+  </si>
+  <si>
+    <t>Confirm the default price display</t>
+  </si>
+  <si>
+    <t>Prices default to Ex. VAT with a toggle to Inc. VAT.</t>
+  </si>
+  <si>
+    <t>Preference persists per browser.</t>
+  </si>
+  <si>
+    <t>BE-13</t>
+  </si>
+  <si>
+    <t>Expire abandoned guest carts</t>
+  </si>
+  <si>
+    <t>Cart rows are never cleaned up. Every visitor who adds an item creates one that lives forever.</t>
+  </si>
+  <si>
+    <t>The spec wants abandoned carts over 24h reportable under Admin &gt; Marketing, so expiry and that report should be designed together.</t>
+  </si>
+  <si>
+    <t>BE-16</t>
+  </si>
+  <si>
+    <t>Confirm the session lifetime</t>
+  </si>
+  <si>
+    <t>OUR INVENTED VALUE: sessions last 7 days, then require signing in again. No idle timeout and no re-authentication for sensitive actions.</t>
+  </si>
+  <si>
+    <t>Cookie is httpOnly and sameSite=lax; secure only in production so local http still works.</t>
+  </si>
+  <si>
+    <t>BE-17</t>
+  </si>
+  <si>
+    <t>Purge expired sessions on a schedule</t>
+  </si>
+  <si>
+    <t>Expired session rows are never deleted. purgeExpiredSessions() exists but nothing calls it.</t>
+  </si>
+  <si>
+    <t>Trivial once any scheduled job exists.</t>
+  </si>
+  <si>
+    <t>BE-18</t>
+  </si>
+  <si>
+    <t>Password hashing uses scrypt, not bcrypt</t>
+  </si>
+  <si>
+    <t>OUR DECISION: scrypt from Node's own crypto module, so there is no dependency to keep patched. The spec names bcrypt. Both are appropriate; only src/lib/auth.ts knows the format.</t>
+  </si>
+  <si>
+    <t>Stored as scrypt$salt$hash so the algorithm is self-describing and can be migrated per user.</t>
+  </si>
+  <si>
+    <t>DA-04</t>
+  </si>
+  <si>
+    <t>Wrong image on the scrub top</t>
+  </si>
+  <si>
+    <t>The product's primary image was a stock photo of a pocket watch. Excluded from the build; the file is still in public/products/.</t>
+  </si>
+  <si>
+    <t>Suggests image uploads were not being checked in the old admin.</t>
+  </si>
+  <si>
+    <t>DA-09</t>
+  </si>
+  <si>
+    <t>Explain the disappearing product</t>
+  </si>
+  <si>
+    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
+  </si>
+  <si>
+    <t>Evidence of a real defect in the old platform. Worth understanding before trusting any migrated data.</t>
+  </si>
+  <si>
+    <t>DA-14</t>
+  </si>
+  <si>
+    <t>Confirm the brand list</t>
+  </si>
+  <si>
+    <t>Brands were assigned by reading product names.</t>
+  </si>
+  <si>
+    <t>Eleven real brands identified.</t>
+  </si>
+  <si>
+    <t>DA-15</t>
+  </si>
+  <si>
+    <t>Decide on duplicate categories</t>
+  </si>
+  <si>
+    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
+  </si>
+  <si>
+    <t>Affected: Respiratory Management, Oral Care, Monitoring &amp; Testing, Dispensers, Bags, Medicine.</t>
+  </si>
+  <si>
+    <t>DA-16</t>
+  </si>
+  <si>
+    <t>Confirm the missing department</t>
+  </si>
+  <si>
+    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
+  </si>
+  <si>
+    <t>Confirm this is intentional rather than lost.</t>
+  </si>
+  <si>
+    <t>FN-10</t>
+  </si>
+  <si>
+    <t>Search is client-side only</t>
+  </si>
+  <si>
+    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
+  </si>
+  <si>
+    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
+  </si>
+  <si>
+    <t>IN-05</t>
+  </si>
+  <si>
+    <t>Supply Google and Facebook OAuth keys</t>
+  </si>
+  <si>
+    <t>Social login endpoints currently return 501.</t>
+  </si>
+  <si>
+    <t>IN-08</t>
+  </si>
+  <si>
+    <t>Correct the git author name</t>
+  </si>
+  <si>
+    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
+  </si>
+  <si>
+    <t>Fixable with git config user.name and an amend.</t>
+  </si>
+  <si>
+    <t>IN-09</t>
+  </si>
+  <si>
+    <t>Set up continuous integration</t>
+  </si>
+  <si>
+    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
+  </si>
+  <si>
+    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
+  </si>
+  <si>
+    <t>IN-10</t>
+  </si>
+  <si>
+    <t>Plan backups and disaster recovery</t>
+  </si>
+  <si>
+    <t>No backup strategy exists for the database or uploaded files.</t>
+  </si>
+  <si>
+    <t>Relevant once there is a real database.</t>
+  </si>
+  <si>
+    <t>LG-04</t>
+  </si>
+  <si>
+    <t>Approve the About / Contact / Order Support copy</t>
+  </si>
+  <si>
+    <t>All placeholder text.</t>
+  </si>
+  <si>
+    <t>Pages carry a visible placeholder notice.</t>
+  </si>
+  <si>
+    <t>DF-01</t>
+  </si>
+  <si>
+    <t>Industry taxonomy</t>
+  </si>
+  <si>
+    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
+  </si>
+  <si>
+    <t>Additive; adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-02</t>
+  </si>
+  <si>
+    <t>Subscribe and Save</t>
+  </si>
+  <si>
+    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
+  </si>
+  <si>
+    <t>Needs the backend.</t>
+  </si>
+  <si>
+    <t>DF-03</t>
+  </si>
+  <si>
+    <t>Frequently bought together</t>
+  </si>
+  <si>
+    <t>Bundle suggestion with a combined total and one action to add all.</t>
+  </si>
+  <si>
+    <t>Adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-04</t>
+  </si>
+  <si>
+    <t>Quick view</t>
+  </si>
+  <si>
+    <t>View a product from the listing without a page load.</t>
+  </si>
+  <si>
+    <t>DF-05</t>
+  </si>
+  <si>
+    <t>Downloadable PDF catalogues</t>
+  </si>
+  <si>
+    <t>Still how a lot of trade buying happens.</t>
+  </si>
+  <si>
+    <t>Needs the actual catalogue files.</t>
+  </si>
+  <si>
+    <t>BE-07</t>
+  </si>
+  <si>
+    <t>Seed the database from the catalogue</t>
+  </si>
+  <si>
+    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
+  </si>
+  <si>
+    <t>BE-09</t>
+  </si>
+  <si>
+    <t>Point the storefront at the database</t>
+  </si>
+  <si>
+    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
+  </si>
+  <si>
+    <t>query.ts was untouched — it never knew where products came from.</t>
+  </si>
+  <si>
     <t>BE-11</t>
   </si>
   <si>
-    <t>Restrict order pages to the account that placed the order</t>
-  </si>
-  <si>
-    <t>An order at /orders/REFERENCE is readable by anyone who knows the reference. There is no sign-in yet, so there is nothing to check against.</t>
-  </si>
-  <si>
-    <t>Must be closed before launch. References are sequential and therefore guessable.</t>
-  </si>
-  <si>
-    <t>DA-01</t>
-  </si>
-  <si>
-    <t>Supply the real product catalogue</t>
-  </si>
-  <si>
-    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
-  </si>
-  <si>
-    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
-  </si>
-  <si>
-    <t>DA-03</t>
-  </si>
-  <si>
-    <t>Supply product photography</t>
-  </si>
-  <si>
-    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
-  </si>
-  <si>
-    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
-  </si>
-  <si>
-    <t>DA-06</t>
-  </si>
-  <si>
-    <t>Supply the real supplier list</t>
-  </si>
-  <si>
-    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
-  </si>
-  <si>
-    <t>All are flagged isPlaceholder in the data.</t>
-  </si>
-  <si>
-    <t>DA-17</t>
-  </si>
-  <si>
-    <t>Replace the test supplier attribution</t>
-  </si>
-  <si>
-    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
-  </si>
-  <si>
-    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
-  </si>
-  <si>
-    <t>FN-02</t>
-  </si>
-  <si>
-    <t>Quote requests are not delivered</t>
-  </si>
-  <si>
-    <t>Captured in the browser only.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend and an email provider.</t>
-  </si>
-  <si>
-    <t>FN-03</t>
-  </si>
-  <si>
-    <t>Bulk buy enquiries are not delivered</t>
-  </si>
-  <si>
-    <t>FN-04</t>
-  </si>
-  <si>
-    <t>Notify Me does not register a subscription</t>
-  </si>
-  <si>
-    <t>Captured locally. The restock email flow does not exist.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend.</t>
+    <t>Order pages restricted to their owner</t>
+  </si>
+  <si>
+    <t>An order was readable by anyone who guessed a sequential reference. Now an admin sees any order, the account that placed it sees it, and a guest sees only an order placed from their own cart.</t>
+  </si>
+  <si>
+    <t>A forbidden order returns 404 rather than 403, so the response cannot be used to discover which references exist.</t>
+  </si>
+  <si>
+    <t>DN-01</t>
+  </si>
+  <si>
+    <t>Currency rendering</t>
+  </si>
+  <si>
+    <t>Was rendering the Arabic symbol and 4 decimals. Now always the English string AED with exactly 2 decimals, enforced by test and by a grep check.</t>
+  </si>
+  <si>
+    <t>Fixed in the initial build.</t>
+  </si>
+  <si>
+    <t>DN-02</t>
+  </si>
+  <si>
+    <t>Integer quantities</t>
+  </si>
+  <si>
+    <t>Quantities were rendering as decimals such as 3.00.</t>
+  </si>
+  <si>
+    <t>DN-03</t>
+  </si>
+  <si>
+    <t>Category filtering</t>
+  </si>
+  <si>
+    <t>Every category link redirected to the full product list. Filtering now works, including rolling a department up to everything beneath it.</t>
+  </si>
+  <si>
+    <t>DN-04</t>
+  </si>
+  <si>
+    <t>Category counts matching results</t>
+  </si>
+  <si>
+    <t>Admin and storefront counts could diverge. Counts are now derived from the same query that lists the products.</t>
+  </si>
+  <si>
+    <t>Asserted in the data checks and the API contract checks.</t>
+  </si>
+  <si>
+    <t>DN-05</t>
+  </si>
+  <si>
+    <t>Category slug collisions</t>
+  </si>
+  <si>
+    <t>Six categories shared a slug with another category, so one was unreachable and the other answered to the wrong name.</t>
+  </si>
+  <si>
+    <t>Found by the API contract check. Slugs are now unique tree-wide and asserted.</t>
+  </si>
+  <si>
+    <t>DN-06</t>
+  </si>
+  <si>
+    <t>Per-supplier invoicing</t>
+  </si>
+  <si>
+    <t>An order spanning N suppliers now produces exactly N invoices under one reference number, with per-invoice VAT summing to the order VAT without drift.</t>
+  </si>
+  <si>
+    <t>Verified end to end in the browser and by test.</t>
+  </si>
+  <si>
+    <t>DN-11</t>
+  </si>
+  <si>
+    <t>Pack and unit of measure model</t>
+  </si>
+  <si>
+    <t>The same line sells by the box and by the carton at different prices. Cart lines are keyed by product and pack so they never merge.</t>
+  </si>
+  <si>
+    <t>Outers are asserted to beat buying their contents separately.</t>
+  </si>
+  <si>
+    <t>DN-14</t>
+  </si>
+  <si>
+    <t>Control characters in generated code</t>
+  </si>
+  <si>
+    <t>Shell escaping wrote literal backspace bytes into regex rules, so every packaging and variant rule silently matched nothing while looking correct in every editor.</t>
+  </si>
+  <si>
+    <t>Found via od. A data check now asserts each variant selection matches an option.</t>
+  </si>
+  <si>
+    <t>DN-16</t>
+  </si>
+  <si>
+    <t>Database schema designed and migrated</t>
+  </si>
+  <si>
+    <t>Thirty tables covering catalogue, packs as SKUs, variants, attributes, documents, batches, orders, per-supplier invoices, quotes, bulk upload and audit.</t>
+  </si>
+  <si>
+    <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
+  </si>
+  <si>
+    <t>DN-17</t>
+  </si>
+  <si>
+    <t>Typecheck was silently passing on a stale cache</t>
+  </si>
+  <si>
+    <t>tsc ran with incremental caching and reported no errors while real type errors existed in the tree. Every earlier typecheck-clean claim was suspect.</t>
+  </si>
+  <si>
+    <t>npm run typecheck now runs with --incremental false. Caught seven genuine errors the moment it was disabled.</t>
+  </si>
+  <si>
+    <t>DN-18</t>
+  </si>
+  <si>
+    <t>Cart moved to the server</t>
+  </si>
+  <si>
+    <t>The cart was localStorage, so the browser held prices. It is now database rows priced entirely on the server; the client cannot tell the server what anything costs.</t>
+  </si>
+  <si>
+    <t>Guest carts are cookie-keyed. The catalogue snapshot endpoint stays until the wishlist and quote cart follow.</t>
+  </si>
+  <si>
+    <t>DN-19</t>
+  </si>
+  <si>
+    <t>Checkout writes real orders</t>
+  </si>
+  <si>
+    <t>One transaction creates the order, one invoice per supplier and every line, or nothing at all. Reference numbers are allocated server-side inside that transaction.</t>
+  </si>
+  <si>
+    <t>Verified in a browser end to end, and by 14 order invariants in npm run db:check.</t>
+  </si>
+  <si>
+    <t>DN-20</t>
+  </si>
+  <si>
+    <t>Four sign-in accounts seeded</t>
+  </si>
+  <si>
+    <t>admin, musawi1989@gmail.com, supplier1 and supplier2, each able to sign in by username or email. Suppliers are attached to their seeded companies.</t>
+  </si>
+  <si>
+    <t>Seeded separately from the catalogue so re-seeding products does not remove accounts.</t>
+  </si>
+  <si>
+    <t>FN-01</t>
+  </si>
+  <si>
+    <t>Checkout does not submit an order</t>
+  </si>
+  <si>
+    <t>Done. Checkout writes a real order in one transaction, with one invoice per supplier and a server-allocated reference number.</t>
+  </si>
+  <si>
+    <t>Payment is still not taken and no email is sent.</t>
   </si>
   <si>
     <t>FN-05</t>
   </si>
   <si>
-    <t>Sign-in is a demo flag</t>
-  </si>
-  <si>
-    <t>A localStorage boolean opens a fabricated session. Real auth is email OTP per the backend spec.</t>
-  </si>
-  <si>
-    <t>Must be replaced wholesale rather than extended.</t>
+    <t>Real sign-in replaced the demo flag</t>
+  </si>
+  <si>
+    <t>Sign-in was a localStorage boolean anyone could set. It is now a database-backed session with a scrypt-hashed password.</t>
+  </si>
+  <si>
+    <t>Sessions are rows; signing out deletes the row, so a copied cookie stops working.</t>
   </si>
   <si>
     <t>FN-06</t>
   </si>
   <si>
-    <t>Account history is fabricated</t>
-  </si>
-  <si>
-    <t>The customer, three orders and their invoices are invented so the account screens could be built and reviewed.</t>
-  </si>
-  <si>
-    <t>Every account page carries a visible notice.</t>
-  </si>
-  <si>
-    <t>IN-06</t>
-  </si>
-  <si>
-    <t>Remove noindex before launch</t>
-  </si>
-  <si>
-    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
-  </si>
-  <si>
-    <t>Must be removed deliberately at launch — and only then.</t>
-  </si>
-  <si>
-    <t>IN-07</t>
-  </si>
-  <si>
-    <t>Confirm the GitHub repository is private</t>
-  </si>
-  <si>
-    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
-  </si>
-  <si>
-    <t>https://github.com/musawi1989/aussiemed</t>
-  </si>
-  <si>
-    <t>LG-01</t>
-  </si>
-  <si>
-    <t>Supply terms and conditions</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
-  </si>
-  <si>
-    <t>Page exists and says so on screen.</t>
-  </si>
-  <si>
-    <t>LG-02</t>
-  </si>
-  <si>
-    <t>Supply the privacy policy</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
-  </si>
-  <si>
-    <t>LG-03</t>
-  </si>
-  <si>
-    <t>Confirm the contact email address</t>
-  </si>
-  <si>
-    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
-  </si>
-  <si>
-    <t>Also determines the sending domain for transactional email.</t>
-  </si>
-  <si>
-    <t>AC-05</t>
-  </si>
-  <si>
-    <t>Confirm the VAT rate and whether it must be configurable</t>
-  </si>
-  <si>
-    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>Rate must be stored on the order at the time it is placed.</t>
-  </si>
-  <si>
-    <t>AC-06</t>
-  </si>
-  <si>
-    <t>Approve the reference number format</t>
-  </si>
-  <si>
-    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
-  </si>
-  <si>
-    <t>Wording is fixed as Reference number, never order number.</t>
-  </si>
-  <si>
-    <t>AC-07</t>
-  </si>
-  <si>
-    <t>Approve the supplier invoice numbering</t>
-  </si>
-  <si>
-    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
-  </si>
-  <si>
-    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
-  </si>
-  <si>
-    <t>AC-09</t>
-  </si>
-  <si>
-    <t>Decide payment terms and credit accounts</t>
-  </si>
-  <si>
-    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
-  </si>
-  <si>
-    <t>Affects the schema — decide before the backend.</t>
-  </si>
-  <si>
-    <t>AC-11</t>
-  </si>
-  <si>
-    <t>Approve the VAT rounding method on invoices</t>
-  </si>
-  <si>
-    <t>VAT is rounded per line rather than once per invoice, so the printed lines always add up to the printed total. The alternative rounds once and can leave lines that do not sum.</t>
-  </si>
-  <si>
-    <t>Verified by test: per-invoice VAT sums to the order VAT exactly.</t>
-  </si>
-  <si>
-    <t>AC-12</t>
-  </si>
-  <si>
-    <t>Confirm the reference number sequence resets each year</t>
-  </si>
-  <si>
-    <t>OUR DECISION: the sequence restarts at 000001 each calendar year, so AM-2026-000001 and AM-2027-000001 can both exist. If accounting needs a single unbroken sequence this must change before real orders.</t>
-  </si>
-  <si>
-    <t>Held in a settings row keyed orderSequence:YYYY and incremented inside the checkout transaction.</t>
-  </si>
-  <si>
-    <t>AC-13</t>
-  </si>
-  <si>
-    <t>Decide whether an order should reserve stock</t>
-  </si>
-  <si>
-    <t>OUR DECISION: checkout does not decrement or reserve anything, because there are no stock levels — only an in/out flag. Two customers can order the last unit.</t>
-  </si>
-  <si>
-    <t>Depends on FN-08. Out-of-stock is re-checked at checkout, so a line that sold out while the form was open is rejected.</t>
-  </si>
-  <si>
-    <t>BE-04</t>
-  </si>
-  <si>
-    <t>Build comma-safe .xlsx bulk upload</t>
-  </si>
-  <si>
-    <t>Parsed natively with exceljs, never by splitting on commas — that is what broke comma-containing category names.</t>
-  </si>
-  <si>
-    <t>Unknown brands must be reported per row, never skipped silently.</t>
-  </si>
-  <si>
-    <t>BE-05</t>
-  </si>
-  <si>
-    <t>Build the email flows</t>
-  </si>
-  <si>
-    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
-  </si>
-  <si>
-    <t>Needs an SMTP provider.</t>
-  </si>
-  <si>
-    <t>BE-06</t>
-  </si>
-  <si>
-    <t>Add an audit log</t>
-  </si>
-  <si>
-    <t>Every status transition and every admin or supplier write should be recorded.</t>
-  </si>
-  <si>
-    <t>Specified in the backend spec.</t>
-  </si>
-  <si>
-    <t>BE-08</t>
-  </si>
-  <si>
-    <t>Decide money representation before any data lands</t>
-  </si>
-  <si>
-    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
-  </si>
-  <si>
-    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
-  </si>
-  <si>
-    <t>BE-10</t>
-  </si>
-  <si>
-    <t>Retire the catalogue snapshot endpoint</t>
-  </si>
-  <si>
-    <t>Client components fetch the whole catalogue from /api/v1/catalog/snapshot. Fine for 71 products; not for thousands. Goes away when the cart moves server-side.</t>
-  </si>
-  <si>
-    <t>Phase 3 removes the need.</t>
-  </si>
-  <si>
-    <t>BE-12</t>
-  </si>
-  <si>
-    <t>Merge a guest cart into the user cart on sign-in</t>
-  </si>
-  <si>
-    <t>Carts are keyed by a cookie so a visitor can shop before signing in. The merge on sign-in is specified but cannot be built until auth exists.</t>
-  </si>
-  <si>
-    <t>Cart cookie: aussiemed_cart, httpOnly, 30 day lifetime — OUR INVENTED VALUES.</t>
-  </si>
-  <si>
-    <t>BE-14</t>
-  </si>
-  <si>
-    <t>Confirm the default order and invoice status</t>
-  </si>
-  <si>
-    <t>OUR DECISION: new orders are Pending and each supplier invoice is Pending. The real workflow — who moves an order to Processing, and when an invoice becomes Issued — is not defined.</t>
-  </si>
-  <si>
-    <t>Order statuses available: Pending, Processing, Dispatched, Delivered, Cancelled.</t>
-  </si>
-  <si>
-    <t>DA-02</t>
-  </si>
-  <si>
-    <t>Verify the product-to-category mapping</t>
-  </si>
-  <si>
-    <t>The extraction had no product-category link at all. All 11 real products were mapped by hand from their names.</t>
-  </si>
-  <si>
-    <t>146 categories exist; the mapping is ours and unverified.</t>
-  </si>
-  <si>
-    <t>DA-05</t>
-  </si>
-  <si>
-    <t>Approve the product descriptions</t>
-  </si>
-  <si>
-    <t>The source had no descriptions. Eleven were written from the product names and need approval before launch.</t>
-  </si>
-  <si>
-    <t>Placeholder products carry generated filler text.</t>
-  </si>
-  <si>
-    <t>DA-07</t>
-  </si>
-  <si>
-    <t>Supply the hero banner image</t>
-  </si>
-  <si>
-    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured — only Brand, Category, Product and WebHtml folders were mirrored.</t>
-  </si>
-  <si>
-    <t>A genuine AussieMed CMS image stands in.</t>
-  </si>
-  <si>
-    <t>DA-08</t>
-  </si>
-  <si>
-    <t>Obtain Gilroy Regular and Medium</t>
-  </si>
-  <si>
-    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
-  </si>
-  <si>
-    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
-  </si>
-  <si>
-    <t>DA-10</t>
-  </si>
-  <si>
-    <t>Supply real pack and carton structures</t>
-  </si>
-  <si>
-    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
-  </si>
-  <si>
-    <t>Pack is the purchasable unit; getting it wrong misprices every carton.</t>
-  </si>
-  <si>
-    <t>DA-11</t>
-  </si>
-  <si>
-    <t>Supply real variant data</t>
-  </si>
-  <si>
-    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
-  </si>
-  <si>
-    <t>Variant switching is not wired until sibling SKUs exist.</t>
-  </si>
-  <si>
-    <t>DA-12</t>
-  </si>
-  <si>
-    <t>Supply real product specifications</t>
-  </si>
-  <si>
-    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
-  </si>
-  <si>
-    <t>These become search filters later.</t>
-  </si>
-  <si>
-    <t>DA-13</t>
-  </si>
-  <si>
-    <t>Supply safety data sheets and spec sheets</t>
-  </si>
-  <si>
-    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
-  </si>
-  <si>
-    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
-  </si>
-  <si>
-    <t>DA-18</t>
-  </si>
-  <si>
-    <t>Product ids are derived from slugs</t>
-  </si>
-  <si>
-    <t>Carts and wishlists are stored in the browser against a product id. Ids are now hashed from the slug so they survive a re-seed, which means CHANGING A PRODUCT SLUG ORPHANS ANY SAVED CART LINE referencing it.</t>
-  </si>
-  <si>
-    <t>Resolved properly when the cart moves server-side and references SKU rows directly.</t>
-  </si>
-  <si>
-    <t>DA-19</t>
-  </si>
-  <si>
-    <t>Supplier email addresses are invented</t>
-  </si>
-  <si>
-    <t>The seed writes orders@&lt;supplier&gt;.example and accounts@&lt;supplier&gt;.example because secondaryEmail is mandatory. No supplier will receive anything at these addresses.</t>
-  </si>
-  <si>
-    <t>Both addresses are meant to receive order notifications once email exists.</t>
-  </si>
-  <si>
-    <t>FN-07</t>
-  </si>
-  <si>
-    <t>Variant switching is not wired</t>
-  </si>
-  <si>
-    <t>Size and colour chips display the current value; other options are disabled because sibling SKUs do not exist yet.</t>
-  </si>
-  <si>
-    <t>Needs the variant model in the database.</t>
-  </si>
-  <si>
-    <t>FN-08</t>
-  </si>
-  <si>
-    <t>Stock is a boolean</t>
-  </si>
-  <si>
-    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
-  </si>
-  <si>
-    <t>Decide whether real stock levels are needed.</t>
-  </si>
-  <si>
-    <t>FN-09</t>
-  </si>
-  <si>
-    <t>Decide on expiry and short-dated stock</t>
-  </si>
-  <si>
-    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
-  </si>
-  <si>
-    <t>Schema-shaping — decide before the backend is built.</t>
-  </si>
-  <si>
-    <t>IN-01</t>
-  </si>
-  <si>
-    <t>Choose a hosting target</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. The site runs locally only.</t>
-  </si>
-  <si>
-    <t>Deliberately deferred until the build is approved.</t>
-  </si>
-  <si>
-    <t>IN-02</t>
-  </si>
-  <si>
-    <t>Choose the database</t>
-  </si>
-  <si>
-    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
-  </si>
-  <si>
-    <t>IN-03</t>
-  </si>
-  <si>
-    <t>Choose an SMTP provider and sending domain</t>
-  </si>
-  <si>
-    <t>Required for every transactional email.</t>
-  </si>
-  <si>
-    <t>Must not be the misspelled assuiemed.com domain.</t>
-  </si>
-  <si>
-    <t>IN-04</t>
-  </si>
-  <si>
-    <t>Decide on a payment gateway</t>
-  </si>
-  <si>
-    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
-  </si>
-  <si>
-    <t>LG-05</t>
-  </si>
-  <si>
-    <t>Transfer the theme licence</t>
-  </si>
-  <si>
-    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
-  </si>
-  <si>
-    <t>Repository must stay private because of this.</t>
-  </si>
-  <si>
-    <t>LG-06</t>
-  </si>
-  <si>
-    <t>Supply company registration details</t>
-  </si>
-  <si>
-    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
-  </si>
-  <si>
-    <t>AC-08</t>
-  </si>
-  <si>
-    <t>Confirm the rounding policy</t>
-  </si>
-  <si>
-    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>Verified by test; needs sign-off that the method is acceptable.</t>
-  </si>
-  <si>
-    <t>AC-10</t>
-  </si>
-  <si>
-    <t>Confirm the default price display</t>
-  </si>
-  <si>
-    <t>Prices default to Ex. VAT with a toggle to Inc. VAT.</t>
-  </si>
-  <si>
-    <t>Preference persists per browser.</t>
-  </si>
-  <si>
-    <t>BE-13</t>
-  </si>
-  <si>
-    <t>Expire abandoned guest carts</t>
-  </si>
-  <si>
-    <t>Cart rows are never cleaned up. Every visitor who adds an item creates one that lives forever.</t>
-  </si>
-  <si>
-    <t>The spec wants abandoned carts over 24h reportable under Admin &gt; Marketing, so expiry and that report should be designed together.</t>
-  </si>
-  <si>
-    <t>DA-04</t>
-  </si>
-  <si>
-    <t>Wrong image on the scrub top</t>
-  </si>
-  <si>
-    <t>The product's primary image was a stock photo of a pocket watch. Excluded from the build; the file is still in public/products/.</t>
-  </si>
-  <si>
-    <t>Suggests image uploads were not being checked in the old admin.</t>
-  </si>
-  <si>
-    <t>DA-09</t>
-  </si>
-  <si>
-    <t>Explain the disappearing product</t>
-  </si>
-  <si>
-    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
-  </si>
-  <si>
-    <t>Evidence of a real defect in the old platform. Worth understanding before trusting any migrated data.</t>
-  </si>
-  <si>
-    <t>DA-14</t>
-  </si>
-  <si>
-    <t>Confirm the brand list</t>
-  </si>
-  <si>
-    <t>Brands were assigned by reading product names.</t>
-  </si>
-  <si>
-    <t>Eleven real brands identified.</t>
-  </si>
-  <si>
-    <t>DA-15</t>
-  </si>
-  <si>
-    <t>Decide on duplicate categories</t>
-  </si>
-  <si>
-    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
-  </si>
-  <si>
-    <t>Affected: Respiratory Management, Oral Care, Monitoring &amp; Testing, Dispensers, Bags, Medicine.</t>
-  </si>
-  <si>
-    <t>DA-16</t>
-  </si>
-  <si>
-    <t>Confirm the missing department</t>
-  </si>
-  <si>
-    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
-  </si>
-  <si>
-    <t>Confirm this is intentional rather than lost.</t>
-  </si>
-  <si>
-    <t>FN-10</t>
-  </si>
-  <si>
-    <t>Search is client-side only</t>
-  </si>
-  <si>
-    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
-  </si>
-  <si>
-    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
-  </si>
-  <si>
-    <t>IN-05</t>
-  </si>
-  <si>
-    <t>Supply Google and Facebook OAuth keys</t>
-  </si>
-  <si>
-    <t>Social login endpoints currently return 501.</t>
-  </si>
-  <si>
-    <t>IN-08</t>
-  </si>
-  <si>
-    <t>Correct the git author name</t>
-  </si>
-  <si>
-    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
-  </si>
-  <si>
-    <t>Fixable with git config user.name and an amend.</t>
-  </si>
-  <si>
-    <t>IN-09</t>
-  </si>
-  <si>
-    <t>Set up continuous integration</t>
-  </si>
-  <si>
-    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
-  </si>
-  <si>
-    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
-  </si>
-  <si>
-    <t>IN-10</t>
-  </si>
-  <si>
-    <t>Plan backups and disaster recovery</t>
-  </si>
-  <si>
-    <t>No backup strategy exists for the database or uploaded files.</t>
-  </si>
-  <si>
-    <t>Relevant once there is a real database.</t>
-  </si>
-  <si>
-    <t>LG-04</t>
-  </si>
-  <si>
-    <t>Approve the About / Contact / Order Support copy</t>
-  </si>
-  <si>
-    <t>All placeholder text.</t>
-  </si>
-  <si>
-    <t>Pages carry a visible placeholder notice.</t>
-  </si>
-  <si>
-    <t>DF-01</t>
-  </si>
-  <si>
-    <t>Industry taxonomy</t>
-  </si>
-  <si>
-    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
-  </si>
-  <si>
-    <t>Additive; adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-02</t>
-  </si>
-  <si>
-    <t>Subscribe and Save</t>
-  </si>
-  <si>
-    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
-  </si>
-  <si>
-    <t>Needs the backend.</t>
-  </si>
-  <si>
-    <t>DF-03</t>
-  </si>
-  <si>
-    <t>Frequently bought together</t>
-  </si>
-  <si>
-    <t>Bundle suggestion with a combined total and one action to add all.</t>
-  </si>
-  <si>
-    <t>Adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-04</t>
-  </si>
-  <si>
-    <t>Quick view</t>
-  </si>
-  <si>
-    <t>View a product from the listing without a page load.</t>
-  </si>
-  <si>
-    <t>DF-05</t>
-  </si>
-  <si>
-    <t>Downloadable PDF catalogues</t>
-  </si>
-  <si>
-    <t>Still how a lot of trade buying happens.</t>
-  </si>
-  <si>
-    <t>Needs the actual catalogue files.</t>
-  </si>
-  <si>
-    <t>BE-07</t>
-  </si>
-  <si>
-    <t>Seed the database from the catalogue</t>
-  </si>
-  <si>
-    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
-  </si>
-  <si>
-    <t>BE-09</t>
-  </si>
-  <si>
-    <t>Point the storefront at the database</t>
-  </si>
-  <si>
-    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
-  </si>
-  <si>
-    <t>query.ts was untouched — it never knew where products came from.</t>
-  </si>
-  <si>
-    <t>DN-01</t>
-  </si>
-  <si>
-    <t>Currency rendering</t>
-  </si>
-  <si>
-    <t>Was rendering the Arabic symbol and 4 decimals. Now always the English string AED with exactly 2 decimals, enforced by test and by a grep check.</t>
-  </si>
-  <si>
-    <t>Fixed in the initial build.</t>
-  </si>
-  <si>
-    <t>DN-02</t>
-  </si>
-  <si>
-    <t>Integer quantities</t>
-  </si>
-  <si>
-    <t>Quantities were rendering as decimals such as 3.00.</t>
-  </si>
-  <si>
-    <t>DN-03</t>
-  </si>
-  <si>
-    <t>Category filtering</t>
-  </si>
-  <si>
-    <t>Every category link redirected to the full product list. Filtering now works, including rolling a department up to everything beneath it.</t>
-  </si>
-  <si>
-    <t>DN-04</t>
-  </si>
-  <si>
-    <t>Category counts matching results</t>
-  </si>
-  <si>
-    <t>Admin and storefront counts could diverge. Counts are now derived from the same query that lists the products.</t>
-  </si>
-  <si>
-    <t>Asserted in the data checks and the API contract checks.</t>
-  </si>
-  <si>
-    <t>DN-05</t>
-  </si>
-  <si>
-    <t>Category slug collisions</t>
-  </si>
-  <si>
-    <t>Six categories shared a slug with another category, so one was unreachable and the other answered to the wrong name.</t>
-  </si>
-  <si>
-    <t>Found by the API contract check. Slugs are now unique tree-wide and asserted.</t>
-  </si>
-  <si>
-    <t>DN-06</t>
-  </si>
-  <si>
-    <t>Per-supplier invoicing</t>
-  </si>
-  <si>
-    <t>An order spanning N suppliers now produces exactly N invoices under one reference number, with per-invoice VAT summing to the order VAT without drift.</t>
-  </si>
-  <si>
-    <t>Verified end to end in the browser and by test.</t>
-  </si>
-  <si>
-    <t>DN-11</t>
-  </si>
-  <si>
-    <t>Pack and unit of measure model</t>
-  </si>
-  <si>
-    <t>The same line sells by the box and by the carton at different prices. Cart lines are keyed by product and pack so they never merge.</t>
-  </si>
-  <si>
-    <t>Outers are asserted to beat buying their contents separately.</t>
-  </si>
-  <si>
-    <t>DN-14</t>
-  </si>
-  <si>
-    <t>Control characters in generated code</t>
-  </si>
-  <si>
-    <t>Shell escaping wrote literal backspace bytes into regex rules, so every packaging and variant rule silently matched nothing while looking correct in every editor.</t>
-  </si>
-  <si>
-    <t>Found via od. A data check now asserts each variant selection matches an option.</t>
-  </si>
-  <si>
-    <t>DN-16</t>
-  </si>
-  <si>
-    <t>Database schema designed and migrated</t>
-  </si>
-  <si>
-    <t>Thirty tables covering catalogue, packs as SKUs, variants, attributes, documents, batches, orders, per-supplier invoices, quotes, bulk upload and audit.</t>
-  </si>
-  <si>
-    <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
-  </si>
-  <si>
-    <t>DN-17</t>
-  </si>
-  <si>
-    <t>Typecheck was silently passing on a stale cache</t>
-  </si>
-  <si>
-    <t>tsc ran with incremental caching and reported no errors while real type errors existed in the tree. Every earlier typecheck-clean claim was suspect.</t>
-  </si>
-  <si>
-    <t>npm run typecheck now runs with --incremental false. Caught seven genuine errors the moment it was disabled.</t>
-  </si>
-  <si>
-    <t>DN-18</t>
-  </si>
-  <si>
-    <t>Cart moved to the server</t>
-  </si>
-  <si>
-    <t>The cart was localStorage, so the browser held prices. It is now database rows priced entirely on the server; the client cannot tell the server what anything costs.</t>
-  </si>
-  <si>
-    <t>Guest carts are cookie-keyed. The catalogue snapshot endpoint stays until the wishlist and quote cart follow.</t>
-  </si>
-  <si>
-    <t>DN-19</t>
-  </si>
-  <si>
-    <t>Checkout writes real orders</t>
-  </si>
-  <si>
-    <t>One transaction creates the order, one invoice per supplier and every line, or nothing at all. Reference numbers are allocated server-side inside that transaction.</t>
-  </si>
-  <si>
-    <t>Verified in a browser end to end, and by 14 order invariants in npm run db:check.</t>
-  </si>
-  <si>
-    <t>FN-01</t>
-  </si>
-  <si>
-    <t>Checkout does not submit an order</t>
-  </si>
-  <si>
-    <t>Done. Checkout writes a real order in one transaction, with one invoice per supplier and a server-allocated reference number.</t>
-  </si>
-  <si>
-    <t>Payment is still not taken and no email is sent.</t>
+    <t>Account history is real</t>
+  </si>
+  <si>
+    <t>The account area showed three fabricated orders. It now reads the signed-in user's actual orders, and reorder-first is built from what they have really bought.</t>
+  </si>
+  <si>
+    <t>Says so plainly when there is no history yet, rather than showing an empty grid.</t>
   </si>
   <si>
     <t>DN-07</t>
@@ -1719,7 +1830,7 @@
   <sheetPr>
     <tabColor rgb="FF29387D"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1752,7 +1863,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1760,7 +1871,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1768,7 +1879,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1794,7 +1905,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1802,7 +1913,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1810,7 +1921,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1828,7 +1939,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="3">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1894,7 +2005,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1902,7 +2013,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1919,6 +2030,14 @@
       </c>
       <c r="B28" s="3">
         <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1936,7 +2055,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1950,496 +2069,496 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>15</v>
+        <v>65</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>12</v>
+        <v>81</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>84</v>
-      </c>
       <c r="E15" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>15</v>
+        <v>95</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>15</v>
+        <v>99</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2447,7 +2566,7 @@
         <v>104</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>105</v>
@@ -2459,10 +2578,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>107</v>
@@ -2473,7 +2592,7 @@
         <v>108</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>109</v>
@@ -2485,10 +2604,10 @@
         <v>12</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>111</v>
@@ -2499,7 +2618,7 @@
         <v>112</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>113</v>
@@ -2508,793 +2627,793 @@
         <v>114</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>34</v>
+        <v>13</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>115</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>34</v>
+      <c r="F23" s="9" t="s">
+        <v>115</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>13</v>
+        <v>143</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>12</v>
+        <v>147</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>15</v>
+        <v>155</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>13</v>
+        <v>163</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>15</v>
+        <v>167</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>15</v>
+        <v>171</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>2</v>
@@ -3302,51 +3421,51 @@
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>2</v>
@@ -3354,51 +3473,51 @@
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>2</v>
@@ -3406,25 +3525,25 @@
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F57" s="10" t="s">
         <v>252</v>
       </c>
+      <c r="E57" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>115</v>
+      </c>
       <c r="G57" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>253</v>
@@ -3435,7 +3554,7 @@
         <v>254</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>255</v>
@@ -3446,11 +3565,11 @@
       <c r="E58" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F58" s="10" t="s">
-        <v>252</v>
+      <c r="F58" s="9" t="s">
+        <v>115</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>257</v>
@@ -3461,7 +3580,7 @@
         <v>258</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>259</v>
@@ -3469,307 +3588,437 @@
       <c r="D59" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="E59" s="6" t="s">
-        <v>15</v>
+      <c r="E59" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>12</v>
+        <v>269</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>12</v>
+        <v>277</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>12</v>
+        <v>281</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>15</v>
+        <v>285</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>2</v>
+        <v>290</v>
       </c>
     </row>
     <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="68" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>15</v>
+        <v>297</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="70" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B70" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B75" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E70" s="7" t="s">
+      <c r="C75" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="E75" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F70" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>304</v>
+      <c r="F75" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H70"/>
+  <autoFilter ref="A1:H75"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3794,126 +4043,126 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>6</v>
@@ -3924,28 +4173,28 @@
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -3960,7 +4209,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3974,604 +4223,708 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>327</v>
-      </c>
       <c r="H8" s="6" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>20</v>
+        <v>348</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>122</v>
+      <c r="F17" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>327</v>
+        <v>20</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>122</v>
+      <c r="F18" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>122</v>
+      <c r="F19" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>316</v>
+        <v>415</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>122</v>
+      <c r="F20" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>409</v>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>446</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H23"/>
+  <autoFilter ref="A1:H27"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="463">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -205,6 +205,30 @@
     <t>Approval is an admin-only transition enforced in the service layer.</t>
   </si>
   <si>
+    <t>BE-20</t>
+  </si>
+  <si>
+    <t>Build the admin screens behind the dashboard</t>
+  </si>
+  <si>
+    <t>/admin authenticates and shows live figures, but every management screen is still missing: products, categories, suppliers, customers, orders, bulk upload, marketing, reports, settings.</t>
+  </si>
+  <si>
+    <t>The dashboard lists them on screen so the gap is visible rather than implied.</t>
+  </si>
+  <si>
+    <t>BE-21</t>
+  </si>
+  <si>
+    <t>Build the supplier portal behind its dashboard</t>
+  </si>
+  <si>
+    <t>The business portal authenticates and shows a supplier their own products and invoice lines, read-only. Creating and editing products, toggling stock and bulk upload are not built.</t>
+  </si>
+  <si>
+    <t>A supplier must never be able to approve their own product — the rule to enforce when editing lands.</t>
+  </si>
+  <si>
     <t>DA-01</t>
   </si>
   <si>
@@ -346,10 +370,10 @@
     <t>Remove the test credentials before any deployment</t>
   </si>
   <si>
-    <t>Four accounts exist with the password 123456: admin, musawi1989@gmail.com, supplier1, supplier2. The sign-in page lists them on screen. This is fine on a local machine and unacceptable anywhere else.</t>
-  </si>
-  <si>
-    <t>Delete the accounts or set real passwords, and remove the credentials panel from src/app/sign-in/page.tsx.</t>
+    <t>Four accounts share the password 123456: admin, musawi1989@gmail.com, supplier1, supplier2. Fine on a laptop, unacceptable anywhere else.</t>
+  </si>
+  <si>
+    <t>The on-screen credentials panel now renders only outside production, so a production build cannot leak it. The accounts themselves still must be removed or given real passwords.</t>
   </si>
   <si>
     <t>AC-05</t>
@@ -547,6 +571,18 @@
     <t>If trade accounts should be required to order, this must change — it also affects credit terms and pricing.</t>
   </si>
   <si>
+    <t>BE-22</t>
+  </si>
+  <si>
+    <t>Confirm one supplier account per company</t>
+  </si>
+  <si>
+    <t>OUR DECISION: each supplier company links to a single user. Real suppliers usually need several people with their own logins.</t>
+  </si>
+  <si>
+    <t>Schema allows it via Supplier.userId; supporting several needs a join table.</t>
+  </si>
+  <si>
     <t>DA-02</t>
   </si>
   <si>
@@ -1355,6 +1391,18 @@
   </si>
   <si>
     <t>Third-party supplier images in public/products/seed. A data check now asserts every referenced image file exists on disk.</t>
+  </si>
+  <si>
+    <t>DN-21</t>
+  </si>
+  <si>
+    <t>Three sign-in doors, one per role</t>
+  </si>
+  <si>
+    <t>Buyers sign in at the account page, suppliers at the business portal, admins at /admin. Signing in at the wrong door names the right one instead of letting someone into the wrong area.</t>
+  </si>
+  <si>
+    <t>Verified: each role accepted at its own door and rejected with 403 at the other two.</t>
   </si>
 </sst>
 </file>
@@ -1863,7 +1911,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1871,7 +1919,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1879,7 +1927,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1905,7 +1953,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1913,7 +1961,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1939,7 +1987,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1963,7 +2011,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2013,7 +2061,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2055,7 +2103,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2280,7 +2328,7 @@
         <v>63</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>64</v>
@@ -2288,8 +2336,8 @@
       <c r="D9" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>12</v>
+      <c r="E9" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>35</v>
@@ -2306,7 +2354,7 @@
         <v>67</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>68</v>
@@ -2314,8 +2362,8 @@
       <c r="D10" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>12</v>
+      <c r="E10" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>35</v>
@@ -2384,7 +2432,7 @@
         <v>79</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>80</v>
@@ -2392,8 +2440,8 @@
       <c r="D13" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>15</v>
+      <c r="E13" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>35</v>
@@ -2410,16 +2458,16 @@
         <v>83</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>15</v>
+        <v>85</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>35</v>
@@ -2428,21 +2476,21 @@
         <v>36</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>15</v>
@@ -2454,21 +2502,21 @@
         <v>36</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>15</v>
@@ -2480,7 +2528,7 @@
         <v>36</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2488,7 +2536,7 @@
         <v>93</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>94</v>
@@ -2496,8 +2544,8 @@
       <c r="D17" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>12</v>
+      <c r="E17" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>35</v>
@@ -2514,7 +2562,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>98</v>
@@ -2522,8 +2570,8 @@
       <c r="D18" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>12</v>
+      <c r="E18" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>35</v>
@@ -2540,7 +2588,7 @@
         <v>101</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>102</v>
@@ -2558,21 +2606,21 @@
         <v>36</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>12</v>
@@ -2584,21 +2632,21 @@
         <v>36</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>12</v>
@@ -2610,7 +2658,7 @@
         <v>36</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2618,7 +2666,7 @@
         <v>112</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>113</v>
@@ -2627,62 +2675,62 @@
         <v>114</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>115</v>
+      <c r="F23" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>36</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>36</v>
@@ -2708,7 +2756,7 @@
         <v>12</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>36</v>
@@ -2734,7 +2782,7 @@
         <v>13</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>36</v>
@@ -2757,10 +2805,10 @@
         <v>135</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>36</v>
@@ -2783,10 +2831,10 @@
         <v>139</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>36</v>
@@ -2800,7 +2848,7 @@
         <v>141</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>142</v>
@@ -2808,11 +2856,11 @@
       <c r="D29" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>15</v>
+      <c r="E29" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>36</v>
@@ -2826,7 +2874,7 @@
         <v>145</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>146</v>
@@ -2834,11 +2882,11 @@
       <c r="D30" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>15</v>
+      <c r="E30" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>36</v>
@@ -2864,7 +2912,7 @@
         <v>15</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>36</v>
@@ -2886,11 +2934,11 @@
       <c r="D32" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>13</v>
+      <c r="E32" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>36</v>
@@ -2916,7 +2964,7 @@
         <v>15</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>36</v>
@@ -2938,11 +2986,11 @@
       <c r="D34" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>15</v>
+      <c r="E34" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>36</v>
@@ -2964,11 +3012,11 @@
       <c r="D35" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>12</v>
+      <c r="E35" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>36</v>
@@ -2990,11 +3038,11 @@
       <c r="D36" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>12</v>
+      <c r="E36" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>36</v>
@@ -3020,7 +3068,7 @@
         <v>12</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>36</v>
@@ -3034,7 +3082,7 @@
         <v>177</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>178</v>
@@ -3046,7 +3094,7 @@
         <v>12</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>36</v>
@@ -3060,7 +3108,7 @@
         <v>181</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>182</v>
@@ -3072,7 +3120,7 @@
         <v>12</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>36</v>
@@ -3086,7 +3134,7 @@
         <v>185</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>186</v>
@@ -3098,7 +3146,7 @@
         <v>12</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>36</v>
@@ -3120,11 +3168,11 @@
       <c r="D41" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>14</v>
+      <c r="E41" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>36</v>
@@ -3150,7 +3198,7 @@
         <v>12</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>36</v>
@@ -3176,7 +3224,7 @@
         <v>12</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>36</v>
@@ -3198,11 +3246,11 @@
       <c r="D44" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="E44" s="7" t="s">
-        <v>12</v>
+      <c r="E44" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>36</v>
@@ -3228,7 +3276,7 @@
         <v>12</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>36</v>
@@ -3250,11 +3298,11 @@
       <c r="D46" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>15</v>
+      <c r="E46" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>36</v>
@@ -3280,7 +3328,7 @@
         <v>12</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>36</v>
@@ -3294,7 +3342,7 @@
         <v>217</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>218</v>
@@ -3302,11 +3350,11 @@
       <c r="D48" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>15</v>
+      <c r="E48" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>36</v>
@@ -3320,7 +3368,7 @@
         <v>221</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>222</v>
@@ -3332,7 +3380,7 @@
         <v>15</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>36</v>
@@ -3346,7 +3394,7 @@
         <v>225</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>226</v>
@@ -3358,7 +3406,7 @@
         <v>12</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>36</v>
@@ -3372,7 +3420,7 @@
         <v>229</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>230</v>
@@ -3380,11 +3428,11 @@
       <c r="D51" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="E51" s="7" t="s">
-        <v>12</v>
+      <c r="E51" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>36</v>
@@ -3398,7 +3446,7 @@
         <v>233</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>234</v>
@@ -3410,267 +3458,267 @@
         <v>15</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>36</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>2</v>
+        <v>236</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>36</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>36</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>2</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>36</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>246</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>36</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>2</v>
+        <v>251</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>15</v>
+        <v>254</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>36</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>253</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>12</v>
+        <v>257</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>36</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>261</v>
+        <v>12</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>123</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>36</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>262</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C60" s="6" t="s">
+      <c r="D60" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="E60" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="B61" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C61" s="6" t="s">
+      <c r="D61" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="E61" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H61" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="B62" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C62" s="6" t="s">
+      <c r="D62" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="E62" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>261</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>36</v>
@@ -3684,7 +3732,7 @@
         <v>275</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>276</v>
@@ -3692,11 +3740,11 @@
       <c r="D63" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="E63" s="6" t="s">
-        <v>15</v>
+      <c r="E63" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>36</v>
@@ -3722,7 +3770,7 @@
         <v>15</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>36</v>
@@ -3736,7 +3784,7 @@
         <v>283</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>284</v>
@@ -3748,7 +3796,7 @@
         <v>12</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>36</v>
@@ -3762,7 +3810,7 @@
         <v>287</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>288</v>
@@ -3770,11 +3818,11 @@
       <c r="D66" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="E66" s="7" t="s">
-        <v>12</v>
+      <c r="E66" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>36</v>
@@ -3788,7 +3836,7 @@
         <v>291</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>292</v>
@@ -3796,11 +3844,11 @@
       <c r="D67" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="E67" s="7" t="s">
-        <v>12</v>
+      <c r="E67" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>36</v>
@@ -3826,7 +3874,7 @@
         <v>12</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>36</v>
@@ -3852,7 +3900,7 @@
         <v>12</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>36</v>
@@ -3866,7 +3914,7 @@
         <v>303</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>304</v>
@@ -3874,11 +3922,11 @@
       <c r="D70" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E70" s="6" t="s">
-        <v>15</v>
+      <c r="E70" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>36</v>
@@ -3892,7 +3940,7 @@
         <v>307</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>308</v>
@@ -3904,91 +3952,91 @@
         <v>12</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>36</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>2</v>
+        <v>310</v>
       </c>
     </row>
     <row r="72" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>36</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="73" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>36</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="74" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>36</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>321</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3996,7 +4044,7 @@
         <v>322</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>323</v>
@@ -4008,7 +4056,7 @@
         <v>12</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>36</v>
@@ -4017,8 +4065,86 @@
         <v>325</v>
       </c>
     </row>
+    <row r="76" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>337</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H75"/>
+  <autoFilter ref="A1:H78"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4069,100 +4195,100 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>6</v>
@@ -4173,28 +4299,28 @@
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>6</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -4209,7 +4335,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -4249,16 +4375,16 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
@@ -4267,24 +4393,24 @@
         <v>35</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>15</v>
@@ -4293,24 +4419,24 @@
         <v>35</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>15</v>
@@ -4319,24 +4445,24 @@
         <v>35</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
@@ -4345,24 +4471,24 @@
         <v>35</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>15</v>
@@ -4371,24 +4497,24 @@
         <v>35</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>15</v>
@@ -4397,24 +4523,24 @@
         <v>35</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>15</v>
@@ -4423,24 +4549,24 @@
         <v>35</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>15</v>
@@ -4449,24 +4575,24 @@
         <v>35</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>15</v>
@@ -4475,24 +4601,24 @@
         <v>35</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>15</v>
@@ -4501,24 +4627,24 @@
         <v>35</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>15</v>
@@ -4527,24 +4653,24 @@
         <v>35</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>15</v>
@@ -4553,24 +4679,24 @@
         <v>35</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>15</v>
@@ -4579,24 +4705,24 @@
         <v>35</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>15</v>
@@ -4605,24 +4731,24 @@
         <v>35</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>15</v>
@@ -4631,24 +4757,24 @@
         <v>35</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>15</v>
@@ -4657,24 +4783,24 @@
         <v>35</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>15</v>
@@ -4683,24 +4809,24 @@
         <v>35</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>15</v>
@@ -4709,24 +4835,24 @@
         <v>35</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>15</v>
@@ -4735,196 +4861,222 @@
         <v>35</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>446</v>
+        <v>458</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H27"/>
+  <autoFilter ref="A1:H28"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -6,15 +6,16 @@
   <sheets>
     <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Needs attention" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Deferred" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Done" state="visible" r:id="rId7"/>
+    <sheet sheetId="3" name="Decisions" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Deferred" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Done" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="513">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -28,6 +29,9 @@
     <t>Total items</t>
   </si>
   <si>
+    <t>Decisions recorded</t>
+  </si>
+  <si>
     <t>Outstanding</t>
   </si>
   <si>
@@ -88,6 +92,9 @@
     <t>Security</t>
   </si>
   <si>
+    <t>Decision</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
@@ -901,6 +908,30 @@
     <t>Stored as scrypt$salt$hash so the algorithm is self-describing and can be migrated per user.</t>
   </si>
   <si>
+    <t>BE-23</t>
+  </si>
+  <si>
+    <t>Admin figures are counted live, never cached</t>
+  </si>
+  <si>
+    <t>OUR DECISION: every number on the admin dashboard is counted from the database on each request. Caching them is how the old platform let admin counts and storefront counts disagree.</t>
+  </si>
+  <si>
+    <t>Revisit only if the dashboard becomes slow, and then with explicit invalidation.</t>
+  </si>
+  <si>
+    <t>BE-24</t>
+  </si>
+  <si>
+    <t>Supplier data is scoped by query, not by filtering</t>
+  </si>
+  <si>
+    <t>OUR DECISION: a supplier's products and invoice lines are fetched through their supplier id, so another supplier's rows are never loaded rather than loaded and hidden.</t>
+  </si>
+  <si>
+    <t>Keep this rule as the supplier portal grows — filtering after fetching is how leaks happen.</t>
+  </si>
+  <si>
     <t>DA-04</t>
   </si>
   <si>
@@ -1030,6 +1061,129 @@
     <t>Pages carry a visible placeholder notice.</t>
   </si>
   <si>
+    <t>DEC-01</t>
+  </si>
+  <si>
+    <t>Fresh build — the previous site is reference only</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: nothing to do with the previous site. The extraction is mined for data and business rules; its code and behaviour are discarded.</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Its category tree, product data and bug history were kept. Its markup was not.</t>
+  </si>
+  <si>
+    <t>DEC-02</t>
+  </si>
+  <si>
+    <t>Keep the existing visual brand</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026, correcting an earlier over-broad reading: the storefront must keep the current AussieMed look, not be redesigned.</t>
+  </si>
+  <si>
+    <t>Navy #29387d, red #ea2227 and Gilroy were read from the live site's computed styles. See DA-08 for the missing Gilroy weights.</t>
+  </si>
+  <si>
+    <t>DEC-03</t>
+  </si>
+  <si>
+    <t>Local only until the client approves</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: not to go online until there is a version they are happy with locally.</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. robots noindex is site-wide. Hosting is IN-01.</t>
+  </si>
+  <si>
+    <t>DEC-04</t>
+  </si>
+  <si>
+    <t>External connectors are handled last</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: anything needing a third-party account waits until the end so the build never stalls on credentials.</t>
+  </si>
+  <si>
+    <t>Payment IN-04, SMTP IN-03, OAuth IN-05, hosting IN-01. Built behind seams with local stand-ins.</t>
+  </si>
+  <si>
+    <t>DEC-05</t>
+  </si>
+  <si>
+    <t>Follow Livingstone for B2B catalogue and pricing behaviour</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026 with livingstone.com.au as the reference, and all suggested changes accepted.</t>
+  </si>
+  <si>
+    <t>Produced the pack/UOM model, price breaks on cards, the Ex/Inc VAT toggle, variant axes, spec attributes and per-product tax class.</t>
+  </si>
+  <si>
+    <t>DEC-06</t>
+  </si>
+  <si>
+    <t>Seed the catalogue from two real suppliers for testing</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: list Chemist Warehouse and Livingstone as suppliers with 30 items each, and remove the invented placeholders.</t>
+  </si>
+  <si>
+    <t>60 real products seeded. Both are unaffiliated third parties — DA-17 must close before launch.</t>
+  </si>
+  <si>
+    <t>DEC-07</t>
+  </si>
+  <si>
+    <t>Add product images</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026. Supplier photography was downloaded for local testing.</t>
+  </si>
+  <si>
+    <t>52 of 71 products have an image. Third-party assets — DA-03 must close before launch.</t>
+  </si>
+  <si>
+    <t>DEC-08</t>
+  </si>
+  <si>
+    <t>Four test accounts with a shared placeholder password</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: admin, musawi1989@gmail.com, supplier1 and supplier2, all with 123456. Explicitly described as local testing only, chosen to be memorable, and to be changed before anything real.</t>
+  </si>
+  <si>
+    <t>Implemented as asked. SEC-01 tracks removing them; SEC-03 tracks agreeing a password policy.</t>
+  </si>
+  <si>
+    <t>DEC-09</t>
+  </si>
+  <si>
+    <t>One sign-in door per role</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the business portal is the supplier login, the account login is for buyers, and admin is reached at /admin.</t>
+  </si>
+  <si>
+    <t>Implemented. Signing in at the wrong door names the right one rather than admitting the user.</t>
+  </si>
+  <si>
+    <t>DEC-10</t>
+  </si>
+  <si>
+    <t>Record every generated value and decision in this register</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026 and repeated 15 Aug: everything invented on the client's behalf must be written down rather than left in the code.</t>
+  </si>
+  <si>
+    <t>This register is the record. docs/Things That Need Attention.xlsx is generated from it and npm run register validates it.</t>
+  </si>
+  <si>
     <t>DF-01</t>
   </si>
   <si>
@@ -1094,9 +1248,6 @@
   </si>
   <si>
     <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
-  </si>
-  <si>
-    <t>Done</t>
   </si>
   <si>
     <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
@@ -1530,10 +1681,10 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1878,7 +2029,7 @@
   <sheetPr>
     <tabColor rgb="FF29387D"/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1911,7 +2062,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1919,7 +2070,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>77</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1927,7 +2078,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>27</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1935,25 +2086,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="B11" s="3">
-        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1961,7 +2112,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1969,25 +2120,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="3">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B16" s="3">
-        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1995,7 +2146,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="3">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2003,7 +2154,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2011,25 +2162,25 @@
         <v>15</v>
       </c>
       <c r="B19" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="B22" s="3">
-        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2037,7 +2188,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="3">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2045,7 +2196,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="3">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2053,7 +2204,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2061,7 +2212,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2069,23 +2220,39 @@
         <v>22</v>
       </c>
       <c r="B27" s="3">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B28" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="3">
         <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2103,7 +2270,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2117,1429 +2284,1429 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="E16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H21" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="G25" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>2</v>
@@ -3547,51 +3714,51 @@
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>2</v>
@@ -3599,51 +3766,51 @@
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>2</v>
@@ -3651,506 +3818,868 @@
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="B63" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F63" s="10" t="s">
-        <v>273</v>
-      </c>
       <c r="G63" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="68" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>12</v>
+        <v>299</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>12</v>
+        <v>303</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="70" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="71" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="72" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="73" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>15</v>
+        <v>319</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="74" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>2</v>
+        <v>324</v>
       </c>
     </row>
     <row r="75" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>12</v>
+        <v>327</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="76" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>15</v>
+        <v>331</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>329</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>12</v>
+        <v>338</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H78"/>
+  <autoFilter ref="A1:H80"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF29387D"/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="58" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H11"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF8B90A0"/>
@@ -4169,129 +4698,129 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>338</v>
+        <v>389</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>339</v>
+        <v>390</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>340</v>
+        <v>391</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>6</v>
+        <v>275</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>342</v>
+        <v>393</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>343</v>
+        <v>394</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>344</v>
+        <v>395</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>6</v>
+        <v>275</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>345</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>346</v>
+        <v>397</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>347</v>
+        <v>398</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>348</v>
+        <v>399</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>6</v>
+        <v>275</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>349</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>350</v>
+        <v>401</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>351</v>
+        <v>402</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>352</v>
+        <v>403</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>6</v>
+        <v>275</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>2</v>
@@ -4299,28 +4828,28 @@
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>353</v>
+        <v>404</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>355</v>
+        <v>406</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>6</v>
+        <v>275</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>356</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -4330,7 +4859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF146C43"/>
@@ -4349,730 +4878,730 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>357</v>
+        <v>408</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>358</v>
+        <v>409</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>359</v>
+        <v>410</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>361</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>362</v>
+        <v>412</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>363</v>
+        <v>413</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>364</v>
+        <v>414</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>365</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>366</v>
+        <v>416</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>367</v>
+        <v>417</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>368</v>
+        <v>418</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>369</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>370</v>
+        <v>420</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>371</v>
+        <v>421</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>372</v>
+        <v>422</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>373</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>374</v>
+        <v>424</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>376</v>
+        <v>426</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>373</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>377</v>
+        <v>427</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>378</v>
+        <v>428</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>379</v>
+        <v>429</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>373</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>380</v>
+        <v>430</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>382</v>
+        <v>432</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>383</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>385</v>
+        <v>435</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>386</v>
+        <v>436</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>387</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>388</v>
+        <v>438</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>389</v>
+        <v>439</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>391</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>393</v>
+        <v>443</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>394</v>
+        <v>444</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>395</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>397</v>
+        <v>447</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>398</v>
+        <v>448</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>399</v>
+        <v>449</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>401</v>
+        <v>451</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>402</v>
+        <v>452</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>403</v>
+        <v>453</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>404</v>
+        <v>454</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>405</v>
+        <v>455</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>406</v>
+        <v>456</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>407</v>
+        <v>457</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>408</v>
+        <v>458</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>409</v>
+        <v>459</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>411</v>
+        <v>461</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>412</v>
+        <v>462</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>413</v>
+        <v>463</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>414</v>
+        <v>464</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>415</v>
+        <v>465</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>417</v>
+        <v>467</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>418</v>
+        <v>468</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>419</v>
+        <v>469</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>422</v>
+        <v>472</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>423</v>
+        <v>473</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>425</v>
+        <v>475</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>426</v>
+        <v>476</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>427</v>
+        <v>477</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>428</v>
+        <v>478</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>429</v>
+        <v>479</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>430</v>
+        <v>480</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>360</v>
+        <v>37</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>431</v>
+        <v>481</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>432</v>
+        <v>482</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>433</v>
+        <v>483</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>434</v>
+        <v>484</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>360</v>
+        <v>125</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>435</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>438</v>
+        <v>488</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>360</v>
+        <v>125</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>439</v>
+        <v>489</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>441</v>
+        <v>491</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>442</v>
+        <v>492</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>360</v>
+        <v>125</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>349</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>443</v>
+        <v>493</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>444</v>
+        <v>494</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>445</v>
+        <v>495</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>360</v>
+        <v>125</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>446</v>
+        <v>496</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>447</v>
+        <v>497</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>448</v>
+        <v>498</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>449</v>
+        <v>499</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>360</v>
+        <v>125</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>451</v>
+        <v>501</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>452</v>
+        <v>502</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>453</v>
+        <v>503</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>360</v>
+        <v>125</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>454</v>
+        <v>504</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>455</v>
+        <v>505</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>457</v>
+        <v>507</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>360</v>
+        <v>125</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>458</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>459</v>
+        <v>509</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>460</v>
+        <v>510</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>461</v>
+        <v>511</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>360</v>
+        <v>125</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>462</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="537">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -284,6 +284,18 @@
     <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
   </si>
   <si>
+    <t>DA-20</t>
+  </si>
+  <si>
+    <t>Supply the real packaging quantities</t>
+  </si>
+  <si>
+    <t>OUR INVENTED VALUES: how many units make a carton, and how many cartons make a box, are guessed per product family (12 and 4 by default, 10 and 5 for gloves, 20 and 5 for masks). The break discounts of 4% and 8% are also invented.</t>
+  </si>
+  <si>
+    <t>These are now shown to buyers as CARTON and BOX, so a wrong number reads as a factual claim about your packaging. In scripts/variants.mjs.</t>
+  </si>
+  <si>
     <t>FN-02</t>
   </si>
   <si>
@@ -590,6 +602,18 @@
     <t>Schema allows it via Supplier.userId; supporting several needs a join table.</t>
   </si>
   <si>
+    <t>BE-25</t>
+  </si>
+  <si>
+    <t>Invalidate the catalogue cache after a seed or an edit</t>
+  </si>
+  <si>
+    <t>The data layer caches the catalogue for the life of the process. Re-seeding the database left the running server serving stale products until it was restarted.</t>
+  </si>
+  <si>
+    <t>invalidateCatalog() exists but nothing calls it. Becomes urgent when admin editing lands, since an edit must show immediately.</t>
+  </si>
+  <si>
     <t>DA-02</t>
   </si>
   <si>
@@ -710,6 +734,18 @@
     <t>Both addresses are meant to receive order notifications once email exists.</t>
   </si>
   <si>
+    <t>DA-21</t>
+  </si>
+  <si>
+    <t>Verify the automatic variant grouping</t>
+  </si>
+  <si>
+    <t>Products are grouped into families by stripping sizes and volumes from their names. It found 2 families in the seeded catalogue. A real catalogue will group differently and some groupings will be wrong.</t>
+  </si>
+  <si>
+    <t>The admin product screens should let a family be set explicitly rather than inferred — see BE-20.</t>
+  </si>
+  <si>
     <t>FN-07</t>
   </si>
   <si>
@@ -1184,6 +1220,30 @@
     <t>This register is the record. docs/Things That Need Attention.xlsx is generated from it and npm run register validates it.</t>
   </si>
   <si>
+    <t>DEC-11</t>
+  </si>
+  <si>
+    <t>Price breaks are packaging levels, not arbitrary quantities</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: a break at 12 exists because a carton holds 12, and a break at 48 because a box holds 4 cartons. The quantity and the packaging level are the same fact.</t>
+  </si>
+  <si>
+    <t>Each break now carries its level name. Corrects an earlier model that treated breaks as percentage discounts at round numbers.</t>
+  </si>
+  <si>
+    <t>DEC-12</t>
+  </si>
+  <si>
+    <t>Variants are a dropdown across sibling products</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the 375ml and the 60ml stay as separate products, and each carries a dropdown listing the whole family so a buyer can find their part quickly.</t>
+  </si>
+  <si>
+    <t>Replaces the Each/Carton chips on cards. Implemented as navigation between products, not options on one product, because each size has its own SKU, stock and price.</t>
+  </si>
+  <si>
     <t>DF-01</t>
   </si>
   <si>
@@ -1554,6 +1614,18 @@
   </si>
   <si>
     <t>Verified: each role accepted at its own door and rejected with 403 at the other two.</t>
+  </si>
+  <si>
+    <t>BE-26</t>
+  </si>
+  <si>
+    <t>Seed now upserts instead of wiping</t>
+  </si>
+  <si>
+    <t>Once orders existed, re-seeding failed on a foreign key: order lines reference SKU rows. The database was correctly refusing to let a re-seed destroy order history.</t>
+  </si>
+  <si>
+    <t>Products, SKUs, categories and brands are matched on natural keys and updated in place. Products absent from the catalogue are deactivated, never deleted.</t>
   </si>
 </sst>
 </file>
@@ -2062,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2070,7 +2142,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2078,7 +2150,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2086,7 +2158,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2112,7 +2184,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2120,7 +2192,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2146,7 +2218,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2170,7 +2242,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2196,7 +2268,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2220,7 +2292,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2270,7 +2342,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2651,7 +2723,7 @@
         <v>89</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>90</v>
@@ -2659,8 +2731,8 @@
       <c r="D15" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>16</v>
+      <c r="E15" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>37</v>
@@ -2683,7 +2755,7 @@
         <v>94</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
@@ -2695,21 +2767,21 @@
         <v>38</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
@@ -2721,7 +2793,7 @@
         <v>38</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2729,7 +2801,7 @@
         <v>99</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>100</v>
@@ -2763,8 +2835,8 @@
       <c r="D19" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>13</v>
+      <c r="E19" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>37</v>
@@ -2781,7 +2853,7 @@
         <v>107</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>108</v>
@@ -2825,21 +2897,21 @@
         <v>38</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>13</v>
@@ -2851,7 +2923,7 @@
         <v>38</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2859,7 +2931,7 @@
         <v>118</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>119</v>
@@ -2885,7 +2957,7 @@
         <v>122</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>123</v>
@@ -2894,36 +2966,36 @@
         <v>124</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C25" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="E25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>129</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>38</v>
@@ -2946,10 +3018,10 @@
         <v>133</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>38</v>
@@ -2972,10 +3044,10 @@
         <v>137</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>38</v>
@@ -2998,10 +3070,10 @@
         <v>141</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>38</v>
@@ -3027,7 +3099,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>38</v>
@@ -3050,10 +3122,10 @@
         <v>149</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>38</v>
@@ -3067,7 +3139,7 @@
         <v>151</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>152</v>
@@ -3075,11 +3147,11 @@
       <c r="D31" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>16</v>
+      <c r="E31" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>38</v>
@@ -3105,7 +3177,7 @@
         <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>38</v>
@@ -3131,7 +3203,7 @@
         <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>38</v>
@@ -3153,11 +3225,11 @@
       <c r="D34" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>14</v>
+      <c r="E34" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>38</v>
@@ -3179,11 +3251,11 @@
       <c r="D35" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>16</v>
+      <c r="E35" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>38</v>
@@ -3209,7 +3281,7 @@
         <v>16</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>38</v>
@@ -3231,11 +3303,11 @@
       <c r="D37" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>13</v>
+      <c r="E37" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>38</v>
@@ -3261,7 +3333,7 @@
         <v>13</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>38</v>
@@ -3287,7 +3359,7 @@
         <v>13</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>38</v>
@@ -3313,7 +3385,7 @@
         <v>13</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>38</v>
@@ -3327,7 +3399,7 @@
         <v>191</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>192</v>
@@ -3339,7 +3411,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>38</v>
@@ -3353,7 +3425,7 @@
         <v>195</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>196</v>
@@ -3361,11 +3433,11 @@
       <c r="D42" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>13</v>
+      <c r="E42" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>38</v>
@@ -3391,7 +3463,7 @@
         <v>13</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>38</v>
@@ -3413,11 +3485,11 @@
       <c r="D44" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>15</v>
+      <c r="E44" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>38</v>
@@ -3443,7 +3515,7 @@
         <v>13</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>38</v>
@@ -3465,11 +3537,11 @@
       <c r="D46" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="E46" s="7" t="s">
-        <v>13</v>
+      <c r="E46" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>38</v>
@@ -3495,7 +3567,7 @@
         <v>13</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>38</v>
@@ -3521,7 +3593,7 @@
         <v>13</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>38</v>
@@ -3543,11 +3615,11 @@
       <c r="D49" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>16</v>
+      <c r="E49" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>38</v>
@@ -3573,7 +3645,7 @@
         <v>13</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>38</v>
@@ -3587,7 +3659,7 @@
         <v>231</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>232</v>
@@ -3599,7 +3671,7 @@
         <v>16</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>38</v>
@@ -3613,7 +3685,7 @@
         <v>235</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>236</v>
@@ -3621,11 +3693,11 @@
       <c r="D52" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="E52" s="6" t="s">
-        <v>16</v>
+      <c r="E52" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>38</v>
@@ -3639,7 +3711,7 @@
         <v>239</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>240</v>
@@ -3651,7 +3723,7 @@
         <v>13</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>38</v>
@@ -3665,7 +3737,7 @@
         <v>243</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>244</v>
@@ -3673,11 +3745,11 @@
       <c r="D54" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E54" s="7" t="s">
-        <v>13</v>
+      <c r="E54" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>38</v>
@@ -3691,7 +3763,7 @@
         <v>247</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>248</v>
@@ -3703,267 +3775,267 @@
         <v>16</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>2</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>2</v>
+        <v>258</v>
       </c>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>260</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>2</v>
+        <v>265</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>16</v>
+        <v>268</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>267</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>13</v>
+        <v>271</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>275</v>
+        <v>13</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B63" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C63" s="6" t="s">
+      <c r="D63" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="E63" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H63" s="6" t="s">
         <v>279</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="B64" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C64" s="6" t="s">
+      <c r="D64" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="E64" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="B65" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C65" s="6" t="s">
+      <c r="D65" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="E65" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F65" s="10" t="s">
         <v>287</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>275</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>38</v>
@@ -3977,7 +4049,7 @@
         <v>289</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>290</v>
@@ -3985,11 +4057,11 @@
       <c r="D66" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>16</v>
+      <c r="E66" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>38</v>
@@ -4015,7 +4087,7 @@
         <v>16</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>38</v>
@@ -4037,11 +4109,11 @@
       <c r="D68" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>16</v>
+      <c r="E68" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>38</v>
@@ -4067,7 +4139,7 @@
         <v>16</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>38</v>
@@ -4081,7 +4153,7 @@
         <v>305</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>306</v>
@@ -4089,11 +4161,11 @@
       <c r="D70" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="E70" s="7" t="s">
-        <v>13</v>
+      <c r="E70" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>38</v>
@@ -4107,7 +4179,7 @@
         <v>309</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>310</v>
@@ -4115,11 +4187,11 @@
       <c r="D71" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="E71" s="7" t="s">
-        <v>13</v>
+      <c r="E71" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>38</v>
@@ -4133,7 +4205,7 @@
         <v>313</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>314</v>
@@ -4141,11 +4213,11 @@
       <c r="D72" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="E72" s="7" t="s">
-        <v>13</v>
+      <c r="E72" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>38</v>
@@ -4171,7 +4243,7 @@
         <v>13</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>38</v>
@@ -4197,7 +4269,7 @@
         <v>13</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>38</v>
@@ -4211,7 +4283,7 @@
         <v>325</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>326</v>
@@ -4219,11 +4291,11 @@
       <c r="D75" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>16</v>
+      <c r="E75" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>38</v>
@@ -4237,7 +4309,7 @@
         <v>329</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>330</v>
@@ -4249,91 +4321,91 @@
         <v>13</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>2</v>
+        <v>332</v>
       </c>
     </row>
     <row r="77" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>343</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4341,7 +4413,7 @@
         <v>344</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>345</v>
@@ -4353,7 +4425,7 @@
         <v>13</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>38</v>
@@ -4362,8 +4434,86 @@
         <v>347</v>
       </c>
     </row>
+    <row r="81" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>359</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H80"/>
+  <autoFilter ref="A1:H83"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4374,7 +4524,7 @@
   <sheetPr>
     <tabColor rgb="FF29387D"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -4414,266 +4564,318 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>388</v>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>408</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4724,100 +4926,100 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
@@ -4828,28 +5030,28 @@
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -4864,7 +5066,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -4904,16 +5106,16 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>16</v>
@@ -4922,24 +5124,24 @@
         <v>37</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
@@ -4948,24 +5150,24 @@
         <v>37</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
@@ -4974,24 +5176,24 @@
         <v>37</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
@@ -5000,24 +5202,24 @@
         <v>37</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
@@ -5026,24 +5228,24 @@
         <v>37</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
@@ -5052,24 +5254,24 @@
         <v>37</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>16</v>
@@ -5078,24 +5280,24 @@
         <v>37</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>16</v>
@@ -5104,24 +5306,24 @@
         <v>37</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
@@ -5130,24 +5332,24 @@
         <v>37</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
@@ -5156,24 +5358,24 @@
         <v>37</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>16</v>
@@ -5182,24 +5384,24 @@
         <v>37</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>16</v>
@@ -5208,24 +5410,24 @@
         <v>37</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>16</v>
@@ -5234,24 +5436,24 @@
         <v>37</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
@@ -5260,24 +5462,24 @@
         <v>37</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
@@ -5286,24 +5488,24 @@
         <v>37</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
@@ -5312,24 +5514,24 @@
         <v>37</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
@@ -5338,24 +5540,24 @@
         <v>37</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
@@ -5364,24 +5566,24 @@
         <v>37</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>16</v>
@@ -5390,222 +5592,248 @@
         <v>37</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>496</v>
+        <v>516</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>512</v>
+        <v>532</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>536</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H28"/>
+  <autoFilter ref="A1:H29"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="569">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -197,7 +197,7 @@
     <t>Products, categories, suppliers, customers, orders, marketing, reports, settings.</t>
   </si>
   <si>
-    <t>Needed before the real catalogue can be loaded.</t>
+    <t>The dashboard exists at /admin and is role-guarded. The screens behind it do not — BE-20 tracks those.</t>
   </si>
   <si>
     <t>BE-03</t>
@@ -209,7 +209,7 @@
     <t>Suppliers manage their own products but can never self-approve. Must have a failing-then-passing test.</t>
   </si>
   <si>
-    <t>Approval is an admin-only transition enforced in the service layer.</t>
+    <t>The dashboard exists at /business-portal and is role-guarded and supplier-scoped. The editing screens behind it do not — BE-21 tracks those. Approval is an admin-only transition enforced in the service layer.</t>
   </si>
   <si>
     <t>BE-20</t>
@@ -236,6 +236,18 @@
     <t>A supplier must never be able to approve their own product — the rule to enforce when editing lands.</t>
   </si>
   <si>
+    <t>BE-25</t>
+  </si>
+  <si>
+    <t>Invalidate the catalogue cache after a seed or an edit</t>
+  </si>
+  <si>
+    <t>The data layer caches the catalogue for the life of the process, so a running server keeps serving whatever it read first. This is not theoretical: on 15 Aug 2026 the dev server was still showing a retired carton SKU as a purchasable unit chip on the product page, hours after the database had deactivated it.</t>
+  </si>
+  <si>
+    <t>invalidateCatalog() exists in src/lib/catalog.ts but nothing calls it. Raised to P1 because it has already served wrong information, and it becomes worse the moment admin editing lands.</t>
+  </si>
+  <si>
     <t>DA-01</t>
   </si>
   <si>
@@ -602,28 +614,16 @@
     <t>Schema allows it via Supplier.userId; supporting several needs a join table.</t>
   </si>
   <si>
-    <t>BE-25</t>
-  </si>
-  <si>
-    <t>Invalidate the catalogue cache after a seed or an edit</t>
-  </si>
-  <si>
-    <t>The data layer caches the catalogue for the life of the process. Re-seeding the database left the running server serving stale products until it was restarted.</t>
-  </si>
-  <si>
-    <t>invalidateCatalog() exists but nothing calls it. Becomes urgent when admin editing lands, since an edit must show immediately.</t>
-  </si>
-  <si>
     <t>DA-02</t>
   </si>
   <si>
     <t>Verify the product-to-category mapping</t>
   </si>
   <si>
-    <t>The extraction had no product-category link at all. All 11 real products were mapped by hand from their names.</t>
-  </si>
-  <si>
-    <t>146 categories exist; the mapping is ours and unverified.</t>
+    <t>The extraction had no product-category link at all, so every mapping on the site is ours. The catalogue is now 71 products across 146 categories and none of that mapping has been checked by anyone who knows the range.</t>
+  </si>
+  <si>
+    <t>Was written when there were 11 products. Re-measured 15 Aug 2026: 71 active products, 0 uncategorised.</t>
   </si>
   <si>
     <t>DA-05</t>
@@ -632,10 +632,10 @@
     <t>Approve the product descriptions</t>
   </si>
   <si>
-    <t>The source had no descriptions. Eleven were written from the product names and need approval before launch.</t>
-  </si>
-  <si>
-    <t>Placeholder products carry generated filler text.</t>
+    <t>The source had no descriptions. All 71 active products now carry text we generated from the product name and supplier listing, and it goes out under AussieMed's name.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: 71 of 71 active products have a generated description.</t>
   </si>
   <si>
     <t>DA-07</t>
@@ -671,7 +671,7 @@
     <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
   </si>
   <si>
-    <t>Pack is the purchasable unit; getting it wrong misprices every carton.</t>
+    <t>Largely superseded by DA-20: packaging moved from separate carton SKUs into named price breaks on 15 Aug 2026, so the invented figures now live in scripts/variants.mjs rather than in outer packs. Kept open because the underlying question — what is a real carton and box for each line — is unanswered either way.</t>
   </si>
   <si>
     <t>DA-11</t>
@@ -683,7 +683,7 @@
     <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
   </si>
   <si>
-    <t>Variant switching is not wired until sibling SKUs exist.</t>
+    <t>Re-measured 15 Aug 2026: the same five sizes and three colours are stamped on all six glove products regardless of what the supplier actually sells. FN-07 covers the wiring; this row covers the data.</t>
   </si>
   <si>
     <t>DA-12</t>
@@ -746,16 +746,52 @@
     <t>The admin product screens should let a family be set explicitly rather than inferred — see BE-20.</t>
   </si>
   <si>
+    <t>DA-23</t>
+  </si>
+  <si>
+    <t>Two suppliers were asked for; four exist</t>
+  </si>
+  <si>
+    <t>The brief was Chemist Warehouse and Livingstone for testing, with the products that made no sense removed. Northline Uniforms and AussieMed Distribution survived that clean-up and still own 11 of the 71 products between them, so a third of the supplier list and a seventh of the catalogue is left over from the old extraction.</t>
+  </si>
+  <si>
+    <t>Measured 15 Aug 2026: Livingstone 30, Chemist Warehouse 30, AussieMed Distribution 10, Northline Uniforms 1. Confirm whether the 11 stragglers go, and see DA-22 on the AussieMed Distribution name.</t>
+  </si>
+  <si>
+    <t>DA-24</t>
+  </si>
+  <si>
+    <t>19 of 71 products have no image at all</t>
+  </si>
+  <si>
+    <t>Those products render as a coloured placeholder with two letters in it. On a trade catalogue an image is often how a buyer confirms they have the right item, and a placeholder reads as a broken listing rather than a pending one.</t>
+  </si>
+  <si>
+    <t>Measured 15 Aug 2026. Includes the Omron blood pressure monitor, TENA pads, Kleenex facial tissues, Swisspers cotton tips and FESS nasal spray. Subset of DA-03.</t>
+  </si>
+  <si>
+    <t>FE-30</t>
+  </si>
+  <si>
+    <t>Prices are still labelled Ex. VAT with no way to see inc-VAT</t>
+  </si>
+  <si>
+    <t>The header toggle was removed before VAT was folded into the displayed price, so a buyer approving an invoice has no inc-VAT figure anywhere on the storefront. Checkout still adds VAT, so the total at the end is higher than every price shown.</t>
+  </si>
+  <si>
+    <t>Follow up to DEC-14. Decide whether displayed prices become VAT inclusive or the Ex. VAT labels simply stay.</t>
+  </si>
+  <si>
     <t>FN-07</t>
   </si>
   <si>
-    <t>Variant switching is not wired</t>
-  </si>
-  <si>
-    <t>Size and colour chips display the current value; other options are disabled because sibling SKUs do not exist yet.</t>
-  </si>
-  <si>
-    <t>Needs the variant model in the database.</t>
+    <t>Size and colour switching is not wired</t>
+  </si>
+  <si>
+    <t>The variant dropdown built on 15 Aug 2026 (DEC-12) switches between sibling products by size or volume, and that works. The separate Size and Colour chips on gloves and the scrub top are a different thing and still do nothing — no sibling SKU exists behind any of them.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: 13 option axes across 6 products. Every glove carries an identical Size = XS/S/M/L/XL and Colour = Black/Blue/Green with no SKU attached to any value.</t>
   </si>
   <si>
     <t>FN-08</t>
@@ -782,6 +818,18 @@
     <t>Schema-shaping — decide before the backend is built.</t>
   </si>
   <si>
+    <t>FN-11</t>
+  </si>
+  <si>
+    <t>Most categories are empty, and three departments are entirely empty</t>
+  </si>
+  <si>
+    <t>112 of the 135 leaf categories contain no products, and Kitchen, Office &amp; Stationery Supplies and Pet Care contain nothing anywhere beneath them. Every one of those is reachable from Browse All Category, so a buyer can click a department on the front page and land on an empty result.</t>
+  </si>
+  <si>
+    <t>Measured 15 Aug 2026. The tree came from Livingstone and is far wider than the 71 test products fill. Decide whether empty categories are hidden, greyed, or left visible with a message — hiding them is the usual choice but it hides the shape of the range too.</t>
+  </si>
+  <si>
     <t>IN-01</t>
   </si>
   <si>
@@ -890,10 +938,10 @@
     <t>Confirm the default price display</t>
   </si>
   <si>
-    <t>Prices default to Ex. VAT with a toggle to Inc. VAT.</t>
-  </si>
-  <si>
-    <t>Preference persists per browser.</t>
+    <t>Prices are shown Ex. VAT everywhere, and since 15 Aug 2026 there is no way for a buyer to see an inc-VAT figure at all — the header toggle was removed at the client's request before VAT was folded into the displayed price.</t>
+  </si>
+  <si>
+    <t>See DEC-14 for the decision and FE-30 for the gap it leaves open.</t>
   </si>
   <si>
     <t>BE-13</t>
@@ -998,10 +1046,10 @@
     <t>Confirm the brand list</t>
   </si>
   <si>
-    <t>Brands were assigned by reading product names.</t>
-  </si>
-  <si>
-    <t>Eleven real brands identified.</t>
+    <t>Brands were assigned by reading product names, because neither source listed a brand field. Bad extractions were caught by hand (Goat, Hello, Roger) but the list has never been checked against reality.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: 34 brands, up from the 11 first identified.</t>
   </si>
   <si>
     <t>DA-15</t>
@@ -1013,7 +1061,7 @@
     <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
   </si>
   <si>
-    <t>Affected: Respiratory Management, Oral Care, Monitoring &amp; Testing, Dispensers, Bags, Medicine.</t>
+    <t>Re-measured 15 Aug 2026: still 6 duplicated names, 12 categories in total. Slugs are disambiguated by appending the numeric id (oral-care vs oral-care-96). 10 of the 12 hold no products at all, so most of the duplication is invisible to buyers today.</t>
   </si>
   <si>
     <t>DA-16</t>
@@ -1028,6 +1076,18 @@
     <t>Confirm this is intentional rather than lost.</t>
   </si>
   <si>
+    <t>DA-22</t>
+  </si>
+  <si>
+    <t>Supplier 1 is named AussieMed Distribution rather than a real trading name</t>
+  </si>
+  <si>
+    <t>The supplier1 login and its company record are named after the storefront itself, so a supplier signing in sees the AussieMed name in the header where their own company should be. The other seeded supplier is correctly Chemist Warehouse.</t>
+  </si>
+  <si>
+    <t>Surfaced by the header change, which now prints the full account name. Confirm whether supplier 1 should be Livingstone, per DA-17.</t>
+  </si>
+  <si>
     <t>FN-10</t>
   </si>
   <si>
@@ -1242,6 +1302,42 @@
   </si>
   <si>
     <t>Replaces the Each/Carton chips on cards. Implemented as navigation between products, not options on one product, because each size has its own SKU, stock and price.</t>
+  </si>
+  <si>
+    <t>DEC-13</t>
+  </si>
+  <si>
+    <t>One sign-in button in the header, with a dropdown per role</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: replace the Business portal and Account links with a single blue Sign in button whose dropdown offers sign in as a buyer and sign in as a supplier.</t>
+  </si>
+  <si>
+    <t>Implemented in src/components/SignInMenu.tsx. Admin is deliberately absent from the dropdown; staff go to /admin directly. Once signed in the button becomes the way back to the user own area.</t>
+  </si>
+  <si>
+    <t>DEC-14</t>
+  </si>
+  <si>
+    <t>The AED label and the Ex/Inc VAT toggle are gone from the header</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: remove the AED text and the VAT options because VAT is to be carried in the displayed price later.</t>
+  </si>
+  <si>
+    <t>VatToggle deleted from the header. includeVat still exists in src/lib/store.tsx defaulting to ex-VAT with no UI control, so prices read ex-VAT everywhere until the pricing change lands. FE-30 tracks that follow up.</t>
+  </si>
+  <si>
+    <t>DEC-15</t>
+  </si>
+  <si>
+    <t>Sign out lives in the header, in the sign in button slot</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the sign out button always sits where the Sign in button would be when signed out.</t>
+  </si>
+  <si>
+    <t>Moved out of the account, admin and business portal pages into src/components/SignInMenu.tsx, so it is reachable from every page rather than only the dashboard. Signed in, the slot shows the account name plus Sign out.</t>
   </si>
   <si>
     <t>DF-01</t>
@@ -2134,7 +2230,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2142,7 +2238,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2150,7 +2246,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2158,7 +2254,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2184,7 +2280,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2192,7 +2288,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2200,7 +2296,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2218,7 +2314,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2242,7 +2338,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="3">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2268,7 +2364,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2284,7 +2380,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2342,7 +2438,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2530,7 +2626,7 @@
         <v>37</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>60</v>
@@ -2556,7 +2652,7 @@
         <v>37</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>64</v>
@@ -2619,7 +2715,7 @@
         <v>73</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>74</v>
@@ -2627,8 +2723,8 @@
       <c r="D11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>13</v>
+      <c r="E11" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>37</v>
@@ -2749,7 +2845,7 @@
         <v>93</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>94</v>
@@ -2757,8 +2853,8 @@
       <c r="D16" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>16</v>
+      <c r="E16" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>37</v>
@@ -2781,7 +2877,7 @@
         <v>98</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
@@ -2793,21 +2889,21 @@
         <v>38</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
@@ -2819,7 +2915,7 @@
         <v>38</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2827,7 +2923,7 @@
         <v>103</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>104</v>
@@ -2861,8 +2957,8 @@
       <c r="D20" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>13</v>
+      <c r="E20" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>37</v>
@@ -2879,7 +2975,7 @@
         <v>111</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>112</v>
@@ -2923,21 +3019,21 @@
         <v>38</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>13</v>
@@ -2949,7 +3045,7 @@
         <v>38</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2957,7 +3053,7 @@
         <v>122</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>123</v>
@@ -2983,7 +3079,7 @@
         <v>126</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>127</v>
@@ -2992,36 +3088,36 @@
         <v>128</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="E26" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="9" t="s">
         <v>133</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>38</v>
@@ -3044,10 +3140,10 @@
         <v>137</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>38</v>
@@ -3070,10 +3166,10 @@
         <v>141</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>38</v>
@@ -3096,10 +3192,10 @@
         <v>145</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>38</v>
@@ -3125,7 +3221,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>38</v>
@@ -3148,10 +3244,10 @@
         <v>153</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>38</v>
@@ -3165,7 +3261,7 @@
         <v>155</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>156</v>
@@ -3173,11 +3269,11 @@
       <c r="D32" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>16</v>
+      <c r="E32" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>38</v>
@@ -3203,7 +3299,7 @@
         <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>38</v>
@@ -3229,7 +3325,7 @@
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>38</v>
@@ -3251,11 +3347,11 @@
       <c r="D35" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>14</v>
+      <c r="E35" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>38</v>
@@ -3277,11 +3373,11 @@
       <c r="D36" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>16</v>
+      <c r="E36" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>38</v>
@@ -3307,7 +3403,7 @@
         <v>16</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>38</v>
@@ -3329,11 +3425,11 @@
       <c r="D38" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="E38" s="7" t="s">
-        <v>13</v>
+      <c r="E38" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>38</v>
@@ -3359,7 +3455,7 @@
         <v>13</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>38</v>
@@ -3385,7 +3481,7 @@
         <v>13</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>38</v>
@@ -3411,7 +3507,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>38</v>
@@ -3433,11 +3529,11 @@
       <c r="D42" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>16</v>
+      <c r="E42" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>38</v>
@@ -3463,7 +3559,7 @@
         <v>13</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>38</v>
@@ -3489,7 +3585,7 @@
         <v>13</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>38</v>
@@ -3515,7 +3611,7 @@
         <v>13</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>38</v>
@@ -3541,7 +3637,7 @@
         <v>15</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>38</v>
@@ -3567,7 +3663,7 @@
         <v>13</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>38</v>
@@ -3593,7 +3689,7 @@
         <v>13</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>38</v>
@@ -3619,7 +3715,7 @@
         <v>13</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>38</v>
@@ -3645,7 +3741,7 @@
         <v>13</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>38</v>
@@ -3671,7 +3767,7 @@
         <v>16</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>38</v>
@@ -3697,7 +3793,7 @@
         <v>13</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>38</v>
@@ -3723,7 +3819,7 @@
         <v>13</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>38</v>
@@ -3737,7 +3833,7 @@
         <v>243</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>244</v>
@@ -3745,11 +3841,11 @@
       <c r="D54" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>16</v>
+      <c r="E54" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>38</v>
@@ -3763,7 +3859,7 @@
         <v>247</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>248</v>
@@ -3771,11 +3867,11 @@
       <c r="D55" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="E55" s="6" t="s">
-        <v>16</v>
+      <c r="E55" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>38</v>
@@ -3797,11 +3893,11 @@
       <c r="D56" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="E56" s="7" t="s">
-        <v>13</v>
+      <c r="E56" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>38</v>
@@ -3815,7 +3911,7 @@
         <v>255</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>256</v>
@@ -3823,11 +3919,11 @@
       <c r="D57" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="E57" s="7" t="s">
-        <v>13</v>
+      <c r="E57" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>38</v>
@@ -3841,7 +3937,7 @@
         <v>259</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>260</v>
@@ -3853,111 +3949,111 @@
         <v>16</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>2</v>
+        <v>262</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>13</v>
+        <v>269</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>2</v>
+        <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>15</v>
+        <v>273</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>13</v>
+        <v>277</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>38</v>
@@ -3968,74 +4064,74 @@
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>16</v>
+        <v>280</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>283</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F65" s="10" t="s">
         <v>287</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>38</v>
@@ -4049,7 +4145,7 @@
         <v>289</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>290</v>
@@ -4060,86 +4156,86 @@
       <c r="E66" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F66" s="10" t="s">
-        <v>287</v>
+      <c r="F66" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>292</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="B67" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C67" s="6" t="s">
+      <c r="D67" s="6" t="s">
         <v>294</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>295</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F67" s="10" t="s">
-        <v>287</v>
+      <c r="F67" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="68" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="B68" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C68" s="6" t="s">
+      <c r="D68" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="E68" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>299</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="B69" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C69" s="6" t="s">
+      <c r="D69" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="E69" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" s="10" t="s">
         <v>303</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>287</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>38</v>
@@ -4153,7 +4249,7 @@
         <v>305</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>306</v>
@@ -4161,11 +4257,11 @@
       <c r="D70" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="E70" s="6" t="s">
-        <v>16</v>
+      <c r="E70" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>38</v>
@@ -4191,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>38</v>
@@ -4213,11 +4309,11 @@
       <c r="D72" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="E72" s="6" t="s">
-        <v>16</v>
+      <c r="E72" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>38</v>
@@ -4231,7 +4327,7 @@
         <v>317</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>318</v>
@@ -4239,11 +4335,11 @@
       <c r="D73" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="E73" s="7" t="s">
-        <v>13</v>
+      <c r="E73" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>38</v>
@@ -4257,7 +4353,7 @@
         <v>321</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>322</v>
@@ -4265,11 +4361,11 @@
       <c r="D74" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E74" s="7" t="s">
-        <v>13</v>
+      <c r="E74" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>38</v>
@@ -4283,7 +4379,7 @@
         <v>325</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>326</v>
@@ -4291,11 +4387,11 @@
       <c r="D75" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="E75" s="7" t="s">
-        <v>13</v>
+      <c r="E75" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>38</v>
@@ -4309,7 +4405,7 @@
         <v>329</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>330</v>
@@ -4317,11 +4413,11 @@
       <c r="D76" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="E76" s="7" t="s">
-        <v>13</v>
+      <c r="E76" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>38</v>
@@ -4347,7 +4443,7 @@
         <v>13</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>38</v>
@@ -4361,7 +4457,7 @@
         <v>337</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>338</v>
@@ -4369,11 +4465,11 @@
       <c r="D78" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="E78" s="6" t="s">
-        <v>16</v>
+      <c r="E78" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>38</v>
@@ -4387,7 +4483,7 @@
         <v>341</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>342</v>
@@ -4399,121 +4495,251 @@
         <v>13</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>2</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="81" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>16</v>
+        <v>351</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G82" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="83" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B83" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B88" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C83" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>359</v>
+      <c r="C88" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H83"/>
+  <autoFilter ref="A1:H88"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4524,7 +4750,7 @@
   <sheetPr>
     <tabColor rgb="FF29387D"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -4564,318 +4790,396 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>408</v>
+        <v>428</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4926,100 +5230,100 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>409</v>
+        <v>441</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>410</v>
+        <v>442</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>414</v>
+        <v>446</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>415</v>
+        <v>447</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>416</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>417</v>
+        <v>449</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>418</v>
+        <v>450</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>421</v>
+        <v>453</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>423</v>
+        <v>455</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
@@ -5030,28 +5334,28 @@
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>424</v>
+        <v>456</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>425</v>
+        <v>457</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>426</v>
+        <v>458</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>427</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -5106,16 +5410,16 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>428</v>
+        <v>460</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>429</v>
+        <v>461</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>16</v>
@@ -5124,24 +5428,24 @@
         <v>37</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>431</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>432</v>
+        <v>464</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>433</v>
+        <v>465</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>434</v>
+        <v>466</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
@@ -5150,24 +5454,24 @@
         <v>37</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>435</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
@@ -5176,24 +5480,24 @@
         <v>37</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>439</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>440</v>
+        <v>472</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>441</v>
+        <v>473</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>442</v>
+        <v>474</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
@@ -5202,24 +5506,24 @@
         <v>37</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>443</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>444</v>
+        <v>476</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
@@ -5228,24 +5532,24 @@
         <v>37</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>443</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>449</v>
+        <v>481</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
@@ -5254,24 +5558,24 @@
         <v>37</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>443</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>450</v>
+        <v>482</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>451</v>
+        <v>483</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>452</v>
+        <v>484</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>16</v>
@@ -5280,24 +5584,24 @@
         <v>37</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>453</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>16</v>
@@ -5306,24 +5610,24 @@
         <v>37</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>457</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>459</v>
+        <v>491</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
@@ -5332,24 +5636,24 @@
         <v>37</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
@@ -5358,24 +5662,24 @@
         <v>37</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>465</v>
+        <v>497</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>467</v>
+        <v>499</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>16</v>
@@ -5384,24 +5688,24 @@
         <v>37</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>469</v>
+        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>471</v>
+        <v>503</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>16</v>
@@ -5410,24 +5714,24 @@
         <v>37</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>473</v>
+        <v>505</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>16</v>
@@ -5436,24 +5740,24 @@
         <v>37</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>477</v>
+        <v>509</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>479</v>
+        <v>511</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
@@ -5462,24 +5766,24 @@
         <v>37</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>481</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
@@ -5488,24 +5792,24 @@
         <v>37</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>485</v>
+        <v>517</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>486</v>
+        <v>518</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>488</v>
+        <v>520</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
@@ -5514,24 +5818,24 @@
         <v>37</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>489</v>
+        <v>521</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>490</v>
+        <v>522</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>491</v>
+        <v>523</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>492</v>
+        <v>524</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
@@ -5540,24 +5844,24 @@
         <v>37</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
@@ -5566,24 +5870,24 @@
         <v>37</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>16</v>
@@ -5592,244 +5896,244 @@
         <v>37</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>501</v>
+        <v>533</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>505</v>
+        <v>537</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>506</v>
+        <v>538</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>509</v>
+        <v>541</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>510</v>
+        <v>542</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>514</v>
+        <v>546</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>516</v>
+        <v>548</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>517</v>
+        <v>549</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>520</v>
+        <v>552</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>521</v>
+        <v>553</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>522</v>
+        <v>554</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>523</v>
+        <v>555</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>524</v>
+        <v>556</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>525</v>
+        <v>557</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>526</v>
+        <v>558</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>527</v>
+        <v>559</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>529</v>
+        <v>561</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>530</v>
+        <v>562</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>531</v>
+        <v>563</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>532</v>
+        <v>564</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>533</v>
+        <v>565</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>534</v>
+        <v>566</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>535</v>
+        <v>567</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>536</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="577">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -236,6 +236,1155 @@
     <t>A supplier must never be able to approve their own product — the rule to enforce when editing lands.</t>
   </si>
   <si>
+    <t>DA-01</t>
+  </si>
+  <si>
+    <t>Supply the real product catalogue</t>
+  </si>
+  <si>
+    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
+  </si>
+  <si>
+    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
+  </si>
+  <si>
+    <t>DA-03</t>
+  </si>
+  <si>
+    <t>Supply product photography</t>
+  </si>
+  <si>
+    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
+  </si>
+  <si>
+    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
+  </si>
+  <si>
+    <t>DA-06</t>
+  </si>
+  <si>
+    <t>Supply the real supplier list</t>
+  </si>
+  <si>
+    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
+  </si>
+  <si>
+    <t>All are flagged isPlaceholder in the data.</t>
+  </si>
+  <si>
+    <t>DA-17</t>
+  </si>
+  <si>
+    <t>Replace the test supplier attribution</t>
+  </si>
+  <si>
+    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
+  </si>
+  <si>
+    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
+  </si>
+  <si>
+    <t>DA-20</t>
+  </si>
+  <si>
+    <t>Supply the real packaging quantities</t>
+  </si>
+  <si>
+    <t>OUR INVENTED VALUES: how many units make a carton, and how many cartons make a box, are guessed per product family (12 and 4 by default, 10 and 5 for gloves, 20 and 5 for masks). The break discounts of 4% and 8% are also invented.</t>
+  </si>
+  <si>
+    <t>These are now shown to buyers as CARTON and BOX, so a wrong number reads as a factual claim about your packaging. In scripts/variants.mjs.</t>
+  </si>
+  <si>
+    <t>FN-02</t>
+  </si>
+  <si>
+    <t>Quote requests are not delivered</t>
+  </si>
+  <si>
+    <t>Captured in the browser only.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend and an email provider.</t>
+  </si>
+  <si>
+    <t>FN-03</t>
+  </si>
+  <si>
+    <t>Bulk buy enquiries are not delivered</t>
+  </si>
+  <si>
+    <t>FN-04</t>
+  </si>
+  <si>
+    <t>Notify Me does not register a subscription</t>
+  </si>
+  <si>
+    <t>Captured locally. The restock email flow does not exist.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend.</t>
+  </si>
+  <si>
+    <t>IN-06</t>
+  </si>
+  <si>
+    <t>Remove noindex before launch</t>
+  </si>
+  <si>
+    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
+  </si>
+  <si>
+    <t>Must be removed deliberately at launch — and only then.</t>
+  </si>
+  <si>
+    <t>IN-07</t>
+  </si>
+  <si>
+    <t>Confirm the GitHub repository is private</t>
+  </si>
+  <si>
+    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
+  </si>
+  <si>
+    <t>https://github.com/musawi1989/aussiemed</t>
+  </si>
+  <si>
+    <t>LG-01</t>
+  </si>
+  <si>
+    <t>Supply terms and conditions</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
+  </si>
+  <si>
+    <t>Page exists and says so on screen.</t>
+  </si>
+  <si>
+    <t>LG-02</t>
+  </si>
+  <si>
+    <t>Supply the privacy policy</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
+  </si>
+  <si>
+    <t>LG-03</t>
+  </si>
+  <si>
+    <t>Confirm the contact email address</t>
+  </si>
+  <si>
+    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
+  </si>
+  <si>
+    <t>Also determines the sending domain for transactional email.</t>
+  </si>
+  <si>
+    <t>SEC-01</t>
+  </si>
+  <si>
+    <t>Remove the test credentials before any deployment</t>
+  </si>
+  <si>
+    <t>Four accounts share the password 123456: admin, musawi1989@gmail.com, supplier1, supplier2. Fine on a laptop, unacceptable anywhere else.</t>
+  </si>
+  <si>
+    <t>The on-screen credentials panel now renders only outside production, so a production build cannot leak it. The accounts themselves still must be removed or given real passwords.</t>
+  </si>
+  <si>
+    <t>AC-05</t>
+  </si>
+  <si>
+    <t>Confirm the VAT rate and whether it must be configurable</t>
+  </si>
+  <si>
+    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Rate must be stored on the order at the time it is placed.</t>
+  </si>
+  <si>
+    <t>AC-06</t>
+  </si>
+  <si>
+    <t>Approve the reference number format</t>
+  </si>
+  <si>
+    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
+  </si>
+  <si>
+    <t>Wording is fixed as Reference number, never order number.</t>
+  </si>
+  <si>
+    <t>AC-07</t>
+  </si>
+  <si>
+    <t>Approve the supplier invoice numbering</t>
+  </si>
+  <si>
+    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
+  </si>
+  <si>
+    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
+  </si>
+  <si>
+    <t>AC-09</t>
+  </si>
+  <si>
+    <t>Decide payment terms and credit accounts</t>
+  </si>
+  <si>
+    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
+  </si>
+  <si>
+    <t>Affects the schema — decide before the backend.</t>
+  </si>
+  <si>
+    <t>AC-11</t>
+  </si>
+  <si>
+    <t>Approve the VAT rounding method on invoices</t>
+  </si>
+  <si>
+    <t>VAT is rounded per line rather than once per invoice, so the printed lines always add up to the printed total. The alternative rounds once and can leave lines that do not sum.</t>
+  </si>
+  <si>
+    <t>Verified by test: per-invoice VAT sums to the order VAT exactly.</t>
+  </si>
+  <si>
+    <t>AC-12</t>
+  </si>
+  <si>
+    <t>Confirm the reference number sequence resets each year</t>
+  </si>
+  <si>
+    <t>OUR DECISION: the sequence restarts at 000001 each calendar year, so AM-2026-000001 and AM-2027-000001 can both exist. If accounting needs a single unbroken sequence this must change before real orders.</t>
+  </si>
+  <si>
+    <t>Held in a settings row keyed orderSequence:YYYY and incremented inside the checkout transaction.</t>
+  </si>
+  <si>
+    <t>AC-13</t>
+  </si>
+  <si>
+    <t>Decide whether an order should reserve stock</t>
+  </si>
+  <si>
+    <t>OUR DECISION: checkout does not decrement or reserve anything, because there are no stock levels — only an in/out flag. Two customers can order the last unit.</t>
+  </si>
+  <si>
+    <t>Depends on FN-08. Out-of-stock is re-checked at checkout, so a line that sold out while the form was open is rejected.</t>
+  </si>
+  <si>
+    <t>BE-04</t>
+  </si>
+  <si>
+    <t>Build comma-safe .xlsx bulk upload</t>
+  </si>
+  <si>
+    <t>Parsed natively with exceljs, never by splitting on commas — that is what broke comma-containing category names.</t>
+  </si>
+  <si>
+    <t>Unknown brands must be reported per row, never skipped silently.</t>
+  </si>
+  <si>
+    <t>BE-05</t>
+  </si>
+  <si>
+    <t>Build the email flows</t>
+  </si>
+  <si>
+    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
+  </si>
+  <si>
+    <t>Needs an SMTP provider.</t>
+  </si>
+  <si>
+    <t>BE-06</t>
+  </si>
+  <si>
+    <t>Add an audit log</t>
+  </si>
+  <si>
+    <t>Every status transition and every admin or supplier write should be recorded.</t>
+  </si>
+  <si>
+    <t>Specified in the backend spec.</t>
+  </si>
+  <si>
+    <t>BE-08</t>
+  </si>
+  <si>
+    <t>Decide money representation before any data lands</t>
+  </si>
+  <si>
+    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
+  </si>
+  <si>
+    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
+  </si>
+  <si>
+    <t>BE-10</t>
+  </si>
+  <si>
+    <t>Retire the catalogue snapshot endpoint</t>
+  </si>
+  <si>
+    <t>Client components fetch the whole catalogue from /api/v1/catalog/snapshot. Fine for 71 products; not for thousands. Goes away when the cart moves server-side.</t>
+  </si>
+  <si>
+    <t>Phase 3 removes the need.</t>
+  </si>
+  <si>
+    <t>BE-12</t>
+  </si>
+  <si>
+    <t>Merge a guest cart into the user cart on sign-in</t>
+  </si>
+  <si>
+    <t>Carts are keyed by a cookie so a visitor can shop before signing in. The merge on sign-in is specified but cannot be built until auth exists.</t>
+  </si>
+  <si>
+    <t>Cart cookie: aussiemed_cart, httpOnly, 30 day lifetime — OUR INVENTED VALUES.</t>
+  </si>
+  <si>
+    <t>BE-14</t>
+  </si>
+  <si>
+    <t>Confirm the default order and invoice status</t>
+  </si>
+  <si>
+    <t>OUR DECISION: new orders are Pending and each supplier invoice is Pending. The real workflow — who moves an order to Processing, and when an invoice becomes Issued — is not defined.</t>
+  </si>
+  <si>
+    <t>Order statuses available: Pending, Processing, Dispatched, Delivered, Cancelled.</t>
+  </si>
+  <si>
+    <t>BE-15</t>
+  </si>
+  <si>
+    <t>Passwords were built instead of the specified email OTP</t>
+  </si>
+  <si>
+    <t>BACKEND_SPEC.md specifies passwordless sign-in by emailed code. Passwords were requested instead and built. Livingstone advertises password-free login as a feature, so the spec was not arbitrary.</t>
+  </si>
+  <si>
+    <t>Both can coexist: the schema keeps otpCode and otpExpiresAt. Decide before launch.</t>
+  </si>
+  <si>
+    <t>BE-19</t>
+  </si>
+  <si>
+    <t>Guest checkout is allowed</t>
+  </si>
+  <si>
+    <t>OUR DECISION: an order can be placed without signing in, and is then tied to the cart cookie. Signing in simply attaches the order to the account.</t>
+  </si>
+  <si>
+    <t>If trade accounts should be required to order, this must change — it also affects credit terms and pricing.</t>
+  </si>
+  <si>
+    <t>BE-22</t>
+  </si>
+  <si>
+    <t>Confirm one supplier account per company</t>
+  </si>
+  <si>
+    <t>OUR DECISION: each supplier company links to a single user. Real suppliers usually need several people with their own logins.</t>
+  </si>
+  <si>
+    <t>Schema allows it via Supplier.userId; supporting several needs a join table.</t>
+  </si>
+  <si>
+    <t>DA-02</t>
+  </si>
+  <si>
+    <t>Verify the product-to-category mapping</t>
+  </si>
+  <si>
+    <t>The extraction had no product-category link at all, so every mapping on the site is ours. The catalogue is now 71 products across 146 categories and none of that mapping has been checked by anyone who knows the range.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026 after DA-23: 60 active products, 0 uncategorised.</t>
+  </si>
+  <si>
+    <t>DA-05</t>
+  </si>
+  <si>
+    <t>Approve the product descriptions</t>
+  </si>
+  <si>
+    <t>The source had no descriptions. All 71 active products now carry text we generated from the product name and supplier listing, and it goes out under AussieMed's name.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026 after DA-23: 60 of 60 active products have a generated description.</t>
+  </si>
+  <si>
+    <t>DA-07</t>
+  </si>
+  <si>
+    <t>Supply the hero banner image</t>
+  </si>
+  <si>
+    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured — only Brand, Category, Product and WebHtml folders were mirrored.</t>
+  </si>
+  <si>
+    <t>A genuine AussieMed CMS image stands in.</t>
+  </si>
+  <si>
+    <t>DA-08</t>
+  </si>
+  <si>
+    <t>Obtain Gilroy Regular and Medium</t>
+  </si>
+  <si>
+    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
+  </si>
+  <si>
+    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
+  </si>
+  <si>
+    <t>DA-10</t>
+  </si>
+  <si>
+    <t>Supply real pack and carton structures</t>
+  </si>
+  <si>
+    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
+  </si>
+  <si>
+    <t>Largely superseded by DA-20: packaging moved from separate carton SKUs into named price breaks on 15 Aug 2026, so the invented figures now live in scripts/variants.mjs rather than in outer packs. Kept open because the underlying question — what is a real carton and box for each line — is unanswered either way.</t>
+  </si>
+  <si>
+    <t>DA-11</t>
+  </si>
+  <si>
+    <t>Supply real variant data</t>
+  </si>
+  <si>
+    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: the same five sizes and three colours are stamped on all six glove products regardless of what the supplier actually sells. FN-07 covers the wiring; this row covers the data.</t>
+  </si>
+  <si>
+    <t>DA-12</t>
+  </si>
+  <si>
+    <t>Supply real product specifications</t>
+  </si>
+  <si>
+    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
+  </si>
+  <si>
+    <t>These become search filters later.</t>
+  </si>
+  <si>
+    <t>DA-13</t>
+  </si>
+  <si>
+    <t>Supply safety data sheets and spec sheets</t>
+  </si>
+  <si>
+    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
+  </si>
+  <si>
+    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
+  </si>
+  <si>
+    <t>DA-18</t>
+  </si>
+  <si>
+    <t>Product ids are derived from slugs</t>
+  </si>
+  <si>
+    <t>Carts and wishlists are stored in the browser against a product id. Ids are now hashed from the slug so they survive a re-seed, which means CHANGING A PRODUCT SLUG ORPHANS ANY SAVED CART LINE referencing it.</t>
+  </si>
+  <si>
+    <t>Resolved properly when the cart moves server-side and references SKU rows directly.</t>
+  </si>
+  <si>
+    <t>DA-19</t>
+  </si>
+  <si>
+    <t>Supplier email addresses are invented</t>
+  </si>
+  <si>
+    <t>The seed writes orders@&lt;supplier&gt;.example and accounts@&lt;supplier&gt;.example because secondaryEmail is mandatory. No supplier will receive anything at these addresses.</t>
+  </si>
+  <si>
+    <t>Both addresses are meant to receive order notifications once email exists.</t>
+  </si>
+  <si>
+    <t>DA-21</t>
+  </si>
+  <si>
+    <t>Verify the automatic variant grouping</t>
+  </si>
+  <si>
+    <t>Products are grouped into families by stripping sizes and volumes from their names. It found 2 families in the seeded catalogue. A real catalogue will group differently and some groupings will be wrong.</t>
+  </si>
+  <si>
+    <t>The admin product screens should let a family be set explicitly rather than inferred — see BE-20.</t>
+  </si>
+  <si>
+    <t>DA-24</t>
+  </si>
+  <si>
+    <t>13 of 60 products have no image</t>
+  </si>
+  <si>
+    <t>Those products render as a monogram tile rather than a photograph. It is a deliberate stand-in and reads acceptably in a grid, but on a trade catalogue an image is often how a buyer confirms they have the right item.</t>
+  </si>
+  <si>
+    <t>Was 19 of 71. Ten went with the extraction products under DA-23. Four more were added deliberately: their image files turned out to be SVG placeholders saved with a .jpg extension, which the image optimiser rejected with a 400 — see DA-25. The remaining nine have no sourceSku or sourceUrl recorded, so there is nothing to retry a fetch against, and no more third-party photography was sourced because DA-17 already limits what may ship. Subset of DA-03.</t>
+  </si>
+  <si>
+    <t>FE-30</t>
+  </si>
+  <si>
+    <t>Prices are still labelled Ex. VAT with no way to see inc-VAT</t>
+  </si>
+  <si>
+    <t>The header toggle was removed before VAT was folded into the displayed price, so a buyer approving an invoice has no inc-VAT figure anywhere on the storefront. Checkout still adds VAT, so the total at the end is higher than every price shown.</t>
+  </si>
+  <si>
+    <t>Follow up to DEC-14. Decide whether displayed prices become VAT inclusive or the Ex. VAT labels simply stay.</t>
+  </si>
+  <si>
+    <t>FN-07</t>
+  </si>
+  <si>
+    <t>Size and colour switching is not wired</t>
+  </si>
+  <si>
+    <t>The variant dropdown built on 15 Aug 2026 (DEC-12) switches between sibling products by size or volume, and that works. The separate Size and Colour chips on gloves and the scrub top are a different thing and still do nothing — no sibling SKU exists behind any of them.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: 13 option axes across 6 products. Every glove carries an identical Size = XS/S/M/L/XL and Colour = Black/Blue/Green with no SKU attached to any value.</t>
+  </si>
+  <si>
+    <t>FN-08</t>
+  </si>
+  <si>
+    <t>Stock is a boolean</t>
+  </si>
+  <si>
+    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
+  </si>
+  <si>
+    <t>Decide whether real stock levels are needed.</t>
+  </si>
+  <si>
+    <t>FN-09</t>
+  </si>
+  <si>
+    <t>Decide on expiry and short-dated stock</t>
+  </si>
+  <si>
+    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
+  </si>
+  <si>
+    <t>Schema-shaping — decide before the backend is built.</t>
+  </si>
+  <si>
+    <t>IN-01</t>
+  </si>
+  <si>
+    <t>Choose a hosting target</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. The site runs locally only.</t>
+  </si>
+  <si>
+    <t>Deliberately deferred until the build is approved.</t>
+  </si>
+  <si>
+    <t>IN-02</t>
+  </si>
+  <si>
+    <t>Choose the database</t>
+  </si>
+  <si>
+    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
+  </si>
+  <si>
+    <t>IN-03</t>
+  </si>
+  <si>
+    <t>Choose an SMTP provider and sending domain</t>
+  </si>
+  <si>
+    <t>Required for every transactional email.</t>
+  </si>
+  <si>
+    <t>Must not be the misspelled assuiemed.com domain.</t>
+  </si>
+  <si>
+    <t>IN-04</t>
+  </si>
+  <si>
+    <t>Decide on a payment gateway</t>
+  </si>
+  <si>
+    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
+  </si>
+  <si>
+    <t>LG-05</t>
+  </si>
+  <si>
+    <t>Transfer the theme licence</t>
+  </si>
+  <si>
+    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
+  </si>
+  <si>
+    <t>Repository must stay private because of this.</t>
+  </si>
+  <si>
+    <t>LG-06</t>
+  </si>
+  <si>
+    <t>Supply company registration details</t>
+  </si>
+  <si>
+    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
+  </si>
+  <si>
+    <t>SEC-02</t>
+  </si>
+  <si>
+    <t>Add rate limiting to sign-in</t>
+  </si>
+  <si>
+    <t>Nothing limits password attempts, so the sign-in endpoint can be brute forced. The spec asks for rate limiting on auth in the hardening phase.</t>
+  </si>
+  <si>
+    <t>Matters more with short passwords than with OTP.</t>
+  </si>
+  <si>
+    <t>SEC-03</t>
+  </si>
+  <si>
+    <t>Agree a password policy</t>
+  </si>
+  <si>
+    <t>No minimum length, complexity or reuse rule is enforced. 123456 was accepted because nothing rejects it.</t>
+  </si>
+  <si>
+    <t>Moot if the OTP flow in BE-15 is adopted instead.</t>
+  </si>
+  <si>
+    <t>AC-08</t>
+  </si>
+  <si>
+    <t>Confirm the rounding policy</t>
+  </si>
+  <si>
+    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Verified by test; needs sign-off that the method is acceptable.</t>
+  </si>
+  <si>
+    <t>AC-10</t>
+  </si>
+  <si>
+    <t>Confirm the default price display</t>
+  </si>
+  <si>
+    <t>Prices are shown Ex. VAT everywhere, and since 15 Aug 2026 there is no way for a buyer to see an inc-VAT figure at all — the header toggle was removed at the client's request before VAT was folded into the displayed price.</t>
+  </si>
+  <si>
+    <t>See DEC-14 for the decision and FE-30 for the gap it leaves open.</t>
+  </si>
+  <si>
+    <t>BE-13</t>
+  </si>
+  <si>
+    <t>Expire abandoned guest carts</t>
+  </si>
+  <si>
+    <t>Cart rows are never cleaned up. Every visitor who adds an item creates one that lives forever.</t>
+  </si>
+  <si>
+    <t>The spec wants abandoned carts over 24h reportable under Admin &gt; Marketing, so expiry and that report should be designed together.</t>
+  </si>
+  <si>
+    <t>BE-16</t>
+  </si>
+  <si>
+    <t>Confirm the session lifetime</t>
+  </si>
+  <si>
+    <t>OUR INVENTED VALUE: sessions last 7 days, then require signing in again. No idle timeout and no re-authentication for sensitive actions.</t>
+  </si>
+  <si>
+    <t>Cookie is httpOnly and sameSite=lax; secure only in production so local http still works.</t>
+  </si>
+  <si>
+    <t>BE-17</t>
+  </si>
+  <si>
+    <t>Purge expired sessions on a schedule</t>
+  </si>
+  <si>
+    <t>Expired session rows are never deleted. purgeExpiredSessions() exists but nothing calls it.</t>
+  </si>
+  <si>
+    <t>Trivial once any scheduled job exists.</t>
+  </si>
+  <si>
+    <t>BE-18</t>
+  </si>
+  <si>
+    <t>Password hashing uses scrypt, not bcrypt</t>
+  </si>
+  <si>
+    <t>OUR DECISION: scrypt from Node's own crypto module, so there is no dependency to keep patched. The spec names bcrypt. Both are appropriate; only src/lib/auth.ts knows the format.</t>
+  </si>
+  <si>
+    <t>Stored as scrypt$salt$hash so the algorithm is self-describing and can be migrated per user.</t>
+  </si>
+  <si>
+    <t>BE-23</t>
+  </si>
+  <si>
+    <t>Admin figures are counted live, never cached</t>
+  </si>
+  <si>
+    <t>OUR DECISION: every number on the admin dashboard is counted from the database on each request. Caching them is how the old platform let admin counts and storefront counts disagree.</t>
+  </si>
+  <si>
+    <t>Revisit only if the dashboard becomes slow, and then with explicit invalidation.</t>
+  </si>
+  <si>
+    <t>BE-24</t>
+  </si>
+  <si>
+    <t>Supplier data is scoped by query, not by filtering</t>
+  </si>
+  <si>
+    <t>OUR DECISION: a supplier's products and invoice lines are fetched through their supplier id, so another supplier's rows are never loaded rather than loaded and hidden.</t>
+  </si>
+  <si>
+    <t>Keep this rule as the supplier portal grows — filtering after fetching is how leaks happen.</t>
+  </si>
+  <si>
+    <t>DA-14</t>
+  </si>
+  <si>
+    <t>Confirm the brand list</t>
+  </si>
+  <si>
+    <t>Brands were assigned by reading product names, because neither source listed a brand field. Bad extractions were caught by hand (Goat, Hello, Roger) but the list has never been checked against reality.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026 after DA-23: 26 brands across the 60 test products.</t>
+  </si>
+  <si>
+    <t>DA-15</t>
+  </si>
+  <si>
+    <t>Decide on duplicate categories</t>
+  </si>
+  <si>
+    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: still 6 duplicated names, 12 categories in total. Slugs are disambiguated by appending the numeric id (oral-care vs oral-care-96). 10 of the 12 hold no products at all, so most of the duplication is invisible to buyers today.</t>
+  </si>
+  <si>
+    <t>DA-16</t>
+  </si>
+  <si>
+    <t>Confirm the missing department</t>
+  </si>
+  <si>
+    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
+  </si>
+  <si>
+    <t>Confirm this is intentional rather than lost.</t>
+  </si>
+  <si>
+    <t>FN-10</t>
+  </si>
+  <si>
+    <t>Search is client-side only</t>
+  </si>
+  <si>
+    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
+  </si>
+  <si>
+    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
+  </si>
+  <si>
+    <t>IN-05</t>
+  </si>
+  <si>
+    <t>Supply Google and Facebook OAuth keys</t>
+  </si>
+  <si>
+    <t>Social login endpoints currently return 501.</t>
+  </si>
+  <si>
+    <t>IN-08</t>
+  </si>
+  <si>
+    <t>Correct the git author name</t>
+  </si>
+  <si>
+    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
+  </si>
+  <si>
+    <t>Fixable with git config user.name and an amend.</t>
+  </si>
+  <si>
+    <t>IN-09</t>
+  </si>
+  <si>
+    <t>Set up continuous integration</t>
+  </si>
+  <si>
+    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
+  </si>
+  <si>
+    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
+  </si>
+  <si>
+    <t>IN-10</t>
+  </si>
+  <si>
+    <t>Plan backups and disaster recovery</t>
+  </si>
+  <si>
+    <t>No backup strategy exists for the database or uploaded files.</t>
+  </si>
+  <si>
+    <t>Relevant once there is a real database.</t>
+  </si>
+  <si>
+    <t>LG-04</t>
+  </si>
+  <si>
+    <t>Approve the About / Contact / Order Support copy</t>
+  </si>
+  <si>
+    <t>All placeholder text.</t>
+  </si>
+  <si>
+    <t>Pages carry a visible placeholder notice.</t>
+  </si>
+  <si>
+    <t>DEC-01</t>
+  </si>
+  <si>
+    <t>Fresh build — the previous site is reference only</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: nothing to do with the previous site. The extraction is mined for data and business rules; its code and behaviour are discarded.</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Its category tree, product data and bug history were kept. Its markup was not.</t>
+  </si>
+  <si>
+    <t>DEC-02</t>
+  </si>
+  <si>
+    <t>Keep the existing visual brand</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026, correcting an earlier over-broad reading: the storefront must keep the current AussieMed look, not be redesigned.</t>
+  </si>
+  <si>
+    <t>Navy #29387d, red #ea2227 and Gilroy were read from the live site's computed styles. See DA-08 for the missing Gilroy weights.</t>
+  </si>
+  <si>
+    <t>DEC-03</t>
+  </si>
+  <si>
+    <t>Local only until the client approves</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: not to go online until there is a version they are happy with locally.</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. robots noindex is site-wide. Hosting is IN-01.</t>
+  </si>
+  <si>
+    <t>DEC-04</t>
+  </si>
+  <si>
+    <t>External connectors are handled last</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: anything needing a third-party account waits until the end so the build never stalls on credentials.</t>
+  </si>
+  <si>
+    <t>Payment IN-04, SMTP IN-03, OAuth IN-05, hosting IN-01. Built behind seams with local stand-ins.</t>
+  </si>
+  <si>
+    <t>DEC-05</t>
+  </si>
+  <si>
+    <t>Follow Livingstone for B2B catalogue and pricing behaviour</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026 with livingstone.com.au as the reference, and all suggested changes accepted.</t>
+  </si>
+  <si>
+    <t>Produced the pack/UOM model, price breaks on cards, the Ex/Inc VAT toggle, variant axes, spec attributes and per-product tax class.</t>
+  </si>
+  <si>
+    <t>DEC-06</t>
+  </si>
+  <si>
+    <t>Seed the catalogue from two real suppliers for testing</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: list Chemist Warehouse and Livingstone as suppliers with 30 items each, and remove the invented placeholders.</t>
+  </si>
+  <si>
+    <t>60 real products seeded. Both are unaffiliated third parties — DA-17 must close before launch.</t>
+  </si>
+  <si>
+    <t>DEC-07</t>
+  </si>
+  <si>
+    <t>Add product images</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026. Supplier photography was downloaded for local testing.</t>
+  </si>
+  <si>
+    <t>52 of 71 products have an image. Third-party assets — DA-03 must close before launch.</t>
+  </si>
+  <si>
+    <t>DEC-08</t>
+  </si>
+  <si>
+    <t>Four test accounts with a shared placeholder password</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: admin, musawi1989@gmail.com, supplier1 and supplier2, all with 123456. Explicitly described as local testing only, chosen to be memorable, and to be changed before anything real.</t>
+  </si>
+  <si>
+    <t>Implemented as asked. SEC-01 tracks removing them; SEC-03 tracks agreeing a password policy.</t>
+  </si>
+  <si>
+    <t>DEC-09</t>
+  </si>
+  <si>
+    <t>One sign-in door per role</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the business portal is the supplier login, the account login is for buyers, and admin is reached at /admin.</t>
+  </si>
+  <si>
+    <t>Implemented. Signing in at the wrong door names the right one rather than admitting the user.</t>
+  </si>
+  <si>
+    <t>DEC-10</t>
+  </si>
+  <si>
+    <t>Record every generated value and decision in this register</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026 and repeated 15 Aug: everything invented on the client's behalf must be written down rather than left in the code.</t>
+  </si>
+  <si>
+    <t>This register is the record. docs/Things That Need Attention.xlsx is generated from it and npm run register validates it.</t>
+  </si>
+  <si>
+    <t>DEC-11</t>
+  </si>
+  <si>
+    <t>Price breaks are packaging levels, not arbitrary quantities</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: a break at 12 exists because a carton holds 12, and a break at 48 because a box holds 4 cartons. The quantity and the packaging level are the same fact.</t>
+  </si>
+  <si>
+    <t>Each break now carries its level name. Corrects an earlier model that treated breaks as percentage discounts at round numbers.</t>
+  </si>
+  <si>
+    <t>DEC-12</t>
+  </si>
+  <si>
+    <t>Variants are a dropdown across sibling products</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the 375ml and the 60ml stay as separate products, and each carries a dropdown listing the whole family so a buyer can find their part quickly.</t>
+  </si>
+  <si>
+    <t>Replaces the Each/Carton chips on cards. Implemented as navigation between products, not options on one product, because each size has its own SKU, stock and price.</t>
+  </si>
+  <si>
+    <t>DEC-13</t>
+  </si>
+  <si>
+    <t>One sign-in button in the header, with a dropdown per role</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: replace the Business portal and Account links with a single blue Sign in button whose dropdown offers sign in as a buyer and sign in as a supplier.</t>
+  </si>
+  <si>
+    <t>Implemented in src/components/SignInMenu.tsx. Admin is deliberately absent from the dropdown; staff go to /admin directly. Once signed in the button becomes the way back to the user own area.</t>
+  </si>
+  <si>
+    <t>DEC-14</t>
+  </si>
+  <si>
+    <t>The AED label and the Ex/Inc VAT toggle are gone from the header</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: remove the AED text and the VAT options because VAT is to be carried in the displayed price later.</t>
+  </si>
+  <si>
+    <t>VatToggle deleted from the header. includeVat still exists in src/lib/store.tsx defaulting to ex-VAT with no UI control, so prices read ex-VAT everywhere until the pricing change lands. FE-30 tracks that follow up.</t>
+  </si>
+  <si>
+    <t>DEC-15</t>
+  </si>
+  <si>
+    <t>Sign out lives in the header, in the sign in button slot</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the sign out button always sits where the Sign in button would be when signed out.</t>
+  </si>
+  <si>
+    <t>Moved out of the account, admin and business portal pages into src/components/SignInMenu.tsx, so it is reachable from every page rather than only the dashboard. Signed in, the slot shows the account name plus Sign out.</t>
+  </si>
+  <si>
+    <t>DEC-16</t>
+  </si>
+  <si>
+    <t>Empty categories are hidden from navigation, not removed</t>
+  </si>
+  <si>
+    <t>The category tree came from Livingstone and is far wider than the 60 test products fill. Hiding what is empty keeps every menu entry useful; removing them would lose the shape of the intended range, and hard-coding a shorter list would need maintaining by hand.</t>
+  </si>
+  <si>
+    <t>Our decision, 15 Aug 2026, taken while closing FN-11. It is computed rather than configured, so categories reappear on their own as products are filed into them. Direct URLs still work. Say if you would rather the full tree stayed visible.</t>
+  </si>
+  <si>
+    <t>DA-09</t>
+  </si>
+  <si>
+    <t>Explain the disappearing product</t>
+  </si>
+  <si>
+    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
+  </si>
+  <si>
+    <t>Deferred 15 Aug 2026. The product in question was one of the 11 removed under DA-23 and nothing is being migrated from the old platform, so this no longer affects the build. Worth revisiting only if data from the old system is ever imported.</t>
+  </si>
+  <si>
+    <t>DF-01</t>
+  </si>
+  <si>
+    <t>Industry taxonomy</t>
+  </si>
+  <si>
+    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
+  </si>
+  <si>
+    <t>Additive; adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-02</t>
+  </si>
+  <si>
+    <t>Subscribe and Save</t>
+  </si>
+  <si>
+    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
+  </si>
+  <si>
+    <t>Needs the backend.</t>
+  </si>
+  <si>
+    <t>DF-03</t>
+  </si>
+  <si>
+    <t>Frequently bought together</t>
+  </si>
+  <si>
+    <t>Bundle suggestion with a combined total and one action to add all.</t>
+  </si>
+  <si>
+    <t>Adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-04</t>
+  </si>
+  <si>
+    <t>Quick view</t>
+  </si>
+  <si>
+    <t>View a product from the listing without a page load.</t>
+  </si>
+  <si>
+    <t>DF-05</t>
+  </si>
+  <si>
+    <t>Downloadable PDF catalogues</t>
+  </si>
+  <si>
+    <t>Still how a lot of trade buying happens.</t>
+  </si>
+  <si>
+    <t>Needs the actual catalogue files.</t>
+  </si>
+  <si>
+    <t>BE-07</t>
+  </si>
+  <si>
+    <t>Seed the database from the catalogue</t>
+  </si>
+  <si>
+    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
+  </si>
+  <si>
+    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
+  </si>
+  <si>
+    <t>BE-09</t>
+  </si>
+  <si>
+    <t>Point the storefront at the database</t>
+  </si>
+  <si>
+    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
+  </si>
+  <si>
+    <t>query.ts was untouched — it never knew where products came from.</t>
+  </si>
+  <si>
+    <t>BE-11</t>
+  </si>
+  <si>
+    <t>Order pages restricted to their owner</t>
+  </si>
+  <si>
+    <t>An order was readable by anyone who guessed a sequential reference. Now an admin sees any order, the account that placed it sees it, and a guest sees only an order placed from their own cart.</t>
+  </si>
+  <si>
+    <t>A forbidden order returns 404 rather than 403, so the response cannot be used to discover which references exist.</t>
+  </si>
+  <si>
     <t>BE-25</t>
   </si>
   <si>
@@ -245,505 +1394,193 @@
     <t>The data layer caches the catalogue for the life of the process, so a running server keeps serving whatever it read first. This is not theoretical: on 15 Aug 2026 the dev server was still showing a retired carton SKU as a purchasable unit chip on the product page, hours after the database had deactivated it.</t>
   </si>
   <si>
-    <t>invalidateCatalog() exists in src/lib/catalog.ts but nothing calls it. Raised to P1 because it has already served wrong information, and it becomes worse the moment admin editing lands.</t>
-  </si>
-  <si>
-    <t>DA-01</t>
-  </si>
-  <si>
-    <t>Supply the real product catalogue</t>
-  </si>
-  <si>
-    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
-  </si>
-  <si>
-    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
-  </si>
-  <si>
-    <t>DA-03</t>
-  </si>
-  <si>
-    <t>Supply product photography</t>
-  </si>
-  <si>
-    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
-  </si>
-  <si>
-    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
-  </si>
-  <si>
-    <t>DA-06</t>
-  </si>
-  <si>
-    <t>Supply the real supplier list</t>
-  </si>
-  <si>
-    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
-  </si>
-  <si>
-    <t>All are flagged isPlaceholder in the data.</t>
-  </si>
-  <si>
-    <t>DA-17</t>
-  </si>
-  <si>
-    <t>Replace the test supplier attribution</t>
-  </si>
-  <si>
-    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
-  </si>
-  <si>
-    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
-  </si>
-  <si>
-    <t>DA-20</t>
-  </si>
-  <si>
-    <t>Supply the real packaging quantities</t>
-  </si>
-  <si>
-    <t>OUR INVENTED VALUES: how many units make a carton, and how many cartons make a box, are guessed per product family (12 and 4 by default, 10 and 5 for gloves, 20 and 5 for masks). The break discounts of 4% and 8% are also invented.</t>
-  </si>
-  <si>
-    <t>These are now shown to buyers as CARTON and BOX, so a wrong number reads as a factual claim about your packaging. In scripts/variants.mjs.</t>
-  </si>
-  <si>
-    <t>FN-02</t>
-  </si>
-  <si>
-    <t>Quote requests are not delivered</t>
-  </si>
-  <si>
-    <t>Captured in the browser only.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend and an email provider.</t>
-  </si>
-  <si>
-    <t>FN-03</t>
-  </si>
-  <si>
-    <t>Bulk buy enquiries are not delivered</t>
-  </si>
-  <si>
-    <t>FN-04</t>
-  </si>
-  <si>
-    <t>Notify Me does not register a subscription</t>
-  </si>
-  <si>
-    <t>Captured locally. The restock email flow does not exist.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend.</t>
-  </si>
-  <si>
-    <t>IN-06</t>
-  </si>
-  <si>
-    <t>Remove noindex before launch</t>
-  </si>
-  <si>
-    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
-  </si>
-  <si>
-    <t>Must be removed deliberately at launch — and only then.</t>
-  </si>
-  <si>
-    <t>IN-07</t>
-  </si>
-  <si>
-    <t>Confirm the GitHub repository is private</t>
-  </si>
-  <si>
-    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
-  </si>
-  <si>
-    <t>https://github.com/musawi1989/aussiemed</t>
-  </si>
-  <si>
-    <t>LG-01</t>
-  </si>
-  <si>
-    <t>Supply terms and conditions</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
-  </si>
-  <si>
-    <t>Page exists and says so on screen.</t>
-  </si>
-  <si>
-    <t>LG-02</t>
-  </si>
-  <si>
-    <t>Supply the privacy policy</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
-  </si>
-  <si>
-    <t>LG-03</t>
-  </si>
-  <si>
-    <t>Confirm the contact email address</t>
-  </si>
-  <si>
-    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
-  </si>
-  <si>
-    <t>Also determines the sending domain for transactional email.</t>
-  </si>
-  <si>
-    <t>SEC-01</t>
-  </si>
-  <si>
-    <t>Remove the test credentials before any deployment</t>
-  </si>
-  <si>
-    <t>Four accounts share the password 123456: admin, musawi1989@gmail.com, supplier1, supplier2. Fine on a laptop, unacceptable anywhere else.</t>
-  </si>
-  <si>
-    <t>The on-screen credentials panel now renders only outside production, so a production build cannot leak it. The accounts themselves still must be removed or given real passwords.</t>
-  </si>
-  <si>
-    <t>AC-05</t>
-  </si>
-  <si>
-    <t>Confirm the VAT rate and whether it must be configurable</t>
-  </si>
-  <si>
-    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>Rate must be stored on the order at the time it is placed.</t>
-  </si>
-  <si>
-    <t>AC-06</t>
-  </si>
-  <si>
-    <t>Approve the reference number format</t>
-  </si>
-  <si>
-    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
-  </si>
-  <si>
-    <t>Wording is fixed as Reference number, never order number.</t>
-  </si>
-  <si>
-    <t>AC-07</t>
-  </si>
-  <si>
-    <t>Approve the supplier invoice numbering</t>
-  </si>
-  <si>
-    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
-  </si>
-  <si>
-    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
-  </si>
-  <si>
-    <t>AC-09</t>
-  </si>
-  <si>
-    <t>Decide payment terms and credit accounts</t>
-  </si>
-  <si>
-    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
-  </si>
-  <si>
-    <t>Affects the schema — decide before the backend.</t>
-  </si>
-  <si>
-    <t>AC-11</t>
-  </si>
-  <si>
-    <t>Approve the VAT rounding method on invoices</t>
-  </si>
-  <si>
-    <t>VAT is rounded per line rather than once per invoice, so the printed lines always add up to the printed total. The alternative rounds once and can leave lines that do not sum.</t>
-  </si>
-  <si>
-    <t>Verified by test: per-invoice VAT sums to the order VAT exactly.</t>
-  </si>
-  <si>
-    <t>AC-12</t>
-  </si>
-  <si>
-    <t>Confirm the reference number sequence resets each year</t>
-  </si>
-  <si>
-    <t>OUR DECISION: the sequence restarts at 000001 each calendar year, so AM-2026-000001 and AM-2027-000001 can both exist. If accounting needs a single unbroken sequence this must change before real orders.</t>
-  </si>
-  <si>
-    <t>Held in a settings row keyed orderSequence:YYYY and incremented inside the checkout transaction.</t>
-  </si>
-  <si>
-    <t>AC-13</t>
-  </si>
-  <si>
-    <t>Decide whether an order should reserve stock</t>
-  </si>
-  <si>
-    <t>OUR DECISION: checkout does not decrement or reserve anything, because there are no stock levels — only an in/out flag. Two customers can order the last unit.</t>
-  </si>
-  <si>
-    <t>Depends on FN-08. Out-of-stock is re-checked at checkout, so a line that sold out while the form was open is rejected.</t>
-  </si>
-  <si>
-    <t>BE-04</t>
-  </si>
-  <si>
-    <t>Build comma-safe .xlsx bulk upload</t>
-  </si>
-  <si>
-    <t>Parsed natively with exceljs, never by splitting on commas — that is what broke comma-containing category names.</t>
-  </si>
-  <si>
-    <t>Unknown brands must be reported per row, never skipped silently.</t>
-  </si>
-  <si>
-    <t>BE-05</t>
-  </si>
-  <si>
-    <t>Build the email flows</t>
-  </si>
-  <si>
-    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
-  </si>
-  <si>
-    <t>Needs an SMTP provider.</t>
-  </si>
-  <si>
-    <t>BE-06</t>
-  </si>
-  <si>
-    <t>Add an audit log</t>
-  </si>
-  <si>
-    <t>Every status transition and every admin or supplier write should be recorded.</t>
-  </si>
-  <si>
-    <t>Specified in the backend spec.</t>
-  </si>
-  <si>
-    <t>BE-08</t>
-  </si>
-  <si>
-    <t>Decide money representation before any data lands</t>
-  </si>
-  <si>
-    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
-  </si>
-  <si>
-    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
-  </si>
-  <si>
-    <t>BE-10</t>
-  </si>
-  <si>
-    <t>Retire the catalogue snapshot endpoint</t>
-  </si>
-  <si>
-    <t>Client components fetch the whole catalogue from /api/v1/catalog/snapshot. Fine for 71 products; not for thousands. Goes away when the cart moves server-side.</t>
-  </si>
-  <si>
-    <t>Phase 3 removes the need.</t>
-  </si>
-  <si>
-    <t>BE-12</t>
-  </si>
-  <si>
-    <t>Merge a guest cart into the user cart on sign-in</t>
-  </si>
-  <si>
-    <t>Carts are keyed by a cookie so a visitor can shop before signing in. The merge on sign-in is specified but cannot be built until auth exists.</t>
-  </si>
-  <si>
-    <t>Cart cookie: aussiemed_cart, httpOnly, 30 day lifetime — OUR INVENTED VALUES.</t>
-  </si>
-  <si>
-    <t>BE-14</t>
-  </si>
-  <si>
-    <t>Confirm the default order and invoice status</t>
-  </si>
-  <si>
-    <t>OUR DECISION: new orders are Pending and each supplier invoice is Pending. The real workflow — who moves an order to Processing, and when an invoice becomes Issued — is not defined.</t>
-  </si>
-  <si>
-    <t>Order statuses available: Pending, Processing, Dispatched, Delivered, Cancelled.</t>
-  </si>
-  <si>
-    <t>BE-15</t>
-  </si>
-  <si>
-    <t>Passwords were built instead of the specified email OTP</t>
-  </si>
-  <si>
-    <t>BACKEND_SPEC.md specifies passwordless sign-in by emailed code. Passwords were requested instead and built. Livingstone advertises password-free login as a feature, so the spec was not arbitrary.</t>
-  </si>
-  <si>
-    <t>Both can coexist: the schema keeps otpCode and otpExpiresAt. Decide before launch.</t>
-  </si>
-  <si>
-    <t>BE-19</t>
-  </si>
-  <si>
-    <t>Guest checkout is allowed</t>
-  </si>
-  <si>
-    <t>OUR DECISION: an order can be placed without signing in, and is then tied to the cart cookie. Signing in simply attaches the order to the account.</t>
-  </si>
-  <si>
-    <t>If trade accounts should be required to order, this must change — it also affects credit terms and pricing.</t>
-  </si>
-  <si>
-    <t>BE-22</t>
-  </si>
-  <si>
-    <t>Confirm one supplier account per company</t>
-  </si>
-  <si>
-    <t>OUR DECISION: each supplier company links to a single user. Real suppliers usually need several people with their own logins.</t>
-  </si>
-  <si>
-    <t>Schema allows it via Supplier.userId; supporting several needs a join table.</t>
-  </si>
-  <si>
-    <t>DA-02</t>
-  </si>
-  <si>
-    <t>Verify the product-to-category mapping</t>
-  </si>
-  <si>
-    <t>The extraction had no product-category link at all, so every mapping on the site is ours. The catalogue is now 71 products across 146 categories and none of that mapping has been checked by anyone who knows the range.</t>
-  </si>
-  <si>
-    <t>Was written when there were 11 products. Re-measured 15 Aug 2026: 71 active products, 0 uncategorised.</t>
-  </si>
-  <si>
-    <t>DA-05</t>
-  </si>
-  <si>
-    <t>Approve the product descriptions</t>
-  </si>
-  <si>
-    <t>The source had no descriptions. All 71 active products now carry text we generated from the product name and supplier listing, and it goes out under AussieMed's name.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: 71 of 71 active products have a generated description.</t>
-  </si>
-  <si>
-    <t>DA-07</t>
-  </si>
-  <si>
-    <t>Supply the hero banner image</t>
-  </si>
-  <si>
-    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured — only Brand, Category, Product and WebHtml folders were mirrored.</t>
-  </si>
-  <si>
-    <t>A genuine AussieMed CMS image stands in.</t>
-  </si>
-  <si>
-    <t>DA-08</t>
-  </si>
-  <si>
-    <t>Obtain Gilroy Regular and Medium</t>
-  </si>
-  <si>
-    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
-  </si>
-  <si>
-    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
-  </si>
-  <si>
-    <t>DA-10</t>
-  </si>
-  <si>
-    <t>Supply real pack and carton structures</t>
-  </si>
-  <si>
-    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
-  </si>
-  <si>
-    <t>Largely superseded by DA-20: packaging moved from separate carton SKUs into named price breaks on 15 Aug 2026, so the invented figures now live in scripts/variants.mjs rather than in outer packs. Kept open because the underlying question — what is a real carton and box for each line — is unanswered either way.</t>
-  </si>
-  <si>
-    <t>DA-11</t>
-  </si>
-  <si>
-    <t>Supply real variant data</t>
-  </si>
-  <si>
-    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: the same five sizes and three colours are stamped on all six glove products regardless of what the supplier actually sells. FN-07 covers the wiring; this row covers the data.</t>
-  </si>
-  <si>
-    <t>DA-12</t>
-  </si>
-  <si>
-    <t>Supply real product specifications</t>
-  </si>
-  <si>
-    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
-  </si>
-  <si>
-    <t>These become search filters later.</t>
-  </si>
-  <si>
-    <t>DA-13</t>
-  </si>
-  <si>
-    <t>Supply safety data sheets and spec sheets</t>
-  </si>
-  <si>
-    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
-  </si>
-  <si>
-    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
-  </si>
-  <si>
-    <t>DA-18</t>
-  </si>
-  <si>
-    <t>Product ids are derived from slugs</t>
-  </si>
-  <si>
-    <t>Carts and wishlists are stored in the browser against a product id. Ids are now hashed from the slug so they survive a re-seed, which means CHANGING A PRODUCT SLUG ORPHANS ANY SAVED CART LINE referencing it.</t>
-  </si>
-  <si>
-    <t>Resolved properly when the cart moves server-side and references SKU rows directly.</t>
-  </si>
-  <si>
-    <t>DA-19</t>
-  </si>
-  <si>
-    <t>Supplier email addresses are invented</t>
-  </si>
-  <si>
-    <t>The seed writes orders@&lt;supplier&gt;.example and accounts@&lt;supplier&gt;.example because secondaryEmail is mandatory. No supplier will receive anything at these addresses.</t>
-  </si>
-  <si>
-    <t>Both addresses are meant to receive order notifications once email exists.</t>
-  </si>
-  <si>
-    <t>DA-21</t>
-  </si>
-  <si>
-    <t>Verify the automatic variant grouping</t>
-  </si>
-  <si>
-    <t>Products are grouped into families by stripping sizes and volumes from their names. It found 2 families in the seeded catalogue. A real catalogue will group differently and some groupings will be wrong.</t>
-  </si>
-  <si>
-    <t>The admin product screens should let a family be set explicitly rather than inferred — see BE-20.</t>
+    <t>Fixed 15 Aug 2026. The cache now carries the catalogVersion stamp it was built from and re-checks it against the database at most once a second; the seed bumps the stamp, and invalidateCatalog() bumps it too so other server processes drop their copy as well. Verified live: a running dev server went from 71 products to 60 without a restart, and the phantom carton chip disappeared.</t>
+  </si>
+  <si>
+    <t>DN-01</t>
+  </si>
+  <si>
+    <t>Currency rendering</t>
+  </si>
+  <si>
+    <t>Was rendering the Arabic symbol and 4 decimals. Now always the English string AED with exactly 2 decimals, enforced by test and by a grep check.</t>
+  </si>
+  <si>
+    <t>Fixed in the initial build.</t>
+  </si>
+  <si>
+    <t>DN-02</t>
+  </si>
+  <si>
+    <t>Integer quantities</t>
+  </si>
+  <si>
+    <t>Quantities were rendering as decimals such as 3.00.</t>
+  </si>
+  <si>
+    <t>DN-03</t>
+  </si>
+  <si>
+    <t>Category filtering</t>
+  </si>
+  <si>
+    <t>Every category link redirected to the full product list. Filtering now works, including rolling a department up to everything beneath it.</t>
+  </si>
+  <si>
+    <t>DN-04</t>
+  </si>
+  <si>
+    <t>Category counts matching results</t>
+  </si>
+  <si>
+    <t>Admin and storefront counts could diverge. Counts are now derived from the same query that lists the products.</t>
+  </si>
+  <si>
+    <t>Asserted in the data checks and the API contract checks.</t>
+  </si>
+  <si>
+    <t>DN-05</t>
+  </si>
+  <si>
+    <t>Category slug collisions</t>
+  </si>
+  <si>
+    <t>Six categories shared a slug with another category, so one was unreachable and the other answered to the wrong name.</t>
+  </si>
+  <si>
+    <t>Found by the API contract check. Slugs are now unique tree-wide and asserted.</t>
+  </si>
+  <si>
+    <t>DN-06</t>
+  </si>
+  <si>
+    <t>Per-supplier invoicing</t>
+  </si>
+  <si>
+    <t>An order spanning N suppliers now produces exactly N invoices under one reference number, with per-invoice VAT summing to the order VAT without drift.</t>
+  </si>
+  <si>
+    <t>Verified end to end in the browser and by test.</t>
+  </si>
+  <si>
+    <t>DN-11</t>
+  </si>
+  <si>
+    <t>Pack and unit of measure model</t>
+  </si>
+  <si>
+    <t>The same line sells by the box and by the carton at different prices. Cart lines are keyed by product and pack so they never merge.</t>
+  </si>
+  <si>
+    <t>Outers are asserted to beat buying their contents separately.</t>
+  </si>
+  <si>
+    <t>DN-14</t>
+  </si>
+  <si>
+    <t>Control characters in generated code</t>
+  </si>
+  <si>
+    <t>Shell escaping wrote literal backspace bytes into regex rules, so every packaging and variant rule silently matched nothing while looking correct in every editor.</t>
+  </si>
+  <si>
+    <t>Found via od. A data check now asserts each variant selection matches an option.</t>
+  </si>
+  <si>
+    <t>DN-16</t>
+  </si>
+  <si>
+    <t>Database schema designed and migrated</t>
+  </si>
+  <si>
+    <t>Thirty tables covering catalogue, packs as SKUs, variants, attributes, documents, batches, orders, per-supplier invoices, quotes, bulk upload and audit.</t>
+  </si>
+  <si>
+    <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
+  </si>
+  <si>
+    <t>DN-17</t>
+  </si>
+  <si>
+    <t>Typecheck was silently passing on a stale cache</t>
+  </si>
+  <si>
+    <t>tsc ran with incremental caching and reported no errors while real type errors existed in the tree. Every earlier typecheck-clean claim was suspect.</t>
+  </si>
+  <si>
+    <t>npm run typecheck now runs with --incremental false. Caught seven genuine errors the moment it was disabled.</t>
+  </si>
+  <si>
+    <t>DN-18</t>
+  </si>
+  <si>
+    <t>Cart moved to the server</t>
+  </si>
+  <si>
+    <t>The cart was localStorage, so the browser held prices. It is now database rows priced entirely on the server; the client cannot tell the server what anything costs.</t>
+  </si>
+  <si>
+    <t>Guest carts are cookie-keyed. The catalogue snapshot endpoint stays until the wishlist and quote cart follow.</t>
+  </si>
+  <si>
+    <t>DN-19</t>
+  </si>
+  <si>
+    <t>Checkout writes real orders</t>
+  </si>
+  <si>
+    <t>One transaction creates the order, one invoice per supplier and every line, or nothing at all. Reference numbers are allocated server-side inside that transaction.</t>
+  </si>
+  <si>
+    <t>Verified in a browser end to end, and by 14 order invariants in npm run db:check.</t>
+  </si>
+  <si>
+    <t>DN-20</t>
+  </si>
+  <si>
+    <t>Four sign-in accounts seeded</t>
+  </si>
+  <si>
+    <t>admin, musawi1989@gmail.com, supplier1 and supplier2, each able to sign in by username or email. Suppliers are attached to their seeded companies.</t>
+  </si>
+  <si>
+    <t>Seeded separately from the catalogue so re-seeding products does not remove accounts.</t>
+  </si>
+  <si>
+    <t>FN-01</t>
+  </si>
+  <si>
+    <t>Checkout does not submit an order</t>
+  </si>
+  <si>
+    <t>Done. Checkout writes a real order in one transaction, with one invoice per supplier and a server-allocated reference number.</t>
+  </si>
+  <si>
+    <t>Payment is still not taken and no email is sent.</t>
+  </si>
+  <si>
+    <t>FN-05</t>
+  </si>
+  <si>
+    <t>Real sign-in replaced the demo flag</t>
+  </si>
+  <si>
+    <t>Sign-in was a localStorage boolean anyone could set. It is now a database-backed session with a scrypt-hashed password.</t>
+  </si>
+  <si>
+    <t>Sessions are rows; signing out deletes the row, so a copied cookie stops working.</t>
+  </si>
+  <si>
+    <t>FN-06</t>
+  </si>
+  <si>
+    <t>Account history is real</t>
+  </si>
+  <si>
+    <t>The account area showed three fabricated orders. It now reads the signed-in user's actual orders, and reorder-first is built from what they have really bought.</t>
+  </si>
+  <si>
+    <t>Says so plainly when there is no history yet, rather than showing an empty grid.</t>
   </si>
   <si>
     <t>DA-23</t>
@@ -755,67 +1592,100 @@
     <t>The brief was Chemist Warehouse and Livingstone for testing, with the products that made no sense removed. Northline Uniforms and AussieMed Distribution survived that clean-up and still own 11 of the 71 products between them, so a third of the supplier list and a seventh of the catalogue is left over from the old extraction.</t>
   </si>
   <si>
-    <t>Measured 15 Aug 2026: Livingstone 30, Chemist Warehouse 30, AussieMed Distribution 10, Northline Uniforms 1. Confirm whether the 11 stragglers go, and see DA-22 on the AussieMed Distribution name.</t>
-  </si>
-  <si>
-    <t>DA-24</t>
-  </si>
-  <si>
-    <t>19 of 71 products have no image at all</t>
-  </si>
-  <si>
-    <t>Those products render as a coloured placeholder with two letters in it. On a trade catalogue an image is often how a buyer confirms they have the right item, and a placeholder reads as a broken listing rather than a pending one.</t>
-  </si>
-  <si>
-    <t>Measured 15 Aug 2026. Includes the Omron blood pressure monitor, TENA pads, Kleenex facial tissues, Swisspers cotton tips and FESS nasal spray. Subset of DA-03.</t>
-  </si>
-  <si>
-    <t>FE-30</t>
-  </si>
-  <si>
-    <t>Prices are still labelled Ex. VAT with no way to see inc-VAT</t>
-  </si>
-  <si>
-    <t>The header toggle was removed before VAT was folded into the displayed price, so a buyer approving an invoice has no inc-VAT figure anywhere on the storefront. Checkout still adds VAT, so the total at the end is higher than every price shown.</t>
-  </si>
-  <si>
-    <t>Follow up to DEC-14. Decide whether displayed prices become VAT inclusive or the Ex. VAT labels simply stay.</t>
-  </si>
-  <si>
-    <t>FN-07</t>
-  </si>
-  <si>
-    <t>Size and colour switching is not wired</t>
-  </si>
-  <si>
-    <t>The variant dropdown built on 15 Aug 2026 (DEC-12) switches between sibling products by size or volume, and that works. The separate Size and Colour chips on gloves and the scrub top are a different thing and still do nothing — no sibling SKU exists behind any of them.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: 13 option axes across 6 products. Every glove carries an identical Size = XS/S/M/L/XL and Colour = Black/Blue/Green with no SKU attached to any value.</t>
-  </si>
-  <si>
-    <t>FN-08</t>
-  </si>
-  <si>
-    <t>Stock is a boolean</t>
-  </si>
-  <si>
-    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
-  </si>
-  <si>
-    <t>Decide whether real stock levels are needed.</t>
-  </si>
-  <si>
-    <t>FN-09</t>
-  </si>
-  <si>
-    <t>Decide on expiry and short-dated stock</t>
-  </si>
-  <si>
-    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
-  </si>
-  <si>
-    <t>Schema-shaping — decide before the backend is built.</t>
+    <t>Done 15 Aug 2026. The 11 extraction products and suppliers 20 and 21 are no longer emitted by scripts/build-catalog.mjs. The database keeps them as Inactive rather than deleting them, because 2 invoices and 3 order lines still name them — order history survives. The catalogue is now exactly the 60 test products, 30 from each supplier.</t>
+  </si>
+  <si>
+    <t>DN-07</t>
+  </si>
+  <si>
+    <t>Unique page titles and meta descriptions</t>
+  </si>
+  <si>
+    <t>Every page carried the identical title 'Aussie Med || Home' with an empty description.</t>
+  </si>
+  <si>
+    <t>Built per page and per product.</t>
+  </si>
+  <si>
+    <t>DN-08</t>
+  </si>
+  <si>
+    <t>Broken cart images and unresolved asset paths</t>
+  </si>
+  <si>
+    <t>Cart images had a bare domain with no path; templates contained literal '~/' paths.</t>
+  </si>
+  <si>
+    <t>All image paths are local and asserted.</t>
+  </si>
+  <si>
+    <t>DN-09</t>
+  </si>
+  <si>
+    <t>Volume breaks visible while scanning</t>
+  </si>
+  <si>
+    <t>Only a savings badge was shown. The full break table now appears on every product card using +1/+10/+50 notation.</t>
+  </si>
+  <si>
+    <t>DN-10</t>
+  </si>
+  <si>
+    <t>Ex VAT / Inc VAT toggle</t>
+  </si>
+  <si>
+    <t>Procurement compares ex-tax and the approver reads inc-tax, so the same buyer needs both during one order.</t>
+  </si>
+  <si>
+    <t>Persists per browser.</t>
+  </si>
+  <si>
+    <t>DN-12</t>
+  </si>
+  <si>
+    <t>Adopt the existing brand theme</t>
+  </si>
+  <si>
+    <t>Navy #29387d, red #ea2227 and Gilroy, read from the live site's computed styles rather than eyeballed.</t>
+  </si>
+  <si>
+    <t>Logo, favicon and all 11 category images are the brand own.</t>
+  </si>
+  <si>
+    <t>DN-13</t>
+  </si>
+  <si>
+    <t>Catalogue seeded with real products</t>
+  </si>
+  <si>
+    <t>Sixty real items replaced invented placeholders so the storefront can be judged against products that actually exist.</t>
+  </si>
+  <si>
+    <t>Thirty from each of two public supplier catalogues, spanning 23 categories.</t>
+  </si>
+  <si>
+    <t>DN-15</t>
+  </si>
+  <si>
+    <t>Product images added for testing</t>
+  </si>
+  <si>
+    <t>Fifty-two of 71 products now carry real photography so the layout can be judged with images rather than placeholder tiles.</t>
+  </si>
+  <si>
+    <t>Third-party supplier images in public/products/seed. A data check now asserts every referenced image file exists on disk.</t>
+  </si>
+  <si>
+    <t>DN-21</t>
+  </si>
+  <si>
+    <t>Three sign-in doors, one per role</t>
+  </si>
+  <si>
+    <t>Buyers sign in at the account page, suppliers at the business portal, admins at /admin. Signing in at the wrong door names the right one instead of letting someone into the wrong area.</t>
+  </si>
+  <si>
+    <t>Verified: each role accepted at its own door and rejected with 403 at the other two.</t>
   </si>
   <si>
     <t>FN-11</t>
@@ -827,193 +1697,19 @@
     <t>112 of the 135 leaf categories contain no products, and Kitchen, Office &amp; Stationery Supplies and Pet Care contain nothing anywhere beneath them. Every one of those is reachable from Browse All Category, so a buyer can click a department on the front page and land on an empty result.</t>
   </si>
   <si>
-    <t>Measured 15 Aug 2026. The tree came from Livingstone and is far wider than the 71 test products fill. Decide whether empty categories are hidden, greyed, or left visible with a message — hiding them is the usual choice but it hides the shape of the range too.</t>
-  </si>
-  <si>
-    <t>IN-01</t>
-  </si>
-  <si>
-    <t>Choose a hosting target</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. The site runs locally only.</t>
-  </si>
-  <si>
-    <t>Deliberately deferred until the build is approved.</t>
-  </si>
-  <si>
-    <t>IN-02</t>
-  </si>
-  <si>
-    <t>Choose the database</t>
-  </si>
-  <si>
-    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
-  </si>
-  <si>
-    <t>IN-03</t>
-  </si>
-  <si>
-    <t>Choose an SMTP provider and sending domain</t>
-  </si>
-  <si>
-    <t>Required for every transactional email.</t>
-  </si>
-  <si>
-    <t>Must not be the misspelled assuiemed.com domain.</t>
-  </si>
-  <si>
-    <t>IN-04</t>
-  </si>
-  <si>
-    <t>Decide on a payment gateway</t>
-  </si>
-  <si>
-    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
-  </si>
-  <si>
-    <t>LG-05</t>
-  </si>
-  <si>
-    <t>Transfer the theme licence</t>
-  </si>
-  <si>
-    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
-  </si>
-  <si>
-    <t>Repository must stay private because of this.</t>
-  </si>
-  <si>
-    <t>LG-06</t>
-  </si>
-  <si>
-    <t>Supply company registration details</t>
-  </si>
-  <si>
-    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
-  </si>
-  <si>
-    <t>SEC-02</t>
-  </si>
-  <si>
-    <t>Add rate limiting to sign-in</t>
-  </si>
-  <si>
-    <t>Nothing limits password attempts, so the sign-in endpoint can be brute forced. The spec asks for rate limiting on auth in the hardening phase.</t>
-  </si>
-  <si>
-    <t>Matters more with short passwords than with OTP.</t>
-  </si>
-  <si>
-    <t>SEC-03</t>
-  </si>
-  <si>
-    <t>Agree a password policy</t>
-  </si>
-  <si>
-    <t>No minimum length, complexity or reuse rule is enforced. 123456 was accepted because nothing rejects it.</t>
-  </si>
-  <si>
-    <t>Moot if the OTP flow in BE-15 is adopted instead.</t>
-  </si>
-  <si>
-    <t>AC-08</t>
-  </si>
-  <si>
-    <t>Confirm the rounding policy</t>
-  </si>
-  <si>
-    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>Verified by test; needs sign-off that the method is acceptable.</t>
-  </si>
-  <si>
-    <t>AC-10</t>
-  </si>
-  <si>
-    <t>Confirm the default price display</t>
-  </si>
-  <si>
-    <t>Prices are shown Ex. VAT everywhere, and since 15 Aug 2026 there is no way for a buyer to see an inc-VAT figure at all — the header toggle was removed at the client's request before VAT was folded into the displayed price.</t>
-  </si>
-  <si>
-    <t>See DEC-14 for the decision and FE-30 for the gap it leaves open.</t>
-  </si>
-  <si>
-    <t>BE-13</t>
-  </si>
-  <si>
-    <t>Expire abandoned guest carts</t>
-  </si>
-  <si>
-    <t>Cart rows are never cleaned up. Every visitor who adds an item creates one that lives forever.</t>
-  </si>
-  <si>
-    <t>The spec wants abandoned carts over 24h reportable under Admin &gt; Marketing, so expiry and that report should be designed together.</t>
-  </si>
-  <si>
-    <t>BE-16</t>
-  </si>
-  <si>
-    <t>Confirm the session lifetime</t>
-  </si>
-  <si>
-    <t>OUR INVENTED VALUE: sessions last 7 days, then require signing in again. No idle timeout and no re-authentication for sensitive actions.</t>
-  </si>
-  <si>
-    <t>Cookie is httpOnly and sameSite=lax; secure only in production so local http still works.</t>
-  </si>
-  <si>
-    <t>BE-17</t>
-  </si>
-  <si>
-    <t>Purge expired sessions on a schedule</t>
-  </si>
-  <si>
-    <t>Expired session rows are never deleted. purgeExpiredSessions() exists but nothing calls it.</t>
-  </si>
-  <si>
-    <t>Trivial once any scheduled job exists.</t>
-  </si>
-  <si>
-    <t>BE-18</t>
-  </si>
-  <si>
-    <t>Password hashing uses scrypt, not bcrypt</t>
-  </si>
-  <si>
-    <t>OUR DECISION: scrypt from Node's own crypto module, so there is no dependency to keep patched. The spec names bcrypt. Both are appropriate; only src/lib/auth.ts knows the format.</t>
-  </si>
-  <si>
-    <t>Stored as scrypt$salt$hash so the algorithm is self-describing and can be migrated per user.</t>
-  </si>
-  <si>
-    <t>BE-23</t>
-  </si>
-  <si>
-    <t>Admin figures are counted live, never cached</t>
-  </si>
-  <si>
-    <t>OUR DECISION: every number on the admin dashboard is counted from the database on each request. Caching them is how the old platform let admin counts and storefront counts disagree.</t>
-  </si>
-  <si>
-    <t>Revisit only if the dashboard becomes slow, and then with explicit invalidation.</t>
-  </si>
-  <si>
-    <t>BE-24</t>
-  </si>
-  <si>
-    <t>Supplier data is scoped by query, not by filtering</t>
-  </si>
-  <si>
-    <t>OUR DECISION: a supplier's products and invoice lines are fetched through their supplier id, so another supplier's rows are never loaded rather than loaded and hidden.</t>
-  </si>
-  <si>
-    <t>Keep this rule as the supplier portal grows — filtering after fetching is how leaks happen.</t>
+    <t>Done 15 Aug 2026. Categories carry a product count, and the header menu and the front page tiles show only what has something in it: 8 departments instead of 11, and 23 menu entries instead of 146. Verified by walking all 23 offered categories in a browser — none is empty. Hidden categories still resolve by direct URL and show the normal no-results state, so nothing 404s and the tree fills itself back in as products arrive.</t>
+  </si>
+  <si>
+    <t>BE-26</t>
+  </si>
+  <si>
+    <t>Seed now upserts instead of wiping</t>
+  </si>
+  <si>
+    <t>Once orders existed, re-seeding failed on a foreign key: order lines reference SKU rows. The database was correctly refusing to let a re-seed destroy order history.</t>
+  </si>
+  <si>
+    <t>Products, SKUs, categories and brands are matched on natural keys and updated in place. Products absent from the catalogue are deactivated, never deleted.</t>
   </si>
   <si>
     <t>DA-04</t>
@@ -1025,55 +1721,7 @@
     <t>The product's primary image was a stock photo of a pocket watch. Excluded from the build; the file is still in public/products/.</t>
   </si>
   <si>
-    <t>Suggests image uploads were not being checked in the old admin.</t>
-  </si>
-  <si>
-    <t>DA-09</t>
-  </si>
-  <si>
-    <t>Explain the disappearing product</t>
-  </si>
-  <si>
-    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
-  </si>
-  <si>
-    <t>Evidence of a real defect in the old platform. Worth understanding before trusting any migrated data.</t>
-  </si>
-  <si>
-    <t>DA-14</t>
-  </si>
-  <si>
-    <t>Confirm the brand list</t>
-  </si>
-  <si>
-    <t>Brands were assigned by reading product names, because neither source listed a brand field. Bad extractions were caught by hand (Goat, Hello, Roger) but the list has never been checked against reality.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: 34 brands, up from the 11 first identified.</t>
-  </si>
-  <si>
-    <t>DA-15</t>
-  </si>
-  <si>
-    <t>Decide on duplicate categories</t>
-  </si>
-  <si>
-    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: still 6 duplicated names, 12 categories in total. Slugs are disambiguated by appending the numeric id (oral-care vs oral-care-96). 10 of the 12 hold no products at all, so most of the duplication is invisible to buyers today.</t>
-  </si>
-  <si>
-    <t>DA-16</t>
-  </si>
-  <si>
-    <t>Confirm the missing department</t>
-  </si>
-  <si>
-    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
-  </si>
-  <si>
-    <t>Confirm this is intentional rather than lost.</t>
+    <t>Resolved 15 Aug 2026: the scrub top was one of the 11 extraction products removed under DA-23, so the pocket watch image is no longer referenced. The file remains in public/products/ unused.</t>
   </si>
   <si>
     <t>DA-22</t>
@@ -1085,643 +1733,19 @@
     <t>The supplier1 login and its company record are named after the storefront itself, so a supplier signing in sees the AussieMed name in the header where their own company should be. The other seeded supplier is correctly Chemist Warehouse.</t>
   </si>
   <si>
-    <t>Surfaced by the header change, which now prints the full account name. Confirm whether supplier 1 should be Livingstone, per DA-17.</t>
-  </si>
-  <si>
-    <t>FN-10</t>
-  </si>
-  <si>
-    <t>Search is client-side only</t>
-  </si>
-  <si>
-    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
-  </si>
-  <si>
-    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
-  </si>
-  <si>
-    <t>IN-05</t>
-  </si>
-  <si>
-    <t>Supply Google and Facebook OAuth keys</t>
-  </si>
-  <si>
-    <t>Social login endpoints currently return 501.</t>
-  </si>
-  <si>
-    <t>IN-08</t>
-  </si>
-  <si>
-    <t>Correct the git author name</t>
-  </si>
-  <si>
-    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
-  </si>
-  <si>
-    <t>Fixable with git config user.name and an amend.</t>
-  </si>
-  <si>
-    <t>IN-09</t>
-  </si>
-  <si>
-    <t>Set up continuous integration</t>
-  </si>
-  <si>
-    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
-  </si>
-  <si>
-    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
-  </si>
-  <si>
-    <t>IN-10</t>
-  </si>
-  <si>
-    <t>Plan backups and disaster recovery</t>
-  </si>
-  <si>
-    <t>No backup strategy exists for the database or uploaded files.</t>
-  </si>
-  <si>
-    <t>Relevant once there is a real database.</t>
-  </si>
-  <si>
-    <t>LG-04</t>
-  </si>
-  <si>
-    <t>Approve the About / Contact / Order Support copy</t>
-  </si>
-  <si>
-    <t>All placeholder text.</t>
-  </si>
-  <si>
-    <t>Pages carry a visible placeholder notice.</t>
-  </si>
-  <si>
-    <t>DEC-01</t>
-  </si>
-  <si>
-    <t>Fresh build — the previous site is reference only</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: nothing to do with the previous site. The extraction is mined for data and business rules; its code and behaviour are discarded.</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>Its category tree, product data and bug history were kept. Its markup was not.</t>
-  </si>
-  <si>
-    <t>DEC-02</t>
-  </si>
-  <si>
-    <t>Keep the existing visual brand</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026, correcting an earlier over-broad reading: the storefront must keep the current AussieMed look, not be redesigned.</t>
-  </si>
-  <si>
-    <t>Navy #29387d, red #ea2227 and Gilroy were read from the live site's computed styles. See DA-08 for the missing Gilroy weights.</t>
-  </si>
-  <si>
-    <t>DEC-03</t>
-  </si>
-  <si>
-    <t>Local only until the client approves</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: not to go online until there is a version they are happy with locally.</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. robots noindex is site-wide. Hosting is IN-01.</t>
-  </si>
-  <si>
-    <t>DEC-04</t>
-  </si>
-  <si>
-    <t>External connectors are handled last</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: anything needing a third-party account waits until the end so the build never stalls on credentials.</t>
-  </si>
-  <si>
-    <t>Payment IN-04, SMTP IN-03, OAuth IN-05, hosting IN-01. Built behind seams with local stand-ins.</t>
-  </si>
-  <si>
-    <t>DEC-05</t>
-  </si>
-  <si>
-    <t>Follow Livingstone for B2B catalogue and pricing behaviour</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026 with livingstone.com.au as the reference, and all suggested changes accepted.</t>
-  </si>
-  <si>
-    <t>Produced the pack/UOM model, price breaks on cards, the Ex/Inc VAT toggle, variant axes, spec attributes and per-product tax class.</t>
-  </si>
-  <si>
-    <t>DEC-06</t>
-  </si>
-  <si>
-    <t>Seed the catalogue from two real suppliers for testing</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: list Chemist Warehouse and Livingstone as suppliers with 30 items each, and remove the invented placeholders.</t>
-  </si>
-  <si>
-    <t>60 real products seeded. Both are unaffiliated third parties — DA-17 must close before launch.</t>
-  </si>
-  <si>
-    <t>DEC-07</t>
-  </si>
-  <si>
-    <t>Add product images</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026. Supplier photography was downloaded for local testing.</t>
-  </si>
-  <si>
-    <t>52 of 71 products have an image. Third-party assets — DA-03 must close before launch.</t>
-  </si>
-  <si>
-    <t>DEC-08</t>
-  </si>
-  <si>
-    <t>Four test accounts with a shared placeholder password</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: admin, musawi1989@gmail.com, supplier1 and supplier2, all with 123456. Explicitly described as local testing only, chosen to be memorable, and to be changed before anything real.</t>
-  </si>
-  <si>
-    <t>Implemented as asked. SEC-01 tracks removing them; SEC-03 tracks agreeing a password policy.</t>
-  </si>
-  <si>
-    <t>DEC-09</t>
-  </si>
-  <si>
-    <t>One sign-in door per role</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the business portal is the supplier login, the account login is for buyers, and admin is reached at /admin.</t>
-  </si>
-  <si>
-    <t>Implemented. Signing in at the wrong door names the right one rather than admitting the user.</t>
-  </si>
-  <si>
-    <t>DEC-10</t>
-  </si>
-  <si>
-    <t>Record every generated value and decision in this register</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026 and repeated 15 Aug: everything invented on the client's behalf must be written down rather than left in the code.</t>
-  </si>
-  <si>
-    <t>This register is the record. docs/Things That Need Attention.xlsx is generated from it and npm run register validates it.</t>
-  </si>
-  <si>
-    <t>DEC-11</t>
-  </si>
-  <si>
-    <t>Price breaks are packaging levels, not arbitrary quantities</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: a break at 12 exists because a carton holds 12, and a break at 48 because a box holds 4 cartons. The quantity and the packaging level are the same fact.</t>
-  </si>
-  <si>
-    <t>Each break now carries its level name. Corrects an earlier model that treated breaks as percentage discounts at round numbers.</t>
-  </si>
-  <si>
-    <t>DEC-12</t>
-  </si>
-  <si>
-    <t>Variants are a dropdown across sibling products</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the 375ml and the 60ml stay as separate products, and each carries a dropdown listing the whole family so a buyer can find their part quickly.</t>
-  </si>
-  <si>
-    <t>Replaces the Each/Carton chips on cards. Implemented as navigation between products, not options on one product, because each size has its own SKU, stock and price.</t>
-  </si>
-  <si>
-    <t>DEC-13</t>
-  </si>
-  <si>
-    <t>One sign-in button in the header, with a dropdown per role</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: replace the Business portal and Account links with a single blue Sign in button whose dropdown offers sign in as a buyer and sign in as a supplier.</t>
-  </si>
-  <si>
-    <t>Implemented in src/components/SignInMenu.tsx. Admin is deliberately absent from the dropdown; staff go to /admin directly. Once signed in the button becomes the way back to the user own area.</t>
-  </si>
-  <si>
-    <t>DEC-14</t>
-  </si>
-  <si>
-    <t>The AED label and the Ex/Inc VAT toggle are gone from the header</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: remove the AED text and the VAT options because VAT is to be carried in the displayed price later.</t>
-  </si>
-  <si>
-    <t>VatToggle deleted from the header. includeVat still exists in src/lib/store.tsx defaulting to ex-VAT with no UI control, so prices read ex-VAT everywhere until the pricing change lands. FE-30 tracks that follow up.</t>
-  </si>
-  <si>
-    <t>DEC-15</t>
-  </si>
-  <si>
-    <t>Sign out lives in the header, in the sign in button slot</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the sign out button always sits where the Sign in button would be when signed out.</t>
-  </si>
-  <si>
-    <t>Moved out of the account, admin and business portal pages into src/components/SignInMenu.tsx, so it is reachable from every page rather than only the dashboard. Signed in, the slot shows the account name plus Sign out.</t>
-  </si>
-  <si>
-    <t>DF-01</t>
-  </si>
-  <si>
-    <t>Industry taxonomy</t>
-  </si>
-  <si>
-    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
-  </si>
-  <si>
-    <t>Additive; adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-02</t>
-  </si>
-  <si>
-    <t>Subscribe and Save</t>
-  </si>
-  <si>
-    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
-  </si>
-  <si>
-    <t>Needs the backend.</t>
-  </si>
-  <si>
-    <t>DF-03</t>
-  </si>
-  <si>
-    <t>Frequently bought together</t>
-  </si>
-  <si>
-    <t>Bundle suggestion with a combined total and one action to add all.</t>
-  </si>
-  <si>
-    <t>Adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-04</t>
-  </si>
-  <si>
-    <t>Quick view</t>
-  </si>
-  <si>
-    <t>View a product from the listing without a page load.</t>
-  </si>
-  <si>
-    <t>DF-05</t>
-  </si>
-  <si>
-    <t>Downloadable PDF catalogues</t>
-  </si>
-  <si>
-    <t>Still how a lot of trade buying happens.</t>
-  </si>
-  <si>
-    <t>Needs the actual catalogue files.</t>
-  </si>
-  <si>
-    <t>BE-07</t>
-  </si>
-  <si>
-    <t>Seed the database from the catalogue</t>
-  </si>
-  <si>
-    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
-  </si>
-  <si>
-    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
-  </si>
-  <si>
-    <t>BE-09</t>
-  </si>
-  <si>
-    <t>Point the storefront at the database</t>
-  </si>
-  <si>
-    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
-  </si>
-  <si>
-    <t>query.ts was untouched — it never knew where products came from.</t>
-  </si>
-  <si>
-    <t>BE-11</t>
-  </si>
-  <si>
-    <t>Order pages restricted to their owner</t>
-  </si>
-  <si>
-    <t>An order was readable by anyone who guessed a sequential reference. Now an admin sees any order, the account that placed it sees it, and a guest sees only an order placed from their own cart.</t>
-  </si>
-  <si>
-    <t>A forbidden order returns 404 rather than 403, so the response cannot be used to discover which references exist.</t>
-  </si>
-  <si>
-    <t>DN-01</t>
-  </si>
-  <si>
-    <t>Currency rendering</t>
-  </si>
-  <si>
-    <t>Was rendering the Arabic symbol and 4 decimals. Now always the English string AED with exactly 2 decimals, enforced by test and by a grep check.</t>
-  </si>
-  <si>
-    <t>Fixed in the initial build.</t>
-  </si>
-  <si>
-    <t>DN-02</t>
-  </si>
-  <si>
-    <t>Integer quantities</t>
-  </si>
-  <si>
-    <t>Quantities were rendering as decimals such as 3.00.</t>
-  </si>
-  <si>
-    <t>DN-03</t>
-  </si>
-  <si>
-    <t>Category filtering</t>
-  </si>
-  <si>
-    <t>Every category link redirected to the full product list. Filtering now works, including rolling a department up to everything beneath it.</t>
-  </si>
-  <si>
-    <t>DN-04</t>
-  </si>
-  <si>
-    <t>Category counts matching results</t>
-  </si>
-  <si>
-    <t>Admin and storefront counts could diverge. Counts are now derived from the same query that lists the products.</t>
-  </si>
-  <si>
-    <t>Asserted in the data checks and the API contract checks.</t>
-  </si>
-  <si>
-    <t>DN-05</t>
-  </si>
-  <si>
-    <t>Category slug collisions</t>
-  </si>
-  <si>
-    <t>Six categories shared a slug with another category, so one was unreachable and the other answered to the wrong name.</t>
-  </si>
-  <si>
-    <t>Found by the API contract check. Slugs are now unique tree-wide and asserted.</t>
-  </si>
-  <si>
-    <t>DN-06</t>
-  </si>
-  <si>
-    <t>Per-supplier invoicing</t>
-  </si>
-  <si>
-    <t>An order spanning N suppliers now produces exactly N invoices under one reference number, with per-invoice VAT summing to the order VAT without drift.</t>
-  </si>
-  <si>
-    <t>Verified end to end in the browser and by test.</t>
-  </si>
-  <si>
-    <t>DN-11</t>
-  </si>
-  <si>
-    <t>Pack and unit of measure model</t>
-  </si>
-  <si>
-    <t>The same line sells by the box and by the carton at different prices. Cart lines are keyed by product and pack so they never merge.</t>
-  </si>
-  <si>
-    <t>Outers are asserted to beat buying their contents separately.</t>
-  </si>
-  <si>
-    <t>DN-14</t>
-  </si>
-  <si>
-    <t>Control characters in generated code</t>
-  </si>
-  <si>
-    <t>Shell escaping wrote literal backspace bytes into regex rules, so every packaging and variant rule silently matched nothing while looking correct in every editor.</t>
-  </si>
-  <si>
-    <t>Found via od. A data check now asserts each variant selection matches an option.</t>
-  </si>
-  <si>
-    <t>DN-16</t>
-  </si>
-  <si>
-    <t>Database schema designed and migrated</t>
-  </si>
-  <si>
-    <t>Thirty tables covering catalogue, packs as SKUs, variants, attributes, documents, batches, orders, per-supplier invoices, quotes, bulk upload and audit.</t>
-  </si>
-  <si>
-    <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
-  </si>
-  <si>
-    <t>DN-17</t>
-  </si>
-  <si>
-    <t>Typecheck was silently passing on a stale cache</t>
-  </si>
-  <si>
-    <t>tsc ran with incremental caching and reported no errors while real type errors existed in the tree. Every earlier typecheck-clean claim was suspect.</t>
-  </si>
-  <si>
-    <t>npm run typecheck now runs with --incremental false. Caught seven genuine errors the moment it was disabled.</t>
-  </si>
-  <si>
-    <t>DN-18</t>
-  </si>
-  <si>
-    <t>Cart moved to the server</t>
-  </si>
-  <si>
-    <t>The cart was localStorage, so the browser held prices. It is now database rows priced entirely on the server; the client cannot tell the server what anything costs.</t>
-  </si>
-  <si>
-    <t>Guest carts are cookie-keyed. The catalogue snapshot endpoint stays until the wishlist and quote cart follow.</t>
-  </si>
-  <si>
-    <t>DN-19</t>
-  </si>
-  <si>
-    <t>Checkout writes real orders</t>
-  </si>
-  <si>
-    <t>One transaction creates the order, one invoice per supplier and every line, or nothing at all. Reference numbers are allocated server-side inside that transaction.</t>
-  </si>
-  <si>
-    <t>Verified in a browser end to end, and by 14 order invariants in npm run db:check.</t>
-  </si>
-  <si>
-    <t>DN-20</t>
-  </si>
-  <si>
-    <t>Four sign-in accounts seeded</t>
-  </si>
-  <si>
-    <t>admin, musawi1989@gmail.com, supplier1 and supplier2, each able to sign in by username or email. Suppliers are attached to their seeded companies.</t>
-  </si>
-  <si>
-    <t>Seeded separately from the catalogue so re-seeding products does not remove accounts.</t>
-  </si>
-  <si>
-    <t>FN-01</t>
-  </si>
-  <si>
-    <t>Checkout does not submit an order</t>
-  </si>
-  <si>
-    <t>Done. Checkout writes a real order in one transaction, with one invoice per supplier and a server-allocated reference number.</t>
-  </si>
-  <si>
-    <t>Payment is still not taken and no email is sent.</t>
-  </si>
-  <si>
-    <t>FN-05</t>
-  </si>
-  <si>
-    <t>Real sign-in replaced the demo flag</t>
-  </si>
-  <si>
-    <t>Sign-in was a localStorage boolean anyone could set. It is now a database-backed session with a scrypt-hashed password.</t>
-  </si>
-  <si>
-    <t>Sessions are rows; signing out deletes the row, so a copied cookie stops working.</t>
-  </si>
-  <si>
-    <t>FN-06</t>
-  </si>
-  <si>
-    <t>Account history is real</t>
-  </si>
-  <si>
-    <t>The account area showed three fabricated orders. It now reads the signed-in user's actual orders, and reorder-first is built from what they have really bought.</t>
-  </si>
-  <si>
-    <t>Says so plainly when there is no history yet, rather than showing an empty grid.</t>
-  </si>
-  <si>
-    <t>DN-07</t>
-  </si>
-  <si>
-    <t>Unique page titles and meta descriptions</t>
-  </si>
-  <si>
-    <t>Every page carried the identical title 'Aussie Med || Home' with an empty description.</t>
-  </si>
-  <si>
-    <t>Built per page and per product.</t>
-  </si>
-  <si>
-    <t>DN-08</t>
-  </si>
-  <si>
-    <t>Broken cart images and unresolved asset paths</t>
-  </si>
-  <si>
-    <t>Cart images had a bare domain with no path; templates contained literal '~/' paths.</t>
-  </si>
-  <si>
-    <t>All image paths are local and asserted.</t>
-  </si>
-  <si>
-    <t>DN-09</t>
-  </si>
-  <si>
-    <t>Volume breaks visible while scanning</t>
-  </si>
-  <si>
-    <t>Only a savings badge was shown. The full break table now appears on every product card using +1/+10/+50 notation.</t>
-  </si>
-  <si>
-    <t>DN-10</t>
-  </si>
-  <si>
-    <t>Ex VAT / Inc VAT toggle</t>
-  </si>
-  <si>
-    <t>Procurement compares ex-tax and the approver reads inc-tax, so the same buyer needs both during one order.</t>
-  </si>
-  <si>
-    <t>Persists per browser.</t>
-  </si>
-  <si>
-    <t>DN-12</t>
-  </si>
-  <si>
-    <t>Adopt the existing brand theme</t>
-  </si>
-  <si>
-    <t>Navy #29387d, red #ea2227 and Gilroy, read from the live site's computed styles rather than eyeballed.</t>
-  </si>
-  <si>
-    <t>Logo, favicon and all 11 category images are the brand own.</t>
-  </si>
-  <si>
-    <t>DN-13</t>
-  </si>
-  <si>
-    <t>Catalogue seeded with real products</t>
-  </si>
-  <si>
-    <t>Sixty real items replaced invented placeholders so the storefront can be judged against products that actually exist.</t>
-  </si>
-  <si>
-    <t>Thirty from each of two public supplier catalogues, spanning 23 categories.</t>
-  </si>
-  <si>
-    <t>DN-15</t>
-  </si>
-  <si>
-    <t>Product images added for testing</t>
-  </si>
-  <si>
-    <t>Fifty-two of 71 products now carry real photography so the layout can be judged with images rather than placeholder tiles.</t>
-  </si>
-  <si>
-    <t>Third-party supplier images in public/products/seed. A data check now asserts every referenced image file exists on disk.</t>
-  </si>
-  <si>
-    <t>DN-21</t>
-  </si>
-  <si>
-    <t>Three sign-in doors, one per role</t>
-  </si>
-  <si>
-    <t>Buyers sign in at the account page, suppliers at the business portal, admins at /admin. Signing in at the wrong door names the right one instead of letting someone into the wrong area.</t>
-  </si>
-  <si>
-    <t>Verified: each role accepted at its own door and rejected with 403 at the other two.</t>
-  </si>
-  <si>
-    <t>BE-26</t>
-  </si>
-  <si>
-    <t>Seed now upserts instead of wiping</t>
-  </si>
-  <si>
-    <t>Once orders existed, re-seeding failed on a foreign key: order lines reference SKU rows. The database was correctly refusing to let a re-seed destroy order history.</t>
-  </si>
-  <si>
-    <t>Products, SKUs, categories and brands are matched on natural keys and updated in place. Products absent from the catalogue are deactivated, never deleted.</t>
+    <t>Resolved 15 Aug 2026 by DA-23: the AussieMed Distribution supplier left the catalogue along with its products, so the name no longer appears anywhere a supplier's own name should.</t>
+  </si>
+  <si>
+    <t>DA-25</t>
+  </si>
+  <si>
+    <t>Four product images were SVG placeholders saved as .jpg</t>
+  </si>
+  <si>
+    <t>Next's image optimiser rejected them with a 400, so those four products showed a broken image — visibly worse than the products with no image at all, which fall back to a monogram tile. The existing check only asked whether the file existed, and it did.</t>
+  </si>
+  <si>
+    <t>Fixed 15 Aug 2026: the four files were deleted and their products now fall back to the placeholder. scripts/check-catalog.mjs now sniffs magic bytes rather than trusting the extension, so a file that is not really an image fails the build. Affected the two HiSmile lines, Neutrogena Ultra Sheer and the Roger Armstrong thermometer.</t>
   </si>
 </sst>
 </file>
@@ -2230,7 +2254,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2238,7 +2262,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2246,7 +2270,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2254,7 +2278,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2262,7 +2286,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2280,7 +2304,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2288,7 +2312,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2296,7 +2320,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2314,7 +2338,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2338,7 +2362,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2364,7 +2388,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2380,7 +2404,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2388,7 +2412,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2438,7 +2462,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2715,7 +2739,7 @@
         <v>73</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>74</v>
@@ -2723,8 +2747,8 @@
       <c r="D11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>16</v>
+      <c r="E11" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>37</v>
@@ -2845,7 +2869,7 @@
         <v>93</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>94</v>
@@ -2853,8 +2877,8 @@
       <c r="D16" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>13</v>
+      <c r="E16" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>37</v>
@@ -2877,7 +2901,7 @@
         <v>98</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
@@ -2889,21 +2913,21 @@
         <v>38</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
@@ -2915,7 +2939,7 @@
         <v>38</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2923,7 +2947,7 @@
         <v>103</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>104</v>
@@ -2957,8 +2981,8 @@
       <c r="D20" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>16</v>
+      <c r="E20" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>37</v>
@@ -2975,7 +2999,7 @@
         <v>111</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>112</v>
@@ -3019,21 +3043,21 @@
         <v>38</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>13</v>
@@ -3045,7 +3069,7 @@
         <v>38</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3053,7 +3077,7 @@
         <v>122</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>123</v>
@@ -3079,7 +3103,7 @@
         <v>126</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>127</v>
@@ -3088,36 +3112,36 @@
         <v>128</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>37</v>
+        <v>14</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>38</v>
@@ -3140,10 +3164,10 @@
         <v>137</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>38</v>
@@ -3166,10 +3190,10 @@
         <v>141</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>38</v>
@@ -3192,10 +3216,10 @@
         <v>145</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>38</v>
@@ -3221,7 +3245,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>38</v>
@@ -3244,10 +3268,10 @@
         <v>153</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>38</v>
@@ -3261,7 +3285,7 @@
         <v>155</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>156</v>
@@ -3269,11 +3293,11 @@
       <c r="D32" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>13</v>
+      <c r="E32" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>38</v>
@@ -3299,7 +3323,7 @@
         <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>38</v>
@@ -3325,7 +3349,7 @@
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>38</v>
@@ -3347,11 +3371,11 @@
       <c r="D35" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>16</v>
+      <c r="E35" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>38</v>
@@ -3373,11 +3397,11 @@
       <c r="D36" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>14</v>
+      <c r="E36" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>38</v>
@@ -3403,7 +3427,7 @@
         <v>16</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>38</v>
@@ -3425,11 +3449,11 @@
       <c r="D38" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>16</v>
+      <c r="E38" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>38</v>
@@ -3455,7 +3479,7 @@
         <v>13</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>38</v>
@@ -3481,7 +3505,7 @@
         <v>13</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>38</v>
@@ -3507,7 +3531,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>38</v>
@@ -3521,7 +3545,7 @@
         <v>195</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>196</v>
@@ -3533,7 +3557,7 @@
         <v>13</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>38</v>
@@ -3559,7 +3583,7 @@
         <v>13</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>38</v>
@@ -3585,7 +3609,7 @@
         <v>13</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>38</v>
@@ -3607,11 +3631,11 @@
       <c r="D45" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E45" s="7" t="s">
-        <v>13</v>
+      <c r="E45" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>38</v>
@@ -3633,11 +3657,11 @@
       <c r="D46" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>15</v>
+      <c r="E46" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>38</v>
@@ -3663,7 +3687,7 @@
         <v>13</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>38</v>
@@ -3689,7 +3713,7 @@
         <v>13</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>38</v>
@@ -3715,7 +3739,7 @@
         <v>13</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>38</v>
@@ -3737,11 +3761,11 @@
       <c r="D50" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="E50" s="7" t="s">
-        <v>13</v>
+      <c r="E50" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>38</v>
@@ -3763,11 +3787,11 @@
       <c r="D51" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>16</v>
+      <c r="E51" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>38</v>
@@ -3793,7 +3817,7 @@
         <v>13</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>38</v>
@@ -3819,7 +3843,7 @@
         <v>13</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>38</v>
@@ -3833,7 +3857,7 @@
         <v>243</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>244</v>
@@ -3841,11 +3865,11 @@
       <c r="D54" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E54" s="7" t="s">
-        <v>13</v>
+      <c r="E54" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>38</v>
@@ -3859,7 +3883,7 @@
         <v>247</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>248</v>
@@ -3867,11 +3891,11 @@
       <c r="D55" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="E55" s="7" t="s">
-        <v>13</v>
+      <c r="E55" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>38</v>
@@ -3897,7 +3921,7 @@
         <v>16</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>38</v>
@@ -3919,11 +3943,11 @@
       <c r="D57" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>16</v>
+      <c r="E57" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>38</v>
@@ -3937,7 +3961,7 @@
         <v>259</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>260</v>
@@ -3945,11 +3969,11 @@
       <c r="D58" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="E58" s="6" t="s">
-        <v>16</v>
+      <c r="E58" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>38</v>
@@ -3963,7 +3987,7 @@
         <v>263</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>264</v>
@@ -3971,271 +3995,271 @@
       <c r="D59" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="E59" s="7" t="s">
-        <v>13</v>
+      <c r="E59" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>266</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C60" s="6" t="s">
+      <c r="D60" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="E60" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C61" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D61" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>273</v>
-      </c>
       <c r="E61" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>274</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D62" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="B62" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="6" t="s">
+      <c r="E62" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="B63" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C63" s="6" t="s">
+      <c r="D63" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>280</v>
-      </c>
       <c r="E63" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>281</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D64" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="B64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C64" s="6" t="s">
+      <c r="E64" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="B65" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C65" s="6" t="s">
+      <c r="D65" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="E65" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H65" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C66" s="6" t="s">
+      <c r="D66" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="E66" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="E66" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>133</v>
-      </c>
       <c r="G66" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>2</v>
+        <v>292</v>
       </c>
     </row>
     <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>133</v>
+        <v>295</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>291</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="68" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>133</v>
+        <v>299</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>291</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>38</v>
@@ -4249,7 +4273,7 @@
         <v>305</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>306</v>
@@ -4257,11 +4281,11 @@
       <c r="D70" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="E70" s="7" t="s">
-        <v>13</v>
+      <c r="E70" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>38</v>
@@ -4287,7 +4311,7 @@
         <v>16</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>38</v>
@@ -4309,11 +4333,11 @@
       <c r="D72" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="E72" s="7" t="s">
-        <v>13</v>
+      <c r="E72" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>38</v>
@@ -4339,7 +4363,7 @@
         <v>16</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>38</v>
@@ -4353,7 +4377,7 @@
         <v>321</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>322</v>
@@ -4361,11 +4385,11 @@
       <c r="D74" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E74" s="6" t="s">
-        <v>16</v>
+      <c r="E74" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>38</v>
@@ -4379,7 +4403,7 @@
         <v>325</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>326</v>
@@ -4387,11 +4411,11 @@
       <c r="D75" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>16</v>
+      <c r="E75" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>38</v>
@@ -4405,7 +4429,7 @@
         <v>329</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>330</v>
@@ -4413,11 +4437,11 @@
       <c r="D76" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="E76" s="6" t="s">
-        <v>16</v>
+      <c r="E76" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>38</v>
@@ -4431,7 +4455,7 @@
         <v>333</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>334</v>
@@ -4439,11 +4463,11 @@
       <c r="D77" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E77" s="7" t="s">
-        <v>13</v>
+      <c r="E77" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>38</v>
@@ -4457,7 +4481,7 @@
         <v>337</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>338</v>
@@ -4469,277 +4493,121 @@
         <v>13</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>340</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="B79" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C79" s="6" t="s">
+      <c r="D79" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="E79" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H79" s="6" t="s">
         <v>343</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C80" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="B80" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C80" s="6" t="s">
+      <c r="D80" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="D80" s="6" t="s">
+      <c r="E80" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>347</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="81" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="B81" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C81" s="6" t="s">
+      <c r="D81" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="E81" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H81" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G81" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="B82" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C82" s="6" t="s">
+      <c r="D82" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="E82" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="E82" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F83" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F84" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F86" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>379</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H88"/>
+  <autoFilter ref="A1:H82"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4750,7 +4618,7 @@
   <sheetPr>
     <tabColor rgb="FF29387D"/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -4790,396 +4658,422 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>440</v>
+        <v>416</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5190,7 +5084,7 @@
   <sheetPr>
     <tabColor rgb="FF8B90A0"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -5230,136 +5124,162 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>16</v>
+        <v>423</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>2</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>13</v>
+        <v>439</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>459</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>443</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5370,7 +5290,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -5410,16 +5330,16 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>16</v>
@@ -5428,24 +5348,24 @@
         <v>37</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
@@ -5454,24 +5374,24 @@
         <v>37</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
@@ -5480,24 +5400,24 @@
         <v>37</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>383</v>
+        <v>22</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
@@ -5506,24 +5426,24 @@
         <v>37</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
@@ -5532,24 +5452,24 @@
         <v>37</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
@@ -5558,24 +5478,24 @@
         <v>37</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>16</v>
@@ -5584,24 +5504,24 @@
         <v>37</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>16</v>
@@ -5610,24 +5530,24 @@
         <v>37</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
@@ -5636,24 +5556,24 @@
         <v>37</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
@@ -5662,24 +5582,24 @@
         <v>37</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>16</v>
@@ -5688,24 +5608,24 @@
         <v>37</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>16</v>
@@ -5714,24 +5634,24 @@
         <v>37</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>16</v>
@@ -5740,24 +5660,24 @@
         <v>37</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
@@ -5766,24 +5686,24 @@
         <v>37</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
@@ -5792,24 +5712,24 @@
         <v>37</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
@@ -5818,24 +5738,24 @@
         <v>37</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
@@ -5844,24 +5764,24 @@
         <v>37</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>383</v>
+        <v>21</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
@@ -5870,24 +5790,24 @@
         <v>37</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>16</v>
@@ -5896,248 +5816,404 @@
         <v>37</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>133</v>
+      <c r="F21" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>383</v>
+        <v>19</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>540</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>16</v>
+        <v>524</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>452</v>
+        <v>529</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>546</v>
+        <v>531</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>548</v>
+        <v>533</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>552</v>
+        <v>436</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>564</v>
+        <v>548</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="B33" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>566</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D33" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>383</v>
-      </c>
-      <c r="H29" s="6" t="s">
+      <c r="E33" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>568</v>
       </c>
     </row>
+    <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>576</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H29"/>
+  <autoFilter ref="A1:H35"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="605">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -188,6 +188,1203 @@
     <t>Phase 1 started. Schema designed and migrated: 30 tables, 19 unique constraints. Application code not started.</t>
   </si>
   <si>
+    <t>BE-03</t>
+  </si>
+  <si>
+    <t>Build the supplier portal</t>
+  </si>
+  <si>
+    <t>Suppliers manage their own products but can never self-approve. Must have a failing-then-passing test.</t>
+  </si>
+  <si>
+    <t>The dashboard exists at /business-portal and is role-guarded and supplier-scoped. The editing screens behind it do not — BE-21 tracks those. Approval is an admin-only transition enforced in the service layer.</t>
+  </si>
+  <si>
+    <t>BE-21</t>
+  </si>
+  <si>
+    <t>Build the supplier portal behind its dashboard</t>
+  </si>
+  <si>
+    <t>The business portal authenticates and shows a supplier their own products and invoice lines, read-only. Creating and editing products, toggling stock and bulk upload are not built.</t>
+  </si>
+  <si>
+    <t>A supplier must never be able to approve their own product — the rule to enforce when editing lands.</t>
+  </si>
+  <si>
+    <t>BE-29</t>
+  </si>
+  <si>
+    <t>Product images cannot be uploaded</t>
+  </si>
+  <si>
+    <t>The admin product screen lists the image files a product references but cannot add or replace one, so the only way to give a product a photograph is to put a file on disk and re-seed. That blocks DA-03 and DA-24 from ever being closed by the client rather than by us.</t>
+  </si>
+  <si>
+    <t>Found while building the admin screens on 16 Aug 2026. Needs a decision on where uploaded files live once this is hosted — local disk will not survive most deployments, so it is tied to IN-01.</t>
+  </si>
+  <si>
+    <t>DA-01</t>
+  </si>
+  <si>
+    <t>Supply the real product catalogue</t>
+  </si>
+  <si>
+    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
+  </si>
+  <si>
+    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
+  </si>
+  <si>
+    <t>DA-03</t>
+  </si>
+  <si>
+    <t>Supply product photography</t>
+  </si>
+  <si>
+    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
+  </si>
+  <si>
+    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
+  </si>
+  <si>
+    <t>DA-06</t>
+  </si>
+  <si>
+    <t>Supply the real supplier list</t>
+  </si>
+  <si>
+    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
+  </si>
+  <si>
+    <t>All are flagged isPlaceholder in the data.</t>
+  </si>
+  <si>
+    <t>DA-17</t>
+  </si>
+  <si>
+    <t>Replace the test supplier attribution</t>
+  </si>
+  <si>
+    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
+  </si>
+  <si>
+    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
+  </si>
+  <si>
+    <t>DA-20</t>
+  </si>
+  <si>
+    <t>Supply the real packaging quantities</t>
+  </si>
+  <si>
+    <t>OUR INVENTED VALUES: how many units make a carton, and how many cartons make a box, are guessed per product family (12 and 4 by default, 10 and 5 for gloves, 20 and 5 for masks). The break discounts of 4% and 8% are also invented.</t>
+  </si>
+  <si>
+    <t>These are now shown to buyers as CARTON and BOX, so a wrong number reads as a factual claim about your packaging. In scripts/variants.mjs.</t>
+  </si>
+  <si>
+    <t>FN-02</t>
+  </si>
+  <si>
+    <t>Quote requests are not delivered</t>
+  </si>
+  <si>
+    <t>Captured in the browser only.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend and an email provider.</t>
+  </si>
+  <si>
+    <t>FN-03</t>
+  </si>
+  <si>
+    <t>Bulk buy enquiries are not delivered</t>
+  </si>
+  <si>
+    <t>FN-04</t>
+  </si>
+  <si>
+    <t>Notify Me does not register a subscription</t>
+  </si>
+  <si>
+    <t>Captured locally. The restock email flow does not exist.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend.</t>
+  </si>
+  <si>
+    <t>IN-06</t>
+  </si>
+  <si>
+    <t>Remove noindex before launch</t>
+  </si>
+  <si>
+    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
+  </si>
+  <si>
+    <t>Must be removed deliberately at launch — and only then.</t>
+  </si>
+  <si>
+    <t>IN-07</t>
+  </si>
+  <si>
+    <t>Confirm the GitHub repository is private</t>
+  </si>
+  <si>
+    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
+  </si>
+  <si>
+    <t>https://github.com/musawi1989/aussiemed</t>
+  </si>
+  <si>
+    <t>LG-01</t>
+  </si>
+  <si>
+    <t>Supply terms and conditions</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
+  </si>
+  <si>
+    <t>Page exists and says so on screen.</t>
+  </si>
+  <si>
+    <t>LG-02</t>
+  </si>
+  <si>
+    <t>Supply the privacy policy</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
+  </si>
+  <si>
+    <t>LG-03</t>
+  </si>
+  <si>
+    <t>Confirm the contact email address</t>
+  </si>
+  <si>
+    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
+  </si>
+  <si>
+    <t>Also determines the sending domain for transactional email.</t>
+  </si>
+  <si>
+    <t>SEC-01</t>
+  </si>
+  <si>
+    <t>Remove the test credentials before any deployment</t>
+  </si>
+  <si>
+    <t>Four accounts share the password 123456: admin, musawi1989@gmail.com, supplier1, supplier2. Fine on a laptop, unacceptable anywhere else.</t>
+  </si>
+  <si>
+    <t>The on-screen credentials panel now renders only outside production, so a production build cannot leak it. The accounts themselves still must be removed or given real passwords.</t>
+  </si>
+  <si>
+    <t>AC-05</t>
+  </si>
+  <si>
+    <t>Confirm the VAT rate and whether it must be configurable</t>
+  </si>
+  <si>
+    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Rate must be stored on the order at the time it is placed.</t>
+  </si>
+  <si>
+    <t>AC-06</t>
+  </si>
+  <si>
+    <t>Approve the reference number format</t>
+  </si>
+  <si>
+    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
+  </si>
+  <si>
+    <t>Wording is fixed as Reference number, never order number.</t>
+  </si>
+  <si>
+    <t>AC-07</t>
+  </si>
+  <si>
+    <t>Approve the supplier invoice numbering</t>
+  </si>
+  <si>
+    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
+  </si>
+  <si>
+    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
+  </si>
+  <si>
+    <t>AC-09</t>
+  </si>
+  <si>
+    <t>Decide payment terms and credit accounts</t>
+  </si>
+  <si>
+    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
+  </si>
+  <si>
+    <t>Affects the schema — decide before the backend.</t>
+  </si>
+  <si>
+    <t>AC-11</t>
+  </si>
+  <si>
+    <t>Approve the VAT rounding method on invoices</t>
+  </si>
+  <si>
+    <t>VAT is rounded per line rather than once per invoice, so the printed lines always add up to the printed total. The alternative rounds once and can leave lines that do not sum.</t>
+  </si>
+  <si>
+    <t>Verified by test: per-invoice VAT sums to the order VAT exactly.</t>
+  </si>
+  <si>
+    <t>AC-12</t>
+  </si>
+  <si>
+    <t>Confirm the reference number sequence resets each year</t>
+  </si>
+  <si>
+    <t>OUR DECISION: the sequence restarts at 000001 each calendar year, so AM-2026-000001 and AM-2027-000001 can both exist. If accounting needs a single unbroken sequence this must change before real orders.</t>
+  </si>
+  <si>
+    <t>Held in a settings row keyed orderSequence:YYYY and incremented inside the checkout transaction.</t>
+  </si>
+  <si>
+    <t>AC-13</t>
+  </si>
+  <si>
+    <t>Decide whether an order should reserve stock</t>
+  </si>
+  <si>
+    <t>OUR DECISION: checkout does not decrement or reserve anything, because there are no stock levels — only an in/out flag. Two customers can order the last unit.</t>
+  </si>
+  <si>
+    <t>Depends on FN-08. Out-of-stock is re-checked at checkout, so a line that sold out while the form was open is rejected.</t>
+  </si>
+  <si>
+    <t>BE-04</t>
+  </si>
+  <si>
+    <t>Build comma-safe .xlsx bulk upload</t>
+  </si>
+  <si>
+    <t>Parsed natively with exceljs, never by splitting on commas — that is what broke comma-containing category names.</t>
+  </si>
+  <si>
+    <t>Unknown brands must be reported per row, never skipped silently.</t>
+  </si>
+  <si>
+    <t>BE-05</t>
+  </si>
+  <si>
+    <t>Build the email flows</t>
+  </si>
+  <si>
+    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
+  </si>
+  <si>
+    <t>Needs an SMTP provider.</t>
+  </si>
+  <si>
+    <t>BE-08</t>
+  </si>
+  <si>
+    <t>Decide money representation before any data lands</t>
+  </si>
+  <si>
+    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
+  </si>
+  <si>
+    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
+  </si>
+  <si>
+    <t>BE-10</t>
+  </si>
+  <si>
+    <t>Retire the catalogue snapshot endpoint</t>
+  </si>
+  <si>
+    <t>Client components fetch the whole catalogue from /api/v1/catalog/snapshot. Fine for 71 products; not for thousands. Goes away when the cart moves server-side.</t>
+  </si>
+  <si>
+    <t>Phase 3 removes the need.</t>
+  </si>
+  <si>
+    <t>BE-12</t>
+  </si>
+  <si>
+    <t>Merge a guest cart into the user cart on sign-in</t>
+  </si>
+  <si>
+    <t>Carts are keyed by a cookie so a visitor can shop before signing in. The merge on sign-in is specified but cannot be built until auth exists.</t>
+  </si>
+  <si>
+    <t>Cart cookie: aussiemed_cart, httpOnly, 30 day lifetime — OUR INVENTED VALUES.</t>
+  </si>
+  <si>
+    <t>BE-14</t>
+  </si>
+  <si>
+    <t>Confirm the default order and invoice status</t>
+  </si>
+  <si>
+    <t>OUR DECISION: new orders are Pending and each supplier invoice is Pending. The real workflow — who moves an order to Processing, and when an invoice becomes Issued — is not defined.</t>
+  </si>
+  <si>
+    <t>Order statuses available: Pending, Processing, Dispatched, Delivered, Cancelled.</t>
+  </si>
+  <si>
+    <t>BE-15</t>
+  </si>
+  <si>
+    <t>Passwords were built instead of the specified email OTP</t>
+  </si>
+  <si>
+    <t>BACKEND_SPEC.md specifies passwordless sign-in by emailed code. Passwords were requested instead and built. Livingstone advertises password-free login as a feature, so the spec was not arbitrary.</t>
+  </si>
+  <si>
+    <t>Both can coexist: the schema keeps otpCode and otpExpiresAt. Decide before launch.</t>
+  </si>
+  <si>
+    <t>BE-19</t>
+  </si>
+  <si>
+    <t>Guest checkout is allowed</t>
+  </si>
+  <si>
+    <t>OUR DECISION: an order can be placed without signing in, and is then tied to the cart cookie. Signing in simply attaches the order to the account.</t>
+  </si>
+  <si>
+    <t>If trade accounts should be required to order, this must change — it also affects credit terms and pricing.</t>
+  </si>
+  <si>
+    <t>BE-22</t>
+  </si>
+  <si>
+    <t>Confirm one supplier account per company</t>
+  </si>
+  <si>
+    <t>OUR DECISION: each supplier company links to a single user. Real suppliers usually need several people with their own logins.</t>
+  </si>
+  <si>
+    <t>Schema allows it via Supplier.userId; supporting several needs a join table.</t>
+  </si>
+  <si>
+    <t>DA-02</t>
+  </si>
+  <si>
+    <t>Verify the product-to-category mapping</t>
+  </si>
+  <si>
+    <t>The extraction had no product-category link at all, so every mapping on the site is ours. The catalogue is now 71 products across 146 categories and none of that mapping has been checked by anyone who knows the range.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026 after DA-23: 60 active products, 0 uncategorised.</t>
+  </si>
+  <si>
+    <t>DA-05</t>
+  </si>
+  <si>
+    <t>Approve the product descriptions</t>
+  </si>
+  <si>
+    <t>The source had no descriptions. All 71 active products now carry text we generated from the product name and supplier listing, and it goes out under AussieMed's name.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026 after DA-23: 60 of 60 active products have a generated description.</t>
+  </si>
+  <si>
+    <t>DA-07</t>
+  </si>
+  <si>
+    <t>Supply the hero banner image</t>
+  </si>
+  <si>
+    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured — only Brand, Category, Product and WebHtml folders were mirrored.</t>
+  </si>
+  <si>
+    <t>A genuine AussieMed CMS image stands in.</t>
+  </si>
+  <si>
+    <t>DA-08</t>
+  </si>
+  <si>
+    <t>Obtain Gilroy Regular and Medium</t>
+  </si>
+  <si>
+    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
+  </si>
+  <si>
+    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
+  </si>
+  <si>
+    <t>DA-10</t>
+  </si>
+  <si>
+    <t>Supply real pack and carton structures</t>
+  </si>
+  <si>
+    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
+  </si>
+  <si>
+    <t>Largely superseded by DA-20: packaging moved from separate carton SKUs into named price breaks on 15 Aug 2026, so the invented figures now live in scripts/variants.mjs rather than in outer packs. Kept open because the underlying question — what is a real carton and box for each line — is unanswered either way.</t>
+  </si>
+  <si>
+    <t>DA-11</t>
+  </si>
+  <si>
+    <t>Supply real variant data</t>
+  </si>
+  <si>
+    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: the same five sizes and three colours are stamped on all six glove products regardless of what the supplier actually sells. FN-07 covers the wiring; this row covers the data.</t>
+  </si>
+  <si>
+    <t>DA-12</t>
+  </si>
+  <si>
+    <t>Supply real product specifications</t>
+  </si>
+  <si>
+    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
+  </si>
+  <si>
+    <t>These become search filters later.</t>
+  </si>
+  <si>
+    <t>DA-13</t>
+  </si>
+  <si>
+    <t>Supply safety data sheets and spec sheets</t>
+  </si>
+  <si>
+    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
+  </si>
+  <si>
+    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
+  </si>
+  <si>
+    <t>DA-18</t>
+  </si>
+  <si>
+    <t>Product ids are derived from slugs</t>
+  </si>
+  <si>
+    <t>Carts and wishlists are stored in the browser against a product id. Ids are now hashed from the slug so they survive a re-seed, which means CHANGING A PRODUCT SLUG ORPHANS ANY SAVED CART LINE referencing it.</t>
+  </si>
+  <si>
+    <t>Resolved properly when the cart moves server-side and references SKU rows directly.</t>
+  </si>
+  <si>
+    <t>DA-19</t>
+  </si>
+  <si>
+    <t>Supplier email addresses are invented</t>
+  </si>
+  <si>
+    <t>The seed writes orders@&lt;supplier&gt;.example and accounts@&lt;supplier&gt;.example because secondaryEmail is mandatory. No supplier will receive anything at these addresses.</t>
+  </si>
+  <si>
+    <t>Both addresses are meant to receive order notifications once email exists.</t>
+  </si>
+  <si>
+    <t>DA-21</t>
+  </si>
+  <si>
+    <t>Verify the automatic variant grouping</t>
+  </si>
+  <si>
+    <t>Products are grouped into families by stripping sizes and volumes from their names. It found 2 families in the seeded catalogue. A real catalogue will group differently and some groupings will be wrong.</t>
+  </si>
+  <si>
+    <t>The admin product screens should let a family be set explicitly rather than inferred — see BE-20.</t>
+  </si>
+  <si>
+    <t>DA-24</t>
+  </si>
+  <si>
+    <t>13 of 60 products have no image</t>
+  </si>
+  <si>
+    <t>Those products render as a monogram tile rather than a photograph. It is a deliberate stand-in and reads acceptably in a grid, but on a trade catalogue an image is often how a buyer confirms they have the right item.</t>
+  </si>
+  <si>
+    <t>Was 19 of 71. Ten went with the extraction products under DA-23. Four more were added deliberately: their image files turned out to be SVG placeholders saved with a .jpg extension, which the image optimiser rejected with a 400 — see DA-25. The remaining nine have no sourceSku or sourceUrl recorded, so there is nothing to retry a fetch against, and no more third-party photography was sourced because DA-17 already limits what may ship. Subset of DA-03.</t>
+  </si>
+  <si>
+    <t>FE-30</t>
+  </si>
+  <si>
+    <t>Prices are still labelled Ex. VAT with no way to see inc-VAT</t>
+  </si>
+  <si>
+    <t>The header toggle was removed before VAT was folded into the displayed price, so a buyer approving an invoice has no inc-VAT figure anywhere on the storefront. Checkout still adds VAT, so the total at the end is higher than every price shown.</t>
+  </si>
+  <si>
+    <t>Follow up to DEC-14. Decide whether displayed prices become VAT inclusive or the Ex. VAT labels simply stay.</t>
+  </si>
+  <si>
+    <t>FN-07</t>
+  </si>
+  <si>
+    <t>Size and colour switching is not wired</t>
+  </si>
+  <si>
+    <t>The variant dropdown built on 15 Aug 2026 (DEC-12) switches between sibling products by size or volume, and that works. The separate Size and Colour chips on gloves and the scrub top are a different thing and still do nothing — no sibling SKU exists behind any of them.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: 13 option axes across 6 products. Every glove carries an identical Size = XS/S/M/L/XL and Colour = Black/Blue/Green with no SKU attached to any value.</t>
+  </si>
+  <si>
+    <t>FN-08</t>
+  </si>
+  <si>
+    <t>Stock is a boolean</t>
+  </si>
+  <si>
+    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
+  </si>
+  <si>
+    <t>Decide whether real stock levels are needed.</t>
+  </si>
+  <si>
+    <t>FN-09</t>
+  </si>
+  <si>
+    <t>Decide on expiry and short-dated stock</t>
+  </si>
+  <si>
+    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
+  </si>
+  <si>
+    <t>Schema-shaping — decide before the backend is built.</t>
+  </si>
+  <si>
+    <t>IN-01</t>
+  </si>
+  <si>
+    <t>Choose a hosting target</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. The site runs locally only.</t>
+  </si>
+  <si>
+    <t>Deliberately deferred until the build is approved.</t>
+  </si>
+  <si>
+    <t>IN-02</t>
+  </si>
+  <si>
+    <t>Choose the database</t>
+  </si>
+  <si>
+    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
+  </si>
+  <si>
+    <t>IN-03</t>
+  </si>
+  <si>
+    <t>Choose an SMTP provider and sending domain</t>
+  </si>
+  <si>
+    <t>Required for every transactional email.</t>
+  </si>
+  <si>
+    <t>Must not be the misspelled assuiemed.com domain.</t>
+  </si>
+  <si>
+    <t>IN-04</t>
+  </si>
+  <si>
+    <t>Decide on a payment gateway</t>
+  </si>
+  <si>
+    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
+  </si>
+  <si>
+    <t>LG-05</t>
+  </si>
+  <si>
+    <t>Transfer the theme licence</t>
+  </si>
+  <si>
+    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
+  </si>
+  <si>
+    <t>Repository must stay private because of this.</t>
+  </si>
+  <si>
+    <t>LG-06</t>
+  </si>
+  <si>
+    <t>Supply company registration details</t>
+  </si>
+  <si>
+    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
+  </si>
+  <si>
+    <t>SEC-02</t>
+  </si>
+  <si>
+    <t>Add rate limiting to sign-in</t>
+  </si>
+  <si>
+    <t>Nothing limits password attempts, so the sign-in endpoint can be brute forced. The spec asks for rate limiting on auth in the hardening phase.</t>
+  </si>
+  <si>
+    <t>Matters more with short passwords than with OTP.</t>
+  </si>
+  <si>
+    <t>SEC-03</t>
+  </si>
+  <si>
+    <t>Agree a password policy</t>
+  </si>
+  <si>
+    <t>No minimum length, complexity or reuse rule is enforced. 123456 was accepted because nothing rejects it.</t>
+  </si>
+  <si>
+    <t>Moot if the OTP flow in BE-15 is adopted instead.</t>
+  </si>
+  <si>
+    <t>AC-08</t>
+  </si>
+  <si>
+    <t>Confirm the rounding policy</t>
+  </si>
+  <si>
+    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Verified by test; needs sign-off that the method is acceptable.</t>
+  </si>
+  <si>
+    <t>AC-10</t>
+  </si>
+  <si>
+    <t>Confirm the default price display</t>
+  </si>
+  <si>
+    <t>Prices are shown Ex. VAT everywhere, and since 15 Aug 2026 there is no way for a buyer to see an inc-VAT figure at all — the header toggle was removed at the client's request before VAT was folded into the displayed price.</t>
+  </si>
+  <si>
+    <t>See DEC-14 for the decision and FE-30 for the gap it leaves open.</t>
+  </si>
+  <si>
+    <t>BE-13</t>
+  </si>
+  <si>
+    <t>Expire abandoned guest carts</t>
+  </si>
+  <si>
+    <t>Cart rows are never cleaned up. Every visitor who adds an item creates one that lives forever.</t>
+  </si>
+  <si>
+    <t>The spec wants abandoned carts over 24h reportable under Admin &gt; Marketing, so expiry and that report should be designed together.</t>
+  </si>
+  <si>
+    <t>BE-16</t>
+  </si>
+  <si>
+    <t>Confirm the session lifetime</t>
+  </si>
+  <si>
+    <t>OUR INVENTED VALUE: sessions last 7 days, then require signing in again. No idle timeout and no re-authentication for sensitive actions.</t>
+  </si>
+  <si>
+    <t>Cookie is httpOnly and sameSite=lax; secure only in production so local http still works.</t>
+  </si>
+  <si>
+    <t>BE-17</t>
+  </si>
+  <si>
+    <t>Purge expired sessions on a schedule</t>
+  </si>
+  <si>
+    <t>Expired session rows are never deleted. purgeExpiredSessions() exists but nothing calls it.</t>
+  </si>
+  <si>
+    <t>Trivial once any scheduled job exists.</t>
+  </si>
+  <si>
+    <t>BE-18</t>
+  </si>
+  <si>
+    <t>Password hashing uses scrypt, not bcrypt</t>
+  </si>
+  <si>
+    <t>OUR DECISION: scrypt from Node's own crypto module, so there is no dependency to keep patched. The spec names bcrypt. Both are appropriate; only src/lib/auth.ts knows the format.</t>
+  </si>
+  <si>
+    <t>Stored as scrypt$salt$hash so the algorithm is self-describing and can be migrated per user.</t>
+  </si>
+  <si>
+    <t>BE-23</t>
+  </si>
+  <si>
+    <t>Admin figures are counted live, never cached</t>
+  </si>
+  <si>
+    <t>OUR DECISION: every number on the admin dashboard is counted from the database on each request. Caching them is how the old platform let admin counts and storefront counts disagree.</t>
+  </si>
+  <si>
+    <t>Still true after the admin build: every dashboard figure is a live count. Cheap at 60 products and 4 orders; revisit when either grows.</t>
+  </si>
+  <si>
+    <t>BE-24</t>
+  </si>
+  <si>
+    <t>Supplier data is scoped by query, not by filtering</t>
+  </si>
+  <si>
+    <t>OUR DECISION: a supplier's products and invoice lines are fetched through their supplier id, so another supplier's rows are never loaded rather than loaded and hidden.</t>
+  </si>
+  <si>
+    <t>Keep this rule as the supplier portal grows — filtering after fetching is how leaks happen.</t>
+  </si>
+  <si>
+    <t>BE-27</t>
+  </si>
+  <si>
+    <t>No marketing screens: wishlists and abandoned carts</t>
+  </si>
+  <si>
+    <t>Both are already recorded in the database and nobody can see either. An abandoned cart is the cheapest sale to recover, and a wishlist says what a buyer wants before they buy it.</t>
+  </si>
+  <si>
+    <t>Split out of BE-02 when the admin screens were built.</t>
+  </si>
+  <si>
+    <t>BE-28</t>
+  </si>
+  <si>
+    <t>No reports: sales by supplier, category or period</t>
+  </si>
+  <si>
+    <t>The dashboard totals every order ever placed and nothing else. There is no way to answer which supplier sells most, what a month looked like, or which categories are dead.</t>
+  </si>
+  <si>
+    <t>Split out of BE-02. Wants AC-09 settled first so periods line up with terms.</t>
+  </si>
+  <si>
+    <t>DA-14</t>
+  </si>
+  <si>
+    <t>Confirm the brand list</t>
+  </si>
+  <si>
+    <t>Brands were assigned by reading product names, because neither source listed a brand field. Bad extractions were caught by hand (Goat, Hello, Roger) but the list has never been checked against reality.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026 after DA-23: 26 brands across the 60 test products.</t>
+  </si>
+  <si>
+    <t>DA-15</t>
+  </si>
+  <si>
+    <t>Decide on duplicate categories</t>
+  </si>
+  <si>
+    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: still 6 duplicated names, 12 categories in total. Slugs are disambiguated by appending the numeric id (oral-care vs oral-care-96). 10 of the 12 hold no products at all, so most of the duplication is invisible to buyers today.</t>
+  </si>
+  <si>
+    <t>DA-16</t>
+  </si>
+  <si>
+    <t>Confirm the missing department</t>
+  </si>
+  <si>
+    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
+  </si>
+  <si>
+    <t>Confirm this is intentional rather than lost.</t>
+  </si>
+  <si>
+    <t>FN-10</t>
+  </si>
+  <si>
+    <t>Search is client-side only</t>
+  </si>
+  <si>
+    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
+  </si>
+  <si>
+    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
+  </si>
+  <si>
+    <t>IN-05</t>
+  </si>
+  <si>
+    <t>Supply Google and Facebook OAuth keys</t>
+  </si>
+  <si>
+    <t>Social login endpoints currently return 501.</t>
+  </si>
+  <si>
+    <t>IN-08</t>
+  </si>
+  <si>
+    <t>Correct the git author name</t>
+  </si>
+  <si>
+    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
+  </si>
+  <si>
+    <t>Fixable with git config user.name and an amend.</t>
+  </si>
+  <si>
+    <t>IN-09</t>
+  </si>
+  <si>
+    <t>Set up continuous integration</t>
+  </si>
+  <si>
+    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
+  </si>
+  <si>
+    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
+  </si>
+  <si>
+    <t>IN-10</t>
+  </si>
+  <si>
+    <t>Plan backups and disaster recovery</t>
+  </si>
+  <si>
+    <t>No backup strategy exists for the database or uploaded files.</t>
+  </si>
+  <si>
+    <t>Relevant once there is a real database.</t>
+  </si>
+  <si>
+    <t>LG-04</t>
+  </si>
+  <si>
+    <t>Approve the About / Contact / Order Support copy</t>
+  </si>
+  <si>
+    <t>All placeholder text.</t>
+  </si>
+  <si>
+    <t>Pages carry a visible placeholder notice.</t>
+  </si>
+  <si>
+    <t>DEC-01</t>
+  </si>
+  <si>
+    <t>Fresh build — the previous site is reference only</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: nothing to do with the previous site. The extraction is mined for data and business rules; its code and behaviour are discarded.</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Its category tree, product data and bug history were kept. Its markup was not.</t>
+  </si>
+  <si>
+    <t>DEC-02</t>
+  </si>
+  <si>
+    <t>Keep the existing visual brand</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026, correcting an earlier over-broad reading: the storefront must keep the current AussieMed look, not be redesigned.</t>
+  </si>
+  <si>
+    <t>Navy #29387d, red #ea2227 and Gilroy were read from the live site's computed styles. See DA-08 for the missing Gilroy weights.</t>
+  </si>
+  <si>
+    <t>DEC-03</t>
+  </si>
+  <si>
+    <t>Local only until the client approves</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: not to go online until there is a version they are happy with locally.</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. robots noindex is site-wide. Hosting is IN-01.</t>
+  </si>
+  <si>
+    <t>DEC-04</t>
+  </si>
+  <si>
+    <t>External connectors are handled last</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: anything needing a third-party account waits until the end so the build never stalls on credentials.</t>
+  </si>
+  <si>
+    <t>Payment IN-04, SMTP IN-03, OAuth IN-05, hosting IN-01. Built behind seams with local stand-ins.</t>
+  </si>
+  <si>
+    <t>DEC-05</t>
+  </si>
+  <si>
+    <t>Follow Livingstone for B2B catalogue and pricing behaviour</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026 with livingstone.com.au as the reference, and all suggested changes accepted.</t>
+  </si>
+  <si>
+    <t>Produced the pack/UOM model, price breaks on cards, the Ex/Inc VAT toggle, variant axes, spec attributes and per-product tax class.</t>
+  </si>
+  <si>
+    <t>DEC-06</t>
+  </si>
+  <si>
+    <t>Seed the catalogue from two real suppliers for testing</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: list Chemist Warehouse and Livingstone as suppliers with 30 items each, and remove the invented placeholders.</t>
+  </si>
+  <si>
+    <t>60 real products seeded. Both are unaffiliated third parties — DA-17 must close before launch.</t>
+  </si>
+  <si>
+    <t>DEC-07</t>
+  </si>
+  <si>
+    <t>Add product images</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026. Supplier photography was downloaded for local testing.</t>
+  </si>
+  <si>
+    <t>52 of 71 products have an image. Third-party assets — DA-03 must close before launch.</t>
+  </si>
+  <si>
+    <t>DEC-08</t>
+  </si>
+  <si>
+    <t>Four test accounts with a shared placeholder password</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: admin, musawi1989@gmail.com, supplier1 and supplier2, all with 123456. Explicitly described as local testing only, chosen to be memorable, and to be changed before anything real.</t>
+  </si>
+  <si>
+    <t>Implemented as asked. SEC-01 tracks removing them; SEC-03 tracks agreeing a password policy.</t>
+  </si>
+  <si>
+    <t>DEC-09</t>
+  </si>
+  <si>
+    <t>One sign-in door per role</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the business portal is the supplier login, the account login is for buyers, and admin is reached at /admin.</t>
+  </si>
+  <si>
+    <t>Implemented. Signing in at the wrong door names the right one rather than admitting the user.</t>
+  </si>
+  <si>
+    <t>DEC-10</t>
+  </si>
+  <si>
+    <t>Record every generated value and decision in this register</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026 and repeated 15 Aug: everything invented on the client's behalf must be written down rather than left in the code.</t>
+  </si>
+  <si>
+    <t>This register is the record. docs/Things That Need Attention.xlsx is generated from it and npm run register validates it.</t>
+  </si>
+  <si>
+    <t>DEC-11</t>
+  </si>
+  <si>
+    <t>Price breaks are packaging levels, not arbitrary quantities</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: a break at 12 exists because a carton holds 12, and a break at 48 because a box holds 4 cartons. The quantity and the packaging level are the same fact.</t>
+  </si>
+  <si>
+    <t>Each break now carries its level name. Corrects an earlier model that treated breaks as percentage discounts at round numbers.</t>
+  </si>
+  <si>
+    <t>DEC-12</t>
+  </si>
+  <si>
+    <t>Variants are a dropdown across sibling products</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the 375ml and the 60ml stay as separate products, and each carries a dropdown listing the whole family so a buyer can find their part quickly.</t>
+  </si>
+  <si>
+    <t>Replaces the Each/Carton chips on cards. Implemented as navigation between products, not options on one product, because each size has its own SKU, stock and price.</t>
+  </si>
+  <si>
+    <t>DEC-13</t>
+  </si>
+  <si>
+    <t>One sign-in button in the header, with a dropdown per role</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: replace the Business portal and Account links with a single blue Sign in button whose dropdown offers sign in as a buyer and sign in as a supplier.</t>
+  </si>
+  <si>
+    <t>Implemented in src/components/SignInMenu.tsx. Admin is deliberately absent from the dropdown; staff go to /admin directly. Once signed in the button becomes the way back to the user own area.</t>
+  </si>
+  <si>
+    <t>DEC-14</t>
+  </si>
+  <si>
+    <t>The AED label and the Ex/Inc VAT toggle are gone from the header</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: remove the AED text and the VAT options because VAT is to be carried in the displayed price later.</t>
+  </si>
+  <si>
+    <t>VatToggle deleted from the header. includeVat still exists in src/lib/store.tsx defaulting to ex-VAT with no UI control, so prices read ex-VAT everywhere until the pricing change lands. FE-30 tracks that follow up.</t>
+  </si>
+  <si>
+    <t>DEC-15</t>
+  </si>
+  <si>
+    <t>Sign out lives in the header, in the sign in button slot</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the sign out button always sits where the Sign in button would be when signed out.</t>
+  </si>
+  <si>
+    <t>Moved out of the account, admin and business portal pages into src/components/SignInMenu.tsx, so it is reachable from every page rather than only the dashboard. Signed in, the slot shows the account name plus Sign out.</t>
+  </si>
+  <si>
+    <t>DEC-16</t>
+  </si>
+  <si>
+    <t>Empty categories are hidden from navigation, not removed</t>
+  </si>
+  <si>
+    <t>The category tree came from Livingstone and is far wider than the 60 test products fill. Hiding what is empty keeps every menu entry useful; removing them would lose the shape of the intended range, and hard-coding a shorter list would need maintaining by hand.</t>
+  </si>
+  <si>
+    <t>Our decision, 15 Aug 2026, taken while closing FN-11. It is computed rather than configured, so categories reappear on their own as products are filed into them. Direct URLs still work. Say if you would rather the full tree stayed visible.</t>
+  </si>
+  <si>
+    <t>DEC-17</t>
+  </si>
+  <si>
+    <t>Renaming a category does not change its URL</t>
+  </si>
+  <si>
+    <t>The slug is the address. A category that has been linked to, bookmarked or indexed keeps working when its display name changes, and changing both would silently break every existing link.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026. Renaming to something genuinely different means creating a category and moving products, or a redirect table we have not built. Say if you would rather the URL followed the name.</t>
+  </si>
+  <si>
+    <t>DEC-18</t>
+  </si>
+  <si>
+    <t>A product cannot go live without a SKU and a category</t>
+  </si>
+  <si>
+    <t>Both make a live product broken rather than merely incomplete: no SKU means nothing to buy, no category means nobody can browse to it. The admin screen refuses the transition and says which one is missing.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026, enforced in src/lib/admin.ts rather than in the form, so posting to the endpoint directly cannot bypass it.</t>
+  </si>
+  <si>
+    <t>DEC-19</t>
+  </si>
+  <si>
+    <t>Delivered and cancelled orders cannot be reopened</t>
+  </si>
+  <si>
+    <t>Both are closed documents the customer already holds. A status that contradicts what they received is worse than no status at all.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026. A delivered order needs a return and a cancelled one needs a new order — neither of which exists yet. Confirm this matches how you actually work.</t>
+  </si>
+  <si>
+    <t>DA-09</t>
+  </si>
+  <si>
+    <t>Explain the disappearing product</t>
+  </si>
+  <si>
+    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
+  </si>
+  <si>
+    <t>Deferred 15 Aug 2026. The product in question was one of the 11 removed under DA-23 and nothing is being migrated from the old platform, so this no longer affects the build. Worth revisiting only if data from the old system is ever imported.</t>
+  </si>
+  <si>
+    <t>DF-01</t>
+  </si>
+  <si>
+    <t>Industry taxonomy</t>
+  </si>
+  <si>
+    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
+  </si>
+  <si>
+    <t>Additive; adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-02</t>
+  </si>
+  <si>
+    <t>Subscribe and Save</t>
+  </si>
+  <si>
+    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
+  </si>
+  <si>
+    <t>Needs the backend.</t>
+  </si>
+  <si>
+    <t>DF-03</t>
+  </si>
+  <si>
+    <t>Frequently bought together</t>
+  </si>
+  <si>
+    <t>Bundle suggestion with a combined total and one action to add all.</t>
+  </si>
+  <si>
+    <t>Adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-04</t>
+  </si>
+  <si>
+    <t>Quick view</t>
+  </si>
+  <si>
+    <t>View a product from the listing without a page load.</t>
+  </si>
+  <si>
+    <t>DF-05</t>
+  </si>
+  <si>
+    <t>Downloadable PDF catalogues</t>
+  </si>
+  <si>
+    <t>Still how a lot of trade buying happens.</t>
+  </si>
+  <si>
+    <t>Needs the actual catalogue files.</t>
+  </si>
+  <si>
     <t>BE-02</t>
   </si>
   <si>
@@ -197,19 +1394,43 @@
     <t>Products, categories, suppliers, customers, orders, marketing, reports, settings.</t>
   </si>
   <si>
-    <t>The dashboard exists at /admin and is role-guarded. The screens behind it do not — BE-20 tracks those.</t>
-  </si>
-  <si>
-    <t>BE-03</t>
-  </si>
-  <si>
-    <t>Build the supplier portal</t>
-  </si>
-  <si>
-    <t>Suppliers manage their own products but can never self-approve. Must have a failing-then-passing test.</t>
-  </si>
-  <si>
-    <t>The dashboard exists at /business-portal and is role-guarded and supplier-scoped. The editing screens behind it do not — BE-21 tracks those. Approval is an admin-only transition enforced in the service layer.</t>
+    <t>Done 16 Aug 2026 by BE-20. Marketing (wishlists, abandoned carts) and reports are not built — BE-27 and BE-28.</t>
+  </si>
+  <si>
+    <t>BE-07</t>
+  </si>
+  <si>
+    <t>Seed the database from the catalogue</t>
+  </si>
+  <si>
+    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
+  </si>
+  <si>
+    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
+  </si>
+  <si>
+    <t>BE-09</t>
+  </si>
+  <si>
+    <t>Point the storefront at the database</t>
+  </si>
+  <si>
+    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
+  </si>
+  <si>
+    <t>query.ts was untouched — it never knew where products came from.</t>
+  </si>
+  <si>
+    <t>BE-11</t>
+  </si>
+  <si>
+    <t>Order pages restricted to their owner</t>
+  </si>
+  <si>
+    <t>An order was readable by anyone who guessed a sequential reference. Now an admin sees any order, the account that placed it sees it, and a guest sees only an order placed from their own cart.</t>
+  </si>
+  <si>
+    <t>A forbidden order returns 404 rather than 403, so the response cannot be used to discover which references exist.</t>
   </si>
   <si>
     <t>BE-20</t>
@@ -221,289 +1442,205 @@
     <t>/admin authenticates and shows live figures, but every management screen is still missing: products, categories, suppliers, customers, orders, bulk upload, marketing, reports, settings.</t>
   </si>
   <si>
-    <t>The dashboard lists them on screen so the gap is visible rather than implied.</t>
-  </si>
-  <si>
-    <t>BE-21</t>
-  </si>
-  <si>
-    <t>Build the supplier portal behind its dashboard</t>
-  </si>
-  <si>
-    <t>The business portal authenticates and shows a supplier their own products and invoice lines, read-only. Creating and editing products, toggling stock and bulk upload are not built.</t>
-  </si>
-  <si>
-    <t>A supplier must never be able to approve their own product — the rule to enforce when editing lands.</t>
-  </si>
-  <si>
-    <t>DA-01</t>
-  </si>
-  <si>
-    <t>Supply the real product catalogue</t>
-  </si>
-  <si>
-    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
-  </si>
-  <si>
-    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
-  </si>
-  <si>
-    <t>DA-03</t>
-  </si>
-  <si>
-    <t>Supply product photography</t>
-  </si>
-  <si>
-    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
-  </si>
-  <si>
-    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
-  </si>
-  <si>
-    <t>DA-06</t>
-  </si>
-  <si>
-    <t>Supply the real supplier list</t>
-  </si>
-  <si>
-    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
-  </si>
-  <si>
-    <t>All are flagged isPlaceholder in the data.</t>
-  </si>
-  <si>
-    <t>DA-17</t>
-  </si>
-  <si>
-    <t>Replace the test supplier attribution</t>
-  </si>
-  <si>
-    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
-  </si>
-  <si>
-    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
-  </si>
-  <si>
-    <t>DA-20</t>
-  </si>
-  <si>
-    <t>Supply the real packaging quantities</t>
-  </si>
-  <si>
-    <t>OUR INVENTED VALUES: how many units make a carton, and how many cartons make a box, are guessed per product family (12 and 4 by default, 10 and 5 for gloves, 20 and 5 for masks). The break discounts of 4% and 8% are also invented.</t>
-  </si>
-  <si>
-    <t>These are now shown to buyers as CARTON and BOX, so a wrong number reads as a factual claim about your packaging. In scripts/variants.mjs.</t>
-  </si>
-  <si>
-    <t>FN-02</t>
-  </si>
-  <si>
-    <t>Quote requests are not delivered</t>
-  </si>
-  <si>
-    <t>Captured in the browser only.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend and an email provider.</t>
-  </si>
-  <si>
-    <t>FN-03</t>
-  </si>
-  <si>
-    <t>Bulk buy enquiries are not delivered</t>
-  </si>
-  <si>
-    <t>FN-04</t>
-  </si>
-  <si>
-    <t>Notify Me does not register a subscription</t>
-  </si>
-  <si>
-    <t>Captured locally. The restock email flow does not exist.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend.</t>
-  </si>
-  <si>
-    <t>IN-06</t>
-  </si>
-  <si>
-    <t>Remove noindex before launch</t>
-  </si>
-  <si>
-    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
-  </si>
-  <si>
-    <t>Must be removed deliberately at launch — and only then.</t>
-  </si>
-  <si>
-    <t>IN-07</t>
-  </si>
-  <si>
-    <t>Confirm the GitHub repository is private</t>
-  </si>
-  <si>
-    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
-  </si>
-  <si>
-    <t>https://github.com/musawi1989/aussiemed</t>
-  </si>
-  <si>
-    <t>LG-01</t>
-  </si>
-  <si>
-    <t>Supply terms and conditions</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
-  </si>
-  <si>
-    <t>Page exists and says so on screen.</t>
-  </si>
-  <si>
-    <t>LG-02</t>
-  </si>
-  <si>
-    <t>Supply the privacy policy</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
-  </si>
-  <si>
-    <t>LG-03</t>
-  </si>
-  <si>
-    <t>Confirm the contact email address</t>
-  </si>
-  <si>
-    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
-  </si>
-  <si>
-    <t>Also determines the sending domain for transactional email.</t>
-  </si>
-  <si>
-    <t>SEC-01</t>
-  </si>
-  <si>
-    <t>Remove the test credentials before any deployment</t>
-  </si>
-  <si>
-    <t>Four accounts share the password 123456: admin, musawi1989@gmail.com, supplier1, supplier2. Fine on a laptop, unacceptable anywhere else.</t>
-  </si>
-  <si>
-    <t>The on-screen credentials panel now renders only outside production, so a production build cannot leak it. The accounts themselves still must be removed or given real passwords.</t>
-  </si>
-  <si>
-    <t>AC-05</t>
-  </si>
-  <si>
-    <t>Confirm the VAT rate and whether it must be configurable</t>
-  </si>
-  <si>
-    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>Rate must be stored on the order at the time it is placed.</t>
-  </si>
-  <si>
-    <t>AC-06</t>
-  </si>
-  <si>
-    <t>Approve the reference number format</t>
-  </si>
-  <si>
-    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
-  </si>
-  <si>
-    <t>Wording is fixed as Reference number, never order number.</t>
-  </si>
-  <si>
-    <t>AC-07</t>
-  </si>
-  <si>
-    <t>Approve the supplier invoice numbering</t>
-  </si>
-  <si>
-    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
-  </si>
-  <si>
-    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
-  </si>
-  <si>
-    <t>AC-09</t>
-  </si>
-  <si>
-    <t>Decide payment terms and credit accounts</t>
-  </si>
-  <si>
-    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
-  </si>
-  <si>
-    <t>Affects the schema — decide before the backend.</t>
-  </si>
-  <si>
-    <t>AC-11</t>
-  </si>
-  <si>
-    <t>Approve the VAT rounding method on invoices</t>
-  </si>
-  <si>
-    <t>VAT is rounded per line rather than once per invoice, so the printed lines always add up to the printed total. The alternative rounds once and can leave lines that do not sum.</t>
-  </si>
-  <si>
-    <t>Verified by test: per-invoice VAT sums to the order VAT exactly.</t>
-  </si>
-  <si>
-    <t>AC-12</t>
-  </si>
-  <si>
-    <t>Confirm the reference number sequence resets each year</t>
-  </si>
-  <si>
-    <t>OUR DECISION: the sequence restarts at 000001 each calendar year, so AM-2026-000001 and AM-2027-000001 can both exist. If accounting needs a single unbroken sequence this must change before real orders.</t>
-  </si>
-  <si>
-    <t>Held in a settings row keyed orderSequence:YYYY and incremented inside the checkout transaction.</t>
-  </si>
-  <si>
-    <t>AC-13</t>
-  </si>
-  <si>
-    <t>Decide whether an order should reserve stock</t>
-  </si>
-  <si>
-    <t>OUR DECISION: checkout does not decrement or reserve anything, because there are no stock levels — only an in/out flag. Two customers can order the last unit.</t>
-  </si>
-  <si>
-    <t>Depends on FN-08. Out-of-stock is re-checked at checkout, so a line that sold out while the form was open is rejected.</t>
-  </si>
-  <si>
-    <t>BE-04</t>
-  </si>
-  <si>
-    <t>Build comma-safe .xlsx bulk upload</t>
-  </si>
-  <si>
-    <t>Parsed natively with exceljs, never by splitting on commas — that is what broke comma-containing category names.</t>
-  </si>
-  <si>
-    <t>Unknown brands must be reported per row, never skipped silently.</t>
-  </si>
-  <si>
-    <t>BE-05</t>
-  </si>
-  <si>
-    <t>Build the email flows</t>
-  </si>
-  <si>
-    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
-  </si>
-  <si>
-    <t>Needs an SMTP provider.</t>
+    <t>Built 16 Aug 2026. Dashboard, products (list, filters, edit, SKUs, price breaks, approval), categories, suppliers, orders, customers, settings and an audit trail. Every write goes through src/lib/admin.ts, which checks the role again in the service layer, records the change, and bumps the catalogue version so the storefront updates without a restart. Bulk upload is BE-04; product image upload is still missing — see BE-29.</t>
+  </si>
+  <si>
+    <t>BE-25</t>
+  </si>
+  <si>
+    <t>Invalidate the catalogue cache after a seed or an edit</t>
+  </si>
+  <si>
+    <t>The data layer caches the catalogue for the life of the process, so a running server keeps serving whatever it read first. This is not theoretical: on 15 Aug 2026 the dev server was still showing a retired carton SKU as a purchasable unit chip on the product page, hours after the database had deactivated it.</t>
+  </si>
+  <si>
+    <t>Fixed 15 Aug 2026. The cache now carries the catalogVersion stamp it was built from and re-checks it against the database at most once a second; the seed bumps the stamp, and invalidateCatalog() bumps it too so other server processes drop their copy as well. Verified live: a running dev server went from 71 products to 60 without a restart, and the phantom carton chip disappeared.</t>
+  </si>
+  <si>
+    <t>DN-01</t>
+  </si>
+  <si>
+    <t>Currency rendering</t>
+  </si>
+  <si>
+    <t>Was rendering the Arabic symbol and 4 decimals. Now always the English string AED with exactly 2 decimals, enforced by test and by a grep check.</t>
+  </si>
+  <si>
+    <t>Fixed in the initial build.</t>
+  </si>
+  <si>
+    <t>DN-02</t>
+  </si>
+  <si>
+    <t>Integer quantities</t>
+  </si>
+  <si>
+    <t>Quantities were rendering as decimals such as 3.00.</t>
+  </si>
+  <si>
+    <t>DN-03</t>
+  </si>
+  <si>
+    <t>Category filtering</t>
+  </si>
+  <si>
+    <t>Every category link redirected to the full product list. Filtering now works, including rolling a department up to everything beneath it.</t>
+  </si>
+  <si>
+    <t>DN-04</t>
+  </si>
+  <si>
+    <t>Category counts matching results</t>
+  </si>
+  <si>
+    <t>Admin and storefront counts could diverge. Counts are now derived from the same query that lists the products.</t>
+  </si>
+  <si>
+    <t>Asserted in the data checks and the API contract checks.</t>
+  </si>
+  <si>
+    <t>DN-05</t>
+  </si>
+  <si>
+    <t>Category slug collisions</t>
+  </si>
+  <si>
+    <t>Six categories shared a slug with another category, so one was unreachable and the other answered to the wrong name.</t>
+  </si>
+  <si>
+    <t>Found by the API contract check. Slugs are now unique tree-wide and asserted.</t>
+  </si>
+  <si>
+    <t>DN-06</t>
+  </si>
+  <si>
+    <t>Per-supplier invoicing</t>
+  </si>
+  <si>
+    <t>An order spanning N suppliers now produces exactly N invoices under one reference number, with per-invoice VAT summing to the order VAT without drift.</t>
+  </si>
+  <si>
+    <t>Verified end to end in the browser and by test.</t>
+  </si>
+  <si>
+    <t>DN-11</t>
+  </si>
+  <si>
+    <t>Pack and unit of measure model</t>
+  </si>
+  <si>
+    <t>The same line sells by the box and by the carton at different prices. Cart lines are keyed by product and pack so they never merge.</t>
+  </si>
+  <si>
+    <t>Outers are asserted to beat buying their contents separately.</t>
+  </si>
+  <si>
+    <t>DN-14</t>
+  </si>
+  <si>
+    <t>Control characters in generated code</t>
+  </si>
+  <si>
+    <t>Shell escaping wrote literal backspace bytes into regex rules, so every packaging and variant rule silently matched nothing while looking correct in every editor.</t>
+  </si>
+  <si>
+    <t>Found via od. A data check now asserts each variant selection matches an option.</t>
+  </si>
+  <si>
+    <t>DN-16</t>
+  </si>
+  <si>
+    <t>Database schema designed and migrated</t>
+  </si>
+  <si>
+    <t>Thirty tables covering catalogue, packs as SKUs, variants, attributes, documents, batches, orders, per-supplier invoices, quotes, bulk upload and audit.</t>
+  </si>
+  <si>
+    <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
+  </si>
+  <si>
+    <t>DN-17</t>
+  </si>
+  <si>
+    <t>Typecheck was silently passing on a stale cache</t>
+  </si>
+  <si>
+    <t>tsc ran with incremental caching and reported no errors while real type errors existed in the tree. Every earlier typecheck-clean claim was suspect.</t>
+  </si>
+  <si>
+    <t>npm run typecheck now runs with --incremental false. Caught seven genuine errors the moment it was disabled.</t>
+  </si>
+  <si>
+    <t>DN-18</t>
+  </si>
+  <si>
+    <t>Cart moved to the server</t>
+  </si>
+  <si>
+    <t>The cart was localStorage, so the browser held prices. It is now database rows priced entirely on the server; the client cannot tell the server what anything costs.</t>
+  </si>
+  <si>
+    <t>Guest carts are cookie-keyed. The catalogue snapshot endpoint stays until the wishlist and quote cart follow.</t>
+  </si>
+  <si>
+    <t>DN-19</t>
+  </si>
+  <si>
+    <t>Checkout writes real orders</t>
+  </si>
+  <si>
+    <t>One transaction creates the order, one invoice per supplier and every line, or nothing at all. Reference numbers are allocated server-side inside that transaction.</t>
+  </si>
+  <si>
+    <t>Verified in a browser end to end, and by 14 order invariants in npm run db:check.</t>
+  </si>
+  <si>
+    <t>DN-20</t>
+  </si>
+  <si>
+    <t>Four sign-in accounts seeded</t>
+  </si>
+  <si>
+    <t>admin, musawi1989@gmail.com, supplier1 and supplier2, each able to sign in by username or email. Suppliers are attached to their seeded companies.</t>
+  </si>
+  <si>
+    <t>Seeded separately from the catalogue so re-seeding products does not remove accounts.</t>
+  </si>
+  <si>
+    <t>FN-01</t>
+  </si>
+  <si>
+    <t>Checkout does not submit an order</t>
+  </si>
+  <si>
+    <t>Done. Checkout writes a real order in one transaction, with one invoice per supplier and a server-allocated reference number.</t>
+  </si>
+  <si>
+    <t>Payment is still not taken and no email is sent.</t>
+  </si>
+  <si>
+    <t>FN-05</t>
+  </si>
+  <si>
+    <t>Real sign-in replaced the demo flag</t>
+  </si>
+  <si>
+    <t>Sign-in was a localStorage boolean anyone could set. It is now a database-backed session with a scrypt-hashed password.</t>
+  </si>
+  <si>
+    <t>Sessions are rows; signing out deletes the row, so a copied cookie stops working.</t>
+  </si>
+  <si>
+    <t>FN-06</t>
+  </si>
+  <si>
+    <t>Account history is real</t>
+  </si>
+  <si>
+    <t>The account area showed three fabricated orders. It now reads the signed-in user's actual orders, and reorder-first is built from what they have really bought.</t>
+  </si>
+  <si>
+    <t>Says so plainly when there is no history yet, rather than showing an empty grid.</t>
   </si>
   <si>
     <t>BE-06</t>
@@ -515,1072 +1652,7 @@
     <t>Every status transition and every admin or supplier write should be recorded.</t>
   </si>
   <si>
-    <t>Specified in the backend spec.</t>
-  </si>
-  <si>
-    <t>BE-08</t>
-  </si>
-  <si>
-    <t>Decide money representation before any data lands</t>
-  </si>
-  <si>
-    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
-  </si>
-  <si>
-    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
-  </si>
-  <si>
-    <t>BE-10</t>
-  </si>
-  <si>
-    <t>Retire the catalogue snapshot endpoint</t>
-  </si>
-  <si>
-    <t>Client components fetch the whole catalogue from /api/v1/catalog/snapshot. Fine for 71 products; not for thousands. Goes away when the cart moves server-side.</t>
-  </si>
-  <si>
-    <t>Phase 3 removes the need.</t>
-  </si>
-  <si>
-    <t>BE-12</t>
-  </si>
-  <si>
-    <t>Merge a guest cart into the user cart on sign-in</t>
-  </si>
-  <si>
-    <t>Carts are keyed by a cookie so a visitor can shop before signing in. The merge on sign-in is specified but cannot be built until auth exists.</t>
-  </si>
-  <si>
-    <t>Cart cookie: aussiemed_cart, httpOnly, 30 day lifetime — OUR INVENTED VALUES.</t>
-  </si>
-  <si>
-    <t>BE-14</t>
-  </si>
-  <si>
-    <t>Confirm the default order and invoice status</t>
-  </si>
-  <si>
-    <t>OUR DECISION: new orders are Pending and each supplier invoice is Pending. The real workflow — who moves an order to Processing, and when an invoice becomes Issued — is not defined.</t>
-  </si>
-  <si>
-    <t>Order statuses available: Pending, Processing, Dispatched, Delivered, Cancelled.</t>
-  </si>
-  <si>
-    <t>BE-15</t>
-  </si>
-  <si>
-    <t>Passwords were built instead of the specified email OTP</t>
-  </si>
-  <si>
-    <t>BACKEND_SPEC.md specifies passwordless sign-in by emailed code. Passwords were requested instead and built. Livingstone advertises password-free login as a feature, so the spec was not arbitrary.</t>
-  </si>
-  <si>
-    <t>Both can coexist: the schema keeps otpCode and otpExpiresAt. Decide before launch.</t>
-  </si>
-  <si>
-    <t>BE-19</t>
-  </si>
-  <si>
-    <t>Guest checkout is allowed</t>
-  </si>
-  <si>
-    <t>OUR DECISION: an order can be placed without signing in, and is then tied to the cart cookie. Signing in simply attaches the order to the account.</t>
-  </si>
-  <si>
-    <t>If trade accounts should be required to order, this must change — it also affects credit terms and pricing.</t>
-  </si>
-  <si>
-    <t>BE-22</t>
-  </si>
-  <si>
-    <t>Confirm one supplier account per company</t>
-  </si>
-  <si>
-    <t>OUR DECISION: each supplier company links to a single user. Real suppliers usually need several people with their own logins.</t>
-  </si>
-  <si>
-    <t>Schema allows it via Supplier.userId; supporting several needs a join table.</t>
-  </si>
-  <si>
-    <t>DA-02</t>
-  </si>
-  <si>
-    <t>Verify the product-to-category mapping</t>
-  </si>
-  <si>
-    <t>The extraction had no product-category link at all, so every mapping on the site is ours. The catalogue is now 71 products across 146 categories and none of that mapping has been checked by anyone who knows the range.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026 after DA-23: 60 active products, 0 uncategorised.</t>
-  </si>
-  <si>
-    <t>DA-05</t>
-  </si>
-  <si>
-    <t>Approve the product descriptions</t>
-  </si>
-  <si>
-    <t>The source had no descriptions. All 71 active products now carry text we generated from the product name and supplier listing, and it goes out under AussieMed's name.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026 after DA-23: 60 of 60 active products have a generated description.</t>
-  </si>
-  <si>
-    <t>DA-07</t>
-  </si>
-  <si>
-    <t>Supply the hero banner image</t>
-  </si>
-  <si>
-    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured — only Brand, Category, Product and WebHtml folders were mirrored.</t>
-  </si>
-  <si>
-    <t>A genuine AussieMed CMS image stands in.</t>
-  </si>
-  <si>
-    <t>DA-08</t>
-  </si>
-  <si>
-    <t>Obtain Gilroy Regular and Medium</t>
-  </si>
-  <si>
-    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
-  </si>
-  <si>
-    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
-  </si>
-  <si>
-    <t>DA-10</t>
-  </si>
-  <si>
-    <t>Supply real pack and carton structures</t>
-  </si>
-  <si>
-    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
-  </si>
-  <si>
-    <t>Largely superseded by DA-20: packaging moved from separate carton SKUs into named price breaks on 15 Aug 2026, so the invented figures now live in scripts/variants.mjs rather than in outer packs. Kept open because the underlying question — what is a real carton and box for each line — is unanswered either way.</t>
-  </si>
-  <si>
-    <t>DA-11</t>
-  </si>
-  <si>
-    <t>Supply real variant data</t>
-  </si>
-  <si>
-    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: the same five sizes and three colours are stamped on all six glove products regardless of what the supplier actually sells. FN-07 covers the wiring; this row covers the data.</t>
-  </si>
-  <si>
-    <t>DA-12</t>
-  </si>
-  <si>
-    <t>Supply real product specifications</t>
-  </si>
-  <si>
-    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
-  </si>
-  <si>
-    <t>These become search filters later.</t>
-  </si>
-  <si>
-    <t>DA-13</t>
-  </si>
-  <si>
-    <t>Supply safety data sheets and spec sheets</t>
-  </si>
-  <si>
-    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
-  </si>
-  <si>
-    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
-  </si>
-  <si>
-    <t>DA-18</t>
-  </si>
-  <si>
-    <t>Product ids are derived from slugs</t>
-  </si>
-  <si>
-    <t>Carts and wishlists are stored in the browser against a product id. Ids are now hashed from the slug so they survive a re-seed, which means CHANGING A PRODUCT SLUG ORPHANS ANY SAVED CART LINE referencing it.</t>
-  </si>
-  <si>
-    <t>Resolved properly when the cart moves server-side and references SKU rows directly.</t>
-  </si>
-  <si>
-    <t>DA-19</t>
-  </si>
-  <si>
-    <t>Supplier email addresses are invented</t>
-  </si>
-  <si>
-    <t>The seed writes orders@&lt;supplier&gt;.example and accounts@&lt;supplier&gt;.example because secondaryEmail is mandatory. No supplier will receive anything at these addresses.</t>
-  </si>
-  <si>
-    <t>Both addresses are meant to receive order notifications once email exists.</t>
-  </si>
-  <si>
-    <t>DA-21</t>
-  </si>
-  <si>
-    <t>Verify the automatic variant grouping</t>
-  </si>
-  <si>
-    <t>Products are grouped into families by stripping sizes and volumes from their names. It found 2 families in the seeded catalogue. A real catalogue will group differently and some groupings will be wrong.</t>
-  </si>
-  <si>
-    <t>The admin product screens should let a family be set explicitly rather than inferred — see BE-20.</t>
-  </si>
-  <si>
-    <t>DA-24</t>
-  </si>
-  <si>
-    <t>13 of 60 products have no image</t>
-  </si>
-  <si>
-    <t>Those products render as a monogram tile rather than a photograph. It is a deliberate stand-in and reads acceptably in a grid, but on a trade catalogue an image is often how a buyer confirms they have the right item.</t>
-  </si>
-  <si>
-    <t>Was 19 of 71. Ten went with the extraction products under DA-23. Four more were added deliberately: their image files turned out to be SVG placeholders saved with a .jpg extension, which the image optimiser rejected with a 400 — see DA-25. The remaining nine have no sourceSku or sourceUrl recorded, so there is nothing to retry a fetch against, and no more third-party photography was sourced because DA-17 already limits what may ship. Subset of DA-03.</t>
-  </si>
-  <si>
-    <t>FE-30</t>
-  </si>
-  <si>
-    <t>Prices are still labelled Ex. VAT with no way to see inc-VAT</t>
-  </si>
-  <si>
-    <t>The header toggle was removed before VAT was folded into the displayed price, so a buyer approving an invoice has no inc-VAT figure anywhere on the storefront. Checkout still adds VAT, so the total at the end is higher than every price shown.</t>
-  </si>
-  <si>
-    <t>Follow up to DEC-14. Decide whether displayed prices become VAT inclusive or the Ex. VAT labels simply stay.</t>
-  </si>
-  <si>
-    <t>FN-07</t>
-  </si>
-  <si>
-    <t>Size and colour switching is not wired</t>
-  </si>
-  <si>
-    <t>The variant dropdown built on 15 Aug 2026 (DEC-12) switches between sibling products by size or volume, and that works. The separate Size and Colour chips on gloves and the scrub top are a different thing and still do nothing — no sibling SKU exists behind any of them.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: 13 option axes across 6 products. Every glove carries an identical Size = XS/S/M/L/XL and Colour = Black/Blue/Green with no SKU attached to any value.</t>
-  </si>
-  <si>
-    <t>FN-08</t>
-  </si>
-  <si>
-    <t>Stock is a boolean</t>
-  </si>
-  <si>
-    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
-  </si>
-  <si>
-    <t>Decide whether real stock levels are needed.</t>
-  </si>
-  <si>
-    <t>FN-09</t>
-  </si>
-  <si>
-    <t>Decide on expiry and short-dated stock</t>
-  </si>
-  <si>
-    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
-  </si>
-  <si>
-    <t>Schema-shaping — decide before the backend is built.</t>
-  </si>
-  <si>
-    <t>IN-01</t>
-  </si>
-  <si>
-    <t>Choose a hosting target</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. The site runs locally only.</t>
-  </si>
-  <si>
-    <t>Deliberately deferred until the build is approved.</t>
-  </si>
-  <si>
-    <t>IN-02</t>
-  </si>
-  <si>
-    <t>Choose the database</t>
-  </si>
-  <si>
-    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
-  </si>
-  <si>
-    <t>IN-03</t>
-  </si>
-  <si>
-    <t>Choose an SMTP provider and sending domain</t>
-  </si>
-  <si>
-    <t>Required for every transactional email.</t>
-  </si>
-  <si>
-    <t>Must not be the misspelled assuiemed.com domain.</t>
-  </si>
-  <si>
-    <t>IN-04</t>
-  </si>
-  <si>
-    <t>Decide on a payment gateway</t>
-  </si>
-  <si>
-    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
-  </si>
-  <si>
-    <t>LG-05</t>
-  </si>
-  <si>
-    <t>Transfer the theme licence</t>
-  </si>
-  <si>
-    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
-  </si>
-  <si>
-    <t>Repository must stay private because of this.</t>
-  </si>
-  <si>
-    <t>LG-06</t>
-  </si>
-  <si>
-    <t>Supply company registration details</t>
-  </si>
-  <si>
-    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
-  </si>
-  <si>
-    <t>SEC-02</t>
-  </si>
-  <si>
-    <t>Add rate limiting to sign-in</t>
-  </si>
-  <si>
-    <t>Nothing limits password attempts, so the sign-in endpoint can be brute forced. The spec asks for rate limiting on auth in the hardening phase.</t>
-  </si>
-  <si>
-    <t>Matters more with short passwords than with OTP.</t>
-  </si>
-  <si>
-    <t>SEC-03</t>
-  </si>
-  <si>
-    <t>Agree a password policy</t>
-  </si>
-  <si>
-    <t>No minimum length, complexity or reuse rule is enforced. 123456 was accepted because nothing rejects it.</t>
-  </si>
-  <si>
-    <t>Moot if the OTP flow in BE-15 is adopted instead.</t>
-  </si>
-  <si>
-    <t>AC-08</t>
-  </si>
-  <si>
-    <t>Confirm the rounding policy</t>
-  </si>
-  <si>
-    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>Verified by test; needs sign-off that the method is acceptable.</t>
-  </si>
-  <si>
-    <t>AC-10</t>
-  </si>
-  <si>
-    <t>Confirm the default price display</t>
-  </si>
-  <si>
-    <t>Prices are shown Ex. VAT everywhere, and since 15 Aug 2026 there is no way for a buyer to see an inc-VAT figure at all — the header toggle was removed at the client's request before VAT was folded into the displayed price.</t>
-  </si>
-  <si>
-    <t>See DEC-14 for the decision and FE-30 for the gap it leaves open.</t>
-  </si>
-  <si>
-    <t>BE-13</t>
-  </si>
-  <si>
-    <t>Expire abandoned guest carts</t>
-  </si>
-  <si>
-    <t>Cart rows are never cleaned up. Every visitor who adds an item creates one that lives forever.</t>
-  </si>
-  <si>
-    <t>The spec wants abandoned carts over 24h reportable under Admin &gt; Marketing, so expiry and that report should be designed together.</t>
-  </si>
-  <si>
-    <t>BE-16</t>
-  </si>
-  <si>
-    <t>Confirm the session lifetime</t>
-  </si>
-  <si>
-    <t>OUR INVENTED VALUE: sessions last 7 days, then require signing in again. No idle timeout and no re-authentication for sensitive actions.</t>
-  </si>
-  <si>
-    <t>Cookie is httpOnly and sameSite=lax; secure only in production so local http still works.</t>
-  </si>
-  <si>
-    <t>BE-17</t>
-  </si>
-  <si>
-    <t>Purge expired sessions on a schedule</t>
-  </si>
-  <si>
-    <t>Expired session rows are never deleted. purgeExpiredSessions() exists but nothing calls it.</t>
-  </si>
-  <si>
-    <t>Trivial once any scheduled job exists.</t>
-  </si>
-  <si>
-    <t>BE-18</t>
-  </si>
-  <si>
-    <t>Password hashing uses scrypt, not bcrypt</t>
-  </si>
-  <si>
-    <t>OUR DECISION: scrypt from Node's own crypto module, so there is no dependency to keep patched. The spec names bcrypt. Both are appropriate; only src/lib/auth.ts knows the format.</t>
-  </si>
-  <si>
-    <t>Stored as scrypt$salt$hash so the algorithm is self-describing and can be migrated per user.</t>
-  </si>
-  <si>
-    <t>BE-23</t>
-  </si>
-  <si>
-    <t>Admin figures are counted live, never cached</t>
-  </si>
-  <si>
-    <t>OUR DECISION: every number on the admin dashboard is counted from the database on each request. Caching them is how the old platform let admin counts and storefront counts disagree.</t>
-  </si>
-  <si>
-    <t>Revisit only if the dashboard becomes slow, and then with explicit invalidation.</t>
-  </si>
-  <si>
-    <t>BE-24</t>
-  </si>
-  <si>
-    <t>Supplier data is scoped by query, not by filtering</t>
-  </si>
-  <si>
-    <t>OUR DECISION: a supplier's products and invoice lines are fetched through their supplier id, so another supplier's rows are never loaded rather than loaded and hidden.</t>
-  </si>
-  <si>
-    <t>Keep this rule as the supplier portal grows — filtering after fetching is how leaks happen.</t>
-  </si>
-  <si>
-    <t>DA-14</t>
-  </si>
-  <si>
-    <t>Confirm the brand list</t>
-  </si>
-  <si>
-    <t>Brands were assigned by reading product names, because neither source listed a brand field. Bad extractions were caught by hand (Goat, Hello, Roger) but the list has never been checked against reality.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026 after DA-23: 26 brands across the 60 test products.</t>
-  </si>
-  <si>
-    <t>DA-15</t>
-  </si>
-  <si>
-    <t>Decide on duplicate categories</t>
-  </si>
-  <si>
-    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: still 6 duplicated names, 12 categories in total. Slugs are disambiguated by appending the numeric id (oral-care vs oral-care-96). 10 of the 12 hold no products at all, so most of the duplication is invisible to buyers today.</t>
-  </si>
-  <si>
-    <t>DA-16</t>
-  </si>
-  <si>
-    <t>Confirm the missing department</t>
-  </si>
-  <si>
-    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
-  </si>
-  <si>
-    <t>Confirm this is intentional rather than lost.</t>
-  </si>
-  <si>
-    <t>FN-10</t>
-  </si>
-  <si>
-    <t>Search is client-side only</t>
-  </si>
-  <si>
-    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
-  </si>
-  <si>
-    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
-  </si>
-  <si>
-    <t>IN-05</t>
-  </si>
-  <si>
-    <t>Supply Google and Facebook OAuth keys</t>
-  </si>
-  <si>
-    <t>Social login endpoints currently return 501.</t>
-  </si>
-  <si>
-    <t>IN-08</t>
-  </si>
-  <si>
-    <t>Correct the git author name</t>
-  </si>
-  <si>
-    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
-  </si>
-  <si>
-    <t>Fixable with git config user.name and an amend.</t>
-  </si>
-  <si>
-    <t>IN-09</t>
-  </si>
-  <si>
-    <t>Set up continuous integration</t>
-  </si>
-  <si>
-    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
-  </si>
-  <si>
-    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
-  </si>
-  <si>
-    <t>IN-10</t>
-  </si>
-  <si>
-    <t>Plan backups and disaster recovery</t>
-  </si>
-  <si>
-    <t>No backup strategy exists for the database or uploaded files.</t>
-  </si>
-  <si>
-    <t>Relevant once there is a real database.</t>
-  </si>
-  <si>
-    <t>LG-04</t>
-  </si>
-  <si>
-    <t>Approve the About / Contact / Order Support copy</t>
-  </si>
-  <si>
-    <t>All placeholder text.</t>
-  </si>
-  <si>
-    <t>Pages carry a visible placeholder notice.</t>
-  </si>
-  <si>
-    <t>DEC-01</t>
-  </si>
-  <si>
-    <t>Fresh build — the previous site is reference only</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: nothing to do with the previous site. The extraction is mined for data and business rules; its code and behaviour are discarded.</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>Its category tree, product data and bug history were kept. Its markup was not.</t>
-  </si>
-  <si>
-    <t>DEC-02</t>
-  </si>
-  <si>
-    <t>Keep the existing visual brand</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026, correcting an earlier over-broad reading: the storefront must keep the current AussieMed look, not be redesigned.</t>
-  </si>
-  <si>
-    <t>Navy #29387d, red #ea2227 and Gilroy were read from the live site's computed styles. See DA-08 for the missing Gilroy weights.</t>
-  </si>
-  <si>
-    <t>DEC-03</t>
-  </si>
-  <si>
-    <t>Local only until the client approves</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: not to go online until there is a version they are happy with locally.</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. robots noindex is site-wide. Hosting is IN-01.</t>
-  </si>
-  <si>
-    <t>DEC-04</t>
-  </si>
-  <si>
-    <t>External connectors are handled last</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: anything needing a third-party account waits until the end so the build never stalls on credentials.</t>
-  </si>
-  <si>
-    <t>Payment IN-04, SMTP IN-03, OAuth IN-05, hosting IN-01. Built behind seams with local stand-ins.</t>
-  </si>
-  <si>
-    <t>DEC-05</t>
-  </si>
-  <si>
-    <t>Follow Livingstone for B2B catalogue and pricing behaviour</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026 with livingstone.com.au as the reference, and all suggested changes accepted.</t>
-  </si>
-  <si>
-    <t>Produced the pack/UOM model, price breaks on cards, the Ex/Inc VAT toggle, variant axes, spec attributes and per-product tax class.</t>
-  </si>
-  <si>
-    <t>DEC-06</t>
-  </si>
-  <si>
-    <t>Seed the catalogue from two real suppliers for testing</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: list Chemist Warehouse and Livingstone as suppliers with 30 items each, and remove the invented placeholders.</t>
-  </si>
-  <si>
-    <t>60 real products seeded. Both are unaffiliated third parties — DA-17 must close before launch.</t>
-  </si>
-  <si>
-    <t>DEC-07</t>
-  </si>
-  <si>
-    <t>Add product images</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026. Supplier photography was downloaded for local testing.</t>
-  </si>
-  <si>
-    <t>52 of 71 products have an image. Third-party assets — DA-03 must close before launch.</t>
-  </si>
-  <si>
-    <t>DEC-08</t>
-  </si>
-  <si>
-    <t>Four test accounts with a shared placeholder password</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: admin, musawi1989@gmail.com, supplier1 and supplier2, all with 123456. Explicitly described as local testing only, chosen to be memorable, and to be changed before anything real.</t>
-  </si>
-  <si>
-    <t>Implemented as asked. SEC-01 tracks removing them; SEC-03 tracks agreeing a password policy.</t>
-  </si>
-  <si>
-    <t>DEC-09</t>
-  </si>
-  <si>
-    <t>One sign-in door per role</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the business portal is the supplier login, the account login is for buyers, and admin is reached at /admin.</t>
-  </si>
-  <si>
-    <t>Implemented. Signing in at the wrong door names the right one rather than admitting the user.</t>
-  </si>
-  <si>
-    <t>DEC-10</t>
-  </si>
-  <si>
-    <t>Record every generated value and decision in this register</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026 and repeated 15 Aug: everything invented on the client's behalf must be written down rather than left in the code.</t>
-  </si>
-  <si>
-    <t>This register is the record. docs/Things That Need Attention.xlsx is generated from it and npm run register validates it.</t>
-  </si>
-  <si>
-    <t>DEC-11</t>
-  </si>
-  <si>
-    <t>Price breaks are packaging levels, not arbitrary quantities</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: a break at 12 exists because a carton holds 12, and a break at 48 because a box holds 4 cartons. The quantity and the packaging level are the same fact.</t>
-  </si>
-  <si>
-    <t>Each break now carries its level name. Corrects an earlier model that treated breaks as percentage discounts at round numbers.</t>
-  </si>
-  <si>
-    <t>DEC-12</t>
-  </si>
-  <si>
-    <t>Variants are a dropdown across sibling products</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the 375ml and the 60ml stay as separate products, and each carries a dropdown listing the whole family so a buyer can find their part quickly.</t>
-  </si>
-  <si>
-    <t>Replaces the Each/Carton chips on cards. Implemented as navigation between products, not options on one product, because each size has its own SKU, stock and price.</t>
-  </si>
-  <si>
-    <t>DEC-13</t>
-  </si>
-  <si>
-    <t>One sign-in button in the header, with a dropdown per role</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: replace the Business portal and Account links with a single blue Sign in button whose dropdown offers sign in as a buyer and sign in as a supplier.</t>
-  </si>
-  <si>
-    <t>Implemented in src/components/SignInMenu.tsx. Admin is deliberately absent from the dropdown; staff go to /admin directly. Once signed in the button becomes the way back to the user own area.</t>
-  </si>
-  <si>
-    <t>DEC-14</t>
-  </si>
-  <si>
-    <t>The AED label and the Ex/Inc VAT toggle are gone from the header</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: remove the AED text and the VAT options because VAT is to be carried in the displayed price later.</t>
-  </si>
-  <si>
-    <t>VatToggle deleted from the header. includeVat still exists in src/lib/store.tsx defaulting to ex-VAT with no UI control, so prices read ex-VAT everywhere until the pricing change lands. FE-30 tracks that follow up.</t>
-  </si>
-  <si>
-    <t>DEC-15</t>
-  </si>
-  <si>
-    <t>Sign out lives in the header, in the sign in button slot</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the sign out button always sits where the Sign in button would be when signed out.</t>
-  </si>
-  <si>
-    <t>Moved out of the account, admin and business portal pages into src/components/SignInMenu.tsx, so it is reachable from every page rather than only the dashboard. Signed in, the slot shows the account name plus Sign out.</t>
-  </si>
-  <si>
-    <t>DEC-16</t>
-  </si>
-  <si>
-    <t>Empty categories are hidden from navigation, not removed</t>
-  </si>
-  <si>
-    <t>The category tree came from Livingstone and is far wider than the 60 test products fill. Hiding what is empty keeps every menu entry useful; removing them would lose the shape of the intended range, and hard-coding a shorter list would need maintaining by hand.</t>
-  </si>
-  <si>
-    <t>Our decision, 15 Aug 2026, taken while closing FN-11. It is computed rather than configured, so categories reappear on their own as products are filed into them. Direct URLs still work. Say if you would rather the full tree stayed visible.</t>
-  </si>
-  <si>
-    <t>DA-09</t>
-  </si>
-  <si>
-    <t>Explain the disappearing product</t>
-  </si>
-  <si>
-    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
-  </si>
-  <si>
-    <t>Deferred 15 Aug 2026. The product in question was one of the 11 removed under DA-23 and nothing is being migrated from the old platform, so this no longer affects the build. Worth revisiting only if data from the old system is ever imported.</t>
-  </si>
-  <si>
-    <t>DF-01</t>
-  </si>
-  <si>
-    <t>Industry taxonomy</t>
-  </si>
-  <si>
-    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
-  </si>
-  <si>
-    <t>Additive; adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-02</t>
-  </si>
-  <si>
-    <t>Subscribe and Save</t>
-  </si>
-  <si>
-    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
-  </si>
-  <si>
-    <t>Needs the backend.</t>
-  </si>
-  <si>
-    <t>DF-03</t>
-  </si>
-  <si>
-    <t>Frequently bought together</t>
-  </si>
-  <si>
-    <t>Bundle suggestion with a combined total and one action to add all.</t>
-  </si>
-  <si>
-    <t>Adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-04</t>
-  </si>
-  <si>
-    <t>Quick view</t>
-  </si>
-  <si>
-    <t>View a product from the listing without a page load.</t>
-  </si>
-  <si>
-    <t>DF-05</t>
-  </si>
-  <si>
-    <t>Downloadable PDF catalogues</t>
-  </si>
-  <si>
-    <t>Still how a lot of trade buying happens.</t>
-  </si>
-  <si>
-    <t>Needs the actual catalogue files.</t>
-  </si>
-  <si>
-    <t>BE-07</t>
-  </si>
-  <si>
-    <t>Seed the database from the catalogue</t>
-  </si>
-  <si>
-    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
-  </si>
-  <si>
-    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
-  </si>
-  <si>
-    <t>BE-09</t>
-  </si>
-  <si>
-    <t>Point the storefront at the database</t>
-  </si>
-  <si>
-    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
-  </si>
-  <si>
-    <t>query.ts was untouched — it never knew where products came from.</t>
-  </si>
-  <si>
-    <t>BE-11</t>
-  </si>
-  <si>
-    <t>Order pages restricted to their owner</t>
-  </si>
-  <si>
-    <t>An order was readable by anyone who guessed a sequential reference. Now an admin sees any order, the account that placed it sees it, and a guest sees only an order placed from their own cart.</t>
-  </si>
-  <si>
-    <t>A forbidden order returns 404 rather than 403, so the response cannot be used to discover which references exist.</t>
-  </si>
-  <si>
-    <t>BE-25</t>
-  </si>
-  <si>
-    <t>Invalidate the catalogue cache after a seed or an edit</t>
-  </si>
-  <si>
-    <t>The data layer caches the catalogue for the life of the process, so a running server keeps serving whatever it read first. This is not theoretical: on 15 Aug 2026 the dev server was still showing a retired carton SKU as a purchasable unit chip on the product page, hours after the database had deactivated it.</t>
-  </si>
-  <si>
-    <t>Fixed 15 Aug 2026. The cache now carries the catalogVersion stamp it was built from and re-checks it against the database at most once a second; the seed bumps the stamp, and invalidateCatalog() bumps it too so other server processes drop their copy as well. Verified live: a running dev server went from 71 products to 60 without a restart, and the phantom carton chip disappeared.</t>
-  </si>
-  <si>
-    <t>DN-01</t>
-  </si>
-  <si>
-    <t>Currency rendering</t>
-  </si>
-  <si>
-    <t>Was rendering the Arabic symbol and 4 decimals. Now always the English string AED with exactly 2 decimals, enforced by test and by a grep check.</t>
-  </si>
-  <si>
-    <t>Fixed in the initial build.</t>
-  </si>
-  <si>
-    <t>DN-02</t>
-  </si>
-  <si>
-    <t>Integer quantities</t>
-  </si>
-  <si>
-    <t>Quantities were rendering as decimals such as 3.00.</t>
-  </si>
-  <si>
-    <t>DN-03</t>
-  </si>
-  <si>
-    <t>Category filtering</t>
-  </si>
-  <si>
-    <t>Every category link redirected to the full product list. Filtering now works, including rolling a department up to everything beneath it.</t>
-  </si>
-  <si>
-    <t>DN-04</t>
-  </si>
-  <si>
-    <t>Category counts matching results</t>
-  </si>
-  <si>
-    <t>Admin and storefront counts could diverge. Counts are now derived from the same query that lists the products.</t>
-  </si>
-  <si>
-    <t>Asserted in the data checks and the API contract checks.</t>
-  </si>
-  <si>
-    <t>DN-05</t>
-  </si>
-  <si>
-    <t>Category slug collisions</t>
-  </si>
-  <si>
-    <t>Six categories shared a slug with another category, so one was unreachable and the other answered to the wrong name.</t>
-  </si>
-  <si>
-    <t>Found by the API contract check. Slugs are now unique tree-wide and asserted.</t>
-  </si>
-  <si>
-    <t>DN-06</t>
-  </si>
-  <si>
-    <t>Per-supplier invoicing</t>
-  </si>
-  <si>
-    <t>An order spanning N suppliers now produces exactly N invoices under one reference number, with per-invoice VAT summing to the order VAT without drift.</t>
-  </si>
-  <si>
-    <t>Verified end to end in the browser and by test.</t>
-  </si>
-  <si>
-    <t>DN-11</t>
-  </si>
-  <si>
-    <t>Pack and unit of measure model</t>
-  </si>
-  <si>
-    <t>The same line sells by the box and by the carton at different prices. Cart lines are keyed by product and pack so they never merge.</t>
-  </si>
-  <si>
-    <t>Outers are asserted to beat buying their contents separately.</t>
-  </si>
-  <si>
-    <t>DN-14</t>
-  </si>
-  <si>
-    <t>Control characters in generated code</t>
-  </si>
-  <si>
-    <t>Shell escaping wrote literal backspace bytes into regex rules, so every packaging and variant rule silently matched nothing while looking correct in every editor.</t>
-  </si>
-  <si>
-    <t>Found via od. A data check now asserts each variant selection matches an option.</t>
-  </si>
-  <si>
-    <t>DN-16</t>
-  </si>
-  <si>
-    <t>Database schema designed and migrated</t>
-  </si>
-  <si>
-    <t>Thirty tables covering catalogue, packs as SKUs, variants, attributes, documents, batches, orders, per-supplier invoices, quotes, bulk upload and audit.</t>
-  </si>
-  <si>
-    <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
-  </si>
-  <si>
-    <t>DN-17</t>
-  </si>
-  <si>
-    <t>Typecheck was silently passing on a stale cache</t>
-  </si>
-  <si>
-    <t>tsc ran with incremental caching and reported no errors while real type errors existed in the tree. Every earlier typecheck-clean claim was suspect.</t>
-  </si>
-  <si>
-    <t>npm run typecheck now runs with --incremental false. Caught seven genuine errors the moment it was disabled.</t>
-  </si>
-  <si>
-    <t>DN-18</t>
-  </si>
-  <si>
-    <t>Cart moved to the server</t>
-  </si>
-  <si>
-    <t>The cart was localStorage, so the browser held prices. It is now database rows priced entirely on the server; the client cannot tell the server what anything costs.</t>
-  </si>
-  <si>
-    <t>Guest carts are cookie-keyed. The catalogue snapshot endpoint stays until the wishlist and quote cart follow.</t>
-  </si>
-  <si>
-    <t>DN-19</t>
-  </si>
-  <si>
-    <t>Checkout writes real orders</t>
-  </si>
-  <si>
-    <t>One transaction creates the order, one invoice per supplier and every line, or nothing at all. Reference numbers are allocated server-side inside that transaction.</t>
-  </si>
-  <si>
-    <t>Verified in a browser end to end, and by 14 order invariants in npm run db:check.</t>
-  </si>
-  <si>
-    <t>DN-20</t>
-  </si>
-  <si>
-    <t>Four sign-in accounts seeded</t>
-  </si>
-  <si>
-    <t>admin, musawi1989@gmail.com, supplier1 and supplier2, each able to sign in by username or email. Suppliers are attached to their seeded companies.</t>
-  </si>
-  <si>
-    <t>Seeded separately from the catalogue so re-seeding products does not remove accounts.</t>
-  </si>
-  <si>
-    <t>FN-01</t>
-  </si>
-  <si>
-    <t>Checkout does not submit an order</t>
-  </si>
-  <si>
-    <t>Done. Checkout writes a real order in one transaction, with one invoice per supplier and a server-allocated reference number.</t>
-  </si>
-  <si>
-    <t>Payment is still not taken and no email is sent.</t>
-  </si>
-  <si>
-    <t>FN-05</t>
-  </si>
-  <si>
-    <t>Real sign-in replaced the demo flag</t>
-  </si>
-  <si>
-    <t>Sign-in was a localStorage boolean anyone could set. It is now a database-backed session with a scrypt-hashed password.</t>
-  </si>
-  <si>
-    <t>Sessions are rows; signing out deletes the row, so a copied cookie stops working.</t>
-  </si>
-  <si>
-    <t>FN-06</t>
-  </si>
-  <si>
-    <t>Account history is real</t>
-  </si>
-  <si>
-    <t>The account area showed three fabricated orders. It now reads the signed-in user's actual orders, and reorder-first is built from what they have really bought.</t>
-  </si>
-  <si>
-    <t>Says so plainly when there is no history yet, rather than showing an empty grid.</t>
+    <t>Done 16 Aug 2026. AuditLog now records every admin write with the actor, the entity and the values that changed, readable at /admin/audit and filtered per record from each product's page. Entries are never edited or deleted, so the screen has no actions on it. Supplier portal writes join it when BE-21 lands.</t>
   </si>
   <si>
     <t>DA-23</t>
@@ -1698,6 +1770,18 @@
   </si>
   <si>
     <t>Done 15 Aug 2026. Categories carry a product count, and the header menu and the front page tiles show only what has something in it: 8 departments instead of 11, and 23 menu entries instead of 146. Verified by walking all 23 offered categories in a browser — none is empty. Hidden categories still resolve by direct URL and show the normal no-results state, so nothing 404s and the tree fills itself back in as products arrive.</t>
+  </si>
+  <si>
+    <t>SEC-04</t>
+  </si>
+  <si>
+    <t>Admin authorisation is enforced twice, deliberately</t>
+  </si>
+  <si>
+    <t>A server action is a public HTTP endpoint. Hiding a button does not stop anyone posting to it, so the role is checked in the layout for rendering and again in the service layer for every write.</t>
+  </si>
+  <si>
+    <t>Verified 16 Aug 2026 in a browser: signed out, every admin path shows the sign-in door; a signed-in buyer is refused at /admin/products. Re-test this whenever an admin screen is added.</t>
   </si>
   <si>
     <t>BE-26</t>
@@ -2254,7 +2338,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2262,7 +2346,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2278,7 +2362,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2304,7 +2388,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2312,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2320,7 +2404,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2676,7 +2760,7 @@
         <v>37</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>64</v>
@@ -2713,7 +2797,7 @@
         <v>69</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>70</v>
@@ -2721,8 +2805,8 @@
       <c r="D10" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>16</v>
+      <c r="E10" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>37</v>
@@ -2843,7 +2927,7 @@
         <v>89</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>90</v>
@@ -2851,8 +2935,8 @@
       <c r="D15" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>13</v>
+      <c r="E15" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>37</v>
@@ -2875,7 +2959,7 @@
         <v>94</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
@@ -2887,21 +2971,21 @@
         <v>38</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
@@ -2913,7 +2997,7 @@
         <v>38</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2921,7 +3005,7 @@
         <v>99</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>100</v>
@@ -2955,8 +3039,8 @@
       <c r="D19" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>16</v>
+      <c r="E19" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>37</v>
@@ -2973,7 +3057,7 @@
         <v>107</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>108</v>
@@ -3017,21 +3101,21 @@
         <v>38</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>13</v>
@@ -3043,7 +3127,7 @@
         <v>38</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3051,7 +3135,7 @@
         <v>118</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>119</v>
@@ -3077,7 +3161,7 @@
         <v>122</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>123</v>
@@ -3086,36 +3170,36 @@
         <v>124</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>37</v>
+        <v>14</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>125</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>38</v>
@@ -3138,10 +3222,10 @@
         <v>133</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>38</v>
@@ -3164,10 +3248,10 @@
         <v>137</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>38</v>
@@ -3190,10 +3274,10 @@
         <v>141</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>38</v>
@@ -3219,7 +3303,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>38</v>
@@ -3242,10 +3326,10 @@
         <v>149</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>38</v>
@@ -3259,7 +3343,7 @@
         <v>151</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>152</v>
@@ -3267,11 +3351,11 @@
       <c r="D31" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>13</v>
+      <c r="E31" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>38</v>
@@ -3297,7 +3381,7 @@
         <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>38</v>
@@ -3319,11 +3403,11 @@
       <c r="D33" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>16</v>
+      <c r="E33" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>38</v>
@@ -3349,7 +3433,7 @@
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>38</v>
@@ -3371,11 +3455,11 @@
       <c r="D35" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>14</v>
+      <c r="E35" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>38</v>
@@ -3397,11 +3481,11 @@
       <c r="D36" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>16</v>
+      <c r="E36" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>38</v>
@@ -3423,11 +3507,11 @@
       <c r="D37" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>16</v>
+      <c r="E37" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>38</v>
@@ -3453,7 +3537,7 @@
         <v>13</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>38</v>
@@ -3479,7 +3563,7 @@
         <v>13</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>38</v>
@@ -3493,7 +3577,7 @@
         <v>187</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>188</v>
@@ -3505,7 +3589,7 @@
         <v>13</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>38</v>
@@ -3519,7 +3603,7 @@
         <v>191</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>192</v>
@@ -3531,7 +3615,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>38</v>
@@ -3557,7 +3641,7 @@
         <v>13</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>38</v>
@@ -3579,11 +3663,11 @@
       <c r="D43" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="E43" s="7" t="s">
-        <v>13</v>
+      <c r="E43" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>38</v>
@@ -3609,7 +3693,7 @@
         <v>13</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>38</v>
@@ -3631,11 +3715,11 @@
       <c r="D45" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>15</v>
+      <c r="E45" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>38</v>
@@ -3661,7 +3745,7 @@
         <v>13</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>38</v>
@@ -3687,7 +3771,7 @@
         <v>13</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>38</v>
@@ -3709,11 +3793,11 @@
       <c r="D48" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="E48" s="7" t="s">
-        <v>13</v>
+      <c r="E48" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>38</v>
@@ -3739,7 +3823,7 @@
         <v>13</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>38</v>
@@ -3761,11 +3845,11 @@
       <c r="D50" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>16</v>
+      <c r="E50" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>38</v>
@@ -3791,7 +3875,7 @@
         <v>13</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>38</v>
@@ -3805,7 +3889,7 @@
         <v>235</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>236</v>
@@ -3813,11 +3897,11 @@
       <c r="D52" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="E52" s="7" t="s">
-        <v>13</v>
+      <c r="E52" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>38</v>
@@ -3831,7 +3915,7 @@
         <v>239</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>240</v>
@@ -3839,11 +3923,11 @@
       <c r="D53" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="E53" s="7" t="s">
-        <v>13</v>
+      <c r="E53" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>38</v>
@@ -3869,7 +3953,7 @@
         <v>16</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>38</v>
@@ -3891,11 +3975,11 @@
       <c r="D55" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="E55" s="6" t="s">
-        <v>16</v>
+      <c r="E55" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>38</v>
@@ -3909,7 +3993,7 @@
         <v>251</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>252</v>
@@ -3917,11 +4001,11 @@
       <c r="D56" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>16</v>
+      <c r="E56" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>38</v>
@@ -3935,7 +4019,7 @@
         <v>255</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>256</v>
@@ -3943,63 +4027,63 @@
       <c r="D57" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="E57" s="7" t="s">
-        <v>13</v>
+      <c r="E57" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>258</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C58" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D58" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="E58" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C59" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D59" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>16</v>
+      <c r="E59" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>38</v>
@@ -4010,48 +4094,48 @@
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C60" s="6" t="s">
+      <c r="D60" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="E60" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="B61" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C61" s="6" t="s">
+      <c r="D61" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>272</v>
-      </c>
       <c r="E61" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>38</v>
@@ -4062,54 +4146,54 @@
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="B62" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C62" s="6" t="s">
+      <c r="D62" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="E62" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>275</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B63" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C63" s="6" t="s">
+      <c r="D63" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="E63" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H63" s="6" t="s">
         <v>279</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4117,7 +4201,7 @@
         <v>280</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>281</v>
@@ -4125,63 +4209,63 @@
       <c r="D64" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="E64" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>129</v>
+      <c r="E64" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>283</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F65" s="9" t="s">
-        <v>129</v>
+      <c r="F65" s="10" t="s">
+        <v>283</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>14</v>
+        <v>291</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>38</v>
@@ -4195,7 +4279,7 @@
         <v>293</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>294</v>
@@ -4207,7 +4291,7 @@
         <v>13</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>38</v>
@@ -4233,7 +4317,7 @@
         <v>16</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>38</v>
@@ -4255,11 +4339,11 @@
       <c r="D69" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="E69" s="7" t="s">
-        <v>13</v>
+      <c r="E69" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>38</v>
@@ -4285,7 +4369,7 @@
         <v>16</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>38</v>
@@ -4311,7 +4395,7 @@
         <v>16</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>38</v>
@@ -4337,7 +4421,7 @@
         <v>16</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>38</v>
@@ -4363,7 +4447,7 @@
         <v>16</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>38</v>
@@ -4389,7 +4473,7 @@
         <v>13</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>38</v>
@@ -4415,7 +4499,7 @@
         <v>13</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>38</v>
@@ -4441,7 +4525,7 @@
         <v>13</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>38</v>
@@ -4467,7 +4551,7 @@
         <v>16</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>38</v>
@@ -4493,7 +4577,7 @@
         <v>13</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>38</v>
@@ -4519,7 +4603,7 @@
         <v>13</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>38</v>
@@ -4545,7 +4629,7 @@
         <v>16</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>38</v>
@@ -4571,7 +4655,7 @@
         <v>13</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>38</v>
@@ -4597,7 +4681,7 @@
         <v>13</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G82" s="6" t="s">
         <v>38</v>
@@ -4618,7 +4702,7 @@
   <sheetPr>
     <tabColor rgb="FF29387D"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -4673,7 +4757,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>359</v>
@@ -4699,7 +4783,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>359</v>
@@ -4725,7 +4809,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>359</v>
@@ -4751,7 +4835,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>359</v>
@@ -4777,7 +4861,7 @@
         <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>359</v>
@@ -4803,7 +4887,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>359</v>
@@ -4829,7 +4913,7 @@
         <v>13</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>359</v>
@@ -4855,7 +4939,7 @@
         <v>13</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>359</v>
@@ -4881,7 +4965,7 @@
         <v>13</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>359</v>
@@ -4907,7 +4991,7 @@
         <v>13</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>359</v>
@@ -4933,7 +5017,7 @@
         <v>13</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>359</v>
@@ -4959,7 +5043,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>359</v>
@@ -4985,7 +5069,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>359</v>
@@ -5011,7 +5095,7 @@
         <v>13</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>359</v>
@@ -5037,7 +5121,7 @@
         <v>13</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G16" s="11" t="s">
         <v>359</v>
@@ -5063,7 +5147,7 @@
         <v>16</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>359</v>
@@ -5072,8 +5156,86 @@
         <v>420</v>
       </c>
     </row>
+    <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>432</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:H20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5124,126 +5286,126 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
@@ -5254,28 +5416,28 @@
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>
@@ -5290,7 +5452,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -5330,16 +5492,16 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>16</v>
@@ -5351,21 +5513,21 @@
         <v>359</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
@@ -5377,21 +5539,21 @@
         <v>359</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>359</v>
+        <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
@@ -5403,21 +5565,21 @@
         <v>359</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>22</v>
+        <v>359</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
@@ -5429,21 +5591,21 @@
         <v>359</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>359</v>
+        <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
@@ -5455,21 +5617,21 @@
         <v>359</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>359</v>
+        <v>22</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
@@ -5481,21 +5643,21 @@
         <v>359</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>16</v>
@@ -5507,21 +5669,21 @@
         <v>359</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>16</v>
@@ -5533,21 +5695,21 @@
         <v>359</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
@@ -5559,21 +5721,21 @@
         <v>359</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
@@ -5585,21 +5747,21 @@
         <v>359</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>16</v>
@@ -5611,21 +5773,21 @@
         <v>359</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>16</v>
@@ -5637,21 +5799,21 @@
         <v>359</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>16</v>
@@ -5663,21 +5825,21 @@
         <v>359</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
@@ -5689,21 +5851,21 @@
         <v>359</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
@@ -5715,21 +5877,21 @@
         <v>359</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
@@ -5741,21 +5903,21 @@
         <v>359</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
@@ -5767,21 +5929,21 @@
         <v>359</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
@@ -5793,21 +5955,21 @@
         <v>359</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>16</v>
@@ -5819,21 +5981,21 @@
         <v>359</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>359</v>
+        <v>21</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>16</v>
@@ -5845,375 +6007,479 @@
         <v>359</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>19</v>
+        <v>359</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>129</v>
+        <v>536</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>129</v>
+      <c r="F23" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>359</v>
+        <v>22</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>359</v>
+        <v>19</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>536</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>16</v>
+        <v>548</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>436</v>
+        <v>549</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>540</v>
+        <v>553</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>548</v>
+        <v>448</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>359</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G31" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>22</v>
+        <v>359</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="10" t="s">
-        <v>291</v>
+      <c r="F32" s="9" t="s">
+        <v>125</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>19</v>
+        <v>359</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>567</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>291</v>
+        <v>579</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>125</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>291</v>
+        <v>583</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>125</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="B35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>574</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>576</v>
+      <c r="C37" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>604</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H35"/>
+  <autoFilter ref="A1:H39"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="622">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -95,6 +95,9 @@
     <t>Decision</t>
   </si>
   <si>
+    <t>Frontend</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
@@ -197,7 +200,7 @@
     <t>Suppliers manage their own products but can never self-approve. Must have a failing-then-passing test.</t>
   </si>
   <si>
-    <t>The dashboard exists at /business-portal and is role-guarded and supplier-scoped. The editing screens behind it do not — BE-21 tracks those. Approval is an admin-only transition enforced in the service layer.</t>
+    <t>The dashboard exists at /business-portal and is role-guarded and supplier-scoped. The editing screens behind it do not â€” BE-21 tracks those. Approval is an admin-only transition enforced in the service layer.</t>
   </si>
   <si>
     <t>BE-21</t>
@@ -209,7 +212,7 @@
     <t>The business portal authenticates and shows a supplier their own products and invoice lines, read-only. Creating and editing products, toggling stock and bulk upload are not built.</t>
   </si>
   <si>
-    <t>A supplier must never be able to approve their own product — the rule to enforce when editing lands.</t>
+    <t>A supplier must never be able to approve their own product â€” the rule to enforce when editing lands.</t>
   </si>
   <si>
     <t>BE-29</t>
@@ -221,7 +224,7 @@
     <t>The admin product screen lists the image files a product references but cannot add or replace one, so the only way to give a product a photograph is to put a file on disk and re-seed. That blocks DA-03 and DA-24 from ever being closed by the client rather than by us.</t>
   </si>
   <si>
-    <t>Found while building the admin screens on 16 Aug 2026. Needs a decision on where uploaded files live once this is hosted — local disk will not survive most deployments, so it is tied to IN-01.</t>
+    <t>Found while building the admin screens on 16 Aug 2026. Needs a decision on where uploaded files live once this is hosted â€” local disk will not survive most deployments, so it is tied to IN-01.</t>
   </si>
   <si>
     <t>DA-01</t>
@@ -323,7 +326,7 @@
     <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
   </si>
   <si>
-    <t>Must be removed deliberately at launch — and only then.</t>
+    <t>Must be removed deliberately at launch â€” and only then.</t>
   </si>
   <si>
     <t>IN-07</t>
@@ -431,7 +434,7 @@
     <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
   </si>
   <si>
-    <t>Affects the schema — decide before the backend.</t>
+    <t>Affects the schema â€” decide before the backend.</t>
   </si>
   <si>
     <t>AC-11</t>
@@ -464,7 +467,7 @@
     <t>Decide whether an order should reserve stock</t>
   </si>
   <si>
-    <t>OUR DECISION: checkout does not decrement or reserve anything, because there are no stock levels — only an in/out flag. Two customers can order the last unit.</t>
+    <t>OUR DECISION: checkout does not decrement or reserve anything, because there are no stock levels â€” only an in/out flag. Two customers can order the last unit.</t>
   </si>
   <si>
     <t>Depends on FN-08. Out-of-stock is re-checked at checkout, so a line that sold out while the form was open is rejected.</t>
@@ -476,7 +479,7 @@
     <t>Build comma-safe .xlsx bulk upload</t>
   </si>
   <si>
-    <t>Parsed natively with exceljs, never by splitting on commas — that is what broke comma-containing category names.</t>
+    <t>Parsed natively with exceljs, never by splitting on commas â€” that is what broke comma-containing category names.</t>
   </si>
   <si>
     <t>Unknown brands must be reported per row, never skipped silently.</t>
@@ -527,7 +530,7 @@
     <t>Carts are keyed by a cookie so a visitor can shop before signing in. The merge on sign-in is specified but cannot be built until auth exists.</t>
   </si>
   <si>
-    <t>Cart cookie: aussiemed_cart, httpOnly, 30 day lifetime — OUR INVENTED VALUES.</t>
+    <t>Cart cookie: aussiemed_cart, httpOnly, 30 day lifetime â€” OUR INVENTED VALUES.</t>
   </si>
   <si>
     <t>BE-14</t>
@@ -536,7 +539,7 @@
     <t>Confirm the default order and invoice status</t>
   </si>
   <si>
-    <t>OUR DECISION: new orders are Pending and each supplier invoice is Pending. The real workflow — who moves an order to Processing, and when an invoice becomes Issued — is not defined.</t>
+    <t>OUR DECISION: new orders are Pending and each supplier invoice is Pending. The real workflow â€” who moves an order to Processing, and when an invoice becomes Issued â€” is not defined.</t>
   </si>
   <si>
     <t>Order statuses available: Pending, Processing, Dispatched, Delivered, Cancelled.</t>
@@ -563,7 +566,7 @@
     <t>OUR DECISION: an order can be placed without signing in, and is then tied to the cart cookie. Signing in simply attaches the order to the account.</t>
   </si>
   <si>
-    <t>If trade accounts should be required to order, this must change — it also affects credit terms and pricing.</t>
+    <t>If trade accounts should be required to order, this must change â€” it also affects credit terms and pricing.</t>
   </si>
   <si>
     <t>BE-22</t>
@@ -608,7 +611,7 @@
     <t>Supply the hero banner image</t>
   </si>
   <si>
-    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured — only Brand, Category, Product and WebHtml folders were mirrored.</t>
+    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured â€” only Brand, Category, Product and WebHtml folders were mirrored.</t>
   </si>
   <si>
     <t>A genuine AussieMed CMS image stands in.</t>
@@ -635,7 +638,7 @@
     <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
   </si>
   <si>
-    <t>Largely superseded by DA-20: packaging moved from separate carton SKUs into named price breaks on 15 Aug 2026, so the invented figures now live in scripts/variants.mjs rather than in outer packs. Kept open because the underlying question — what is a real carton and box for each line — is unanswered either way.</t>
+    <t>Largely superseded by DA-20: packaging moved from separate carton SKUs into named price breaks on 15 Aug 2026, so the invented figures now live in scripts/variants.mjs rather than in outer packs. Kept open because the underlying question â€” what is a real carton and box for each line â€” is unanswered either way.</t>
   </si>
   <si>
     <t>DA-11</t>
@@ -707,7 +710,7 @@
     <t>Products are grouped into families by stripping sizes and volumes from their names. It found 2 families in the seeded catalogue. A real catalogue will group differently and some groupings will be wrong.</t>
   </si>
   <si>
-    <t>The admin product screens should let a family be set explicitly rather than inferred — see BE-20.</t>
+    <t>The admin product screens should let a family be set explicitly rather than inferred â€” see BE-20.</t>
   </si>
   <si>
     <t>DA-24</t>
@@ -719,7 +722,7 @@
     <t>Those products render as a monogram tile rather than a photograph. It is a deliberate stand-in and reads acceptably in a grid, but on a trade catalogue an image is often how a buyer confirms they have the right item.</t>
   </si>
   <si>
-    <t>Was 19 of 71. Ten went with the extraction products under DA-23. Four more were added deliberately: their image files turned out to be SVG placeholders saved with a .jpg extension, which the image optimiser rejected with a 400 — see DA-25. The remaining nine have no sourceSku or sourceUrl recorded, so there is nothing to retry a fetch against, and no more third-party photography was sourced because DA-17 already limits what may ship. Subset of DA-03.</t>
+    <t>Was 19 of 71. Ten went with the extraction products under DA-23. Four more were added deliberately: their image files turned out to be SVG placeholders saved with a .jpg extension, which the image optimiser rejected with a 400 â€” see DA-25. The remaining nine have no sourceSku or sourceUrl recorded, so there is nothing to retry a fetch against, and no more third-party photography was sourced because DA-17 already limits what may ship. Subset of DA-03.</t>
   </si>
   <si>
     <t>FE-30</t>
@@ -734,13 +737,25 @@
     <t>Follow up to DEC-14. Decide whether displayed prices become VAT inclusive or the Ex. VAT labels simply stay.</t>
   </si>
   <si>
+    <t>FE-35</t>
+  </si>
+  <si>
+    <t>The first admin page after signing in shows the sign-in door</t>
+  </si>
+  <si>
+    <t>An admin signs in, lands on a page that still shows the sign-in form, and reasonably concludes their password was wrong. A reload fixes it.</t>
+  </si>
+  <si>
+    <t>Found 16 Aug 2026 in a browser walk, reproduced 4 times out of 4. Not an auth or data fault: identical HTTP requests carrying the same session cookie return the signed-in page every time, so the server is correct and this is in the client navigation layer. Most likely the payload prefetched while signed out being reused by the router push in RoleSignInForm.</t>
+  </si>
+  <si>
     <t>FN-07</t>
   </si>
   <si>
     <t>Size and colour switching is not wired</t>
   </si>
   <si>
-    <t>The variant dropdown built on 15 Aug 2026 (DEC-12) switches between sibling products by size or volume, and that works. The separate Size and Colour chips on gloves and the scrub top are a different thing and still do nothing — no sibling SKU exists behind any of them.</t>
+    <t>The variant dropdown built on 15 Aug 2026 (DEC-12) switches between sibling products by size or volume, and that works. The separate Size and Colour chips on gloves and the scrub top are a different thing and still do nothing â€” no sibling SKU exists behind any of them.</t>
   </si>
   <si>
     <t>Re-measured 15 Aug 2026: 13 option axes across 6 products. Every glove carries an identical Size = XS/S/M/L/XL and Colour = Black/Blue/Green with no SKU attached to any value.</t>
@@ -767,7 +782,7 @@
     <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
   </si>
   <si>
-    <t>Schema-shaping — decide before the backend is built.</t>
+    <t>Schema-shaping â€” decide before the backend is built.</t>
   </si>
   <si>
     <t>IN-01</t>
@@ -878,7 +893,7 @@
     <t>Confirm the default price display</t>
   </si>
   <si>
-    <t>Prices are shown Ex. VAT everywhere, and since 15 Aug 2026 there is no way for a buyer to see an inc-VAT figure at all — the header toggle was removed at the client's request before VAT was folded into the displayed price.</t>
+    <t>Prices are shown Ex. VAT everywhere, and since 15 Aug 2026 there is no way for a buyer to see an inc-VAT figure at all â€” the header toggle was removed at the client's request before VAT was folded into the displayed price.</t>
   </si>
   <si>
     <t>See DEC-14 for the decision and FE-30 for the gap it leaves open.</t>
@@ -953,7 +968,7 @@
     <t>OUR DECISION: a supplier's products and invoice lines are fetched through their supplier id, so another supplier's rows are never loaded rather than loaded and hidden.</t>
   </si>
   <si>
-    <t>Keep this rule as the supplier portal grows — filtering after fetching is how leaks happen.</t>
+    <t>Keep this rule as the supplier portal grows â€” filtering after fetching is how leaks happen.</t>
   </si>
   <si>
     <t>BE-27</t>
@@ -1088,7 +1103,7 @@
     <t>DEC-01</t>
   </si>
   <si>
-    <t>Fresh build — the previous site is reference only</t>
+    <t>Fresh build â€” the previous site is reference only</t>
   </si>
   <si>
     <t>Stated 14 Aug 2026: nothing to do with the previous site. The extraction is mined for data and business rules; its code and behaviour are discarded.</t>
@@ -1157,7 +1172,7 @@
     <t>Stated 14 Aug 2026: list Chemist Warehouse and Livingstone as suppliers with 30 items each, and remove the invented placeholders.</t>
   </si>
   <si>
-    <t>60 real products seeded. Both are unaffiliated third parties — DA-17 must close before launch.</t>
+    <t>60 real products seeded. Both are unaffiliated third parties â€” DA-17 must close before launch.</t>
   </si>
   <si>
     <t>DEC-07</t>
@@ -1169,7 +1184,7 @@
     <t>Stated 15 Aug 2026. Supplier photography was downloaded for local testing.</t>
   </si>
   <si>
-    <t>52 of 71 products have an image. Third-party assets — DA-03 must close before launch.</t>
+    <t>52 of 71 products have an image. Third-party assets â€” DA-03 must close before launch.</t>
   </si>
   <si>
     <t>DEC-08</t>
@@ -1313,7 +1328,19 @@
     <t>Both are closed documents the customer already holds. A status that contradicts what they received is worse than no status at all.</t>
   </si>
   <si>
-    <t>Our decision, 16 Aug 2026. A delivered order needs a return and a cancelled one needs a new order — neither of which exists yet. Confirm this matches how you actually work.</t>
+    <t>Our decision, 16 Aug 2026. A delivered order needs a return and a cancelled one needs a new order â€” neither of which exists yet. Confirm this matches how you actually work.</t>
+  </si>
+  <si>
+    <t>DEC-20</t>
+  </si>
+  <si>
+    <t>The back office looks like the reference operations UI, not like the shop</t>
+  </si>
+  <si>
+    <t>The client supplied screenshots of the tool they use day to day. Staff processing orders are doing operational work, and the storefront chrome was both a distraction and the reason documents printed badly.</t>
+  </si>
+  <si>
+    <t>Agreed 16 Aug 2026. Admin and the supplier portal both use the operations shell; the light sidebar follows the reference rather than the AussieMed navy, chosen so the data on screen is what stands out. The supplier rail lists only the one screen that exists, because an entry leading to an unbuilt page is worse than no entry â€” the rest is BE-21.</t>
   </si>
   <si>
     <t>DA-09</t>
@@ -1394,7 +1421,7 @@
     <t>Products, categories, suppliers, customers, orders, marketing, reports, settings.</t>
   </si>
   <si>
-    <t>Done 16 Aug 2026 by BE-20. Marketing (wishlists, abandoned carts) and reports are not built — BE-27 and BE-28.</t>
+    <t>Done 16 Aug 2026 by BE-20. Marketing (wishlists, abandoned carts) and reports are not built â€” BE-27 and BE-28.</t>
   </si>
   <si>
     <t>BE-07</t>
@@ -1418,7 +1445,7 @@
     <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
   </si>
   <si>
-    <t>query.ts was untouched — it never knew where products came from.</t>
+    <t>query.ts was untouched â€” it never knew where products came from.</t>
   </si>
   <si>
     <t>BE-11</t>
@@ -1442,7 +1469,7 @@
     <t>/admin authenticates and shows live figures, but every management screen is still missing: products, categories, suppliers, customers, orders, bulk upload, marketing, reports, settings.</t>
   </si>
   <si>
-    <t>Built 16 Aug 2026. Dashboard, products (list, filters, edit, SKUs, price breaks, approval), categories, suppliers, orders, customers, settings and an audit trail. Every write goes through src/lib/admin.ts, which checks the role again in the service layer, records the change, and bumps the catalogue version so the storefront updates without a restart. Bulk upload is BE-04; product image upload is still missing — see BE-29.</t>
+    <t>Built 16 Aug 2026. Dashboard, products (list, filters, edit, SKUs, price breaks, approval), categories, suppliers, orders, customers, settings and an audit trail. Every write goes through src/lib/admin.ts, which checks the role again in the service layer, records the change, and bumps the catalogue version so the storefront updates without a restart. Bulk upload is BE-04; product image upload is still missing â€” see BE-29.</t>
   </si>
   <si>
     <t>BE-25</t>
@@ -1664,7 +1691,7 @@
     <t>The brief was Chemist Warehouse and Livingstone for testing, with the products that made no sense removed. Northline Uniforms and AussieMed Distribution survived that clean-up and still own 11 of the 71 products between them, so a third of the supplier list and a seventh of the catalogue is left over from the old extraction.</t>
   </si>
   <si>
-    <t>Done 15 Aug 2026. The 11 extraction products and suppliers 20 and 21 are no longer emitted by scripts/build-catalog.mjs. The database keeps them as Inactive rather than deleting them, because 2 invoices and 3 order lines still name them — order history survives. The catalogue is now exactly the 60 test products, 30 from each supplier.</t>
+    <t>Done 15 Aug 2026. The 11 extraction products and suppliers 20 and 21 are no longer emitted by scripts/build-catalog.mjs. The database keeps them as Inactive rather than deleting them, because 2 invoices and 3 order lines still name them â€” order history survives. The catalogue is now exactly the 60 test products, 30 from each supplier.</t>
   </si>
   <si>
     <t>DN-07</t>
@@ -1760,6 +1787,30 @@
     <t>Verified: each role accepted at its own door and rejected with 403 at the other two.</t>
   </si>
   <si>
+    <t>FE-33</t>
+  </si>
+  <si>
+    <t>The back office had the shop wrapped around it</t>
+  </si>
+  <si>
+    <t>Every admin and supplier screen rendered inside the storefront header and footer, so warehouse staff worked around a cart and a Browse All Category bar, and the printed order documents carried both onto the paper.</t>
+  </si>
+  <si>
+    <t>Fixed 16 Aug 2026. The storefront moved into a (shop) route group that owns the header and footer; /admin and /business-portal now use an operations shell with a left sidebar, per the reference UI the client supplied. No URL changed. Verified in a browser: shop chrome absent from every back-office screen, present on the storefront and the 404, and print media shows no navigation on any of the three documents.</t>
+  </si>
+  <si>
+    <t>FE-34</t>
+  </si>
+  <si>
+    <t>The delivery address printed as raw JSON</t>
+  </si>
+  <si>
+    <t>The address is stored as a JSON snapshot so editing an address book entry cannot alter where a historical order was sent. Two screens printed that string verbatim, including the delivery note the customer receives.</t>
+  </si>
+  <si>
+    <t>Fixed 16 Aug 2026. Parsing moved to src/lib/shipping-address.ts and is shared by the admin order screen, the delivery note and the customer order page, so the three cannot drift. A snapshot that fails to parse now degrades to not recorded rather than throwing.</t>
+  </si>
+  <si>
     <t>FN-11</t>
   </si>
   <si>
@@ -1769,7 +1820,7 @@
     <t>112 of the 135 leaf categories contain no products, and Kitchen, Office &amp; Stationery Supplies and Pet Care contain nothing anywhere beneath them. Every one of those is reachable from Browse All Category, so a buyer can click a department on the front page and land on an empty result.</t>
   </si>
   <si>
-    <t>Done 15 Aug 2026. Categories carry a product count, and the header menu and the front page tiles show only what has something in it: 8 departments instead of 11, and 23 menu entries instead of 146. Verified by walking all 23 offered categories in a browser — none is empty. Hidden categories still resolve by direct URL and show the normal no-results state, so nothing 404s and the tree fills itself back in as products arrive.</t>
+    <t>Done 15 Aug 2026. Categories carry a product count, and the header menu and the front page tiles show only what has something in it: 8 departments instead of 11, and 23 menu entries instead of 146. Verified by walking all 23 offered categories in a browser â€” none is empty. Hidden categories still resolve by direct URL and show the normal no-results state, so nothing 404s and the tree fills itself back in as products arrive.</t>
   </si>
   <si>
     <t>SEC-04</t>
@@ -1826,7 +1877,7 @@
     <t>Four product images were SVG placeholders saved as .jpg</t>
   </si>
   <si>
-    <t>Next's image optimiser rejected them with a 400, so those four products showed a broken image — visibly worse than the products with no image at all, which fall back to a monogram tile. The existing check only asked whether the file existed, and it did.</t>
+    <t>Next's image optimiser rejected them with a 400, so those four products showed a broken image â€” visibly worse than the products with no image at all, which fall back to a monogram tile. The existing check only asked whether the file existed, and it did.</t>
   </si>
   <si>
     <t>Fixed 15 Aug 2026: the four files were deleted and their products now fall back to the placeholder. scripts/check-catalog.mjs now sniffs magic bytes rather than trusting the extension, so a file that is not really an image fails the build. Affected the two HiSmile lines, Neutrogena Ultra Sheer and the Roger Armstrong thermometer.</t>
@@ -2305,7 +2356,7 @@
   <sheetPr>
     <tabColor rgb="FF29387D"/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2338,7 +2389,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2346,7 +2397,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2354,7 +2405,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2362,7 +2413,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2396,7 +2447,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2446,7 +2497,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2529,6 +2580,14 @@
       </c>
       <c r="B31" s="3">
         <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2546,7 +2605,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2560,1663 +2619,1663 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>13</v>
+        <v>250</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>16</v>
+        <v>258</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>2</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>13</v>
+        <v>262</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>261</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>2</v>
+        <v>266</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>15</v>
+        <v>269</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>268</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>13</v>
+        <v>272</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>2</v>
+        <v>273</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>16</v>
+        <v>276</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>275</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>13</v>
+        <v>279</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>283</v>
+        <v>13</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>284</v>
@@ -4236,462 +4295,488 @@
         <v>287</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>16</v>
+        <v>292</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>13</v>
+        <v>296</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>16</v>
+        <v>300</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="70" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="71" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="72" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="73" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="74" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>13</v>
+        <v>324</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="75" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="76" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="77" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>16</v>
+        <v>336</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>13</v>
+        <v>340</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>2</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>343</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>16</v>
+        <v>347</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="81" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>13</v>
+        <v>351</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B83" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C82" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>355</v>
+      <c r="C83" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H82"/>
+  <autoFilter ref="A1:H83"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4702,7 +4787,7 @@
   <sheetPr>
     <tabColor rgb="FF29387D"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -4716,526 +4801,552 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>432</v>
+        <v>437</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>441</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H20"/>
+  <autoFilter ref="A1:H21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5260,152 +5371,152 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
@@ -5416,28 +5527,28 @@
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -5452,7 +5563,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -5466,1020 +5577,1072 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F36" s="10" t="s">
-        <v>283</v>
+      <c r="F36" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>595</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>283</v>
+        <v>604</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>596</v>
+        <v>605</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>599</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>13</v>
+        <v>608</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>603</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>16</v>
+        <v>612</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>604</v>
+        <v>613</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>621</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H39"/>
+  <autoFilter ref="A1:H41"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -737,1150 +737,1150 @@
     <t>Follow up to DEC-14. Decide whether displayed prices become VAT inclusive or the Ex. VAT labels simply stay.</t>
   </si>
   <si>
+    <t>FN-07</t>
+  </si>
+  <si>
+    <t>Size and colour switching is not wired</t>
+  </si>
+  <si>
+    <t>The variant dropdown built on 15 Aug 2026 (DEC-12) switches between sibling products by size or volume, and that works. The separate Size and Colour chips on gloves and the scrub top are a different thing and still do nothing â€” no sibling SKU exists behind any of them.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: 13 option axes across 6 products. Every glove carries an identical Size = XS/S/M/L/XL and Colour = Black/Blue/Green with no SKU attached to any value.</t>
+  </si>
+  <si>
+    <t>FN-08</t>
+  </si>
+  <si>
+    <t>Stock is a boolean</t>
+  </si>
+  <si>
+    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
+  </si>
+  <si>
+    <t>Decide whether real stock levels are needed.</t>
+  </si>
+  <si>
+    <t>FN-09</t>
+  </si>
+  <si>
+    <t>Decide on expiry and short-dated stock</t>
+  </si>
+  <si>
+    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
+  </si>
+  <si>
+    <t>Schema-shaping â€” decide before the backend is built.</t>
+  </si>
+  <si>
+    <t>IN-01</t>
+  </si>
+  <si>
+    <t>Choose a hosting target</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. The site runs locally only.</t>
+  </si>
+  <si>
+    <t>Deliberately deferred until the build is approved.</t>
+  </si>
+  <si>
+    <t>IN-02</t>
+  </si>
+  <si>
+    <t>Choose the database</t>
+  </si>
+  <si>
+    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
+  </si>
+  <si>
+    <t>IN-03</t>
+  </si>
+  <si>
+    <t>Choose an SMTP provider and sending domain</t>
+  </si>
+  <si>
+    <t>Required for every transactional email.</t>
+  </si>
+  <si>
+    <t>Must not be the misspelled assuiemed.com domain.</t>
+  </si>
+  <si>
+    <t>IN-04</t>
+  </si>
+  <si>
+    <t>Decide on a payment gateway</t>
+  </si>
+  <si>
+    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
+  </si>
+  <si>
+    <t>LG-05</t>
+  </si>
+  <si>
+    <t>Transfer the theme licence</t>
+  </si>
+  <si>
+    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
+  </si>
+  <si>
+    <t>Repository must stay private because of this.</t>
+  </si>
+  <si>
+    <t>LG-06</t>
+  </si>
+  <si>
+    <t>Supply company registration details</t>
+  </si>
+  <si>
+    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
+  </si>
+  <si>
+    <t>SEC-02</t>
+  </si>
+  <si>
+    <t>Add rate limiting to sign-in</t>
+  </si>
+  <si>
+    <t>Nothing limits password attempts, so the sign-in endpoint can be brute forced. The spec asks for rate limiting on auth in the hardening phase.</t>
+  </si>
+  <si>
+    <t>Matters more with short passwords than with OTP.</t>
+  </si>
+  <si>
+    <t>SEC-03</t>
+  </si>
+  <si>
+    <t>Agree a password policy</t>
+  </si>
+  <si>
+    <t>No minimum length, complexity or reuse rule is enforced. 123456 was accepted because nothing rejects it.</t>
+  </si>
+  <si>
+    <t>Moot if the OTP flow in BE-15 is adopted instead.</t>
+  </si>
+  <si>
+    <t>AC-08</t>
+  </si>
+  <si>
+    <t>Confirm the rounding policy</t>
+  </si>
+  <si>
+    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Verified by test; needs sign-off that the method is acceptable.</t>
+  </si>
+  <si>
+    <t>AC-10</t>
+  </si>
+  <si>
+    <t>Confirm the default price display</t>
+  </si>
+  <si>
+    <t>Prices are shown Ex. VAT everywhere, and since 15 Aug 2026 there is no way for a buyer to see an inc-VAT figure at all â€” the header toggle was removed at the client's request before VAT was folded into the displayed price.</t>
+  </si>
+  <si>
+    <t>See DEC-14 for the decision and FE-30 for the gap it leaves open.</t>
+  </si>
+  <si>
+    <t>BE-13</t>
+  </si>
+  <si>
+    <t>Expire abandoned guest carts</t>
+  </si>
+  <si>
+    <t>Cart rows are never cleaned up. Every visitor who adds an item creates one that lives forever.</t>
+  </si>
+  <si>
+    <t>The spec wants abandoned carts over 24h reportable under Admin &gt; Marketing, so expiry and that report should be designed together.</t>
+  </si>
+  <si>
+    <t>BE-16</t>
+  </si>
+  <si>
+    <t>Confirm the session lifetime</t>
+  </si>
+  <si>
+    <t>OUR INVENTED VALUE: sessions last 7 days, then require signing in again. No idle timeout and no re-authentication for sensitive actions.</t>
+  </si>
+  <si>
+    <t>Cookie is httpOnly and sameSite=lax; secure only in production so local http still works.</t>
+  </si>
+  <si>
+    <t>BE-17</t>
+  </si>
+  <si>
+    <t>Purge expired sessions on a schedule</t>
+  </si>
+  <si>
+    <t>Expired session rows are never deleted. purgeExpiredSessions() exists but nothing calls it.</t>
+  </si>
+  <si>
+    <t>Trivial once any scheduled job exists.</t>
+  </si>
+  <si>
+    <t>BE-18</t>
+  </si>
+  <si>
+    <t>Password hashing uses scrypt, not bcrypt</t>
+  </si>
+  <si>
+    <t>OUR DECISION: scrypt from Node's own crypto module, so there is no dependency to keep patched. The spec names bcrypt. Both are appropriate; only src/lib/auth.ts knows the format.</t>
+  </si>
+  <si>
+    <t>Stored as scrypt$salt$hash so the algorithm is self-describing and can be migrated per user.</t>
+  </si>
+  <si>
+    <t>BE-23</t>
+  </si>
+  <si>
+    <t>Admin figures are counted live, never cached</t>
+  </si>
+  <si>
+    <t>OUR DECISION: every number on the admin dashboard is counted from the database on each request. Caching them is how the old platform let admin counts and storefront counts disagree.</t>
+  </si>
+  <si>
+    <t>Still true after the admin build: every dashboard figure is a live count. Cheap at 60 products and 4 orders; revisit when either grows.</t>
+  </si>
+  <si>
+    <t>BE-24</t>
+  </si>
+  <si>
+    <t>Supplier data is scoped by query, not by filtering</t>
+  </si>
+  <si>
+    <t>OUR DECISION: a supplier's products and invoice lines are fetched through their supplier id, so another supplier's rows are never loaded rather than loaded and hidden.</t>
+  </si>
+  <si>
+    <t>Keep this rule as the supplier portal grows â€” filtering after fetching is how leaks happen.</t>
+  </si>
+  <si>
+    <t>BE-27</t>
+  </si>
+  <si>
+    <t>No marketing screens: wishlists and abandoned carts</t>
+  </si>
+  <si>
+    <t>Both are already recorded in the database and nobody can see either. An abandoned cart is the cheapest sale to recover, and a wishlist says what a buyer wants before they buy it.</t>
+  </si>
+  <si>
+    <t>Split out of BE-02 when the admin screens were built.</t>
+  </si>
+  <si>
+    <t>BE-28</t>
+  </si>
+  <si>
+    <t>No reports: sales by supplier, category or period</t>
+  </si>
+  <si>
+    <t>The dashboard totals every order ever placed and nothing else. There is no way to answer which supplier sells most, what a month looked like, or which categories are dead.</t>
+  </si>
+  <si>
+    <t>Split out of BE-02. Wants AC-09 settled first so periods line up with terms.</t>
+  </si>
+  <si>
+    <t>DA-14</t>
+  </si>
+  <si>
+    <t>Confirm the brand list</t>
+  </si>
+  <si>
+    <t>Brands were assigned by reading product names, because neither source listed a brand field. Bad extractions were caught by hand (Goat, Hello, Roger) but the list has never been checked against reality.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026 after DA-23: 26 brands across the 60 test products.</t>
+  </si>
+  <si>
+    <t>DA-15</t>
+  </si>
+  <si>
+    <t>Decide on duplicate categories</t>
+  </si>
+  <si>
+    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: still 6 duplicated names, 12 categories in total. Slugs are disambiguated by appending the numeric id (oral-care vs oral-care-96). 10 of the 12 hold no products at all, so most of the duplication is invisible to buyers today.</t>
+  </si>
+  <si>
+    <t>DA-16</t>
+  </si>
+  <si>
+    <t>Confirm the missing department</t>
+  </si>
+  <si>
+    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
+  </si>
+  <si>
+    <t>Confirm this is intentional rather than lost.</t>
+  </si>
+  <si>
+    <t>FN-10</t>
+  </si>
+  <si>
+    <t>Search is client-side only</t>
+  </si>
+  <si>
+    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
+  </si>
+  <si>
+    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
+  </si>
+  <si>
+    <t>IN-05</t>
+  </si>
+  <si>
+    <t>Supply Google and Facebook OAuth keys</t>
+  </si>
+  <si>
+    <t>Social login endpoints currently return 501.</t>
+  </si>
+  <si>
+    <t>IN-08</t>
+  </si>
+  <si>
+    <t>Correct the git author name</t>
+  </si>
+  <si>
+    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
+  </si>
+  <si>
+    <t>Fixable with git config user.name and an amend.</t>
+  </si>
+  <si>
+    <t>IN-09</t>
+  </si>
+  <si>
+    <t>Set up continuous integration</t>
+  </si>
+  <si>
+    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
+  </si>
+  <si>
+    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
+  </si>
+  <si>
+    <t>IN-10</t>
+  </si>
+  <si>
+    <t>Plan backups and disaster recovery</t>
+  </si>
+  <si>
+    <t>No backup strategy exists for the database or uploaded files.</t>
+  </si>
+  <si>
+    <t>Relevant once there is a real database.</t>
+  </si>
+  <si>
+    <t>LG-04</t>
+  </si>
+  <si>
+    <t>Approve the About / Contact / Order Support copy</t>
+  </si>
+  <si>
+    <t>All placeholder text.</t>
+  </si>
+  <si>
+    <t>Pages carry a visible placeholder notice.</t>
+  </si>
+  <si>
+    <t>DEC-01</t>
+  </si>
+  <si>
+    <t>Fresh build â€” the previous site is reference only</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: nothing to do with the previous site. The extraction is mined for data and business rules; its code and behaviour are discarded.</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Its category tree, product data and bug history were kept. Its markup was not.</t>
+  </si>
+  <si>
+    <t>DEC-02</t>
+  </si>
+  <si>
+    <t>Keep the existing visual brand</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026, correcting an earlier over-broad reading: the storefront must keep the current AussieMed look, not be redesigned.</t>
+  </si>
+  <si>
+    <t>Navy #29387d, red #ea2227 and Gilroy were read from the live site's computed styles. See DA-08 for the missing Gilroy weights.</t>
+  </si>
+  <si>
+    <t>DEC-03</t>
+  </si>
+  <si>
+    <t>Local only until the client approves</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: not to go online until there is a version they are happy with locally.</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. robots noindex is site-wide. Hosting is IN-01.</t>
+  </si>
+  <si>
+    <t>DEC-04</t>
+  </si>
+  <si>
+    <t>External connectors are handled last</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: anything needing a third-party account waits until the end so the build never stalls on credentials.</t>
+  </si>
+  <si>
+    <t>Payment IN-04, SMTP IN-03, OAuth IN-05, hosting IN-01. Built behind seams with local stand-ins.</t>
+  </si>
+  <si>
+    <t>DEC-05</t>
+  </si>
+  <si>
+    <t>Follow Livingstone for B2B catalogue and pricing behaviour</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026 with livingstone.com.au as the reference, and all suggested changes accepted.</t>
+  </si>
+  <si>
+    <t>Produced the pack/UOM model, price breaks on cards, the Ex/Inc VAT toggle, variant axes, spec attributes and per-product tax class.</t>
+  </si>
+  <si>
+    <t>DEC-06</t>
+  </si>
+  <si>
+    <t>Seed the catalogue from two real suppliers for testing</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: list Chemist Warehouse and Livingstone as suppliers with 30 items each, and remove the invented placeholders.</t>
+  </si>
+  <si>
+    <t>60 real products seeded. Both are unaffiliated third parties â€” DA-17 must close before launch.</t>
+  </si>
+  <si>
+    <t>DEC-07</t>
+  </si>
+  <si>
+    <t>Add product images</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026. Supplier photography was downloaded for local testing.</t>
+  </si>
+  <si>
+    <t>52 of 71 products have an image. Third-party assets â€” DA-03 must close before launch.</t>
+  </si>
+  <si>
+    <t>DEC-08</t>
+  </si>
+  <si>
+    <t>Four test accounts with a shared placeholder password</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: admin, musawi1989@gmail.com, supplier1 and supplier2, all with 123456. Explicitly described as local testing only, chosen to be memorable, and to be changed before anything real.</t>
+  </si>
+  <si>
+    <t>Implemented as asked. SEC-01 tracks removing them; SEC-03 tracks agreeing a password policy.</t>
+  </si>
+  <si>
+    <t>DEC-09</t>
+  </si>
+  <si>
+    <t>One sign-in door per role</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the business portal is the supplier login, the account login is for buyers, and admin is reached at /admin.</t>
+  </si>
+  <si>
+    <t>Implemented. Signing in at the wrong door names the right one rather than admitting the user.</t>
+  </si>
+  <si>
+    <t>DEC-10</t>
+  </si>
+  <si>
+    <t>Record every generated value and decision in this register</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026 and repeated 15 Aug: everything invented on the client's behalf must be written down rather than left in the code.</t>
+  </si>
+  <si>
+    <t>This register is the record. docs/Things That Need Attention.xlsx is generated from it and npm run register validates it.</t>
+  </si>
+  <si>
+    <t>DEC-11</t>
+  </si>
+  <si>
+    <t>Price breaks are packaging levels, not arbitrary quantities</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: a break at 12 exists because a carton holds 12, and a break at 48 because a box holds 4 cartons. The quantity and the packaging level are the same fact.</t>
+  </si>
+  <si>
+    <t>Each break now carries its level name. Corrects an earlier model that treated breaks as percentage discounts at round numbers.</t>
+  </si>
+  <si>
+    <t>DEC-12</t>
+  </si>
+  <si>
+    <t>Variants are a dropdown across sibling products</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the 375ml and the 60ml stay as separate products, and each carries a dropdown listing the whole family so a buyer can find their part quickly.</t>
+  </si>
+  <si>
+    <t>Replaces the Each/Carton chips on cards. Implemented as navigation between products, not options on one product, because each size has its own SKU, stock and price.</t>
+  </si>
+  <si>
+    <t>DEC-13</t>
+  </si>
+  <si>
+    <t>One sign-in button in the header, with a dropdown per role</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: replace the Business portal and Account links with a single blue Sign in button whose dropdown offers sign in as a buyer and sign in as a supplier.</t>
+  </si>
+  <si>
+    <t>Implemented in src/components/SignInMenu.tsx. Admin is deliberately absent from the dropdown; staff go to /admin directly. Once signed in the button becomes the way back to the user own area.</t>
+  </si>
+  <si>
+    <t>DEC-14</t>
+  </si>
+  <si>
+    <t>The AED label and the Ex/Inc VAT toggle are gone from the header</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: remove the AED text and the VAT options because VAT is to be carried in the displayed price later.</t>
+  </si>
+  <si>
+    <t>VatToggle deleted from the header. includeVat still exists in src/lib/store.tsx defaulting to ex-VAT with no UI control, so prices read ex-VAT everywhere until the pricing change lands. FE-30 tracks that follow up.</t>
+  </si>
+  <si>
+    <t>DEC-15</t>
+  </si>
+  <si>
+    <t>Sign out lives in the header, in the sign in button slot</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the sign out button always sits where the Sign in button would be when signed out.</t>
+  </si>
+  <si>
+    <t>Moved out of the account, admin and business portal pages into src/components/SignInMenu.tsx, so it is reachable from every page rather than only the dashboard. Signed in, the slot shows the account name plus Sign out.</t>
+  </si>
+  <si>
+    <t>DEC-16</t>
+  </si>
+  <si>
+    <t>Empty categories are hidden from navigation, not removed</t>
+  </si>
+  <si>
+    <t>The category tree came from Livingstone and is far wider than the 60 test products fill. Hiding what is empty keeps every menu entry useful; removing them would lose the shape of the intended range, and hard-coding a shorter list would need maintaining by hand.</t>
+  </si>
+  <si>
+    <t>Our decision, 15 Aug 2026, taken while closing FN-11. It is computed rather than configured, so categories reappear on their own as products are filed into them. Direct URLs still work. Say if you would rather the full tree stayed visible.</t>
+  </si>
+  <si>
+    <t>DEC-17</t>
+  </si>
+  <si>
+    <t>Renaming a category does not change its URL</t>
+  </si>
+  <si>
+    <t>The slug is the address. A category that has been linked to, bookmarked or indexed keeps working when its display name changes, and changing both would silently break every existing link.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026. Renaming to something genuinely different means creating a category and moving products, or a redirect table we have not built. Say if you would rather the URL followed the name.</t>
+  </si>
+  <si>
+    <t>DEC-18</t>
+  </si>
+  <si>
+    <t>A product cannot go live without a SKU and a category</t>
+  </si>
+  <si>
+    <t>Both make a live product broken rather than merely incomplete: no SKU means nothing to buy, no category means nobody can browse to it. The admin screen refuses the transition and says which one is missing.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026, enforced in src/lib/admin.ts rather than in the form, so posting to the endpoint directly cannot bypass it.</t>
+  </si>
+  <si>
+    <t>DEC-19</t>
+  </si>
+  <si>
+    <t>Delivered and cancelled orders cannot be reopened</t>
+  </si>
+  <si>
+    <t>Both are closed documents the customer already holds. A status that contradicts what they received is worse than no status at all.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026. A delivered order needs a return and a cancelled one needs a new order â€” neither of which exists yet. Confirm this matches how you actually work.</t>
+  </si>
+  <si>
+    <t>DEC-20</t>
+  </si>
+  <si>
+    <t>The back office looks like the reference operations UI, not like the shop</t>
+  </si>
+  <si>
+    <t>The client supplied screenshots of the tool they use day to day. Staff processing orders are doing operational work, and the storefront chrome was both a distraction and the reason documents printed badly.</t>
+  </si>
+  <si>
+    <t>Agreed 16 Aug 2026. Admin and the supplier portal both use the operations shell; the light sidebar follows the reference rather than the AussieMed navy, chosen so the data on screen is what stands out. The supplier rail lists only the one screen that exists, because an entry leading to an unbuilt page is worse than no entry â€” the rest is BE-21.</t>
+  </si>
+  <si>
+    <t>DA-09</t>
+  </si>
+  <si>
+    <t>Explain the disappearing product</t>
+  </si>
+  <si>
+    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
+  </si>
+  <si>
+    <t>Deferred 15 Aug 2026. The product in question was one of the 11 removed under DA-23 and nothing is being migrated from the old platform, so this no longer affects the build. Worth revisiting only if data from the old system is ever imported.</t>
+  </si>
+  <si>
+    <t>DF-01</t>
+  </si>
+  <si>
+    <t>Industry taxonomy</t>
+  </si>
+  <si>
+    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
+  </si>
+  <si>
+    <t>Additive; adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-02</t>
+  </si>
+  <si>
+    <t>Subscribe and Save</t>
+  </si>
+  <si>
+    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
+  </si>
+  <si>
+    <t>Needs the backend.</t>
+  </si>
+  <si>
+    <t>DF-03</t>
+  </si>
+  <si>
+    <t>Frequently bought together</t>
+  </si>
+  <si>
+    <t>Bundle suggestion with a combined total and one action to add all.</t>
+  </si>
+  <si>
+    <t>Adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-04</t>
+  </si>
+  <si>
+    <t>Quick view</t>
+  </si>
+  <si>
+    <t>View a product from the listing without a page load.</t>
+  </si>
+  <si>
+    <t>DF-05</t>
+  </si>
+  <si>
+    <t>Downloadable PDF catalogues</t>
+  </si>
+  <si>
+    <t>Still how a lot of trade buying happens.</t>
+  </si>
+  <si>
+    <t>Needs the actual catalogue files.</t>
+  </si>
+  <si>
+    <t>BE-02</t>
+  </si>
+  <si>
+    <t>Build the admin panel</t>
+  </si>
+  <si>
+    <t>Products, categories, suppliers, customers, orders, marketing, reports, settings.</t>
+  </si>
+  <si>
+    <t>Done 16 Aug 2026 by BE-20. Marketing (wishlists, abandoned carts) and reports are not built â€” BE-27 and BE-28.</t>
+  </si>
+  <si>
+    <t>BE-07</t>
+  </si>
+  <si>
+    <t>Seed the database from the catalogue</t>
+  </si>
+  <si>
+    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
+  </si>
+  <si>
+    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
+  </si>
+  <si>
+    <t>BE-09</t>
+  </si>
+  <si>
+    <t>Point the storefront at the database</t>
+  </si>
+  <si>
+    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
+  </si>
+  <si>
+    <t>query.ts was untouched â€” it never knew where products came from.</t>
+  </si>
+  <si>
+    <t>BE-11</t>
+  </si>
+  <si>
+    <t>Order pages restricted to their owner</t>
+  </si>
+  <si>
+    <t>An order was readable by anyone who guessed a sequential reference. Now an admin sees any order, the account that placed it sees it, and a guest sees only an order placed from their own cart.</t>
+  </si>
+  <si>
+    <t>A forbidden order returns 404 rather than 403, so the response cannot be used to discover which references exist.</t>
+  </si>
+  <si>
+    <t>BE-20</t>
+  </si>
+  <si>
+    <t>Build the admin screens behind the dashboard</t>
+  </si>
+  <si>
+    <t>/admin authenticates and shows live figures, but every management screen is still missing: products, categories, suppliers, customers, orders, bulk upload, marketing, reports, settings.</t>
+  </si>
+  <si>
+    <t>Built 16 Aug 2026. Dashboard, products (list, filters, edit, SKUs, price breaks, approval), categories, suppliers, orders, customers, settings and an audit trail. Every write goes through src/lib/admin.ts, which checks the role again in the service layer, records the change, and bumps the catalogue version so the storefront updates without a restart. Bulk upload is BE-04; product image upload is still missing â€” see BE-29.</t>
+  </si>
+  <si>
+    <t>BE-25</t>
+  </si>
+  <si>
+    <t>Invalidate the catalogue cache after a seed or an edit</t>
+  </si>
+  <si>
+    <t>The data layer caches the catalogue for the life of the process, so a running server keeps serving whatever it read first. This is not theoretical: on 15 Aug 2026 the dev server was still showing a retired carton SKU as a purchasable unit chip on the product page, hours after the database had deactivated it.</t>
+  </si>
+  <si>
+    <t>Fixed 15 Aug 2026. The cache now carries the catalogVersion stamp it was built from and re-checks it against the database at most once a second; the seed bumps the stamp, and invalidateCatalog() bumps it too so other server processes drop their copy as well. Verified live: a running dev server went from 71 products to 60 without a restart, and the phantom carton chip disappeared.</t>
+  </si>
+  <si>
+    <t>DN-01</t>
+  </si>
+  <si>
+    <t>Currency rendering</t>
+  </si>
+  <si>
+    <t>Was rendering the Arabic symbol and 4 decimals. Now always the English string AED with exactly 2 decimals, enforced by test and by a grep check.</t>
+  </si>
+  <si>
+    <t>Fixed in the initial build.</t>
+  </si>
+  <si>
+    <t>DN-02</t>
+  </si>
+  <si>
+    <t>Integer quantities</t>
+  </si>
+  <si>
+    <t>Quantities were rendering as decimals such as 3.00.</t>
+  </si>
+  <si>
+    <t>DN-03</t>
+  </si>
+  <si>
+    <t>Category filtering</t>
+  </si>
+  <si>
+    <t>Every category link redirected to the full product list. Filtering now works, including rolling a department up to everything beneath it.</t>
+  </si>
+  <si>
+    <t>DN-04</t>
+  </si>
+  <si>
+    <t>Category counts matching results</t>
+  </si>
+  <si>
+    <t>Admin and storefront counts could diverge. Counts are now derived from the same query that lists the products.</t>
+  </si>
+  <si>
+    <t>Asserted in the data checks and the API contract checks.</t>
+  </si>
+  <si>
+    <t>DN-05</t>
+  </si>
+  <si>
+    <t>Category slug collisions</t>
+  </si>
+  <si>
+    <t>Six categories shared a slug with another category, so one was unreachable and the other answered to the wrong name.</t>
+  </si>
+  <si>
+    <t>Found by the API contract check. Slugs are now unique tree-wide and asserted.</t>
+  </si>
+  <si>
+    <t>DN-06</t>
+  </si>
+  <si>
+    <t>Per-supplier invoicing</t>
+  </si>
+  <si>
+    <t>An order spanning N suppliers now produces exactly N invoices under one reference number, with per-invoice VAT summing to the order VAT without drift.</t>
+  </si>
+  <si>
+    <t>Verified end to end in the browser and by test.</t>
+  </si>
+  <si>
+    <t>DN-11</t>
+  </si>
+  <si>
+    <t>Pack and unit of measure model</t>
+  </si>
+  <si>
+    <t>The same line sells by the box and by the carton at different prices. Cart lines are keyed by product and pack so they never merge.</t>
+  </si>
+  <si>
+    <t>Outers are asserted to beat buying their contents separately.</t>
+  </si>
+  <si>
+    <t>DN-14</t>
+  </si>
+  <si>
+    <t>Control characters in generated code</t>
+  </si>
+  <si>
+    <t>Shell escaping wrote literal backspace bytes into regex rules, so every packaging and variant rule silently matched nothing while looking correct in every editor.</t>
+  </si>
+  <si>
+    <t>Found via od. A data check now asserts each variant selection matches an option.</t>
+  </si>
+  <si>
+    <t>DN-16</t>
+  </si>
+  <si>
+    <t>Database schema designed and migrated</t>
+  </si>
+  <si>
+    <t>Thirty tables covering catalogue, packs as SKUs, variants, attributes, documents, batches, orders, per-supplier invoices, quotes, bulk upload and audit.</t>
+  </si>
+  <si>
+    <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
+  </si>
+  <si>
+    <t>DN-17</t>
+  </si>
+  <si>
+    <t>Typecheck was silently passing on a stale cache</t>
+  </si>
+  <si>
+    <t>tsc ran with incremental caching and reported no errors while real type errors existed in the tree. Every earlier typecheck-clean claim was suspect.</t>
+  </si>
+  <si>
+    <t>npm run typecheck now runs with --incremental false. Caught seven genuine errors the moment it was disabled.</t>
+  </si>
+  <si>
+    <t>DN-18</t>
+  </si>
+  <si>
+    <t>Cart moved to the server</t>
+  </si>
+  <si>
+    <t>The cart was localStorage, so the browser held prices. It is now database rows priced entirely on the server; the client cannot tell the server what anything costs.</t>
+  </si>
+  <si>
+    <t>Guest carts are cookie-keyed. The catalogue snapshot endpoint stays until the wishlist and quote cart follow.</t>
+  </si>
+  <si>
+    <t>DN-19</t>
+  </si>
+  <si>
+    <t>Checkout writes real orders</t>
+  </si>
+  <si>
+    <t>One transaction creates the order, one invoice per supplier and every line, or nothing at all. Reference numbers are allocated server-side inside that transaction.</t>
+  </si>
+  <si>
+    <t>Verified in a browser end to end, and by 14 order invariants in npm run db:check.</t>
+  </si>
+  <si>
+    <t>DN-20</t>
+  </si>
+  <si>
+    <t>Four sign-in accounts seeded</t>
+  </si>
+  <si>
+    <t>admin, musawi1989@gmail.com, supplier1 and supplier2, each able to sign in by username or email. Suppliers are attached to their seeded companies.</t>
+  </si>
+  <si>
+    <t>Seeded separately from the catalogue so re-seeding products does not remove accounts.</t>
+  </si>
+  <si>
+    <t>FN-01</t>
+  </si>
+  <si>
+    <t>Checkout does not submit an order</t>
+  </si>
+  <si>
+    <t>Done. Checkout writes a real order in one transaction, with one invoice per supplier and a server-allocated reference number.</t>
+  </si>
+  <si>
+    <t>Payment is still not taken and no email is sent.</t>
+  </si>
+  <si>
+    <t>FN-05</t>
+  </si>
+  <si>
+    <t>Real sign-in replaced the demo flag</t>
+  </si>
+  <si>
+    <t>Sign-in was a localStorage boolean anyone could set. It is now a database-backed session with a scrypt-hashed password.</t>
+  </si>
+  <si>
+    <t>Sessions are rows; signing out deletes the row, so a copied cookie stops working.</t>
+  </si>
+  <si>
+    <t>FN-06</t>
+  </si>
+  <si>
+    <t>Account history is real</t>
+  </si>
+  <si>
+    <t>The account area showed three fabricated orders. It now reads the signed-in user's actual orders, and reorder-first is built from what they have really bought.</t>
+  </si>
+  <si>
+    <t>Says so plainly when there is no history yet, rather than showing an empty grid.</t>
+  </si>
+  <si>
+    <t>BE-06</t>
+  </si>
+  <si>
+    <t>Add an audit log</t>
+  </si>
+  <si>
+    <t>Every status transition and every admin or supplier write should be recorded.</t>
+  </si>
+  <si>
+    <t>Done 16 Aug 2026. AuditLog now records every admin write with the actor, the entity and the values that changed, readable at /admin/audit and filtered per record from each product's page. Entries are never edited or deleted, so the screen has no actions on it. Supplier portal writes join it when BE-21 lands.</t>
+  </si>
+  <si>
+    <t>DA-23</t>
+  </si>
+  <si>
+    <t>Two suppliers were asked for; four exist</t>
+  </si>
+  <si>
+    <t>The brief was Chemist Warehouse and Livingstone for testing, with the products that made no sense removed. Northline Uniforms and AussieMed Distribution survived that clean-up and still own 11 of the 71 products between them, so a third of the supplier list and a seventh of the catalogue is left over from the old extraction.</t>
+  </si>
+  <si>
+    <t>Done 15 Aug 2026. The 11 extraction products and suppliers 20 and 21 are no longer emitted by scripts/build-catalog.mjs. The database keeps them as Inactive rather than deleting them, because 2 invoices and 3 order lines still name them â€” order history survives. The catalogue is now exactly the 60 test products, 30 from each supplier.</t>
+  </si>
+  <si>
+    <t>DN-07</t>
+  </si>
+  <si>
+    <t>Unique page titles and meta descriptions</t>
+  </si>
+  <si>
+    <t>Every page carried the identical title 'Aussie Med || Home' with an empty description.</t>
+  </si>
+  <si>
+    <t>Built per page and per product.</t>
+  </si>
+  <si>
+    <t>DN-08</t>
+  </si>
+  <si>
+    <t>Broken cart images and unresolved asset paths</t>
+  </si>
+  <si>
+    <t>Cart images had a bare domain with no path; templates contained literal '~/' paths.</t>
+  </si>
+  <si>
+    <t>All image paths are local and asserted.</t>
+  </si>
+  <si>
+    <t>DN-09</t>
+  </si>
+  <si>
+    <t>Volume breaks visible while scanning</t>
+  </si>
+  <si>
+    <t>Only a savings badge was shown. The full break table now appears on every product card using +1/+10/+50 notation.</t>
+  </si>
+  <si>
+    <t>DN-10</t>
+  </si>
+  <si>
+    <t>Ex VAT / Inc VAT toggle</t>
+  </si>
+  <si>
+    <t>Procurement compares ex-tax and the approver reads inc-tax, so the same buyer needs both during one order.</t>
+  </si>
+  <si>
+    <t>Persists per browser.</t>
+  </si>
+  <si>
+    <t>DN-12</t>
+  </si>
+  <si>
+    <t>Adopt the existing brand theme</t>
+  </si>
+  <si>
+    <t>Navy #29387d, red #ea2227 and Gilroy, read from the live site's computed styles rather than eyeballed.</t>
+  </si>
+  <si>
+    <t>Logo, favicon and all 11 category images are the brand own.</t>
+  </si>
+  <si>
+    <t>DN-13</t>
+  </si>
+  <si>
+    <t>Catalogue seeded with real products</t>
+  </si>
+  <si>
+    <t>Sixty real items replaced invented placeholders so the storefront can be judged against products that actually exist.</t>
+  </si>
+  <si>
+    <t>Thirty from each of two public supplier catalogues, spanning 23 categories.</t>
+  </si>
+  <si>
+    <t>DN-15</t>
+  </si>
+  <si>
+    <t>Product images added for testing</t>
+  </si>
+  <si>
+    <t>Fifty-two of 71 products now carry real photography so the layout can be judged with images rather than placeholder tiles.</t>
+  </si>
+  <si>
+    <t>Third-party supplier images in public/products/seed. A data check now asserts every referenced image file exists on disk.</t>
+  </si>
+  <si>
+    <t>DN-21</t>
+  </si>
+  <si>
+    <t>Three sign-in doors, one per role</t>
+  </si>
+  <si>
+    <t>Buyers sign in at the account page, suppliers at the business portal, admins at /admin. Signing in at the wrong door names the right one instead of letting someone into the wrong area.</t>
+  </si>
+  <si>
+    <t>Verified: each role accepted at its own door and rejected with 403 at the other two.</t>
+  </si>
+  <si>
+    <t>FE-33</t>
+  </si>
+  <si>
+    <t>The back office had the shop wrapped around it</t>
+  </si>
+  <si>
+    <t>Every admin and supplier screen rendered inside the storefront header and footer, so warehouse staff worked around a cart and a Browse All Category bar, and the printed order documents carried both onto the paper.</t>
+  </si>
+  <si>
+    <t>Fixed 16 Aug 2026. The storefront moved into a (shop) route group that owns the header and footer; /admin and /business-portal now use an operations shell with a left sidebar, per the reference UI the client supplied. No URL changed. Verified in a browser: shop chrome absent from every back-office screen, present on the storefront and the 404, and print media shows no navigation on any of the three documents.</t>
+  </si>
+  <si>
+    <t>FE-34</t>
+  </si>
+  <si>
+    <t>The delivery address printed as raw JSON</t>
+  </si>
+  <si>
+    <t>The address is stored as a JSON snapshot so editing an address book entry cannot alter where a historical order was sent. Two screens printed that string verbatim, including the delivery note the customer receives.</t>
+  </si>
+  <si>
+    <t>Fixed 16 Aug 2026. Parsing moved to src/lib/shipping-address.ts and is shared by the admin order screen, the delivery note and the customer order page, so the three cannot drift. A snapshot that fails to parse now degrades to not recorded rather than throwing.</t>
+  </si>
+  <si>
+    <t>FN-11</t>
+  </si>
+  <si>
+    <t>Most categories are empty, and three departments are entirely empty</t>
+  </si>
+  <si>
+    <t>112 of the 135 leaf categories contain no products, and Kitchen, Office &amp; Stationery Supplies and Pet Care contain nothing anywhere beneath them. Every one of those is reachable from Browse All Category, so a buyer can click a department on the front page and land on an empty result.</t>
+  </si>
+  <si>
+    <t>Done 15 Aug 2026. Categories carry a product count, and the header menu and the front page tiles show only what has something in it: 8 departments instead of 11, and 23 menu entries instead of 146. Verified by walking all 23 offered categories in a browser â€” none is empty. Hidden categories still resolve by direct URL and show the normal no-results state, so nothing 404s and the tree fills itself back in as products arrive.</t>
+  </si>
+  <si>
+    <t>SEC-04</t>
+  </si>
+  <si>
+    <t>Admin authorisation is enforced twice, deliberately</t>
+  </si>
+  <si>
+    <t>A server action is a public HTTP endpoint. Hiding a button does not stop anyone posting to it, so the role is checked in the layout for rendering and again in the service layer for every write.</t>
+  </si>
+  <si>
+    <t>Verified 16 Aug 2026 in a browser: signed out, every admin path shows the sign-in door; a signed-in buyer is refused at /admin/products. Re-test this whenever an admin screen is added.</t>
+  </si>
+  <si>
+    <t>BE-26</t>
+  </si>
+  <si>
+    <t>Seed now upserts instead of wiping</t>
+  </si>
+  <si>
+    <t>Once orders existed, re-seeding failed on a foreign key: order lines reference SKU rows. The database was correctly refusing to let a re-seed destroy order history.</t>
+  </si>
+  <si>
+    <t>Products, SKUs, categories and brands are matched on natural keys and updated in place. Products absent from the catalogue are deactivated, never deleted.</t>
+  </si>
+  <si>
+    <t>DA-04</t>
+  </si>
+  <si>
+    <t>Wrong image on the scrub top</t>
+  </si>
+  <si>
+    <t>The product's primary image was a stock photo of a pocket watch. Excluded from the build; the file is still in public/products/.</t>
+  </si>
+  <si>
+    <t>Resolved 15 Aug 2026: the scrub top was one of the 11 extraction products removed under DA-23, so the pocket watch image is no longer referenced. The file remains in public/products/ unused.</t>
+  </si>
+  <si>
+    <t>DA-22</t>
+  </si>
+  <si>
+    <t>Supplier 1 is named AussieMed Distribution rather than a real trading name</t>
+  </si>
+  <si>
+    <t>The supplier1 login and its company record are named after the storefront itself, so a supplier signing in sees the AussieMed name in the header where their own company should be. The other seeded supplier is correctly Chemist Warehouse.</t>
+  </si>
+  <si>
+    <t>Resolved 15 Aug 2026 by DA-23: the AussieMed Distribution supplier left the catalogue along with its products, so the name no longer appears anywhere a supplier's own name should.</t>
+  </si>
+  <si>
+    <t>DA-25</t>
+  </si>
+  <si>
+    <t>Four product images were SVG placeholders saved as .jpg</t>
+  </si>
+  <si>
+    <t>Next's image optimiser rejected them with a 400, so those four products showed a broken image â€” visibly worse than the products with no image at all, which fall back to a monogram tile. The existing check only asked whether the file existed, and it did.</t>
+  </si>
+  <si>
+    <t>Fixed 15 Aug 2026: the four files were deleted and their products now fall back to the placeholder. scripts/check-catalog.mjs now sniffs magic bytes rather than trusting the extension, so a file that is not really an image fails the build. Affected the two HiSmile lines, Neutrogena Ultra Sheer and the Roger Armstrong thermometer.</t>
+  </si>
+  <si>
     <t>FE-35</t>
   </si>
   <si>
-    <t>The first admin page after signing in shows the sign-in door</t>
-  </si>
-  <si>
-    <t>An admin signs in, lands on a page that still shows the sign-in form, and reasonably concludes their password was wrong. A reload fixes it.</t>
-  </si>
-  <si>
-    <t>Found 16 Aug 2026 in a browser walk, reproduced 4 times out of 4. Not an auth or data fault: identical HTTP requests carrying the same session cookie return the signed-in page every time, so the server is correct and this is in the client navigation layer. Most likely the payload prefetched while signed out being reused by the router push in RoleSignInForm.</t>
-  </si>
-  <si>
-    <t>FN-07</t>
-  </si>
-  <si>
-    <t>Size and colour switching is not wired</t>
-  </si>
-  <si>
-    <t>The variant dropdown built on 15 Aug 2026 (DEC-12) switches between sibling products by size or volume, and that works. The separate Size and Colour chips on gloves and the scrub top are a different thing and still do nothing â€” no sibling SKU exists behind any of them.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: 13 option axes across 6 products. Every glove carries an identical Size = XS/S/M/L/XL and Colour = Black/Blue/Green with no SKU attached to any value.</t>
-  </si>
-  <si>
-    <t>FN-08</t>
-  </si>
-  <si>
-    <t>Stock is a boolean</t>
-  </si>
-  <si>
-    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
-  </si>
-  <si>
-    <t>Decide whether real stock levels are needed.</t>
-  </si>
-  <si>
-    <t>FN-09</t>
-  </si>
-  <si>
-    <t>Decide on expiry and short-dated stock</t>
-  </si>
-  <si>
-    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
-  </si>
-  <si>
-    <t>Schema-shaping â€” decide before the backend is built.</t>
-  </si>
-  <si>
-    <t>IN-01</t>
-  </si>
-  <si>
-    <t>Choose a hosting target</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. The site runs locally only.</t>
-  </si>
-  <si>
-    <t>Deliberately deferred until the build is approved.</t>
-  </si>
-  <si>
-    <t>IN-02</t>
-  </si>
-  <si>
-    <t>Choose the database</t>
-  </si>
-  <si>
-    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
-  </si>
-  <si>
-    <t>IN-03</t>
-  </si>
-  <si>
-    <t>Choose an SMTP provider and sending domain</t>
-  </si>
-  <si>
-    <t>Required for every transactional email.</t>
-  </si>
-  <si>
-    <t>Must not be the misspelled assuiemed.com domain.</t>
-  </si>
-  <si>
-    <t>IN-04</t>
-  </si>
-  <si>
-    <t>Decide on a payment gateway</t>
-  </si>
-  <si>
-    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
-  </si>
-  <si>
-    <t>LG-05</t>
-  </si>
-  <si>
-    <t>Transfer the theme licence</t>
-  </si>
-  <si>
-    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
-  </si>
-  <si>
-    <t>Repository must stay private because of this.</t>
-  </si>
-  <si>
-    <t>LG-06</t>
-  </si>
-  <si>
-    <t>Supply company registration details</t>
-  </si>
-  <si>
-    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
-  </si>
-  <si>
-    <t>SEC-02</t>
-  </si>
-  <si>
-    <t>Add rate limiting to sign-in</t>
-  </si>
-  <si>
-    <t>Nothing limits password attempts, so the sign-in endpoint can be brute forced. The spec asks for rate limiting on auth in the hardening phase.</t>
-  </si>
-  <si>
-    <t>Matters more with short passwords than with OTP.</t>
-  </si>
-  <si>
-    <t>SEC-03</t>
-  </si>
-  <si>
-    <t>Agree a password policy</t>
-  </si>
-  <si>
-    <t>No minimum length, complexity or reuse rule is enforced. 123456 was accepted because nothing rejects it.</t>
-  </si>
-  <si>
-    <t>Moot if the OTP flow in BE-15 is adopted instead.</t>
-  </si>
-  <si>
-    <t>AC-08</t>
-  </si>
-  <si>
-    <t>Confirm the rounding policy</t>
-  </si>
-  <si>
-    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>Verified by test; needs sign-off that the method is acceptable.</t>
-  </si>
-  <si>
-    <t>AC-10</t>
-  </si>
-  <si>
-    <t>Confirm the default price display</t>
-  </si>
-  <si>
-    <t>Prices are shown Ex. VAT everywhere, and since 15 Aug 2026 there is no way for a buyer to see an inc-VAT figure at all â€” the header toggle was removed at the client's request before VAT was folded into the displayed price.</t>
-  </si>
-  <si>
-    <t>See DEC-14 for the decision and FE-30 for the gap it leaves open.</t>
-  </si>
-  <si>
-    <t>BE-13</t>
-  </si>
-  <si>
-    <t>Expire abandoned guest carts</t>
-  </si>
-  <si>
-    <t>Cart rows are never cleaned up. Every visitor who adds an item creates one that lives forever.</t>
-  </si>
-  <si>
-    <t>The spec wants abandoned carts over 24h reportable under Admin &gt; Marketing, so expiry and that report should be designed together.</t>
-  </si>
-  <si>
-    <t>BE-16</t>
-  </si>
-  <si>
-    <t>Confirm the session lifetime</t>
-  </si>
-  <si>
-    <t>OUR INVENTED VALUE: sessions last 7 days, then require signing in again. No idle timeout and no re-authentication for sensitive actions.</t>
-  </si>
-  <si>
-    <t>Cookie is httpOnly and sameSite=lax; secure only in production so local http still works.</t>
-  </si>
-  <si>
-    <t>BE-17</t>
-  </si>
-  <si>
-    <t>Purge expired sessions on a schedule</t>
-  </si>
-  <si>
-    <t>Expired session rows are never deleted. purgeExpiredSessions() exists but nothing calls it.</t>
-  </si>
-  <si>
-    <t>Trivial once any scheduled job exists.</t>
-  </si>
-  <si>
-    <t>BE-18</t>
-  </si>
-  <si>
-    <t>Password hashing uses scrypt, not bcrypt</t>
-  </si>
-  <si>
-    <t>OUR DECISION: scrypt from Node's own crypto module, so there is no dependency to keep patched. The spec names bcrypt. Both are appropriate; only src/lib/auth.ts knows the format.</t>
-  </si>
-  <si>
-    <t>Stored as scrypt$salt$hash so the algorithm is self-describing and can be migrated per user.</t>
-  </si>
-  <si>
-    <t>BE-23</t>
-  </si>
-  <si>
-    <t>Admin figures are counted live, never cached</t>
-  </si>
-  <si>
-    <t>OUR DECISION: every number on the admin dashboard is counted from the database on each request. Caching them is how the old platform let admin counts and storefront counts disagree.</t>
-  </si>
-  <si>
-    <t>Still true after the admin build: every dashboard figure is a live count. Cheap at 60 products and 4 orders; revisit when either grows.</t>
-  </si>
-  <si>
-    <t>BE-24</t>
-  </si>
-  <si>
-    <t>Supplier data is scoped by query, not by filtering</t>
-  </si>
-  <si>
-    <t>OUR DECISION: a supplier's products and invoice lines are fetched through their supplier id, so another supplier's rows are never loaded rather than loaded and hidden.</t>
-  </si>
-  <si>
-    <t>Keep this rule as the supplier portal grows â€” filtering after fetching is how leaks happen.</t>
-  </si>
-  <si>
-    <t>BE-27</t>
-  </si>
-  <si>
-    <t>No marketing screens: wishlists and abandoned carts</t>
-  </si>
-  <si>
-    <t>Both are already recorded in the database and nobody can see either. An abandoned cart is the cheapest sale to recover, and a wishlist says what a buyer wants before they buy it.</t>
-  </si>
-  <si>
-    <t>Split out of BE-02 when the admin screens were built.</t>
-  </si>
-  <si>
-    <t>BE-28</t>
-  </si>
-  <si>
-    <t>No reports: sales by supplier, category or period</t>
-  </si>
-  <si>
-    <t>The dashboard totals every order ever placed and nothing else. There is no way to answer which supplier sells most, what a month looked like, or which categories are dead.</t>
-  </si>
-  <si>
-    <t>Split out of BE-02. Wants AC-09 settled first so periods line up with terms.</t>
-  </si>
-  <si>
-    <t>DA-14</t>
-  </si>
-  <si>
-    <t>Confirm the brand list</t>
-  </si>
-  <si>
-    <t>Brands were assigned by reading product names, because neither source listed a brand field. Bad extractions were caught by hand (Goat, Hello, Roger) but the list has never been checked against reality.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026 after DA-23: 26 brands across the 60 test products.</t>
-  </si>
-  <si>
-    <t>DA-15</t>
-  </si>
-  <si>
-    <t>Decide on duplicate categories</t>
-  </si>
-  <si>
-    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: still 6 duplicated names, 12 categories in total. Slugs are disambiguated by appending the numeric id (oral-care vs oral-care-96). 10 of the 12 hold no products at all, so most of the duplication is invisible to buyers today.</t>
-  </si>
-  <si>
-    <t>DA-16</t>
-  </si>
-  <si>
-    <t>Confirm the missing department</t>
-  </si>
-  <si>
-    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
-  </si>
-  <si>
-    <t>Confirm this is intentional rather than lost.</t>
-  </si>
-  <si>
-    <t>FN-10</t>
-  </si>
-  <si>
-    <t>Search is client-side only</t>
-  </si>
-  <si>
-    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
-  </si>
-  <si>
-    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
-  </si>
-  <si>
-    <t>IN-05</t>
-  </si>
-  <si>
-    <t>Supply Google and Facebook OAuth keys</t>
-  </si>
-  <si>
-    <t>Social login endpoints currently return 501.</t>
-  </si>
-  <si>
-    <t>IN-08</t>
-  </si>
-  <si>
-    <t>Correct the git author name</t>
-  </si>
-  <si>
-    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
-  </si>
-  <si>
-    <t>Fixable with git config user.name and an amend.</t>
-  </si>
-  <si>
-    <t>IN-09</t>
-  </si>
-  <si>
-    <t>Set up continuous integration</t>
-  </si>
-  <si>
-    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
-  </si>
-  <si>
-    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
-  </si>
-  <si>
-    <t>IN-10</t>
-  </si>
-  <si>
-    <t>Plan backups and disaster recovery</t>
-  </si>
-  <si>
-    <t>No backup strategy exists for the database or uploaded files.</t>
-  </si>
-  <si>
-    <t>Relevant once there is a real database.</t>
-  </si>
-  <si>
-    <t>LG-04</t>
-  </si>
-  <si>
-    <t>Approve the About / Contact / Order Support copy</t>
-  </si>
-  <si>
-    <t>All placeholder text.</t>
-  </si>
-  <si>
-    <t>Pages carry a visible placeholder notice.</t>
-  </si>
-  <si>
-    <t>DEC-01</t>
-  </si>
-  <si>
-    <t>Fresh build â€” the previous site is reference only</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: nothing to do with the previous site. The extraction is mined for data and business rules; its code and behaviour are discarded.</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>Its category tree, product data and bug history were kept. Its markup was not.</t>
-  </si>
-  <si>
-    <t>DEC-02</t>
-  </si>
-  <si>
-    <t>Keep the existing visual brand</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026, correcting an earlier over-broad reading: the storefront must keep the current AussieMed look, not be redesigned.</t>
-  </si>
-  <si>
-    <t>Navy #29387d, red #ea2227 and Gilroy were read from the live site's computed styles. See DA-08 for the missing Gilroy weights.</t>
-  </si>
-  <si>
-    <t>DEC-03</t>
-  </si>
-  <si>
-    <t>Local only until the client approves</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: not to go online until there is a version they are happy with locally.</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. robots noindex is site-wide. Hosting is IN-01.</t>
-  </si>
-  <si>
-    <t>DEC-04</t>
-  </si>
-  <si>
-    <t>External connectors are handled last</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: anything needing a third-party account waits until the end so the build never stalls on credentials.</t>
-  </si>
-  <si>
-    <t>Payment IN-04, SMTP IN-03, OAuth IN-05, hosting IN-01. Built behind seams with local stand-ins.</t>
-  </si>
-  <si>
-    <t>DEC-05</t>
-  </si>
-  <si>
-    <t>Follow Livingstone for B2B catalogue and pricing behaviour</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026 with livingstone.com.au as the reference, and all suggested changes accepted.</t>
-  </si>
-  <si>
-    <t>Produced the pack/UOM model, price breaks on cards, the Ex/Inc VAT toggle, variant axes, spec attributes and per-product tax class.</t>
-  </si>
-  <si>
-    <t>DEC-06</t>
-  </si>
-  <si>
-    <t>Seed the catalogue from two real suppliers for testing</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: list Chemist Warehouse and Livingstone as suppliers with 30 items each, and remove the invented placeholders.</t>
-  </si>
-  <si>
-    <t>60 real products seeded. Both are unaffiliated third parties â€” DA-17 must close before launch.</t>
-  </si>
-  <si>
-    <t>DEC-07</t>
-  </si>
-  <si>
-    <t>Add product images</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026. Supplier photography was downloaded for local testing.</t>
-  </si>
-  <si>
-    <t>52 of 71 products have an image. Third-party assets â€” DA-03 must close before launch.</t>
-  </si>
-  <si>
-    <t>DEC-08</t>
-  </si>
-  <si>
-    <t>Four test accounts with a shared placeholder password</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: admin, musawi1989@gmail.com, supplier1 and supplier2, all with 123456. Explicitly described as local testing only, chosen to be memorable, and to be changed before anything real.</t>
-  </si>
-  <si>
-    <t>Implemented as asked. SEC-01 tracks removing them; SEC-03 tracks agreeing a password policy.</t>
-  </si>
-  <si>
-    <t>DEC-09</t>
-  </si>
-  <si>
-    <t>One sign-in door per role</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the business portal is the supplier login, the account login is for buyers, and admin is reached at /admin.</t>
-  </si>
-  <si>
-    <t>Implemented. Signing in at the wrong door names the right one rather than admitting the user.</t>
-  </si>
-  <si>
-    <t>DEC-10</t>
-  </si>
-  <si>
-    <t>Record every generated value and decision in this register</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026 and repeated 15 Aug: everything invented on the client's behalf must be written down rather than left in the code.</t>
-  </si>
-  <si>
-    <t>This register is the record. docs/Things That Need Attention.xlsx is generated from it and npm run register validates it.</t>
-  </si>
-  <si>
-    <t>DEC-11</t>
-  </si>
-  <si>
-    <t>Price breaks are packaging levels, not arbitrary quantities</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: a break at 12 exists because a carton holds 12, and a break at 48 because a box holds 4 cartons. The quantity and the packaging level are the same fact.</t>
-  </si>
-  <si>
-    <t>Each break now carries its level name. Corrects an earlier model that treated breaks as percentage discounts at round numbers.</t>
-  </si>
-  <si>
-    <t>DEC-12</t>
-  </si>
-  <si>
-    <t>Variants are a dropdown across sibling products</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the 375ml and the 60ml stay as separate products, and each carries a dropdown listing the whole family so a buyer can find their part quickly.</t>
-  </si>
-  <si>
-    <t>Replaces the Each/Carton chips on cards. Implemented as navigation between products, not options on one product, because each size has its own SKU, stock and price.</t>
-  </si>
-  <si>
-    <t>DEC-13</t>
-  </si>
-  <si>
-    <t>One sign-in button in the header, with a dropdown per role</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: replace the Business portal and Account links with a single blue Sign in button whose dropdown offers sign in as a buyer and sign in as a supplier.</t>
-  </si>
-  <si>
-    <t>Implemented in src/components/SignInMenu.tsx. Admin is deliberately absent from the dropdown; staff go to /admin directly. Once signed in the button becomes the way back to the user own area.</t>
-  </si>
-  <si>
-    <t>DEC-14</t>
-  </si>
-  <si>
-    <t>The AED label and the Ex/Inc VAT toggle are gone from the header</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: remove the AED text and the VAT options because VAT is to be carried in the displayed price later.</t>
-  </si>
-  <si>
-    <t>VatToggle deleted from the header. includeVat still exists in src/lib/store.tsx defaulting to ex-VAT with no UI control, so prices read ex-VAT everywhere until the pricing change lands. FE-30 tracks that follow up.</t>
-  </si>
-  <si>
-    <t>DEC-15</t>
-  </si>
-  <si>
-    <t>Sign out lives in the header, in the sign in button slot</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the sign out button always sits where the Sign in button would be when signed out.</t>
-  </si>
-  <si>
-    <t>Moved out of the account, admin and business portal pages into src/components/SignInMenu.tsx, so it is reachable from every page rather than only the dashboard. Signed in, the slot shows the account name plus Sign out.</t>
-  </si>
-  <si>
-    <t>DEC-16</t>
-  </si>
-  <si>
-    <t>Empty categories are hidden from navigation, not removed</t>
-  </si>
-  <si>
-    <t>The category tree came from Livingstone and is far wider than the 60 test products fill. Hiding what is empty keeps every menu entry useful; removing them would lose the shape of the intended range, and hard-coding a shorter list would need maintaining by hand.</t>
-  </si>
-  <si>
-    <t>Our decision, 15 Aug 2026, taken while closing FN-11. It is computed rather than configured, so categories reappear on their own as products are filed into them. Direct URLs still work. Say if you would rather the full tree stayed visible.</t>
-  </si>
-  <si>
-    <t>DEC-17</t>
-  </si>
-  <si>
-    <t>Renaming a category does not change its URL</t>
-  </si>
-  <si>
-    <t>The slug is the address. A category that has been linked to, bookmarked or indexed keeps working when its display name changes, and changing both would silently break every existing link.</t>
-  </si>
-  <si>
-    <t>Our decision, 16 Aug 2026. Renaming to something genuinely different means creating a category and moving products, or a redirect table we have not built. Say if you would rather the URL followed the name.</t>
-  </si>
-  <si>
-    <t>DEC-18</t>
-  </si>
-  <si>
-    <t>A product cannot go live without a SKU and a category</t>
-  </si>
-  <si>
-    <t>Both make a live product broken rather than merely incomplete: no SKU means nothing to buy, no category means nobody can browse to it. The admin screen refuses the transition and says which one is missing.</t>
-  </si>
-  <si>
-    <t>Our decision, 16 Aug 2026, enforced in src/lib/admin.ts rather than in the form, so posting to the endpoint directly cannot bypass it.</t>
-  </si>
-  <si>
-    <t>DEC-19</t>
-  </si>
-  <si>
-    <t>Delivered and cancelled orders cannot be reopened</t>
-  </si>
-  <si>
-    <t>Both are closed documents the customer already holds. A status that contradicts what they received is worse than no status at all.</t>
-  </si>
-  <si>
-    <t>Our decision, 16 Aug 2026. A delivered order needs a return and a cancelled one needs a new order â€” neither of which exists yet. Confirm this matches how you actually work.</t>
-  </si>
-  <si>
-    <t>DEC-20</t>
-  </si>
-  <si>
-    <t>The back office looks like the reference operations UI, not like the shop</t>
-  </si>
-  <si>
-    <t>The client supplied screenshots of the tool they use day to day. Staff processing orders are doing operational work, and the storefront chrome was both a distraction and the reason documents printed badly.</t>
-  </si>
-  <si>
-    <t>Agreed 16 Aug 2026. Admin and the supplier portal both use the operations shell; the light sidebar follows the reference rather than the AussieMed navy, chosen so the data on screen is what stands out. The supplier rail lists only the one screen that exists, because an entry leading to an unbuilt page is worse than no entry â€” the rest is BE-21.</t>
-  </si>
-  <si>
-    <t>DA-09</t>
-  </si>
-  <si>
-    <t>Explain the disappearing product</t>
-  </si>
-  <si>
-    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
-  </si>
-  <si>
-    <t>Deferred 15 Aug 2026. The product in question was one of the 11 removed under DA-23 and nothing is being migrated from the old platform, so this no longer affects the build. Worth revisiting only if data from the old system is ever imported.</t>
-  </si>
-  <si>
-    <t>DF-01</t>
-  </si>
-  <si>
-    <t>Industry taxonomy</t>
-  </si>
-  <si>
-    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
-  </si>
-  <si>
-    <t>Additive; adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-02</t>
-  </si>
-  <si>
-    <t>Subscribe and Save</t>
-  </si>
-  <si>
-    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
-  </si>
-  <si>
-    <t>Needs the backend.</t>
-  </si>
-  <si>
-    <t>DF-03</t>
-  </si>
-  <si>
-    <t>Frequently bought together</t>
-  </si>
-  <si>
-    <t>Bundle suggestion with a combined total and one action to add all.</t>
-  </si>
-  <si>
-    <t>Adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-04</t>
-  </si>
-  <si>
-    <t>Quick view</t>
-  </si>
-  <si>
-    <t>View a product from the listing without a page load.</t>
-  </si>
-  <si>
-    <t>DF-05</t>
-  </si>
-  <si>
-    <t>Downloadable PDF catalogues</t>
-  </si>
-  <si>
-    <t>Still how a lot of trade buying happens.</t>
-  </si>
-  <si>
-    <t>Needs the actual catalogue files.</t>
-  </si>
-  <si>
-    <t>BE-02</t>
-  </si>
-  <si>
-    <t>Build the admin panel</t>
-  </si>
-  <si>
-    <t>Products, categories, suppliers, customers, orders, marketing, reports, settings.</t>
-  </si>
-  <si>
-    <t>Done 16 Aug 2026 by BE-20. Marketing (wishlists, abandoned carts) and reports are not built â€” BE-27 and BE-28.</t>
-  </si>
-  <si>
-    <t>BE-07</t>
-  </si>
-  <si>
-    <t>Seed the database from the catalogue</t>
-  </si>
-  <si>
-    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
-  </si>
-  <si>
-    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
-  </si>
-  <si>
-    <t>BE-09</t>
-  </si>
-  <si>
-    <t>Point the storefront at the database</t>
-  </si>
-  <si>
-    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
-  </si>
-  <si>
-    <t>query.ts was untouched â€” it never knew where products came from.</t>
-  </si>
-  <si>
-    <t>BE-11</t>
-  </si>
-  <si>
-    <t>Order pages restricted to their owner</t>
-  </si>
-  <si>
-    <t>An order was readable by anyone who guessed a sequential reference. Now an admin sees any order, the account that placed it sees it, and a guest sees only an order placed from their own cart.</t>
-  </si>
-  <si>
-    <t>A forbidden order returns 404 rather than 403, so the response cannot be used to discover which references exist.</t>
-  </si>
-  <si>
-    <t>BE-20</t>
-  </si>
-  <si>
-    <t>Build the admin screens behind the dashboard</t>
-  </si>
-  <si>
-    <t>/admin authenticates and shows live figures, but every management screen is still missing: products, categories, suppliers, customers, orders, bulk upload, marketing, reports, settings.</t>
-  </si>
-  <si>
-    <t>Built 16 Aug 2026. Dashboard, products (list, filters, edit, SKUs, price breaks, approval), categories, suppliers, orders, customers, settings and an audit trail. Every write goes through src/lib/admin.ts, which checks the role again in the service layer, records the change, and bumps the catalogue version so the storefront updates without a restart. Bulk upload is BE-04; product image upload is still missing â€” see BE-29.</t>
-  </si>
-  <si>
-    <t>BE-25</t>
-  </si>
-  <si>
-    <t>Invalidate the catalogue cache after a seed or an edit</t>
-  </si>
-  <si>
-    <t>The data layer caches the catalogue for the life of the process, so a running server keeps serving whatever it read first. This is not theoretical: on 15 Aug 2026 the dev server was still showing a retired carton SKU as a purchasable unit chip on the product page, hours after the database had deactivated it.</t>
-  </si>
-  <si>
-    <t>Fixed 15 Aug 2026. The cache now carries the catalogVersion stamp it was built from and re-checks it against the database at most once a second; the seed bumps the stamp, and invalidateCatalog() bumps it too so other server processes drop their copy as well. Verified live: a running dev server went from 71 products to 60 without a restart, and the phantom carton chip disappeared.</t>
-  </si>
-  <si>
-    <t>DN-01</t>
-  </si>
-  <si>
-    <t>Currency rendering</t>
-  </si>
-  <si>
-    <t>Was rendering the Arabic symbol and 4 decimals. Now always the English string AED with exactly 2 decimals, enforced by test and by a grep check.</t>
-  </si>
-  <si>
-    <t>Fixed in the initial build.</t>
-  </si>
-  <si>
-    <t>DN-02</t>
-  </si>
-  <si>
-    <t>Integer quantities</t>
-  </si>
-  <si>
-    <t>Quantities were rendering as decimals such as 3.00.</t>
-  </si>
-  <si>
-    <t>DN-03</t>
-  </si>
-  <si>
-    <t>Category filtering</t>
-  </si>
-  <si>
-    <t>Every category link redirected to the full product list. Filtering now works, including rolling a department up to everything beneath it.</t>
-  </si>
-  <si>
-    <t>DN-04</t>
-  </si>
-  <si>
-    <t>Category counts matching results</t>
-  </si>
-  <si>
-    <t>Admin and storefront counts could diverge. Counts are now derived from the same query that lists the products.</t>
-  </si>
-  <si>
-    <t>Asserted in the data checks and the API contract checks.</t>
-  </si>
-  <si>
-    <t>DN-05</t>
-  </si>
-  <si>
-    <t>Category slug collisions</t>
-  </si>
-  <si>
-    <t>Six categories shared a slug with another category, so one was unreachable and the other answered to the wrong name.</t>
-  </si>
-  <si>
-    <t>Found by the API contract check. Slugs are now unique tree-wide and asserted.</t>
-  </si>
-  <si>
-    <t>DN-06</t>
-  </si>
-  <si>
-    <t>Per-supplier invoicing</t>
-  </si>
-  <si>
-    <t>An order spanning N suppliers now produces exactly N invoices under one reference number, with per-invoice VAT summing to the order VAT without drift.</t>
-  </si>
-  <si>
-    <t>Verified end to end in the browser and by test.</t>
-  </si>
-  <si>
-    <t>DN-11</t>
-  </si>
-  <si>
-    <t>Pack and unit of measure model</t>
-  </si>
-  <si>
-    <t>The same line sells by the box and by the carton at different prices. Cart lines are keyed by product and pack so they never merge.</t>
-  </si>
-  <si>
-    <t>Outers are asserted to beat buying their contents separately.</t>
-  </si>
-  <si>
-    <t>DN-14</t>
-  </si>
-  <si>
-    <t>Control characters in generated code</t>
-  </si>
-  <si>
-    <t>Shell escaping wrote literal backspace bytes into regex rules, so every packaging and variant rule silently matched nothing while looking correct in every editor.</t>
-  </si>
-  <si>
-    <t>Found via od. A data check now asserts each variant selection matches an option.</t>
-  </si>
-  <si>
-    <t>DN-16</t>
-  </si>
-  <si>
-    <t>Database schema designed and migrated</t>
-  </si>
-  <si>
-    <t>Thirty tables covering catalogue, packs as SKUs, variants, attributes, documents, batches, orders, per-supplier invoices, quotes, bulk upload and audit.</t>
-  </si>
-  <si>
-    <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
-  </si>
-  <si>
-    <t>DN-17</t>
-  </si>
-  <si>
-    <t>Typecheck was silently passing on a stale cache</t>
-  </si>
-  <si>
-    <t>tsc ran with incremental caching and reported no errors while real type errors existed in the tree. Every earlier typecheck-clean claim was suspect.</t>
-  </si>
-  <si>
-    <t>npm run typecheck now runs with --incremental false. Caught seven genuine errors the moment it was disabled.</t>
-  </si>
-  <si>
-    <t>DN-18</t>
-  </si>
-  <si>
-    <t>Cart moved to the server</t>
-  </si>
-  <si>
-    <t>The cart was localStorage, so the browser held prices. It is now database rows priced entirely on the server; the client cannot tell the server what anything costs.</t>
-  </si>
-  <si>
-    <t>Guest carts are cookie-keyed. The catalogue snapshot endpoint stays until the wishlist and quote cart follow.</t>
-  </si>
-  <si>
-    <t>DN-19</t>
-  </si>
-  <si>
-    <t>Checkout writes real orders</t>
-  </si>
-  <si>
-    <t>One transaction creates the order, one invoice per supplier and every line, or nothing at all. Reference numbers are allocated server-side inside that transaction.</t>
-  </si>
-  <si>
-    <t>Verified in a browser end to end, and by 14 order invariants in npm run db:check.</t>
-  </si>
-  <si>
-    <t>DN-20</t>
-  </si>
-  <si>
-    <t>Four sign-in accounts seeded</t>
-  </si>
-  <si>
-    <t>admin, musawi1989@gmail.com, supplier1 and supplier2, each able to sign in by username or email. Suppliers are attached to their seeded companies.</t>
-  </si>
-  <si>
-    <t>Seeded separately from the catalogue so re-seeding products does not remove accounts.</t>
-  </si>
-  <si>
-    <t>FN-01</t>
-  </si>
-  <si>
-    <t>Checkout does not submit an order</t>
-  </si>
-  <si>
-    <t>Done. Checkout writes a real order in one transaction, with one invoice per supplier and a server-allocated reference number.</t>
-  </si>
-  <si>
-    <t>Payment is still not taken and no email is sent.</t>
-  </si>
-  <si>
-    <t>FN-05</t>
-  </si>
-  <si>
-    <t>Real sign-in replaced the demo flag</t>
-  </si>
-  <si>
-    <t>Sign-in was a localStorage boolean anyone could set. It is now a database-backed session with a scrypt-hashed password.</t>
-  </si>
-  <si>
-    <t>Sessions are rows; signing out deletes the row, so a copied cookie stops working.</t>
-  </si>
-  <si>
-    <t>FN-06</t>
-  </si>
-  <si>
-    <t>Account history is real</t>
-  </si>
-  <si>
-    <t>The account area showed three fabricated orders. It now reads the signed-in user's actual orders, and reorder-first is built from what they have really bought.</t>
-  </si>
-  <si>
-    <t>Says so plainly when there is no history yet, rather than showing an empty grid.</t>
-  </si>
-  <si>
-    <t>BE-06</t>
-  </si>
-  <si>
-    <t>Add an audit log</t>
-  </si>
-  <si>
-    <t>Every status transition and every admin or supplier write should be recorded.</t>
-  </si>
-  <si>
-    <t>Done 16 Aug 2026. AuditLog now records every admin write with the actor, the entity and the values that changed, readable at /admin/audit and filtered per record from each product's page. Entries are never edited or deleted, so the screen has no actions on it. Supplier portal writes join it when BE-21 lands.</t>
-  </si>
-  <si>
-    <t>DA-23</t>
-  </si>
-  <si>
-    <t>Two suppliers were asked for; four exist</t>
-  </si>
-  <si>
-    <t>The brief was Chemist Warehouse and Livingstone for testing, with the products that made no sense removed. Northline Uniforms and AussieMed Distribution survived that clean-up and still own 11 of the 71 products between them, so a third of the supplier list and a seventh of the catalogue is left over from the old extraction.</t>
-  </si>
-  <si>
-    <t>Done 15 Aug 2026. The 11 extraction products and suppliers 20 and 21 are no longer emitted by scripts/build-catalog.mjs. The database keeps them as Inactive rather than deleting them, because 2 invoices and 3 order lines still name them â€” order history survives. The catalogue is now exactly the 60 test products, 30 from each supplier.</t>
-  </si>
-  <si>
-    <t>DN-07</t>
-  </si>
-  <si>
-    <t>Unique page titles and meta descriptions</t>
-  </si>
-  <si>
-    <t>Every page carried the identical title 'Aussie Med || Home' with an empty description.</t>
-  </si>
-  <si>
-    <t>Built per page and per product.</t>
-  </si>
-  <si>
-    <t>DN-08</t>
-  </si>
-  <si>
-    <t>Broken cart images and unresolved asset paths</t>
-  </si>
-  <si>
-    <t>Cart images had a bare domain with no path; templates contained literal '~/' paths.</t>
-  </si>
-  <si>
-    <t>All image paths are local and asserted.</t>
-  </si>
-  <si>
-    <t>DN-09</t>
-  </si>
-  <si>
-    <t>Volume breaks visible while scanning</t>
-  </si>
-  <si>
-    <t>Only a savings badge was shown. The full break table now appears on every product card using +1/+10/+50 notation.</t>
-  </si>
-  <si>
-    <t>DN-10</t>
-  </si>
-  <si>
-    <t>Ex VAT / Inc VAT toggle</t>
-  </si>
-  <si>
-    <t>Procurement compares ex-tax and the approver reads inc-tax, so the same buyer needs both during one order.</t>
-  </si>
-  <si>
-    <t>Persists per browser.</t>
-  </si>
-  <si>
-    <t>DN-12</t>
-  </si>
-  <si>
-    <t>Adopt the existing brand theme</t>
-  </si>
-  <si>
-    <t>Navy #29387d, red #ea2227 and Gilroy, read from the live site's computed styles rather than eyeballed.</t>
-  </si>
-  <si>
-    <t>Logo, favicon and all 11 category images are the brand own.</t>
-  </si>
-  <si>
-    <t>DN-13</t>
-  </si>
-  <si>
-    <t>Catalogue seeded with real products</t>
-  </si>
-  <si>
-    <t>Sixty real items replaced invented placeholders so the storefront can be judged against products that actually exist.</t>
-  </si>
-  <si>
-    <t>Thirty from each of two public supplier catalogues, spanning 23 categories.</t>
-  </si>
-  <si>
-    <t>DN-15</t>
-  </si>
-  <si>
-    <t>Product images added for testing</t>
-  </si>
-  <si>
-    <t>Fifty-two of 71 products now carry real photography so the layout can be judged with images rather than placeholder tiles.</t>
-  </si>
-  <si>
-    <t>Third-party supplier images in public/products/seed. A data check now asserts every referenced image file exists on disk.</t>
-  </si>
-  <si>
-    <t>DN-21</t>
-  </si>
-  <si>
-    <t>Three sign-in doors, one per role</t>
-  </si>
-  <si>
-    <t>Buyers sign in at the account page, suppliers at the business portal, admins at /admin. Signing in at the wrong door names the right one instead of letting someone into the wrong area.</t>
-  </si>
-  <si>
-    <t>Verified: each role accepted at its own door and rejected with 403 at the other two.</t>
-  </si>
-  <si>
-    <t>FE-33</t>
-  </si>
-  <si>
-    <t>The back office had the shop wrapped around it</t>
-  </si>
-  <si>
-    <t>Every admin and supplier screen rendered inside the storefront header and footer, so warehouse staff worked around a cart and a Browse All Category bar, and the printed order documents carried both onto the paper.</t>
-  </si>
-  <si>
-    <t>Fixed 16 Aug 2026. The storefront moved into a (shop) route group that owns the header and footer; /admin and /business-portal now use an operations shell with a left sidebar, per the reference UI the client supplied. No URL changed. Verified in a browser: shop chrome absent from every back-office screen, present on the storefront and the 404, and print media shows no navigation on any of the three documents.</t>
-  </si>
-  <si>
-    <t>FE-34</t>
-  </si>
-  <si>
-    <t>The delivery address printed as raw JSON</t>
-  </si>
-  <si>
-    <t>The address is stored as a JSON snapshot so editing an address book entry cannot alter where a historical order was sent. Two screens printed that string verbatim, including the delivery note the customer receives.</t>
-  </si>
-  <si>
-    <t>Fixed 16 Aug 2026. Parsing moved to src/lib/shipping-address.ts and is shared by the admin order screen, the delivery note and the customer order page, so the three cannot drift. A snapshot that fails to parse now degrades to not recorded rather than throwing.</t>
-  </si>
-  <si>
-    <t>FN-11</t>
-  </si>
-  <si>
-    <t>Most categories are empty, and three departments are entirely empty</t>
-  </si>
-  <si>
-    <t>112 of the 135 leaf categories contain no products, and Kitchen, Office &amp; Stationery Supplies and Pet Care contain nothing anywhere beneath them. Every one of those is reachable from Browse All Category, so a buyer can click a department on the front page and land on an empty result.</t>
-  </si>
-  <si>
-    <t>Done 15 Aug 2026. Categories carry a product count, and the header menu and the front page tiles show only what has something in it: 8 departments instead of 11, and 23 menu entries instead of 146. Verified by walking all 23 offered categories in a browser â€” none is empty. Hidden categories still resolve by direct URL and show the normal no-results state, so nothing 404s and the tree fills itself back in as products arrive.</t>
-  </si>
-  <si>
-    <t>SEC-04</t>
-  </si>
-  <si>
-    <t>Admin authorisation is enforced twice, deliberately</t>
-  </si>
-  <si>
-    <t>A server action is a public HTTP endpoint. Hiding a button does not stop anyone posting to it, so the role is checked in the layout for rendering and again in the service layer for every write.</t>
-  </si>
-  <si>
-    <t>Verified 16 Aug 2026 in a browser: signed out, every admin path shows the sign-in door; a signed-in buyer is refused at /admin/products. Re-test this whenever an admin screen is added.</t>
-  </si>
-  <si>
-    <t>BE-26</t>
-  </si>
-  <si>
-    <t>Seed now upserts instead of wiping</t>
-  </si>
-  <si>
-    <t>Once orders existed, re-seeding failed on a foreign key: order lines reference SKU rows. The database was correctly refusing to let a re-seed destroy order history.</t>
-  </si>
-  <si>
-    <t>Products, SKUs, categories and brands are matched on natural keys and updated in place. Products absent from the catalogue are deactivated, never deleted.</t>
-  </si>
-  <si>
-    <t>DA-04</t>
-  </si>
-  <si>
-    <t>Wrong image on the scrub top</t>
-  </si>
-  <si>
-    <t>The product's primary image was a stock photo of a pocket watch. Excluded from the build; the file is still in public/products/.</t>
-  </si>
-  <si>
-    <t>Resolved 15 Aug 2026: the scrub top was one of the 11 extraction products removed under DA-23, so the pocket watch image is no longer referenced. The file remains in public/products/ unused.</t>
-  </si>
-  <si>
-    <t>DA-22</t>
-  </si>
-  <si>
-    <t>Supplier 1 is named AussieMed Distribution rather than a real trading name</t>
-  </si>
-  <si>
-    <t>The supplier1 login and its company record are named after the storefront itself, so a supplier signing in sees the AussieMed name in the header where their own company should be. The other seeded supplier is correctly Chemist Warehouse.</t>
-  </si>
-  <si>
-    <t>Resolved 15 Aug 2026 by DA-23: the AussieMed Distribution supplier left the catalogue along with its products, so the name no longer appears anywhere a supplier's own name should.</t>
-  </si>
-  <si>
-    <t>DA-25</t>
-  </si>
-  <si>
-    <t>Four product images were SVG placeholders saved as .jpg</t>
-  </si>
-  <si>
-    <t>Next's image optimiser rejected them with a 400, so those four products showed a broken image â€” visibly worse than the products with no image at all, which fall back to a monogram tile. The existing check only asked whether the file existed, and it did.</t>
-  </si>
-  <si>
-    <t>Fixed 15 Aug 2026: the four files were deleted and their products now fall back to the placeholder. scripts/check-catalog.mjs now sniffs magic bytes rather than trusting the extension, so a file that is not really an image fails the build. Affected the two HiSmile lines, Neutrogena Ultra Sheer and the Roger Armstrong thermometer.</t>
+    <t>Withdrawn: the first admin page after signing in was reported as showing the sign-in door</t>
+  </si>
+  <si>
+    <t>Recorded on 16 Aug 2026 as a defect. It was not one — the finding was an artefact of the test that produced it, and the record is kept so nobody investigates it a second time.</t>
+  </si>
+  <si>
+    <t>Withdrawn 16 Aug 2026. The browser test navigated as soon as the sign-in button was clicked, without waiting for the sign-in request to finish, so the session cookie genuinely was not set yet and the door was the correct response. Re-tested twice with one variable changed: waiting for the /api/v1/auth response before navigating gives the signed-in page every time, and not waiting gives the door every time. This also explains why plain HTTP never reproduced it — those requests always carried the cookie. No product change was needed.</t>
   </si>
 </sst>
 </file>
@@ -2405,7 +2405,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2413,7 +2413,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2447,7 +2447,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2497,7 +2497,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2587,7 +2587,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2605,7 +2605,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3974,7 +3974,7 @@
         <v>240</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>241</v>
@@ -4034,8 +4034,8 @@
       <c r="D55" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="E55" s="6" t="s">
-        <v>16</v>
+      <c r="E55" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>126</v>
@@ -4052,7 +4052,7 @@
         <v>252</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>253</v>
@@ -4086,8 +4086,8 @@
       <c r="D57" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="E57" s="7" t="s">
-        <v>13</v>
+      <c r="E57" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>126</v>
@@ -4096,24 +4096,24 @@
         <v>39</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>259</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C58" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D58" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>16</v>
+      <c r="E58" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>126</v>
@@ -4122,7 +4122,7 @@
         <v>39</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>2</v>
+        <v>262</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4148,24 +4148,24 @@
         <v>39</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>266</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C60" s="6" t="s">
+      <c r="D60" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>13</v>
+      <c r="E60" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>126</v>
@@ -4174,7 +4174,7 @@
         <v>39</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>2</v>
+        <v>269</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4190,8 +4190,8 @@
       <c r="D61" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>15</v>
+      <c r="E61" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>126</v>
@@ -4200,24 +4200,24 @@
         <v>39</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>273</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B62" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C62" s="6" t="s">
+      <c r="D62" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>13</v>
+      <c r="E62" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>126</v>
@@ -4226,7 +4226,7 @@
         <v>39</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>2</v>
+        <v>276</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4242,8 +4242,8 @@
       <c r="D63" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E63" s="6" t="s">
-        <v>16</v>
+      <c r="E63" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>126</v>
@@ -4260,7 +4260,7 @@
         <v>281</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>282</v>
@@ -4269,36 +4269,36 @@
         <v>283</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>126</v>
+        <v>14</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>284</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>39</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>39</v>
@@ -4312,7 +4312,7 @@
         <v>290</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>291</v>
@@ -4320,11 +4320,11 @@
       <c r="D66" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="E66" s="7" t="s">
-        <v>13</v>
+      <c r="E66" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>39</v>
@@ -4346,11 +4346,11 @@
       <c r="D67" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>16</v>
+      <c r="E67" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>39</v>
@@ -4372,11 +4372,11 @@
       <c r="D68" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="E68" s="7" t="s">
-        <v>13</v>
+      <c r="E68" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>39</v>
@@ -4402,7 +4402,7 @@
         <v>16</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>39</v>
@@ -4428,7 +4428,7 @@
         <v>16</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>39</v>
@@ -4454,7 +4454,7 @@
         <v>16</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>39</v>
@@ -4480,7 +4480,7 @@
         <v>16</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>39</v>
@@ -4506,7 +4506,7 @@
         <v>16</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>39</v>
@@ -4520,7 +4520,7 @@
         <v>322</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>323</v>
@@ -4528,11 +4528,11 @@
       <c r="D74" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="E74" s="6" t="s">
-        <v>16</v>
+      <c r="E74" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>39</v>
@@ -4558,7 +4558,7 @@
         <v>13</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>39</v>
@@ -4584,7 +4584,7 @@
         <v>13</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>39</v>
@@ -4598,7 +4598,7 @@
         <v>334</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>335</v>
@@ -4606,11 +4606,11 @@
       <c r="D77" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E77" s="7" t="s">
-        <v>13</v>
+      <c r="E77" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>39</v>
@@ -4624,7 +4624,7 @@
         <v>338</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>339</v>
@@ -4632,43 +4632,43 @@
       <c r="D78" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="E78" s="6" t="s">
-        <v>16</v>
+      <c r="E78" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>39</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>341</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C79" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="D79" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="E79" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H79" s="6" t="s">
         <v>344</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4684,11 +4684,11 @@
       <c r="D80" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="E80" s="7" t="s">
-        <v>13</v>
+      <c r="E80" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>39</v>
@@ -4710,11 +4710,11 @@
       <c r="D81" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E81" s="6" t="s">
-        <v>16</v>
+      <c r="E81" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>39</v>
@@ -4728,7 +4728,7 @@
         <v>353</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>354</v>
@@ -4740,7 +4740,7 @@
         <v>13</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G82" s="6" t="s">
         <v>39</v>
@@ -4749,34 +4749,8 @@
         <v>356</v>
       </c>
     </row>
-    <row r="83" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>360</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H83"/>
+  <autoFilter ref="A1:H82"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4827,522 +4801,522 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -5397,126 +5371,126 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
@@ -5527,28 +5501,28 @@
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -5563,7 +5537,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -5603,16 +5577,16 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>16</v>
@@ -5621,24 +5595,24 @@
         <v>38</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
@@ -5647,24 +5621,24 @@
         <v>38</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
@@ -5673,24 +5647,24 @@
         <v>38</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
@@ -5699,24 +5673,24 @@
         <v>38</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
@@ -5725,24 +5699,24 @@
         <v>38</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
@@ -5751,24 +5725,24 @@
         <v>38</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>16</v>
@@ -5777,24 +5751,24 @@
         <v>38</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>16</v>
@@ -5803,24 +5777,24 @@
         <v>38</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
@@ -5829,24 +5803,24 @@
         <v>38</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
@@ -5855,24 +5829,24 @@
         <v>38</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>16</v>
@@ -5881,24 +5855,24 @@
         <v>38</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>16</v>
@@ -5907,24 +5881,24 @@
         <v>38</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>16</v>
@@ -5933,24 +5907,24 @@
         <v>38</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
@@ -5959,24 +5933,24 @@
         <v>38</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
@@ -5985,24 +5959,24 @@
         <v>38</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
@@ -6011,24 +5985,24 @@
         <v>38</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
@@ -6037,24 +6011,24 @@
         <v>38</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
@@ -6063,24 +6037,24 @@
         <v>38</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>16</v>
@@ -6089,24 +6063,24 @@
         <v>38</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>16</v>
@@ -6115,24 +6089,24 @@
         <v>38</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>16</v>
@@ -6141,24 +6115,24 @@
         <v>38</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>16</v>
@@ -6167,24 +6141,24 @@
         <v>38</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>16</v>
@@ -6193,24 +6167,24 @@
         <v>126</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>13</v>
@@ -6219,24 +6193,24 @@
         <v>126</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>16</v>
@@ -6245,24 +6219,24 @@
         <v>126</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>16</v>
@@ -6271,24 +6245,24 @@
         <v>126</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>16</v>
@@ -6297,24 +6271,24 @@
         <v>126</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>16</v>
@@ -6323,24 +6297,24 @@
         <v>126</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>16</v>
@@ -6349,24 +6323,24 @@
         <v>126</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>16</v>
@@ -6375,24 +6349,24 @@
         <v>126</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>16</v>
@@ -6401,24 +6375,24 @@
         <v>126</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>16</v>
@@ -6427,24 +6401,24 @@
         <v>126</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>16</v>
@@ -6453,24 +6427,24 @@
         <v>126</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>16</v>
@@ -6479,24 +6453,24 @@
         <v>126</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>16</v>
@@ -6505,24 +6479,24 @@
         <v>126</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>16</v>
@@ -6531,118 +6505,144 @@
         <v>126</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C41" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D42" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="H41" s="6" t="s">
+      <c r="E42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>621</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H41"/>
+  <autoFilter ref="A1:H42"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="630">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -215,1261 +215,1273 @@
     <t>A supplier must never be able to approve their own product â€” the rule to enforce when editing lands.</t>
   </si>
   <si>
+    <t>DA-01</t>
+  </si>
+  <si>
+    <t>Supply the real product catalogue</t>
+  </si>
+  <si>
+    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
+  </si>
+  <si>
+    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
+  </si>
+  <si>
+    <t>DA-03</t>
+  </si>
+  <si>
+    <t>Supply product photography</t>
+  </si>
+  <si>
+    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
+  </si>
+  <si>
+    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
+  </si>
+  <si>
+    <t>DA-06</t>
+  </si>
+  <si>
+    <t>Supply the real supplier list</t>
+  </si>
+  <si>
+    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
+  </si>
+  <si>
+    <t>All are flagged isPlaceholder in the data.</t>
+  </si>
+  <si>
+    <t>DA-17</t>
+  </si>
+  <si>
+    <t>Replace the test supplier attribution</t>
+  </si>
+  <si>
+    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
+  </si>
+  <si>
+    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
+  </si>
+  <si>
+    <t>DA-20</t>
+  </si>
+  <si>
+    <t>Supply the real packaging quantities</t>
+  </si>
+  <si>
+    <t>OUR INVENTED VALUES: how many units make a carton, and how many cartons make a box, are guessed per product family (12 and 4 by default, 10 and 5 for gloves, 20 and 5 for masks). The break discounts of 4% and 8% are also invented.</t>
+  </si>
+  <si>
+    <t>These are now shown to buyers as CARTON and BOX, so a wrong number reads as a factual claim about your packaging. In scripts/variants.mjs.</t>
+  </si>
+  <si>
+    <t>FN-02</t>
+  </si>
+  <si>
+    <t>Quote requests are not delivered</t>
+  </si>
+  <si>
+    <t>Captured in the browser only.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend and an email provider.</t>
+  </si>
+  <si>
+    <t>FN-03</t>
+  </si>
+  <si>
+    <t>Bulk buy enquiries are not delivered</t>
+  </si>
+  <si>
+    <t>FN-04</t>
+  </si>
+  <si>
+    <t>Notify Me does not register a subscription</t>
+  </si>
+  <si>
+    <t>Captured locally. The restock email flow does not exist.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend.</t>
+  </si>
+  <si>
+    <t>IN-06</t>
+  </si>
+  <si>
+    <t>Remove noindex before launch</t>
+  </si>
+  <si>
+    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
+  </si>
+  <si>
+    <t>Must be removed deliberately at launch â€” and only then.</t>
+  </si>
+  <si>
+    <t>IN-07</t>
+  </si>
+  <si>
+    <t>Confirm the GitHub repository is private</t>
+  </si>
+  <si>
+    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
+  </si>
+  <si>
+    <t>https://github.com/musawi1989/aussiemed</t>
+  </si>
+  <si>
+    <t>LG-01</t>
+  </si>
+  <si>
+    <t>Supply terms and conditions</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
+  </si>
+  <si>
+    <t>Page exists and says so on screen.</t>
+  </si>
+  <si>
+    <t>LG-02</t>
+  </si>
+  <si>
+    <t>Supply the privacy policy</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
+  </si>
+  <si>
+    <t>LG-03</t>
+  </si>
+  <si>
+    <t>Confirm the contact email address</t>
+  </si>
+  <si>
+    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
+  </si>
+  <si>
+    <t>Also determines the sending domain for transactional email.</t>
+  </si>
+  <si>
+    <t>SEC-01</t>
+  </si>
+  <si>
+    <t>Remove the test credentials before any deployment</t>
+  </si>
+  <si>
+    <t>Four accounts share the password 123456: admin, musawi1989@gmail.com, supplier1, supplier2. Fine on a laptop, unacceptable anywhere else.</t>
+  </si>
+  <si>
+    <t>The on-screen credentials panel now renders only outside production, so a production build cannot leak it. The accounts themselves still must be removed or given real passwords.</t>
+  </si>
+  <si>
+    <t>AC-05</t>
+  </si>
+  <si>
+    <t>Confirm the VAT rate and whether it must be configurable</t>
+  </si>
+  <si>
+    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Rate must be stored on the order at the time it is placed.</t>
+  </si>
+  <si>
+    <t>AC-06</t>
+  </si>
+  <si>
+    <t>Approve the reference number format</t>
+  </si>
+  <si>
+    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
+  </si>
+  <si>
+    <t>Wording is fixed as Reference number, never order number.</t>
+  </si>
+  <si>
+    <t>AC-07</t>
+  </si>
+  <si>
+    <t>Approve the supplier invoice numbering</t>
+  </si>
+  <si>
+    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
+  </si>
+  <si>
+    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
+  </si>
+  <si>
+    <t>AC-09</t>
+  </si>
+  <si>
+    <t>Decide payment terms and credit accounts</t>
+  </si>
+  <si>
+    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
+  </si>
+  <si>
+    <t>Affects the schema â€” decide before the backend.</t>
+  </si>
+  <si>
+    <t>AC-11</t>
+  </si>
+  <si>
+    <t>Approve the VAT rounding method on invoices</t>
+  </si>
+  <si>
+    <t>VAT is rounded per line rather than once per invoice, so the printed lines always add up to the printed total. The alternative rounds once and can leave lines that do not sum.</t>
+  </si>
+  <si>
+    <t>Verified by test: per-invoice VAT sums to the order VAT exactly.</t>
+  </si>
+  <si>
+    <t>AC-12</t>
+  </si>
+  <si>
+    <t>Confirm the reference number sequence resets each year</t>
+  </si>
+  <si>
+    <t>OUR DECISION: the sequence restarts at 000001 each calendar year, so AM-2026-000001 and AM-2027-000001 can both exist. If accounting needs a single unbroken sequence this must change before real orders.</t>
+  </si>
+  <si>
+    <t>Held in a settings row keyed orderSequence:YYYY and incremented inside the checkout transaction.</t>
+  </si>
+  <si>
+    <t>AC-13</t>
+  </si>
+  <si>
+    <t>Decide whether an order should reserve stock</t>
+  </si>
+  <si>
+    <t>OUR DECISION: checkout does not decrement or reserve anything, because there are no stock levels â€” only an in/out flag. Two customers can order the last unit.</t>
+  </si>
+  <si>
+    <t>Depends on FN-08. Out-of-stock is re-checked at checkout, so a line that sold out while the form was open is rejected.</t>
+  </si>
+  <si>
+    <t>BE-04</t>
+  </si>
+  <si>
+    <t>Build comma-safe .xlsx bulk upload</t>
+  </si>
+  <si>
+    <t>Parsed natively with exceljs, never by splitting on commas â€” that is what broke comma-containing category names.</t>
+  </si>
+  <si>
+    <t>Unknown brands must be reported per row, never skipped silently.</t>
+  </si>
+  <si>
+    <t>BE-05</t>
+  </si>
+  <si>
+    <t>Build the email flows</t>
+  </si>
+  <si>
+    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
+  </si>
+  <si>
+    <t>Needs an SMTP provider.</t>
+  </si>
+  <si>
+    <t>BE-08</t>
+  </si>
+  <si>
+    <t>Decide money representation before any data lands</t>
+  </si>
+  <si>
+    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
+  </si>
+  <si>
+    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
+  </si>
+  <si>
+    <t>BE-10</t>
+  </si>
+  <si>
+    <t>Retire the catalogue snapshot endpoint</t>
+  </si>
+  <si>
+    <t>Client components fetch the whole catalogue from /api/v1/catalog/snapshot. Fine for 71 products; not for thousands. Goes away when the cart moves server-side.</t>
+  </si>
+  <si>
+    <t>Phase 3 removes the need.</t>
+  </si>
+  <si>
+    <t>BE-12</t>
+  </si>
+  <si>
+    <t>Merge a guest cart into the user cart on sign-in</t>
+  </si>
+  <si>
+    <t>Carts are keyed by a cookie so a visitor can shop before signing in. The merge on sign-in is specified but cannot be built until auth exists.</t>
+  </si>
+  <si>
+    <t>Cart cookie: aussiemed_cart, httpOnly, 30 day lifetime â€” OUR INVENTED VALUES.</t>
+  </si>
+  <si>
+    <t>BE-14</t>
+  </si>
+  <si>
+    <t>Confirm the default order and invoice status</t>
+  </si>
+  <si>
+    <t>OUR DECISION: new orders are Pending and each supplier invoice is Pending. The real workflow â€” who moves an order to Processing, and when an invoice becomes Issued â€” is not defined.</t>
+  </si>
+  <si>
+    <t>Order statuses available: Pending, Processing, Dispatched, Delivered, Cancelled.</t>
+  </si>
+  <si>
+    <t>BE-15</t>
+  </si>
+  <si>
+    <t>Passwords were built instead of the specified email OTP</t>
+  </si>
+  <si>
+    <t>BACKEND_SPEC.md specifies passwordless sign-in by emailed code. Passwords were requested instead and built. Livingstone advertises password-free login as a feature, so the spec was not arbitrary.</t>
+  </si>
+  <si>
+    <t>Both can coexist: the schema keeps otpCode and otpExpiresAt. Decide before launch.</t>
+  </si>
+  <si>
+    <t>BE-19</t>
+  </si>
+  <si>
+    <t>Guest checkout is allowed</t>
+  </si>
+  <si>
+    <t>OUR DECISION: an order can be placed without signing in, and is then tied to the cart cookie. Signing in simply attaches the order to the account.</t>
+  </si>
+  <si>
+    <t>If trade accounts should be required to order, this must change â€” it also affects credit terms and pricing.</t>
+  </si>
+  <si>
+    <t>BE-22</t>
+  </si>
+  <si>
+    <t>Confirm one supplier account per company</t>
+  </si>
+  <si>
+    <t>OUR DECISION: each supplier company links to a single user. Real suppliers usually need several people with their own logins.</t>
+  </si>
+  <si>
+    <t>Schema allows it via Supplier.userId; supporting several needs a join table.</t>
+  </si>
+  <si>
+    <t>DA-02</t>
+  </si>
+  <si>
+    <t>Verify the product-to-category mapping</t>
+  </si>
+  <si>
+    <t>The extraction had no product-category link at all, so every mapping on the site is ours. The catalogue is now 71 products across 146 categories and none of that mapping has been checked by anyone who knows the range.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026 after DA-23: 60 active products, 0 uncategorised.</t>
+  </si>
+  <si>
+    <t>DA-05</t>
+  </si>
+  <si>
+    <t>Approve the product descriptions</t>
+  </si>
+  <si>
+    <t>The source had no descriptions. All 71 active products now carry text we generated from the product name and supplier listing, and it goes out under AussieMed's name.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026 after DA-23: 60 of 60 active products have a generated description.</t>
+  </si>
+  <si>
+    <t>DA-07</t>
+  </si>
+  <si>
+    <t>Supply the hero banner image</t>
+  </si>
+  <si>
+    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured â€” only Brand, Category, Product and WebHtml folders were mirrored.</t>
+  </si>
+  <si>
+    <t>A genuine AussieMed CMS image stands in.</t>
+  </si>
+  <si>
+    <t>DA-08</t>
+  </si>
+  <si>
+    <t>Obtain Gilroy Regular and Medium</t>
+  </si>
+  <si>
+    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
+  </si>
+  <si>
+    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
+  </si>
+  <si>
+    <t>DA-10</t>
+  </si>
+  <si>
+    <t>Supply real pack and carton structures</t>
+  </si>
+  <si>
+    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
+  </si>
+  <si>
+    <t>Largely superseded by DA-20: packaging moved from separate carton SKUs into named price breaks on 15 Aug 2026, so the invented figures now live in scripts/variants.mjs rather than in outer packs. Kept open because the underlying question â€” what is a real carton and box for each line â€” is unanswered either way.</t>
+  </si>
+  <si>
+    <t>DA-11</t>
+  </si>
+  <si>
+    <t>Supply real variant data</t>
+  </si>
+  <si>
+    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: the same five sizes and three colours are stamped on all six glove products regardless of what the supplier actually sells. FN-07 covers the wiring; this row covers the data.</t>
+  </si>
+  <si>
+    <t>DA-12</t>
+  </si>
+  <si>
+    <t>Supply real product specifications</t>
+  </si>
+  <si>
+    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
+  </si>
+  <si>
+    <t>These become search filters later.</t>
+  </si>
+  <si>
+    <t>DA-13</t>
+  </si>
+  <si>
+    <t>Supply safety data sheets and spec sheets</t>
+  </si>
+  <si>
+    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
+  </si>
+  <si>
+    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
+  </si>
+  <si>
+    <t>DA-18</t>
+  </si>
+  <si>
+    <t>Product ids are derived from slugs</t>
+  </si>
+  <si>
+    <t>Carts and wishlists are stored in the browser against a product id. Ids are now hashed from the slug so they survive a re-seed, which means CHANGING A PRODUCT SLUG ORPHANS ANY SAVED CART LINE referencing it.</t>
+  </si>
+  <si>
+    <t>Resolved properly when the cart moves server-side and references SKU rows directly.</t>
+  </si>
+  <si>
+    <t>DA-19</t>
+  </si>
+  <si>
+    <t>Supplier email addresses are invented</t>
+  </si>
+  <si>
+    <t>The seed writes orders@&lt;supplier&gt;.example and accounts@&lt;supplier&gt;.example because secondaryEmail is mandatory. No supplier will receive anything at these addresses.</t>
+  </si>
+  <si>
+    <t>Both addresses are meant to receive order notifications once email exists.</t>
+  </si>
+  <si>
+    <t>DA-21</t>
+  </si>
+  <si>
+    <t>Verify the automatic variant grouping</t>
+  </si>
+  <si>
+    <t>Products are grouped into families by stripping sizes and volumes from their names. It found 2 families in the seeded catalogue. A real catalogue will group differently and some groupings will be wrong.</t>
+  </si>
+  <si>
+    <t>The admin product screens should let a family be set explicitly rather than inferred â€” see BE-20.</t>
+  </si>
+  <si>
+    <t>DA-24</t>
+  </si>
+  <si>
+    <t>13 of 60 products have no image</t>
+  </si>
+  <si>
+    <t>Those products render as a monogram tile rather than a photograph. It is a deliberate stand-in and reads acceptably in a grid, but on a trade catalogue an image is often how a buyer confirms they have the right item.</t>
+  </si>
+  <si>
+    <t>Was 19 of 71. Ten went with the extraction products under DA-23. Four more were added deliberately: their image files turned out to be SVG placeholders saved with a .jpg extension, which the image optimiser rejected with a 400 â€” see DA-25. The remaining nine have no sourceSku or sourceUrl recorded, so there is nothing to retry a fetch against, and no more third-party photography was sourced because DA-17 already limits what may ship. Subset of DA-03.</t>
+  </si>
+  <si>
+    <t>FE-30</t>
+  </si>
+  <si>
+    <t>Prices are still labelled Ex. VAT with no way to see inc-VAT</t>
+  </si>
+  <si>
+    <t>The header toggle was removed before VAT was folded into the displayed price, so a buyer approving an invoice has no inc-VAT figure anywhere on the storefront. Checkout still adds VAT, so the total at the end is higher than every price shown.</t>
+  </si>
+  <si>
+    <t>Follow up to DEC-14. Decide whether displayed prices become VAT inclusive or the Ex. VAT labels simply stay.</t>
+  </si>
+  <si>
+    <t>FN-07</t>
+  </si>
+  <si>
+    <t>Size and colour switching is not wired</t>
+  </si>
+  <si>
+    <t>The variant dropdown built on 15 Aug 2026 (DEC-12) switches between sibling products by size or volume, and that works. The separate Size and Colour chips on gloves and the scrub top are a different thing and still do nothing â€” no sibling SKU exists behind any of them.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: 13 option axes across 6 products. Every glove carries an identical Size = XS/S/M/L/XL and Colour = Black/Blue/Green with no SKU attached to any value.</t>
+  </si>
+  <si>
+    <t>FN-08</t>
+  </si>
+  <si>
+    <t>Stock is a boolean</t>
+  </si>
+  <si>
+    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
+  </si>
+  <si>
+    <t>Decide whether real stock levels are needed.</t>
+  </si>
+  <si>
+    <t>FN-09</t>
+  </si>
+  <si>
+    <t>Decide on expiry and short-dated stock</t>
+  </si>
+  <si>
+    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
+  </si>
+  <si>
+    <t>Schema-shaping â€” decide before the backend is built.</t>
+  </si>
+  <si>
+    <t>IN-01</t>
+  </si>
+  <si>
+    <t>Choose a hosting target</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. The site runs locally only.</t>
+  </si>
+  <si>
+    <t>Deliberately deferred until the build is approved.</t>
+  </si>
+  <si>
+    <t>IN-02</t>
+  </si>
+  <si>
+    <t>Choose the database</t>
+  </si>
+  <si>
+    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
+  </si>
+  <si>
+    <t>IN-03</t>
+  </si>
+  <si>
+    <t>Choose an SMTP provider and sending domain</t>
+  </si>
+  <si>
+    <t>Required for every transactional email.</t>
+  </si>
+  <si>
+    <t>Must not be the misspelled assuiemed.com domain.</t>
+  </si>
+  <si>
+    <t>IN-04</t>
+  </si>
+  <si>
+    <t>Decide on a payment gateway</t>
+  </si>
+  <si>
+    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
+  </si>
+  <si>
+    <t>LG-05</t>
+  </si>
+  <si>
+    <t>Transfer the theme licence</t>
+  </si>
+  <si>
+    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
+  </si>
+  <si>
+    <t>Repository must stay private because of this.</t>
+  </si>
+  <si>
+    <t>LG-06</t>
+  </si>
+  <si>
+    <t>Supply company registration details</t>
+  </si>
+  <si>
+    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
+  </si>
+  <si>
+    <t>SEC-02</t>
+  </si>
+  <si>
+    <t>Add rate limiting to sign-in</t>
+  </si>
+  <si>
+    <t>Nothing limits password attempts, so the sign-in endpoint can be brute forced. The spec asks for rate limiting on auth in the hardening phase.</t>
+  </si>
+  <si>
+    <t>Matters more with short passwords than with OTP.</t>
+  </si>
+  <si>
+    <t>SEC-03</t>
+  </si>
+  <si>
+    <t>Agree a password policy</t>
+  </si>
+  <si>
+    <t>No minimum length, complexity or reuse rule is enforced. 123456 was accepted because nothing rejects it.</t>
+  </si>
+  <si>
+    <t>Moot if the OTP flow in BE-15 is adopted instead.</t>
+  </si>
+  <si>
+    <t>AC-08</t>
+  </si>
+  <si>
+    <t>Confirm the rounding policy</t>
+  </si>
+  <si>
+    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Verified by test; needs sign-off that the method is acceptable.</t>
+  </si>
+  <si>
+    <t>AC-10</t>
+  </si>
+  <si>
+    <t>Confirm the default price display</t>
+  </si>
+  <si>
+    <t>Prices are shown Ex. VAT everywhere, and since 15 Aug 2026 there is no way for a buyer to see an inc-VAT figure at all â€” the header toggle was removed at the client's request before VAT was folded into the displayed price.</t>
+  </si>
+  <si>
+    <t>See DEC-14 for the decision and FE-30 for the gap it leaves open.</t>
+  </si>
+  <si>
+    <t>BE-13</t>
+  </si>
+  <si>
+    <t>Expire abandoned guest carts</t>
+  </si>
+  <si>
+    <t>Cart rows are never cleaned up. Every visitor who adds an item creates one that lives forever.</t>
+  </si>
+  <si>
+    <t>The spec wants abandoned carts over 24h reportable under Admin &gt; Marketing, so expiry and that report should be designed together.</t>
+  </si>
+  <si>
+    <t>BE-16</t>
+  </si>
+  <si>
+    <t>Confirm the session lifetime</t>
+  </si>
+  <si>
+    <t>OUR INVENTED VALUE: sessions last 7 days, then require signing in again. No idle timeout and no re-authentication for sensitive actions.</t>
+  </si>
+  <si>
+    <t>Cookie is httpOnly and sameSite=lax; secure only in production so local http still works.</t>
+  </si>
+  <si>
+    <t>BE-17</t>
+  </si>
+  <si>
+    <t>Purge expired sessions on a schedule</t>
+  </si>
+  <si>
+    <t>Expired session rows are never deleted. purgeExpiredSessions() exists but nothing calls it.</t>
+  </si>
+  <si>
+    <t>Trivial once any scheduled job exists.</t>
+  </si>
+  <si>
+    <t>BE-18</t>
+  </si>
+  <si>
+    <t>Password hashing uses scrypt, not bcrypt</t>
+  </si>
+  <si>
+    <t>OUR DECISION: scrypt from Node's own crypto module, so there is no dependency to keep patched. The spec names bcrypt. Both are appropriate; only src/lib/auth.ts knows the format.</t>
+  </si>
+  <si>
+    <t>Stored as scrypt$salt$hash so the algorithm is self-describing and can be migrated per user.</t>
+  </si>
+  <si>
+    <t>BE-23</t>
+  </si>
+  <si>
+    <t>Admin figures are counted live, never cached</t>
+  </si>
+  <si>
+    <t>OUR DECISION: every number on the admin dashboard is counted from the database on each request. Caching them is how the old platform let admin counts and storefront counts disagree.</t>
+  </si>
+  <si>
+    <t>Still true after the admin build: every dashboard figure is a live count. Cheap at 60 products and 4 orders; revisit when either grows.</t>
+  </si>
+  <si>
+    <t>BE-24</t>
+  </si>
+  <si>
+    <t>Supplier data is scoped by query, not by filtering</t>
+  </si>
+  <si>
+    <t>OUR DECISION: a supplier's products and invoice lines are fetched through their supplier id, so another supplier's rows are never loaded rather than loaded and hidden.</t>
+  </si>
+  <si>
+    <t>Keep this rule as the supplier portal grows â€” filtering after fetching is how leaks happen.</t>
+  </si>
+  <si>
+    <t>BE-27</t>
+  </si>
+  <si>
+    <t>No marketing screens: wishlists and abandoned carts</t>
+  </si>
+  <si>
+    <t>Both are already recorded in the database and nobody can see either. An abandoned cart is the cheapest sale to recover, and a wishlist says what a buyer wants before they buy it.</t>
+  </si>
+  <si>
+    <t>Split out of BE-02 when the admin screens were built.</t>
+  </si>
+  <si>
+    <t>BE-28</t>
+  </si>
+  <si>
+    <t>No reports: sales by supplier, category or period</t>
+  </si>
+  <si>
+    <t>The dashboard totals every order ever placed and nothing else. There is no way to answer which supplier sells most, what a month looked like, or which categories are dead.</t>
+  </si>
+  <si>
+    <t>Split out of BE-02. Wants AC-09 settled first so periods line up with terms.</t>
+  </si>
+  <si>
+    <t>DA-14</t>
+  </si>
+  <si>
+    <t>Confirm the brand list</t>
+  </si>
+  <si>
+    <t>Brands were assigned by reading product names, because neither source listed a brand field. Bad extractions were caught by hand (Goat, Hello, Roger) but the list has never been checked against reality.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026 after DA-23: 26 brands across the 60 test products.</t>
+  </si>
+  <si>
+    <t>DA-15</t>
+  </si>
+  <si>
+    <t>Decide on duplicate categories</t>
+  </si>
+  <si>
+    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: still 6 duplicated names, 12 categories in total. Slugs are disambiguated by appending the numeric id (oral-care vs oral-care-96). 10 of the 12 hold no products at all, so most of the duplication is invisible to buyers today.</t>
+  </si>
+  <si>
+    <t>DA-16</t>
+  </si>
+  <si>
+    <t>Confirm the missing department</t>
+  </si>
+  <si>
+    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
+  </si>
+  <si>
+    <t>Confirm this is intentional rather than lost.</t>
+  </si>
+  <si>
+    <t>FN-10</t>
+  </si>
+  <si>
+    <t>Search is client-side only</t>
+  </si>
+  <si>
+    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
+  </si>
+  <si>
+    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
+  </si>
+  <si>
+    <t>IN-05</t>
+  </si>
+  <si>
+    <t>Supply Google and Facebook OAuth keys</t>
+  </si>
+  <si>
+    <t>Social login endpoints currently return 501.</t>
+  </si>
+  <si>
+    <t>IN-08</t>
+  </si>
+  <si>
+    <t>Correct the git author name</t>
+  </si>
+  <si>
+    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
+  </si>
+  <si>
+    <t>Fixable with git config user.name and an amend.</t>
+  </si>
+  <si>
+    <t>IN-09</t>
+  </si>
+  <si>
+    <t>Set up continuous integration</t>
+  </si>
+  <si>
+    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
+  </si>
+  <si>
+    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
+  </si>
+  <si>
+    <t>IN-10</t>
+  </si>
+  <si>
+    <t>Plan backups and disaster recovery</t>
+  </si>
+  <si>
+    <t>No backup strategy exists for the database or uploaded files.</t>
+  </si>
+  <si>
+    <t>Relevant once there is a real database.</t>
+  </si>
+  <si>
+    <t>LG-04</t>
+  </si>
+  <si>
+    <t>Approve the About / Contact / Order Support copy</t>
+  </si>
+  <si>
+    <t>All placeholder text.</t>
+  </si>
+  <si>
+    <t>Pages carry a visible placeholder notice.</t>
+  </si>
+  <si>
+    <t>DEC-01</t>
+  </si>
+  <si>
+    <t>Fresh build â€” the previous site is reference only</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: nothing to do with the previous site. The extraction is mined for data and business rules; its code and behaviour are discarded.</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Its category tree, product data and bug history were kept. Its markup was not.</t>
+  </si>
+  <si>
+    <t>DEC-02</t>
+  </si>
+  <si>
+    <t>Keep the existing visual brand</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026, correcting an earlier over-broad reading: the storefront must keep the current AussieMed look, not be redesigned.</t>
+  </si>
+  <si>
+    <t>Navy #29387d, red #ea2227 and Gilroy were read from the live site's computed styles. See DA-08 for the missing Gilroy weights.</t>
+  </si>
+  <si>
+    <t>DEC-03</t>
+  </si>
+  <si>
+    <t>Local only until the client approves</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: not to go online until there is a version they are happy with locally.</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. robots noindex is site-wide. Hosting is IN-01.</t>
+  </si>
+  <si>
+    <t>DEC-04</t>
+  </si>
+  <si>
+    <t>External connectors are handled last</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: anything needing a third-party account waits until the end so the build never stalls on credentials.</t>
+  </si>
+  <si>
+    <t>Payment IN-04, SMTP IN-03, OAuth IN-05, hosting IN-01. Built behind seams with local stand-ins.</t>
+  </si>
+  <si>
+    <t>DEC-05</t>
+  </si>
+  <si>
+    <t>Follow Livingstone for B2B catalogue and pricing behaviour</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026 with livingstone.com.au as the reference, and all suggested changes accepted.</t>
+  </si>
+  <si>
+    <t>Produced the pack/UOM model, price breaks on cards, the Ex/Inc VAT toggle, variant axes, spec attributes and per-product tax class.</t>
+  </si>
+  <si>
+    <t>DEC-06</t>
+  </si>
+  <si>
+    <t>Seed the catalogue from two real suppliers for testing</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: list Chemist Warehouse and Livingstone as suppliers with 30 items each, and remove the invented placeholders.</t>
+  </si>
+  <si>
+    <t>60 real products seeded. Both are unaffiliated third parties â€” DA-17 must close before launch.</t>
+  </si>
+  <si>
+    <t>DEC-07</t>
+  </si>
+  <si>
+    <t>Add product images</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026. Supplier photography was downloaded for local testing.</t>
+  </si>
+  <si>
+    <t>52 of 71 products have an image. Third-party assets â€” DA-03 must close before launch.</t>
+  </si>
+  <si>
+    <t>DEC-08</t>
+  </si>
+  <si>
+    <t>Four test accounts with a shared placeholder password</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: admin, musawi1989@gmail.com, supplier1 and supplier2, all with 123456. Explicitly described as local testing only, chosen to be memorable, and to be changed before anything real.</t>
+  </si>
+  <si>
+    <t>Implemented as asked. SEC-01 tracks removing them; SEC-03 tracks agreeing a password policy.</t>
+  </si>
+  <si>
+    <t>DEC-09</t>
+  </si>
+  <si>
+    <t>One sign-in door per role</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the business portal is the supplier login, the account login is for buyers, and admin is reached at /admin.</t>
+  </si>
+  <si>
+    <t>Implemented. Signing in at the wrong door names the right one rather than admitting the user.</t>
+  </si>
+  <si>
+    <t>DEC-10</t>
+  </si>
+  <si>
+    <t>Record every generated value and decision in this register</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026 and repeated 15 Aug: everything invented on the client's behalf must be written down rather than left in the code.</t>
+  </si>
+  <si>
+    <t>This register is the record. docs/Things That Need Attention.xlsx is generated from it and npm run register validates it.</t>
+  </si>
+  <si>
+    <t>DEC-11</t>
+  </si>
+  <si>
+    <t>Price breaks are packaging levels, not arbitrary quantities</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: a break at 12 exists because a carton holds 12, and a break at 48 because a box holds 4 cartons. The quantity and the packaging level are the same fact.</t>
+  </si>
+  <si>
+    <t>Each break now carries its level name. Corrects an earlier model that treated breaks as percentage discounts at round numbers.</t>
+  </si>
+  <si>
+    <t>DEC-12</t>
+  </si>
+  <si>
+    <t>Variants are a dropdown across sibling products</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the 375ml and the 60ml stay as separate products, and each carries a dropdown listing the whole family so a buyer can find their part quickly.</t>
+  </si>
+  <si>
+    <t>Replaces the Each/Carton chips on cards. Implemented as navigation between products, not options on one product, because each size has its own SKU, stock and price.</t>
+  </si>
+  <si>
+    <t>DEC-13</t>
+  </si>
+  <si>
+    <t>One sign-in button in the header, with a dropdown per role</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: replace the Business portal and Account links with a single blue Sign in button whose dropdown offers sign in as a buyer and sign in as a supplier.</t>
+  </si>
+  <si>
+    <t>Implemented in src/components/SignInMenu.tsx. Admin is deliberately absent from the dropdown; staff go to /admin directly. Once signed in the button becomes the way back to the user own area.</t>
+  </si>
+  <si>
+    <t>DEC-14</t>
+  </si>
+  <si>
+    <t>The AED label and the Ex/Inc VAT toggle are gone from the header</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: remove the AED text and the VAT options because VAT is to be carried in the displayed price later.</t>
+  </si>
+  <si>
+    <t>VatToggle deleted from the header. includeVat still exists in src/lib/store.tsx defaulting to ex-VAT with no UI control, so prices read ex-VAT everywhere until the pricing change lands. FE-30 tracks that follow up.</t>
+  </si>
+  <si>
+    <t>DEC-15</t>
+  </si>
+  <si>
+    <t>Sign out lives in the header, in the sign in button slot</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the sign out button always sits where the Sign in button would be when signed out.</t>
+  </si>
+  <si>
+    <t>Moved out of the account, admin and business portal pages into src/components/SignInMenu.tsx, so it is reachable from every page rather than only the dashboard. Signed in, the slot shows the account name plus Sign out.</t>
+  </si>
+  <si>
+    <t>DEC-16</t>
+  </si>
+  <si>
+    <t>Empty categories are hidden from navigation, not removed</t>
+  </si>
+  <si>
+    <t>The category tree came from Livingstone and is far wider than the 60 test products fill. Hiding what is empty keeps every menu entry useful; removing them would lose the shape of the intended range, and hard-coding a shorter list would need maintaining by hand.</t>
+  </si>
+  <si>
+    <t>Our decision, 15 Aug 2026, taken while closing FN-11. It is computed rather than configured, so categories reappear on their own as products are filed into them. Direct URLs still work. Say if you would rather the full tree stayed visible.</t>
+  </si>
+  <si>
+    <t>DEC-17</t>
+  </si>
+  <si>
+    <t>Renaming a category does not change its URL</t>
+  </si>
+  <si>
+    <t>The slug is the address. A category that has been linked to, bookmarked or indexed keeps working when its display name changes, and changing both would silently break every existing link.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026. Renaming to something genuinely different means creating a category and moving products, or a redirect table we have not built. Say if you would rather the URL followed the name.</t>
+  </si>
+  <si>
+    <t>DEC-18</t>
+  </si>
+  <si>
+    <t>A product cannot go live without a SKU and a category</t>
+  </si>
+  <si>
+    <t>Both make a live product broken rather than merely incomplete: no SKU means nothing to buy, no category means nobody can browse to it. The admin screen refuses the transition and says which one is missing.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026, enforced in src/lib/admin.ts rather than in the form, so posting to the endpoint directly cannot bypass it.</t>
+  </si>
+  <si>
+    <t>DEC-19</t>
+  </si>
+  <si>
+    <t>Delivered and cancelled orders cannot be reopened</t>
+  </si>
+  <si>
+    <t>Both are closed documents the customer already holds. A status that contradicts what they received is worse than no status at all.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026. A delivered order needs a return and a cancelled one needs a new order â€” neither of which exists yet. Confirm this matches how you actually work.</t>
+  </si>
+  <si>
+    <t>DEC-20</t>
+  </si>
+  <si>
+    <t>The back office looks like the reference operations UI, not like the shop</t>
+  </si>
+  <si>
+    <t>The client supplied screenshots of the tool they use day to day. Staff processing orders are doing operational work, and the storefront chrome was both a distraction and the reason documents printed badly.</t>
+  </si>
+  <si>
+    <t>Agreed 16 Aug 2026. Admin and the supplier portal both use the operations shell; the light sidebar follows the reference rather than the AussieMed navy, chosen so the data on screen is what stands out. The supplier rail lists only the one screen that exists, because an entry leading to an unbuilt page is worse than no entry â€” the rest is BE-21.</t>
+  </si>
+  <si>
+    <t>DEC-21</t>
+  </si>
+  <si>
+    <t>Uploaded files go through a storage seam, not straight to disk</t>
+  </si>
+  <si>
+    <t>Local disk is right for a laptop and wrong for most hosting: a container filesystem is discarded on every deploy, and two instances behind a load balancer do not share one. Hosting is IN-01 and is not chosen yet.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026, taken while building BE-29. Everything touching a filesystem is confined to src/lib/storage.ts behind a driver interface; local disk is the only driver today and STORAGE_DRIVER selects it. Adding S3, R2 or Blob storage means writing one more driver and changing an environment variable, with no calling code touched. What counts as an acceptable image is decided separately in image-file.ts, which is pure and unit tested, so a second driver cannot accept what this one refuses.</t>
+  </si>
+  <si>
+    <t>DA-09</t>
+  </si>
+  <si>
+    <t>Explain the disappearing product</t>
+  </si>
+  <si>
+    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
+  </si>
+  <si>
+    <t>Deferred 15 Aug 2026. The product in question was one of the 11 removed under DA-23 and nothing is being migrated from the old platform, so this no longer affects the build. Worth revisiting only if data from the old system is ever imported.</t>
+  </si>
+  <si>
+    <t>DF-01</t>
+  </si>
+  <si>
+    <t>Industry taxonomy</t>
+  </si>
+  <si>
+    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
+  </si>
+  <si>
+    <t>Additive; adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-02</t>
+  </si>
+  <si>
+    <t>Subscribe and Save</t>
+  </si>
+  <si>
+    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
+  </si>
+  <si>
+    <t>Needs the backend.</t>
+  </si>
+  <si>
+    <t>DF-03</t>
+  </si>
+  <si>
+    <t>Frequently bought together</t>
+  </si>
+  <si>
+    <t>Bundle suggestion with a combined total and one action to add all.</t>
+  </si>
+  <si>
+    <t>Adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-04</t>
+  </si>
+  <si>
+    <t>Quick view</t>
+  </si>
+  <si>
+    <t>View a product from the listing without a page load.</t>
+  </si>
+  <si>
+    <t>DF-05</t>
+  </si>
+  <si>
+    <t>Downloadable PDF catalogues</t>
+  </si>
+  <si>
+    <t>Still how a lot of trade buying happens.</t>
+  </si>
+  <si>
+    <t>Needs the actual catalogue files.</t>
+  </si>
+  <si>
+    <t>BE-02</t>
+  </si>
+  <si>
+    <t>Build the admin panel</t>
+  </si>
+  <si>
+    <t>Products, categories, suppliers, customers, orders, marketing, reports, settings.</t>
+  </si>
+  <si>
+    <t>Done 16 Aug 2026 by BE-20. Marketing (wishlists, abandoned carts) and reports are not built â€” BE-27 and BE-28.</t>
+  </si>
+  <si>
+    <t>BE-07</t>
+  </si>
+  <si>
+    <t>Seed the database from the catalogue</t>
+  </si>
+  <si>
+    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
+  </si>
+  <si>
+    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
+  </si>
+  <si>
+    <t>BE-09</t>
+  </si>
+  <si>
+    <t>Point the storefront at the database</t>
+  </si>
+  <si>
+    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
+  </si>
+  <si>
+    <t>query.ts was untouched â€” it never knew where products came from.</t>
+  </si>
+  <si>
+    <t>BE-11</t>
+  </si>
+  <si>
+    <t>Order pages restricted to their owner</t>
+  </si>
+  <si>
+    <t>An order was readable by anyone who guessed a sequential reference. Now an admin sees any order, the account that placed it sees it, and a guest sees only an order placed from their own cart.</t>
+  </si>
+  <si>
+    <t>A forbidden order returns 404 rather than 403, so the response cannot be used to discover which references exist.</t>
+  </si>
+  <si>
+    <t>BE-20</t>
+  </si>
+  <si>
+    <t>Build the admin screens behind the dashboard</t>
+  </si>
+  <si>
+    <t>/admin authenticates and shows live figures, but every management screen is still missing: products, categories, suppliers, customers, orders, bulk upload, marketing, reports, settings.</t>
+  </si>
+  <si>
+    <t>Built 16 Aug 2026. Dashboard, products (list, filters, edit, SKUs, price breaks, approval), categories, suppliers, orders, customers, settings and an audit trail. Every write goes through src/lib/admin.ts, which checks the role again in the service layer, records the change, and bumps the catalogue version so the storefront updates without a restart. Bulk upload is BE-04; product image upload is still missing â€” see BE-29.</t>
+  </si>
+  <si>
+    <t>BE-25</t>
+  </si>
+  <si>
+    <t>Invalidate the catalogue cache after a seed or an edit</t>
+  </si>
+  <si>
+    <t>The data layer caches the catalogue for the life of the process, so a running server keeps serving whatever it read first. This is not theoretical: on 15 Aug 2026 the dev server was still showing a retired carton SKU as a purchasable unit chip on the product page, hours after the database had deactivated it.</t>
+  </si>
+  <si>
+    <t>Fixed 15 Aug 2026. The cache now carries the catalogVersion stamp it was built from and re-checks it against the database at most once a second; the seed bumps the stamp, and invalidateCatalog() bumps it too so other server processes drop their copy as well. Verified live: a running dev server went from 71 products to 60 without a restart, and the phantom carton chip disappeared.</t>
+  </si>
+  <si>
     <t>BE-29</t>
   </si>
   <si>
     <t>Product images cannot be uploaded</t>
   </si>
   <si>
-    <t>The admin product screen lists the image files a product references but cannot add or replace one, so the only way to give a product a photograph is to put a file on disk and re-seed. That blocks DA-03 and DA-24 from ever being closed by the client rather than by us.</t>
-  </si>
-  <si>
-    <t>Found while building the admin screens on 16 Aug 2026. Needs a decision on where uploaded files live once this is hosted â€” local disk will not survive most deployments, so it is tied to IN-01.</t>
-  </si>
-  <si>
-    <t>DA-01</t>
-  </si>
-  <si>
-    <t>Supply the real product catalogue</t>
-  </si>
-  <si>
-    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
-  </si>
-  <si>
-    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
-  </si>
-  <si>
-    <t>DA-03</t>
-  </si>
-  <si>
-    <t>Supply product photography</t>
-  </si>
-  <si>
-    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
-  </si>
-  <si>
-    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
-  </si>
-  <si>
-    <t>DA-06</t>
-  </si>
-  <si>
-    <t>Supply the real supplier list</t>
-  </si>
-  <si>
-    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
-  </si>
-  <si>
-    <t>All are flagged isPlaceholder in the data.</t>
-  </si>
-  <si>
-    <t>DA-17</t>
-  </si>
-  <si>
-    <t>Replace the test supplier attribution</t>
-  </si>
-  <si>
-    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
-  </si>
-  <si>
-    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
-  </si>
-  <si>
-    <t>DA-20</t>
-  </si>
-  <si>
-    <t>Supply the real packaging quantities</t>
-  </si>
-  <si>
-    <t>OUR INVENTED VALUES: how many units make a carton, and how many cartons make a box, are guessed per product family (12 and 4 by default, 10 and 5 for gloves, 20 and 5 for masks). The break discounts of 4% and 8% are also invented.</t>
-  </si>
-  <si>
-    <t>These are now shown to buyers as CARTON and BOX, so a wrong number reads as a factual claim about your packaging. In scripts/variants.mjs.</t>
-  </si>
-  <si>
-    <t>FN-02</t>
-  </si>
-  <si>
-    <t>Quote requests are not delivered</t>
-  </si>
-  <si>
-    <t>Captured in the browser only.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend and an email provider.</t>
-  </si>
-  <si>
-    <t>FN-03</t>
-  </si>
-  <si>
-    <t>Bulk buy enquiries are not delivered</t>
-  </si>
-  <si>
-    <t>FN-04</t>
-  </si>
-  <si>
-    <t>Notify Me does not register a subscription</t>
-  </si>
-  <si>
-    <t>Captured locally. The restock email flow does not exist.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend.</t>
-  </si>
-  <si>
-    <t>IN-06</t>
-  </si>
-  <si>
-    <t>Remove noindex before launch</t>
-  </si>
-  <si>
-    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
-  </si>
-  <si>
-    <t>Must be removed deliberately at launch â€” and only then.</t>
-  </si>
-  <si>
-    <t>IN-07</t>
-  </si>
-  <si>
-    <t>Confirm the GitHub repository is private</t>
-  </si>
-  <si>
-    <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
-  </si>
-  <si>
-    <t>https://github.com/musawi1989/aussiemed</t>
-  </si>
-  <si>
-    <t>LG-01</t>
-  </si>
-  <si>
-    <t>Supply terms and conditions</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
-  </si>
-  <si>
-    <t>Page exists and says so on screen.</t>
-  </si>
-  <si>
-    <t>LG-02</t>
-  </si>
-  <si>
-    <t>Supply the privacy policy</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
-  </si>
-  <si>
-    <t>LG-03</t>
-  </si>
-  <si>
-    <t>Confirm the contact email address</t>
-  </si>
-  <si>
-    <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
-  </si>
-  <si>
-    <t>Also determines the sending domain for transactional email.</t>
-  </si>
-  <si>
-    <t>SEC-01</t>
-  </si>
-  <si>
-    <t>Remove the test credentials before any deployment</t>
-  </si>
-  <si>
-    <t>Four accounts share the password 123456: admin, musawi1989@gmail.com, supplier1, supplier2. Fine on a laptop, unacceptable anywhere else.</t>
-  </si>
-  <si>
-    <t>The on-screen credentials panel now renders only outside production, so a production build cannot leak it. The accounts themselves still must be removed or given real passwords.</t>
-  </si>
-  <si>
-    <t>AC-05</t>
-  </si>
-  <si>
-    <t>Confirm the VAT rate and whether it must be configurable</t>
-  </si>
-  <si>
-    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>Rate must be stored on the order at the time it is placed.</t>
-  </si>
-  <si>
-    <t>AC-06</t>
-  </si>
-  <si>
-    <t>Approve the reference number format</t>
-  </si>
-  <si>
-    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
-  </si>
-  <si>
-    <t>Wording is fixed as Reference number, never order number.</t>
-  </si>
-  <si>
-    <t>AC-07</t>
-  </si>
-  <si>
-    <t>Approve the supplier invoice numbering</t>
-  </si>
-  <si>
-    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
-  </si>
-  <si>
-    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
-  </si>
-  <si>
-    <t>AC-09</t>
-  </si>
-  <si>
-    <t>Decide payment terms and credit accounts</t>
-  </si>
-  <si>
-    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
-  </si>
-  <si>
-    <t>Affects the schema â€” decide before the backend.</t>
-  </si>
-  <si>
-    <t>AC-11</t>
-  </si>
-  <si>
-    <t>Approve the VAT rounding method on invoices</t>
-  </si>
-  <si>
-    <t>VAT is rounded per line rather than once per invoice, so the printed lines always add up to the printed total. The alternative rounds once and can leave lines that do not sum.</t>
-  </si>
-  <si>
-    <t>Verified by test: per-invoice VAT sums to the order VAT exactly.</t>
-  </si>
-  <si>
-    <t>AC-12</t>
-  </si>
-  <si>
-    <t>Confirm the reference number sequence resets each year</t>
-  </si>
-  <si>
-    <t>OUR DECISION: the sequence restarts at 000001 each calendar year, so AM-2026-000001 and AM-2027-000001 can both exist. If accounting needs a single unbroken sequence this must change before real orders.</t>
-  </si>
-  <si>
-    <t>Held in a settings row keyed orderSequence:YYYY and incremented inside the checkout transaction.</t>
-  </si>
-  <si>
-    <t>AC-13</t>
-  </si>
-  <si>
-    <t>Decide whether an order should reserve stock</t>
-  </si>
-  <si>
-    <t>OUR DECISION: checkout does not decrement or reserve anything, because there are no stock levels â€” only an in/out flag. Two customers can order the last unit.</t>
-  </si>
-  <si>
-    <t>Depends on FN-08. Out-of-stock is re-checked at checkout, so a line that sold out while the form was open is rejected.</t>
-  </si>
-  <si>
-    <t>BE-04</t>
-  </si>
-  <si>
-    <t>Build comma-safe .xlsx bulk upload</t>
-  </si>
-  <si>
-    <t>Parsed natively with exceljs, never by splitting on commas â€” that is what broke comma-containing category names.</t>
-  </si>
-  <si>
-    <t>Unknown brands must be reported per row, never skipped silently.</t>
-  </si>
-  <si>
-    <t>BE-05</t>
-  </si>
-  <si>
-    <t>Build the email flows</t>
-  </si>
-  <si>
-    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
-  </si>
-  <si>
-    <t>Needs an SMTP provider.</t>
-  </si>
-  <si>
-    <t>BE-08</t>
-  </si>
-  <si>
-    <t>Decide money representation before any data lands</t>
-  </si>
-  <si>
-    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
-  </si>
-  <si>
-    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
-  </si>
-  <si>
-    <t>BE-10</t>
-  </si>
-  <si>
-    <t>Retire the catalogue snapshot endpoint</t>
-  </si>
-  <si>
-    <t>Client components fetch the whole catalogue from /api/v1/catalog/snapshot. Fine for 71 products; not for thousands. Goes away when the cart moves server-side.</t>
-  </si>
-  <si>
-    <t>Phase 3 removes the need.</t>
-  </si>
-  <si>
-    <t>BE-12</t>
-  </si>
-  <si>
-    <t>Merge a guest cart into the user cart on sign-in</t>
-  </si>
-  <si>
-    <t>Carts are keyed by a cookie so a visitor can shop before signing in. The merge on sign-in is specified but cannot be built until auth exists.</t>
-  </si>
-  <si>
-    <t>Cart cookie: aussiemed_cart, httpOnly, 30 day lifetime â€” OUR INVENTED VALUES.</t>
-  </si>
-  <si>
-    <t>BE-14</t>
-  </si>
-  <si>
-    <t>Confirm the default order and invoice status</t>
-  </si>
-  <si>
-    <t>OUR DECISION: new orders are Pending and each supplier invoice is Pending. The real workflow â€” who moves an order to Processing, and when an invoice becomes Issued â€” is not defined.</t>
-  </si>
-  <si>
-    <t>Order statuses available: Pending, Processing, Dispatched, Delivered, Cancelled.</t>
-  </si>
-  <si>
-    <t>BE-15</t>
-  </si>
-  <si>
-    <t>Passwords were built instead of the specified email OTP</t>
-  </si>
-  <si>
-    <t>BACKEND_SPEC.md specifies passwordless sign-in by emailed code. Passwords were requested instead and built. Livingstone advertises password-free login as a feature, so the spec was not arbitrary.</t>
-  </si>
-  <si>
-    <t>Both can coexist: the schema keeps otpCode and otpExpiresAt. Decide before launch.</t>
-  </si>
-  <si>
-    <t>BE-19</t>
-  </si>
-  <si>
-    <t>Guest checkout is allowed</t>
-  </si>
-  <si>
-    <t>OUR DECISION: an order can be placed without signing in, and is then tied to the cart cookie. Signing in simply attaches the order to the account.</t>
-  </si>
-  <si>
-    <t>If trade accounts should be required to order, this must change â€” it also affects credit terms and pricing.</t>
-  </si>
-  <si>
-    <t>BE-22</t>
-  </si>
-  <si>
-    <t>Confirm one supplier account per company</t>
-  </si>
-  <si>
-    <t>OUR DECISION: each supplier company links to a single user. Real suppliers usually need several people with their own logins.</t>
-  </si>
-  <si>
-    <t>Schema allows it via Supplier.userId; supporting several needs a join table.</t>
-  </si>
-  <si>
-    <t>DA-02</t>
-  </si>
-  <si>
-    <t>Verify the product-to-category mapping</t>
-  </si>
-  <si>
-    <t>The extraction had no product-category link at all, so every mapping on the site is ours. The catalogue is now 71 products across 146 categories and none of that mapping has been checked by anyone who knows the range.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026 after DA-23: 60 active products, 0 uncategorised.</t>
-  </si>
-  <si>
-    <t>DA-05</t>
-  </si>
-  <si>
-    <t>Approve the product descriptions</t>
-  </si>
-  <si>
-    <t>The source had no descriptions. All 71 active products now carry text we generated from the product name and supplier listing, and it goes out under AussieMed's name.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026 after DA-23: 60 of 60 active products have a generated description.</t>
-  </si>
-  <si>
-    <t>DA-07</t>
-  </si>
-  <si>
-    <t>Supply the hero banner image</t>
-  </si>
-  <si>
-    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured â€” only Brand, Category, Product and WebHtml folders were mirrored.</t>
-  </si>
-  <si>
-    <t>A genuine AussieMed CMS image stands in.</t>
-  </si>
-  <si>
-    <t>DA-08</t>
-  </si>
-  <si>
-    <t>Obtain Gilroy Regular and Medium</t>
-  </si>
-  <si>
-    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
-  </si>
-  <si>
-    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
-  </si>
-  <si>
-    <t>DA-10</t>
-  </si>
-  <si>
-    <t>Supply real pack and carton structures</t>
-  </si>
-  <si>
-    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
-  </si>
-  <si>
-    <t>Largely superseded by DA-20: packaging moved from separate carton SKUs into named price breaks on 15 Aug 2026, so the invented figures now live in scripts/variants.mjs rather than in outer packs. Kept open because the underlying question â€” what is a real carton and box for each line â€” is unanswered either way.</t>
-  </si>
-  <si>
-    <t>DA-11</t>
-  </si>
-  <si>
-    <t>Supply real variant data</t>
-  </si>
-  <si>
-    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: the same five sizes and three colours are stamped on all six glove products regardless of what the supplier actually sells. FN-07 covers the wiring; this row covers the data.</t>
-  </si>
-  <si>
-    <t>DA-12</t>
-  </si>
-  <si>
-    <t>Supply real product specifications</t>
-  </si>
-  <si>
-    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
-  </si>
-  <si>
-    <t>These become search filters later.</t>
-  </si>
-  <si>
-    <t>DA-13</t>
-  </si>
-  <si>
-    <t>Supply safety data sheets and spec sheets</t>
-  </si>
-  <si>
-    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
-  </si>
-  <si>
-    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
-  </si>
-  <si>
-    <t>DA-18</t>
-  </si>
-  <si>
-    <t>Product ids are derived from slugs</t>
-  </si>
-  <si>
-    <t>Carts and wishlists are stored in the browser against a product id. Ids are now hashed from the slug so they survive a re-seed, which means CHANGING A PRODUCT SLUG ORPHANS ANY SAVED CART LINE referencing it.</t>
-  </si>
-  <si>
-    <t>Resolved properly when the cart moves server-side and references SKU rows directly.</t>
-  </si>
-  <si>
-    <t>DA-19</t>
-  </si>
-  <si>
-    <t>Supplier email addresses are invented</t>
-  </si>
-  <si>
-    <t>The seed writes orders@&lt;supplier&gt;.example and accounts@&lt;supplier&gt;.example because secondaryEmail is mandatory. No supplier will receive anything at these addresses.</t>
-  </si>
-  <si>
-    <t>Both addresses are meant to receive order notifications once email exists.</t>
-  </si>
-  <si>
-    <t>DA-21</t>
-  </si>
-  <si>
-    <t>Verify the automatic variant grouping</t>
-  </si>
-  <si>
-    <t>Products are grouped into families by stripping sizes and volumes from their names. It found 2 families in the seeded catalogue. A real catalogue will group differently and some groupings will be wrong.</t>
-  </si>
-  <si>
-    <t>The admin product screens should let a family be set explicitly rather than inferred â€” see BE-20.</t>
-  </si>
-  <si>
-    <t>DA-24</t>
-  </si>
-  <si>
-    <t>13 of 60 products have no image</t>
-  </si>
-  <si>
-    <t>Those products render as a monogram tile rather than a photograph. It is a deliberate stand-in and reads acceptably in a grid, but on a trade catalogue an image is often how a buyer confirms they have the right item.</t>
-  </si>
-  <si>
-    <t>Was 19 of 71. Ten went with the extraction products under DA-23. Four more were added deliberately: their image files turned out to be SVG placeholders saved with a .jpg extension, which the image optimiser rejected with a 400 â€” see DA-25. The remaining nine have no sourceSku or sourceUrl recorded, so there is nothing to retry a fetch against, and no more third-party photography was sourced because DA-17 already limits what may ship. Subset of DA-03.</t>
-  </si>
-  <si>
-    <t>FE-30</t>
-  </si>
-  <si>
-    <t>Prices are still labelled Ex. VAT with no way to see inc-VAT</t>
-  </si>
-  <si>
-    <t>The header toggle was removed before VAT was folded into the displayed price, so a buyer approving an invoice has no inc-VAT figure anywhere on the storefront. Checkout still adds VAT, so the total at the end is higher than every price shown.</t>
-  </si>
-  <si>
-    <t>Follow up to DEC-14. Decide whether displayed prices become VAT inclusive or the Ex. VAT labels simply stay.</t>
-  </si>
-  <si>
-    <t>FN-07</t>
-  </si>
-  <si>
-    <t>Size and colour switching is not wired</t>
-  </si>
-  <si>
-    <t>The variant dropdown built on 15 Aug 2026 (DEC-12) switches between sibling products by size or volume, and that works. The separate Size and Colour chips on gloves and the scrub top are a different thing and still do nothing â€” no sibling SKU exists behind any of them.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: 13 option axes across 6 products. Every glove carries an identical Size = XS/S/M/L/XL and Colour = Black/Blue/Green with no SKU attached to any value.</t>
-  </si>
-  <si>
-    <t>FN-08</t>
-  </si>
-  <si>
-    <t>Stock is a boolean</t>
-  </si>
-  <si>
-    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
-  </si>
-  <si>
-    <t>Decide whether real stock levels are needed.</t>
-  </si>
-  <si>
-    <t>FN-09</t>
-  </si>
-  <si>
-    <t>Decide on expiry and short-dated stock</t>
-  </si>
-  <si>
-    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
-  </si>
-  <si>
-    <t>Schema-shaping â€” decide before the backend is built.</t>
-  </si>
-  <si>
-    <t>IN-01</t>
-  </si>
-  <si>
-    <t>Choose a hosting target</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. The site runs locally only.</t>
-  </si>
-  <si>
-    <t>Deliberately deferred until the build is approved.</t>
-  </si>
-  <si>
-    <t>IN-02</t>
-  </si>
-  <si>
-    <t>Choose the database</t>
-  </si>
-  <si>
-    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
-  </si>
-  <si>
-    <t>IN-03</t>
-  </si>
-  <si>
-    <t>Choose an SMTP provider and sending domain</t>
-  </si>
-  <si>
-    <t>Required for every transactional email.</t>
-  </si>
-  <si>
-    <t>Must not be the misspelled assuiemed.com domain.</t>
-  </si>
-  <si>
-    <t>IN-04</t>
-  </si>
-  <si>
-    <t>Decide on a payment gateway</t>
-  </si>
-  <si>
-    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
-  </si>
-  <si>
-    <t>LG-05</t>
-  </si>
-  <si>
-    <t>Transfer the theme licence</t>
-  </si>
-  <si>
-    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
-  </si>
-  <si>
-    <t>Repository must stay private because of this.</t>
-  </si>
-  <si>
-    <t>LG-06</t>
-  </si>
-  <si>
-    <t>Supply company registration details</t>
-  </si>
-  <si>
-    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
-  </si>
-  <si>
-    <t>SEC-02</t>
-  </si>
-  <si>
-    <t>Add rate limiting to sign-in</t>
-  </si>
-  <si>
-    <t>Nothing limits password attempts, so the sign-in endpoint can be brute forced. The spec asks for rate limiting on auth in the hardening phase.</t>
-  </si>
-  <si>
-    <t>Matters more with short passwords than with OTP.</t>
-  </si>
-  <si>
-    <t>SEC-03</t>
-  </si>
-  <si>
-    <t>Agree a password policy</t>
-  </si>
-  <si>
-    <t>No minimum length, complexity or reuse rule is enforced. 123456 was accepted because nothing rejects it.</t>
-  </si>
-  <si>
-    <t>Moot if the OTP flow in BE-15 is adopted instead.</t>
-  </si>
-  <si>
-    <t>AC-08</t>
-  </si>
-  <si>
-    <t>Confirm the rounding policy</t>
-  </si>
-  <si>
-    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>Verified by test; needs sign-off that the method is acceptable.</t>
-  </si>
-  <si>
-    <t>AC-10</t>
-  </si>
-  <si>
-    <t>Confirm the default price display</t>
-  </si>
-  <si>
-    <t>Prices are shown Ex. VAT everywhere, and since 15 Aug 2026 there is no way for a buyer to see an inc-VAT figure at all â€” the header toggle was removed at the client's request before VAT was folded into the displayed price.</t>
-  </si>
-  <si>
-    <t>See DEC-14 for the decision and FE-30 for the gap it leaves open.</t>
-  </si>
-  <si>
-    <t>BE-13</t>
-  </si>
-  <si>
-    <t>Expire abandoned guest carts</t>
-  </si>
-  <si>
-    <t>Cart rows are never cleaned up. Every visitor who adds an item creates one that lives forever.</t>
-  </si>
-  <si>
-    <t>The spec wants abandoned carts over 24h reportable under Admin &gt; Marketing, so expiry and that report should be designed together.</t>
-  </si>
-  <si>
-    <t>BE-16</t>
-  </si>
-  <si>
-    <t>Confirm the session lifetime</t>
-  </si>
-  <si>
-    <t>OUR INVENTED VALUE: sessions last 7 days, then require signing in again. No idle timeout and no re-authentication for sensitive actions.</t>
-  </si>
-  <si>
-    <t>Cookie is httpOnly and sameSite=lax; secure only in production so local http still works.</t>
-  </si>
-  <si>
-    <t>BE-17</t>
-  </si>
-  <si>
-    <t>Purge expired sessions on a schedule</t>
-  </si>
-  <si>
-    <t>Expired session rows are never deleted. purgeExpiredSessions() exists but nothing calls it.</t>
-  </si>
-  <si>
-    <t>Trivial once any scheduled job exists.</t>
-  </si>
-  <si>
-    <t>BE-18</t>
-  </si>
-  <si>
-    <t>Password hashing uses scrypt, not bcrypt</t>
-  </si>
-  <si>
-    <t>OUR DECISION: scrypt from Node's own crypto module, so there is no dependency to keep patched. The spec names bcrypt. Both are appropriate; only src/lib/auth.ts knows the format.</t>
-  </si>
-  <si>
-    <t>Stored as scrypt$salt$hash so the algorithm is self-describing and can be migrated per user.</t>
-  </si>
-  <si>
-    <t>BE-23</t>
-  </si>
-  <si>
-    <t>Admin figures are counted live, never cached</t>
-  </si>
-  <si>
-    <t>OUR DECISION: every number on the admin dashboard is counted from the database on each request. Caching them is how the old platform let admin counts and storefront counts disagree.</t>
-  </si>
-  <si>
-    <t>Still true after the admin build: every dashboard figure is a live count. Cheap at 60 products and 4 orders; revisit when either grows.</t>
-  </si>
-  <si>
-    <t>BE-24</t>
-  </si>
-  <si>
-    <t>Supplier data is scoped by query, not by filtering</t>
-  </si>
-  <si>
-    <t>OUR DECISION: a supplier's products and invoice lines are fetched through their supplier id, so another supplier's rows are never loaded rather than loaded and hidden.</t>
-  </si>
-  <si>
-    <t>Keep this rule as the supplier portal grows â€” filtering after fetching is how leaks happen.</t>
-  </si>
-  <si>
-    <t>BE-27</t>
-  </si>
-  <si>
-    <t>No marketing screens: wishlists and abandoned carts</t>
-  </si>
-  <si>
-    <t>Both are already recorded in the database and nobody can see either. An abandoned cart is the cheapest sale to recover, and a wishlist says what a buyer wants before they buy it.</t>
-  </si>
-  <si>
-    <t>Split out of BE-02 when the admin screens were built.</t>
-  </si>
-  <si>
-    <t>BE-28</t>
-  </si>
-  <si>
-    <t>No reports: sales by supplier, category or period</t>
-  </si>
-  <si>
-    <t>The dashboard totals every order ever placed and nothing else. There is no way to answer which supplier sells most, what a month looked like, or which categories are dead.</t>
-  </si>
-  <si>
-    <t>Split out of BE-02. Wants AC-09 settled first so periods line up with terms.</t>
-  </si>
-  <si>
-    <t>DA-14</t>
-  </si>
-  <si>
-    <t>Confirm the brand list</t>
-  </si>
-  <si>
-    <t>Brands were assigned by reading product names, because neither source listed a brand field. Bad extractions were caught by hand (Goat, Hello, Roger) but the list has never been checked against reality.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026 after DA-23: 26 brands across the 60 test products.</t>
-  </si>
-  <si>
-    <t>DA-15</t>
-  </si>
-  <si>
-    <t>Decide on duplicate categories</t>
-  </si>
-  <si>
-    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: still 6 duplicated names, 12 categories in total. Slugs are disambiguated by appending the numeric id (oral-care vs oral-care-96). 10 of the 12 hold no products at all, so most of the duplication is invisible to buyers today.</t>
-  </si>
-  <si>
-    <t>DA-16</t>
-  </si>
-  <si>
-    <t>Confirm the missing department</t>
-  </si>
-  <si>
-    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
-  </si>
-  <si>
-    <t>Confirm this is intentional rather than lost.</t>
-  </si>
-  <si>
-    <t>FN-10</t>
-  </si>
-  <si>
-    <t>Search is client-side only</t>
-  </si>
-  <si>
-    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
-  </si>
-  <si>
-    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
-  </si>
-  <si>
-    <t>IN-05</t>
-  </si>
-  <si>
-    <t>Supply Google and Facebook OAuth keys</t>
-  </si>
-  <si>
-    <t>Social login endpoints currently return 501.</t>
-  </si>
-  <si>
-    <t>IN-08</t>
-  </si>
-  <si>
-    <t>Correct the git author name</t>
-  </si>
-  <si>
-    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
-  </si>
-  <si>
-    <t>Fixable with git config user.name and an amend.</t>
-  </si>
-  <si>
-    <t>IN-09</t>
-  </si>
-  <si>
-    <t>Set up continuous integration</t>
-  </si>
-  <si>
-    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
-  </si>
-  <si>
-    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
-  </si>
-  <si>
-    <t>IN-10</t>
-  </si>
-  <si>
-    <t>Plan backups and disaster recovery</t>
-  </si>
-  <si>
-    <t>No backup strategy exists for the database or uploaded files.</t>
-  </si>
-  <si>
-    <t>Relevant once there is a real database.</t>
-  </si>
-  <si>
-    <t>LG-04</t>
-  </si>
-  <si>
-    <t>Approve the About / Contact / Order Support copy</t>
-  </si>
-  <si>
-    <t>All placeholder text.</t>
-  </si>
-  <si>
-    <t>Pages carry a visible placeholder notice.</t>
-  </si>
-  <si>
-    <t>DEC-01</t>
-  </si>
-  <si>
-    <t>Fresh build â€” the previous site is reference only</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: nothing to do with the previous site. The extraction is mined for data and business rules; its code and behaviour are discarded.</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>Its category tree, product data and bug history were kept. Its markup was not.</t>
-  </si>
-  <si>
-    <t>DEC-02</t>
-  </si>
-  <si>
-    <t>Keep the existing visual brand</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026, correcting an earlier over-broad reading: the storefront must keep the current AussieMed look, not be redesigned.</t>
-  </si>
-  <si>
-    <t>Navy #29387d, red #ea2227 and Gilroy were read from the live site's computed styles. See DA-08 for the missing Gilroy weights.</t>
-  </si>
-  <si>
-    <t>DEC-03</t>
-  </si>
-  <si>
-    <t>Local only until the client approves</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: not to go online until there is a version they are happy with locally.</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. robots noindex is site-wide. Hosting is IN-01.</t>
-  </si>
-  <si>
-    <t>DEC-04</t>
-  </si>
-  <si>
-    <t>External connectors are handled last</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: anything needing a third-party account waits until the end so the build never stalls on credentials.</t>
-  </si>
-  <si>
-    <t>Payment IN-04, SMTP IN-03, OAuth IN-05, hosting IN-01. Built behind seams with local stand-ins.</t>
-  </si>
-  <si>
-    <t>DEC-05</t>
-  </si>
-  <si>
-    <t>Follow Livingstone for B2B catalogue and pricing behaviour</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026 with livingstone.com.au as the reference, and all suggested changes accepted.</t>
-  </si>
-  <si>
-    <t>Produced the pack/UOM model, price breaks on cards, the Ex/Inc VAT toggle, variant axes, spec attributes and per-product tax class.</t>
-  </si>
-  <si>
-    <t>DEC-06</t>
-  </si>
-  <si>
-    <t>Seed the catalogue from two real suppliers for testing</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: list Chemist Warehouse and Livingstone as suppliers with 30 items each, and remove the invented placeholders.</t>
-  </si>
-  <si>
-    <t>60 real products seeded. Both are unaffiliated third parties â€” DA-17 must close before launch.</t>
-  </si>
-  <si>
-    <t>DEC-07</t>
-  </si>
-  <si>
-    <t>Add product images</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026. Supplier photography was downloaded for local testing.</t>
-  </si>
-  <si>
-    <t>52 of 71 products have an image. Third-party assets â€” DA-03 must close before launch.</t>
-  </si>
-  <si>
-    <t>DEC-08</t>
-  </si>
-  <si>
-    <t>Four test accounts with a shared placeholder password</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: admin, musawi1989@gmail.com, supplier1 and supplier2, all with 123456. Explicitly described as local testing only, chosen to be memorable, and to be changed before anything real.</t>
-  </si>
-  <si>
-    <t>Implemented as asked. SEC-01 tracks removing them; SEC-03 tracks agreeing a password policy.</t>
-  </si>
-  <si>
-    <t>DEC-09</t>
-  </si>
-  <si>
-    <t>One sign-in door per role</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the business portal is the supplier login, the account login is for buyers, and admin is reached at /admin.</t>
-  </si>
-  <si>
-    <t>Implemented. Signing in at the wrong door names the right one rather than admitting the user.</t>
-  </si>
-  <si>
-    <t>DEC-10</t>
-  </si>
-  <si>
-    <t>Record every generated value and decision in this register</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026 and repeated 15 Aug: everything invented on the client's behalf must be written down rather than left in the code.</t>
-  </si>
-  <si>
-    <t>This register is the record. docs/Things That Need Attention.xlsx is generated from it and npm run register validates it.</t>
-  </si>
-  <si>
-    <t>DEC-11</t>
-  </si>
-  <si>
-    <t>Price breaks are packaging levels, not arbitrary quantities</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: a break at 12 exists because a carton holds 12, and a break at 48 because a box holds 4 cartons. The quantity and the packaging level are the same fact.</t>
-  </si>
-  <si>
-    <t>Each break now carries its level name. Corrects an earlier model that treated breaks as percentage discounts at round numbers.</t>
-  </si>
-  <si>
-    <t>DEC-12</t>
-  </si>
-  <si>
-    <t>Variants are a dropdown across sibling products</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the 375ml and the 60ml stay as separate products, and each carries a dropdown listing the whole family so a buyer can find their part quickly.</t>
-  </si>
-  <si>
-    <t>Replaces the Each/Carton chips on cards. Implemented as navigation between products, not options on one product, because each size has its own SKU, stock and price.</t>
-  </si>
-  <si>
-    <t>DEC-13</t>
-  </si>
-  <si>
-    <t>One sign-in button in the header, with a dropdown per role</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: replace the Business portal and Account links with a single blue Sign in button whose dropdown offers sign in as a buyer and sign in as a supplier.</t>
-  </si>
-  <si>
-    <t>Implemented in src/components/SignInMenu.tsx. Admin is deliberately absent from the dropdown; staff go to /admin directly. Once signed in the button becomes the way back to the user own area.</t>
-  </si>
-  <si>
-    <t>DEC-14</t>
-  </si>
-  <si>
-    <t>The AED label and the Ex/Inc VAT toggle are gone from the header</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: remove the AED text and the VAT options because VAT is to be carried in the displayed price later.</t>
-  </si>
-  <si>
-    <t>VatToggle deleted from the header. includeVat still exists in src/lib/store.tsx defaulting to ex-VAT with no UI control, so prices read ex-VAT everywhere until the pricing change lands. FE-30 tracks that follow up.</t>
-  </si>
-  <si>
-    <t>DEC-15</t>
-  </si>
-  <si>
-    <t>Sign out lives in the header, in the sign in button slot</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the sign out button always sits where the Sign in button would be when signed out.</t>
-  </si>
-  <si>
-    <t>Moved out of the account, admin and business portal pages into src/components/SignInMenu.tsx, so it is reachable from every page rather than only the dashboard. Signed in, the slot shows the account name plus Sign out.</t>
-  </si>
-  <si>
-    <t>DEC-16</t>
-  </si>
-  <si>
-    <t>Empty categories are hidden from navigation, not removed</t>
-  </si>
-  <si>
-    <t>The category tree came from Livingstone and is far wider than the 60 test products fill. Hiding what is empty keeps every menu entry useful; removing them would lose the shape of the intended range, and hard-coding a shorter list would need maintaining by hand.</t>
-  </si>
-  <si>
-    <t>Our decision, 15 Aug 2026, taken while closing FN-11. It is computed rather than configured, so categories reappear on their own as products are filed into them. Direct URLs still work. Say if you would rather the full tree stayed visible.</t>
-  </si>
-  <si>
-    <t>DEC-17</t>
-  </si>
-  <si>
-    <t>Renaming a category does not change its URL</t>
-  </si>
-  <si>
-    <t>The slug is the address. A category that has been linked to, bookmarked or indexed keeps working when its display name changes, and changing both would silently break every existing link.</t>
-  </si>
-  <si>
-    <t>Our decision, 16 Aug 2026. Renaming to something genuinely different means creating a category and moving products, or a redirect table we have not built. Say if you would rather the URL followed the name.</t>
-  </si>
-  <si>
-    <t>DEC-18</t>
-  </si>
-  <si>
-    <t>A product cannot go live without a SKU and a category</t>
-  </si>
-  <si>
-    <t>Both make a live product broken rather than merely incomplete: no SKU means nothing to buy, no category means nobody can browse to it. The admin screen refuses the transition and says which one is missing.</t>
-  </si>
-  <si>
-    <t>Our decision, 16 Aug 2026, enforced in src/lib/admin.ts rather than in the form, so posting to the endpoint directly cannot bypass it.</t>
-  </si>
-  <si>
-    <t>DEC-19</t>
-  </si>
-  <si>
-    <t>Delivered and cancelled orders cannot be reopened</t>
-  </si>
-  <si>
-    <t>Both are closed documents the customer already holds. A status that contradicts what they received is worse than no status at all.</t>
-  </si>
-  <si>
-    <t>Our decision, 16 Aug 2026. A delivered order needs a return and a cancelled one needs a new order â€” neither of which exists yet. Confirm this matches how you actually work.</t>
-  </si>
-  <si>
-    <t>DEC-20</t>
-  </si>
-  <si>
-    <t>The back office looks like the reference operations UI, not like the shop</t>
-  </si>
-  <si>
-    <t>The client supplied screenshots of the tool they use day to day. Staff processing orders are doing operational work, and the storefront chrome was both a distraction and the reason documents printed badly.</t>
-  </si>
-  <si>
-    <t>Agreed 16 Aug 2026. Admin and the supplier portal both use the operations shell; the light sidebar follows the reference rather than the AussieMed navy, chosen so the data on screen is what stands out. The supplier rail lists only the one screen that exists, because an entry leading to an unbuilt page is worse than no entry â€” the rest is BE-21.</t>
-  </si>
-  <si>
-    <t>DA-09</t>
-  </si>
-  <si>
-    <t>Explain the disappearing product</t>
-  </si>
-  <si>
-    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
-  </si>
-  <si>
-    <t>Deferred 15 Aug 2026. The product in question was one of the 11 removed under DA-23 and nothing is being migrated from the old platform, so this no longer affects the build. Worth revisiting only if data from the old system is ever imported.</t>
-  </si>
-  <si>
-    <t>DF-01</t>
-  </si>
-  <si>
-    <t>Industry taxonomy</t>
-  </si>
-  <si>
-    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
-  </si>
-  <si>
-    <t>Additive; adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-02</t>
-  </si>
-  <si>
-    <t>Subscribe and Save</t>
-  </si>
-  <si>
-    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
-  </si>
-  <si>
-    <t>Needs the backend.</t>
-  </si>
-  <si>
-    <t>DF-03</t>
-  </si>
-  <si>
-    <t>Frequently bought together</t>
-  </si>
-  <si>
-    <t>Bundle suggestion with a combined total and one action to add all.</t>
-  </si>
-  <si>
-    <t>Adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-04</t>
-  </si>
-  <si>
-    <t>Quick view</t>
-  </si>
-  <si>
-    <t>View a product from the listing without a page load.</t>
-  </si>
-  <si>
-    <t>DF-05</t>
-  </si>
-  <si>
-    <t>Downloadable PDF catalogues</t>
-  </si>
-  <si>
-    <t>Still how a lot of trade buying happens.</t>
-  </si>
-  <si>
-    <t>Needs the actual catalogue files.</t>
-  </si>
-  <si>
-    <t>BE-02</t>
-  </si>
-  <si>
-    <t>Build the admin panel</t>
-  </si>
-  <si>
-    <t>Products, categories, suppliers, customers, orders, marketing, reports, settings.</t>
-  </si>
-  <si>
-    <t>Done 16 Aug 2026 by BE-20. Marketing (wishlists, abandoned carts) and reports are not built â€” BE-27 and BE-28.</t>
-  </si>
-  <si>
-    <t>BE-07</t>
-  </si>
-  <si>
-    <t>Seed the database from the catalogue</t>
-  </si>
-  <si>
-    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
-  </si>
-  <si>
-    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
-  </si>
-  <si>
-    <t>BE-09</t>
-  </si>
-  <si>
-    <t>Point the storefront at the database</t>
-  </si>
-  <si>
-    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
-  </si>
-  <si>
-    <t>query.ts was untouched â€” it never knew where products came from.</t>
-  </si>
-  <si>
-    <t>BE-11</t>
-  </si>
-  <si>
-    <t>Order pages restricted to their owner</t>
-  </si>
-  <si>
-    <t>An order was readable by anyone who guessed a sequential reference. Now an admin sees any order, the account that placed it sees it, and a guest sees only an order placed from their own cart.</t>
-  </si>
-  <si>
-    <t>A forbidden order returns 404 rather than 403, so the response cannot be used to discover which references exist.</t>
-  </si>
-  <si>
-    <t>BE-20</t>
-  </si>
-  <si>
-    <t>Build the admin screens behind the dashboard</t>
-  </si>
-  <si>
-    <t>/admin authenticates and shows live figures, but every management screen is still missing: products, categories, suppliers, customers, orders, bulk upload, marketing, reports, settings.</t>
-  </si>
-  <si>
-    <t>Built 16 Aug 2026. Dashboard, products (list, filters, edit, SKUs, price breaks, approval), categories, suppliers, orders, customers, settings and an audit trail. Every write goes through src/lib/admin.ts, which checks the role again in the service layer, records the change, and bumps the catalogue version so the storefront updates without a restart. Bulk upload is BE-04; product image upload is still missing â€” see BE-29.</t>
-  </si>
-  <si>
-    <t>BE-25</t>
-  </si>
-  <si>
-    <t>Invalidate the catalogue cache after a seed or an edit</t>
-  </si>
-  <si>
-    <t>The data layer caches the catalogue for the life of the process, so a running server keeps serving whatever it read first. This is not theoretical: on 15 Aug 2026 the dev server was still showing a retired carton SKU as a purchasable unit chip on the product page, hours after the database had deactivated it.</t>
-  </si>
-  <si>
-    <t>Fixed 15 Aug 2026. The cache now carries the catalogVersion stamp it was built from and re-checks it against the database at most once a second; the seed bumps the stamp, and invalidateCatalog() bumps it too so other server processes drop their copy as well. Verified live: a running dev server went from 71 products to 60 without a restart, and the phantom carton chip disappeared.</t>
+    <t>The admin product screen listed the image files a product references but could not add or replace one, so the only way to give a product a photograph was to put a file on disk and re-seed. That blocked DA-03 and DA-24 from ever being closed by the client rather than by us.</t>
+  </si>
+  <si>
+    <t>Built 16 Aug 2026. Upload, alt text, choose which image the catalogue shows, and remove — on the product screen, through src/lib/admin.ts like every other write, so it is admin-checked, audited and bumps the catalogue version. Files go through the src/lib/storage.ts seam; see DEC-21. Images are accepted on their leading bytes rather than their filename, which turns the DA-25 defect into a refusal at upload time instead of a 400 from the image optimiser at request time. 15 unit tests cover the checks and the key generation. Verified end to end in a browser: a renamed SVG is refused, a real PNG is stored, served and reaches the storefront with no restart, promotion leaves a dense order, removal deletes both the row and the file, and all five actions appear in the audit trail.</t>
   </si>
   <si>
     <t>DN-01</t>
@@ -1797,6 +1809,18 @@
   </si>
   <si>
     <t>Fixed 16 Aug 2026. Parsing moved to src/lib/shipping-address.ts and is shared by the admin order screen, the delivery note and the customer order page, so the three cannot drift. A snapshot that fails to parse now degrades to not recorded rather than throwing.</t>
+  </si>
+  <si>
+    <t>FE-36</t>
+  </si>
+  <si>
+    <t>The 404 page rendered its header and footer twice</t>
+  </si>
+  <si>
+    <t>Introduced by the (shop) route group split in c75b2b5 and live for one commit. An unmatched URL was fine; a notFound() thrown inside the storefront — an unlisted product, an order reference that is not yours — came out with two headers and two footers.</t>
+  </si>
+  <si>
+    <t>Found 16 Aug 2026 by reading a screenshot, not by a test — every automated check passed. The root not-found carries its own chrome because unmatched URLs resolve above every route group, but when notFound() is thrown inside (shop) that same file renders inside the shop layout, which had already supplied it. Fixed by giving (shop) its own not-found with no chrome, both sharing one NotFoundContent component.</t>
   </si>
   <si>
     <t>FN-11</t>
@@ -2389,7 +2413,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2397,7 +2421,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2405,7 +2429,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2413,7 +2437,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2439,7 +2463,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2497,7 +2521,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2547,7 +2571,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2605,7 +2629,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2830,7 +2854,7 @@
         <v>66</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>67</v>
@@ -2838,8 +2862,8 @@
       <c r="D9" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>16</v>
+      <c r="E9" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>38</v>
@@ -2960,7 +2984,7 @@
         <v>86</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>87</v>
@@ -2968,8 +2992,8 @@
       <c r="D14" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>13</v>
+      <c r="E14" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>38</v>
@@ -2992,7 +3016,7 @@
         <v>91</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
@@ -3004,21 +3028,21 @@
         <v>39</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
@@ -3030,7 +3054,7 @@
         <v>39</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3038,7 +3062,7 @@
         <v>96</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>97</v>
@@ -3072,8 +3096,8 @@
       <c r="D18" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>16</v>
+      <c r="E18" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>38</v>
@@ -3090,7 +3114,7 @@
         <v>104</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>105</v>
@@ -3134,21 +3158,21 @@
         <v>39</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
@@ -3160,7 +3184,7 @@
         <v>39</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3168,7 +3192,7 @@
         <v>115</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>116</v>
@@ -3194,7 +3218,7 @@
         <v>119</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>120</v>
@@ -3203,36 +3227,36 @@
         <v>121</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>38</v>
+        <v>14</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>39</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>39</v>
@@ -3255,10 +3279,10 @@
         <v>130</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>39</v>
@@ -3281,10 +3305,10 @@
         <v>134</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>39</v>
@@ -3307,10 +3331,10 @@
         <v>138</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>39</v>
@@ -3336,7 +3360,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>39</v>
@@ -3359,10 +3383,10 @@
         <v>146</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>39</v>
@@ -3376,7 +3400,7 @@
         <v>148</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>149</v>
@@ -3384,11 +3408,11 @@
       <c r="D30" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>13</v>
+      <c r="E30" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>39</v>
@@ -3414,7 +3438,7 @@
         <v>16</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>39</v>
@@ -3436,11 +3460,11 @@
       <c r="D32" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>16</v>
+      <c r="E32" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>39</v>
@@ -3462,11 +3486,11 @@
       <c r="D33" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>14</v>
+      <c r="E33" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>39</v>
@@ -3492,7 +3516,7 @@
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>39</v>
@@ -3514,11 +3538,11 @@
       <c r="D35" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>16</v>
+      <c r="E35" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>39</v>
@@ -3544,7 +3568,7 @@
         <v>13</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>39</v>
@@ -3570,7 +3594,7 @@
         <v>13</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>39</v>
@@ -3596,7 +3620,7 @@
         <v>13</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>39</v>
@@ -3610,7 +3634,7 @@
         <v>184</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>185</v>
@@ -3622,7 +3646,7 @@
         <v>13</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>39</v>
@@ -3648,7 +3672,7 @@
         <v>13</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>39</v>
@@ -3674,7 +3698,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>39</v>
@@ -3696,11 +3720,11 @@
       <c r="D42" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>13</v>
+      <c r="E42" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>39</v>
@@ -3722,11 +3746,11 @@
       <c r="D43" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>15</v>
+      <c r="E43" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>39</v>
@@ -3752,7 +3776,7 @@
         <v>13</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>39</v>
@@ -3778,7 +3802,7 @@
         <v>13</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>39</v>
@@ -3804,7 +3828,7 @@
         <v>13</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>39</v>
@@ -3826,11 +3850,11 @@
       <c r="D47" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="7" t="s">
-        <v>13</v>
+      <c r="E47" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>39</v>
@@ -3852,11 +3876,11 @@
       <c r="D48" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>16</v>
+      <c r="E48" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>39</v>
@@ -3882,7 +3906,7 @@
         <v>13</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>39</v>
@@ -3908,7 +3932,7 @@
         <v>13</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>39</v>
@@ -3922,7 +3946,7 @@
         <v>232</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>233</v>
@@ -3930,11 +3954,11 @@
       <c r="D51" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="E51" s="7" t="s">
-        <v>13</v>
+      <c r="E51" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>39</v>
@@ -3960,7 +3984,7 @@
         <v>16</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>39</v>
@@ -3986,7 +4010,7 @@
         <v>16</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>39</v>
@@ -4008,11 +4032,11 @@
       <c r="D54" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>16</v>
+      <c r="E54" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>39</v>
@@ -4026,7 +4050,7 @@
         <v>248</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>249</v>
@@ -4038,7 +4062,7 @@
         <v>13</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>39</v>
@@ -4060,43 +4084,43 @@
       <c r="D56" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="E56" s="7" t="s">
-        <v>13</v>
+      <c r="E56" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>39</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>255</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C57" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D57" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="E57" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H57" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4116,39 +4140,39 @@
         <v>13</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>39</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>262</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B59" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C59" s="6" t="s">
+      <c r="D59" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="E59" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H59" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4164,43 +4188,43 @@
       <c r="D60" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="E60" s="6" t="s">
-        <v>15</v>
+      <c r="E60" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>39</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>269</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="B61" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C61" s="6" t="s">
+      <c r="D61" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="E61" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H61" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4216,11 +4240,11 @@
       <c r="D62" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>16</v>
+      <c r="E62" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>39</v>
@@ -4234,7 +4258,7 @@
         <v>277</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>278</v>
@@ -4243,36 +4267,36 @@
         <v>279</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>126</v>
+        <v>14</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>280</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>39</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>39</v>
@@ -4286,7 +4310,7 @@
         <v>286</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>287</v>
@@ -4294,11 +4318,11 @@
       <c r="D65" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="E65" s="7" t="s">
-        <v>13</v>
+      <c r="E65" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>39</v>
@@ -4320,11 +4344,11 @@
       <c r="D66" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>16</v>
+      <c r="E66" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>39</v>
@@ -4346,11 +4370,11 @@
       <c r="D67" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="E67" s="7" t="s">
-        <v>13</v>
+      <c r="E67" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>39</v>
@@ -4376,7 +4400,7 @@
         <v>16</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>39</v>
@@ -4402,7 +4426,7 @@
         <v>16</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>39</v>
@@ -4428,7 +4452,7 @@
         <v>16</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>39</v>
@@ -4454,7 +4478,7 @@
         <v>16</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>39</v>
@@ -4480,7 +4504,7 @@
         <v>16</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>39</v>
@@ -4494,7 +4518,7 @@
         <v>318</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>319</v>
@@ -4502,11 +4526,11 @@
       <c r="D73" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>16</v>
+      <c r="E73" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>39</v>
@@ -4532,7 +4556,7 @@
         <v>13</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>39</v>
@@ -4558,7 +4582,7 @@
         <v>13</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>39</v>
@@ -4572,7 +4596,7 @@
         <v>330</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>331</v>
@@ -4580,11 +4604,11 @@
       <c r="D76" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E76" s="7" t="s">
-        <v>13</v>
+      <c r="E76" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>39</v>
@@ -4598,7 +4622,7 @@
         <v>334</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>335</v>
@@ -4606,43 +4630,43 @@
       <c r="D77" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E77" s="6" t="s">
-        <v>16</v>
+      <c r="E77" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>39</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>337</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C78" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D78" s="6" t="s">
         <v>339</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>340</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>39</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>2</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4658,11 +4682,11 @@
       <c r="D79" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="E79" s="7" t="s">
-        <v>13</v>
+      <c r="E79" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>39</v>
@@ -4684,11 +4708,11 @@
       <c r="D80" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="E80" s="6" t="s">
-        <v>16</v>
+      <c r="E80" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>39</v>
@@ -4702,7 +4726,7 @@
         <v>349</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>350</v>
@@ -4714,7 +4738,7 @@
         <v>13</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>39</v>
@@ -4723,34 +4747,8 @@
         <v>352</v>
       </c>
     </row>
-    <row r="82" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>356</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H82"/>
+  <autoFilter ref="A1:H81"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4761,7 +4759,7 @@
   <sheetPr>
     <tabColor rgb="FF29387D"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -4801,526 +4799,552 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H21" s="6" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>437</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H21"/>
+  <autoFilter ref="A1:H22"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5386,7 +5410,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
@@ -5412,7 +5436,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
@@ -5438,7 +5462,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
@@ -5464,7 +5488,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
@@ -5490,7 +5514,7 @@
         <v>16</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
@@ -5516,7 +5540,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>7</v>
@@ -5537,7 +5561,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -5595,7 +5619,7 @@
         <v>38</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>464</v>
@@ -5621,7 +5645,7 @@
         <v>38</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>468</v>
@@ -5647,7 +5671,7 @@
         <v>38</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>472</v>
@@ -5658,7 +5682,7 @@
         <v>473</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>474</v>
@@ -5673,7 +5697,7 @@
         <v>38</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>476</v>
@@ -5699,7 +5723,7 @@
         <v>38</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>480</v>
@@ -5725,7 +5749,7 @@
         <v>38</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>484</v>
@@ -5736,7 +5760,7 @@
         <v>485</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>360</v>
+        <v>22</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>486</v>
@@ -5751,7 +5775,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>488</v>
@@ -5762,7 +5786,7 @@
         <v>489</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>490</v>
@@ -5777,24 +5801,24 @@
         <v>38</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
@@ -5803,24 +5827,24 @@
         <v>38</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
@@ -5829,10 +5853,10 @@
         <v>38</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -5840,7 +5864,7 @@
         <v>499</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>500</v>
@@ -5855,7 +5879,7 @@
         <v>38</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>502</v>
@@ -5866,7 +5890,7 @@
         <v>503</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>504</v>
@@ -5881,7 +5905,7 @@
         <v>38</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>506</v>
@@ -5892,7 +5916,7 @@
         <v>507</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>508</v>
@@ -5907,7 +5931,7 @@
         <v>38</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>510</v>
@@ -5918,7 +5942,7 @@
         <v>511</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>512</v>
@@ -5933,7 +5957,7 @@
         <v>38</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>514</v>
@@ -5944,7 +5968,7 @@
         <v>515</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>516</v>
@@ -5959,7 +5983,7 @@
         <v>38</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>518</v>
@@ -5970,7 +5994,7 @@
         <v>519</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>520</v>
@@ -5985,7 +6009,7 @@
         <v>38</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>522</v>
@@ -5996,7 +6020,7 @@
         <v>523</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>524</v>
@@ -6011,7 +6035,7 @@
         <v>38</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>526</v>
@@ -6022,7 +6046,7 @@
         <v>527</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>528</v>
@@ -6037,7 +6061,7 @@
         <v>38</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>530</v>
@@ -6048,7 +6072,7 @@
         <v>531</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>532</v>
@@ -6063,7 +6087,7 @@
         <v>38</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>534</v>
@@ -6074,7 +6098,7 @@
         <v>535</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>536</v>
@@ -6089,7 +6113,7 @@
         <v>38</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>538</v>
@@ -6100,7 +6124,7 @@
         <v>539</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>540</v>
@@ -6115,7 +6139,7 @@
         <v>38</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>542</v>
@@ -6126,7 +6150,7 @@
         <v>543</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>544</v>
@@ -6141,7 +6165,7 @@
         <v>38</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>546</v>
@@ -6152,7 +6176,7 @@
         <v>547</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>22</v>
+        <v>356</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>548</v>
@@ -6163,11 +6187,11 @@
       <c r="E24" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>126</v>
+      <c r="F24" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>550</v>
@@ -6178,7 +6202,7 @@
         <v>551</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>552</v>
@@ -6186,14 +6210,14 @@
       <c r="D25" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>13</v>
+      <c r="E25" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>554</v>
@@ -6204,7 +6228,7 @@
         <v>555</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>556</v>
@@ -6212,14 +6236,14 @@
       <c r="D26" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>16</v>
+      <c r="E26" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>558</v>
@@ -6230,7 +6254,7 @@
         <v>559</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>560</v>
@@ -6242,10 +6266,10 @@
         <v>16</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>562</v>
@@ -6256,7 +6280,7 @@
         <v>563</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>564</v>
@@ -6268,39 +6292,39 @@
         <v>16</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>453</v>
+        <v>566</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>569</v>
+        <v>453</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6308,7 +6332,7 @@
         <v>570</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>571</v>
@@ -6320,10 +6344,10 @@
         <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>573</v>
@@ -6334,7 +6358,7 @@
         <v>574</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>575</v>
@@ -6346,10 +6370,10 @@
         <v>16</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>577</v>
@@ -6360,7 +6384,7 @@
         <v>578</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>579</v>
@@ -6372,10 +6396,10 @@
         <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>581</v>
@@ -6386,7 +6410,7 @@
         <v>582</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>583</v>
@@ -6398,10 +6422,10 @@
         <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>585</v>
@@ -6412,7 +6436,7 @@
         <v>586</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>26</v>
+        <v>356</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>587</v>
@@ -6424,10 +6448,10 @@
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>589</v>
@@ -6450,10 +6474,10 @@
         <v>16</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>593</v>
@@ -6464,7 +6488,7 @@
         <v>594</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>595</v>
@@ -6476,10 +6500,10 @@
         <v>16</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>597</v>
@@ -6490,7 +6514,7 @@
         <v>598</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>599</v>
@@ -6502,10 +6526,10 @@
         <v>16</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>601</v>
@@ -6516,7 +6540,7 @@
         <v>602</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>603</v>
@@ -6527,11 +6551,11 @@
       <c r="E38" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F38" s="10" t="s">
-        <v>284</v>
+      <c r="F38" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>605</v>
@@ -6542,7 +6566,7 @@
         <v>606</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>607</v>
@@ -6550,14 +6574,14 @@
       <c r="D39" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>284</v>
+      <c r="E39" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>609</v>
@@ -6568,7 +6592,7 @@
         <v>610</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>611</v>
@@ -6576,14 +6600,14 @@
       <c r="D40" s="6" t="s">
         <v>612</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>13</v>
+      <c r="E40" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>613</v>
@@ -6602,14 +6626,14 @@
       <c r="D41" s="6" t="s">
         <v>616</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>16</v>
+      <c r="E41" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>617</v>
@@ -6620,7 +6644,7 @@
         <v>618</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>619</v>
@@ -6628,21 +6652,73 @@
       <c r="D42" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>16</v>
+      <c r="E42" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>621</v>
       </c>
     </row>
+    <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>629</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H42"/>
+  <autoFilter ref="A1:H44"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="659">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -98,6 +98,9 @@
     <t>Frontend</t>
   </si>
   <si>
+    <t>Note</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
@@ -215,6 +218,18 @@
     <t>A supplier must never be able to approve their own product â€” the rule to enforce when editing lands.</t>
   </si>
   <si>
+    <t>BE-30</t>
+  </si>
+  <si>
+    <t>Capture supplier sub-order lifecycle timestamps and an immutable status log</t>
+  </si>
+  <si>
+    <t>Nothing records when a supplier acknowledged, dispatched or delivered a sub-order, so no fulfilment or lead-time question can be answered about any supplier. Unlike most gaps this one cannot be repaired later: a timestamp not captured at the moment it happened is gone, and the same reasoning already applied to SkuBatch under FN-09.</t>
+  </si>
+  <si>
+    <t>From docs/DASHBOARD_METRICS_SPEC.md sections 1.1 and 5.3. Cheap now, impossible to backfill, and it must be in place before the first real order or the first months of trading are unmeasurable. OrderSupplierInvoice is already the sub-order and already has status, so this is timestamp columns plus a log table, not a new entity. AuditLog is close but generic and admin-scoped; a typed log keyed to the sub-order is what the metrics need. Pairs naturally with BE-21, which builds the screens that would set these.</t>
+  </si>
+  <si>
     <t>DA-01</t>
   </si>
   <si>
@@ -569,6 +584,42 @@
     <t>Schema allows it via Supplier.userId; supporting several needs a join table.</t>
   </si>
   <si>
+    <t>BE-31</t>
+  </si>
+  <si>
+    <t>Log every out-of-stock toggle instead of only the current flag</t>
+  </si>
+  <si>
+    <t>The manual out-of-stock checkbox stores current state only. How long a product has been unavailable, and how quickly a supplier restocks, are unanswerable — and both are conversations the admin has with suppliers.</t>
+  </si>
+  <si>
+    <t>From spec section 1.4. Same one-way-door property as BE-30: every toggle that happens before this exists is lost. Small change — a log table written from the same service function that sets the flag.</t>
+  </si>
+  <si>
+    <t>BE-32</t>
+  </si>
+  <si>
+    <t>Log storefront searches, especially the ones that return nothing</t>
+  </si>
+  <si>
+    <t>A search that returns no results is a customer telling you what to stock, and it is currently discarded. For a distributor deciding what to source next, the list of terms that found nothing is one of the most valuable things the site can produce.</t>
+  </si>
+  <si>
+    <t>From spec section 2.4 D-2. Cannot be reconstructed later — nobody can recall what a visitor searched for last month. Distinct from FN-10 (search is client-side only), though doing FN-10 first would make the logging server-side and simpler.</t>
+  </si>
+  <si>
+    <t>BE-33</t>
+  </si>
+  <si>
+    <t>Record what each supplier has promised: lead time and acknowledgement SLA</t>
+  </si>
+  <si>
+    <t>On-time means nothing without a promise to measure against. These are numbers agreed personally with each supplier during onboarding, and there is nowhere to put them.</t>
+  </si>
+  <si>
+    <t>From spec section 1.2. Two integer columns on Supplier plus admin fields, but note the dependency runs the other way: the numbers are a business input the admin has to collect from each supplier, so ask for them before building anything that displays an on-time rate.</t>
+  </si>
+  <si>
     <t>DA-02</t>
   </si>
   <si>
@@ -761,6 +812,30 @@
     <t>Schema-shaping â€” decide before the backend is built.</t>
   </si>
   <si>
+    <t>FN-12</t>
+  </si>
+  <si>
+    <t>Nothing shows which clients are overdue to reorder</t>
+  </si>
+  <si>
+    <t>In a reorder-first business this is the single most useful signal there is: a clinic that buys gloves every three weeks and has not ordered in five needs a phone call. It is computable from order history alone once there are three orders per client — no new data capture required.</t>
+  </si>
+  <si>
+    <t>From spec sections 2.3 C-4 and C-5 and queue Q-3. Unlike BE-30 to BE-32 this is not urgent, because the underlying order history is already being recorded and the calculation can be added at any time. Build it once real clients are ordering; with four test orders it would only ever say insufficient data.</t>
+  </si>
+  <si>
+    <t>FN-13</t>
+  </si>
+  <si>
+    <t>The client account has no Buy Again</t>
+  </si>
+  <si>
+    <t>A returning buyer has to search for products they have already bought. For a reorder-first marketplace this is the shortest path between the platform and revenue, and it needs no metrics work at all — just their own order history, sorted by how often they buy each line.</t>
+  </si>
+  <si>
+    <t>From spec section 4 CL-1 and CL-3. Independent of the whole metrics programme and arguably worth more than any dashboard in it. Depends on nothing that is not already built.</t>
+  </si>
+  <si>
     <t>IN-01</t>
   </si>
   <si>
@@ -1893,6 +1968,18 @@
   </si>
   <si>
     <t>Fixed 15 Aug 2026: the four files were deleted and their products now fall back to the placeholder. scripts/check-catalog.mjs now sniffs magic bytes rather than trusting the extension, so a file that is not really an image fails the build. Affected the two HiSmile lines, Neutrogena Ultra Sheer and the Roger Armstrong thermometer.</t>
+  </si>
+  <si>
+    <t>DN-22</t>
+  </si>
+  <si>
+    <t>The dashboard metrics spec is an idea source, not a plan</t>
+  </si>
+  <si>
+    <t>A specification document generated on 16 Aug 2026 proposes roughly sixty metrics across three dashboards. It was written without sight of this codebase, so it assumes work that is already done and priorities that are not ours.</t>
+  </si>
+  <si>
+    <t>Installed at docs/DASHBOARD_METRICS_SPEC.md and framed in CLAUDE.md, with its known errors listed so nobody re-derives them — most importantly that OrderSupplierInvoice is already the supplier sub-order it asks to be created. Its genuinely new ideas were extracted into BE-30 to BE-33, FN-12 and FN-13; the rest is either already registered, already built, or cannot be validated until there is real trading data. Client decision 16 Aug 2026: treat it as idea generation, our judgement ranks above it.</t>
   </si>
   <si>
     <t>FE-35</t>
@@ -2380,7 +2467,7 @@
   <sheetPr>
     <tabColor rgb="FF29387D"/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2413,7 +2500,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2429,7 +2516,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2437,7 +2524,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2463,7 +2550,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2471,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2521,7 +2608,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="3">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2563,7 +2650,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2571,7 +2658,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2611,6 +2698,14 @@
         <v>26</v>
       </c>
       <c r="B32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2629,7 +2724,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2643,597 +2738,597 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>13</v>
+        <v>69</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>16</v>
+        <v>89</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="E16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>13</v>
+        <v>103</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>122</v>
+        <v>13</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>123</v>
@@ -3253,1108 +3348,1108 @@
         <v>126</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>16</v>
+        <v>151</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>14</v>
+        <v>159</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>16</v>
+        <v>163</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>13</v>
+        <v>171</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>13</v>
+        <v>191</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>13</v>
+        <v>195</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>13</v>
+        <v>215</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>16</v>
+        <v>219</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>16</v>
+        <v>239</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>16</v>
+        <v>243</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>13</v>
+        <v>251</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>2</v>
+        <v>256</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>13</v>
+        <v>259</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>2</v>
+        <v>264</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>13</v>
+        <v>271</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>2</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>16</v>
+        <v>275</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>13</v>
+        <v>279</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F63" s="10" t="s">
-        <v>280</v>
+        <v>13</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F64" s="10" t="s">
-        <v>280</v>
+      <c r="F64" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>285</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>280</v>
+        <v>15</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F66" s="10" t="s">
-        <v>280</v>
+      <c r="F66" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>293</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4362,7 +4457,7 @@
         <v>294</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>295</v>
@@ -4373,11 +4468,11 @@
       <c r="E67" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F67" s="10" t="s">
-        <v>280</v>
+      <c r="F67" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>297</v>
@@ -4388,7 +4483,7 @@
         <v>298</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>299</v>
@@ -4396,14 +4491,14 @@
       <c r="D68" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>280</v>
+      <c r="E68" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>301</v>
@@ -4414,7 +4509,7 @@
         <v>302</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>303</v>
@@ -4422,333 +4517,489 @@
       <c r="D69" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>16</v>
+      <c r="E69" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="70" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>16</v>
+        <v>309</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="71" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="72" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>16</v>
+        <v>317</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="73" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>13</v>
+        <v>321</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="74" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>13</v>
+        <v>325</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="75" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>13</v>
+        <v>329</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="76" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>13</v>
+        <v>337</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>2</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>13</v>
+        <v>341</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>16</v>
+        <v>345</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>377</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H81"/>
+  <autoFilter ref="A1:H87"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4773,574 +5024,574 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>401</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -5369,152 +5620,152 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>442</v>
+        <v>467</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>444</v>
+        <v>469</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>449</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>452</v>
+        <v>477</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
@@ -5525,28 +5776,28 @@
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>459</v>
+        <v>484</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>460</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -5561,7 +5812,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -5575,1150 +5826,1176 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>461</v>
+        <v>486</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>469</v>
+        <v>494</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>471</v>
+        <v>496</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>472</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>476</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>477</v>
+        <v>502</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>478</v>
+        <v>503</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>483</v>
+        <v>508</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>484</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>485</v>
+        <v>510</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>487</v>
+        <v>512</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>488</v>
+        <v>513</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>489</v>
+        <v>514</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>494</v>
+        <v>519</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>496</v>
+        <v>521</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>497</v>
+        <v>522</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>499</v>
+        <v>524</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>501</v>
+        <v>526</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>502</v>
+        <v>527</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>506</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>507</v>
+        <v>532</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>508</v>
+        <v>533</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>509</v>
+        <v>534</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>510</v>
+        <v>535</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>513</v>
+        <v>538</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>514</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>515</v>
+        <v>540</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>516</v>
+        <v>541</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>517</v>
+        <v>542</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>518</v>
+        <v>543</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>521</v>
+        <v>546</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>523</v>
+        <v>548</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>526</v>
+        <v>551</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>527</v>
+        <v>552</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>528</v>
+        <v>553</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>530</v>
+        <v>555</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>531</v>
+        <v>556</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>532</v>
+        <v>557</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>533</v>
+        <v>558</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>534</v>
+        <v>559</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>535</v>
+        <v>560</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>538</v>
+        <v>563</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>540</v>
+        <v>565</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>542</v>
+        <v>567</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>544</v>
+        <v>569</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>545</v>
+        <v>570</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>546</v>
+        <v>571</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>547</v>
+        <v>572</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>548</v>
+        <v>573</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>549</v>
+        <v>574</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>550</v>
+        <v>575</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>552</v>
+        <v>577</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>553</v>
+        <v>578</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>556</v>
+        <v>581</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>557</v>
+        <v>582</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>558</v>
+        <v>583</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>559</v>
+        <v>584</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>561</v>
+        <v>586</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>562</v>
+        <v>587</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>563</v>
+        <v>588</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>565</v>
+        <v>590</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>566</v>
+        <v>591</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>569</v>
+        <v>594</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>573</v>
+        <v>598</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>574</v>
+        <v>599</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>576</v>
+        <v>601</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>582</v>
+        <v>607</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>585</v>
+        <v>610</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>586</v>
+        <v>611</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>587</v>
+        <v>612</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>588</v>
+        <v>613</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>589</v>
+        <v>614</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>590</v>
+        <v>615</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>592</v>
+        <v>617</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>593</v>
+        <v>618</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>595</v>
+        <v>620</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>598</v>
+        <v>623</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>602</v>
+        <v>627</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>604</v>
+        <v>629</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>605</v>
+        <v>630</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>606</v>
+        <v>631</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>607</v>
+        <v>632</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>608</v>
+        <v>633</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>609</v>
+        <v>634</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>610</v>
+        <v>635</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>612</v>
+        <v>637</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>613</v>
+        <v>638</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>614</v>
+        <v>639</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>615</v>
+        <v>640</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>616</v>
+        <v>641</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>617</v>
+        <v>642</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>618</v>
+        <v>643</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>619</v>
+        <v>644</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>620</v>
+        <v>645</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>621</v>
+        <v>646</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>622</v>
+        <v>647</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>624</v>
+        <v>649</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>625</v>
+        <v>650</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="B44" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>627</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>628</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="G44" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>629</v>
+      <c r="C45" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>658</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H44"/>
+  <autoFilter ref="A1:H45"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="672">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -140,7 +140,220 @@
     <t>Open</t>
   </si>
   <si>
-    <t>Omron currently reads 1-2: AED 186.99 / 3+: AED 179.99. Supplier 20's product 183 ([1,5,10]-&gt;[100,95,90]) was the only well-formed example and set the interpretation.</t>
+    <t>Decided with the client 16 Aug 2026. Superseded in practice: real break quantities and prices come in through the upload template, so the repaired guesses are deleted on import. What survives is the convention the importer enforces, which the database already requires and which is unit tested: breaks must ascend by quantity and descend in price, and a row violating it is rejected rather than loaded.</t>
+  </si>
+  <si>
+    <t>AC-03</t>
+  </si>
+  <si>
+    <t>Capture the Tax Registration Number (TRN)</t>
+  </si>
+  <si>
+    <t>A UAE tax invoice must show the supplier TRN. It is not captured or displayed anywhere.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. AussieMed is the seller of record and issues one invoice to the customer — see DEC-22. Required: AussieMed's own TRN held in Settings and printed on every invoice, and the customer's TRN captured at signup or checkout, since a UAE tax invoice must carry the recipient's TRN above AED 10,000. Supplier TRNs are still needed, but for supplier-to-AussieMed invoicing and settlement rather than for the customer's document.</t>
+  </si>
+  <si>
+    <t>AC-04</t>
+  </si>
+  <si>
+    <t>Make order documents compliant tax invoices</t>
+  </si>
+  <si>
+    <t>The order page is a summary, not a compliant tax invoice. UAE FTA mandates specific fields.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. Scope changed by DEC-22. The customer receives a single AussieMed tax invoice, not one document per supplier, so the existing tax invoice page needs rework: the per-supplier split stays in the data and on the internal picking list and delivery note, but is no longer the customer-facing document structure. Confirm the FTA-mandated field list before that rework, so it is done once.</t>
+  </si>
+  <si>
+    <t>BE-01</t>
+  </si>
+  <si>
+    <t>Build the backend</t>
+  </si>
+  <si>
+    <t>Express and Prisma per extraction/BACKEND_SPEC.md: roles, auth, orders, invoices, emails. Eight phases.</t>
+  </si>
+  <si>
+    <t>In progress</t>
+  </si>
+  <si>
+    <t>Phase 1 started. Schema designed and migrated: 30 tables, 19 unique constraints. Application code not started.</t>
+  </si>
+  <si>
+    <t>BE-03</t>
+  </si>
+  <si>
+    <t>Build the supplier portal</t>
+  </si>
+  <si>
+    <t>Suppliers manage their own products but can never self-approve. Must have a failing-then-passing test.</t>
+  </si>
+  <si>
+    <t>The dashboard exists at /business-portal and is role-guarded and supplier-scoped. The editing screens behind it do not â€” BE-21 tracks those. Approval is an admin-only transition enforced in the service layer.</t>
+  </si>
+  <si>
+    <t>BE-21</t>
+  </si>
+  <si>
+    <t>Build the supplier portal behind its dashboard</t>
+  </si>
+  <si>
+    <t>The business portal authenticates and shows a supplier their own products and invoice lines, read-only. Creating and editing products, toggling stock and bulk upload are not built.</t>
+  </si>
+  <si>
+    <t>A supplier must never be able to approve their own product â€” the rule to enforce when editing lands.</t>
+  </si>
+  <si>
+    <t>BE-30</t>
+  </si>
+  <si>
+    <t>Capture supplier sub-order lifecycle timestamps and an immutable status log</t>
+  </si>
+  <si>
+    <t>Nothing records when a supplier acknowledged, dispatched or delivered a sub-order, so no fulfilment or lead-time question can be answered about any supplier. Unlike most gaps this one cannot be repaired later: a timestamp not captured at the moment it happened is gone, and the same reasoning already applied to SkuBatch under FN-09.</t>
+  </si>
+  <si>
+    <t>From docs/DASHBOARD_METRICS_SPEC.md sections 1.1 and 5.3. Cheap now, impossible to backfill, and it must be in place before the first real order or the first months of trading are unmeasurable. OrderSupplierInvoice is already the sub-order and already has status, so this is timestamp columns plus a log table, not a new entity. AuditLog is close but generic and admin-scoped; a typed log keyed to the sub-order is what the metrics need. Pairs naturally with BE-21, which builds the screens that would set these.</t>
+  </si>
+  <si>
+    <t>DA-01</t>
+  </si>
+  <si>
+    <t>Supply the real product catalogue</t>
+  </si>
+  <si>
+    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. The real catalogue arrives through the bulk upload tool (BE-04), not as a one-off import, so the client can re-upload whenever it changes and suppliers can maintain their own lines later. Sequencing is the client's: they review how products list and display against the current placeholder catalogue first, then populate the template. The seeded products therefore stay for now as a working backdrop, and this no longer blocks build work.</t>
+  </si>
+  <si>
+    <t>DA-03</t>
+  </si>
+  <si>
+    <t>Supply product photography</t>
+  </si>
+  <si>
+    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. Photography arrives in bulk, as a folder of files named by SKU code, matched during the same catalogue import. The per-product upload built under BE-29 remains available for corrections. Raised with the client: manufacturer imagery is usually conditional on being an authorised distributor, so replacing Livingstone's photographs with manufacturer photographs may swap one rights problem for another.</t>
+  </si>
+  <si>
+    <t>DA-06</t>
+  </si>
+  <si>
+    <t>Supply the real supplier list</t>
+  </si>
+  <si>
+    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. The client adds real suppliers through the admin screens, which are built. The four placeholders are deleted as the real ones land. Capture promised lead time and acknowledgement window on the same form (BE-33) so the numbers are collected once during onboarding rather than revisited per supplier later.</t>
+  </si>
+  <si>
+    <t>DA-17</t>
+  </si>
+  <si>
+    <t>Replace the test supplier attribution</t>
+  </si>
+  <si>
+    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
+  </si>
+  <si>
+    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
+  </si>
+  <si>
+    <t>DA-20</t>
+  </si>
+  <si>
+    <t>Supply the real packaging quantities</t>
+  </si>
+  <si>
+    <t>OUR INVENTED VALUES: how many units make a carton, and how many cartons make a box, are guessed per product family (12 and 4 by default, 10 and 5 for gloves, 20 and 5 for masks). The break discounts of 4% and 8% are also invented.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. Packaging levels and break prices become columns in the upload template and are supplied per product, replacing the invented 12/4, gloves 10/5, masks 20/5 and the invented 4% and 8% discounts. Until the real catalogue lands these remain visible to buyers as factual claims about packaging, which is acceptable only because there are no real customers.</t>
+  </si>
+  <si>
+    <t>FN-02</t>
+  </si>
+  <si>
+    <t>Quote requests are not delivered</t>
+  </si>
+  <si>
+    <t>Captured in the browser only.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend and an email provider.</t>
+  </si>
+  <si>
+    <t>FN-03</t>
+  </si>
+  <si>
+    <t>Bulk buy enquiries are not delivered</t>
+  </si>
+  <si>
+    <t>FN-04</t>
+  </si>
+  <si>
+    <t>Notify Me does not register a subscription</t>
+  </si>
+  <si>
+    <t>Captured locally. The restock email flow does not exist.</t>
+  </si>
+  <si>
+    <t>Blocked on the backend.</t>
+  </si>
+  <si>
+    <t>IN-06</t>
+  </si>
+  <si>
+    <t>Remove noindex before launch</t>
+  </si>
+  <si>
+    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
+  </si>
+  <si>
+    <t>Must be removed deliberately at launch â€” and only then.</t>
+  </si>
+  <si>
+    <t>LG-01</t>
+  </si>
+  <si>
+    <t>Supply terms and conditions</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. Claude drafts a plain-English starting point describing how the platform actually behaves — payment terms and late payment, delivery and title transfer, returns of sterile or short-dated stock, and supplier non-fulfilment — for the client to edit and have reviewed. This is structure and description, not legal advice, and must be reviewed by someone qualified before launch.</t>
+  </si>
+  <si>
+    <t>LG-02</t>
+  </si>
+  <si>
+    <t>Supply the privacy policy</t>
+  </si>
+  <si>
+    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. Claude drafts a starting point describing what the platform actually collects: trade account details, order history, and the addresses held against an organisation. Same caveat as LG-01 — a draft to react to, not legal advice.</t>
+  </si>
+  <si>
+    <t>SEC-01</t>
+  </si>
+  <si>
+    <t>Remove the test credentials before any deployment</t>
+  </si>
+  <si>
+    <t>Four accounts share the password 123456: admin, musawi1989@gmail.com, supplier1, supplier2. Fine on a laptop, unacceptable anywhere else.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. Plan agreed: the supplier test accounts are deleted and real passwords forced on the admin and owner accounts as part of the deploy, not before, since they are needed while building. The on-screen credentials panel already renders only outside production, so a production build cannot leak it.</t>
   </si>
   <si>
     <t>AC-02</t>
@@ -152,184 +365,1387 @@
     <t>23 of 61 lines are classified zero-rated rather than 5%. Classified by reading product names, which is not good enough for tax. Charging VAT on a zero-rated line misstates a document the customer keeps.</t>
   </si>
   <si>
-    <t>Currently zero-rated: gloves, masks, respirators, gowns, syringes, needles, lancets, cannulae, gauze, dressings, bandages, sutures, catheters, incontinence, thermometers, oximeters, sphygmomanometers, stethoscopes.</t>
-  </si>
-  <si>
-    <t>AC-03</t>
-  </si>
-  <si>
-    <t>Capture the Tax Registration Number (TRN)</t>
-  </si>
-  <si>
-    <t>A UAE tax invoice must show the supplier TRN. It is not captured or displayed anywhere.</t>
-  </si>
-  <si>
-    <t>Needed for both AussieMed and each supplier if suppliers invoice in their own name.</t>
-  </si>
-  <si>
-    <t>AC-04</t>
-  </si>
-  <si>
-    <t>Make order documents compliant tax invoices</t>
-  </si>
-  <si>
-    <t>The order page is a summary, not a compliant tax invoice. UAE FTA mandates specific fields.</t>
-  </si>
-  <si>
-    <t>Confirm required fields before the backend generates invoices.</t>
-  </si>
-  <si>
-    <t>BE-01</t>
-  </si>
-  <si>
-    <t>Build the backend</t>
-  </si>
-  <si>
-    <t>Express and Prisma per extraction/BACKEND_SPEC.md: roles, auth, orders, invoices, emails. Eight phases.</t>
-  </si>
-  <si>
-    <t>In progress</t>
-  </si>
-  <si>
-    <t>Phase 1 started. Schema designed and migrated: 30 tables, 19 unique constraints. Application code not started.</t>
-  </si>
-  <si>
-    <t>BE-03</t>
-  </si>
-  <si>
-    <t>Build the supplier portal</t>
-  </si>
-  <si>
-    <t>Suppliers manage their own products but can never self-approve. Must have a failing-then-passing test.</t>
-  </si>
-  <si>
-    <t>The dashboard exists at /business-portal and is role-guarded and supplier-scoped. The editing screens behind it do not â€” BE-21 tracks those. Approval is an admin-only transition enforced in the service layer.</t>
-  </si>
-  <si>
-    <t>BE-21</t>
-  </si>
-  <si>
-    <t>Build the supplier portal behind its dashboard</t>
-  </si>
-  <si>
-    <t>The business portal authenticates and shows a supplier their own products and invoice lines, read-only. Creating and editing products, toggling stock and bulk upload are not built.</t>
-  </si>
-  <si>
-    <t>A supplier must never be able to approve their own product â€” the rule to enforce when editing lands.</t>
-  </si>
-  <si>
-    <t>BE-30</t>
-  </si>
-  <si>
-    <t>Capture supplier sub-order lifecycle timestamps and an immutable status log</t>
-  </si>
-  <si>
-    <t>Nothing records when a supplier acknowledged, dispatched or delivered a sub-order, so no fulfilment or lead-time question can be answered about any supplier. Unlike most gaps this one cannot be repaired later: a timestamp not captured at the moment it happened is gone, and the same reasoning already applied to SkuBatch under FN-09.</t>
-  </si>
-  <si>
-    <t>From docs/DASHBOARD_METRICS_SPEC.md sections 1.1 and 5.3. Cheap now, impossible to backfill, and it must be in place before the first real order or the first months of trading are unmeasurable. OrderSupplierInvoice is already the sub-order and already has status, so this is timestamp columns plus a log table, not a new entity. AuditLog is close but generic and admin-scoped; a typed log keyed to the sub-order is what the metrics need. Pairs naturally with BE-21, which builds the screens that would set these.</t>
-  </si>
-  <si>
-    <t>DA-01</t>
-  </si>
-  <si>
-    <t>Supply the real product catalogue</t>
-  </si>
-  <si>
-    <t>60 of 71 products are seeded from Livingstone and Chemist Warehouse public catalogues for testing. Only 11 are AussieMed products and they carry no categories or images.</t>
-  </si>
-  <si>
-    <t>Seeds live in scripts/seed-catalogue.mjs and are flagged isPlaceholder. Factual data only; descriptions are generated and no supplier imagery is used. Prices are AUD converted at 2.42 for testing.</t>
-  </si>
-  <si>
-    <t>DA-03</t>
-  </si>
-  <si>
-    <t>Supply product photography</t>
-  </si>
-  <si>
-    <t>AussieMed has almost no imagery of its own: only 2 usable photos in the whole extraction. The 52 images now on the site are the seed suppliers own photographs used for local testing and cannot ship.</t>
-  </si>
-  <si>
-    <t>Seed images live in public/products/seed and are deletable in one command. 19 products still fall back to the generated tile.</t>
-  </si>
-  <si>
-    <t>DA-06</t>
-  </si>
-  <si>
-    <t>Supply the real supplier list</t>
-  </si>
-  <si>
-    <t>Four suppliers exist: two carried over from the extraction with invented names and two test suppliers (Livingstone and Chemist Warehouse) whose catalogues seeded the products.</t>
-  </si>
-  <si>
-    <t>All are flagged isPlaceholder in the data.</t>
-  </si>
-  <si>
-    <t>DA-17</t>
-  </si>
-  <si>
-    <t>Replace the test supplier attribution</t>
-  </si>
-  <si>
-    <t>Livingstone and Chemist Warehouse are listed as suppliers for testing only. They are unaffiliated third parties and must not appear on a live storefront.</t>
-  </si>
-  <si>
-    <t>Remove scripts/seed-catalogue.mjs when the real catalogue lands.</t>
-  </si>
-  <si>
-    <t>DA-20</t>
-  </si>
-  <si>
-    <t>Supply the real packaging quantities</t>
-  </si>
-  <si>
-    <t>OUR INVENTED VALUES: how many units make a carton, and how many cartons make a box, are guessed per product family (12 and 4 by default, 10 and 5 for gloves, 20 and 5 for masks). The break discounts of 4% and 8% are also invented.</t>
-  </si>
-  <si>
-    <t>These are now shown to buyers as CARTON and BOX, so a wrong number reads as a factual claim about your packaging. In scripts/variants.mjs.</t>
-  </si>
-  <si>
-    <t>FN-02</t>
-  </si>
-  <si>
-    <t>Quote requests are not delivered</t>
-  </si>
-  <si>
-    <t>Captured in the browser only.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend and an email provider.</t>
-  </si>
-  <si>
-    <t>FN-03</t>
-  </si>
-  <si>
-    <t>Bulk buy enquiries are not delivered</t>
-  </si>
-  <si>
-    <t>FN-04</t>
-  </si>
-  <si>
-    <t>Notify Me does not register a subscription</t>
-  </si>
-  <si>
-    <t>Captured locally. The restock email flow does not exist.</t>
-  </si>
-  <si>
-    <t>Blocked on the backend.</t>
-  </si>
-  <si>
-    <t>IN-06</t>
-  </si>
-  <si>
-    <t>Remove noindex before launch</t>
-  </si>
-  <si>
-    <t>The site is set to noindex, nofollow site-wide so it cannot be indexed while in development.</t>
-  </si>
-  <si>
-    <t>Must be removed deliberately at launch â€” and only then.</t>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. Client's position: these are placeholder products and their values should not be over-weighted. Tax class becomes a column in the upload template, so classification is decided per product when the real catalogue lands rather than inherited from a script that matched product names. A best-effort default is applied meanwhile. This is not a professional ruling and must still be confirmed against the real range before any real order is priced, but it is no longer a decision blocking build work.</t>
+  </si>
+  <si>
+    <t>AC-05</t>
+  </si>
+  <si>
+    <t>Confirm the VAT rate and whether it must be configurable</t>
+  </si>
+  <si>
+    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
+  </si>
+  <si>
+    <t>Rate must be stored on the order at the time it is placed.</t>
+  </si>
+  <si>
+    <t>AC-06</t>
+  </si>
+  <si>
+    <t>Approve the reference number format</t>
+  </si>
+  <si>
+    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
+  </si>
+  <si>
+    <t>Wording is fixed as Reference number, never order number.</t>
+  </si>
+  <si>
+    <t>AC-07</t>
+  </si>
+  <si>
+    <t>Approve the supplier invoice numbering</t>
+  </si>
+  <si>
+    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
+  </si>
+  <si>
+    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
+  </si>
+  <si>
+    <t>AC-09</t>
+  </si>
+  <si>
+    <t>Decide payment terms and credit accounts</t>
+  </si>
+  <si>
+    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
+  </si>
+  <si>
+    <t>Affects the schema â€” decide before the backend.</t>
+  </si>
+  <si>
+    <t>AC-11</t>
+  </si>
+  <si>
+    <t>Approve the VAT rounding method on invoices</t>
+  </si>
+  <si>
+    <t>VAT is rounded per line rather than once per invoice, so the printed lines always add up to the printed total. The alternative rounds once and can leave lines that do not sum.</t>
+  </si>
+  <si>
+    <t>Verified by test: per-invoice VAT sums to the order VAT exactly.</t>
+  </si>
+  <si>
+    <t>AC-12</t>
+  </si>
+  <si>
+    <t>Confirm the reference number sequence resets each year</t>
+  </si>
+  <si>
+    <t>OUR DECISION: the sequence restarts at 000001 each calendar year, so AM-2026-000001 and AM-2027-000001 can both exist. If accounting needs a single unbroken sequence this must change before real orders.</t>
+  </si>
+  <si>
+    <t>Held in a settings row keyed orderSequence:YYYY and incremented inside the checkout transaction.</t>
+  </si>
+  <si>
+    <t>AC-13</t>
+  </si>
+  <si>
+    <t>Decide whether an order should reserve stock</t>
+  </si>
+  <si>
+    <t>OUR DECISION: checkout does not decrement or reserve anything, because there are no stock levels â€” only an in/out flag. Two customers can order the last unit.</t>
+  </si>
+  <si>
+    <t>Depends on FN-08. Out-of-stock is re-checked at checkout, so a line that sold out while the form was open is rejected.</t>
+  </si>
+  <si>
+    <t>BE-04</t>
+  </si>
+  <si>
+    <t>Build comma-safe .xlsx bulk upload</t>
+  </si>
+  <si>
+    <t>Parsed natively with exceljs, never by splitting on commas â€” that is what broke comma-containing category names.</t>
+  </si>
+  <si>
+    <t>Unknown brands must be reported per row, never skipped silently.</t>
+  </si>
+  <si>
+    <t>BE-05</t>
+  </si>
+  <si>
+    <t>Build the email flows</t>
+  </si>
+  <si>
+    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
+  </si>
+  <si>
+    <t>Needs an SMTP provider.</t>
+  </si>
+  <si>
+    <t>BE-08</t>
+  </si>
+  <si>
+    <t>Decide money representation before any data lands</t>
+  </si>
+  <si>
+    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
+  </si>
+  <si>
+    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
+  </si>
+  <si>
+    <t>BE-10</t>
+  </si>
+  <si>
+    <t>Retire the catalogue snapshot endpoint</t>
+  </si>
+  <si>
+    <t>Client components fetch the whole catalogue from /api/v1/catalog/snapshot. Fine for 71 products; not for thousands. Goes away when the cart moves server-side.</t>
+  </si>
+  <si>
+    <t>Phase 3 removes the need.</t>
+  </si>
+  <si>
+    <t>BE-12</t>
+  </si>
+  <si>
+    <t>Merge a guest cart into the user cart on sign-in</t>
+  </si>
+  <si>
+    <t>Carts are keyed by a cookie so a visitor can shop before signing in. The merge on sign-in is specified but cannot be built until auth exists.</t>
+  </si>
+  <si>
+    <t>Cart cookie: aussiemed_cart, httpOnly, 30 day lifetime â€” OUR INVENTED VALUES.</t>
+  </si>
+  <si>
+    <t>BE-14</t>
+  </si>
+  <si>
+    <t>Confirm the default order and invoice status</t>
+  </si>
+  <si>
+    <t>OUR DECISION: new orders are Pending and each supplier invoice is Pending. The real workflow â€” who moves an order to Processing, and when an invoice becomes Issued â€” is not defined.</t>
+  </si>
+  <si>
+    <t>Order statuses available: Pending, Processing, Dispatched, Delivered, Cancelled.</t>
+  </si>
+  <si>
+    <t>BE-15</t>
+  </si>
+  <si>
+    <t>Passwords were built instead of the specified email OTP</t>
+  </si>
+  <si>
+    <t>BACKEND_SPEC.md specifies passwordless sign-in by emailed code. Passwords were requested instead and built. Livingstone advertises password-free login as a feature, so the spec was not arbitrary.</t>
+  </si>
+  <si>
+    <t>Both can coexist: the schema keeps otpCode and otpExpiresAt. Decide before launch.</t>
+  </si>
+  <si>
+    <t>BE-19</t>
+  </si>
+  <si>
+    <t>Guest checkout is allowed</t>
+  </si>
+  <si>
+    <t>OUR DECISION: an order can be placed without signing in, and is then tied to the cart cookie. Signing in simply attaches the order to the account.</t>
+  </si>
+  <si>
+    <t>If trade accounts should be required to order, this must change â€” it also affects credit terms and pricing.</t>
+  </si>
+  <si>
+    <t>BE-22</t>
+  </si>
+  <si>
+    <t>Confirm one supplier account per company</t>
+  </si>
+  <si>
+    <t>OUR DECISION: each supplier company links to a single user. Real suppliers usually need several people with their own logins.</t>
+  </si>
+  <si>
+    <t>Schema allows it via Supplier.userId; supporting several needs a join table.</t>
+  </si>
+  <si>
+    <t>BE-31</t>
+  </si>
+  <si>
+    <t>Log every out-of-stock toggle instead of only the current flag</t>
+  </si>
+  <si>
+    <t>The manual out-of-stock checkbox stores current state only. How long a product has been unavailable, and how quickly a supplier restocks, are unanswerable — and both are conversations the admin has with suppliers.</t>
+  </si>
+  <si>
+    <t>From spec section 1.4. Same one-way-door property as BE-30: every toggle that happens before this exists is lost. Small change — a log table written from the same service function that sets the flag.</t>
+  </si>
+  <si>
+    <t>BE-32</t>
+  </si>
+  <si>
+    <t>Log storefront searches, especially the ones that return nothing</t>
+  </si>
+  <si>
+    <t>A search that returns no results is a customer telling you what to stock, and it is currently discarded. For a distributor deciding what to source next, the list of terms that found nothing is one of the most valuable things the site can produce.</t>
+  </si>
+  <si>
+    <t>From spec section 2.4 D-2. Cannot be reconstructed later — nobody can recall what a visitor searched for last month. Distinct from FN-10 (search is client-side only), though doing FN-10 first would make the logging server-side and simpler.</t>
+  </si>
+  <si>
+    <t>BE-33</t>
+  </si>
+  <si>
+    <t>Record what each supplier has promised: lead time and acknowledgement SLA</t>
+  </si>
+  <si>
+    <t>On-time means nothing without a promise to measure against. These are numbers agreed personally with each supplier during onboarding, and there is nowhere to put them.</t>
+  </si>
+  <si>
+    <t>From spec section 1.2. Two integer columns on Supplier plus admin fields, but note the dependency runs the other way: the numbers are a business input the admin has to collect from each supplier, so ask for them before building anything that displays an on-time rate.</t>
+  </si>
+  <si>
+    <t>BE-34</t>
+  </si>
+  <si>
+    <t>No cost price, so no margin is known</t>
+  </si>
+  <si>
+    <t>The system records what a product sells for but not what it costs to buy, so nothing can say whether a line, an order or a supplier is profitable. Requested by the client 16 Aug 2026.</t>
+  </si>
+  <si>
+    <t>Three things to build in from the start rather than retrofit. Cost is held per SKU in integer fils like every other money value, and margin is computed rather than stored so it cannot drift out of step with price. Cost is snapshotted onto the order line at the moment of sale, exactly as sell price, VAT rate and product name already are — without it, renegotiating a supplier price silently rewrites the margin on every historical order and last quarter's figures change retrospectively. And it is admin-only, enforced server-side: cost must never reach the storefront, the browser-side catalogue snapshot, or the supplier portal, because a supplier seeing the markup on their own goods is a commercial problem, not merely a privacy one. A cost column goes into the BE-04 upload template now, so the client populates it once.</t>
+  </si>
+  <si>
+    <t>DA-02</t>
+  </si>
+  <si>
+    <t>Verify the product-to-category mapping</t>
+  </si>
+  <si>
+    <t>The extraction had no product-category link at all, so every mapping on the site is ours. The catalogue is now 71 products across 146 categories and none of that mapping has been checked by anyone who knows the range.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026 after DA-23: 60 active products, 0 uncategorised.</t>
+  </si>
+  <si>
+    <t>DA-05</t>
+  </si>
+  <si>
+    <t>Approve the product descriptions</t>
+  </si>
+  <si>
+    <t>The source had no descriptions. All 71 active products now carry text we generated from the product name and supplier listing, and it goes out under AussieMed's name.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026 after DA-23: 60 of 60 active products have a generated description.</t>
+  </si>
+  <si>
+    <t>DA-07</t>
+  </si>
+  <si>
+    <t>Supply the hero banner image</t>
+  </si>
+  <si>
+    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured â€” only Brand, Category, Product and WebHtml folders were mirrored.</t>
+  </si>
+  <si>
+    <t>A genuine AussieMed CMS image stands in.</t>
+  </si>
+  <si>
+    <t>DA-08</t>
+  </si>
+  <si>
+    <t>Obtain Gilroy Regular and Medium</t>
+  </si>
+  <si>
+    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
+  </si>
+  <si>
+    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
+  </si>
+  <si>
+    <t>DA-10</t>
+  </si>
+  <si>
+    <t>Supply real pack and carton structures</t>
+  </si>
+  <si>
+    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
+  </si>
+  <si>
+    <t>Largely superseded by DA-20: packaging moved from separate carton SKUs into named price breaks on 15 Aug 2026, so the invented figures now live in scripts/variants.mjs rather than in outer packs. Kept open because the underlying question â€” what is a real carton and box for each line â€” is unanswered either way.</t>
+  </si>
+  <si>
+    <t>DA-11</t>
+  </si>
+  <si>
+    <t>Supply real variant data</t>
+  </si>
+  <si>
+    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: the same five sizes and three colours are stamped on all six glove products regardless of what the supplier actually sells. FN-07 covers the wiring; this row covers the data.</t>
+  </si>
+  <si>
+    <t>DA-12</t>
+  </si>
+  <si>
+    <t>Supply real product specifications</t>
+  </si>
+  <si>
+    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
+  </si>
+  <si>
+    <t>These become search filters later.</t>
+  </si>
+  <si>
+    <t>DA-13</t>
+  </si>
+  <si>
+    <t>Supply safety data sheets and spec sheets</t>
+  </si>
+  <si>
+    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
+  </si>
+  <si>
+    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
+  </si>
+  <si>
+    <t>DA-18</t>
+  </si>
+  <si>
+    <t>Product ids are derived from slugs</t>
+  </si>
+  <si>
+    <t>Carts and wishlists are stored in the browser against a product id. Ids are now hashed from the slug so they survive a re-seed, which means CHANGING A PRODUCT SLUG ORPHANS ANY SAVED CART LINE referencing it.</t>
+  </si>
+  <si>
+    <t>Resolved properly when the cart moves server-side and references SKU rows directly.</t>
+  </si>
+  <si>
+    <t>DA-19</t>
+  </si>
+  <si>
+    <t>Supplier email addresses are invented</t>
+  </si>
+  <si>
+    <t>The seed writes orders@&lt;supplier&gt;.example and accounts@&lt;supplier&gt;.example because secondaryEmail is mandatory. No supplier will receive anything at these addresses.</t>
+  </si>
+  <si>
+    <t>Both addresses are meant to receive order notifications once email exists.</t>
+  </si>
+  <si>
+    <t>DA-21</t>
+  </si>
+  <si>
+    <t>Verify the automatic variant grouping</t>
+  </si>
+  <si>
+    <t>Products are grouped into families by stripping sizes and volumes from their names. It found 2 families in the seeded catalogue. A real catalogue will group differently and some groupings will be wrong.</t>
+  </si>
+  <si>
+    <t>The admin product screens should let a family be set explicitly rather than inferred â€” see BE-20.</t>
+  </si>
+  <si>
+    <t>DA-24</t>
+  </si>
+  <si>
+    <t>13 of 60 products have no image</t>
+  </si>
+  <si>
+    <t>Those products render as a monogram tile rather than a photograph. It is a deliberate stand-in and reads acceptably in a grid, but on a trade catalogue an image is often how a buyer confirms they have the right item.</t>
+  </si>
+  <si>
+    <t>Was 19 of 71. Ten went with the extraction products under DA-23. Four more were added deliberately: their image files turned out to be SVG placeholders saved with a .jpg extension, which the image optimiser rejected with a 400 â€” see DA-25. The remaining nine have no sourceSku or sourceUrl recorded, so there is nothing to retry a fetch against, and no more third-party photography was sourced because DA-17 already limits what may ship. Subset of DA-03.</t>
+  </si>
+  <si>
+    <t>FN-07</t>
+  </si>
+  <si>
+    <t>Size and colour switching is not wired</t>
+  </si>
+  <si>
+    <t>The variant dropdown built on 15 Aug 2026 (DEC-12) switches between sibling products by size or volume, and that works. The separate Size and Colour chips on gloves and the scrub top are a different thing and still do nothing â€” no sibling SKU exists behind any of them.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: 13 option axes across 6 products. Every glove carries an identical Size = XS/S/M/L/XL and Colour = Black/Blue/Green with no SKU attached to any value.</t>
+  </si>
+  <si>
+    <t>FN-08</t>
+  </si>
+  <si>
+    <t>Stock is a boolean</t>
+  </si>
+  <si>
+    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
+  </si>
+  <si>
+    <t>Decide whether real stock levels are needed.</t>
+  </si>
+  <si>
+    <t>FN-09</t>
+  </si>
+  <si>
+    <t>Decide on expiry and short-dated stock</t>
+  </si>
+  <si>
+    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
+  </si>
+  <si>
+    <t>Schema-shaping â€” decide before the backend is built.</t>
+  </si>
+  <si>
+    <t>FN-12</t>
+  </si>
+  <si>
+    <t>Nothing shows which clients are overdue to reorder</t>
+  </si>
+  <si>
+    <t>In a reorder-first business this is the single most useful signal there is: a clinic that buys gloves every three weeks and has not ordered in five needs a phone call. It is computable from order history alone once there are three orders per client — no new data capture required.</t>
+  </si>
+  <si>
+    <t>From spec sections 2.3 C-4 and C-5 and queue Q-3. Unlike BE-30 to BE-32 this is not urgent, because the underlying order history is already being recorded and the calculation can be added at any time. Build it once real clients are ordering; with four test orders it would only ever say insufficient data.</t>
+  </si>
+  <si>
+    <t>FN-13</t>
+  </si>
+  <si>
+    <t>The client account has no Buy Again</t>
+  </si>
+  <si>
+    <t>A returning buyer has to search for products they have already bought. For a reorder-first marketplace this is the shortest path between the platform and revenue, and it needs no metrics work at all — just their own order history, sorted by how often they buy each line.</t>
+  </si>
+  <si>
+    <t>From spec section 4 CL-1 and CL-3. Independent of the whole metrics programme and arguably worth more than any dashboard in it. Depends on nothing that is not already built.</t>
+  </si>
+  <si>
+    <t>IN-01</t>
+  </si>
+  <si>
+    <t>Choose a hosting target</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. The site runs locally only.</t>
+  </si>
+  <si>
+    <t>Deliberately deferred until the build is approved.</t>
+  </si>
+  <si>
+    <t>IN-02</t>
+  </si>
+  <si>
+    <t>Choose the database</t>
+  </si>
+  <si>
+    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
+  </si>
+  <si>
+    <t>IN-03</t>
+  </si>
+  <si>
+    <t>Choose an SMTP provider and sending domain</t>
+  </si>
+  <si>
+    <t>Required for every transactional email.</t>
+  </si>
+  <si>
+    <t>Must not be the misspelled assuiemed.com domain.</t>
+  </si>
+  <si>
+    <t>IN-04</t>
+  </si>
+  <si>
+    <t>Decide on a payment gateway</t>
+  </si>
+  <si>
+    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
+  </si>
+  <si>
+    <t>LG-05</t>
+  </si>
+  <si>
+    <t>Transfer the theme licence</t>
+  </si>
+  <si>
+    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
+  </si>
+  <si>
+    <t>Repository must stay private because of this.</t>
+  </si>
+  <si>
+    <t>LG-06</t>
+  </si>
+  <si>
+    <t>Supply company registration details</t>
+  </si>
+  <si>
+    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
+  </si>
+  <si>
+    <t>SEC-02</t>
+  </si>
+  <si>
+    <t>Add rate limiting to sign-in</t>
+  </si>
+  <si>
+    <t>Nothing limits password attempts, so the sign-in endpoint can be brute forced. The spec asks for rate limiting on auth in the hardening phase.</t>
+  </si>
+  <si>
+    <t>Matters more with short passwords than with OTP.</t>
+  </si>
+  <si>
+    <t>SEC-03</t>
+  </si>
+  <si>
+    <t>Agree a password policy</t>
+  </si>
+  <si>
+    <t>No minimum length, complexity or reuse rule is enforced. 123456 was accepted because nothing rejects it.</t>
+  </si>
+  <si>
+    <t>Moot if the OTP flow in BE-15 is adopted instead.</t>
+  </si>
+  <si>
+    <t>AC-08</t>
+  </si>
+  <si>
+    <t>Confirm the rounding policy</t>
+  </si>
+  <si>
+    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Verified by test; needs sign-off that the method is acceptable.</t>
+  </si>
+  <si>
+    <t>AC-10</t>
+  </si>
+  <si>
+    <t>Confirm the default price display</t>
+  </si>
+  <si>
+    <t>Prices are shown Ex. VAT everywhere, and since 15 Aug 2026 there is no way for a buyer to see an inc-VAT figure at all â€” the header toggle was removed at the client's request before VAT was folded into the displayed price.</t>
+  </si>
+  <si>
+    <t>See DEC-14 for the decision and FE-30 for the gap it leaves open.</t>
+  </si>
+  <si>
+    <t>BE-13</t>
+  </si>
+  <si>
+    <t>Expire abandoned guest carts</t>
+  </si>
+  <si>
+    <t>Cart rows are never cleaned up. Every visitor who adds an item creates one that lives forever.</t>
+  </si>
+  <si>
+    <t>The spec wants abandoned carts over 24h reportable under Admin &gt; Marketing, so expiry and that report should be designed together.</t>
+  </si>
+  <si>
+    <t>BE-16</t>
+  </si>
+  <si>
+    <t>Confirm the session lifetime</t>
+  </si>
+  <si>
+    <t>OUR INVENTED VALUE: sessions last 7 days, then require signing in again. No idle timeout and no re-authentication for sensitive actions.</t>
+  </si>
+  <si>
+    <t>Cookie is httpOnly and sameSite=lax; secure only in production so local http still works.</t>
+  </si>
+  <si>
+    <t>BE-17</t>
+  </si>
+  <si>
+    <t>Purge expired sessions on a schedule</t>
+  </si>
+  <si>
+    <t>Expired session rows are never deleted. purgeExpiredSessions() exists but nothing calls it.</t>
+  </si>
+  <si>
+    <t>Trivial once any scheduled job exists.</t>
+  </si>
+  <si>
+    <t>BE-18</t>
+  </si>
+  <si>
+    <t>Password hashing uses scrypt, not bcrypt</t>
+  </si>
+  <si>
+    <t>OUR DECISION: scrypt from Node's own crypto module, so there is no dependency to keep patched. The spec names bcrypt. Both are appropriate; only src/lib/auth.ts knows the format.</t>
+  </si>
+  <si>
+    <t>Stored as scrypt$salt$hash so the algorithm is self-describing and can be migrated per user.</t>
+  </si>
+  <si>
+    <t>BE-23</t>
+  </si>
+  <si>
+    <t>Admin figures are counted live, never cached</t>
+  </si>
+  <si>
+    <t>OUR DECISION: every number on the admin dashboard is counted from the database on each request. Caching them is how the old platform let admin counts and storefront counts disagree.</t>
+  </si>
+  <si>
+    <t>Still true after the admin build: every dashboard figure is a live count. Cheap at 60 products and 4 orders; revisit when either grows.</t>
+  </si>
+  <si>
+    <t>BE-24</t>
+  </si>
+  <si>
+    <t>Supplier data is scoped by query, not by filtering</t>
+  </si>
+  <si>
+    <t>OUR DECISION: a supplier's products and invoice lines are fetched through their supplier id, so another supplier's rows are never loaded rather than loaded and hidden.</t>
+  </si>
+  <si>
+    <t>Keep this rule as the supplier portal grows â€” filtering after fetching is how leaks happen.</t>
+  </si>
+  <si>
+    <t>BE-27</t>
+  </si>
+  <si>
+    <t>No marketing screens: wishlists and abandoned carts</t>
+  </si>
+  <si>
+    <t>Both are already recorded in the database and nobody can see either. An abandoned cart is the cheapest sale to recover, and a wishlist says what a buyer wants before they buy it.</t>
+  </si>
+  <si>
+    <t>Split out of BE-02 when the admin screens were built.</t>
+  </si>
+  <si>
+    <t>BE-28</t>
+  </si>
+  <si>
+    <t>No reports: sales by supplier, category or period</t>
+  </si>
+  <si>
+    <t>The dashboard totals every order ever placed and nothing else. There is no way to answer which supplier sells most, what a month looked like, or which categories are dead.</t>
+  </si>
+  <si>
+    <t>Split out of BE-02. Wants AC-09 settled first so periods line up with terms.</t>
+  </si>
+  <si>
+    <t>DA-14</t>
+  </si>
+  <si>
+    <t>Confirm the brand list</t>
+  </si>
+  <si>
+    <t>Brands were assigned by reading product names, because neither source listed a brand field. Bad extractions were caught by hand (Goat, Hello, Roger) but the list has never been checked against reality.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026 after DA-23: 26 brands across the 60 test products.</t>
+  </si>
+  <si>
+    <t>DA-15</t>
+  </si>
+  <si>
+    <t>Decide on duplicate categories</t>
+  </si>
+  <si>
+    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
+  </si>
+  <si>
+    <t>Re-measured 15 Aug 2026: still 6 duplicated names, 12 categories in total. Slugs are disambiguated by appending the numeric id (oral-care vs oral-care-96). 10 of the 12 hold no products at all, so most of the duplication is invisible to buyers today.</t>
+  </si>
+  <si>
+    <t>DA-16</t>
+  </si>
+  <si>
+    <t>Confirm the missing department</t>
+  </si>
+  <si>
+    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
+  </si>
+  <si>
+    <t>Confirm this is intentional rather than lost.</t>
+  </si>
+  <si>
+    <t>FN-10</t>
+  </si>
+  <si>
+    <t>Search is client-side only</t>
+  </si>
+  <si>
+    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
+  </si>
+  <si>
+    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
+  </si>
+  <si>
+    <t>IN-05</t>
+  </si>
+  <si>
+    <t>Supply Google and Facebook OAuth keys</t>
+  </si>
+  <si>
+    <t>Social login endpoints currently return 501.</t>
+  </si>
+  <si>
+    <t>IN-08</t>
+  </si>
+  <si>
+    <t>Correct the git author name</t>
+  </si>
+  <si>
+    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
+  </si>
+  <si>
+    <t>Fixable with git config user.name and an amend.</t>
+  </si>
+  <si>
+    <t>IN-09</t>
+  </si>
+  <si>
+    <t>Set up continuous integration</t>
+  </si>
+  <si>
+    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
+  </si>
+  <si>
+    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
+  </si>
+  <si>
+    <t>IN-10</t>
+  </si>
+  <si>
+    <t>Plan backups and disaster recovery</t>
+  </si>
+  <si>
+    <t>No backup strategy exists for the database or uploaded files.</t>
+  </si>
+  <si>
+    <t>Relevant once there is a real database.</t>
+  </si>
+  <si>
+    <t>LG-04</t>
+  </si>
+  <si>
+    <t>Approve the About / Contact / Order Support copy</t>
+  </si>
+  <si>
+    <t>All placeholder text.</t>
+  </si>
+  <si>
+    <t>Pages carry a visible placeholder notice.</t>
+  </si>
+  <si>
+    <t>DEC-01</t>
+  </si>
+  <si>
+    <t>Fresh build â€” the previous site is reference only</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: nothing to do with the previous site. The extraction is mined for data and business rules; its code and behaviour are discarded.</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Its category tree, product data and bug history were kept. Its markup was not.</t>
+  </si>
+  <si>
+    <t>DEC-02</t>
+  </si>
+  <si>
+    <t>Keep the existing visual brand</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026, correcting an earlier over-broad reading: the storefront must keep the current AussieMed look, not be redesigned.</t>
+  </si>
+  <si>
+    <t>Navy #29387d, red #ea2227 and Gilroy were read from the live site's computed styles. See DA-08 for the missing Gilroy weights.</t>
+  </si>
+  <si>
+    <t>DEC-03</t>
+  </si>
+  <si>
+    <t>Local only until the client approves</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: not to go online until there is a version they are happy with locally.</t>
+  </si>
+  <si>
+    <t>Nothing is deployed. robots noindex is site-wide. Hosting is IN-01.</t>
+  </si>
+  <si>
+    <t>DEC-04</t>
+  </si>
+  <si>
+    <t>External connectors are handled last</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: anything needing a third-party account waits until the end so the build never stalls on credentials.</t>
+  </si>
+  <si>
+    <t>Payment IN-04, SMTP IN-03, OAuth IN-05, hosting IN-01. Built behind seams with local stand-ins.</t>
+  </si>
+  <si>
+    <t>DEC-05</t>
+  </si>
+  <si>
+    <t>Follow Livingstone for B2B catalogue and pricing behaviour</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026 with livingstone.com.au as the reference, and all suggested changes accepted.</t>
+  </si>
+  <si>
+    <t>Produced the pack/UOM model, price breaks on cards, the Ex/Inc VAT toggle, variant axes, spec attributes and per-product tax class.</t>
+  </si>
+  <si>
+    <t>DEC-06</t>
+  </si>
+  <si>
+    <t>Seed the catalogue from two real suppliers for testing</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026: list Chemist Warehouse and Livingstone as suppliers with 30 items each, and remove the invented placeholders.</t>
+  </si>
+  <si>
+    <t>60 real products seeded. Both are unaffiliated third parties â€” DA-17 must close before launch.</t>
+  </si>
+  <si>
+    <t>DEC-07</t>
+  </si>
+  <si>
+    <t>Add product images</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026. Supplier photography was downloaded for local testing.</t>
+  </si>
+  <si>
+    <t>52 of 71 products have an image. Third-party assets â€” DA-03 must close before launch.</t>
+  </si>
+  <si>
+    <t>DEC-08</t>
+  </si>
+  <si>
+    <t>Four test accounts with a shared placeholder password</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: admin, musawi1989@gmail.com, supplier1 and supplier2, all with 123456. Explicitly described as local testing only, chosen to be memorable, and to be changed before anything real.</t>
+  </si>
+  <si>
+    <t>Implemented as asked. SEC-01 tracks removing them; SEC-03 tracks agreeing a password policy.</t>
+  </si>
+  <si>
+    <t>DEC-09</t>
+  </si>
+  <si>
+    <t>One sign-in door per role</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the business portal is the supplier login, the account login is for buyers, and admin is reached at /admin.</t>
+  </si>
+  <si>
+    <t>Implemented. Signing in at the wrong door names the right one rather than admitting the user.</t>
+  </si>
+  <si>
+    <t>DEC-10</t>
+  </si>
+  <si>
+    <t>Record every generated value and decision in this register</t>
+  </si>
+  <si>
+    <t>Stated 14 Aug 2026 and repeated 15 Aug: everything invented on the client's behalf must be written down rather than left in the code.</t>
+  </si>
+  <si>
+    <t>This register is the record. docs/Things That Need Attention.xlsx is generated from it and npm run register validates it.</t>
+  </si>
+  <si>
+    <t>DEC-11</t>
+  </si>
+  <si>
+    <t>Price breaks are packaging levels, not arbitrary quantities</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: a break at 12 exists because a carton holds 12, and a break at 48 because a box holds 4 cartons. The quantity and the packaging level are the same fact.</t>
+  </si>
+  <si>
+    <t>Each break now carries its level name. Corrects an earlier model that treated breaks as percentage discounts at round numbers.</t>
+  </si>
+  <si>
+    <t>DEC-12</t>
+  </si>
+  <si>
+    <t>Variants are a dropdown across sibling products</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the 375ml and the 60ml stay as separate products, and each carries a dropdown listing the whole family so a buyer can find their part quickly.</t>
+  </si>
+  <si>
+    <t>Replaces the Each/Carton chips on cards. Implemented as navigation between products, not options on one product, because each size has its own SKU, stock and price.</t>
+  </si>
+  <si>
+    <t>DEC-13</t>
+  </si>
+  <si>
+    <t>One sign-in button in the header, with a dropdown per role</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: replace the Business portal and Account links with a single blue Sign in button whose dropdown offers sign in as a buyer and sign in as a supplier.</t>
+  </si>
+  <si>
+    <t>Implemented in src/components/SignInMenu.tsx. Admin is deliberately absent from the dropdown; staff go to /admin directly. Once signed in the button becomes the way back to the user own area.</t>
+  </si>
+  <si>
+    <t>DEC-14</t>
+  </si>
+  <si>
+    <t>The AED label and the Ex/Inc VAT toggle are gone from the header</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: remove the AED text and the VAT options because VAT is to be carried in the displayed price later.</t>
+  </si>
+  <si>
+    <t>VatToggle deleted from the header. includeVat still exists in src/lib/store.tsx defaulting to ex-VAT with no UI control, so prices read ex-VAT everywhere until the pricing change lands. FE-30 tracks that follow up.</t>
+  </si>
+  <si>
+    <t>DEC-15</t>
+  </si>
+  <si>
+    <t>Sign out lives in the header, in the sign in button slot</t>
+  </si>
+  <si>
+    <t>Stated 15 Aug 2026: the sign out button always sits where the Sign in button would be when signed out.</t>
+  </si>
+  <si>
+    <t>Moved out of the account, admin and business portal pages into src/components/SignInMenu.tsx, so it is reachable from every page rather than only the dashboard. Signed in, the slot shows the account name plus Sign out.</t>
+  </si>
+  <si>
+    <t>DEC-16</t>
+  </si>
+  <si>
+    <t>Empty categories are hidden from navigation, not removed</t>
+  </si>
+  <si>
+    <t>The category tree came from Livingstone and is far wider than the 60 test products fill. Hiding what is empty keeps every menu entry useful; removing them would lose the shape of the intended range, and hard-coding a shorter list would need maintaining by hand.</t>
+  </si>
+  <si>
+    <t>Our decision, 15 Aug 2026, taken while closing FN-11. It is computed rather than configured, so categories reappear on their own as products are filed into them. Direct URLs still work. Say if you would rather the full tree stayed visible.</t>
+  </si>
+  <si>
+    <t>DEC-17</t>
+  </si>
+  <si>
+    <t>Renaming a category does not change its URL</t>
+  </si>
+  <si>
+    <t>The slug is the address. A category that has been linked to, bookmarked or indexed keeps working when its display name changes, and changing both would silently break every existing link.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026. Renaming to something genuinely different means creating a category and moving products, or a redirect table we have not built. Say if you would rather the URL followed the name.</t>
+  </si>
+  <si>
+    <t>DEC-18</t>
+  </si>
+  <si>
+    <t>A product cannot go live without a SKU and a category</t>
+  </si>
+  <si>
+    <t>Both make a live product broken rather than merely incomplete: no SKU means nothing to buy, no category means nobody can browse to it. The admin screen refuses the transition and says which one is missing.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026, enforced in src/lib/admin.ts rather than in the form, so posting to the endpoint directly cannot bypass it.</t>
+  </si>
+  <si>
+    <t>DEC-19</t>
+  </si>
+  <si>
+    <t>Delivered and cancelled orders cannot be reopened</t>
+  </si>
+  <si>
+    <t>Both are closed documents the customer already holds. A status that contradicts what they received is worse than no status at all.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026. A delivered order needs a return and a cancelled one needs a new order â€” neither of which exists yet. Confirm this matches how you actually work.</t>
+  </si>
+  <si>
+    <t>DEC-20</t>
+  </si>
+  <si>
+    <t>The back office looks like the reference operations UI, not like the shop</t>
+  </si>
+  <si>
+    <t>The client supplied screenshots of the tool they use day to day. Staff processing orders are doing operational work, and the storefront chrome was both a distraction and the reason documents printed badly.</t>
+  </si>
+  <si>
+    <t>Agreed 16 Aug 2026. Admin and the supplier portal both use the operations shell; the light sidebar follows the reference rather than the AussieMed navy, chosen so the data on screen is what stands out. The supplier rail lists only the one screen that exists, because an entry leading to an unbuilt page is worse than no entry â€” the rest is BE-21.</t>
+  </si>
+  <si>
+    <t>DEC-21</t>
+  </si>
+  <si>
+    <t>Uploaded files go through a storage seam, not straight to disk</t>
+  </si>
+  <si>
+    <t>Local disk is right for a laptop and wrong for most hosting: a container filesystem is discarded on every deploy, and two instances behind a load balancer do not share one. Hosting is IN-01 and is not chosen yet.</t>
+  </si>
+  <si>
+    <t>Our decision, 16 Aug 2026, taken while building BE-29. Everything touching a filesystem is confined to src/lib/storage.ts behind a driver interface; local disk is the only driver today and STORAGE_DRIVER selects it. Adding S3, R2 or Blob storage means writing one more driver and changing an environment variable, with no calling code touched. What counts as an acceptable image is decided separately in image-file.ts, which is pure and unit tested, so a second driver cannot accept what this one refuses.</t>
+  </si>
+  <si>
+    <t>DEC-22</t>
+  </si>
+  <si>
+    <t>AussieMed is the seller of record</t>
+  </si>
+  <si>
+    <t>Determines who carries the VAT liability and the credit risk, what the customer's invoice looks like, and who chases payment. It had been drifting undecided while the build leaned the other way.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. AussieMed buys from suppliers and resells: the customer receives one invoice from AussieMed carrying AussieMed's TRN, and suppliers invoice AussieMed separately. Note this reverses the direction the build had taken — orders split into one invoice per supplier, with a database constraint enforcing it, and that split was being shown to the customer. The split is still correct and still needed for picking, delivery notes and paying suppliers; it simply stops being the customer's document. See AC-03 and AC-04 for the consequences.</t>
+  </si>
+  <si>
+    <t>DEC-23</t>
+  </si>
+  <si>
+    <t>VAT is a checkout concern only</t>
+  </si>
+  <si>
+    <t>Settles a question open since the Ex/Inc VAT toggle was removed: whether buyers need to see VAT while browsing.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. VAT is calculated at checkout and shown on the invoice. It appears nowhere on product pages or listings, which show trade prices only. Consistent with DEC-13. Product tax class still matters, because it decides what checkout charges, but it is never surfaced before then. Closes FE-30.</t>
+  </si>
+  <si>
+    <t>DA-09</t>
+  </si>
+  <si>
+    <t>Explain the disappearing product</t>
+  </si>
+  <si>
+    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
+  </si>
+  <si>
+    <t>Deferred 15 Aug 2026. The product in question was one of the 11 removed under DA-23 and nothing is being migrated from the old platform, so this no longer affects the build. Worth revisiting only if data from the old system is ever imported.</t>
+  </si>
+  <si>
+    <t>DF-01</t>
+  </si>
+  <si>
+    <t>Industry taxonomy</t>
+  </si>
+  <si>
+    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
+  </si>
+  <si>
+    <t>Additive; adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-02</t>
+  </si>
+  <si>
+    <t>Subscribe and Save</t>
+  </si>
+  <si>
+    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
+  </si>
+  <si>
+    <t>Needs the backend.</t>
+  </si>
+  <si>
+    <t>DF-03</t>
+  </si>
+  <si>
+    <t>Frequently bought together</t>
+  </si>
+  <si>
+    <t>Bundle suggestion with a combined total and one action to add all.</t>
+  </si>
+  <si>
+    <t>Adopted from Livingstone.</t>
+  </si>
+  <si>
+    <t>DF-04</t>
+  </si>
+  <si>
+    <t>Quick view</t>
+  </si>
+  <si>
+    <t>View a product from the listing without a page load.</t>
+  </si>
+  <si>
+    <t>DF-05</t>
+  </si>
+  <si>
+    <t>Downloadable PDF catalogues</t>
+  </si>
+  <si>
+    <t>Still how a lot of trade buying happens.</t>
+  </si>
+  <si>
+    <t>Needs the actual catalogue files.</t>
+  </si>
+  <si>
+    <t>BE-02</t>
+  </si>
+  <si>
+    <t>Build the admin panel</t>
+  </si>
+  <si>
+    <t>Products, categories, suppliers, customers, orders, marketing, reports, settings.</t>
+  </si>
+  <si>
+    <t>Done 16 Aug 2026 by BE-20. Marketing (wishlists, abandoned carts) and reports are not built â€” BE-27 and BE-28.</t>
+  </si>
+  <si>
+    <t>BE-07</t>
+  </si>
+  <si>
+    <t>Seed the database from the catalogue</t>
+  </si>
+  <si>
+    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
+  </si>
+  <si>
+    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
+  </si>
+  <si>
+    <t>BE-09</t>
+  </si>
+  <si>
+    <t>Point the storefront at the database</t>
+  </si>
+  <si>
+    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
+  </si>
+  <si>
+    <t>query.ts was untouched â€” it never knew where products came from.</t>
+  </si>
+  <si>
+    <t>BE-11</t>
+  </si>
+  <si>
+    <t>Order pages restricted to their owner</t>
+  </si>
+  <si>
+    <t>An order was readable by anyone who guessed a sequential reference. Now an admin sees any order, the account that placed it sees it, and a guest sees only an order placed from their own cart.</t>
+  </si>
+  <si>
+    <t>A forbidden order returns 404 rather than 403, so the response cannot be used to discover which references exist.</t>
+  </si>
+  <si>
+    <t>BE-20</t>
+  </si>
+  <si>
+    <t>Build the admin screens behind the dashboard</t>
+  </si>
+  <si>
+    <t>/admin authenticates and shows live figures, but every management screen is still missing: products, categories, suppliers, customers, orders, bulk upload, marketing, reports, settings.</t>
+  </si>
+  <si>
+    <t>Built 16 Aug 2026. Dashboard, products (list, filters, edit, SKUs, price breaks, approval), categories, suppliers, orders, customers, settings and an audit trail. Every write goes through src/lib/admin.ts, which checks the role again in the service layer, records the change, and bumps the catalogue version so the storefront updates without a restart. Bulk upload is BE-04; product image upload is still missing â€” see BE-29.</t>
+  </si>
+  <si>
+    <t>BE-25</t>
+  </si>
+  <si>
+    <t>Invalidate the catalogue cache after a seed or an edit</t>
+  </si>
+  <si>
+    <t>The data layer caches the catalogue for the life of the process, so a running server keeps serving whatever it read first. This is not theoretical: on 15 Aug 2026 the dev server was still showing a retired carton SKU as a purchasable unit chip on the product page, hours after the database had deactivated it.</t>
+  </si>
+  <si>
+    <t>Fixed 15 Aug 2026. The cache now carries the catalogVersion stamp it was built from and re-checks it against the database at most once a second; the seed bumps the stamp, and invalidateCatalog() bumps it too so other server processes drop their copy as well. Verified live: a running dev server went from 71 products to 60 without a restart, and the phantom carton chip disappeared.</t>
+  </si>
+  <si>
+    <t>BE-29</t>
+  </si>
+  <si>
+    <t>Product images cannot be uploaded</t>
+  </si>
+  <si>
+    <t>The admin product screen listed the image files a product references but could not add or replace one, so the only way to give a product a photograph was to put a file on disk and re-seed. That blocked DA-03 and DA-24 from ever being closed by the client rather than by us.</t>
+  </si>
+  <si>
+    <t>Built 16 Aug 2026. Upload, alt text, choose which image the catalogue shows, and remove — on the product screen, through src/lib/admin.ts like every other write, so it is admin-checked, audited and bumps the catalogue version. Files go through the src/lib/storage.ts seam; see DEC-21. Images are accepted on their leading bytes rather than their filename, which turns the DA-25 defect into a refusal at upload time instead of a 400 from the image optimiser at request time. 15 unit tests cover the checks and the key generation. Verified end to end in a browser: a renamed SVG is refused, a real PNG is stored, served and reaches the storefront with no restart, promotion leaves a dense order, removal deletes both the row and the file, and all five actions appear in the audit trail.</t>
+  </si>
+  <si>
+    <t>DN-01</t>
+  </si>
+  <si>
+    <t>Currency rendering</t>
+  </si>
+  <si>
+    <t>Was rendering the Arabic symbol and 4 decimals. Now always the English string AED with exactly 2 decimals, enforced by test and by a grep check.</t>
+  </si>
+  <si>
+    <t>Fixed in the initial build.</t>
+  </si>
+  <si>
+    <t>DN-02</t>
+  </si>
+  <si>
+    <t>Integer quantities</t>
+  </si>
+  <si>
+    <t>Quantities were rendering as decimals such as 3.00.</t>
+  </si>
+  <si>
+    <t>DN-03</t>
+  </si>
+  <si>
+    <t>Category filtering</t>
+  </si>
+  <si>
+    <t>Every category link redirected to the full product list. Filtering now works, including rolling a department up to everything beneath it.</t>
+  </si>
+  <si>
+    <t>DN-04</t>
+  </si>
+  <si>
+    <t>Category counts matching results</t>
+  </si>
+  <si>
+    <t>Admin and storefront counts could diverge. Counts are now derived from the same query that lists the products.</t>
+  </si>
+  <si>
+    <t>Asserted in the data checks and the API contract checks.</t>
+  </si>
+  <si>
+    <t>DN-05</t>
+  </si>
+  <si>
+    <t>Category slug collisions</t>
+  </si>
+  <si>
+    <t>Six categories shared a slug with another category, so one was unreachable and the other answered to the wrong name.</t>
+  </si>
+  <si>
+    <t>Found by the API contract check. Slugs are now unique tree-wide and asserted.</t>
+  </si>
+  <si>
+    <t>DN-06</t>
+  </si>
+  <si>
+    <t>Per-supplier invoicing</t>
+  </si>
+  <si>
+    <t>An order spanning N suppliers now produces exactly N invoices under one reference number, with per-invoice VAT summing to the order VAT without drift.</t>
+  </si>
+  <si>
+    <t>Verified end to end in the browser and by test.</t>
+  </si>
+  <si>
+    <t>DN-11</t>
+  </si>
+  <si>
+    <t>Pack and unit of measure model</t>
+  </si>
+  <si>
+    <t>The same line sells by the box and by the carton at different prices. Cart lines are keyed by product and pack so they never merge.</t>
+  </si>
+  <si>
+    <t>Outers are asserted to beat buying their contents separately.</t>
+  </si>
+  <si>
+    <t>DN-14</t>
+  </si>
+  <si>
+    <t>Control characters in generated code</t>
+  </si>
+  <si>
+    <t>Shell escaping wrote literal backspace bytes into regex rules, so every packaging and variant rule silently matched nothing while looking correct in every editor.</t>
+  </si>
+  <si>
+    <t>Found via od. A data check now asserts each variant selection matches an option.</t>
+  </si>
+  <si>
+    <t>DN-16</t>
+  </si>
+  <si>
+    <t>Database schema designed and migrated</t>
+  </si>
+  <si>
+    <t>Thirty tables covering catalogue, packs as SKUs, variants, attributes, documents, batches, orders, per-supplier invoices, quotes, bulk upload and audit.</t>
+  </si>
+  <si>
+    <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
+  </si>
+  <si>
+    <t>DN-17</t>
+  </si>
+  <si>
+    <t>Typecheck was silently passing on a stale cache</t>
+  </si>
+  <si>
+    <t>tsc ran with incremental caching and reported no errors while real type errors existed in the tree. Every earlier typecheck-clean claim was suspect.</t>
+  </si>
+  <si>
+    <t>npm run typecheck now runs with --incremental false. Caught seven genuine errors the moment it was disabled.</t>
+  </si>
+  <si>
+    <t>DN-18</t>
+  </si>
+  <si>
+    <t>Cart moved to the server</t>
+  </si>
+  <si>
+    <t>The cart was localStorage, so the browser held prices. It is now database rows priced entirely on the server; the client cannot tell the server what anything costs.</t>
+  </si>
+  <si>
+    <t>Guest carts are cookie-keyed. The catalogue snapshot endpoint stays until the wishlist and quote cart follow.</t>
+  </si>
+  <si>
+    <t>DN-19</t>
+  </si>
+  <si>
+    <t>Checkout writes real orders</t>
+  </si>
+  <si>
+    <t>One transaction creates the order, one invoice per supplier and every line, or nothing at all. Reference numbers are allocated server-side inside that transaction.</t>
+  </si>
+  <si>
+    <t>Verified in a browser end to end, and by 14 order invariants in npm run db:check.</t>
+  </si>
+  <si>
+    <t>DN-20</t>
+  </si>
+  <si>
+    <t>Four sign-in accounts seeded</t>
+  </si>
+  <si>
+    <t>admin, musawi1989@gmail.com, supplier1 and supplier2, each able to sign in by username or email. Suppliers are attached to their seeded companies.</t>
+  </si>
+  <si>
+    <t>Seeded separately from the catalogue so re-seeding products does not remove accounts.</t>
+  </si>
+  <si>
+    <t>FN-01</t>
+  </si>
+  <si>
+    <t>Checkout does not submit an order</t>
+  </si>
+  <si>
+    <t>Done. Checkout writes a real order in one transaction, with one invoice per supplier and a server-allocated reference number.</t>
+  </si>
+  <si>
+    <t>Payment is still not taken and no email is sent.</t>
+  </si>
+  <si>
+    <t>FN-05</t>
+  </si>
+  <si>
+    <t>Real sign-in replaced the demo flag</t>
+  </si>
+  <si>
+    <t>Sign-in was a localStorage boolean anyone could set. It is now a database-backed session with a scrypt-hashed password.</t>
+  </si>
+  <si>
+    <t>Sessions are rows; signing out deletes the row, so a copied cookie stops working.</t>
+  </si>
+  <si>
+    <t>FN-06</t>
+  </si>
+  <si>
+    <t>Account history is real</t>
+  </si>
+  <si>
+    <t>The account area showed three fabricated orders. It now reads the signed-in user's actual orders, and reorder-first is built from what they have really bought.</t>
+  </si>
+  <si>
+    <t>Says so plainly when there is no history yet, rather than showing an empty grid.</t>
   </si>
   <si>
     <t>IN-07</t>
@@ -341,28 +1757,7 @@
     <t>The repository contains the previous agency's purchased theme, fonts and vendor libraries.</t>
   </si>
   <si>
-    <t>https://github.com/musawi1989/aussiemed</t>
-  </si>
-  <si>
-    <t>LG-01</t>
-  </si>
-  <si>
-    <t>Supply terms and conditions</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. Terms of sale are a legal document and must come from the business.</t>
-  </si>
-  <si>
-    <t>Page exists and says so on screen.</t>
-  </si>
-  <si>
-    <t>LG-02</t>
-  </si>
-  <si>
-    <t>Supply the privacy policy</t>
-  </si>
-  <si>
-    <t>Deliberately left empty. A privacy policy must describe what the system actually does with personal data, so it depends on the backend.</t>
+    <t>Decided with the client 16 Aug 2026. Confirmed private. It must stay private for as long as extraction/ holds the previous agency's purchased theme, fonts and vendor libraries, and public/products/seed holds third-party product photography.</t>
   </si>
   <si>
     <t>LG-03</t>
@@ -374,394 +1769,124 @@
     <t>info@aussiemed.com is assumed throughout. The old site used the misspelled assuiemed.com.</t>
   </si>
   <si>
-    <t>Also determines the sending domain for transactional email.</t>
-  </si>
-  <si>
-    <t>SEC-01</t>
-  </si>
-  <si>
-    <t>Remove the test credentials before any deployment</t>
-  </si>
-  <si>
-    <t>Four accounts share the password 123456: admin, musawi1989@gmail.com, supplier1, supplier2. Fine on a laptop, unacceptable anywhere else.</t>
-  </si>
-  <si>
-    <t>The on-screen credentials panel now renders only outside production, so a production build cannot leak it. The accounts themselves still must be removed or given real passwords.</t>
-  </si>
-  <si>
-    <t>AC-05</t>
-  </si>
-  <si>
-    <t>Confirm the VAT rate and whether it must be configurable</t>
-  </si>
-  <si>
-    <t>5% is hardcoded as a constant. A rate change would need a code change and would break historical orders if applied retroactively.</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>Rate must be stored on the order at the time it is placed.</t>
-  </si>
-  <si>
-    <t>AC-06</t>
-  </si>
-  <si>
-    <t>Approve the reference number format</t>
-  </si>
-  <si>
-    <t>AM-2026-000318 is invented. Must be server-allocated, unique and sequential; never generated in the browser.</t>
-  </si>
-  <si>
-    <t>Wording is fixed as Reference number, never order number.</t>
-  </si>
-  <si>
-    <t>AC-07</t>
-  </si>
-  <si>
-    <t>Approve the supplier invoice numbering</t>
-  </si>
-  <si>
-    <t>AM-2026-000318-01 is invented. One invoice per supplier per order.</t>
-  </si>
-  <si>
-    <t>Structure is enforced by a UNIQUE(orderId supplierId) constraint in the spec.</t>
-  </si>
-  <si>
-    <t>AC-09</t>
-  </si>
-  <si>
-    <t>Decide payment terms and credit accounts</t>
-  </si>
-  <si>
-    <t>Trade buyers usually expect credit limits and 30-day terms. Not modelled at all. v1 ships offline / purchase order only.</t>
-  </si>
-  <si>
-    <t>Affects the schema â€” decide before the backend.</t>
-  </si>
-  <si>
-    <t>AC-11</t>
-  </si>
-  <si>
-    <t>Approve the VAT rounding method on invoices</t>
-  </si>
-  <si>
-    <t>VAT is rounded per line rather than once per invoice, so the printed lines always add up to the printed total. The alternative rounds once and can leave lines that do not sum.</t>
-  </si>
-  <si>
-    <t>Verified by test: per-invoice VAT sums to the order VAT exactly.</t>
-  </si>
-  <si>
-    <t>AC-12</t>
-  </si>
-  <si>
-    <t>Confirm the reference number sequence resets each year</t>
-  </si>
-  <si>
-    <t>OUR DECISION: the sequence restarts at 000001 each calendar year, so AM-2026-000001 and AM-2027-000001 can both exist. If accounting needs a single unbroken sequence this must change before real orders.</t>
-  </si>
-  <si>
-    <t>Held in a settings row keyed orderSequence:YYYY and incremented inside the checkout transaction.</t>
-  </si>
-  <si>
-    <t>AC-13</t>
-  </si>
-  <si>
-    <t>Decide whether an order should reserve stock</t>
-  </si>
-  <si>
-    <t>OUR DECISION: checkout does not decrement or reserve anything, because there are no stock levels â€” only an in/out flag. Two customers can order the last unit.</t>
-  </si>
-  <si>
-    <t>Depends on FN-08. Out-of-stock is re-checked at checkout, so a line that sold out while the form was open is rejected.</t>
-  </si>
-  <si>
-    <t>BE-04</t>
-  </si>
-  <si>
-    <t>Build comma-safe .xlsx bulk upload</t>
-  </si>
-  <si>
-    <t>Parsed natively with exceljs, never by splitting on commas â€” that is what broke comma-containing category names.</t>
-  </si>
-  <si>
-    <t>Unknown brands must be reported per row, never skipped silently.</t>
-  </si>
-  <si>
-    <t>BE-05</t>
-  </si>
-  <si>
-    <t>Build the email flows</t>
-  </si>
-  <si>
-    <t>OTP verification, order confirmation, restock alerts, supplier notifications to both primary and secondary addresses.</t>
-  </si>
-  <si>
-    <t>Needs an SMTP provider.</t>
-  </si>
-  <si>
-    <t>BE-08</t>
-  </si>
-  <si>
-    <t>Decide money representation before any data lands</t>
-  </si>
-  <si>
-    <t>Money is stored as integer fils rather than Decimal, because SQLite has no native decimal type and Prisma falls back to a float there. Confirm this is acceptable to the accountant.</t>
-  </si>
-  <si>
-    <t>Every money column is named *Fils. Switching to Decimal on Postgres later is a mechanical migration.</t>
-  </si>
-  <si>
-    <t>BE-10</t>
-  </si>
-  <si>
-    <t>Retire the catalogue snapshot endpoint</t>
-  </si>
-  <si>
-    <t>Client components fetch the whole catalogue from /api/v1/catalog/snapshot. Fine for 71 products; not for thousands. Goes away when the cart moves server-side.</t>
-  </si>
-  <si>
-    <t>Phase 3 removes the need.</t>
-  </si>
-  <si>
-    <t>BE-12</t>
-  </si>
-  <si>
-    <t>Merge a guest cart into the user cart on sign-in</t>
-  </si>
-  <si>
-    <t>Carts are keyed by a cookie so a visitor can shop before signing in. The merge on sign-in is specified but cannot be built until auth exists.</t>
-  </si>
-  <si>
-    <t>Cart cookie: aussiemed_cart, httpOnly, 30 day lifetime â€” OUR INVENTED VALUES.</t>
-  </si>
-  <si>
-    <t>BE-14</t>
-  </si>
-  <si>
-    <t>Confirm the default order and invoice status</t>
-  </si>
-  <si>
-    <t>OUR DECISION: new orders are Pending and each supplier invoice is Pending. The real workflow â€” who moves an order to Processing, and when an invoice becomes Issued â€” is not defined.</t>
-  </si>
-  <si>
-    <t>Order statuses available: Pending, Processing, Dispatched, Delivered, Cancelled.</t>
-  </si>
-  <si>
-    <t>BE-15</t>
-  </si>
-  <si>
-    <t>Passwords were built instead of the specified email OTP</t>
-  </si>
-  <si>
-    <t>BACKEND_SPEC.md specifies passwordless sign-in by emailed code. Passwords were requested instead and built. Livingstone advertises password-free login as a feature, so the spec was not arbitrary.</t>
-  </si>
-  <si>
-    <t>Both can coexist: the schema keeps otpCode and otpExpiresAt. Decide before launch.</t>
-  </si>
-  <si>
-    <t>BE-19</t>
-  </si>
-  <si>
-    <t>Guest checkout is allowed</t>
-  </si>
-  <si>
-    <t>OUR DECISION: an order can be placed without signing in, and is then tied to the cart cookie. Signing in simply attaches the order to the account.</t>
-  </si>
-  <si>
-    <t>If trade accounts should be required to order, this must change â€” it also affects credit terms and pricing.</t>
-  </si>
-  <si>
-    <t>BE-22</t>
-  </si>
-  <si>
-    <t>Confirm one supplier account per company</t>
-  </si>
-  <si>
-    <t>OUR DECISION: each supplier company links to a single user. Real suppliers usually need several people with their own logins.</t>
-  </si>
-  <si>
-    <t>Schema allows it via Supplier.userId; supporting several needs a join table.</t>
-  </si>
-  <si>
-    <t>BE-31</t>
-  </si>
-  <si>
-    <t>Log every out-of-stock toggle instead of only the current flag</t>
-  </si>
-  <si>
-    <t>The manual out-of-stock checkbox stores current state only. How long a product has been unavailable, and how quickly a supplier restocks, are unanswerable — and both are conversations the admin has with suppliers.</t>
-  </si>
-  <si>
-    <t>From spec section 1.4. Same one-way-door property as BE-30: every toggle that happens before this exists is lost. Small change — a log table written from the same service function that sets the flag.</t>
-  </si>
-  <si>
-    <t>BE-32</t>
-  </si>
-  <si>
-    <t>Log storefront searches, especially the ones that return nothing</t>
-  </si>
-  <si>
-    <t>A search that returns no results is a customer telling you what to stock, and it is currently discarded. For a distributor deciding what to source next, the list of terms that found nothing is one of the most valuable things the site can produce.</t>
-  </si>
-  <si>
-    <t>From spec section 2.4 D-2. Cannot be reconstructed later — nobody can recall what a visitor searched for last month. Distinct from FN-10 (search is client-side only), though doing FN-10 first would make the logging server-side and simpler.</t>
-  </si>
-  <si>
-    <t>BE-33</t>
-  </si>
-  <si>
-    <t>Record what each supplier has promised: lead time and acknowledgement SLA</t>
-  </si>
-  <si>
-    <t>On-time means nothing without a promise to measure against. These are numbers agreed personally with each supplier during onboarding, and there is nowhere to put them.</t>
-  </si>
-  <si>
-    <t>From spec section 1.2. Two integer columns on Supplier plus admin fields, but note the dependency runs the other way: the numbers are a business input the admin has to collect from each supplier, so ask for them before building anything that displays an on-time rate.</t>
-  </si>
-  <si>
-    <t>DA-02</t>
-  </si>
-  <si>
-    <t>Verify the product-to-category mapping</t>
-  </si>
-  <si>
-    <t>The extraction had no product-category link at all, so every mapping on the site is ours. The catalogue is now 71 products across 146 categories and none of that mapping has been checked by anyone who knows the range.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026 after DA-23: 60 active products, 0 uncategorised.</t>
-  </si>
-  <si>
-    <t>DA-05</t>
-  </si>
-  <si>
-    <t>Approve the product descriptions</t>
-  </si>
-  <si>
-    <t>The source had no descriptions. All 71 active products now carry text we generated from the product name and supplier listing, and it goes out under AussieMed's name.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026 after DA-23: 60 of 60 active products have a generated description.</t>
-  </si>
-  <si>
-    <t>DA-07</t>
-  </si>
-  <si>
-    <t>Supply the hero banner image</t>
-  </si>
-  <si>
-    <t>The live site loads Content/Banner/July-2026/u1oannrj.png, which the extraction never captured â€” only Brand, Category, Product and WebHtml folders were mirrored.</t>
-  </si>
-  <si>
-    <t>A genuine AussieMed CMS image stands in.</t>
-  </si>
-  <si>
-    <t>DA-08</t>
-  </si>
-  <si>
-    <t>Obtain Gilroy Regular and Medium</t>
-  </si>
-  <si>
-    <t>The theme references them but the files were never delivered, so the live site already falls back to a generic sans for body text. Gilroy is a commercial typeface.</t>
-  </si>
-  <si>
-    <t>Figtree stands in. Swap --font-body when the licensed files arrive; nothing else changes.</t>
-  </si>
-  <si>
-    <t>DA-10</t>
-  </si>
-  <si>
-    <t>Supply real pack and carton structures</t>
-  </si>
-  <si>
-    <t>Outer packs were invented for 15 lines (a box that comes 10 to a carton). Real pack hierarchies are needed.</t>
-  </si>
-  <si>
-    <t>Largely superseded by DA-20: packaging moved from separate carton SKUs into named price breaks on 15 Aug 2026, so the invented figures now live in scripts/variants.mjs rather than in outer packs. Kept open because the underlying question â€” what is a real carton and box for each line â€” is unanswered either way.</t>
-  </si>
-  <si>
-    <t>DA-11</t>
-  </si>
-  <si>
-    <t>Supply real variant data</t>
-  </si>
-  <si>
-    <t>Size and colour axes are invented. Product 183 had variationButtons: 6, so real variant data existed in the old system.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: the same five sizes and three colours are stamped on all six glove products regardless of what the supplier actually sells. FN-07 covers the wiring; this row covers the data.</t>
-  </si>
-  <si>
-    <t>DA-12</t>
-  </si>
-  <si>
-    <t>Supply real product specifications</t>
-  </si>
-  <si>
-    <t>Spec attributes are currently derived generically. Trade buyers check material, standard, sterility and pack size before ordering.</t>
-  </si>
-  <si>
-    <t>These become search filters later.</t>
-  </si>
-  <si>
-    <t>DA-13</t>
-  </si>
-  <si>
-    <t>Supply safety data sheets and spec sheets</t>
-  </si>
-  <si>
-    <t>For laboratory and medical buyers an SDS is frequently a compliance requirement, not a nicety. None were supplied.</t>
-  </si>
-  <si>
-    <t>The data model supports documents; the UI section stays hidden until real files exist.</t>
-  </si>
-  <si>
-    <t>DA-18</t>
-  </si>
-  <si>
-    <t>Product ids are derived from slugs</t>
-  </si>
-  <si>
-    <t>Carts and wishlists are stored in the browser against a product id. Ids are now hashed from the slug so they survive a re-seed, which means CHANGING A PRODUCT SLUG ORPHANS ANY SAVED CART LINE referencing it.</t>
-  </si>
-  <si>
-    <t>Resolved properly when the cart moves server-side and references SKU rows directly.</t>
-  </si>
-  <si>
-    <t>DA-19</t>
-  </si>
-  <si>
-    <t>Supplier email addresses are invented</t>
-  </si>
-  <si>
-    <t>The seed writes orders@&lt;supplier&gt;.example and accounts@&lt;supplier&gt;.example because secondaryEmail is mandatory. No supplier will receive anything at these addresses.</t>
-  </si>
-  <si>
-    <t>Both addresses are meant to receive order notifications once email exists.</t>
-  </si>
-  <si>
-    <t>DA-21</t>
-  </si>
-  <si>
-    <t>Verify the automatic variant grouping</t>
-  </si>
-  <si>
-    <t>Products are grouped into families by stripping sizes and volumes from their names. It found 2 families in the seeded catalogue. A real catalogue will group differently and some groupings will be wrong.</t>
-  </si>
-  <si>
-    <t>The admin product screens should let a family be set explicitly rather than inferred â€” see BE-20.</t>
-  </si>
-  <si>
-    <t>DA-24</t>
-  </si>
-  <si>
-    <t>13 of 60 products have no image</t>
-  </si>
-  <si>
-    <t>Those products render as a monogram tile rather than a photograph. It is a deliberate stand-in and reads acceptably in a grid, but on a trade catalogue an image is often how a buyer confirms they have the right item.</t>
-  </si>
-  <si>
-    <t>Was 19 of 71. Ten went with the extraction products under DA-23. Four more were added deliberately: their image files turned out to be SVG placeholders saved with a .jpg extension, which the image optimiser rejected with a 400 â€” see DA-25. The remaining nine have no sourceSku or sourceUrl recorded, so there is nothing to retry a fetch against, and no more third-party photography was sourced because DA-17 already limits what may ship. Subset of DA-03.</t>
+    <t>Decided with the client 16 Aug 2026. info@aussiemed.com, used both as the public contact address and as the sending domain for transactional email. The business owns aussiemed.com; the old misspelled assuiemed.com is not to be used anywhere.</t>
+  </si>
+  <si>
+    <t>BE-06</t>
+  </si>
+  <si>
+    <t>Add an audit log</t>
+  </si>
+  <si>
+    <t>Every status transition and every admin or supplier write should be recorded.</t>
+  </si>
+  <si>
+    <t>Done 16 Aug 2026. AuditLog now records every admin write with the actor, the entity and the values that changed, readable at /admin/audit and filtered per record from each product's page. Entries are never edited or deleted, so the screen has no actions on it. Supplier portal writes join it when BE-21 lands.</t>
+  </si>
+  <si>
+    <t>DA-23</t>
+  </si>
+  <si>
+    <t>Two suppliers were asked for; four exist</t>
+  </si>
+  <si>
+    <t>The brief was Chemist Warehouse and Livingstone for testing, with the products that made no sense removed. Northline Uniforms and AussieMed Distribution survived that clean-up and still own 11 of the 71 products between them, so a third of the supplier list and a seventh of the catalogue is left over from the old extraction.</t>
+  </si>
+  <si>
+    <t>Done 15 Aug 2026. The 11 extraction products and suppliers 20 and 21 are no longer emitted by scripts/build-catalog.mjs. The database keeps them as Inactive rather than deleting them, because 2 invoices and 3 order lines still name them â€” order history survives. The catalogue is now exactly the 60 test products, 30 from each supplier.</t>
+  </si>
+  <si>
+    <t>DN-07</t>
+  </si>
+  <si>
+    <t>Unique page titles and meta descriptions</t>
+  </si>
+  <si>
+    <t>Every page carried the identical title 'Aussie Med || Home' with an empty description.</t>
+  </si>
+  <si>
+    <t>Built per page and per product.</t>
+  </si>
+  <si>
+    <t>DN-08</t>
+  </si>
+  <si>
+    <t>Broken cart images and unresolved asset paths</t>
+  </si>
+  <si>
+    <t>Cart images had a bare domain with no path; templates contained literal '~/' paths.</t>
+  </si>
+  <si>
+    <t>All image paths are local and asserted.</t>
+  </si>
+  <si>
+    <t>DN-09</t>
+  </si>
+  <si>
+    <t>Volume breaks visible while scanning</t>
+  </si>
+  <si>
+    <t>Only a savings badge was shown. The full break table now appears on every product card using +1/+10/+50 notation.</t>
+  </si>
+  <si>
+    <t>DN-10</t>
+  </si>
+  <si>
+    <t>Ex VAT / Inc VAT toggle</t>
+  </si>
+  <si>
+    <t>Procurement compares ex-tax and the approver reads inc-tax, so the same buyer needs both during one order.</t>
+  </si>
+  <si>
+    <t>Persists per browser.</t>
+  </si>
+  <si>
+    <t>DN-12</t>
+  </si>
+  <si>
+    <t>Adopt the existing brand theme</t>
+  </si>
+  <si>
+    <t>Navy #29387d, red #ea2227 and Gilroy, read from the live site's computed styles rather than eyeballed.</t>
+  </si>
+  <si>
+    <t>Logo, favicon and all 11 category images are the brand own.</t>
+  </si>
+  <si>
+    <t>DN-13</t>
+  </si>
+  <si>
+    <t>Catalogue seeded with real products</t>
+  </si>
+  <si>
+    <t>Sixty real items replaced invented placeholders so the storefront can be judged against products that actually exist.</t>
+  </si>
+  <si>
+    <t>Thirty from each of two public supplier catalogues, spanning 23 categories.</t>
+  </si>
+  <si>
+    <t>DN-15</t>
+  </si>
+  <si>
+    <t>Product images added for testing</t>
+  </si>
+  <si>
+    <t>Fifty-two of 71 products now carry real photography so the layout can be judged with images rather than placeholder tiles.</t>
+  </si>
+  <si>
+    <t>Third-party supplier images in public/products/seed. A data check now asserts every referenced image file exists on disk.</t>
+  </si>
+  <si>
+    <t>DN-21</t>
+  </si>
+  <si>
+    <t>Three sign-in doors, one per role</t>
+  </si>
+  <si>
+    <t>Buyers sign in at the account page, suppliers at the business portal, admins at /admin. Signing in at the wrong door names the right one instead of letting someone into the wrong area.</t>
+  </si>
+  <si>
+    <t>Verified: each role accepted at its own door and rejected with 403 at the other two.</t>
   </si>
   <si>
     <t>FE-30</t>
@@ -773,1093 +1898,7 @@
     <t>The header toggle was removed before VAT was folded into the displayed price, so a buyer approving an invoice has no inc-VAT figure anywhere on the storefront. Checkout still adds VAT, so the total at the end is higher than every price shown.</t>
   </si>
   <si>
-    <t>Follow up to DEC-14. Decide whether displayed prices become VAT inclusive or the Ex. VAT labels simply stay.</t>
-  </si>
-  <si>
-    <t>FN-07</t>
-  </si>
-  <si>
-    <t>Size and colour switching is not wired</t>
-  </si>
-  <si>
-    <t>The variant dropdown built on 15 Aug 2026 (DEC-12) switches between sibling products by size or volume, and that works. The separate Size and Colour chips on gloves and the scrub top are a different thing and still do nothing â€” no sibling SKU exists behind any of them.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: 13 option axes across 6 products. Every glove carries an identical Size = XS/S/M/L/XL and Colour = Black/Blue/Green with no SKU attached to any value.</t>
-  </si>
-  <si>
-    <t>FN-08</t>
-  </si>
-  <si>
-    <t>Stock is a boolean</t>
-  </si>
-  <si>
-    <t>Products are either in or out of stock. There are no quantities, so no low-stock warnings and no backorder handling.</t>
-  </si>
-  <si>
-    <t>Decide whether real stock levels are needed.</t>
-  </si>
-  <si>
-    <t>FN-09</t>
-  </si>
-  <si>
-    <t>Decide on expiry and short-dated stock</t>
-  </si>
-  <si>
-    <t>Medical stock expires. Livingstone sells short-dated lines at a discount. This needs batch and expiry tracking in the schema if wanted.</t>
-  </si>
-  <si>
-    <t>Schema-shaping â€” decide before the backend is built.</t>
-  </si>
-  <si>
-    <t>FN-12</t>
-  </si>
-  <si>
-    <t>Nothing shows which clients are overdue to reorder</t>
-  </si>
-  <si>
-    <t>In a reorder-first business this is the single most useful signal there is: a clinic that buys gloves every three weeks and has not ordered in five needs a phone call. It is computable from order history alone once there are three orders per client — no new data capture required.</t>
-  </si>
-  <si>
-    <t>From spec sections 2.3 C-4 and C-5 and queue Q-3. Unlike BE-30 to BE-32 this is not urgent, because the underlying order history is already being recorded and the calculation can be added at any time. Build it once real clients are ordering; with four test orders it would only ever say insufficient data.</t>
-  </si>
-  <si>
-    <t>FN-13</t>
-  </si>
-  <si>
-    <t>The client account has no Buy Again</t>
-  </si>
-  <si>
-    <t>A returning buyer has to search for products they have already bought. For a reorder-first marketplace this is the shortest path between the platform and revenue, and it needs no metrics work at all — just their own order history, sorted by how often they buy each line.</t>
-  </si>
-  <si>
-    <t>From spec section 4 CL-1 and CL-3. Independent of the whole metrics programme and arguably worth more than any dashboard in it. Depends on nothing that is not already built.</t>
-  </si>
-  <si>
-    <t>IN-01</t>
-  </si>
-  <si>
-    <t>Choose a hosting target</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. The site runs locally only.</t>
-  </si>
-  <si>
-    <t>Deliberately deferred until the build is approved.</t>
-  </si>
-  <si>
-    <t>IN-02</t>
-  </si>
-  <si>
-    <t>Choose the database</t>
-  </si>
-  <si>
-    <t>SQLite for development with a switch to Postgres. No SQLite-only SQL.</t>
-  </si>
-  <si>
-    <t>IN-03</t>
-  </si>
-  <si>
-    <t>Choose an SMTP provider and sending domain</t>
-  </si>
-  <si>
-    <t>Required for every transactional email.</t>
-  </si>
-  <si>
-    <t>Must not be the misspelled assuiemed.com domain.</t>
-  </si>
-  <si>
-    <t>IN-04</t>
-  </si>
-  <si>
-    <t>Decide on a payment gateway</t>
-  </si>
-  <si>
-    <t>v1 ships offline / purchase order only. Gateway integration is a pluggable interface.</t>
-  </si>
-  <si>
-    <t>LG-05</t>
-  </si>
-  <si>
-    <t>Transfer the theme licence</t>
-  </si>
-  <si>
-    <t>The front-end theme was likely purchased under the development agency's account. The extraction also contains their vendor libraries and fonts.</t>
-  </si>
-  <si>
-    <t>Repository must stay private because of this.</t>
-  </si>
-  <si>
-    <t>LG-06</t>
-  </si>
-  <si>
-    <t>Supply company registration details</t>
-  </si>
-  <si>
-    <t>Trade licence number, registered address and TRN are needed for the footer and for invoices.</t>
-  </si>
-  <si>
-    <t>SEC-02</t>
-  </si>
-  <si>
-    <t>Add rate limiting to sign-in</t>
-  </si>
-  <si>
-    <t>Nothing limits password attempts, so the sign-in endpoint can be brute forced. The spec asks for rate limiting on auth in the hardening phase.</t>
-  </si>
-  <si>
-    <t>Matters more with short passwords than with OTP.</t>
-  </si>
-  <si>
-    <t>SEC-03</t>
-  </si>
-  <si>
-    <t>Agree a password policy</t>
-  </si>
-  <si>
-    <t>No minimum length, complexity or reuse rule is enforced. 123456 was accepted because nothing rejects it.</t>
-  </si>
-  <si>
-    <t>Moot if the OTP flow in BE-15 is adopted instead.</t>
-  </si>
-  <si>
-    <t>AC-08</t>
-  </si>
-  <si>
-    <t>Confirm the rounding policy</t>
-  </si>
-  <si>
-    <t>Half-up to 2 decimals. Per-line VAT is accumulated then rounded once, so the invoice split and the order total agree to the cent.</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>Verified by test; needs sign-off that the method is acceptable.</t>
-  </si>
-  <si>
-    <t>AC-10</t>
-  </si>
-  <si>
-    <t>Confirm the default price display</t>
-  </si>
-  <si>
-    <t>Prices are shown Ex. VAT everywhere, and since 15 Aug 2026 there is no way for a buyer to see an inc-VAT figure at all â€” the header toggle was removed at the client's request before VAT was folded into the displayed price.</t>
-  </si>
-  <si>
-    <t>See DEC-14 for the decision and FE-30 for the gap it leaves open.</t>
-  </si>
-  <si>
-    <t>BE-13</t>
-  </si>
-  <si>
-    <t>Expire abandoned guest carts</t>
-  </si>
-  <si>
-    <t>Cart rows are never cleaned up. Every visitor who adds an item creates one that lives forever.</t>
-  </si>
-  <si>
-    <t>The spec wants abandoned carts over 24h reportable under Admin &gt; Marketing, so expiry and that report should be designed together.</t>
-  </si>
-  <si>
-    <t>BE-16</t>
-  </si>
-  <si>
-    <t>Confirm the session lifetime</t>
-  </si>
-  <si>
-    <t>OUR INVENTED VALUE: sessions last 7 days, then require signing in again. No idle timeout and no re-authentication for sensitive actions.</t>
-  </si>
-  <si>
-    <t>Cookie is httpOnly and sameSite=lax; secure only in production so local http still works.</t>
-  </si>
-  <si>
-    <t>BE-17</t>
-  </si>
-  <si>
-    <t>Purge expired sessions on a schedule</t>
-  </si>
-  <si>
-    <t>Expired session rows are never deleted. purgeExpiredSessions() exists but nothing calls it.</t>
-  </si>
-  <si>
-    <t>Trivial once any scheduled job exists.</t>
-  </si>
-  <si>
-    <t>BE-18</t>
-  </si>
-  <si>
-    <t>Password hashing uses scrypt, not bcrypt</t>
-  </si>
-  <si>
-    <t>OUR DECISION: scrypt from Node's own crypto module, so there is no dependency to keep patched. The spec names bcrypt. Both are appropriate; only src/lib/auth.ts knows the format.</t>
-  </si>
-  <si>
-    <t>Stored as scrypt$salt$hash so the algorithm is self-describing and can be migrated per user.</t>
-  </si>
-  <si>
-    <t>BE-23</t>
-  </si>
-  <si>
-    <t>Admin figures are counted live, never cached</t>
-  </si>
-  <si>
-    <t>OUR DECISION: every number on the admin dashboard is counted from the database on each request. Caching them is how the old platform let admin counts and storefront counts disagree.</t>
-  </si>
-  <si>
-    <t>Still true after the admin build: every dashboard figure is a live count. Cheap at 60 products and 4 orders; revisit when either grows.</t>
-  </si>
-  <si>
-    <t>BE-24</t>
-  </si>
-  <si>
-    <t>Supplier data is scoped by query, not by filtering</t>
-  </si>
-  <si>
-    <t>OUR DECISION: a supplier's products and invoice lines are fetched through their supplier id, so another supplier's rows are never loaded rather than loaded and hidden.</t>
-  </si>
-  <si>
-    <t>Keep this rule as the supplier portal grows â€” filtering after fetching is how leaks happen.</t>
-  </si>
-  <si>
-    <t>BE-27</t>
-  </si>
-  <si>
-    <t>No marketing screens: wishlists and abandoned carts</t>
-  </si>
-  <si>
-    <t>Both are already recorded in the database and nobody can see either. An abandoned cart is the cheapest sale to recover, and a wishlist says what a buyer wants before they buy it.</t>
-  </si>
-  <si>
-    <t>Split out of BE-02 when the admin screens were built.</t>
-  </si>
-  <si>
-    <t>BE-28</t>
-  </si>
-  <si>
-    <t>No reports: sales by supplier, category or period</t>
-  </si>
-  <si>
-    <t>The dashboard totals every order ever placed and nothing else. There is no way to answer which supplier sells most, what a month looked like, or which categories are dead.</t>
-  </si>
-  <si>
-    <t>Split out of BE-02. Wants AC-09 settled first so periods line up with terms.</t>
-  </si>
-  <si>
-    <t>DA-14</t>
-  </si>
-  <si>
-    <t>Confirm the brand list</t>
-  </si>
-  <si>
-    <t>Brands were assigned by reading product names, because neither source listed a brand field. Bad extractions were caught by hand (Goat, Hello, Roger) but the list has never been checked against reality.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026 after DA-23: 26 brands across the 60 test products.</t>
-  </si>
-  <si>
-    <t>DA-15</t>
-  </si>
-  <si>
-    <t>Decide on duplicate categories</t>
-  </si>
-  <si>
-    <t>Six category names are duplicated across the tree and two ('Oral Care') are duplicated inside one department. Slugs were disambiguated by appending the ID.</t>
-  </si>
-  <si>
-    <t>Re-measured 15 Aug 2026: still 6 duplicated names, 12 categories in total. Slugs are disambiguated by appending the numeric id (oral-care vs oral-care-96). 10 of the 12 hold no products at all, so most of the duplication is invisible to buyers today.</t>
-  </si>
-  <si>
-    <t>DA-16</t>
-  </si>
-  <si>
-    <t>Confirm the missing department</t>
-  </si>
-  <si>
-    <t>Livingstone has 12 departments; AussieMed has 11 of them. 'Tattoo &amp; Piercing' is absent.</t>
-  </si>
-  <si>
-    <t>Confirm this is intentional rather than lost.</t>
-  </si>
-  <si>
-    <t>FN-10</t>
-  </si>
-  <si>
-    <t>Search is client-side only</t>
-  </si>
-  <si>
-    <t>No synonyms, no typo tolerance, no ranking beyond term matching.</t>
-  </si>
-  <si>
-    <t>Adequate for 61 products; will not scale to a real catalogue.</t>
-  </si>
-  <si>
-    <t>IN-05</t>
-  </si>
-  <si>
-    <t>Supply Google and Facebook OAuth keys</t>
-  </si>
-  <si>
-    <t>Social login endpoints currently return 501.</t>
-  </si>
-  <si>
-    <t>IN-08</t>
-  </si>
-  <si>
-    <t>Correct the git author name</t>
-  </si>
-  <si>
-    <t>Commits are authored as 'AussieMed' because git had no identity configured.</t>
-  </si>
-  <si>
-    <t>Fixable with git config user.name and an amend.</t>
-  </si>
-  <si>
-    <t>IN-09</t>
-  </si>
-  <si>
-    <t>Set up continuous integration</t>
-  </si>
-  <si>
-    <t>No CI runs the checks automatically. The spec asks for the currency grep check to run in CI.</t>
-  </si>
-  <si>
-    <t>Locally: npm run verify covers data checks, tests and typecheck.</t>
-  </si>
-  <si>
-    <t>IN-10</t>
-  </si>
-  <si>
-    <t>Plan backups and disaster recovery</t>
-  </si>
-  <si>
-    <t>No backup strategy exists for the database or uploaded files.</t>
-  </si>
-  <si>
-    <t>Relevant once there is a real database.</t>
-  </si>
-  <si>
-    <t>LG-04</t>
-  </si>
-  <si>
-    <t>Approve the About / Contact / Order Support copy</t>
-  </si>
-  <si>
-    <t>All placeholder text.</t>
-  </si>
-  <si>
-    <t>Pages carry a visible placeholder notice.</t>
-  </si>
-  <si>
-    <t>DEC-01</t>
-  </si>
-  <si>
-    <t>Fresh build â€” the previous site is reference only</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: nothing to do with the previous site. The extraction is mined for data and business rules; its code and behaviour are discarded.</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>Its category tree, product data and bug history were kept. Its markup was not.</t>
-  </si>
-  <si>
-    <t>DEC-02</t>
-  </si>
-  <si>
-    <t>Keep the existing visual brand</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026, correcting an earlier over-broad reading: the storefront must keep the current AussieMed look, not be redesigned.</t>
-  </si>
-  <si>
-    <t>Navy #29387d, red #ea2227 and Gilroy were read from the live site's computed styles. See DA-08 for the missing Gilroy weights.</t>
-  </si>
-  <si>
-    <t>DEC-03</t>
-  </si>
-  <si>
-    <t>Local only until the client approves</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: not to go online until there is a version they are happy with locally.</t>
-  </si>
-  <si>
-    <t>Nothing is deployed. robots noindex is site-wide. Hosting is IN-01.</t>
-  </si>
-  <si>
-    <t>DEC-04</t>
-  </si>
-  <si>
-    <t>External connectors are handled last</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: anything needing a third-party account waits until the end so the build never stalls on credentials.</t>
-  </si>
-  <si>
-    <t>Payment IN-04, SMTP IN-03, OAuth IN-05, hosting IN-01. Built behind seams with local stand-ins.</t>
-  </si>
-  <si>
-    <t>DEC-05</t>
-  </si>
-  <si>
-    <t>Follow Livingstone for B2B catalogue and pricing behaviour</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026 with livingstone.com.au as the reference, and all suggested changes accepted.</t>
-  </si>
-  <si>
-    <t>Produced the pack/UOM model, price breaks on cards, the Ex/Inc VAT toggle, variant axes, spec attributes and per-product tax class.</t>
-  </si>
-  <si>
-    <t>DEC-06</t>
-  </si>
-  <si>
-    <t>Seed the catalogue from two real suppliers for testing</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026: list Chemist Warehouse and Livingstone as suppliers with 30 items each, and remove the invented placeholders.</t>
-  </si>
-  <si>
-    <t>60 real products seeded. Both are unaffiliated third parties â€” DA-17 must close before launch.</t>
-  </si>
-  <si>
-    <t>DEC-07</t>
-  </si>
-  <si>
-    <t>Add product images</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026. Supplier photography was downloaded for local testing.</t>
-  </si>
-  <si>
-    <t>52 of 71 products have an image. Third-party assets â€” DA-03 must close before launch.</t>
-  </si>
-  <si>
-    <t>DEC-08</t>
-  </si>
-  <si>
-    <t>Four test accounts with a shared placeholder password</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: admin, musawi1989@gmail.com, supplier1 and supplier2, all with 123456. Explicitly described as local testing only, chosen to be memorable, and to be changed before anything real.</t>
-  </si>
-  <si>
-    <t>Implemented as asked. SEC-01 tracks removing them; SEC-03 tracks agreeing a password policy.</t>
-  </si>
-  <si>
-    <t>DEC-09</t>
-  </si>
-  <si>
-    <t>One sign-in door per role</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the business portal is the supplier login, the account login is for buyers, and admin is reached at /admin.</t>
-  </si>
-  <si>
-    <t>Implemented. Signing in at the wrong door names the right one rather than admitting the user.</t>
-  </si>
-  <si>
-    <t>DEC-10</t>
-  </si>
-  <si>
-    <t>Record every generated value and decision in this register</t>
-  </si>
-  <si>
-    <t>Stated 14 Aug 2026 and repeated 15 Aug: everything invented on the client's behalf must be written down rather than left in the code.</t>
-  </si>
-  <si>
-    <t>This register is the record. docs/Things That Need Attention.xlsx is generated from it and npm run register validates it.</t>
-  </si>
-  <si>
-    <t>DEC-11</t>
-  </si>
-  <si>
-    <t>Price breaks are packaging levels, not arbitrary quantities</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: a break at 12 exists because a carton holds 12, and a break at 48 because a box holds 4 cartons. The quantity and the packaging level are the same fact.</t>
-  </si>
-  <si>
-    <t>Each break now carries its level name. Corrects an earlier model that treated breaks as percentage discounts at round numbers.</t>
-  </si>
-  <si>
-    <t>DEC-12</t>
-  </si>
-  <si>
-    <t>Variants are a dropdown across sibling products</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the 375ml and the 60ml stay as separate products, and each carries a dropdown listing the whole family so a buyer can find their part quickly.</t>
-  </si>
-  <si>
-    <t>Replaces the Each/Carton chips on cards. Implemented as navigation between products, not options on one product, because each size has its own SKU, stock and price.</t>
-  </si>
-  <si>
-    <t>DEC-13</t>
-  </si>
-  <si>
-    <t>One sign-in button in the header, with a dropdown per role</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: replace the Business portal and Account links with a single blue Sign in button whose dropdown offers sign in as a buyer and sign in as a supplier.</t>
-  </si>
-  <si>
-    <t>Implemented in src/components/SignInMenu.tsx. Admin is deliberately absent from the dropdown; staff go to /admin directly. Once signed in the button becomes the way back to the user own area.</t>
-  </si>
-  <si>
-    <t>DEC-14</t>
-  </si>
-  <si>
-    <t>The AED label and the Ex/Inc VAT toggle are gone from the header</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: remove the AED text and the VAT options because VAT is to be carried in the displayed price later.</t>
-  </si>
-  <si>
-    <t>VatToggle deleted from the header. includeVat still exists in src/lib/store.tsx defaulting to ex-VAT with no UI control, so prices read ex-VAT everywhere until the pricing change lands. FE-30 tracks that follow up.</t>
-  </si>
-  <si>
-    <t>DEC-15</t>
-  </si>
-  <si>
-    <t>Sign out lives in the header, in the sign in button slot</t>
-  </si>
-  <si>
-    <t>Stated 15 Aug 2026: the sign out button always sits where the Sign in button would be when signed out.</t>
-  </si>
-  <si>
-    <t>Moved out of the account, admin and business portal pages into src/components/SignInMenu.tsx, so it is reachable from every page rather than only the dashboard. Signed in, the slot shows the account name plus Sign out.</t>
-  </si>
-  <si>
-    <t>DEC-16</t>
-  </si>
-  <si>
-    <t>Empty categories are hidden from navigation, not removed</t>
-  </si>
-  <si>
-    <t>The category tree came from Livingstone and is far wider than the 60 test products fill. Hiding what is empty keeps every menu entry useful; removing them would lose the shape of the intended range, and hard-coding a shorter list would need maintaining by hand.</t>
-  </si>
-  <si>
-    <t>Our decision, 15 Aug 2026, taken while closing FN-11. It is computed rather than configured, so categories reappear on their own as products are filed into them. Direct URLs still work. Say if you would rather the full tree stayed visible.</t>
-  </si>
-  <si>
-    <t>DEC-17</t>
-  </si>
-  <si>
-    <t>Renaming a category does not change its URL</t>
-  </si>
-  <si>
-    <t>The slug is the address. A category that has been linked to, bookmarked or indexed keeps working when its display name changes, and changing both would silently break every existing link.</t>
-  </si>
-  <si>
-    <t>Our decision, 16 Aug 2026. Renaming to something genuinely different means creating a category and moving products, or a redirect table we have not built. Say if you would rather the URL followed the name.</t>
-  </si>
-  <si>
-    <t>DEC-18</t>
-  </si>
-  <si>
-    <t>A product cannot go live without a SKU and a category</t>
-  </si>
-  <si>
-    <t>Both make a live product broken rather than merely incomplete: no SKU means nothing to buy, no category means nobody can browse to it. The admin screen refuses the transition and says which one is missing.</t>
-  </si>
-  <si>
-    <t>Our decision, 16 Aug 2026, enforced in src/lib/admin.ts rather than in the form, so posting to the endpoint directly cannot bypass it.</t>
-  </si>
-  <si>
-    <t>DEC-19</t>
-  </si>
-  <si>
-    <t>Delivered and cancelled orders cannot be reopened</t>
-  </si>
-  <si>
-    <t>Both are closed documents the customer already holds. A status that contradicts what they received is worse than no status at all.</t>
-  </si>
-  <si>
-    <t>Our decision, 16 Aug 2026. A delivered order needs a return and a cancelled one needs a new order â€” neither of which exists yet. Confirm this matches how you actually work.</t>
-  </si>
-  <si>
-    <t>DEC-20</t>
-  </si>
-  <si>
-    <t>The back office looks like the reference operations UI, not like the shop</t>
-  </si>
-  <si>
-    <t>The client supplied screenshots of the tool they use day to day. Staff processing orders are doing operational work, and the storefront chrome was both a distraction and the reason documents printed badly.</t>
-  </si>
-  <si>
-    <t>Agreed 16 Aug 2026. Admin and the supplier portal both use the operations shell; the light sidebar follows the reference rather than the AussieMed navy, chosen so the data on screen is what stands out. The supplier rail lists only the one screen that exists, because an entry leading to an unbuilt page is worse than no entry â€” the rest is BE-21.</t>
-  </si>
-  <si>
-    <t>DEC-21</t>
-  </si>
-  <si>
-    <t>Uploaded files go through a storage seam, not straight to disk</t>
-  </si>
-  <si>
-    <t>Local disk is right for a laptop and wrong for most hosting: a container filesystem is discarded on every deploy, and two instances behind a load balancer do not share one. Hosting is IN-01 and is not chosen yet.</t>
-  </si>
-  <si>
-    <t>Our decision, 16 Aug 2026, taken while building BE-29. Everything touching a filesystem is confined to src/lib/storage.ts behind a driver interface; local disk is the only driver today and STORAGE_DRIVER selects it. Adding S3, R2 or Blob storage means writing one more driver and changing an environment variable, with no calling code touched. What counts as an acceptable image is decided separately in image-file.ts, which is pure and unit tested, so a second driver cannot accept what this one refuses.</t>
-  </si>
-  <si>
-    <t>DA-09</t>
-  </si>
-  <si>
-    <t>Explain the disappearing product</t>
-  </si>
-  <si>
-    <t>Product 180 (Vaseline) was on the storefront listing at 12:45 UTC and gone by 13:05 the same day, while its detail page still loaded.</t>
-  </si>
-  <si>
-    <t>Deferred 15 Aug 2026. The product in question was one of the 11 removed under DA-23 and nothing is being migrated from the old platform, so this no longer affects the build. Worth revisiting only if data from the old system is ever imported.</t>
-  </si>
-  <si>
-    <t>DF-01</t>
-  </si>
-  <si>
-    <t>Industry taxonomy</t>
-  </si>
-  <si>
-    <t>A second navigation tree by customer type (Healthcare, Dental, Laboratory, Education, Hospitality, Beauty, First Aid, Facilities) alongside product categories.</t>
-  </si>
-  <si>
-    <t>Additive; adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-02</t>
-  </si>
-  <si>
-    <t>Subscribe and Save</t>
-  </si>
-  <si>
-    <t>Recurring scheduled orders. Pairs naturally with the reorder-first account.</t>
-  </si>
-  <si>
-    <t>Needs the backend.</t>
-  </si>
-  <si>
-    <t>DF-03</t>
-  </si>
-  <si>
-    <t>Frequently bought together</t>
-  </si>
-  <si>
-    <t>Bundle suggestion with a combined total and one action to add all.</t>
-  </si>
-  <si>
-    <t>Adopted from Livingstone.</t>
-  </si>
-  <si>
-    <t>DF-04</t>
-  </si>
-  <si>
-    <t>Quick view</t>
-  </si>
-  <si>
-    <t>View a product from the listing without a page load.</t>
-  </si>
-  <si>
-    <t>DF-05</t>
-  </si>
-  <si>
-    <t>Downloadable PDF catalogues</t>
-  </si>
-  <si>
-    <t>Still how a lot of trade buying happens.</t>
-  </si>
-  <si>
-    <t>Needs the actual catalogue files.</t>
-  </si>
-  <si>
-    <t>BE-02</t>
-  </si>
-  <si>
-    <t>Build the admin panel</t>
-  </si>
-  <si>
-    <t>Products, categories, suppliers, customers, orders, marketing, reports, settings.</t>
-  </si>
-  <si>
-    <t>Done 16 Aug 2026 by BE-20. Marketing (wishlists, abandoned carts) and reports are not built â€” BE-27 and BE-28.</t>
-  </si>
-  <si>
-    <t>BE-07</t>
-  </si>
-  <si>
-    <t>Seed the database from the catalogue</t>
-  </si>
-  <si>
-    <t>Done. 146 categories, 71 products, 94 SKUs, 173 price tiers and 4 suppliers loaded from src/data/catalog.json.</t>
-  </si>
-  <si>
-    <t>npm run db:seed is idempotent; npm run db:check verifies the database against the JSON including exact money round-trips.</t>
-  </si>
-  <si>
-    <t>BE-09</t>
-  </si>
-  <si>
-    <t>Point the storefront at the database</t>
-  </si>
-  <si>
-    <t>Done. Every page and API route reads Prisma. Client components read a snapshot over HTTP because a browser cannot query the database.</t>
-  </si>
-  <si>
-    <t>query.ts was untouched â€” it never knew where products came from.</t>
-  </si>
-  <si>
-    <t>BE-11</t>
-  </si>
-  <si>
-    <t>Order pages restricted to their owner</t>
-  </si>
-  <si>
-    <t>An order was readable by anyone who guessed a sequential reference. Now an admin sees any order, the account that placed it sees it, and a guest sees only an order placed from their own cart.</t>
-  </si>
-  <si>
-    <t>A forbidden order returns 404 rather than 403, so the response cannot be used to discover which references exist.</t>
-  </si>
-  <si>
-    <t>BE-20</t>
-  </si>
-  <si>
-    <t>Build the admin screens behind the dashboard</t>
-  </si>
-  <si>
-    <t>/admin authenticates and shows live figures, but every management screen is still missing: products, categories, suppliers, customers, orders, bulk upload, marketing, reports, settings.</t>
-  </si>
-  <si>
-    <t>Built 16 Aug 2026. Dashboard, products (list, filters, edit, SKUs, price breaks, approval), categories, suppliers, orders, customers, settings and an audit trail. Every write goes through src/lib/admin.ts, which checks the role again in the service layer, records the change, and bumps the catalogue version so the storefront updates without a restart. Bulk upload is BE-04; product image upload is still missing â€” see BE-29.</t>
-  </si>
-  <si>
-    <t>BE-25</t>
-  </si>
-  <si>
-    <t>Invalidate the catalogue cache after a seed or an edit</t>
-  </si>
-  <si>
-    <t>The data layer caches the catalogue for the life of the process, so a running server keeps serving whatever it read first. This is not theoretical: on 15 Aug 2026 the dev server was still showing a retired carton SKU as a purchasable unit chip on the product page, hours after the database had deactivated it.</t>
-  </si>
-  <si>
-    <t>Fixed 15 Aug 2026. The cache now carries the catalogVersion stamp it was built from and re-checks it against the database at most once a second; the seed bumps the stamp, and invalidateCatalog() bumps it too so other server processes drop their copy as well. Verified live: a running dev server went from 71 products to 60 without a restart, and the phantom carton chip disappeared.</t>
-  </si>
-  <si>
-    <t>BE-29</t>
-  </si>
-  <si>
-    <t>Product images cannot be uploaded</t>
-  </si>
-  <si>
-    <t>The admin product screen listed the image files a product references but could not add or replace one, so the only way to give a product a photograph was to put a file on disk and re-seed. That blocked DA-03 and DA-24 from ever being closed by the client rather than by us.</t>
-  </si>
-  <si>
-    <t>Built 16 Aug 2026. Upload, alt text, choose which image the catalogue shows, and remove — on the product screen, through src/lib/admin.ts like every other write, so it is admin-checked, audited and bumps the catalogue version. Files go through the src/lib/storage.ts seam; see DEC-21. Images are accepted on their leading bytes rather than their filename, which turns the DA-25 defect into a refusal at upload time instead of a 400 from the image optimiser at request time. 15 unit tests cover the checks and the key generation. Verified end to end in a browser: a renamed SVG is refused, a real PNG is stored, served and reaches the storefront with no restart, promotion leaves a dense order, removal deletes both the row and the file, and all five actions appear in the audit trail.</t>
-  </si>
-  <si>
-    <t>DN-01</t>
-  </si>
-  <si>
-    <t>Currency rendering</t>
-  </si>
-  <si>
-    <t>Was rendering the Arabic symbol and 4 decimals. Now always the English string AED with exactly 2 decimals, enforced by test and by a grep check.</t>
-  </si>
-  <si>
-    <t>Fixed in the initial build.</t>
-  </si>
-  <si>
-    <t>DN-02</t>
-  </si>
-  <si>
-    <t>Integer quantities</t>
-  </si>
-  <si>
-    <t>Quantities were rendering as decimals such as 3.00.</t>
-  </si>
-  <si>
-    <t>DN-03</t>
-  </si>
-  <si>
-    <t>Category filtering</t>
-  </si>
-  <si>
-    <t>Every category link redirected to the full product list. Filtering now works, including rolling a department up to everything beneath it.</t>
-  </si>
-  <si>
-    <t>DN-04</t>
-  </si>
-  <si>
-    <t>Category counts matching results</t>
-  </si>
-  <si>
-    <t>Admin and storefront counts could diverge. Counts are now derived from the same query that lists the products.</t>
-  </si>
-  <si>
-    <t>Asserted in the data checks and the API contract checks.</t>
-  </si>
-  <si>
-    <t>DN-05</t>
-  </si>
-  <si>
-    <t>Category slug collisions</t>
-  </si>
-  <si>
-    <t>Six categories shared a slug with another category, so one was unreachable and the other answered to the wrong name.</t>
-  </si>
-  <si>
-    <t>Found by the API contract check. Slugs are now unique tree-wide and asserted.</t>
-  </si>
-  <si>
-    <t>DN-06</t>
-  </si>
-  <si>
-    <t>Per-supplier invoicing</t>
-  </si>
-  <si>
-    <t>An order spanning N suppliers now produces exactly N invoices under one reference number, with per-invoice VAT summing to the order VAT without drift.</t>
-  </si>
-  <si>
-    <t>Verified end to end in the browser and by test.</t>
-  </si>
-  <si>
-    <t>DN-11</t>
-  </si>
-  <si>
-    <t>Pack and unit of measure model</t>
-  </si>
-  <si>
-    <t>The same line sells by the box and by the carton at different prices. Cart lines are keyed by product and pack so they never merge.</t>
-  </si>
-  <si>
-    <t>Outers are asserted to beat buying their contents separately.</t>
-  </si>
-  <si>
-    <t>DN-14</t>
-  </si>
-  <si>
-    <t>Control characters in generated code</t>
-  </si>
-  <si>
-    <t>Shell escaping wrote literal backspace bytes into regex rules, so every packaging and variant rule silently matched nothing while looking correct in every editor.</t>
-  </si>
-  <si>
-    <t>Found via od. A data check now asserts each variant selection matches an option.</t>
-  </si>
-  <si>
-    <t>DN-16</t>
-  </si>
-  <si>
-    <t>Database schema designed and migrated</t>
-  </si>
-  <si>
-    <t>Thirty tables covering catalogue, packs as SKUs, variants, attributes, documents, batches, orders, per-supplier invoices, quotes, bulk upload and audit.</t>
-  </si>
-  <si>
-    <t>The UNIQUE(orderId supplierId) constraint was verified by attempting a duplicate invoice: the database rejected it.</t>
-  </si>
-  <si>
-    <t>DN-17</t>
-  </si>
-  <si>
-    <t>Typecheck was silently passing on a stale cache</t>
-  </si>
-  <si>
-    <t>tsc ran with incremental caching and reported no errors while real type errors existed in the tree. Every earlier typecheck-clean claim was suspect.</t>
-  </si>
-  <si>
-    <t>npm run typecheck now runs with --incremental false. Caught seven genuine errors the moment it was disabled.</t>
-  </si>
-  <si>
-    <t>DN-18</t>
-  </si>
-  <si>
-    <t>Cart moved to the server</t>
-  </si>
-  <si>
-    <t>The cart was localStorage, so the browser held prices. It is now database rows priced entirely on the server; the client cannot tell the server what anything costs.</t>
-  </si>
-  <si>
-    <t>Guest carts are cookie-keyed. The catalogue snapshot endpoint stays until the wishlist and quote cart follow.</t>
-  </si>
-  <si>
-    <t>DN-19</t>
-  </si>
-  <si>
-    <t>Checkout writes real orders</t>
-  </si>
-  <si>
-    <t>One transaction creates the order, one invoice per supplier and every line, or nothing at all. Reference numbers are allocated server-side inside that transaction.</t>
-  </si>
-  <si>
-    <t>Verified in a browser end to end, and by 14 order invariants in npm run db:check.</t>
-  </si>
-  <si>
-    <t>DN-20</t>
-  </si>
-  <si>
-    <t>Four sign-in accounts seeded</t>
-  </si>
-  <si>
-    <t>admin, musawi1989@gmail.com, supplier1 and supplier2, each able to sign in by username or email. Suppliers are attached to their seeded companies.</t>
-  </si>
-  <si>
-    <t>Seeded separately from the catalogue so re-seeding products does not remove accounts.</t>
-  </si>
-  <si>
-    <t>FN-01</t>
-  </si>
-  <si>
-    <t>Checkout does not submit an order</t>
-  </si>
-  <si>
-    <t>Done. Checkout writes a real order in one transaction, with one invoice per supplier and a server-allocated reference number.</t>
-  </si>
-  <si>
-    <t>Payment is still not taken and no email is sent.</t>
-  </si>
-  <si>
-    <t>FN-05</t>
-  </si>
-  <si>
-    <t>Real sign-in replaced the demo flag</t>
-  </si>
-  <si>
-    <t>Sign-in was a localStorage boolean anyone could set. It is now a database-backed session with a scrypt-hashed password.</t>
-  </si>
-  <si>
-    <t>Sessions are rows; signing out deletes the row, so a copied cookie stops working.</t>
-  </si>
-  <si>
-    <t>FN-06</t>
-  </si>
-  <si>
-    <t>Account history is real</t>
-  </si>
-  <si>
-    <t>The account area showed three fabricated orders. It now reads the signed-in user's actual orders, and reorder-first is built from what they have really bought.</t>
-  </si>
-  <si>
-    <t>Says so plainly when there is no history yet, rather than showing an empty grid.</t>
-  </si>
-  <si>
-    <t>BE-06</t>
-  </si>
-  <si>
-    <t>Add an audit log</t>
-  </si>
-  <si>
-    <t>Every status transition and every admin or supplier write should be recorded.</t>
-  </si>
-  <si>
-    <t>Done 16 Aug 2026. AuditLog now records every admin write with the actor, the entity and the values that changed, readable at /admin/audit and filtered per record from each product's page. Entries are never edited or deleted, so the screen has no actions on it. Supplier portal writes join it when BE-21 lands.</t>
-  </si>
-  <si>
-    <t>DA-23</t>
-  </si>
-  <si>
-    <t>Two suppliers were asked for; four exist</t>
-  </si>
-  <si>
-    <t>The brief was Chemist Warehouse and Livingstone for testing, with the products that made no sense removed. Northline Uniforms and AussieMed Distribution survived that clean-up and still own 11 of the 71 products between them, so a third of the supplier list and a seventh of the catalogue is left over from the old extraction.</t>
-  </si>
-  <si>
-    <t>Done 15 Aug 2026. The 11 extraction products and suppliers 20 and 21 are no longer emitted by scripts/build-catalog.mjs. The database keeps them as Inactive rather than deleting them, because 2 invoices and 3 order lines still name them â€” order history survives. The catalogue is now exactly the 60 test products, 30 from each supplier.</t>
-  </si>
-  <si>
-    <t>DN-07</t>
-  </si>
-  <si>
-    <t>Unique page titles and meta descriptions</t>
-  </si>
-  <si>
-    <t>Every page carried the identical title 'Aussie Med || Home' with an empty description.</t>
-  </si>
-  <si>
-    <t>Built per page and per product.</t>
-  </si>
-  <si>
-    <t>DN-08</t>
-  </si>
-  <si>
-    <t>Broken cart images and unresolved asset paths</t>
-  </si>
-  <si>
-    <t>Cart images had a bare domain with no path; templates contained literal '~/' paths.</t>
-  </si>
-  <si>
-    <t>All image paths are local and asserted.</t>
-  </si>
-  <si>
-    <t>DN-09</t>
-  </si>
-  <si>
-    <t>Volume breaks visible while scanning</t>
-  </si>
-  <si>
-    <t>Only a savings badge was shown. The full break table now appears on every product card using +1/+10/+50 notation.</t>
-  </si>
-  <si>
-    <t>DN-10</t>
-  </si>
-  <si>
-    <t>Ex VAT / Inc VAT toggle</t>
-  </si>
-  <si>
-    <t>Procurement compares ex-tax and the approver reads inc-tax, so the same buyer needs both during one order.</t>
-  </si>
-  <si>
-    <t>Persists per browser.</t>
-  </si>
-  <si>
-    <t>DN-12</t>
-  </si>
-  <si>
-    <t>Adopt the existing brand theme</t>
-  </si>
-  <si>
-    <t>Navy #29387d, red #ea2227 and Gilroy, read from the live site's computed styles rather than eyeballed.</t>
-  </si>
-  <si>
-    <t>Logo, favicon and all 11 category images are the brand own.</t>
-  </si>
-  <si>
-    <t>DN-13</t>
-  </si>
-  <si>
-    <t>Catalogue seeded with real products</t>
-  </si>
-  <si>
-    <t>Sixty real items replaced invented placeholders so the storefront can be judged against products that actually exist.</t>
-  </si>
-  <si>
-    <t>Thirty from each of two public supplier catalogues, spanning 23 categories.</t>
-  </si>
-  <si>
-    <t>DN-15</t>
-  </si>
-  <si>
-    <t>Product images added for testing</t>
-  </si>
-  <si>
-    <t>Fifty-two of 71 products now carry real photography so the layout can be judged with images rather than placeholder tiles.</t>
-  </si>
-  <si>
-    <t>Third-party supplier images in public/products/seed. A data check now asserts every referenced image file exists on disk.</t>
-  </si>
-  <si>
-    <t>DN-21</t>
-  </si>
-  <si>
-    <t>Three sign-in doors, one per role</t>
-  </si>
-  <si>
-    <t>Buyers sign in at the account page, suppliers at the business portal, admins at /admin. Signing in at the wrong door names the right one instead of letting someone into the wrong area.</t>
-  </si>
-  <si>
-    <t>Verified: each role accepted at its own door and rejected with 403 at the other two.</t>
+    <t>Decided with the client 16 Aug 2026. VAT is calculated at checkout and shown on the invoice only. Product pages and listings show trade prices with no VAT arithmetic anywhere. This confirms DEC-13 rather than reversing it: no inc-VAT view is wanted, so there is nothing to build.</t>
   </si>
   <si>
     <t>FE-33</t>
@@ -2500,7 +2539,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2508,7 +2547,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2516,7 +2555,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2524,7 +2563,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2550,7 +2589,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2558,7 +2597,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2584,7 +2623,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="3">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2642,7 +2681,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2650,7 +2689,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2658,7 +2697,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2666,7 +2705,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -2724,7 +2763,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2802,7 +2841,7 @@
         <v>44</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>39</v>
@@ -2828,7 +2867,7 @@
         <v>48</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>39</v>
@@ -2845,7 +2884,7 @@
         <v>50</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>51</v>
@@ -2853,31 +2892,31 @@
       <c r="D5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>14</v>
+      <c r="E5" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>39</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
@@ -2886,7 +2925,7 @@
         <v>39</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>58</v>
@@ -2912,7 +2951,7 @@
         <v>39</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>62</v>
@@ -2949,7 +2988,7 @@
         <v>67</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>68</v>
@@ -2957,8 +2996,8 @@
       <c r="D9" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>16</v>
+      <c r="E9" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>39</v>
@@ -3079,7 +3118,7 @@
         <v>87</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>88</v>
@@ -3087,8 +3126,8 @@
       <c r="D14" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>13</v>
+      <c r="E14" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>39</v>
@@ -3111,7 +3150,7 @@
         <v>92</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
@@ -3123,21 +3162,21 @@
         <v>40</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
@@ -3149,7 +3188,7 @@
         <v>40</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3157,7 +3196,7 @@
         <v>97</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>98</v>
@@ -3183,7 +3222,7 @@
         <v>101</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>102</v>
@@ -3191,8 +3230,8 @@
       <c r="D18" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>16</v>
+      <c r="E18" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>39</v>
@@ -3209,7 +3248,7 @@
         <v>105</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>106</v>
@@ -3235,7 +3274,7 @@
         <v>109</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>110</v>
@@ -3261,7 +3300,7 @@
         <v>113</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>114</v>
@@ -3270,1030 +3309,1030 @@
         <v>115</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>39</v>
+        <v>14</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>39</v>
-      </c>
       <c r="G22" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>39</v>
+      <c r="F23" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>14</v>
+        <v>148</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>13</v>
+        <v>152</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>16</v>
+        <v>156</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>14</v>
+        <v>164</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>16</v>
+        <v>168</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>16</v>
+        <v>172</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>13</v>
+        <v>188</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>16</v>
+        <v>200</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>13</v>
+        <v>212</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>15</v>
+        <v>216</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>13</v>
+        <v>232</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>16</v>
+        <v>236</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>13</v>
+        <v>248</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>16</v>
+        <v>256</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>13</v>
+        <v>264</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>16</v>
+        <v>268</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>272</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4313,7 +4352,7 @@
         <v>13</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>40</v>
@@ -4335,11 +4374,11 @@
       <c r="D62" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>16</v>
+      <c r="E62" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>40</v>
@@ -4353,7 +4392,7 @@
         <v>280</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>281</v>
@@ -4361,11 +4400,11 @@
       <c r="D63" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="E63" s="7" t="s">
-        <v>13</v>
+      <c r="E63" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>40</v>
@@ -4379,7 +4418,7 @@
         <v>284</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>285</v>
@@ -4391,7 +4430,7 @@
         <v>13</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>40</v>
@@ -4405,7 +4444,7 @@
         <v>287</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>288</v>
@@ -4414,10 +4453,10 @@
         <v>289</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>40</v>
@@ -4431,7 +4470,7 @@
         <v>291</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>292</v>
@@ -4443,403 +4482,403 @@
         <v>13</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>2</v>
+        <v>294</v>
       </c>
     </row>
     <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>127</v>
+        <v>297</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>298</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="68" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F68" s="9" t="s">
-        <v>127</v>
+      <c r="F68" s="10" t="s">
+        <v>298</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>14</v>
+        <v>306</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="70" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="71" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="72" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>13</v>
+        <v>318</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="73" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="74" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="76" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>16</v>
+        <v>338</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>16</v>
+        <v>342</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="80" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>13</v>
+        <v>350</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="81" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>354</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4847,7 +4886,7 @@
         <v>355</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>356</v>
@@ -4855,11 +4894,11 @@
       <c r="D82" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="E82" s="6" t="s">
-        <v>16</v>
+      <c r="E82" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G82" s="6" t="s">
         <v>40</v>
@@ -4881,125 +4920,73 @@
       <c r="D83" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="E83" s="7" t="s">
-        <v>13</v>
+      <c r="E83" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G83" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>2</v>
+        <v>362</v>
       </c>
     </row>
     <row r="84" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E84" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G84" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="85" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>16</v>
+        <v>369</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G85" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="B86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F86" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>377</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H87"/>
+  <autoFilter ref="A1:H85"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5010,7 +4997,7 @@
   <sheetPr>
     <tabColor rgb="FF29387D"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -5050,552 +5037,604 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="B24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="H22" s="6" t="s">
+      <c r="D24" s="6" t="s">
         <v>462</v>
       </c>
+      <c r="E24" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>463</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H22"/>
+  <autoFilter ref="A1:H24"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5646,126 +5685,126 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
@@ -5776,28 +5815,28 @@
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -5812,7 +5851,7 @@
   <sheetPr>
     <tabColor rgb="FF146C43"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -5852,16 +5891,16 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>16</v>
@@ -5870,24 +5909,24 @@
         <v>39</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
@@ -5896,24 +5935,24 @@
         <v>39</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
@@ -5922,24 +5961,24 @@
         <v>39</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
@@ -5948,24 +5987,24 @@
         <v>39</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
@@ -5974,24 +6013,24 @@
         <v>39</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
@@ -6000,24 +6039,24 @@
         <v>39</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>16</v>
@@ -6026,24 +6065,24 @@
         <v>39</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>16</v>
@@ -6052,24 +6091,24 @@
         <v>39</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
@@ -6078,24 +6117,24 @@
         <v>39</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
@@ -6104,24 +6143,24 @@
         <v>39</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>16</v>
@@ -6130,24 +6169,24 @@
         <v>39</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>16</v>
@@ -6156,24 +6195,24 @@
         <v>39</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>16</v>
@@ -6182,24 +6221,24 @@
         <v>39</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
@@ -6208,24 +6247,24 @@
         <v>39</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
@@ -6234,24 +6273,24 @@
         <v>39</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
@@ -6260,24 +6299,24 @@
         <v>39</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
@@ -6286,24 +6325,24 @@
         <v>39</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
@@ -6312,24 +6351,24 @@
         <v>39</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>16</v>
@@ -6338,24 +6377,24 @@
         <v>39</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>16</v>
@@ -6364,24 +6403,24 @@
         <v>39</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>16</v>
@@ -6390,24 +6429,24 @@
         <v>39</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>16</v>
@@ -6416,24 +6455,24 @@
         <v>39</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>16</v>
@@ -6442,560 +6481,638 @@
         <v>39</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>578</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>127</v>
+        <v>579</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F26" s="9" t="s">
-        <v>127</v>
+      <c r="F26" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>381</v>
+        <v>22</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>381</v>
+        <v>19</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>16</v>
+        <v>591</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>478</v>
+        <v>596</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>602</v>
+        <v>479</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>26</v>
+        <v>374</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>26</v>
+        <v>374</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F40" s="10" t="s">
-        <v>305</v>
+      <c r="F40" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>641</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>305</v>
+        <v>642</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>645</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>305</v>
+        <v>646</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>16</v>
+        <v>654</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B45" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>656</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>657</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="G45" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>658</v>
+      <c r="C48" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>670</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>671</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H45"/>
+  <autoFilter ref="A1:H48"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="704">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -218,6 +218,54 @@
     <t>From docs/DASHBOARD_METRICS_SPEC.md sections 1.1 and 5.3. Cheap now, impossible to backfill, and it must be in place before the first real order or the first months of trading are unmeasurable. OrderSupplierInvoice is already the sub-order and already has status, so this is timestamp columns plus a log table, not a new entity. AuditLog is close but generic and admin-scoped; a typed log keyed to the sub-order is what the metrics need. Pairs naturally with BE-21, which builds the screens that would set these.</t>
   </si>
   <si>
+    <t>BE-35</t>
+  </si>
+  <si>
+    <t>Products are hard-tied to one supplier</t>
+  </si>
+  <si>
+    <t>ProductMaster.supplierId is a required field, so every product belongs to exactly one supplier and cannot have a backup. It also means supplier identity is carried on the product record itself, which is how it leaks to customers.</t>
+  </si>
+  <si>
+    <t>From DEC-24 and DEC-25. Replace with a ProductSupply relation joining SKU to supplier with a rank of Primary or Backup, plus that supplier's cost, their own part number, their lead time and an availability flag. Build additively first — create the table and backfill each existing supplierId as the primary supply — so nothing breaks while the purchase order flow is built on top; remove ProductMaster.supplierId only once nothing reads it. Note this supersedes part of BE-34: cost belongs on the supply relationship, not the SKU, because two suppliers means two costs.</t>
+  </si>
+  <si>
+    <t>BE-36</t>
+  </si>
+  <si>
+    <t>No purchase orders exist</t>
+  </si>
+  <si>
+    <t>Nothing buys anything. Customer orders are recorded but there is no mechanism to order the goods from a supplier, which is the entire middle of the business.</t>
+  </si>
+  <si>
+    <t>From DEC-26. PurchaseOrder and PurchaseOrderLine, built at the cutoff by grouping unpurchased order lines by chosen supplier and summing quantity per SKU. Draft, review, send, acknowledge, receive. The document must carry no customer name, address or order reference of any kind — that is the whole point, and it should be an acceptance test rather than an assumption. Re-raising declined lines to the backup supplier after a purchase order has already been sent is part of this, not a later refinement, since in cross-dock a supplier declining means a customer waits.</t>
+  </si>
+  <si>
+    <t>BE-37</t>
+  </si>
+  <si>
+    <t>Nothing links received goods back to the customers waiting for them</t>
+  </si>
+  <si>
+    <t>Goods arrive pooled by item, not by customer. Without an allocation record there is no way to know whose units arrived, and no way to answer a recall.</t>
+  </si>
+  <si>
+    <t>From DEC-24. A PurchaseAllocation joining a received purchase order line to a customer order line with a quantity, and carrying the batch code and expiry recorded at goods-in. This is the keystone of the whole model: it is what lets a recalled batch be traced to the exact clinics that received it while keeping the supplier on the far side of the wall, and what makes partial receipts and shortages expressible. The per-line fulfilment statuses already built map onto it directly — Allocated stops meaning reserved and starts meaning physically received and assigned.</t>
+  </si>
+  <si>
+    <t>BE-38</t>
+  </si>
+  <si>
+    <t>Supplier identity is exposed to customers today</t>
+  </si>
+  <si>
+    <t>DEC-24 requires that customers never learn who supplied their goods. Three routes currently break that, and one of them ships supplier records to every visitor's browser.</t>
+  </si>
+  <si>
+    <t>supplierId travels into src/data/catalog.json, which is handed to the browser-side catalogue provider on every storefront page; there is a public /api/v1/suppliers endpoint; and supplier company names appear on customer-facing order views. All three must go, along with any supplier facet or filter in query.ts. Treat as a security item as much as a feature: verify by fetching the storefront and the public API as an anonymous visitor and asserting that no supplier name or id appears in either payload.</t>
+  </si>
+  <si>
     <t>DA-01</t>
   </si>
   <si>
@@ -356,6 +404,18 @@
     <t>Decided with the client 16 Aug 2026. Plan agreed: the supplier test accounts are deleted and real passwords forced on the admin and owner accounts as part of the deploy, not before, since they are needed while building. The on-screen credentials panel already renders only outside production, so a production build cannot leak it.</t>
   </si>
   <si>
+    <t>SEC-05</t>
+  </si>
+  <si>
+    <t>Customer identity must never reach a supplier</t>
+  </si>
+  <si>
+    <t>The mirror of BE-38 and equally load-bearing. A supplier seeing which clinics buy what would hand them the client book.</t>
+  </si>
+  <si>
+    <t>From DEC-24. Purchase orders, the supplier portal and any supplier-facing document or email must contain no customer name, address, order reference or count of customers. This is a scoping rule to test rather than trust — the register already notes under BE-24 that supplier permission bypass has been a recurring bug class. Note the metrics document's supplier-portal ideas assume suppliers see customer orders, which is now wrong; supplier performance is measured against purchase orders instead.</t>
+  </si>
+  <si>
     <t>AC-02</t>
   </si>
   <si>
@@ -1407,6 +1467,42 @@
   </si>
   <si>
     <t>Decided with the client 16 Aug 2026. VAT is calculated at checkout and shown on the invoice. It appears nowhere on product pages or listings, which show trade prices only. Consistent with DEC-13. Product tax class still matters, because it decides what checkout charges, but it is never surfaced before then. Closes FE-30.</t>
+  </si>
+  <si>
+    <t>DEC-24</t>
+  </si>
+  <si>
+    <t>AussieMed is a cross-dock distributor, not a marketplace</t>
+  </si>
+  <si>
+    <t>Changes what the platform fundamentally is. Neither side of a transaction may see the other, which rules out the supplier-facing order model the build had grown.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. AussieMed buys from suppliers and resells; the customer never learns who supplied their goods and the supplier never learns who bought them. Nothing is purchased until a customer has ordered it — the sorting facility is a transit point, never a warehouse, so there is no inventory to hold or reconcile. Goods arrive against a purchase order, are broken down and sorted by customer, then despatched by AussieMed. Depends on DEC-22, which was decided an hour earlier and turns out to be a prerequisite rather than a coincidence.</t>
+  </si>
+  <si>
+    <t>DEC-25</t>
+  </si>
+  <si>
+    <t>Two suppliers per item, with automatic fallback</t>
+  </si>
+  <si>
+    <t>A single supplier per product makes every product only as reliable as one company, and in cross-dock a supplier who cannot supply means a customer waits a full cycle.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. Each item carries a primary and a backup supplier, each with their own cost, lead time and part number. Purchase order lines default to the primary and revert to the backup automatically when either the supplier is marked unavailable wholesale or that supplier cannot supply that particular item — two distinct flags, because they are different situations. Any line can still be moved by hand before sending. When both suppliers are unavailable the line cannot be sourced and must surface in an exception queue rather than fall silently off the purchase order, because a customer is waiting on each one.</t>
+  </si>
+  <si>
+    <t>DEC-26</t>
+  </si>
+  <si>
+    <t>One consolidated purchase order per supplier per day</t>
+  </si>
+  <si>
+    <t>Sending a purchase order per customer order would flood suppliers and lose the buying power of pooled quantities.</t>
+  </si>
+  <si>
+    <t>Decided with the client 16 Aug 2026. Customer orders accumulate through the day; at a configurable cutoff, 5pm Asia/Dubai by default, the system groups every unpurchased line by supplier and sums quantities per item into one purchase order. Anything ordered after the cutoff rolls into the next day. Drafts are prepared for review and sent by hand, with an auto-send toggle in Settings and reachable from the orders section, defaulting to off — nothing commits money to a supplier until a person turns that on deliberately. Purchase order lines lead with the supplier's own part number, with the AussieMed SKU and product name alongside as reference.</t>
   </si>
   <si>
     <t>DA-09</t>
@@ -2539,7 +2635,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2547,7 +2643,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2555,7 +2651,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2563,7 +2659,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2589,7 +2685,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2647,7 +2743,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="3">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2697,7 +2793,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="3">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2721,7 +2817,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2763,7 +2859,7 @@
   <sheetPr>
     <tabColor rgb="FFEA2227"/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2988,7 +3084,7 @@
         <v>67</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>68</v>
@@ -2996,8 +3092,8 @@
       <c r="D9" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>13</v>
+      <c r="E9" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>39</v>
@@ -3014,7 +3110,7 @@
         <v>71</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>72</v>
@@ -3022,8 +3118,8 @@
       <c r="D10" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>13</v>
+      <c r="E10" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>39</v>
@@ -3040,7 +3136,7 @@
         <v>75</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>76</v>
@@ -3048,8 +3144,8 @@
       <c r="D11" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>13</v>
+      <c r="E11" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>39</v>
@@ -3066,7 +3162,7 @@
         <v>79</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>80</v>
@@ -3074,8 +3170,8 @@
       <c r="D12" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>13</v>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>39</v>
@@ -3118,7 +3214,7 @@
         <v>87</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>88</v>
@@ -3126,8 +3222,8 @@
       <c r="D14" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>16</v>
+      <c r="E14" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>39</v>
@@ -3144,16 +3240,16 @@
         <v>91</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>92</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>16</v>
+        <v>93</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>39</v>
@@ -3162,24 +3258,24 @@
         <v>40</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>16</v>
+        <v>97</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>39</v>
@@ -3188,24 +3284,24 @@
         <v>40</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>16</v>
+        <v>101</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>39</v>
@@ -3214,24 +3310,24 @@
         <v>40</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>13</v>
+        <v>105</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>39</v>
@@ -3240,24 +3336,24 @@
         <v>40</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>13</v>
+      <c r="E19" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>39</v>
@@ -3266,7 +3362,7 @@
         <v>40</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3274,7 +3370,7 @@
         <v>109</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>110</v>
@@ -3282,8 +3378,8 @@
       <c r="D20" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>13</v>
+      <c r="E20" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>39</v>
@@ -3300,7 +3396,7 @@
         <v>113</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>114</v>
@@ -3308,141 +3404,141 @@
       <c r="D21" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="9" t="s">
+      <c r="E21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="6" t="s">
+      <c r="D22" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="E22" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>116</v>
+      <c r="F23" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="6" t="s">
+      <c r="D24" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="E24" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="E25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>40</v>
@@ -3468,7 +3564,7 @@
         <v>14</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>40</v>
@@ -3494,7 +3590,7 @@
         <v>13</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>40</v>
@@ -3508,7 +3604,7 @@
         <v>146</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>147</v>
@@ -3516,11 +3612,11 @@
       <c r="D29" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>16</v>
+      <c r="E29" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>40</v>
@@ -3534,7 +3630,7 @@
         <v>150</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>151</v>
@@ -3542,11 +3638,11 @@
       <c r="D30" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>16</v>
+      <c r="E30" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>40</v>
@@ -3560,7 +3656,7 @@
         <v>154</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>155</v>
@@ -3572,7 +3668,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>40</v>
@@ -3586,7 +3682,7 @@
         <v>158</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>159</v>
@@ -3594,11 +3690,11 @@
       <c r="D32" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>16</v>
+      <c r="E32" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>40</v>
@@ -3612,7 +3708,7 @@
         <v>162</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>163</v>
@@ -3620,11 +3716,11 @@
       <c r="D33" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>16</v>
+      <c r="E33" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>40</v>
@@ -3646,11 +3742,11 @@
       <c r="D34" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>13</v>
+      <c r="E34" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>40</v>
@@ -3672,11 +3768,11 @@
       <c r="D35" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>13</v>
+      <c r="E35" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>40</v>
@@ -3699,10 +3795,10 @@
         <v>176</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>40</v>
@@ -3724,11 +3820,11 @@
       <c r="D37" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>13</v>
+      <c r="E37" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>40</v>
@@ -3754,7 +3850,7 @@
         <v>16</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>40</v>
@@ -3776,11 +3872,11 @@
       <c r="D39" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>16</v>
+      <c r="E39" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>40</v>
@@ -3802,11 +3898,11 @@
       <c r="D40" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>16</v>
+      <c r="E40" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>40</v>
@@ -3828,11 +3924,11 @@
       <c r="D41" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>16</v>
+      <c r="E41" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>40</v>
@@ -3846,7 +3942,7 @@
         <v>198</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>199</v>
@@ -3858,7 +3954,7 @@
         <v>13</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>40</v>
@@ -3872,7 +3968,7 @@
         <v>202</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>203</v>
@@ -3880,11 +3976,11 @@
       <c r="D43" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="E43" s="7" t="s">
-        <v>13</v>
+      <c r="E43" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>40</v>
@@ -3898,7 +3994,7 @@
         <v>206</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>207</v>
@@ -3906,11 +4002,11 @@
       <c r="D44" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="E44" s="7" t="s">
-        <v>13</v>
+      <c r="E44" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>40</v>
@@ -3924,7 +4020,7 @@
         <v>210</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>211</v>
@@ -3933,10 +4029,10 @@
         <v>212</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>40</v>
@@ -3950,7 +4046,7 @@
         <v>214</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>215</v>
@@ -3958,11 +4054,11 @@
       <c r="D46" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E46" s="7" t="s">
-        <v>13</v>
+      <c r="E46" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>40</v>
@@ -3988,7 +4084,7 @@
         <v>13</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>40</v>
@@ -4014,7 +4110,7 @@
         <v>13</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>40</v>
@@ -4040,7 +4136,7 @@
         <v>13</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>40</v>
@@ -4063,10 +4159,10 @@
         <v>232</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>40</v>
@@ -4092,7 +4188,7 @@
         <v>13</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>40</v>
@@ -4118,7 +4214,7 @@
         <v>13</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>40</v>
@@ -4144,7 +4240,7 @@
         <v>13</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>40</v>
@@ -4158,7 +4254,7 @@
         <v>246</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>247</v>
@@ -4166,11 +4262,11 @@
       <c r="D54" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>16</v>
+      <c r="E54" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>40</v>
@@ -4184,7 +4280,7 @@
         <v>250</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>251</v>
@@ -4196,7 +4292,7 @@
         <v>16</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>40</v>
@@ -4210,7 +4306,7 @@
         <v>254</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>255</v>
@@ -4222,7 +4318,7 @@
         <v>13</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>40</v>
@@ -4236,7 +4332,7 @@
         <v>258</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>259</v>
@@ -4244,11 +4340,11 @@
       <c r="D57" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>16</v>
+      <c r="E57" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>40</v>
@@ -4262,7 +4358,7 @@
         <v>262</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>263</v>
@@ -4270,11 +4366,11 @@
       <c r="D58" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="E58" s="6" t="s">
-        <v>16</v>
+      <c r="E58" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>40</v>
@@ -4288,7 +4384,7 @@
         <v>266</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>267</v>
@@ -4296,11 +4392,11 @@
       <c r="D59" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="E59" s="7" t="s">
-        <v>13</v>
+      <c r="E59" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>40</v>
@@ -4314,7 +4410,7 @@
         <v>270</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>271</v>
@@ -4326,195 +4422,195 @@
         <v>16</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>2</v>
+        <v>273</v>
       </c>
     </row>
     <row r="61" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>13</v>
+        <v>280</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>2</v>
+        <v>281</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>2</v>
+        <v>289</v>
       </c>
     </row>
     <row r="65" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>290</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F67" s="10" t="s">
-        <v>298</v>
+        <v>13</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>299</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -4522,7 +4618,7 @@
         <v>300</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>301</v>
@@ -4530,11 +4626,11 @@
       <c r="D68" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="E68" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>298</v>
+      <c r="E68" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>40</v>
@@ -4548,7 +4644,7 @@
         <v>304</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>305</v>
@@ -4556,89 +4652,89 @@
       <c r="D69" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>298</v>
+      <c r="E69" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>307</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="B70" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C70" s="6" t="s">
+      <c r="D70" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="E70" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>310</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="71" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="B71" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C71" s="6" t="s">
+      <c r="D71" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="E71" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H71" s="6" t="s">
         <v>314</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F71" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H71" s="6" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="72" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="B72" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C72" s="6" t="s">
+      <c r="D72" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="E72" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" s="10" t="s">
         <v>318</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F72" s="10" t="s">
-        <v>298</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>40</v>
@@ -4652,7 +4748,7 @@
         <v>320</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>321</v>
@@ -4660,11 +4756,11 @@
       <c r="D73" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>16</v>
+      <c r="E73" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>40</v>
@@ -4690,7 +4786,7 @@
         <v>16</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>40</v>
@@ -4712,11 +4808,11 @@
       <c r="D75" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>16</v>
+      <c r="E75" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>40</v>
@@ -4742,7 +4838,7 @@
         <v>16</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>40</v>
@@ -4756,7 +4852,7 @@
         <v>336</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>337</v>
@@ -4764,11 +4860,11 @@
       <c r="D77" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="E77" s="7" t="s">
-        <v>13</v>
+      <c r="E77" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>40</v>
@@ -4782,7 +4878,7 @@
         <v>340</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>341</v>
@@ -4790,11 +4886,11 @@
       <c r="D78" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="E78" s="7" t="s">
-        <v>13</v>
+      <c r="E78" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>40</v>
@@ -4808,7 +4904,7 @@
         <v>344</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>345</v>
@@ -4816,11 +4912,11 @@
       <c r="D79" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="E79" s="7" t="s">
-        <v>13</v>
+      <c r="E79" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>40</v>
@@ -4834,7 +4930,7 @@
         <v>348</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>349</v>
@@ -4846,7 +4942,7 @@
         <v>16</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>40</v>
@@ -4860,7 +4956,7 @@
         <v>352</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>353</v>
@@ -4868,125 +4964,255 @@
       <c r="D81" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="E81" s="7" t="s">
-        <v>13</v>
+      <c r="E81" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>2</v>
+        <v>355</v>
       </c>
     </row>
     <row r="82" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G82" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="83" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>16</v>
+        <v>362</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G83" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="84" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E84" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G84" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="85" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B85" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C85" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="E85" s="7" t="s">
+      <c r="C90" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="E90" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>370</v>
+      <c r="F90" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H85"/>
+  <autoFilter ref="A1:H90"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4997,7 +5223,7 @@
   <sheetPr>
     <tabColor rgb="FF29387D"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -5037,604 +5263,682 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>463</v>
+        <v>483</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>495</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H24"/>
+  <autoFilter ref="A1:H27"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5685,126 +5989,126 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>467</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>469</v>
+        <v>501</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>471</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>479</v>
+        <v>511</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
@@ -5815,28 +6119,28 @@
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>485</v>
+        <v>517</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>486</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -5891,16 +6195,16 @@
     </row>
     <row r="2" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>488</v>
+        <v>520</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>16</v>
@@ -5909,24 +6213,24 @@
         <v>39</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>490</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>491</v>
+        <v>523</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>492</v>
+        <v>524</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
@@ -5935,24 +6239,24 @@
         <v>39</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>16</v>
@@ -5961,24 +6265,24 @@
         <v>39</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>498</v>
+        <v>530</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
@@ -5987,24 +6291,24 @@
         <v>39</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>505</v>
+        <v>537</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
@@ -6013,24 +6317,24 @@
         <v>39</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>506</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>509</v>
+        <v>541</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>16</v>
@@ -6039,24 +6343,24 @@
         <v>39</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>510</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>16</v>
@@ -6065,24 +6369,24 @@
         <v>39</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>514</v>
+        <v>546</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>516</v>
+        <v>548</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>517</v>
+        <v>549</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>16</v>
@@ -6091,24 +6395,24 @@
         <v>39</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>520</v>
+        <v>552</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>521</v>
+        <v>553</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
@@ -6117,24 +6421,24 @@
         <v>39</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>522</v>
+        <v>554</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>523</v>
+        <v>555</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>524</v>
+        <v>556</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>16</v>
@@ -6143,24 +6447,24 @@
         <v>39</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>525</v>
+        <v>557</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>526</v>
+        <v>558</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>527</v>
+        <v>559</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>16</v>
@@ -6169,24 +6473,24 @@
         <v>39</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>529</v>
+        <v>561</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>530</v>
+        <v>562</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>531</v>
+        <v>563</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>16</v>
@@ -6195,24 +6499,24 @@
         <v>39</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>532</v>
+        <v>564</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>533</v>
+        <v>565</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>534</v>
+        <v>566</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>535</v>
+        <v>567</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>16</v>
@@ -6221,24 +6525,24 @@
         <v>39</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>536</v>
+        <v>568</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>537</v>
+        <v>569</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>538</v>
+        <v>570</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>539</v>
+        <v>571</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
@@ -6247,24 +6551,24 @@
         <v>39</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>540</v>
+        <v>572</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>541</v>
+        <v>573</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>542</v>
+        <v>574</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>543</v>
+        <v>575</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>16</v>
@@ -6273,24 +6577,24 @@
         <v>39</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>544</v>
+        <v>576</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>547</v>
+        <v>579</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
@@ -6299,24 +6603,24 @@
         <v>39</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>548</v>
+        <v>580</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>549</v>
+        <v>581</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>16</v>
@@ -6325,24 +6629,24 @@
         <v>39</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>552</v>
+        <v>584</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>554</v>
+        <v>586</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>555</v>
+        <v>587</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>16</v>
@@ -6351,24 +6655,24 @@
         <v>39</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>556</v>
+        <v>588</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>558</v>
+        <v>590</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>559</v>
+        <v>591</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>16</v>
@@ -6377,24 +6681,24 @@
         <v>39</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>560</v>
+        <v>592</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>561</v>
+        <v>593</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>562</v>
+        <v>594</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>563</v>
+        <v>595</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>16</v>
@@ -6403,24 +6707,24 @@
         <v>39</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>564</v>
+        <v>596</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>565</v>
+        <v>597</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>566</v>
+        <v>598</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>567</v>
+        <v>599</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>16</v>
@@ -6429,24 +6733,24 @@
         <v>39</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>568</v>
+        <v>600</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>569</v>
+        <v>601</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>570</v>
+        <v>602</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>571</v>
+        <v>603</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>16</v>
@@ -6455,24 +6759,24 @@
         <v>39</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>572</v>
+        <v>604</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>573</v>
+        <v>605</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>574</v>
+        <v>606</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>16</v>
@@ -6481,24 +6785,24 @@
         <v>39</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>576</v>
+        <v>608</v>
       </c>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>577</v>
+        <v>609</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>578</v>
+        <v>610</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>579</v>
+        <v>611</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>13</v>
@@ -6507,24 +6811,24 @@
         <v>39</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>580</v>
+        <v>612</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>581</v>
+        <v>613</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>582</v>
+        <v>614</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>583</v>
+        <v>615</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>13</v>
@@ -6533,582 +6837,582 @@
         <v>39</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>584</v>
+        <v>616</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>585</v>
+        <v>617</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>586</v>
+        <v>618</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>587</v>
+        <v>619</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>588</v>
+        <v>620</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>589</v>
+        <v>621</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>590</v>
+        <v>622</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>591</v>
+        <v>623</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>592</v>
+        <v>624</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>593</v>
+        <v>625</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>594</v>
+        <v>626</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>595</v>
+        <v>627</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>596</v>
+        <v>628</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>597</v>
+        <v>629</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>598</v>
+        <v>630</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>599</v>
+        <v>631</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>600</v>
+        <v>632</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>601</v>
+        <v>633</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>602</v>
+        <v>634</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>603</v>
+        <v>635</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>479</v>
+        <v>511</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>604</v>
+        <v>636</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>605</v>
+        <v>637</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>607</v>
+        <v>639</v>
       </c>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>608</v>
+        <v>640</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>609</v>
+        <v>641</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>610</v>
+        <v>642</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>611</v>
+        <v>643</v>
       </c>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>612</v>
+        <v>644</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>613</v>
+        <v>645</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>614</v>
+        <v>646</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>615</v>
+        <v>647</v>
       </c>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>616</v>
+        <v>648</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>617</v>
+        <v>649</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>618</v>
+        <v>650</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>619</v>
+        <v>651</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>620</v>
+        <v>652</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>621</v>
+        <v>653</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>622</v>
+        <v>654</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>623</v>
+        <v>655</v>
       </c>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>624</v>
+        <v>656</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>625</v>
+        <v>657</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>626</v>
+        <v>658</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>627</v>
+        <v>659</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>628</v>
+        <v>660</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>629</v>
+        <v>661</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>630</v>
+        <v>662</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>631</v>
+        <v>663</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>633</v>
+        <v>665</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>634</v>
+        <v>666</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>635</v>
+        <v>667</v>
       </c>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>636</v>
+        <v>668</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>637</v>
+        <v>669</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>638</v>
+        <v>670</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>639</v>
+        <v>671</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>640</v>
+        <v>672</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>641</v>
+        <v>673</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>642</v>
+        <v>674</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>643</v>
+        <v>675</v>
       </c>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>644</v>
+        <v>676</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>645</v>
+        <v>677</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>647</v>
+        <v>679</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>648</v>
+        <v>680</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>649</v>
+        <v>681</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>650</v>
+        <v>682</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>651</v>
+        <v>683</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>652</v>
+        <v>684</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>653</v>
+        <v>685</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>654</v>
+        <v>686</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>655</v>
+        <v>687</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>656</v>
+        <v>688</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>657</v>
+        <v>689</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>658</v>
+        <v>690</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>659</v>
+        <v>691</v>
       </c>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>660</v>
+        <v>692</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>662</v>
+        <v>694</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>663</v>
+        <v>695</v>
       </c>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>664</v>
+        <v>696</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>665</v>
+        <v>697</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>666</v>
+        <v>698</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>667</v>
+        <v>699</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>668</v>
+        <v>700</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>669</v>
+        <v>701</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>670</v>
+        <v>702</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>671</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Things That Need Attention.xlsx
+++ b/docs/Things That Need Attention.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="708">
   <si>
     <t>AussieMed — things that need attention</t>
   </si>
@@ -230,178 +230,1642 @@
     <t>From DEC-24 and DEC-25. Replace with a ProductSupply relation joining SKU to supplier with a rank of Primary or Backup, plus that supplier's cost, their own part number, their lead time and an availability flag. Build additively first — create the table and backfill each existing supplierId as the primary supply — so nothing breaks while the purchase order flow is built on top; remove ProductMaster.supplierId only once nothing reads it. Note this supersedes part of BE-34: cost belongs on the supply relationship, not the SKU, because two suppliers means two costs.</t>
   </si>
   <si>
+    <t>BE-37</t>
+  </si>
+  <si>
+    <t>Nothing links received goods back to the customers waiting for them</t>
+  </si>
+  <si>
+    <t>Goods arrive pooled by item, not by customer. Without an allocation record there is no way to know whose units arrived, and no way to answer a recall.</t>
+  </si>
+  <si>
+    <t>From DEC-24. A PurchaseAllocation joining a received purchase order line to a customer order line with a quantity, and carrying the batch code and expiry recorded at goods-in. This is the keystone of the whole model: it is what lets a recalled batch be traced to the exact clinics that received it while keeping the supplier on the far side of the wall, and what makes partial receipts and shortages expressible. The per-line fulfilment statuses already built map onto it directly — Allocated stops meaning reserved and starts meaning physically received and assigned.</t>
+  </si>
+  <si>
+    <t>BE-38</t>
+  </si>
+  <si>
+    <t>Supplier identity is exposed to customers today</t>
+  </si>
+  <si>
+    <t>DEC-24 requires that customers never learn who supplied their goods. Three routes currently break that, and one of them ships supplier records to every visitor's browser.</t>
+  </si>
+  <si>
+    <t>supplierId travels into src/data/catalog.json, which is handed to the browser-side catalogue provider on every storefront page; there is a public /api/v1/suppliers endpoint; and supplier company names appear on customer-facing order views. All three must go, along with any supplier facet or filter in query.ts. Treat as a security item as much as a feature: verify by fetching the storefront and the public API as an anonymous visitor and asserting that no supplier name or id appears in either payload.</t>
+  </si>
+  <si>
+    <t>BE-39</t>
+  </si>
+  <si>
+    <t>The supplier portal still shows customer orders</t>
+  </si>
+  <si>
+    <t>It lists order references and invoice lines drawn from customer orders, which contradicts DEC-24 now that suppliers deal only in purchase orders.</t>
+  </si>
+  <si>
+    <t>Split from BE-21 on 16 Aug 2026. The portal should show purchase orders and nothing e